--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ABC0967-C54E-429F-942B-AD2521819E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB81220E-E4C0-41D0-BCD9-639772D84880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5F7F8293-F828-4F69-82C7-C4FE5960B235}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84CE8CCA-E32B-455C-A40A-2FCB7EBF8490}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="113">
   <si>
     <t>종목코드</t>
   </si>
@@ -346,6 +346,12 @@
   </si>
   <si>
     <t>한국타이어앤테크놀로</t>
+  </si>
+  <si>
+    <t>175330</t>
+  </si>
+  <si>
+    <t>JB금융지주</t>
   </si>
   <si>
     <t>192080</t>
@@ -735,14 +741,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256801B4-D930-4D03-BF1E-267B69E10599}">
-  <dimension ref="A1:M51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C883D38-5ED9-40BA-8890-F9B467A3FC71}">
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -801,10 +807,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>30550</v>
+        <v>33050</v>
       </c>
       <c r="D2" s="3">
-        <v>1.6000000000000001E-3</v>
+        <v>-2.2200000000000001E-2</v>
       </c>
       <c r="E2">
         <v>8.2799999999999994</v>
@@ -819,19 +825,19 @@
         <v>48390.96</v>
       </c>
       <c r="I2">
-        <v>3.27</v>
+        <v>3.03</v>
       </c>
       <c r="J2">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K2">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="L2">
-        <v>110.95</v>
+        <v>114.71</v>
       </c>
       <c r="M2">
-        <v>13.99</v>
+        <v>8.36</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -842,10 +848,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>164100</v>
+        <v>174000</v>
       </c>
       <c r="D3" s="3">
-        <v>-1.32E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="E3">
         <v>19.09</v>
@@ -860,19 +866,19 @@
         <v>150938.41</v>
       </c>
       <c r="I3">
-        <v>3.96</v>
+        <v>3.74</v>
       </c>
       <c r="J3">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K3">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L3">
-        <v>103.71</v>
+        <v>109.33</v>
       </c>
       <c r="M3">
-        <v>8.0299999999999994</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -883,10 +889,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>559000</v>
+        <v>553000</v>
       </c>
       <c r="D4" s="3">
-        <v>-3.7900000000000003E-2</v>
+        <v>-2.12E-2</v>
       </c>
       <c r="E4">
         <v>13.09</v>
@@ -901,19 +907,19 @@
         <v>405451.96</v>
       </c>
       <c r="I4">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="J4">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L4">
-        <v>109.5</v>
+        <v>104.87</v>
       </c>
       <c r="M4">
-        <v>7.71</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -924,10 +930,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>45600</v>
+        <v>48450</v>
       </c>
       <c r="D5" s="3">
-        <v>1.2200000000000001E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="E5">
         <v>7.12</v>
@@ -942,19 +948,19 @@
         <v>72041.39</v>
       </c>
       <c r="I5">
-        <v>4.3899999999999997</v>
+        <v>4.13</v>
       </c>
       <c r="J5">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K5">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="L5">
-        <v>115.72</v>
+        <v>116.17</v>
       </c>
       <c r="M5">
-        <v>11.49</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -965,10 +971,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>77700</v>
+        <v>98400</v>
       </c>
       <c r="D6" s="3">
-        <v>3.8999999999999998E-3</v>
+        <v>-4.7399999999999998E-2</v>
       </c>
       <c r="E6">
         <v>4.05</v>
@@ -983,19 +989,19 @@
         <v>65679.45</v>
       </c>
       <c r="I6">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="J6">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K6">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="L6">
-        <v>110.74</v>
+        <v>128.66999999999999</v>
       </c>
       <c r="M6">
-        <v>11.48</v>
+        <v>27.13</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -1006,10 +1012,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>74100</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2.7000000000000001E-3</v>
+        <v>70500</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1.04</v>
@@ -1024,19 +1030,19 @@
         <v>53899.69</v>
       </c>
       <c r="I7">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="J7">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K7">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="L7">
-        <v>97.73</v>
+        <v>93.32</v>
       </c>
       <c r="M7">
-        <v>-11.58</v>
+        <v>-4.5999999999999996</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -1047,10 +1053,10 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>227500</v>
+        <v>237500</v>
       </c>
       <c r="D8" s="3">
-        <v>0.1721</v>
+        <v>-6.8599999999999994E-2</v>
       </c>
       <c r="E8">
         <v>6.45</v>
@@ -1065,19 +1071,19 @@
         <v>125080.37</v>
       </c>
       <c r="I8">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="J8">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="K8">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="L8">
-        <v>129.21</v>
+        <v>122.01</v>
       </c>
       <c r="M8">
-        <v>27.88</v>
+        <v>22.36</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1088,10 +1094,10 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>41400</v>
+        <v>46850</v>
       </c>
       <c r="D9" s="3">
-        <v>0.14680000000000001</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="E9">
         <v>4.57</v>
@@ -1106,19 +1112,19 @@
         <v>42814.52</v>
       </c>
       <c r="I9">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="J9">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K9">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L9">
-        <v>133.22</v>
+        <v>133.85</v>
       </c>
       <c r="M9">
-        <v>38</v>
+        <v>29.78</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1129,10 +1135,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>95700</v>
+        <v>100000</v>
       </c>
       <c r="D10" s="3">
-        <v>-5.1999999999999998E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E10">
         <v>2.16</v>
@@ -1147,19 +1153,19 @@
         <v>177736.27</v>
       </c>
       <c r="I10">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="J10">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K10">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="L10">
-        <v>104.34</v>
+        <v>106.76</v>
       </c>
       <c r="M10">
-        <v>6.69</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1170,10 +1176,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>13580</v>
+        <v>14390</v>
       </c>
       <c r="D11" s="3">
-        <v>1.2699999999999999E-2</v>
+        <v>2.4899999999999999E-2</v>
       </c>
       <c r="E11">
         <v>9.44</v>
@@ -1188,19 +1194,19 @@
         <v>19219.419999999998</v>
       </c>
       <c r="I11">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="J11">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="K11">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L11">
-        <v>114</v>
+        <v>115.13</v>
       </c>
       <c r="M11">
-        <v>11.22</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1211,10 +1217,10 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>84800</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0</v>
+        <v>86500</v>
+      </c>
+      <c r="D12" s="3">
+        <v>-4.5999999999999999E-3</v>
       </c>
       <c r="E12">
         <v>15.14</v>
@@ -1229,19 +1235,19 @@
         <v>82759.37</v>
       </c>
       <c r="I12">
-        <v>3.89</v>
+        <v>3.82</v>
       </c>
       <c r="J12">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K12">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L12">
-        <v>109.1</v>
+        <v>108.63</v>
       </c>
       <c r="M12">
-        <v>8.16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1252,10 +1258,10 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>499000</v>
+        <v>524000</v>
       </c>
       <c r="D13" s="3">
-        <v>-1.38E-2</v>
+        <v>1.9E-3</v>
       </c>
       <c r="E13">
         <v>12.43</v>
@@ -1270,19 +1276,19 @@
         <v>429918.88</v>
       </c>
       <c r="I13">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="J13">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K13">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L13">
-        <v>100.3</v>
+        <v>104.98</v>
       </c>
       <c r="M13">
-        <v>6.74</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1293,10 +1299,10 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>182100</v>
+        <v>196000</v>
       </c>
       <c r="D14" s="3">
-        <v>-2.46E-2</v>
+        <v>-2.9700000000000001E-2</v>
       </c>
       <c r="E14">
         <v>18.96</v>
@@ -1311,19 +1317,19 @@
         <v>144109.65</v>
       </c>
       <c r="I14">
-        <v>3.73</v>
+        <v>3.47</v>
       </c>
       <c r="J14">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K14">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="L14">
-        <v>122.59</v>
+        <v>121.23</v>
       </c>
       <c r="M14">
-        <v>10.97</v>
+        <v>4.9800000000000004</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1334,10 +1340,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>30900</v>
+        <v>36400</v>
       </c>
       <c r="D15" s="3">
-        <v>0.06</v>
+        <v>-5.0799999999999998E-2</v>
       </c>
       <c r="E15">
         <v>8.73</v>
@@ -1352,19 +1358,19 @@
         <v>24348.21</v>
       </c>
       <c r="I15">
-        <v>3.07</v>
+        <v>2.61</v>
       </c>
       <c r="J15">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K15">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="L15">
-        <v>119.55</v>
+        <v>126.19</v>
       </c>
       <c r="M15">
-        <v>19.079999999999998</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1375,10 +1381,10 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>32800</v>
+        <v>30500</v>
       </c>
       <c r="D16" s="3">
-        <v>2.5000000000000001E-2</v>
+        <v>-2.87E-2</v>
       </c>
       <c r="E16">
         <v>19.78</v>
@@ -1393,19 +1399,19 @@
         <v>32624.26</v>
       </c>
       <c r="I16">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="J16">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K16">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="L16">
-        <v>123.48</v>
+        <v>109.69</v>
       </c>
       <c r="M16">
-        <v>24.48</v>
+        <v>-4.6900000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1416,10 +1422,10 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>233000</v>
+        <v>231500</v>
       </c>
       <c r="D17" s="3">
-        <v>-3.7199999999999997E-2</v>
+        <v>4.3E-3</v>
       </c>
       <c r="E17">
         <v>13.17</v>
@@ -1434,19 +1440,19 @@
         <v>207156.6</v>
       </c>
       <c r="I17">
-        <v>2.2999999999999998</v>
+        <v>2.31</v>
       </c>
       <c r="J17">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K17">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L17">
-        <v>112.68</v>
+        <v>108</v>
       </c>
       <c r="M17">
-        <v>12.29</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1457,10 +1463,10 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>101000</v>
+        <v>107900</v>
       </c>
       <c r="D18" s="3">
-        <v>4.02E-2</v>
+        <v>-1.37E-2</v>
       </c>
       <c r="E18">
         <v>12.89</v>
@@ -1475,19 +1481,19 @@
         <v>87743.72</v>
       </c>
       <c r="I18">
-        <v>3.47</v>
+        <v>3.24</v>
       </c>
       <c r="J18">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K18">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="L18">
-        <v>113.03</v>
+        <v>113.66</v>
       </c>
       <c r="M18">
-        <v>13.87</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1498,10 +1504,10 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>86500</v>
+        <v>80900</v>
       </c>
       <c r="D19" s="3">
-        <v>0.109</v>
+        <v>0.01</v>
       </c>
       <c r="E19">
         <v>10.83</v>
@@ -1516,19 +1522,19 @@
         <v>54894.12</v>
       </c>
       <c r="I19">
-        <v>4.09</v>
+        <v>4.38</v>
       </c>
       <c r="J19">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K19">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L19">
-        <v>123.28</v>
+        <v>109.14</v>
       </c>
       <c r="M19">
-        <v>25</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1539,10 +1545,10 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>103300</v>
+        <v>111100</v>
       </c>
       <c r="D20" s="3">
-        <v>4.9799999999999997E-2</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="E20">
         <v>14.42</v>
@@ -1557,19 +1563,19 @@
         <v>36460.550000000003</v>
       </c>
       <c r="I20">
-        <v>5.32</v>
+        <v>4.95</v>
       </c>
       <c r="J20">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K20">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L20">
-        <v>107.79</v>
+        <v>111.73</v>
       </c>
       <c r="M20">
-        <v>1.08</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1580,10 +1586,10 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>89600</v>
+        <v>85100</v>
       </c>
       <c r="D21" s="3">
-        <v>1.9300000000000001E-2</v>
+        <v>-1.7299999999999999E-2</v>
       </c>
       <c r="E21">
         <v>19.38</v>
@@ -1598,19 +1604,19 @@
         <v>48549.53</v>
       </c>
       <c r="I21">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="J21">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="K21">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="L21">
-        <v>109.94</v>
+        <v>101.89</v>
       </c>
       <c r="M21">
-        <v>14.58</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1621,10 +1627,10 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>26150</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0</v>
+        <v>26350</v>
+      </c>
+      <c r="D22" s="3">
+        <v>-2.9499999999999998E-2</v>
       </c>
       <c r="E22">
         <v>8.06</v>
@@ -1639,19 +1645,19 @@
         <v>44443.18</v>
       </c>
       <c r="I22">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="J22">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K22">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L22">
-        <v>116.18</v>
+        <v>110.71</v>
       </c>
       <c r="M22">
-        <v>13.7</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1662,10 +1668,10 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>62300</v>
+        <v>64000</v>
       </c>
       <c r="D23" s="3">
-        <v>1.2999999999999999E-2</v>
+        <v>-3.4700000000000002E-2</v>
       </c>
       <c r="E23">
         <v>8</v>
@@ -1680,19 +1686,19 @@
         <v>78673.05</v>
       </c>
       <c r="I23">
-        <v>4.49</v>
+        <v>4.38</v>
       </c>
       <c r="J23">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K23">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="L23">
-        <v>109.25</v>
+        <v>107.72</v>
       </c>
       <c r="M23">
-        <v>5.77</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1703,10 +1709,10 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>22200</v>
+        <v>22050</v>
       </c>
       <c r="D24" s="3">
-        <v>9.1000000000000004E-3</v>
+        <v>-3.7100000000000001E-2</v>
       </c>
       <c r="E24">
         <v>15.12</v>
@@ -1721,19 +1727,19 @@
         <v>15310.06</v>
       </c>
       <c r="I24">
-        <v>5.54</v>
+        <v>5.58</v>
       </c>
       <c r="J24">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K24">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L24">
-        <v>104.62</v>
+        <v>102.43</v>
       </c>
       <c r="M24">
-        <v>6.99</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1744,10 +1750,10 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>64500</v>
+        <v>65700</v>
       </c>
       <c r="D25" s="3">
-        <v>3.0999999999999999E-3</v>
+        <v>-2.9499999999999998E-2</v>
       </c>
       <c r="E25">
         <v>2.85</v>
@@ -1762,19 +1768,19 @@
         <v>71073.47</v>
       </c>
       <c r="I25">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="J25">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K25">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L25">
-        <v>112.63</v>
+        <v>110</v>
       </c>
       <c r="M25">
-        <v>14.56</v>
+        <v>2.1800000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1785,10 +1791,10 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>17170</v>
-      </c>
-      <c r="D26" s="5">
-        <v>0</v>
+        <v>17370</v>
+      </c>
+      <c r="D26" s="3">
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E26">
         <v>4.4000000000000004</v>
@@ -1803,19 +1809,19 @@
         <v>20394.86</v>
       </c>
       <c r="I26">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
       <c r="J26">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K26">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L26">
-        <v>107.87</v>
+        <v>106.4</v>
       </c>
       <c r="M26">
-        <v>10.7</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1826,10 +1832,10 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>205500</v>
+        <v>224000</v>
       </c>
       <c r="D27" s="3">
-        <v>2.3999999999999998E-3</v>
+        <v>-3.4500000000000003E-2</v>
       </c>
       <c r="E27">
         <v>5.76</v>
@@ -1844,19 +1850,19 @@
         <v>204813.77</v>
       </c>
       <c r="I27">
-        <v>2.19</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J27">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="K27">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="L27">
-        <v>109.23</v>
+        <v>113.39</v>
       </c>
       <c r="M27">
-        <v>11.5</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1867,10 +1873,10 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>27750</v>
+        <v>30850</v>
       </c>
       <c r="D28" s="3">
-        <v>-3.4799999999999998E-2</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="E28">
         <v>21.07</v>
@@ -1885,19 +1891,19 @@
         <v>8151.56</v>
       </c>
       <c r="I28">
-        <v>1.26</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="J28">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K28">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L28">
-        <v>99.03</v>
+        <v>107.98</v>
       </c>
       <c r="M28">
-        <v>-1.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1908,10 +1914,10 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>173800</v>
+        <v>173400</v>
       </c>
       <c r="D29" s="3">
-        <v>9.2999999999999992E-3</v>
+        <v>-1.7600000000000001E-2</v>
       </c>
       <c r="E29">
         <v>12.66</v>
@@ -1929,16 +1935,16 @@
         <v>3.11</v>
       </c>
       <c r="J29">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K29">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="L29">
-        <v>111.75</v>
+        <v>107.24</v>
       </c>
       <c r="M29">
-        <v>6.43</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1949,10 +1955,10 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>18860</v>
+        <v>19410</v>
       </c>
       <c r="D30" s="3">
-        <v>-7.4000000000000003E-3</v>
+        <v>-4.5999999999999999E-3</v>
       </c>
       <c r="E30">
         <v>12.08</v>
@@ -1967,19 +1973,19 @@
         <v>19234.22</v>
       </c>
       <c r="I30">
-        <v>6.2</v>
+        <v>6.03</v>
       </c>
       <c r="J30">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K30">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L30">
-        <v>105.7</v>
+        <v>106.97</v>
       </c>
       <c r="M30">
-        <v>6.61</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1990,10 +1996,10 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>42000</v>
+        <v>44250</v>
       </c>
       <c r="D31" s="3">
-        <v>-1.52E-2</v>
+        <v>-1.01E-2</v>
       </c>
       <c r="E31">
         <v>11.21</v>
@@ -2008,19 +2014,19 @@
         <v>122131.86</v>
       </c>
       <c r="I31">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="J31">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K31">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L31">
-        <v>102.78</v>
+        <v>106.15</v>
       </c>
       <c r="M31">
-        <v>3.07</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -2031,10 +2037,10 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>65800</v>
+        <v>73400</v>
       </c>
       <c r="D32" s="3">
-        <v>-4.6399999999999997E-2</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="E32">
         <v>8.14</v>
@@ -2049,19 +2055,19 @@
         <v>37401.51</v>
       </c>
       <c r="I32">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="J32">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K32">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L32">
-        <v>102.58</v>
+        <v>110.95</v>
       </c>
       <c r="M32">
-        <v>2.81</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2072,10 +2078,10 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>58300</v>
+        <v>62100</v>
       </c>
       <c r="D33" s="3">
-        <v>8.6999999999999994E-3</v>
+        <v>-1.5800000000000002E-2</v>
       </c>
       <c r="E33">
         <v>13.26</v>
@@ -2090,19 +2096,19 @@
         <v>29169.68</v>
       </c>
       <c r="I33">
-        <v>4.2300000000000004</v>
+        <v>3.98</v>
       </c>
       <c r="J33">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K33">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L33">
-        <v>101.27</v>
+        <v>106.23</v>
       </c>
       <c r="M33">
-        <v>2.1</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2113,10 +2119,10 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>102500</v>
+        <v>100900</v>
       </c>
       <c r="D34" s="3">
-        <v>-3.3000000000000002E-2</v>
+        <v>-8.8000000000000005E-3</v>
       </c>
       <c r="E34">
         <v>8.11</v>
@@ -2131,19 +2137,19 @@
         <v>119742.76</v>
       </c>
       <c r="I34">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="J34">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K34">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L34">
-        <v>115.34</v>
+        <v>108.69</v>
       </c>
       <c r="M34">
-        <v>9.51</v>
+        <v>-4.8099999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2154,10 +2160,10 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>238000</v>
+        <v>248500</v>
       </c>
       <c r="D35" s="3">
-        <v>-2.0999999999999999E-3</v>
+        <v>2.2599999999999999E-2</v>
       </c>
       <c r="E35">
         <v>2.46</v>
@@ -2172,19 +2178,19 @@
         <v>81630.009999999995</v>
       </c>
       <c r="I35">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="J35">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K35">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L35">
-        <v>109.6</v>
+        <v>110.55</v>
       </c>
       <c r="M35">
-        <v>8.18</v>
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2195,10 +2201,10 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>257500</v>
+        <v>268000</v>
       </c>
       <c r="D36" s="3">
-        <v>4.4600000000000001E-2</v>
+        <v>-3.9399999999999998E-2</v>
       </c>
       <c r="E36">
         <v>11.54</v>
@@ -2213,19 +2219,19 @@
         <v>189057.03</v>
       </c>
       <c r="I36">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="J36">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K36">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="L36">
-        <v>122.39</v>
+        <v>116.57</v>
       </c>
       <c r="M36">
-        <v>25.3</v>
+        <v>8.7200000000000006</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2236,10 +2242,10 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>71000</v>
-      </c>
-      <c r="D37" s="3">
-        <v>1.14E-2</v>
+        <v>73000</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0</v>
       </c>
       <c r="E37">
         <v>4.12</v>
@@ -2254,19 +2260,19 @@
         <v>151788</v>
       </c>
       <c r="I37">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J37">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K37">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="L37">
-        <v>107.43</v>
+        <v>106.29</v>
       </c>
       <c r="M37">
-        <v>4.87</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2277,10 +2283,10 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>53000</v>
+        <v>52100</v>
       </c>
       <c r="D38" s="3">
-        <v>7.6E-3</v>
+        <v>-2.98E-2</v>
       </c>
       <c r="E38">
         <v>4.3</v>
@@ -2295,19 +2301,19 @@
         <v>37299.07</v>
       </c>
       <c r="I38">
-        <v>2.2599999999999998</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J38">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K38">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L38">
-        <v>109.95</v>
+        <v>104.71</v>
       </c>
       <c r="M38">
-        <v>4.95</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2318,10 +2324,10 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>255000</v>
+        <v>269500</v>
       </c>
       <c r="D39" s="3">
-        <v>-2.3E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="E39">
         <v>13.24</v>
@@ -2336,19 +2342,19 @@
         <v>130762.28</v>
       </c>
       <c r="I39">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="J39">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K39">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L39">
-        <v>101.72</v>
+        <v>107.22</v>
       </c>
       <c r="M39">
-        <v>6.92</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2359,10 +2365,10 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>127600</v>
+        <v>126100</v>
       </c>
       <c r="D40" s="3">
-        <v>-1.8499999999999999E-2</v>
+        <v>-2.3199999999999998E-2</v>
       </c>
       <c r="E40">
         <v>9.11</v>
@@ -2377,19 +2383,19 @@
         <v>159337.74</v>
       </c>
       <c r="I40">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="J40">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K40">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L40">
-        <v>116.55</v>
+        <v>109.39</v>
       </c>
       <c r="M40">
-        <v>11.34</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2400,10 +2406,10 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>130200</v>
+        <v>131200</v>
       </c>
       <c r="D41" s="3">
-        <v>-2.3300000000000001E-2</v>
+        <v>-2.3E-3</v>
       </c>
       <c r="E41">
         <v>3.62</v>
@@ -2427,10 +2433,10 @@
         <v>16</v>
       </c>
       <c r="L41">
-        <v>101.19</v>
+        <v>99.76</v>
       </c>
       <c r="M41">
-        <v>3.01</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2441,10 +2447,10 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>222500</v>
+        <v>219500</v>
       </c>
       <c r="D42" s="3">
-        <v>-3.4700000000000002E-2</v>
+        <v>-1.1299999999999999E-2</v>
       </c>
       <c r="E42">
         <v>1.97</v>
@@ -2459,19 +2465,19 @@
         <v>481098.45</v>
       </c>
       <c r="I42">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="J42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L42">
-        <v>102.43</v>
+        <v>100.22</v>
       </c>
       <c r="M42">
-        <v>1.83</v>
+        <v>-4.7699999999999996</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2482,10 +2488,10 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>109900</v>
+        <v>115600</v>
       </c>
       <c r="D43" s="3">
-        <v>-2.7400000000000001E-2</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="E43">
         <v>11.33</v>
@@ -2500,19 +2506,19 @@
         <v>81339.91</v>
       </c>
       <c r="I43">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="J43">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K43">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L43">
-        <v>92.29</v>
+        <v>98.48</v>
       </c>
       <c r="M43">
-        <v>2.33</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
@@ -2523,10 +2529,10 @@
         <v>96</v>
       </c>
       <c r="C44" s="2">
-        <v>167900</v>
+        <v>166700</v>
       </c>
       <c r="D44" s="3">
-        <v>-3.5999999999999999E-3</v>
+        <v>-1.1900000000000001E-2</v>
       </c>
       <c r="E44">
         <v>8.86</v>
@@ -2541,19 +2547,19 @@
         <v>160038.65</v>
       </c>
       <c r="I44">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="J44">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K44">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L44">
-        <v>116.99</v>
+        <v>110.88</v>
       </c>
       <c r="M44">
-        <v>12.46</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
@@ -2564,10 +2570,10 @@
         <v>98</v>
       </c>
       <c r="C45" s="2">
-        <v>55300</v>
+        <v>55800</v>
       </c>
       <c r="D45" s="3">
-        <v>-1.43E-2</v>
+        <v>-3.5999999999999999E-3</v>
       </c>
       <c r="E45">
         <v>12.69</v>
@@ -2582,19 +2588,19 @@
         <v>67868.45</v>
       </c>
       <c r="I45">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="J45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L45">
-        <v>103.2</v>
+        <v>102.28</v>
       </c>
       <c r="M45">
-        <v>2.2200000000000002</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
@@ -2605,10 +2611,10 @@
         <v>100</v>
       </c>
       <c r="C46" s="2">
-        <v>62700</v>
-      </c>
-      <c r="D46" s="5">
-        <v>0</v>
+        <v>61700</v>
+      </c>
+      <c r="D46" s="3">
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="E46">
         <v>3.06</v>
@@ -2623,19 +2629,19 @@
         <v>127255.06</v>
       </c>
       <c r="I46">
-        <v>2.0699999999999998</v>
+        <v>2.11</v>
       </c>
       <c r="J46">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K46">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L46">
-        <v>116.45</v>
+        <v>107.51</v>
       </c>
       <c r="M46">
-        <v>13.18</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
@@ -2646,10 +2652,10 @@
         <v>102</v>
       </c>
       <c r="C47" s="2">
-        <v>22050</v>
+        <v>21800</v>
       </c>
       <c r="D47" s="3">
-        <v>2.8000000000000001E-2</v>
+        <v>-3.1099999999999999E-2</v>
       </c>
       <c r="E47">
         <v>6.96</v>
@@ -2664,19 +2670,19 @@
         <v>34223.949999999997</v>
       </c>
       <c r="I47">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="J47">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K47">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L47">
-        <v>125.97</v>
+        <v>115.41</v>
       </c>
       <c r="M47">
-        <v>19.190000000000001</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
@@ -2687,10 +2693,10 @@
         <v>104</v>
       </c>
       <c r="C48" s="2">
-        <v>20800</v>
+        <v>20400</v>
       </c>
       <c r="D48" s="3">
-        <v>2.7199999999999998E-2</v>
+        <v>-4.2299999999999997E-2</v>
       </c>
       <c r="E48">
         <v>3.6</v>
@@ -2705,19 +2711,19 @@
         <v>38541.279999999999</v>
       </c>
       <c r="I48">
-        <v>2.4</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="J48">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K48">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="L48">
-        <v>127.86</v>
+        <v>115.74</v>
       </c>
       <c r="M48">
-        <v>18.86</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.4">
@@ -2728,10 +2734,10 @@
         <v>106</v>
       </c>
       <c r="C49" s="2">
-        <v>72100</v>
+        <v>75100</v>
       </c>
       <c r="D49" s="3">
-        <v>-1.9E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="E49">
         <v>10.79</v>
@@ -2746,7 +2752,7 @@
         <v>92723.77</v>
       </c>
       <c r="I49">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="J49">
         <v>93</v>
@@ -2755,10 +2761,10 @@
         <v>93</v>
       </c>
       <c r="L49">
-        <v>107.81</v>
+        <v>109.12</v>
       </c>
       <c r="M49">
-        <v>7.29</v>
+        <v>2.1800000000000002</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.4">
@@ -2769,37 +2775,37 @@
         <v>108</v>
       </c>
       <c r="C50" s="2">
-        <v>53700</v>
+        <v>34150</v>
       </c>
       <c r="D50" s="3">
-        <v>-2.8899999999999999E-2</v>
+        <v>-6.5699999999999995E-2</v>
       </c>
       <c r="E50">
-        <v>18.690000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="F50">
-        <v>11.56</v>
+        <v>13.49</v>
       </c>
       <c r="G50">
-        <v>6.83</v>
+        <v>12.93</v>
       </c>
       <c r="H50" s="4">
-        <v>57293.3</v>
+        <v>31004.78</v>
       </c>
       <c r="I50">
-        <v>2.23</v>
+        <v>2.91</v>
       </c>
       <c r="J50">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="K50">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="L50">
-        <v>101.2</v>
+        <v>116.21</v>
       </c>
       <c r="M50">
-        <v>-3.42</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.4">
@@ -2810,37 +2816,78 @@
         <v>110</v>
       </c>
       <c r="C51" s="2">
-        <v>38950</v>
+        <v>56800</v>
       </c>
       <c r="D51" s="3">
-        <v>-5.1000000000000004E-3</v>
+        <v>-7.0000000000000001E-3</v>
       </c>
       <c r="E51">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="F51">
+        <v>11.56</v>
+      </c>
+      <c r="G51">
+        <v>6.83</v>
+      </c>
+      <c r="H51" s="4">
+        <v>57293.3</v>
+      </c>
+      <c r="I51">
+        <v>2.11</v>
+      </c>
+      <c r="J51">
+        <v>61</v>
+      </c>
+      <c r="K51">
+        <v>61</v>
+      </c>
+      <c r="L51">
+        <v>104.99</v>
+      </c>
+      <c r="M51">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="2">
+        <v>39100</v>
+      </c>
+      <c r="D52" s="3">
+        <v>-2.98E-2</v>
+      </c>
+      <c r="E52">
         <v>9.39</v>
       </c>
-      <c r="F51">
+      <c r="F52">
         <v>10.74</v>
       </c>
-      <c r="G51">
+      <c r="G52">
         <v>9.73</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H52" s="4">
         <v>48211.77</v>
       </c>
-      <c r="I51">
-        <v>3.08</v>
-      </c>
-      <c r="J51">
+      <c r="I52">
+        <v>3.07</v>
+      </c>
+      <c r="J52">
         <v>92</v>
       </c>
-      <c r="K51">
+      <c r="K52">
         <v>92</v>
       </c>
-      <c r="L51">
-        <v>122</v>
-      </c>
-      <c r="M51">
-        <v>20.03</v>
+      <c r="L52">
+        <v>114.29</v>
+      </c>
+      <c r="M52">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB81220E-E4C0-41D0-BCD9-639772D84880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF6E8557-D0A7-45D7-A4FB-10C6DA217AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84CE8CCA-E32B-455C-A40A-2FCB7EBF8490}"/>
+    <workbookView xWindow="9804" yWindow="3312" windowWidth="9036" windowHeight="9648" xr2:uid="{C79B7C84-46C7-4704-AE12-5ECC362CAF7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="149">
   <si>
     <t>종목코드</t>
   </si>
@@ -60,10 +60,10 @@
     <t>해당등락률</t>
   </si>
   <si>
-    <t>000240</t>
-  </si>
-  <si>
-    <t>한국앤컴퍼니</t>
+    <t>000100</t>
+  </si>
+  <si>
+    <t>유한양행</t>
   </si>
   <si>
     <t>000270</t>
@@ -72,40 +72,40 @@
     <t>기아</t>
   </si>
   <si>
+    <t>000660</t>
+  </si>
+  <si>
+    <t>SK하이닉스</t>
+  </si>
+  <si>
     <t>000810</t>
   </si>
   <si>
     <t>삼성화재</t>
   </si>
   <si>
-    <t>001120</t>
-  </si>
-  <si>
-    <t>LX인터내셔널</t>
-  </si>
-  <si>
-    <t>001270</t>
-  </si>
-  <si>
-    <t>부국증권</t>
-  </si>
-  <si>
-    <t>001430</t>
-  </si>
-  <si>
-    <t>세아베스틸지주</t>
-  </si>
-  <si>
-    <t>001720</t>
-  </si>
-  <si>
-    <t>신영증권</t>
-  </si>
-  <si>
-    <t>003540</t>
-  </si>
-  <si>
-    <t>대신증권</t>
+    <t>000880</t>
+  </si>
+  <si>
+    <t>한화</t>
+  </si>
+  <si>
+    <t>001040</t>
+  </si>
+  <si>
+    <t>CJ</t>
+  </si>
+  <si>
+    <t>003230</t>
+  </si>
+  <si>
+    <t>삼양식품</t>
+  </si>
+  <si>
+    <t>003490</t>
+  </si>
+  <si>
+    <t>대한항공</t>
   </si>
   <si>
     <t>003550</t>
@@ -114,46 +114,94 @@
     <t>LG</t>
   </si>
   <si>
-    <t>003690</t>
-  </si>
-  <si>
-    <t>코리안리</t>
-  </si>
-  <si>
-    <t>005180</t>
-  </si>
-  <si>
-    <t>빙그레</t>
-  </si>
-  <si>
     <t>005380</t>
   </si>
   <si>
     <t>현대차</t>
   </si>
   <si>
+    <t>005490</t>
+  </si>
+  <si>
+    <t>POSCO홀딩스</t>
+  </si>
+  <si>
     <t>005830</t>
   </si>
   <si>
     <t>DB손해보험</t>
   </si>
   <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>삼성전자</t>
+  </si>
+  <si>
     <t>005940</t>
   </si>
   <si>
     <t>NH투자증권</t>
   </si>
   <si>
-    <t>007340</t>
-  </si>
-  <si>
-    <t>DN오토모티브</t>
-  </si>
-  <si>
-    <t>009970</t>
-  </si>
-  <si>
-    <t>영원무역홀딩스</t>
+    <t>006260</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>006800</t>
+  </si>
+  <si>
+    <t>미래에셋증권</t>
+  </si>
+  <si>
+    <t>007660</t>
+  </si>
+  <si>
+    <t>이수페타시스</t>
+  </si>
+  <si>
+    <t>009150</t>
+  </si>
+  <si>
+    <t>삼성전기</t>
+  </si>
+  <si>
+    <t>009540</t>
+  </si>
+  <si>
+    <t>HD한국조선해양</t>
+  </si>
+  <si>
+    <t>010120</t>
+  </si>
+  <si>
+    <t>LS ELECTRIC</t>
+  </si>
+  <si>
+    <t>010130</t>
+  </si>
+  <si>
+    <t>고려아연</t>
+  </si>
+  <si>
+    <t>011200</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
+    <t>012330</t>
+  </si>
+  <si>
+    <t>현대모비스</t>
+  </si>
+  <si>
+    <t>012450</t>
+  </si>
+  <si>
+    <t>한화에어로스페이스</t>
   </si>
   <si>
     <t>016360</t>
@@ -168,10 +216,10 @@
     <t>SK텔레콤</t>
   </si>
   <si>
-    <t>017800</t>
-  </si>
-  <si>
-    <t>현대엘리베이터</t>
+    <t>018260</t>
+  </si>
+  <si>
+    <t>삼성에스디에스</t>
   </si>
   <si>
     <t>021240</t>
@@ -186,18 +234,24 @@
     <t>기업은행</t>
   </si>
   <si>
+    <t>028050</t>
+  </si>
+  <si>
+    <t>삼성E&amp;A</t>
+  </si>
+  <si>
+    <t>028260</t>
+  </si>
+  <si>
+    <t>삼성물산</t>
+  </si>
+  <si>
     <t>029780</t>
   </si>
   <si>
     <t>삼성카드</t>
   </si>
   <si>
-    <t>030000</t>
-  </si>
-  <si>
-    <t>제일기획</t>
-  </si>
-  <si>
     <t>030200</t>
   </si>
   <si>
@@ -216,12 +270,6 @@
     <t>삼성생명</t>
   </si>
   <si>
-    <t>033500</t>
-  </si>
-  <si>
-    <t>동성화인텍</t>
-  </si>
-  <si>
     <t>033780</t>
   </si>
   <si>
@@ -234,10 +282,34 @@
     <t>강원랜드</t>
   </si>
   <si>
-    <t>036460</t>
-  </si>
-  <si>
-    <t>한국가스공사</t>
+    <t>035420</t>
+  </si>
+  <si>
+    <t>NAVER</t>
+  </si>
+  <si>
+    <t>035720</t>
+  </si>
+  <si>
+    <t>카카오</t>
+  </si>
+  <si>
+    <t>036570</t>
+  </si>
+  <si>
+    <t>엔씨소프트</t>
+  </si>
+  <si>
+    <t>039490</t>
+  </si>
+  <si>
+    <t>키움증권</t>
+  </si>
+  <si>
+    <t>042700</t>
+  </si>
+  <si>
+    <t>한미반도체</t>
   </si>
   <si>
     <t>047050</t>
@@ -246,10 +318,10 @@
     <t>포스코인터내셔널</t>
   </si>
   <si>
-    <t>051600</t>
-  </si>
-  <si>
-    <t>한전KPS</t>
+    <t>047810</t>
+  </si>
+  <si>
+    <t>한국항공우주</t>
   </si>
   <si>
     <t>055550</t>
@@ -258,6 +330,18 @@
     <t>신한지주</t>
   </si>
   <si>
+    <t>064350</t>
+  </si>
+  <si>
+    <t>현대로템</t>
+  </si>
+  <si>
+    <t>066570</t>
+  </si>
+  <si>
+    <t>LG전자</t>
+  </si>
+  <si>
     <t>068270</t>
   </si>
   <si>
@@ -276,10 +360,10 @@
     <t>GS</t>
   </si>
   <si>
-    <t>081660</t>
-  </si>
-  <si>
-    <t>미스토홀딩스</t>
+    <t>079550</t>
+  </si>
+  <si>
+    <t>LIG넥스원</t>
   </si>
   <si>
     <t>086280</t>
@@ -294,22 +378,10 @@
     <t>하나금융지주</t>
   </si>
   <si>
-    <t>086900</t>
-  </si>
-  <si>
-    <t>메디톡스</t>
-  </si>
-  <si>
-    <t>097950</t>
-  </si>
-  <si>
-    <t>CJ제일제당</t>
-  </si>
-  <si>
-    <t>103140</t>
-  </si>
-  <si>
-    <t>풍산</t>
+    <t>090430</t>
+  </si>
+  <si>
+    <t>아모레퍼시픽</t>
   </si>
   <si>
     <t>105560</t>
@@ -318,16 +390,10 @@
     <t>KB금융</t>
   </si>
   <si>
-    <t>108320</t>
-  </si>
-  <si>
-    <t>LX세미콘</t>
-  </si>
-  <si>
-    <t>120110</t>
-  </si>
-  <si>
-    <t>코오롱인더</t>
+    <t>138040</t>
+  </si>
+  <si>
+    <t>메리츠금융지주</t>
   </si>
   <si>
     <t>138930</t>
@@ -336,12 +402,6 @@
     <t>BNK금융지주</t>
   </si>
   <si>
-    <t>139130</t>
-  </si>
-  <si>
-    <t>iM금융지주</t>
-  </si>
-  <si>
     <t>161390</t>
   </si>
   <si>
@@ -354,16 +414,64 @@
     <t>JB금융지주</t>
   </si>
   <si>
-    <t>192080</t>
-  </si>
-  <si>
-    <t>더블유게임즈</t>
+    <t>180640</t>
+  </si>
+  <si>
+    <t>한진칼</t>
+  </si>
+  <si>
+    <t>241560</t>
+  </si>
+  <si>
+    <t>두산밥캣</t>
+  </si>
+  <si>
+    <t>267250</t>
+  </si>
+  <si>
+    <t>HD현대</t>
+  </si>
+  <si>
+    <t>267260</t>
+  </si>
+  <si>
+    <t>HD현대일렉트릭</t>
+  </si>
+  <si>
+    <t>271560</t>
+  </si>
+  <si>
+    <t>오리온</t>
+  </si>
+  <si>
+    <t>272210</t>
+  </si>
+  <si>
+    <t>한화시스템</t>
+  </si>
+  <si>
+    <t>298040</t>
+  </si>
+  <si>
+    <t>효성중공업</t>
+  </si>
+  <si>
+    <t>307950</t>
+  </si>
+  <si>
+    <t>현대오토에버</t>
   </si>
   <si>
     <t>316140</t>
   </si>
   <si>
     <t>우리금융지주</t>
+  </si>
+  <si>
+    <t>352820</t>
+  </si>
+  <si>
+    <t>하이브</t>
   </si>
 </sst>
 </file>
@@ -741,14 +849,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C883D38-5ED9-40BA-8890-F9B467A3FC71}">
-  <dimension ref="A1:M52"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF6CBEB1-5612-4276-873B-52B6147F91D3}">
+  <dimension ref="A1:M70"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -807,37 +915,37 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>33050</v>
+        <v>110200</v>
       </c>
       <c r="D2" s="3">
-        <v>-2.2200000000000001E-2</v>
+        <v>-6.3E-3</v>
       </c>
       <c r="E2">
-        <v>8.2799999999999994</v>
+        <v>3.41</v>
       </c>
       <c r="F2">
-        <v>8.9</v>
+        <v>4.99</v>
       </c>
       <c r="G2">
-        <v>5.8</v>
+        <v>5.01</v>
       </c>
       <c r="H2" s="4">
-        <v>48390.96</v>
+        <v>29428.94</v>
       </c>
       <c r="I2">
-        <v>3.03</v>
+        <v>0.45</v>
       </c>
       <c r="J2">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="K2">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="L2">
-        <v>114.71</v>
+        <v>100.63</v>
       </c>
       <c r="M2">
-        <v>8.36</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -848,10 +956,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>174000</v>
+        <v>205500</v>
       </c>
       <c r="D3" s="3">
-        <v>7.4999999999999997E-3</v>
+        <v>-2.3999999999999998E-3</v>
       </c>
       <c r="E3">
         <v>19.09</v>
@@ -866,19 +974,19 @@
         <v>150938.41</v>
       </c>
       <c r="I3">
-        <v>3.74</v>
+        <v>3.16</v>
       </c>
       <c r="J3">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K3">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L3">
-        <v>109.33</v>
+        <v>123.68</v>
       </c>
       <c r="M3">
-        <v>4.63</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -889,37 +997,37 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>553000</v>
+        <v>1061000</v>
       </c>
       <c r="D4" s="3">
-        <v>-2.12E-2</v>
+        <v>-3.4599999999999999E-2</v>
       </c>
       <c r="E4">
-        <v>13.09</v>
+        <v>31.06</v>
       </c>
       <c r="F4">
-        <v>13.88</v>
+        <v>42.48</v>
       </c>
       <c r="G4">
-        <v>12.47</v>
+        <v>6.34</v>
       </c>
       <c r="H4" s="4">
-        <v>405451.96</v>
+        <v>140282.54999999999</v>
       </c>
       <c r="I4">
-        <v>3.44</v>
+        <v>0.21</v>
       </c>
       <c r="J4">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K4">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="L4">
-        <v>104.87</v>
+        <v>115.98</v>
       </c>
       <c r="M4">
-        <v>-4.82</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -930,37 +1038,37 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>48450</v>
+        <v>530000</v>
       </c>
       <c r="D5" s="3">
-        <v>1.6799999999999999E-2</v>
+        <v>-3.2800000000000003E-2</v>
       </c>
       <c r="E5">
-        <v>7.12</v>
+        <v>13.09</v>
       </c>
       <c r="F5">
-        <v>9.6199999999999992</v>
+        <v>13.88</v>
       </c>
       <c r="G5">
-        <v>12.61</v>
+        <v>12.47</v>
       </c>
       <c r="H5" s="4">
-        <v>72041.39</v>
+        <v>405451.96</v>
       </c>
       <c r="I5">
-        <v>4.13</v>
+        <v>3.58</v>
       </c>
       <c r="J5">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="K5">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="L5">
-        <v>116.17</v>
+        <v>99.18</v>
       </c>
       <c r="M5">
-        <v>7.55</v>
+        <v>-14.24</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -971,25 +1079,25 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>98400</v>
+        <v>136600</v>
       </c>
       <c r="D6" s="3">
-        <v>-4.7399999999999998E-2</v>
+        <v>-1.8700000000000001E-2</v>
       </c>
       <c r="E6">
-        <v>4.05</v>
+        <v>7.19</v>
       </c>
       <c r="F6">
-        <v>7.82</v>
+        <v>6.47</v>
       </c>
       <c r="G6">
-        <v>6.06</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="H6" s="4">
-        <v>65679.45</v>
+        <v>117241.22</v>
       </c>
       <c r="I6">
-        <v>1.52</v>
+        <v>0.59</v>
       </c>
       <c r="J6">
         <v>93</v>
@@ -998,10 +1106,10 @@
         <v>93</v>
       </c>
       <c r="L6">
-        <v>128.66999999999999</v>
+        <v>112.34</v>
       </c>
       <c r="M6">
-        <v>27.13</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -1012,37 +1120,37 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>70500</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0</v>
+        <v>218500</v>
+      </c>
+      <c r="D7" s="3">
+        <v>-9.1000000000000004E-3</v>
       </c>
       <c r="E7">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="F7">
-        <v>3.97</v>
+        <v>9.24</v>
       </c>
       <c r="G7">
-        <v>4.21</v>
+        <v>3.14</v>
       </c>
       <c r="H7" s="4">
-        <v>53899.69</v>
+        <v>156275.9</v>
       </c>
       <c r="I7">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="J7">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K7">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="L7">
-        <v>93.32</v>
+        <v>100.73</v>
       </c>
       <c r="M7">
-        <v>-4.5999999999999996</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -1053,37 +1161,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>237500</v>
+        <v>1221000</v>
       </c>
       <c r="D8" s="3">
-        <v>-6.8599999999999994E-2</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="E8">
-        <v>6.45</v>
+        <v>39.369999999999997</v>
       </c>
       <c r="F8">
-        <v>9.77</v>
+        <v>41.29</v>
       </c>
       <c r="G8">
-        <v>7.46</v>
+        <v>27.7</v>
       </c>
       <c r="H8" s="4">
-        <v>125080.37</v>
+        <v>144393.44</v>
       </c>
       <c r="I8">
-        <v>1.89</v>
+        <v>0.27</v>
       </c>
       <c r="J8">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="K8">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="L8">
-        <v>122.01</v>
+        <v>104.53</v>
       </c>
       <c r="M8">
-        <v>22.36</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1094,37 +1202,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>46850</v>
-      </c>
-      <c r="D9" s="3">
-        <v>5.4000000000000003E-3</v>
+        <v>28100</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>4.57</v>
+        <v>13.17</v>
       </c>
       <c r="F9">
-        <v>7.42</v>
+        <v>8.14</v>
       </c>
       <c r="G9">
-        <v>4.55</v>
+        <v>15.53</v>
       </c>
       <c r="H9" s="4">
-        <v>42814.52</v>
+        <v>29309.19</v>
       </c>
       <c r="I9">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="J9">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="K9">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="L9">
-        <v>133.85</v>
+        <v>112.38</v>
       </c>
       <c r="M9">
-        <v>29.78</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1135,10 +1243,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>100000</v>
+        <v>107700</v>
       </c>
       <c r="D10" s="3">
-        <v>5.0000000000000001E-3</v>
+        <v>4.1599999999999998E-2</v>
       </c>
       <c r="E10">
         <v>2.16</v>
@@ -1153,19 +1261,19 @@
         <v>177736.27</v>
       </c>
       <c r="I10">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="J10">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K10">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L10">
-        <v>106.76</v>
+        <v>112.75</v>
       </c>
       <c r="M10">
-        <v>3.95</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1176,37 +1284,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>14390</v>
+        <v>674000</v>
       </c>
       <c r="D11" s="3">
-        <v>2.4899999999999999E-2</v>
+        <v>0.1067</v>
       </c>
       <c r="E11">
-        <v>9.44</v>
+        <v>12.43</v>
       </c>
       <c r="F11">
-        <v>10.67</v>
+        <v>10.08</v>
       </c>
       <c r="G11">
-        <v>9.86</v>
+        <v>11.82</v>
       </c>
       <c r="H11" s="4">
-        <v>19219.419999999998</v>
+        <v>429918.88</v>
       </c>
       <c r="I11">
-        <v>3.58</v>
+        <v>1.78</v>
       </c>
       <c r="J11">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K11">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="L11">
-        <v>115.13</v>
+        <v>130.29</v>
       </c>
       <c r="M11">
-        <v>7.31</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1217,37 +1325,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>86500</v>
+        <v>413000</v>
       </c>
       <c r="D12" s="3">
-        <v>-4.5999999999999999E-3</v>
+        <v>1.35E-2</v>
       </c>
       <c r="E12">
-        <v>15.14</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>14.47</v>
+        <v>2.12</v>
       </c>
       <c r="G12">
-        <v>11.28</v>
+        <v>3.76</v>
       </c>
       <c r="H12" s="4">
-        <v>82759.37</v>
+        <v>701760.86</v>
       </c>
       <c r="I12">
-        <v>3.82</v>
+        <v>2.42</v>
       </c>
       <c r="J12">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="K12">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="L12">
-        <v>108.63</v>
+        <v>109.54</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1258,37 +1366,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>524000</v>
+        <v>183100</v>
       </c>
       <c r="D13" s="3">
-        <v>1.9E-3</v>
+        <v>-0.109</v>
       </c>
       <c r="E13">
-        <v>12.43</v>
+        <v>18.96</v>
       </c>
       <c r="F13">
-        <v>10.08</v>
+        <v>19.43</v>
       </c>
       <c r="G13">
-        <v>11.82</v>
+        <v>18.8</v>
       </c>
       <c r="H13" s="4">
-        <v>429918.88</v>
+        <v>144109.65</v>
       </c>
       <c r="I13">
-        <v>2.29</v>
+        <v>3.71</v>
       </c>
       <c r="J13">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K13">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L13">
-        <v>104.98</v>
+        <v>106.9</v>
       </c>
       <c r="M13">
-        <v>3.56</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1299,37 +1407,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>196000</v>
+        <v>216500</v>
       </c>
       <c r="D14" s="3">
-        <v>-2.9700000000000001E-2</v>
+        <v>-6.8999999999999999E-3</v>
       </c>
       <c r="E14">
-        <v>18.96</v>
+        <v>10.85</v>
       </c>
       <c r="F14">
-        <v>19.43</v>
+        <v>10.85</v>
       </c>
       <c r="G14">
-        <v>18.8</v>
+        <v>8.01</v>
       </c>
       <c r="H14" s="4">
-        <v>144109.65</v>
+        <v>63976.31</v>
       </c>
       <c r="I14">
-        <v>3.47</v>
+        <v>0.77</v>
       </c>
       <c r="J14">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K14">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L14">
-        <v>121.23</v>
+        <v>121.65</v>
       </c>
       <c r="M14">
-        <v>4.9800000000000004</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1340,10 +1448,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>36400</v>
+        <v>35500</v>
       </c>
       <c r="D15" s="3">
-        <v>-5.0799999999999998E-2</v>
+        <v>-2.7400000000000001E-2</v>
       </c>
       <c r="E15">
         <v>8.73</v>
@@ -1358,19 +1466,19 @@
         <v>24348.21</v>
       </c>
       <c r="I15">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="J15">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K15">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L15">
-        <v>126.19</v>
+        <v>115.84</v>
       </c>
       <c r="M15">
-        <v>24.87</v>
+        <v>-9.44</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1381,37 +1489,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>30500</v>
+        <v>284500</v>
       </c>
       <c r="D16" s="3">
-        <v>-2.87E-2</v>
+        <v>-1.9E-2</v>
       </c>
       <c r="E16">
-        <v>19.78</v>
+        <v>5.09</v>
       </c>
       <c r="F16">
-        <v>13.82</v>
+        <v>7.08</v>
       </c>
       <c r="G16">
-        <v>23.29</v>
+        <v>11.63</v>
       </c>
       <c r="H16" s="4">
-        <v>32624.26</v>
+        <v>158418.68</v>
       </c>
       <c r="I16">
-        <v>3.28</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="J16">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K16">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L16">
-        <v>109.69</v>
+        <v>116.82</v>
       </c>
       <c r="M16">
-        <v>-4.6900000000000004</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1422,37 +1530,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>231500</v>
+        <v>72000</v>
       </c>
       <c r="D17" s="3">
-        <v>4.3E-3</v>
+        <v>-2.1700000000000001E-2</v>
       </c>
       <c r="E17">
-        <v>13.17</v>
+        <v>7.94</v>
       </c>
       <c r="F17">
-        <v>11.69</v>
+        <v>10.76</v>
       </c>
       <c r="G17">
-        <v>18.010000000000002</v>
+        <v>5.75</v>
       </c>
       <c r="H17" s="4">
-        <v>207156.6</v>
+        <v>18036.09</v>
       </c>
       <c r="I17">
-        <v>2.31</v>
+        <v>0.35</v>
       </c>
       <c r="J17">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K17">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L17">
-        <v>108</v>
+        <v>128.1</v>
       </c>
       <c r="M17">
-        <v>-4.34</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1463,37 +1571,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>107900</v>
+        <v>127600</v>
       </c>
       <c r="D18" s="3">
-        <v>-1.37E-2</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="E18">
-        <v>12.89</v>
+        <v>24.91</v>
       </c>
       <c r="F18">
-        <v>13.94</v>
+        <v>29.9</v>
       </c>
       <c r="G18">
-        <v>9.44</v>
+        <v>34.450000000000003</v>
       </c>
       <c r="H18" s="4">
-        <v>87743.72</v>
+        <v>9737.2999999999993</v>
       </c>
       <c r="I18">
-        <v>3.24</v>
+        <v>0.12</v>
       </c>
       <c r="J18">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K18">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="L18">
-        <v>113.66</v>
+        <v>112.13</v>
       </c>
       <c r="M18">
-        <v>11.12</v>
+        <v>26.97</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1504,37 +1612,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>80900</v>
+        <v>448500</v>
       </c>
       <c r="D19" s="3">
-        <v>0.01</v>
+        <v>-3.8600000000000002E-2</v>
       </c>
       <c r="E19">
-        <v>10.83</v>
+        <v>7.7</v>
       </c>
       <c r="F19">
-        <v>3.37</v>
+        <v>7.7</v>
       </c>
       <c r="G19">
-        <v>9.48</v>
+        <v>7.12</v>
       </c>
       <c r="H19" s="4">
-        <v>54894.12</v>
+        <v>124850.23</v>
       </c>
       <c r="I19">
-        <v>4.38</v>
+        <v>0.52</v>
       </c>
       <c r="J19">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="K19">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L19">
-        <v>109.14</v>
+        <v>130.91999999999999</v>
       </c>
       <c r="M19">
-        <v>3.72</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1545,37 +1653,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>111100</v>
+        <v>450000</v>
       </c>
       <c r="D20" s="3">
-        <v>-5.4000000000000003E-3</v>
+        <v>-4.4000000000000003E-3</v>
       </c>
       <c r="E20">
-        <v>14.42</v>
+        <v>11.16</v>
       </c>
       <c r="F20">
-        <v>24.2</v>
+        <v>16.829999999999998</v>
       </c>
       <c r="G20">
-        <v>15.82</v>
+        <v>3.73</v>
       </c>
       <c r="H20" s="4">
-        <v>36460.550000000003</v>
+        <v>175890.96</v>
       </c>
       <c r="I20">
-        <v>4.95</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="J20">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="K20">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="L20">
-        <v>111.73</v>
+        <v>106.7</v>
       </c>
       <c r="M20">
-        <v>12.91</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1586,37 +1694,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>85100</v>
+        <v>787000</v>
       </c>
       <c r="D21" s="3">
-        <v>-1.7299999999999999E-2</v>
+        <v>-1.9900000000000001E-2</v>
       </c>
       <c r="E21">
-        <v>19.38</v>
+        <v>13.44</v>
       </c>
       <c r="F21">
-        <v>18.93</v>
+        <v>14.22</v>
       </c>
       <c r="G21">
-        <v>20.04</v>
+        <v>10.67</v>
       </c>
       <c r="H21" s="4">
-        <v>48549.53</v>
+        <v>66213.7</v>
       </c>
       <c r="I21">
-        <v>3.09</v>
+        <v>0.37</v>
       </c>
       <c r="J21">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="K21">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="L21">
-        <v>101.89</v>
+        <v>119.73</v>
       </c>
       <c r="M21">
-        <v>-3.19</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1627,37 +1735,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>26350</v>
+        <v>2030000</v>
       </c>
       <c r="D22" s="3">
-        <v>-2.9499999999999998E-2</v>
+        <v>-1.2200000000000001E-2</v>
       </c>
       <c r="E22">
-        <v>8.06</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="F22">
-        <v>8.64</v>
+        <v>9.98</v>
       </c>
       <c r="G22">
-        <v>8.77</v>
+        <v>5.79</v>
       </c>
       <c r="H22" s="4">
-        <v>44443.18</v>
+        <v>451423.76</v>
       </c>
       <c r="I22">
-        <v>4.04</v>
+        <v>0.86</v>
       </c>
       <c r="J22">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K22">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L22">
-        <v>110.71</v>
+        <v>113.39</v>
       </c>
       <c r="M22">
-        <v>0.76</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1668,37 +1776,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>64000</v>
+        <v>21350</v>
       </c>
       <c r="D23" s="3">
-        <v>-3.4700000000000002E-2</v>
+        <v>-4.2599999999999999E-2</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>15.35</v>
       </c>
       <c r="F23">
-        <v>7.71</v>
+        <v>7.57</v>
       </c>
       <c r="G23">
-        <v>7.9</v>
+        <v>28.31</v>
       </c>
       <c r="H23" s="4">
-        <v>78673.05</v>
+        <v>27017.48</v>
       </c>
       <c r="I23">
-        <v>4.38</v>
+        <v>2.81</v>
       </c>
       <c r="J23">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="K23">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="L23">
-        <v>107.72</v>
+        <v>100.42</v>
       </c>
       <c r="M23">
-        <v>4.07</v>
+        <v>-7.78</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1709,37 +1817,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>22050</v>
+        <v>517000</v>
       </c>
       <c r="D24" s="3">
-        <v>-3.7100000000000001E-2</v>
+        <v>-2.2700000000000001E-2</v>
       </c>
       <c r="E24">
-        <v>15.12</v>
+        <v>9.35</v>
       </c>
       <c r="F24">
-        <v>13.07</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="G24">
-        <v>15.58</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="H24" s="4">
-        <v>15310.06</v>
+        <v>528506.16</v>
       </c>
       <c r="I24">
-        <v>5.58</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="J24">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="K24">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="L24">
-        <v>102.43</v>
+        <v>114.41</v>
       </c>
       <c r="M24">
-        <v>0.23</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1750,37 +1858,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>65700</v>
+        <v>1195000</v>
       </c>
       <c r="D25" s="3">
-        <v>-2.9499999999999998E-2</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="E25">
-        <v>2.85</v>
+        <v>53.94</v>
       </c>
       <c r="F25">
-        <v>12.83</v>
+        <v>14.72</v>
       </c>
       <c r="G25">
-        <v>5.63</v>
+        <v>28.78</v>
       </c>
       <c r="H25" s="4">
-        <v>71073.47</v>
+        <v>174991.05</v>
       </c>
       <c r="I25">
-        <v>3.04</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J25">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="K25">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L25">
-        <v>110</v>
+        <v>98.22</v>
       </c>
       <c r="M25">
-        <v>2.1800000000000002</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1791,37 +1899,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>17370</v>
+        <v>106800</v>
       </c>
       <c r="D26" s="3">
-        <v>4.0000000000000001E-3</v>
+        <v>-3.8699999999999998E-2</v>
       </c>
       <c r="E26">
-        <v>4.4000000000000004</v>
+        <v>12.89</v>
       </c>
       <c r="F26">
-        <v>6.71</v>
+        <v>13.94</v>
       </c>
       <c r="G26">
-        <v>6.75</v>
+        <v>9.44</v>
       </c>
       <c r="H26" s="4">
-        <v>20394.86</v>
+        <v>87743.72</v>
       </c>
       <c r="I26">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="J26">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="K26">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L26">
-        <v>106.4</v>
+        <v>108.33</v>
       </c>
       <c r="M26">
-        <v>1.1599999999999999</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1832,37 +1940,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>224000</v>
+        <v>79800</v>
       </c>
       <c r="D27" s="3">
-        <v>-3.4500000000000003E-2</v>
+        <v>-3.04E-2</v>
       </c>
       <c r="E27">
-        <v>5.76</v>
+        <v>10.83</v>
       </c>
       <c r="F27">
-        <v>8.11</v>
+        <v>3.37</v>
       </c>
       <c r="G27">
-        <v>5.33</v>
+        <v>9.48</v>
       </c>
       <c r="H27" s="4">
-        <v>204813.77</v>
+        <v>54894.12</v>
       </c>
       <c r="I27">
-        <v>2.0099999999999998</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="J27">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="K27">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="L27">
-        <v>113.39</v>
+        <v>104.2</v>
       </c>
       <c r="M27">
-        <v>9.27</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1873,37 +1981,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>30850</v>
+        <v>195000</v>
       </c>
       <c r="D28" s="3">
-        <v>9.7999999999999997E-3</v>
+        <v>1.9300000000000001E-2</v>
       </c>
       <c r="E28">
-        <v>21.07</v>
+        <v>8.42</v>
       </c>
       <c r="F28">
-        <v>24.22</v>
+        <v>8.11</v>
       </c>
       <c r="G28">
-        <v>15.16</v>
+        <v>10.29</v>
       </c>
       <c r="H28" s="4">
-        <v>8151.56</v>
+        <v>124608.94</v>
       </c>
       <c r="I28">
-        <v>1.1299999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="J28">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="K28">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="L28">
-        <v>107.98</v>
+        <v>111.95</v>
       </c>
       <c r="M28">
-        <v>7.3</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1914,37 +2022,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>173400</v>
+        <v>81900</v>
       </c>
       <c r="D29" s="3">
-        <v>-1.7600000000000001E-2</v>
+        <v>-2.6200000000000001E-2</v>
       </c>
       <c r="E29">
-        <v>12.66</v>
+        <v>19.38</v>
       </c>
       <c r="F29">
-        <v>11.88</v>
+        <v>18.93</v>
       </c>
       <c r="G29">
-        <v>11.14</v>
+        <v>20.04</v>
       </c>
       <c r="H29" s="4">
-        <v>83639.03</v>
+        <v>48549.53</v>
       </c>
       <c r="I29">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="J29">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="K29">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="L29">
-        <v>107.24</v>
+        <v>96.83</v>
       </c>
       <c r="M29">
-        <v>0.7</v>
+        <v>-6.19</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1955,37 +2063,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>19410</v>
+        <v>25750</v>
       </c>
       <c r="D30" s="3">
-        <v>-4.5999999999999999E-3</v>
+        <v>-2.8299999999999999E-2</v>
       </c>
       <c r="E30">
-        <v>12.08</v>
+        <v>8.06</v>
       </c>
       <c r="F30">
-        <v>8.58</v>
+        <v>8.64</v>
       </c>
       <c r="G30">
-        <v>8.39</v>
+        <v>8.77</v>
       </c>
       <c r="H30" s="4">
-        <v>19234.22</v>
+        <v>44443.18</v>
       </c>
       <c r="I30">
-        <v>6.03</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="J30">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="K30">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="L30">
-        <v>106.97</v>
+        <v>104.82</v>
       </c>
       <c r="M30">
-        <v>2.16</v>
+        <v>-9.81</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1996,37 +2104,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>44250</v>
+        <v>36400</v>
       </c>
       <c r="D31" s="3">
-        <v>-1.01E-2</v>
+        <v>-6.5500000000000003E-2</v>
       </c>
       <c r="E31">
-        <v>11.21</v>
+        <v>19.649999999999999</v>
       </c>
       <c r="F31">
-        <v>6.55</v>
+        <v>13.15</v>
       </c>
       <c r="G31">
-        <v>6.4</v>
+        <v>24.14</v>
       </c>
       <c r="H31" s="4">
-        <v>122131.86</v>
+        <v>23223.11</v>
       </c>
       <c r="I31">
-        <v>3.29</v>
+        <v>1.81</v>
       </c>
       <c r="J31">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="K31">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="L31">
-        <v>106.15</v>
+        <v>107.79</v>
       </c>
       <c r="M31">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -2037,37 +2145,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>73400</v>
+        <v>350500</v>
       </c>
       <c r="D32" s="3">
-        <v>2.7000000000000001E-3</v>
+        <v>-2.64E-2</v>
       </c>
       <c r="E32">
-        <v>8.14</v>
+        <v>6.83</v>
       </c>
       <c r="F32">
-        <v>10.050000000000001</v>
+        <v>6.08</v>
       </c>
       <c r="G32">
-        <v>12.43</v>
+        <v>7.09</v>
       </c>
       <c r="H32" s="4">
-        <v>37401.51</v>
+        <v>245146.58</v>
       </c>
       <c r="I32">
-        <v>2.11</v>
+        <v>0.74</v>
       </c>
       <c r="J32">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="K32">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="L32">
-        <v>110.95</v>
+        <v>109.52</v>
       </c>
       <c r="M32">
-        <v>6.38</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2078,37 +2186,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>62100</v>
+        <v>63000</v>
       </c>
       <c r="D33" s="3">
-        <v>-1.5800000000000002E-2</v>
+        <v>-1.6000000000000001E-3</v>
       </c>
       <c r="E33">
-        <v>13.26</v>
+        <v>7.45</v>
       </c>
       <c r="F33">
-        <v>10.58</v>
+        <v>7.45</v>
       </c>
       <c r="G33">
-        <v>11.65</v>
+        <v>7.69</v>
       </c>
       <c r="H33" s="4">
-        <v>29169.68</v>
+        <v>79986.48</v>
       </c>
       <c r="I33">
-        <v>3.98</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="J33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L33">
-        <v>106.23</v>
+        <v>103.99</v>
       </c>
       <c r="M33">
-        <v>7.44</v>
+        <v>-6.53</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2119,37 +2227,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>100900</v>
+        <v>63800</v>
       </c>
       <c r="D34" s="3">
-        <v>-8.8000000000000005E-3</v>
+        <v>-1.24E-2</v>
       </c>
       <c r="E34">
-        <v>8.11</v>
+        <v>2.85</v>
       </c>
       <c r="F34">
-        <v>10.44</v>
+        <v>12.83</v>
       </c>
       <c r="G34">
-        <v>8.66</v>
+        <v>5.63</v>
       </c>
       <c r="H34" s="4">
-        <v>119742.76</v>
+        <v>71073.47</v>
       </c>
       <c r="I34">
-        <v>2.14</v>
+        <v>3.13</v>
       </c>
       <c r="J34">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K34">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L34">
-        <v>108.69</v>
+        <v>104.27</v>
       </c>
       <c r="M34">
-        <v>-4.8099999999999996</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2160,37 +2268,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>248500</v>
+        <v>16540</v>
       </c>
       <c r="D35" s="3">
-        <v>2.2599999999999999E-2</v>
+        <v>-7.1300000000000002E-2</v>
       </c>
       <c r="E35">
-        <v>2.46</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F35">
-        <v>3.92</v>
+        <v>6.71</v>
       </c>
       <c r="G35">
-        <v>6.96</v>
+        <v>6.75</v>
       </c>
       <c r="H35" s="4">
-        <v>81630.009999999995</v>
+        <v>20394.86</v>
       </c>
       <c r="I35">
-        <v>0.3</v>
+        <v>3.93</v>
       </c>
       <c r="J35">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="K35">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="L35">
-        <v>110.55</v>
+        <v>99.82</v>
       </c>
       <c r="M35">
-        <v>4.1900000000000004</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2201,37 +2309,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>268000</v>
+        <v>230000</v>
       </c>
       <c r="D36" s="3">
-        <v>-3.9399999999999998E-2</v>
+        <v>-3.7699999999999997E-2</v>
       </c>
       <c r="E36">
-        <v>11.54</v>
+        <v>4.66</v>
       </c>
       <c r="F36">
-        <v>20.98</v>
+        <v>4.66</v>
       </c>
       <c r="G36">
-        <v>9.6</v>
+        <v>4.88</v>
       </c>
       <c r="H36" s="4">
-        <v>189057.03</v>
+        <v>324173.33</v>
       </c>
       <c r="I36">
-        <v>1.49</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J36">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K36">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L36">
-        <v>116.57</v>
+        <v>111.88</v>
       </c>
       <c r="M36">
-        <v>8.7200000000000006</v>
+        <v>5.0199999999999996</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2242,37 +2350,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>73000</v>
-      </c>
-      <c r="D37" s="5">
-        <v>0</v>
+        <v>163100</v>
+      </c>
+      <c r="D37" s="3">
+        <v>-3.8899999999999997E-2</v>
       </c>
       <c r="E37">
-        <v>4.12</v>
+        <v>12.66</v>
       </c>
       <c r="F37">
-        <v>5.22</v>
+        <v>11.88</v>
       </c>
       <c r="G37">
-        <v>11.01</v>
+        <v>11.14</v>
       </c>
       <c r="H37" s="4">
-        <v>151788</v>
+        <v>83639.03</v>
       </c>
       <c r="I37">
-        <v>3.7</v>
+        <v>3.31</v>
       </c>
       <c r="J37">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K37">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L37">
-        <v>106.29</v>
+        <v>98.41</v>
       </c>
       <c r="M37">
-        <v>3.99</v>
+        <v>-7.91</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2283,37 +2391,37 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>52100</v>
+        <v>19050</v>
       </c>
       <c r="D38" s="3">
-        <v>-2.98E-2</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="E38">
-        <v>4.3</v>
+        <v>12.08</v>
       </c>
       <c r="F38">
-        <v>15.4</v>
+        <v>8.58</v>
       </c>
       <c r="G38">
-        <v>8.75</v>
+        <v>8.39</v>
       </c>
       <c r="H38" s="4">
-        <v>37299.07</v>
+        <v>19234.22</v>
       </c>
       <c r="I38">
-        <v>2.2999999999999998</v>
+        <v>6.14</v>
       </c>
       <c r="J38">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="K38">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="L38">
-        <v>104.71</v>
+        <v>103.52</v>
       </c>
       <c r="M38">
-        <v>-0.95</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2324,37 +2432,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>269500</v>
+        <v>254500</v>
       </c>
       <c r="D39" s="3">
-        <v>7.4999999999999997E-3</v>
+        <v>-2.3E-2</v>
       </c>
       <c r="E39">
-        <v>13.24</v>
+        <v>7.9</v>
       </c>
       <c r="F39">
-        <v>18.559999999999999</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="G39">
-        <v>15.51</v>
+        <v>5.2</v>
       </c>
       <c r="H39" s="4">
-        <v>130762.28</v>
+        <v>178255.48</v>
       </c>
       <c r="I39">
-        <v>1.37</v>
+        <v>0.44</v>
       </c>
       <c r="J39">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="K39">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="L39">
-        <v>107.22</v>
+        <v>97.84</v>
       </c>
       <c r="M39">
-        <v>3.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2365,37 +2473,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>126100</v>
+        <v>62300</v>
       </c>
       <c r="D40" s="3">
-        <v>-2.3199999999999998E-2</v>
+        <v>1.47E-2</v>
       </c>
       <c r="E40">
-        <v>9.11</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F40">
-        <v>10.57</v>
+        <v>5.88</v>
       </c>
       <c r="G40">
-        <v>9.4</v>
+        <v>1.31</v>
       </c>
       <c r="H40" s="4">
-        <v>159337.74</v>
+        <v>24000.959999999999</v>
       </c>
       <c r="I40">
-        <v>2.85</v>
+        <v>0.11</v>
       </c>
       <c r="J40">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K40">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="L40">
-        <v>109.39</v>
+        <v>105.68</v>
       </c>
       <c r="M40">
-        <v>-3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2406,37 +2514,37 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>131200</v>
+        <v>231000</v>
       </c>
       <c r="D41" s="3">
-        <v>-2.3E-3</v>
+        <v>-2.2000000000000001E-3</v>
       </c>
       <c r="E41">
-        <v>3.62</v>
+        <v>2.99</v>
       </c>
       <c r="F41">
-        <v>5.61</v>
+        <v>14.36</v>
       </c>
       <c r="G41">
-        <v>4.91</v>
+        <v>7.77</v>
       </c>
       <c r="H41" s="4">
-        <v>75207.820000000007</v>
+        <v>189738.22</v>
       </c>
       <c r="I41">
-        <v>0.84</v>
+        <v>0.63</v>
       </c>
       <c r="J41">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K41">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L41">
-        <v>99.76</v>
+        <v>103.97</v>
       </c>
       <c r="M41">
-        <v>-1.58</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2447,37 +2555,37 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>219500</v>
+        <v>466000</v>
       </c>
       <c r="D42" s="3">
-        <v>-1.1299999999999999E-2</v>
+        <v>-1.17E-2</v>
       </c>
       <c r="E42">
-        <v>1.97</v>
+        <v>15.98</v>
       </c>
       <c r="F42">
-        <v>4.25</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="G42">
-        <v>5.59</v>
+        <v>12.25</v>
       </c>
       <c r="H42" s="4">
-        <v>481098.45</v>
+        <v>238844.91</v>
       </c>
       <c r="I42">
-        <v>2.73</v>
+        <v>1.61</v>
       </c>
       <c r="J42">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="K42">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="L42">
-        <v>100.22</v>
+        <v>103.61</v>
       </c>
       <c r="M42">
-        <v>-4.7699999999999996</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2488,37 +2596,37 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>115600</v>
+        <v>323500</v>
       </c>
       <c r="D43" s="3">
-        <v>2.0299999999999999E-2</v>
+        <v>0.17419999999999999</v>
       </c>
       <c r="E43">
-        <v>11.33</v>
+        <v>27.43</v>
       </c>
       <c r="F43">
-        <v>8.2799999999999994</v>
+        <v>41.23</v>
       </c>
       <c r="G43">
-        <v>9.83</v>
+        <v>36</v>
       </c>
       <c r="H43" s="4">
-        <v>81339.91</v>
+        <v>7170.29</v>
       </c>
       <c r="I43">
-        <v>2.25</v>
+        <v>0.22</v>
       </c>
       <c r="J43">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="K43">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="L43">
-        <v>98.48</v>
+        <v>154.06</v>
       </c>
       <c r="M43">
-        <v>2.2999999999999998</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
@@ -2529,37 +2637,37 @@
         <v>96</v>
       </c>
       <c r="C44" s="2">
-        <v>166700</v>
+        <v>72200</v>
       </c>
       <c r="D44" s="3">
-        <v>-1.1900000000000001E-2</v>
+        <v>-4.4999999999999998E-2</v>
       </c>
       <c r="E44">
-        <v>8.86</v>
+        <v>8.14</v>
       </c>
       <c r="F44">
-        <v>11.63</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="G44">
-        <v>8.51</v>
+        <v>12.43</v>
       </c>
       <c r="H44" s="4">
-        <v>160038.65</v>
+        <v>37401.51</v>
       </c>
       <c r="I44">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="J44">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="K44">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="L44">
-        <v>110.88</v>
+        <v>106.49</v>
       </c>
       <c r="M44">
-        <v>-1.07</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
@@ -2570,37 +2678,37 @@
         <v>98</v>
       </c>
       <c r="C45" s="2">
-        <v>55800</v>
+        <v>191500</v>
       </c>
       <c r="D45" s="3">
-        <v>-3.5999999999999999E-3</v>
+        <v>4.1300000000000003E-2</v>
       </c>
       <c r="E45">
-        <v>12.69</v>
+        <v>10.42</v>
       </c>
       <c r="F45">
-        <v>7.79</v>
+        <v>9.58</v>
       </c>
       <c r="G45">
-        <v>16.63</v>
+        <v>11.34</v>
       </c>
       <c r="H45" s="4">
-        <v>67868.45</v>
+        <v>18284.689999999999</v>
       </c>
       <c r="I45">
-        <v>4.3</v>
+        <v>0.26</v>
       </c>
       <c r="J45">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="K45">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="L45">
-        <v>102.28</v>
+        <v>112.05</v>
       </c>
       <c r="M45">
-        <v>-0.53</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
@@ -2611,37 +2719,37 @@
         <v>100</v>
       </c>
       <c r="C46" s="2">
-        <v>61700</v>
+        <v>96900</v>
       </c>
       <c r="D46" s="3">
-        <v>8.2000000000000007E-3</v>
+        <v>-0.03</v>
       </c>
       <c r="E46">
-        <v>3.06</v>
+        <v>8.11</v>
       </c>
       <c r="F46">
-        <v>1.7</v>
+        <v>10.44</v>
       </c>
       <c r="G46">
-        <v>3.92</v>
+        <v>8.66</v>
       </c>
       <c r="H46" s="4">
-        <v>127255.06</v>
+        <v>119742.76</v>
       </c>
       <c r="I46">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="J46">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="K46">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="L46">
-        <v>107.51</v>
+        <v>101.97</v>
       </c>
       <c r="M46">
-        <v>-1.59</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
@@ -2652,37 +2760,37 @@
         <v>102</v>
       </c>
       <c r="C47" s="2">
-        <v>21800</v>
+        <v>230500</v>
       </c>
       <c r="D47" s="3">
-        <v>-3.1099999999999999E-2</v>
+        <v>4.7699999999999999E-2</v>
       </c>
       <c r="E47">
-        <v>6.96</v>
+        <v>21.85</v>
       </c>
       <c r="F47">
-        <v>9.58</v>
+        <v>29.6</v>
       </c>
       <c r="G47">
-        <v>7.18</v>
+        <v>15.32</v>
       </c>
       <c r="H47" s="4">
-        <v>34223.949999999997</v>
+        <v>26462.02</v>
       </c>
       <c r="I47">
-        <v>2.98</v>
+        <v>0.09</v>
       </c>
       <c r="J47">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K47">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L47">
-        <v>115.41</v>
+        <v>106.64</v>
       </c>
       <c r="M47">
-        <v>1.63</v>
+        <v>4.7699999999999996</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
@@ -2693,37 +2801,37 @@
         <v>104</v>
       </c>
       <c r="C48" s="2">
-        <v>20400</v>
+        <v>145700</v>
       </c>
       <c r="D48" s="3">
-        <v>-4.2299999999999997E-2</v>
+        <v>-6.7999999999999996E-3</v>
       </c>
       <c r="E48">
-        <v>3.6</v>
+        <v>1.81</v>
       </c>
       <c r="F48">
-        <v>9.42</v>
+        <v>10.94</v>
       </c>
       <c r="G48">
-        <v>5.91</v>
+        <v>4.04</v>
       </c>
       <c r="H48" s="4">
-        <v>38541.279999999999</v>
+        <v>125574.14</v>
       </c>
       <c r="I48">
-        <v>2.4500000000000002</v>
+        <v>0.69</v>
       </c>
       <c r="J48">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="K48">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L48">
-        <v>115.74</v>
+        <v>126.16</v>
       </c>
       <c r="M48">
-        <v>0.74</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.4">
@@ -2734,37 +2842,37 @@
         <v>106</v>
       </c>
       <c r="C49" s="2">
-        <v>75100</v>
+        <v>238500</v>
       </c>
       <c r="D49" s="3">
-        <v>1.9E-2</v>
+        <v>-1.4500000000000001E-2</v>
       </c>
       <c r="E49">
-        <v>10.79</v>
+        <v>2.46</v>
       </c>
       <c r="F49">
-        <v>10.55</v>
+        <v>3.92</v>
       </c>
       <c r="G49">
-        <v>8.93</v>
+        <v>6.96</v>
       </c>
       <c r="H49" s="4">
-        <v>92723.77</v>
+        <v>81630.009999999995</v>
       </c>
       <c r="I49">
-        <v>2.66</v>
+        <v>0.31</v>
       </c>
       <c r="J49">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="K49">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="L49">
-        <v>109.12</v>
+        <v>104.1</v>
       </c>
       <c r="M49">
-        <v>2.1800000000000002</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.4">
@@ -2775,37 +2883,37 @@
         <v>108</v>
       </c>
       <c r="C50" s="2">
-        <v>34150</v>
+        <v>258500</v>
       </c>
       <c r="D50" s="3">
-        <v>-6.5699999999999995E-2</v>
+        <v>-3.1800000000000002E-2</v>
       </c>
       <c r="E50">
-        <v>12.8</v>
+        <v>11.54</v>
       </c>
       <c r="F50">
-        <v>13.49</v>
+        <v>20.98</v>
       </c>
       <c r="G50">
-        <v>12.93</v>
+        <v>9.6</v>
       </c>
       <c r="H50" s="4">
-        <v>31004.78</v>
+        <v>189057.03</v>
       </c>
       <c r="I50">
-        <v>2.91</v>
+        <v>1.54</v>
       </c>
       <c r="J50">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K50">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L50">
-        <v>116.21</v>
+        <v>107.8</v>
       </c>
       <c r="M50">
-        <v>0.28999999999999998</v>
+        <v>-11.62</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.4">
@@ -2816,37 +2924,37 @@
         <v>110</v>
       </c>
       <c r="C51" s="2">
-        <v>56800</v>
+        <v>68700</v>
       </c>
       <c r="D51" s="3">
-        <v>-7.0000000000000001E-3</v>
+        <v>-2.1399999999999999E-2</v>
       </c>
       <c r="E51">
-        <v>18.690000000000001</v>
+        <v>4.12</v>
       </c>
       <c r="F51">
-        <v>11.56</v>
+        <v>5.22</v>
       </c>
       <c r="G51">
-        <v>6.83</v>
+        <v>11.01</v>
       </c>
       <c r="H51" s="4">
-        <v>57293.3</v>
+        <v>151788</v>
       </c>
       <c r="I51">
-        <v>2.11</v>
+        <v>3.93</v>
       </c>
       <c r="J51">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="K51">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="L51">
-        <v>104.99</v>
+        <v>98.27</v>
       </c>
       <c r="M51">
-        <v>2.71</v>
+        <v>-9.25</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.4">
@@ -2857,37 +2965,775 @@
         <v>112</v>
       </c>
       <c r="C52" s="2">
-        <v>39100</v>
+        <v>509000</v>
       </c>
       <c r="D52" s="3">
-        <v>-2.98E-2</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="E52">
+        <v>19.59</v>
+      </c>
+      <c r="F52">
+        <v>25.3</v>
+      </c>
+      <c r="G52">
+        <v>17.23</v>
+      </c>
+      <c r="H52" s="4">
+        <v>64298.52</v>
+      </c>
+      <c r="I52">
+        <v>0.47</v>
+      </c>
+      <c r="J52">
+        <v>77</v>
+      </c>
+      <c r="K52">
+        <v>77</v>
+      </c>
+      <c r="L52">
+        <v>106.66</v>
+      </c>
+      <c r="M52">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="2">
+        <v>289500</v>
+      </c>
+      <c r="D53" s="3">
+        <v>-3.3999999999999998E-3</v>
+      </c>
+      <c r="E53">
+        <v>13.24</v>
+      </c>
+      <c r="F53">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="G53">
+        <v>15.51</v>
+      </c>
+      <c r="H53" s="4">
+        <v>130762.28</v>
+      </c>
+      <c r="I53">
+        <v>1.28</v>
+      </c>
+      <c r="J53">
+        <v>97</v>
+      </c>
+      <c r="K53">
+        <v>97</v>
+      </c>
+      <c r="L53">
+        <v>112.38</v>
+      </c>
+      <c r="M53">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="2">
+        <v>121800</v>
+      </c>
+      <c r="D54" s="3">
+        <v>-2.4799999999999999E-2</v>
+      </c>
+      <c r="E54">
+        <v>9.11</v>
+      </c>
+      <c r="F54">
+        <v>10.57</v>
+      </c>
+      <c r="G54">
+        <v>9.4</v>
+      </c>
+      <c r="H54" s="4">
+        <v>159337.74</v>
+      </c>
+      <c r="I54">
+        <v>2.96</v>
+      </c>
+      <c r="J54">
+        <v>88</v>
+      </c>
+      <c r="K54">
+        <v>88</v>
+      </c>
+      <c r="L54">
+        <v>102.74</v>
+      </c>
+      <c r="M54">
+        <v>-7.24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B55" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="2">
+        <v>151400</v>
+      </c>
+      <c r="D55" s="3">
+        <v>-3.32E-2</v>
+      </c>
+      <c r="E55">
+        <v>11.69</v>
+      </c>
+      <c r="F55">
+        <v>5.33</v>
+      </c>
+      <c r="G55">
+        <v>6.07</v>
+      </c>
+      <c r="H55" s="4">
+        <v>77979.460000000006</v>
+      </c>
+      <c r="I55">
+        <v>0.74</v>
+      </c>
+      <c r="J55">
+        <v>30</v>
+      </c>
+      <c r="K55">
+        <v>30</v>
+      </c>
+      <c r="L55">
+        <v>100.41</v>
+      </c>
+      <c r="M55">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A56" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="2">
+        <v>159000</v>
+      </c>
+      <c r="D56" s="3">
+        <v>-3.8100000000000002E-2</v>
+      </c>
+      <c r="E56">
+        <v>8.86</v>
+      </c>
+      <c r="F56">
+        <v>11.63</v>
+      </c>
+      <c r="G56">
+        <v>8.51</v>
+      </c>
+      <c r="H56" s="4">
+        <v>160038.65</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+      <c r="J56">
+        <v>90</v>
+      </c>
+      <c r="K56">
+        <v>90</v>
+      </c>
+      <c r="L56">
+        <v>103.09</v>
+      </c>
+      <c r="M56">
+        <v>-5.81</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A57" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="2">
+        <v>127100</v>
+      </c>
+      <c r="D57" s="3">
+        <v>-3.1300000000000001E-2</v>
+      </c>
+      <c r="E57">
+        <v>23.44</v>
+      </c>
+      <c r="F57">
+        <v>25.94</v>
+      </c>
+      <c r="G57">
+        <v>27.89</v>
+      </c>
+      <c r="H57" s="4">
+        <v>59980.14</v>
+      </c>
+      <c r="I57">
+        <v>1.06</v>
+      </c>
+      <c r="J57">
+        <v>84</v>
+      </c>
+      <c r="K57">
+        <v>84</v>
+      </c>
+      <c r="L57">
+        <v>100.14</v>
+      </c>
+      <c r="M57">
+        <v>-13.06</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A58" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="2">
+        <v>19930</v>
+      </c>
+      <c r="D58" s="3">
+        <v>-2.7799999999999998E-2</v>
+      </c>
+      <c r="E58">
+        <v>6.96</v>
+      </c>
+      <c r="F58">
+        <v>9.58</v>
+      </c>
+      <c r="G58">
+        <v>7.18</v>
+      </c>
+      <c r="H58" s="4">
+        <v>34223.949999999997</v>
+      </c>
+      <c r="I58">
+        <v>3.26</v>
+      </c>
+      <c r="J58">
+        <v>82</v>
+      </c>
+      <c r="K58">
+        <v>82</v>
+      </c>
+      <c r="L58">
+        <v>101.69</v>
+      </c>
+      <c r="M58">
+        <v>-12.01</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A59" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" s="2">
+        <v>72900</v>
+      </c>
+      <c r="D59" s="3">
+        <v>-3.95E-2</v>
+      </c>
+      <c r="E59">
+        <v>10.79</v>
+      </c>
+      <c r="F59">
+        <v>10.55</v>
+      </c>
+      <c r="G59">
+        <v>8.93</v>
+      </c>
+      <c r="H59" s="4">
+        <v>92723.77</v>
+      </c>
+      <c r="I59">
+        <v>2.74</v>
+      </c>
+      <c r="J59">
+        <v>89</v>
+      </c>
+      <c r="K59">
+        <v>89</v>
+      </c>
+      <c r="L59">
+        <v>104.03</v>
+      </c>
+      <c r="M59">
+        <v>-3.57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A60" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" s="2">
+        <v>31750</v>
+      </c>
+      <c r="D60" s="3">
+        <v>-1.7000000000000001E-2</v>
+      </c>
+      <c r="E60">
+        <v>12.8</v>
+      </c>
+      <c r="F60">
+        <v>13.49</v>
+      </c>
+      <c r="G60">
+        <v>12.93</v>
+      </c>
+      <c r="H60" s="4">
+        <v>31004.78</v>
+      </c>
+      <c r="I60">
+        <v>3.13</v>
+      </c>
+      <c r="J60">
+        <v>79</v>
+      </c>
+      <c r="K60">
+        <v>79</v>
+      </c>
+      <c r="L60">
+        <v>103.53</v>
+      </c>
+      <c r="M60">
+        <v>-15.33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A61" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="2">
+        <v>156300</v>
+      </c>
+      <c r="D61" s="3">
+        <v>-9.3899999999999997E-2</v>
+      </c>
+      <c r="E61">
+        <v>16.75</v>
+      </c>
+      <c r="F61">
+        <v>4.34</v>
+      </c>
+      <c r="G61">
+        <v>21.73</v>
+      </c>
+      <c r="H61" s="4">
+        <v>49146.79</v>
+      </c>
+      <c r="I61">
+        <v>0.23</v>
+      </c>
+      <c r="J61">
+        <v>86</v>
+      </c>
+      <c r="K61">
+        <v>86</v>
+      </c>
+      <c r="L61">
+        <v>117.89</v>
+      </c>
+      <c r="M61">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A62" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="2">
+        <v>65000</v>
+      </c>
+      <c r="D62" s="3">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="E62">
+        <v>8.77</v>
+      </c>
+      <c r="F62">
+        <v>6.11</v>
+      </c>
+      <c r="G62">
+        <v>13.11</v>
+      </c>
+      <c r="H62" s="4">
+        <v>72587.83</v>
+      </c>
+      <c r="I62">
+        <v>2.46</v>
+      </c>
+      <c r="J62">
+        <v>81</v>
+      </c>
+      <c r="K62">
+        <v>81</v>
+      </c>
+      <c r="L62">
+        <v>103.04</v>
+      </c>
+      <c r="M62">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="2">
+        <v>292500</v>
+      </c>
+      <c r="D63" s="3">
+        <v>-1.0200000000000001E-2</v>
+      </c>
+      <c r="E63">
+        <v>6.36</v>
+      </c>
+      <c r="F63">
+        <v>7.5</v>
+      </c>
+      <c r="G63">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="H63" s="4">
+        <v>128102.48</v>
+      </c>
+      <c r="I63">
+        <v>1.23</v>
+      </c>
+      <c r="J63">
+        <v>96</v>
+      </c>
+      <c r="K63">
+        <v>96</v>
+      </c>
+      <c r="L63">
+        <v>113</v>
+      </c>
+      <c r="M63">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A64" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="2">
+        <v>1050000</v>
+      </c>
+      <c r="D64" s="3">
+        <v>-5.4899999999999997E-2</v>
+      </c>
+      <c r="E64">
+        <v>39.340000000000003</v>
+      </c>
+      <c r="F64">
+        <v>39.64</v>
+      </c>
+      <c r="G64">
+        <v>29.72</v>
+      </c>
+      <c r="H64" s="4">
+        <v>49760.73</v>
+      </c>
+      <c r="I64">
+        <v>0.51</v>
+      </c>
+      <c r="J64">
+        <v>94</v>
+      </c>
+      <c r="K64">
+        <v>94</v>
+      </c>
+      <c r="L64">
+        <v>109.53</v>
+      </c>
+      <c r="M64">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B65" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="2">
+        <v>133400</v>
+      </c>
+      <c r="D65" s="3">
+        <v>-1.77E-2</v>
+      </c>
+      <c r="E65">
+        <v>16.57</v>
+      </c>
+      <c r="F65">
+        <v>10.4</v>
+      </c>
+      <c r="G65">
+        <v>15.65</v>
+      </c>
+      <c r="H65" s="4">
+        <v>91733.3</v>
+      </c>
+      <c r="I65">
+        <v>1.87</v>
+      </c>
+      <c r="J65">
+        <v>78</v>
+      </c>
+      <c r="K65">
+        <v>78</v>
+      </c>
+      <c r="L65">
+        <v>103.39</v>
+      </c>
+      <c r="M65">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A66" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B66" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="2">
+        <v>113600</v>
+      </c>
+      <c r="D66" s="3">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="E66">
+        <v>19.62</v>
+      </c>
+      <c r="F66">
+        <v>8.48</v>
+      </c>
+      <c r="G66">
+        <v>10.95</v>
+      </c>
+      <c r="H66" s="4">
+        <v>25351.89</v>
+      </c>
+      <c r="I66">
+        <v>0.31</v>
+      </c>
+      <c r="J66">
+        <v>90</v>
+      </c>
+      <c r="K66">
+        <v>90</v>
+      </c>
+      <c r="L66">
+        <v>107.04</v>
+      </c>
+      <c r="M66">
+        <v>-2.4900000000000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A67" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="2">
+        <v>2823000</v>
+      </c>
+      <c r="D67" s="3">
+        <v>-2.5899999999999999E-2</v>
+      </c>
+      <c r="E67">
+        <v>14.9</v>
+      </c>
+      <c r="F67">
+        <v>22.48</v>
+      </c>
+      <c r="G67">
+        <v>9.09</v>
+      </c>
+      <c r="H67" s="4">
+        <v>234092.2</v>
+      </c>
+      <c r="I67">
+        <v>0.18</v>
+      </c>
+      <c r="J67">
+        <v>96</v>
+      </c>
+      <c r="K67">
+        <v>96</v>
+      </c>
+      <c r="L67">
+        <v>112.36</v>
+      </c>
+      <c r="M67">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A68" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" s="2">
+        <v>501000</v>
+      </c>
+      <c r="D68" s="3">
+        <v>-7.9000000000000008E-3</v>
+      </c>
+      <c r="E68">
+        <v>10.4</v>
+      </c>
+      <c r="F68">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="G68">
+        <v>9.14</v>
+      </c>
+      <c r="H68" s="4">
+        <v>65279.4</v>
+      </c>
+      <c r="I68">
+        <v>0.36</v>
+      </c>
+      <c r="J68">
+        <v>91</v>
+      </c>
+      <c r="K68">
+        <v>91</v>
+      </c>
+      <c r="L68">
+        <v>112.08</v>
+      </c>
+      <c r="M68">
+        <v>15.44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="2">
+        <v>36000</v>
+      </c>
+      <c r="D69" s="3">
+        <v>-4.8899999999999999E-2</v>
+      </c>
+      <c r="E69">
         <v>9.39</v>
       </c>
-      <c r="F52">
+      <c r="F69">
         <v>10.74</v>
       </c>
-      <c r="G52">
+      <c r="G69">
         <v>9.73</v>
       </c>
-      <c r="H52" s="4">
+      <c r="H69" s="4">
         <v>48211.77</v>
       </c>
-      <c r="I52">
-        <v>3.07</v>
-      </c>
-      <c r="J52">
-        <v>92</v>
-      </c>
-      <c r="K52">
-        <v>92</v>
-      </c>
-      <c r="L52">
-        <v>114.29</v>
-      </c>
-      <c r="M52">
-        <v>-0.13</v>
+      <c r="I69">
+        <v>3.33</v>
+      </c>
+      <c r="J69">
+        <v>83</v>
+      </c>
+      <c r="K69">
+        <v>83</v>
+      </c>
+      <c r="L69">
+        <v>101.8</v>
+      </c>
+      <c r="M69">
+        <v>-11.76</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="2">
+        <v>387500</v>
+      </c>
+      <c r="D70" s="3">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="E70">
+        <v>0.31</v>
+      </c>
+      <c r="F70">
+        <v>1.17</v>
+      </c>
+      <c r="G70">
+        <v>2.92</v>
+      </c>
+      <c r="H70" s="4">
+        <v>76848.399999999994</v>
+      </c>
+      <c r="I70">
+        <v>0.05</v>
+      </c>
+      <c r="J70">
+        <v>89</v>
+      </c>
+      <c r="K70">
+        <v>89</v>
+      </c>
+      <c r="L70">
+        <v>101.55</v>
+      </c>
+      <c r="M70">
+        <v>-2.76</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A5DC813-ED3D-4C14-BFD6-72ECEE3EB76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1D3F5F7-08C1-4EBD-848C-6DCFAF9610F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{7E291988-C5EE-4736-A064-6EA78F68D55A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{EDCB5021-593E-4C50-B2F1-2FC3BD4B9FF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="157">
   <si>
     <t>종목코드</t>
   </si>
@@ -78,6 +78,12 @@
     <t>삼성화재</t>
   </si>
   <si>
+    <t>001040</t>
+  </si>
+  <si>
+    <t>CJ</t>
+  </si>
+  <si>
     <t>001120</t>
   </si>
   <si>
@@ -96,6 +102,24 @@
     <t>세아베스틸지주</t>
   </si>
   <si>
+    <t>001680</t>
+  </si>
+  <si>
+    <t>대상</t>
+  </si>
+  <si>
+    <t>001800</t>
+  </si>
+  <si>
+    <t>오리온홀딩스</t>
+  </si>
+  <si>
+    <t>003230</t>
+  </si>
+  <si>
+    <t>삼양식품</t>
+  </si>
+  <si>
     <t>003540</t>
   </si>
   <si>
@@ -120,6 +144,12 @@
     <t>현대차</t>
   </si>
   <si>
+    <t>005440</t>
+  </si>
+  <si>
+    <t>현대지에프홀딩스</t>
+  </si>
+  <si>
     <t>005830</t>
   </si>
   <si>
@@ -132,18 +162,78 @@
     <t>NH투자증권</t>
   </si>
   <si>
+    <t>006260</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>006800</t>
+  </si>
+  <si>
+    <t>미래에셋증권</t>
+  </si>
+  <si>
+    <t>007310</t>
+  </si>
+  <si>
+    <t>오뚜기</t>
+  </si>
+  <si>
     <t>007340</t>
   </si>
   <si>
     <t>DN오토모티브</t>
   </si>
   <si>
+    <t>009450</t>
+  </si>
+  <si>
+    <t>경동나비엔</t>
+  </si>
+  <si>
     <t>009970</t>
   </si>
   <si>
     <t>영원무역홀딩스</t>
   </si>
   <si>
+    <t>010120</t>
+  </si>
+  <si>
+    <t>LS ELECTRIC</t>
+  </si>
+  <si>
+    <t>011070</t>
+  </si>
+  <si>
+    <t>LG이노텍</t>
+  </si>
+  <si>
+    <t>012330</t>
+  </si>
+  <si>
+    <t>현대모비스</t>
+  </si>
+  <si>
+    <t>012510</t>
+  </si>
+  <si>
+    <t>더존비즈온</t>
+  </si>
+  <si>
+    <t>014680</t>
+  </si>
+  <si>
+    <t>한솔케미칼</t>
+  </si>
+  <si>
+    <t>014830</t>
+  </si>
+  <si>
+    <t>유니드</t>
+  </si>
+  <si>
     <t>016360</t>
   </si>
   <si>
@@ -162,12 +252,48 @@
     <t>현대엘리베이터</t>
   </si>
   <si>
+    <t>018260</t>
+  </si>
+  <si>
+    <t>삼성에스디에스</t>
+  </si>
+  <si>
+    <t>018670</t>
+  </si>
+  <si>
+    <t>SK가스</t>
+  </si>
+  <si>
+    <t>023590</t>
+  </si>
+  <si>
+    <t>다우기술</t>
+  </si>
+  <si>
     <t>024110</t>
   </si>
   <si>
     <t>기업은행</t>
   </si>
   <si>
+    <t>025540</t>
+  </si>
+  <si>
+    <t>한국단자</t>
+  </si>
+  <si>
+    <t>026890</t>
+  </si>
+  <si>
+    <t>스틱인베스트먼트</t>
+  </si>
+  <si>
+    <t>028260</t>
+  </si>
+  <si>
+    <t>삼성물산</t>
+  </si>
+  <si>
     <t>029780</t>
   </si>
   <si>
@@ -186,6 +312,12 @@
     <t>KT</t>
   </si>
   <si>
+    <t>031430</t>
+  </si>
+  <si>
+    <t>신세계인터내셔날</t>
+  </si>
+  <si>
     <t>032640</t>
   </si>
   <si>
@@ -210,12 +342,48 @@
     <t>강원랜드</t>
   </si>
   <si>
+    <t>035420</t>
+  </si>
+  <si>
+    <t>NAVER</t>
+  </si>
+  <si>
     <t>036460</t>
   </si>
   <si>
     <t>한국가스공사</t>
   </si>
   <si>
+    <t>039490</t>
+  </si>
+  <si>
+    <t>키움증권</t>
+  </si>
+  <si>
+    <t>042700</t>
+  </si>
+  <si>
+    <t>한미반도체</t>
+  </si>
+  <si>
+    <t>047050</t>
+  </si>
+  <si>
+    <t>포스코인터내셔널</t>
+  </si>
+  <si>
+    <t>047810</t>
+  </si>
+  <si>
+    <t>한국항공우주</t>
+  </si>
+  <si>
+    <t>052690</t>
+  </si>
+  <si>
+    <t>한전기술</t>
+  </si>
+  <si>
     <t>055550</t>
   </si>
   <si>
@@ -234,18 +402,54 @@
     <t>GS</t>
   </si>
   <si>
+    <t>079550</t>
+  </si>
+  <si>
+    <t>LIG넥스원</t>
+  </si>
+  <si>
     <t>086790</t>
   </si>
   <si>
     <t>하나금융지주</t>
   </si>
   <si>
+    <t>090430</t>
+  </si>
+  <si>
+    <t>아모레퍼시픽</t>
+  </si>
+  <si>
+    <t>097950</t>
+  </si>
+  <si>
+    <t>CJ제일제당</t>
+  </si>
+  <si>
     <t>105560</t>
   </si>
   <si>
     <t>KB금융</t>
   </si>
   <si>
+    <t>120110</t>
+  </si>
+  <si>
+    <t>코오롱인더</t>
+  </si>
+  <si>
+    <t>128940</t>
+  </si>
+  <si>
+    <t>한미약품</t>
+  </si>
+  <si>
+    <t>138040</t>
+  </si>
+  <si>
+    <t>메리츠금융지주</t>
+  </si>
+  <si>
     <t>138930</t>
   </si>
   <si>
@@ -270,10 +474,22 @@
     <t>JB금융지주</t>
   </si>
   <si>
+    <t>185750</t>
+  </si>
+  <si>
+    <t>종근당</t>
+  </si>
+  <si>
     <t>192080</t>
   </si>
   <si>
     <t>더블유게임즈</t>
+  </si>
+  <si>
+    <t>271560</t>
+  </si>
+  <si>
+    <t>오리온</t>
   </si>
   <si>
     <t>316140</t>
@@ -654,13 +870,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2CD6CDD-7DD5-4854-8A7D-03BED52CAE80}">
-  <dimension ref="A1:M38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8C0DCC-1005-4FFC-B3CB-1340BF375E42}">
+  <dimension ref="A1:M74"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
@@ -843,37 +1059,37 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>42600</v>
+        <v>218500</v>
       </c>
       <c r="D5" s="3">
-        <v>-4.7E-2</v>
+        <v>-9.1000000000000004E-3</v>
       </c>
       <c r="E5">
-        <v>7.12</v>
+        <v>1.83</v>
       </c>
       <c r="F5">
-        <v>9.6199999999999992</v>
+        <v>9.24</v>
       </c>
       <c r="G5">
-        <v>12.61</v>
+        <v>3.14</v>
       </c>
       <c r="H5" s="4">
-        <v>72041.39</v>
+        <v>156275.9</v>
       </c>
       <c r="I5">
-        <v>4.6900000000000004</v>
+        <v>1.37</v>
       </c>
       <c r="J5">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="K5">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="L5">
-        <v>99.06</v>
+        <v>100.73</v>
       </c>
       <c r="M5">
-        <v>-10.69</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -884,37 +1100,37 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>90300</v>
+        <v>42600</v>
       </c>
       <c r="D6" s="3">
-        <v>-6.4199999999999993E-2</v>
+        <v>-4.7E-2</v>
       </c>
       <c r="E6">
-        <v>4.05</v>
+        <v>7.12</v>
       </c>
       <c r="F6">
-        <v>7.82</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="G6">
-        <v>6.06</v>
+        <v>12.61</v>
       </c>
       <c r="H6" s="4">
-        <v>65679.45</v>
+        <v>72041.39</v>
       </c>
       <c r="I6">
-        <v>1.66</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="J6">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K6">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="L6">
-        <v>112.16</v>
+        <v>99.06</v>
       </c>
       <c r="M6">
-        <v>1.8</v>
+        <v>-10.69</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -925,37 +1141,37 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>69100</v>
+        <v>90300</v>
       </c>
       <c r="D7" s="3">
-        <v>4.4000000000000003E-3</v>
+        <v>-6.4199999999999993E-2</v>
       </c>
       <c r="E7">
-        <v>1.04</v>
+        <v>4.05</v>
       </c>
       <c r="F7">
-        <v>3.97</v>
+        <v>7.82</v>
       </c>
       <c r="G7">
-        <v>4.21</v>
+        <v>6.06</v>
       </c>
       <c r="H7" s="4">
-        <v>53899.69</v>
+        <v>65679.45</v>
       </c>
       <c r="I7">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="J7">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="K7">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="L7">
-        <v>91.69</v>
+        <v>112.16</v>
       </c>
       <c r="M7">
-        <v>-7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -966,37 +1182,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>44850</v>
+        <v>69100</v>
       </c>
       <c r="D8" s="3">
-        <v>-3.44E-2</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="E8">
-        <v>4.57</v>
+        <v>1.04</v>
       </c>
       <c r="F8">
-        <v>7.42</v>
+        <v>3.97</v>
       </c>
       <c r="G8">
-        <v>4.55</v>
+        <v>4.21</v>
       </c>
       <c r="H8" s="4">
-        <v>42814.52</v>
+        <v>53899.69</v>
       </c>
       <c r="I8">
-        <v>2.68</v>
+        <v>1.74</v>
       </c>
       <c r="J8">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K8">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="L8">
-        <v>119.7</v>
+        <v>91.69</v>
       </c>
       <c r="M8">
-        <v>-8.4700000000000006</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1007,37 +1223,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>107700</v>
+        <v>22600</v>
       </c>
       <c r="D9" s="3">
-        <v>4.1599999999999998E-2</v>
+        <v>-8.8000000000000005E-3</v>
       </c>
       <c r="E9">
-        <v>2.16</v>
+        <v>6.94</v>
       </c>
       <c r="F9">
-        <v>5.36</v>
+        <v>6.38</v>
       </c>
       <c r="G9">
-        <v>5.18</v>
+        <v>6.21</v>
       </c>
       <c r="H9" s="4">
-        <v>177736.27</v>
+        <v>39784.050000000003</v>
       </c>
       <c r="I9">
-        <v>2.88</v>
+        <v>3.76</v>
       </c>
       <c r="J9">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="K9">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="L9">
-        <v>112.75</v>
+        <v>99.57</v>
       </c>
       <c r="M9">
-        <v>9.34</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1048,37 +1264,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>13920</v>
+        <v>23850</v>
       </c>
       <c r="D10" s="3">
-        <v>-3.2000000000000001E-2</v>
+        <v>-1.04E-2</v>
       </c>
       <c r="E10">
-        <v>9.44</v>
+        <v>7.03</v>
       </c>
       <c r="F10">
-        <v>10.67</v>
+        <v>5.14</v>
       </c>
       <c r="G10">
-        <v>9.86</v>
+        <v>5.26</v>
       </c>
       <c r="H10" s="4">
-        <v>19219.419999999998</v>
+        <v>38512.769999999997</v>
       </c>
       <c r="I10">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="J10">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K10">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="L10">
-        <v>107.47</v>
+        <v>102.95</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1089,37 +1305,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>674000</v>
+        <v>1221000</v>
       </c>
       <c r="D11" s="3">
-        <v>0.1067</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="E11">
-        <v>12.43</v>
+        <v>39.369999999999997</v>
       </c>
       <c r="F11">
-        <v>10.08</v>
+        <v>41.29</v>
       </c>
       <c r="G11">
-        <v>11.82</v>
+        <v>27.7</v>
       </c>
       <c r="H11" s="4">
-        <v>429918.88</v>
+        <v>144393.44</v>
       </c>
       <c r="I11">
-        <v>1.78</v>
+        <v>0.27</v>
       </c>
       <c r="J11">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="K11">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="L11">
-        <v>130.29</v>
+        <v>104.53</v>
       </c>
       <c r="M11">
-        <v>32.42</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1130,37 +1346,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>183100</v>
+        <v>44850</v>
       </c>
       <c r="D12" s="3">
-        <v>-0.109</v>
+        <v>-3.44E-2</v>
       </c>
       <c r="E12">
-        <v>18.96</v>
+        <v>4.57</v>
       </c>
       <c r="F12">
-        <v>19.43</v>
+        <v>7.42</v>
       </c>
       <c r="G12">
-        <v>18.8</v>
+        <v>4.55</v>
       </c>
       <c r="H12" s="4">
-        <v>144109.65</v>
+        <v>42814.52</v>
       </c>
       <c r="I12">
-        <v>3.71</v>
+        <v>2.68</v>
       </c>
       <c r="J12">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K12">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L12">
-        <v>106.9</v>
+        <v>119.7</v>
       </c>
       <c r="M12">
-        <v>-4.78</v>
+        <v>-8.4700000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1171,37 +1387,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>35500</v>
+        <v>107700</v>
       </c>
       <c r="D13" s="3">
-        <v>-2.7400000000000001E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
       <c r="E13">
-        <v>8.73</v>
+        <v>2.16</v>
       </c>
       <c r="F13">
-        <v>11.57</v>
+        <v>5.36</v>
       </c>
       <c r="G13">
-        <v>6.85</v>
+        <v>5.18</v>
       </c>
       <c r="H13" s="4">
-        <v>24348.21</v>
+        <v>177736.27</v>
       </c>
       <c r="I13">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="J13">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K13">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L13">
-        <v>115.84</v>
+        <v>112.75</v>
       </c>
       <c r="M13">
-        <v>-9.44</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1212,37 +1428,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>27200</v>
+        <v>13920</v>
       </c>
       <c r="D14" s="3">
-        <v>-3.3700000000000001E-2</v>
+        <v>-3.2000000000000001E-2</v>
       </c>
       <c r="E14">
-        <v>19.78</v>
+        <v>9.44</v>
       </c>
       <c r="F14">
-        <v>13.82</v>
+        <v>10.67</v>
       </c>
       <c r="G14">
-        <v>23.29</v>
+        <v>9.86</v>
       </c>
       <c r="H14" s="4">
-        <v>32624.26</v>
+        <v>19219.419999999998</v>
       </c>
       <c r="I14">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="J14">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K14">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="L14">
-        <v>96.18</v>
+        <v>107.47</v>
       </c>
       <c r="M14">
-        <v>-13.38</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1253,37 +1469,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>249500</v>
+        <v>674000</v>
       </c>
       <c r="D15" s="3">
-        <v>1.84E-2</v>
+        <v>0.1067</v>
       </c>
       <c r="E15">
-        <v>13.17</v>
+        <v>12.43</v>
       </c>
       <c r="F15">
-        <v>11.69</v>
+        <v>10.08</v>
       </c>
       <c r="G15">
-        <v>18.010000000000002</v>
+        <v>11.82</v>
       </c>
       <c r="H15" s="4">
-        <v>207156.6</v>
+        <v>429918.88</v>
       </c>
       <c r="I15">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="J15">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K15">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="L15">
-        <v>112.06</v>
+        <v>130.29</v>
       </c>
       <c r="M15">
-        <v>10.64</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1294,37 +1510,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>106800</v>
+        <v>16000</v>
       </c>
       <c r="D16" s="3">
-        <v>-3.8699999999999998E-2</v>
+        <v>-3.6700000000000003E-2</v>
       </c>
       <c r="E16">
-        <v>12.89</v>
+        <v>23.02</v>
       </c>
       <c r="F16">
-        <v>13.94</v>
+        <v>13.72</v>
       </c>
       <c r="G16">
-        <v>9.44</v>
+        <v>25.35</v>
       </c>
       <c r="H16" s="4">
-        <v>87743.72</v>
+        <v>25051.51</v>
       </c>
       <c r="I16">
-        <v>3.28</v>
+        <v>1.31</v>
       </c>
       <c r="J16">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K16">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="L16">
-        <v>108.33</v>
+        <v>126.83</v>
       </c>
       <c r="M16">
-        <v>-6.72</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1335,37 +1551,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>79800</v>
+        <v>183100</v>
       </c>
       <c r="D17" s="3">
-        <v>-3.04E-2</v>
+        <v>-0.109</v>
       </c>
       <c r="E17">
-        <v>10.83</v>
+        <v>18.96</v>
       </c>
       <c r="F17">
-        <v>3.37</v>
+        <v>19.43</v>
       </c>
       <c r="G17">
-        <v>9.48</v>
+        <v>18.8</v>
       </c>
       <c r="H17" s="4">
-        <v>54894.12</v>
+        <v>144109.65</v>
       </c>
       <c r="I17">
-        <v>4.4400000000000004</v>
+        <v>3.71</v>
       </c>
       <c r="J17">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K17">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L17">
-        <v>104.2</v>
+        <v>106.9</v>
       </c>
       <c r="M17">
-        <v>-1.24</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1376,37 +1592,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>98700</v>
+        <v>35500</v>
       </c>
       <c r="D18" s="3">
-        <v>-1.7899999999999999E-2</v>
+        <v>-2.7400000000000001E-2</v>
       </c>
       <c r="E18">
-        <v>14.42</v>
+        <v>8.73</v>
       </c>
       <c r="F18">
-        <v>24.2</v>
+        <v>11.57</v>
       </c>
       <c r="G18">
-        <v>15.82</v>
+        <v>6.85</v>
       </c>
       <c r="H18" s="4">
-        <v>36460.550000000003</v>
+        <v>24348.21</v>
       </c>
       <c r="I18">
-        <v>5.57</v>
+        <v>2.68</v>
       </c>
       <c r="J18">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K18">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L18">
-        <v>97.6</v>
+        <v>115.84</v>
       </c>
       <c r="M18">
-        <v>-10.44</v>
+        <v>-9.44</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1417,37 +1633,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>25750</v>
+        <v>284500</v>
       </c>
       <c r="D19" s="3">
-        <v>-2.8299999999999999E-2</v>
+        <v>-1.9E-2</v>
       </c>
       <c r="E19">
-        <v>8.06</v>
+        <v>5.09</v>
       </c>
       <c r="F19">
-        <v>8.64</v>
+        <v>7.08</v>
       </c>
       <c r="G19">
-        <v>8.77</v>
+        <v>11.63</v>
       </c>
       <c r="H19" s="4">
-        <v>44443.18</v>
+        <v>158418.68</v>
       </c>
       <c r="I19">
-        <v>4.1399999999999997</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="J19">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K19">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L19">
-        <v>104.82</v>
+        <v>116.82</v>
       </c>
       <c r="M19">
-        <v>-9.81</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1458,37 +1674,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>63000</v>
+        <v>72000</v>
       </c>
       <c r="D20" s="3">
-        <v>-1.6000000000000001E-3</v>
+        <v>-2.1700000000000001E-2</v>
       </c>
       <c r="E20">
-        <v>7.45</v>
+        <v>7.94</v>
       </c>
       <c r="F20">
-        <v>7.45</v>
+        <v>10.76</v>
       </c>
       <c r="G20">
-        <v>7.69</v>
+        <v>5.75</v>
       </c>
       <c r="H20" s="4">
-        <v>79986.48</v>
+        <v>18036.09</v>
       </c>
       <c r="I20">
-        <v>4.4400000000000004</v>
+        <v>0.35</v>
       </c>
       <c r="J20">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K20">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="L20">
-        <v>103.99</v>
+        <v>128.1</v>
       </c>
       <c r="M20">
-        <v>-6.53</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1499,37 +1715,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>21950</v>
+        <v>397500</v>
       </c>
       <c r="D21" s="3">
-        <v>-4.4999999999999997E-3</v>
+        <v>-3.8E-3</v>
       </c>
       <c r="E21">
-        <v>15.12</v>
+        <v>6.85</v>
       </c>
       <c r="F21">
-        <v>13.07</v>
+        <v>6.19</v>
       </c>
       <c r="G21">
-        <v>15.58</v>
+        <v>10.64</v>
       </c>
       <c r="H21" s="4">
-        <v>15310.06</v>
+        <v>605494.72</v>
       </c>
       <c r="I21">
-        <v>5.6</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J21">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="K21">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L21">
-        <v>101.34</v>
+        <v>100.54</v>
       </c>
       <c r="M21">
-        <v>-2.23</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1540,37 +1756,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>63800</v>
+        <v>27200</v>
       </c>
       <c r="D22" s="3">
-        <v>-1.24E-2</v>
+        <v>-3.3700000000000001E-2</v>
       </c>
       <c r="E22">
-        <v>2.85</v>
+        <v>19.78</v>
       </c>
       <c r="F22">
-        <v>12.83</v>
+        <v>13.82</v>
       </c>
       <c r="G22">
-        <v>5.63</v>
+        <v>23.29</v>
       </c>
       <c r="H22" s="4">
-        <v>71073.47</v>
+        <v>32624.26</v>
       </c>
       <c r="I22">
-        <v>3.13</v>
+        <v>3.68</v>
       </c>
       <c r="J22">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K22">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="L22">
-        <v>104.27</v>
+        <v>96.18</v>
       </c>
       <c r="M22">
-        <v>-7.4</v>
+        <v>-13.38</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1581,37 +1797,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>16540</v>
+        <v>64300</v>
       </c>
       <c r="D23" s="3">
-        <v>-7.1300000000000002E-2</v>
+        <v>-4.0300000000000002E-2</v>
       </c>
       <c r="E23">
-        <v>4.4000000000000004</v>
+        <v>19.43</v>
       </c>
       <c r="F23">
-        <v>6.71</v>
+        <v>13.05</v>
       </c>
       <c r="G23">
-        <v>6.75</v>
+        <v>15.2</v>
       </c>
       <c r="H23" s="4">
-        <v>20394.86</v>
+        <v>51878.87</v>
       </c>
       <c r="I23">
-        <v>3.93</v>
+        <v>1.01</v>
       </c>
       <c r="J23">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="K23">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="L23">
-        <v>99.82</v>
+        <v>102.23</v>
       </c>
       <c r="M23">
-        <v>-5.49</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1622,37 +1838,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>230000</v>
+        <v>249500</v>
       </c>
       <c r="D24" s="3">
-        <v>-3.7699999999999997E-2</v>
+        <v>1.84E-2</v>
       </c>
       <c r="E24">
-        <v>4.66</v>
+        <v>13.17</v>
       </c>
       <c r="F24">
-        <v>4.66</v>
+        <v>11.69</v>
       </c>
       <c r="G24">
-        <v>4.88</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H24" s="4">
-        <v>324173.33</v>
+        <v>207156.6</v>
       </c>
       <c r="I24">
-        <v>2.2999999999999998</v>
+        <v>2.14</v>
       </c>
       <c r="J24">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K24">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L24">
-        <v>111.88</v>
+        <v>112.06</v>
       </c>
       <c r="M24">
-        <v>5.0199999999999996</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1663,37 +1879,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>163100</v>
+        <v>787000</v>
       </c>
       <c r="D25" s="3">
-        <v>-3.8899999999999997E-2</v>
+        <v>-1.9900000000000001E-2</v>
       </c>
       <c r="E25">
-        <v>12.66</v>
+        <v>13.44</v>
       </c>
       <c r="F25">
-        <v>11.88</v>
+        <v>14.22</v>
       </c>
       <c r="G25">
-        <v>11.14</v>
+        <v>10.67</v>
       </c>
       <c r="H25" s="4">
-        <v>83639.03</v>
+        <v>66213.7</v>
       </c>
       <c r="I25">
-        <v>3.31</v>
+        <v>0.37</v>
       </c>
       <c r="J25">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K25">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="L25">
-        <v>98.41</v>
+        <v>119.73</v>
       </c>
       <c r="M25">
-        <v>-7.91</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1704,37 +1920,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>19050</v>
+        <v>319000</v>
       </c>
       <c r="D26" s="3">
-        <v>-1.7999999999999999E-2</v>
+        <v>-7.5399999999999995E-2</v>
       </c>
       <c r="E26">
-        <v>12.08</v>
+        <v>8.92</v>
       </c>
       <c r="F26">
-        <v>8.58</v>
+        <v>5.05</v>
       </c>
       <c r="G26">
-        <v>8.39</v>
+        <v>15.79</v>
       </c>
       <c r="H26" s="4">
-        <v>19234.22</v>
+        <v>231811.94</v>
       </c>
       <c r="I26">
-        <v>6.14</v>
+        <v>0.66</v>
       </c>
       <c r="J26">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="K26">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="L26">
-        <v>103.52</v>
+        <v>123.11</v>
       </c>
       <c r="M26">
-        <v>-1.75</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1745,37 +1961,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>41200</v>
+        <v>517000</v>
       </c>
       <c r="D27" s="3">
-        <v>-6.1499999999999999E-2</v>
+        <v>-2.2700000000000001E-2</v>
       </c>
       <c r="E27">
-        <v>11.21</v>
+        <v>9.35</v>
       </c>
       <c r="F27">
-        <v>6.55</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="G27">
-        <v>6.4</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="H27" s="4">
-        <v>122131.86</v>
+        <v>528506.16</v>
       </c>
       <c r="I27">
-        <v>3.53</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="J27">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="K27">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="L27">
-        <v>97.96</v>
+        <v>114.41</v>
       </c>
       <c r="M27">
-        <v>-9.65</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1786,37 +2002,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>96900</v>
+        <v>118400</v>
       </c>
       <c r="D28" s="3">
-        <v>-0.03</v>
+        <v>-8.0000000000000004E-4</v>
       </c>
       <c r="E28">
-        <v>8.11</v>
+        <v>17.03</v>
       </c>
       <c r="F28">
-        <v>10.44</v>
+        <v>12.71</v>
       </c>
       <c r="G28">
-        <v>8.66</v>
+        <v>8.98</v>
       </c>
       <c r="H28" s="4">
-        <v>119742.76</v>
+        <v>20872.84</v>
       </c>
       <c r="I28">
-        <v>2.23</v>
+        <v>0.4</v>
       </c>
       <c r="J28">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="K28">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="L28">
-        <v>101.97</v>
+        <v>122.33</v>
       </c>
       <c r="M28">
-        <v>-5</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1827,37 +2043,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>258500</v>
+        <v>338000</v>
       </c>
       <c r="D29" s="3">
-        <v>-3.1800000000000002E-2</v>
+        <v>2.4199999999999999E-2</v>
       </c>
       <c r="E29">
-        <v>11.54</v>
+        <v>13.48</v>
       </c>
       <c r="F29">
-        <v>20.98</v>
+        <v>17.11</v>
       </c>
       <c r="G29">
-        <v>9.6</v>
+        <v>15.98</v>
       </c>
       <c r="H29" s="4">
-        <v>189057.03</v>
+        <v>99320.85</v>
       </c>
       <c r="I29">
-        <v>1.54</v>
+        <v>0.62</v>
       </c>
       <c r="J29">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K29">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L29">
-        <v>107.8</v>
+        <v>113.65</v>
       </c>
       <c r="M29">
-        <v>-11.62</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1868,37 +2084,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>68700</v>
+        <v>82100</v>
       </c>
       <c r="D30" s="3">
-        <v>-2.1399999999999999E-2</v>
+        <v>-4.7999999999999996E-3</v>
       </c>
       <c r="E30">
-        <v>4.12</v>
+        <v>7.96</v>
       </c>
       <c r="F30">
-        <v>5.22</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="G30">
-        <v>11.01</v>
+        <v>7.62</v>
       </c>
       <c r="H30" s="4">
-        <v>151788</v>
+        <v>156393.74</v>
       </c>
       <c r="I30">
-        <v>3.93</v>
+        <v>2.19</v>
       </c>
       <c r="J30">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="K30">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="L30">
-        <v>98.27</v>
+        <v>100.57</v>
       </c>
       <c r="M30">
-        <v>-9.25</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1909,37 +2125,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>121800</v>
+        <v>106800</v>
       </c>
       <c r="D31" s="3">
-        <v>-2.4799999999999999E-2</v>
+        <v>-3.8699999999999998E-2</v>
       </c>
       <c r="E31">
-        <v>9.11</v>
+        <v>12.89</v>
       </c>
       <c r="F31">
-        <v>10.57</v>
+        <v>13.94</v>
       </c>
       <c r="G31">
-        <v>9.4</v>
+        <v>9.44</v>
       </c>
       <c r="H31" s="4">
-        <v>159337.74</v>
+        <v>87743.72</v>
       </c>
       <c r="I31">
-        <v>2.96</v>
+        <v>3.28</v>
       </c>
       <c r="J31">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K31">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L31">
-        <v>102.74</v>
+        <v>108.33</v>
       </c>
       <c r="M31">
-        <v>-7.24</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1950,37 +2166,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>159000</v>
+        <v>79800</v>
       </c>
       <c r="D32" s="3">
-        <v>-3.8100000000000002E-2</v>
+        <v>-3.04E-2</v>
       </c>
       <c r="E32">
-        <v>8.86</v>
+        <v>10.83</v>
       </c>
       <c r="F32">
-        <v>11.63</v>
+        <v>3.37</v>
       </c>
       <c r="G32">
-        <v>8.51</v>
+        <v>9.48</v>
       </c>
       <c r="H32" s="4">
-        <v>160038.65</v>
+        <v>54894.12</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="J32">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K32">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="L32">
-        <v>103.09</v>
+        <v>104.2</v>
       </c>
       <c r="M32">
-        <v>-5.81</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -1991,37 +2207,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>19930</v>
+        <v>98700</v>
       </c>
       <c r="D33" s="3">
-        <v>-2.7799999999999998E-2</v>
+        <v>-1.7899999999999999E-2</v>
       </c>
       <c r="E33">
-        <v>6.96</v>
+        <v>14.42</v>
       </c>
       <c r="F33">
-        <v>9.58</v>
+        <v>24.2</v>
       </c>
       <c r="G33">
-        <v>7.18</v>
+        <v>15.82</v>
       </c>
       <c r="H33" s="4">
-        <v>34223.949999999997</v>
+        <v>36460.550000000003</v>
       </c>
       <c r="I33">
-        <v>3.26</v>
+        <v>5.57</v>
       </c>
       <c r="J33">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K33">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L33">
-        <v>101.69</v>
+        <v>97.6</v>
       </c>
       <c r="M33">
-        <v>-12.01</v>
+        <v>-10.44</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2032,37 +2248,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>18390</v>
+        <v>195000</v>
       </c>
       <c r="D34" s="3">
-        <v>-3.6700000000000003E-2</v>
+        <v>1.9300000000000001E-2</v>
       </c>
       <c r="E34">
-        <v>3.6</v>
+        <v>8.42</v>
       </c>
       <c r="F34">
-        <v>9.42</v>
+        <v>8.11</v>
       </c>
       <c r="G34">
-        <v>5.91</v>
+        <v>10.29</v>
       </c>
       <c r="H34" s="4">
-        <v>38541.279999999999</v>
+        <v>124608.94</v>
       </c>
       <c r="I34">
-        <v>2.72</v>
+        <v>1.49</v>
       </c>
       <c r="J34">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="K34">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="L34">
-        <v>100.32</v>
+        <v>111.95</v>
       </c>
       <c r="M34">
-        <v>-15.06</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2073,37 +2289,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>72900</v>
+        <v>233000</v>
       </c>
       <c r="D35" s="3">
-        <v>-3.95E-2</v>
+        <v>-1.89E-2</v>
       </c>
       <c r="E35">
-        <v>10.79</v>
+        <v>6.74</v>
       </c>
       <c r="F35">
-        <v>10.55</v>
+        <v>11.86</v>
       </c>
       <c r="G35">
-        <v>8.93</v>
+        <v>10.37</v>
       </c>
       <c r="H35" s="4">
-        <v>92723.77</v>
+        <v>316132.59999999998</v>
       </c>
       <c r="I35">
-        <v>2.74</v>
+        <v>3.43</v>
       </c>
       <c r="J35">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="K35">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="L35">
-        <v>104.03</v>
+        <v>100.59</v>
       </c>
       <c r="M35">
-        <v>-3.57</v>
+        <v>-5.09</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2114,37 +2330,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>31750</v>
+        <v>54300</v>
       </c>
       <c r="D36" s="3">
-        <v>-1.7000000000000001E-2</v>
+        <v>-4.9000000000000002E-2</v>
       </c>
       <c r="E36">
-        <v>12.8</v>
+        <v>13.16</v>
       </c>
       <c r="F36">
-        <v>13.49</v>
+        <v>16.66</v>
       </c>
       <c r="G36">
-        <v>12.93</v>
+        <v>13.29</v>
       </c>
       <c r="H36" s="4">
-        <v>31004.78</v>
+        <v>73964.55</v>
       </c>
       <c r="I36">
-        <v>3.13</v>
+        <v>2.58</v>
       </c>
       <c r="J36">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K36">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L36">
-        <v>103.53</v>
+        <v>101.56</v>
       </c>
       <c r="M36">
-        <v>-15.33</v>
+        <v>-9.8000000000000007</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2155,37 +2371,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>53000</v>
+        <v>25750</v>
       </c>
       <c r="D37" s="3">
-        <v>-2.75E-2</v>
+        <v>-2.8299999999999999E-2</v>
       </c>
       <c r="E37">
-        <v>18.690000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="F37">
-        <v>11.56</v>
+        <v>8.64</v>
       </c>
       <c r="G37">
-        <v>6.83</v>
+        <v>8.77</v>
       </c>
       <c r="H37" s="4">
-        <v>57293.3</v>
+        <v>44443.18</v>
       </c>
       <c r="I37">
-        <v>2.2599999999999998</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="J37">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="K37">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="L37">
-        <v>97.48</v>
+        <v>104.82</v>
       </c>
       <c r="M37">
-        <v>-2.93</v>
+        <v>-9.81</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2196,36 +2412,1512 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
+        <v>80700</v>
+      </c>
+      <c r="D38" s="3">
+        <v>-2.8899999999999999E-2</v>
+      </c>
+      <c r="E38">
+        <v>14.16</v>
+      </c>
+      <c r="F38">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>9.31</v>
+      </c>
+      <c r="H38" s="4">
+        <v>112832.69</v>
+      </c>
+      <c r="I38">
+        <v>2.73</v>
+      </c>
+      <c r="J38">
+        <v>52</v>
+      </c>
+      <c r="K38">
+        <v>52</v>
+      </c>
+      <c r="L38">
+        <v>106.44</v>
+      </c>
+      <c r="M38">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="2">
+        <v>11910</v>
+      </c>
+      <c r="D39" s="3">
+        <v>-4.1999999999999997E-3</v>
+      </c>
+      <c r="E39">
+        <v>3.72</v>
+      </c>
+      <c r="F39">
+        <v>1.33</v>
+      </c>
+      <c r="G39">
+        <v>7.32</v>
+      </c>
+      <c r="H39" s="4">
+        <v>6359.62</v>
+      </c>
+      <c r="I39">
+        <v>2.1</v>
+      </c>
+      <c r="J39">
+        <v>43</v>
+      </c>
+      <c r="K39">
+        <v>43</v>
+      </c>
+      <c r="L39">
+        <v>101.09</v>
+      </c>
+      <c r="M39">
+        <v>-4.18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="2">
+        <v>350500</v>
+      </c>
+      <c r="D40" s="3">
+        <v>-2.64E-2</v>
+      </c>
+      <c r="E40">
+        <v>6.83</v>
+      </c>
+      <c r="F40">
+        <v>6.08</v>
+      </c>
+      <c r="G40">
+        <v>7.09</v>
+      </c>
+      <c r="H40" s="4">
+        <v>245146.58</v>
+      </c>
+      <c r="I40">
+        <v>0.74</v>
+      </c>
+      <c r="J40">
+        <v>95</v>
+      </c>
+      <c r="K40">
+        <v>95</v>
+      </c>
+      <c r="L40">
+        <v>109.52</v>
+      </c>
+      <c r="M40">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="2">
+        <v>63000</v>
+      </c>
+      <c r="D41" s="3">
+        <v>-1.6000000000000001E-3</v>
+      </c>
+      <c r="E41">
+        <v>7.45</v>
+      </c>
+      <c r="F41">
+        <v>7.45</v>
+      </c>
+      <c r="G41">
+        <v>7.69</v>
+      </c>
+      <c r="H41" s="4">
+        <v>79986.48</v>
+      </c>
+      <c r="I41">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="J41">
+        <v>85</v>
+      </c>
+      <c r="K41">
+        <v>85</v>
+      </c>
+      <c r="L41">
+        <v>103.99</v>
+      </c>
+      <c r="M41">
+        <v>-6.53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="2">
+        <v>21950</v>
+      </c>
+      <c r="D42" s="3">
+        <v>-4.4999999999999997E-3</v>
+      </c>
+      <c r="E42">
+        <v>15.12</v>
+      </c>
+      <c r="F42">
+        <v>13.07</v>
+      </c>
+      <c r="G42">
+        <v>15.58</v>
+      </c>
+      <c r="H42" s="4">
+        <v>15310.06</v>
+      </c>
+      <c r="I42">
+        <v>5.6</v>
+      </c>
+      <c r="J42">
+        <v>54</v>
+      </c>
+      <c r="K42">
+        <v>54</v>
+      </c>
+      <c r="L42">
+        <v>101.34</v>
+      </c>
+      <c r="M42">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="2">
+        <v>63800</v>
+      </c>
+      <c r="D43" s="3">
+        <v>-1.24E-2</v>
+      </c>
+      <c r="E43">
+        <v>2.85</v>
+      </c>
+      <c r="F43">
+        <v>12.83</v>
+      </c>
+      <c r="G43">
+        <v>5.63</v>
+      </c>
+      <c r="H43" s="4">
+        <v>71073.47</v>
+      </c>
+      <c r="I43">
+        <v>3.13</v>
+      </c>
+      <c r="J43">
+        <v>87</v>
+      </c>
+      <c r="K43">
+        <v>87</v>
+      </c>
+      <c r="L43">
+        <v>104.27</v>
+      </c>
+      <c r="M43">
+        <v>-7.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="2">
+        <v>13290</v>
+      </c>
+      <c r="D44" s="3">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="E44">
+        <v>3.85</v>
+      </c>
+      <c r="F44">
+        <v>0.43</v>
+      </c>
+      <c r="G44">
+        <v>7.94</v>
+      </c>
+      <c r="H44" s="4">
+        <v>23881.66</v>
+      </c>
+      <c r="I44">
+        <v>3.01</v>
+      </c>
+      <c r="J44">
+        <v>11</v>
+      </c>
+      <c r="K44">
+        <v>11</v>
+      </c>
+      <c r="L44">
+        <v>107.09</v>
+      </c>
+      <c r="M44">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="2">
+        <v>16540</v>
+      </c>
+      <c r="D45" s="3">
+        <v>-7.1300000000000002E-2</v>
+      </c>
+      <c r="E45">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F45">
+        <v>6.71</v>
+      </c>
+      <c r="G45">
+        <v>6.75</v>
+      </c>
+      <c r="H45" s="4">
+        <v>20394.86</v>
+      </c>
+      <c r="I45">
+        <v>3.93</v>
+      </c>
+      <c r="J45">
+        <v>83</v>
+      </c>
+      <c r="K45">
+        <v>83</v>
+      </c>
+      <c r="L45">
+        <v>99.82</v>
+      </c>
+      <c r="M45">
+        <v>-5.49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="2">
+        <v>230000</v>
+      </c>
+      <c r="D46" s="3">
+        <v>-3.7699999999999997E-2</v>
+      </c>
+      <c r="E46">
+        <v>4.66</v>
+      </c>
+      <c r="F46">
+        <v>4.66</v>
+      </c>
+      <c r="G46">
+        <v>4.88</v>
+      </c>
+      <c r="H46" s="4">
+        <v>324173.33</v>
+      </c>
+      <c r="I46">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J46">
+        <v>86</v>
+      </c>
+      <c r="K46">
+        <v>86</v>
+      </c>
+      <c r="L46">
+        <v>111.88</v>
+      </c>
+      <c r="M46">
+        <v>5.0199999999999996</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="2">
+        <v>163100</v>
+      </c>
+      <c r="D47" s="3">
+        <v>-3.8899999999999997E-2</v>
+      </c>
+      <c r="E47">
+        <v>12.66</v>
+      </c>
+      <c r="F47">
+        <v>11.88</v>
+      </c>
+      <c r="G47">
+        <v>11.14</v>
+      </c>
+      <c r="H47" s="4">
+        <v>83639.03</v>
+      </c>
+      <c r="I47">
+        <v>3.31</v>
+      </c>
+      <c r="J47">
+        <v>82</v>
+      </c>
+      <c r="K47">
+        <v>82</v>
+      </c>
+      <c r="L47">
+        <v>98.41</v>
+      </c>
+      <c r="M47">
+        <v>-7.91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B48" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="2">
+        <v>19050</v>
+      </c>
+      <c r="D48" s="3">
+        <v>-1.7999999999999999E-2</v>
+      </c>
+      <c r="E48">
+        <v>12.08</v>
+      </c>
+      <c r="F48">
+        <v>8.58</v>
+      </c>
+      <c r="G48">
+        <v>8.39</v>
+      </c>
+      <c r="H48" s="4">
+        <v>19234.22</v>
+      </c>
+      <c r="I48">
+        <v>6.14</v>
+      </c>
+      <c r="J48">
+        <v>35</v>
+      </c>
+      <c r="K48">
+        <v>35</v>
+      </c>
+      <c r="L48">
+        <v>103.52</v>
+      </c>
+      <c r="M48">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="2">
+        <v>254500</v>
+      </c>
+      <c r="D49" s="3">
+        <v>-2.3E-2</v>
+      </c>
+      <c r="E49">
+        <v>7.9</v>
+      </c>
+      <c r="F49">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G49">
+        <v>5.2</v>
+      </c>
+      <c r="H49" s="4">
+        <v>178255.48</v>
+      </c>
+      <c r="I49">
+        <v>0.44</v>
+      </c>
+      <c r="J49">
+        <v>33</v>
+      </c>
+      <c r="K49">
+        <v>33</v>
+      </c>
+      <c r="L49">
+        <v>97.84</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="2">
+        <v>41200</v>
+      </c>
+      <c r="D50" s="3">
+        <v>-6.1499999999999999E-2</v>
+      </c>
+      <c r="E50">
+        <v>11.21</v>
+      </c>
+      <c r="F50">
+        <v>6.55</v>
+      </c>
+      <c r="G50">
+        <v>6.4</v>
+      </c>
+      <c r="H50" s="4">
+        <v>122131.86</v>
+      </c>
+      <c r="I50">
+        <v>3.53</v>
+      </c>
+      <c r="J50">
+        <v>44</v>
+      </c>
+      <c r="K50">
+        <v>44</v>
+      </c>
+      <c r="L50">
+        <v>97.96</v>
+      </c>
+      <c r="M50">
+        <v>-9.65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="2">
+        <v>466000</v>
+      </c>
+      <c r="D51" s="3">
+        <v>-1.17E-2</v>
+      </c>
+      <c r="E51">
+        <v>15.98</v>
+      </c>
+      <c r="F51">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="G51">
+        <v>12.25</v>
+      </c>
+      <c r="H51" s="4">
+        <v>238844.91</v>
+      </c>
+      <c r="I51">
+        <v>1.61</v>
+      </c>
+      <c r="J51">
+        <v>89</v>
+      </c>
+      <c r="K51">
+        <v>89</v>
+      </c>
+      <c r="L51">
+        <v>103.61</v>
+      </c>
+      <c r="M51">
+        <v>-5.95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="2">
+        <v>323500</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0.17419999999999999</v>
+      </c>
+      <c r="E52">
+        <v>27.43</v>
+      </c>
+      <c r="F52">
+        <v>41.23</v>
+      </c>
+      <c r="G52">
+        <v>36</v>
+      </c>
+      <c r="H52" s="4">
+        <v>7170.29</v>
+      </c>
+      <c r="I52">
+        <v>0.22</v>
+      </c>
+      <c r="J52">
+        <v>97</v>
+      </c>
+      <c r="K52">
+        <v>97</v>
+      </c>
+      <c r="L52">
+        <v>154.06</v>
+      </c>
+      <c r="M52">
+        <v>61.35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="2">
+        <v>72200</v>
+      </c>
+      <c r="D53" s="3">
+        <v>-4.4999999999999998E-2</v>
+      </c>
+      <c r="E53">
+        <v>8.14</v>
+      </c>
+      <c r="F53">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="G53">
+        <v>12.43</v>
+      </c>
+      <c r="H53" s="4">
+        <v>37401.51</v>
+      </c>
+      <c r="I53">
+        <v>2.15</v>
+      </c>
+      <c r="J53">
+        <v>69</v>
+      </c>
+      <c r="K53">
+        <v>69</v>
+      </c>
+      <c r="L53">
+        <v>106.49</v>
+      </c>
+      <c r="M53">
+        <v>-4.12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="2">
+        <v>191500</v>
+      </c>
+      <c r="D54" s="3">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="E54">
+        <v>10.42</v>
+      </c>
+      <c r="F54">
+        <v>9.58</v>
+      </c>
+      <c r="G54">
+        <v>11.34</v>
+      </c>
+      <c r="H54" s="4">
+        <v>18284.689999999999</v>
+      </c>
+      <c r="I54">
+        <v>0.26</v>
+      </c>
+      <c r="J54">
+        <v>96</v>
+      </c>
+      <c r="K54">
+        <v>96</v>
+      </c>
+      <c r="L54">
+        <v>112.05</v>
+      </c>
+      <c r="M54">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B55" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="2">
+        <v>175100</v>
+      </c>
+      <c r="D55" s="3">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="E55">
+        <v>10.4</v>
+      </c>
+      <c r="F55">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="G55">
+        <v>6.6</v>
+      </c>
+      <c r="H55" s="4">
+        <v>16324.19</v>
+      </c>
+      <c r="I55">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J55">
+        <v>90</v>
+      </c>
+      <c r="K55">
+        <v>90</v>
+      </c>
+      <c r="L55">
+        <v>117.18</v>
+      </c>
+      <c r="M55">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A56" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="2">
+        <v>96900</v>
+      </c>
+      <c r="D56" s="3">
+        <v>-0.03</v>
+      </c>
+      <c r="E56">
+        <v>8.11</v>
+      </c>
+      <c r="F56">
+        <v>10.44</v>
+      </c>
+      <c r="G56">
+        <v>8.66</v>
+      </c>
+      <c r="H56" s="4">
+        <v>119742.76</v>
+      </c>
+      <c r="I56">
+        <v>2.23</v>
+      </c>
+      <c r="J56">
+        <v>86</v>
+      </c>
+      <c r="K56">
+        <v>86</v>
+      </c>
+      <c r="L56">
+        <v>101.97</v>
+      </c>
+      <c r="M56">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A57" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="2">
+        <v>258500</v>
+      </c>
+      <c r="D57" s="3">
+        <v>-3.1800000000000002E-2</v>
+      </c>
+      <c r="E57">
+        <v>11.54</v>
+      </c>
+      <c r="F57">
+        <v>20.98</v>
+      </c>
+      <c r="G57">
+        <v>9.6</v>
+      </c>
+      <c r="H57" s="4">
+        <v>189057.03</v>
+      </c>
+      <c r="I57">
+        <v>1.54</v>
+      </c>
+      <c r="J57">
+        <v>83</v>
+      </c>
+      <c r="K57">
+        <v>83</v>
+      </c>
+      <c r="L57">
+        <v>107.8</v>
+      </c>
+      <c r="M57">
+        <v>-11.62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A58" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="2">
+        <v>68700</v>
+      </c>
+      <c r="D58" s="3">
+        <v>-2.1399999999999999E-2</v>
+      </c>
+      <c r="E58">
+        <v>4.12</v>
+      </c>
+      <c r="F58">
+        <v>5.22</v>
+      </c>
+      <c r="G58">
+        <v>11.01</v>
+      </c>
+      <c r="H58" s="4">
+        <v>151788</v>
+      </c>
+      <c r="I58">
+        <v>3.93</v>
+      </c>
+      <c r="J58">
+        <v>74</v>
+      </c>
+      <c r="K58">
+        <v>74</v>
+      </c>
+      <c r="L58">
+        <v>98.27</v>
+      </c>
+      <c r="M58">
+        <v>-9.25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A59" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" s="2">
+        <v>509000</v>
+      </c>
+      <c r="D59" s="3">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="E59">
+        <v>19.59</v>
+      </c>
+      <c r="F59">
+        <v>25.3</v>
+      </c>
+      <c r="G59">
+        <v>17.23</v>
+      </c>
+      <c r="H59" s="4">
+        <v>64298.52</v>
+      </c>
+      <c r="I59">
+        <v>0.47</v>
+      </c>
+      <c r="J59">
+        <v>77</v>
+      </c>
+      <c r="K59">
+        <v>77</v>
+      </c>
+      <c r="L59">
+        <v>106.66</v>
+      </c>
+      <c r="M59">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A60" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" s="2">
+        <v>121800</v>
+      </c>
+      <c r="D60" s="3">
+        <v>-2.4799999999999999E-2</v>
+      </c>
+      <c r="E60">
+        <v>9.11</v>
+      </c>
+      <c r="F60">
+        <v>10.57</v>
+      </c>
+      <c r="G60">
+        <v>9.4</v>
+      </c>
+      <c r="H60" s="4">
+        <v>159337.74</v>
+      </c>
+      <c r="I60">
+        <v>2.96</v>
+      </c>
+      <c r="J60">
+        <v>88</v>
+      </c>
+      <c r="K60">
+        <v>88</v>
+      </c>
+      <c r="L60">
+        <v>102.74</v>
+      </c>
+      <c r="M60">
+        <v>-7.24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A61" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="2">
+        <v>151400</v>
+      </c>
+      <c r="D61" s="3">
+        <v>-3.32E-2</v>
+      </c>
+      <c r="E61">
+        <v>11.69</v>
+      </c>
+      <c r="F61">
+        <v>5.33</v>
+      </c>
+      <c r="G61">
+        <v>6.07</v>
+      </c>
+      <c r="H61" s="4">
+        <v>77979.460000000006</v>
+      </c>
+      <c r="I61">
+        <v>0.74</v>
+      </c>
+      <c r="J61">
+        <v>30</v>
+      </c>
+      <c r="K61">
+        <v>30</v>
+      </c>
+      <c r="L61">
+        <v>100.41</v>
+      </c>
+      <c r="M61">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A62" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="2">
+        <v>214000</v>
+      </c>
+      <c r="D62" s="3">
+        <v>-9.2999999999999992E-3</v>
+      </c>
+      <c r="E62">
+        <v>1.97</v>
+      </c>
+      <c r="F62">
+        <v>4.25</v>
+      </c>
+      <c r="G62">
+        <v>5.59</v>
+      </c>
+      <c r="H62" s="4">
+        <v>481098.45</v>
+      </c>
+      <c r="I62">
+        <v>2.8</v>
+      </c>
+      <c r="J62">
+        <v>5</v>
+      </c>
+      <c r="K62">
+        <v>5</v>
+      </c>
+      <c r="L62">
+        <v>97.56</v>
+      </c>
+      <c r="M62">
+        <v>-3.17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="2">
+        <v>159000</v>
+      </c>
+      <c r="D63" s="3">
+        <v>-3.8100000000000002E-2</v>
+      </c>
+      <c r="E63">
+        <v>8.86</v>
+      </c>
+      <c r="F63">
+        <v>11.63</v>
+      </c>
+      <c r="G63">
+        <v>8.51</v>
+      </c>
+      <c r="H63" s="4">
+        <v>160038.65</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63">
+        <v>90</v>
+      </c>
+      <c r="K63">
+        <v>90</v>
+      </c>
+      <c r="L63">
+        <v>103.09</v>
+      </c>
+      <c r="M63">
+        <v>-5.81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A64" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="2">
+        <v>67600</v>
+      </c>
+      <c r="D64" s="3">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="E64">
+        <v>3.06</v>
+      </c>
+      <c r="F64">
+        <v>1.7</v>
+      </c>
+      <c r="G64">
+        <v>3.92</v>
+      </c>
+      <c r="H64" s="4">
+        <v>127255.06</v>
+      </c>
+      <c r="I64">
+        <v>1.92</v>
+      </c>
+      <c r="J64">
+        <v>47</v>
+      </c>
+      <c r="K64">
+        <v>47</v>
+      </c>
+      <c r="L64">
+        <v>112.58</v>
+      </c>
+      <c r="M64">
+        <v>9.39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B65" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="2">
+        <v>593000</v>
+      </c>
+      <c r="D65" s="3">
+        <v>-1.6999999999999999E-3</v>
+      </c>
+      <c r="E65">
+        <v>11.89</v>
+      </c>
+      <c r="F65">
+        <v>14.27</v>
+      </c>
+      <c r="G65">
+        <v>12.6</v>
+      </c>
+      <c r="H65" s="4">
+        <v>95809.42</v>
+      </c>
+      <c r="I65">
+        <v>0.21</v>
+      </c>
+      <c r="J65">
+        <v>88</v>
+      </c>
+      <c r="K65">
+        <v>88</v>
+      </c>
+      <c r="L65">
+        <v>104.52</v>
+      </c>
+      <c r="M65">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A66" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B66" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="2">
+        <v>127100</v>
+      </c>
+      <c r="D66" s="3">
+        <v>-3.1300000000000001E-2</v>
+      </c>
+      <c r="E66">
+        <v>23.44</v>
+      </c>
+      <c r="F66">
+        <v>25.94</v>
+      </c>
+      <c r="G66">
+        <v>27.89</v>
+      </c>
+      <c r="H66" s="4">
+        <v>59980.14</v>
+      </c>
+      <c r="I66">
+        <v>1.06</v>
+      </c>
+      <c r="J66">
+        <v>84</v>
+      </c>
+      <c r="K66">
+        <v>84</v>
+      </c>
+      <c r="L66">
+        <v>100.14</v>
+      </c>
+      <c r="M66">
+        <v>-13.06</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A67" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="2">
+        <v>19930</v>
+      </c>
+      <c r="D67" s="3">
+        <v>-2.7799999999999998E-2</v>
+      </c>
+      <c r="E67">
+        <v>6.96</v>
+      </c>
+      <c r="F67">
+        <v>9.58</v>
+      </c>
+      <c r="G67">
+        <v>7.18</v>
+      </c>
+      <c r="H67" s="4">
+        <v>34223.949999999997</v>
+      </c>
+      <c r="I67">
+        <v>3.26</v>
+      </c>
+      <c r="J67">
+        <v>82</v>
+      </c>
+      <c r="K67">
+        <v>82</v>
+      </c>
+      <c r="L67">
+        <v>101.69</v>
+      </c>
+      <c r="M67">
+        <v>-12.01</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A68" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" s="2">
+        <v>18390</v>
+      </c>
+      <c r="D68" s="3">
+        <v>-3.6700000000000003E-2</v>
+      </c>
+      <c r="E68">
+        <v>3.6</v>
+      </c>
+      <c r="F68">
+        <v>9.42</v>
+      </c>
+      <c r="G68">
+        <v>5.91</v>
+      </c>
+      <c r="H68" s="4">
+        <v>38541.279999999999</v>
+      </c>
+      <c r="I68">
+        <v>2.72</v>
+      </c>
+      <c r="J68">
+        <v>77</v>
+      </c>
+      <c r="K68">
+        <v>77</v>
+      </c>
+      <c r="L68">
+        <v>100.32</v>
+      </c>
+      <c r="M68">
+        <v>-15.06</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="2">
+        <v>72900</v>
+      </c>
+      <c r="D69" s="3">
+        <v>-3.95E-2</v>
+      </c>
+      <c r="E69">
+        <v>10.79</v>
+      </c>
+      <c r="F69">
+        <v>10.55</v>
+      </c>
+      <c r="G69">
+        <v>8.93</v>
+      </c>
+      <c r="H69" s="4">
+        <v>92723.77</v>
+      </c>
+      <c r="I69">
+        <v>2.74</v>
+      </c>
+      <c r="J69">
+        <v>89</v>
+      </c>
+      <c r="K69">
+        <v>89</v>
+      </c>
+      <c r="L69">
+        <v>104.03</v>
+      </c>
+      <c r="M69">
+        <v>-3.57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="2">
+        <v>31750</v>
+      </c>
+      <c r="D70" s="3">
+        <v>-1.7000000000000001E-2</v>
+      </c>
+      <c r="E70">
+        <v>12.8</v>
+      </c>
+      <c r="F70">
+        <v>13.49</v>
+      </c>
+      <c r="G70">
+        <v>12.93</v>
+      </c>
+      <c r="H70" s="4">
+        <v>31004.78</v>
+      </c>
+      <c r="I70">
+        <v>3.13</v>
+      </c>
+      <c r="J70">
+        <v>79</v>
+      </c>
+      <c r="K70">
+        <v>79</v>
+      </c>
+      <c r="L70">
+        <v>103.53</v>
+      </c>
+      <c r="M70">
+        <v>-15.33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A71" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" s="2">
+        <v>93400</v>
+      </c>
+      <c r="D71" s="3">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="E71">
+        <v>12.76</v>
+      </c>
+      <c r="F71">
+        <v>7.4</v>
+      </c>
+      <c r="G71">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="H71" s="4">
+        <v>73076.42</v>
+      </c>
+      <c r="I71">
+        <v>1.18</v>
+      </c>
+      <c r="J71">
+        <v>27</v>
+      </c>
+      <c r="K71">
+        <v>27</v>
+      </c>
+      <c r="L71">
+        <v>102.61</v>
+      </c>
+      <c r="M71">
+        <v>-3.11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A72" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" s="2">
+        <v>53000</v>
+      </c>
+      <c r="D72" s="3">
+        <v>-2.75E-2</v>
+      </c>
+      <c r="E72">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="F72">
+        <v>11.56</v>
+      </c>
+      <c r="G72">
+        <v>6.83</v>
+      </c>
+      <c r="H72" s="4">
+        <v>57293.3</v>
+      </c>
+      <c r="I72">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J72">
+        <v>52</v>
+      </c>
+      <c r="K72">
+        <v>52</v>
+      </c>
+      <c r="L72">
+        <v>97.48</v>
+      </c>
+      <c r="M72">
+        <v>-2.93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A73" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" s="2">
+        <v>133400</v>
+      </c>
+      <c r="D73" s="3">
+        <v>-1.77E-2</v>
+      </c>
+      <c r="E73">
+        <v>16.57</v>
+      </c>
+      <c r="F73">
+        <v>10.4</v>
+      </c>
+      <c r="G73">
+        <v>15.65</v>
+      </c>
+      <c r="H73" s="4">
+        <v>91733.3</v>
+      </c>
+      <c r="I73">
+        <v>1.87</v>
+      </c>
+      <c r="J73">
+        <v>78</v>
+      </c>
+      <c r="K73">
+        <v>78</v>
+      </c>
+      <c r="L73">
+        <v>103.39</v>
+      </c>
+      <c r="M73">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A74" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="2">
         <v>36000</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D74" s="3">
         <v>-4.8899999999999999E-2</v>
       </c>
-      <c r="E38">
+      <c r="E74">
         <v>9.39</v>
       </c>
-      <c r="F38">
+      <c r="F74">
         <v>10.74</v>
       </c>
-      <c r="G38">
+      <c r="G74">
         <v>9.73</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H74" s="4">
         <v>48211.77</v>
       </c>
-      <c r="I38">
+      <c r="I74">
         <v>3.33</v>
       </c>
-      <c r="J38">
+      <c r="J74">
         <v>83</v>
       </c>
-      <c r="K38">
+      <c r="K74">
         <v>83</v>
       </c>
-      <c r="L38">
+      <c r="L74">
         <v>101.8</v>
       </c>
-      <c r="M38">
+      <c r="M74">
         <v>-11.76</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94B3C824-B77E-4024-92F4-A5CBDB1B6ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25320D90-7848-4234-9667-B18561844C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{CE85D9D7-6ED7-418A-9914-D2C51AD0796F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B352F64F-BC69-454B-9BB0-98056DB1768D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -654,7 +654,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56A52FE-94A8-4CC7-9F12-E19E78B252D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8A8F70-21E5-430F-8ADA-06281722AF1F}">
   <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -720,10 +720,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>31300</v>
+        <v>24350</v>
       </c>
       <c r="D2" s="3">
-        <v>-4.8599999999999997E-2</v>
+        <v>-0.15160000000000001</v>
       </c>
       <c r="E2">
         <v>8.2799999999999994</v>
@@ -738,19 +738,19 @@
         <v>48390.96</v>
       </c>
       <c r="I2">
-        <v>3.19</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="K2">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="L2">
-        <v>105.23</v>
+        <v>81.84</v>
       </c>
       <c r="M2">
-        <v>-9.67</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -761,10 +761,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>205500</v>
+        <v>156700</v>
       </c>
       <c r="D3" s="3">
-        <v>-2.3999999999999998E-3</v>
+        <v>-0.1404</v>
       </c>
       <c r="E3">
         <v>19.09</v>
@@ -779,19 +779,19 @@
         <v>150938.41</v>
       </c>
       <c r="I3">
-        <v>3.16</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="J3">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="K3">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="L3">
-        <v>123.68</v>
+        <v>93.35</v>
       </c>
       <c r="M3">
-        <v>19.62</v>
+        <v>-23.75</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -802,10 +802,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>530000</v>
+        <v>468000</v>
       </c>
       <c r="D4" s="3">
-        <v>-3.2800000000000003E-2</v>
+        <v>-0.10340000000000001</v>
       </c>
       <c r="E4">
         <v>13.09</v>
@@ -820,19 +820,19 @@
         <v>405451.96</v>
       </c>
       <c r="I4">
-        <v>3.58</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="J4">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="K4">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="L4">
-        <v>99.18</v>
+        <v>87.57</v>
       </c>
       <c r="M4">
-        <v>-14.24</v>
+        <v>-11.7</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -843,10 +843,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>42600</v>
+        <v>38500</v>
       </c>
       <c r="D5" s="3">
-        <v>-4.7E-2</v>
+        <v>-0.10879999999999999</v>
       </c>
       <c r="E5">
         <v>7.12</v>
@@ -861,19 +861,19 @@
         <v>72041.39</v>
       </c>
       <c r="I5">
-        <v>4.6900000000000004</v>
+        <v>5.19</v>
       </c>
       <c r="J5">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="K5">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="L5">
-        <v>99.06</v>
+        <v>88.78</v>
       </c>
       <c r="M5">
-        <v>-10.69</v>
+        <v>-9.6199999999999992</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -884,10 +884,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>90300</v>
+        <v>67900</v>
       </c>
       <c r="D6" s="3">
-        <v>-6.4199999999999993E-2</v>
+        <v>-0.14810000000000001</v>
       </c>
       <c r="E6">
         <v>4.05</v>
@@ -902,19 +902,19 @@
         <v>65679.45</v>
       </c>
       <c r="I6">
-        <v>1.66</v>
+        <v>2.21</v>
       </c>
       <c r="J6">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="K6">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="L6">
-        <v>112.16</v>
+        <v>83.97</v>
       </c>
       <c r="M6">
-        <v>1.8</v>
+        <v>-24.81</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -925,10 +925,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>69100</v>
+        <v>58500</v>
       </c>
       <c r="D7" s="3">
-        <v>4.4000000000000003E-3</v>
+        <v>-0.12690000000000001</v>
       </c>
       <c r="E7">
         <v>1.04</v>
@@ -943,19 +943,19 @@
         <v>53899.69</v>
       </c>
       <c r="I7">
-        <v>1.74</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="J7">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="K7">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L7">
-        <v>91.69</v>
+        <v>78.459999999999994</v>
       </c>
       <c r="M7">
-        <v>-7</v>
+        <v>-15.34</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -966,10 +966,10 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>44850</v>
+        <v>36050</v>
       </c>
       <c r="D8" s="3">
-        <v>-3.44E-2</v>
+        <v>-0.12920000000000001</v>
       </c>
       <c r="E8">
         <v>4.57</v>
@@ -984,19 +984,19 @@
         <v>42814.52</v>
       </c>
       <c r="I8">
-        <v>2.68</v>
+        <v>3.33</v>
       </c>
       <c r="J8">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="K8">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="L8">
-        <v>119.7</v>
+        <v>94.03</v>
       </c>
       <c r="M8">
-        <v>-8.4700000000000006</v>
+        <v>-19.62</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1007,10 +1007,10 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>107700</v>
+        <v>91300</v>
       </c>
       <c r="D9" s="3">
-        <v>4.1599999999999998E-2</v>
+        <v>-0.10929999999999999</v>
       </c>
       <c r="E9">
         <v>2.16</v>
@@ -1025,19 +1025,19 @@
         <v>177736.27</v>
       </c>
       <c r="I9">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="J9">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="K9">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="L9">
-        <v>112.75</v>
+        <v>95.08</v>
       </c>
       <c r="M9">
-        <v>9.34</v>
+        <v>-15.23</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1048,10 +1048,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>13920</v>
+        <v>12360</v>
       </c>
       <c r="D10" s="3">
-        <v>-3.2000000000000001E-2</v>
+        <v>-8.1000000000000003E-2</v>
       </c>
       <c r="E10">
         <v>9.44</v>
@@ -1066,19 +1066,19 @@
         <v>19219.419999999998</v>
       </c>
       <c r="I10">
-        <v>3.7</v>
+        <v>4.17</v>
       </c>
       <c r="J10">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="K10">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="L10">
-        <v>107.47</v>
+        <v>94.37</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>-11.21</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1089,10 +1089,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>674000</v>
+        <v>501000</v>
       </c>
       <c r="D11" s="3">
-        <v>0.1067</v>
+        <v>-0.158</v>
       </c>
       <c r="E11">
         <v>12.43</v>
@@ -1107,19 +1107,19 @@
         <v>429918.88</v>
       </c>
       <c r="I11">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="J11">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="K11">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="L11">
-        <v>130.29</v>
+        <v>96.14</v>
       </c>
       <c r="M11">
-        <v>32.42</v>
+        <v>-25.67</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1130,10 +1130,10 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>183100</v>
+        <v>175500</v>
       </c>
       <c r="D12" s="3">
-        <v>-0.109</v>
+        <v>-0.06</v>
       </c>
       <c r="E12">
         <v>18.96</v>
@@ -1148,19 +1148,19 @@
         <v>144109.65</v>
       </c>
       <c r="I12">
-        <v>3.71</v>
+        <v>3.87</v>
       </c>
       <c r="J12">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K12">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="L12">
-        <v>106.9</v>
+        <v>100.06</v>
       </c>
       <c r="M12">
-        <v>-4.78</v>
+        <v>-4.1500000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1171,10 +1171,10 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>35500</v>
+        <v>28800</v>
       </c>
       <c r="D13" s="3">
-        <v>-2.7400000000000001E-2</v>
+        <v>-0.1351</v>
       </c>
       <c r="E13">
         <v>8.73</v>
@@ -1189,19 +1189,19 @@
         <v>24348.21</v>
       </c>
       <c r="I13">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="J13">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="K13">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="L13">
-        <v>115.84</v>
+        <v>92.3</v>
       </c>
       <c r="M13">
-        <v>-9.44</v>
+        <v>-18.87</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1212,10 +1212,10 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>27200</v>
+        <v>23350</v>
       </c>
       <c r="D14" s="3">
-        <v>-3.3700000000000001E-2</v>
+        <v>-0.11890000000000001</v>
       </c>
       <c r="E14">
         <v>19.78</v>
@@ -1230,19 +1230,19 @@
         <v>32624.26</v>
       </c>
       <c r="I14">
-        <v>3.68</v>
+        <v>4.28</v>
       </c>
       <c r="J14">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K14">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="L14">
-        <v>96.18</v>
+        <v>82.76</v>
       </c>
       <c r="M14">
-        <v>-13.38</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1253,10 +1253,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>249500</v>
+        <v>214000</v>
       </c>
       <c r="D15" s="3">
-        <v>1.84E-2</v>
+        <v>-0.123</v>
       </c>
       <c r="E15">
         <v>13.17</v>
@@ -1271,19 +1271,19 @@
         <v>207156.6</v>
       </c>
       <c r="I15">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="J15">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="K15">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="L15">
-        <v>112.06</v>
+        <v>94.85</v>
       </c>
       <c r="M15">
-        <v>10.64</v>
+        <v>-14.23</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1294,10 +1294,10 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>106800</v>
+        <v>88000</v>
       </c>
       <c r="D16" s="3">
-        <v>-3.8699999999999998E-2</v>
+        <v>-0.1244</v>
       </c>
       <c r="E16">
         <v>12.89</v>
@@ -1312,19 +1312,19 @@
         <v>87743.72</v>
       </c>
       <c r="I16">
-        <v>3.28</v>
+        <v>3.98</v>
       </c>
       <c r="J16">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="K16">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="L16">
-        <v>108.33</v>
+        <v>88.88</v>
       </c>
       <c r="M16">
-        <v>-6.72</v>
+        <v>-17.600000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1335,10 +1335,10 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>79800</v>
+        <v>70300</v>
       </c>
       <c r="D17" s="3">
-        <v>-3.04E-2</v>
+        <v>-0.10100000000000001</v>
       </c>
       <c r="E17">
         <v>10.83</v>
@@ -1353,19 +1353,19 @@
         <v>54894.12</v>
       </c>
       <c r="I17">
-        <v>4.4400000000000004</v>
+        <v>5.04</v>
       </c>
       <c r="J17">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K17">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="L17">
-        <v>104.2</v>
+        <v>91.2</v>
       </c>
       <c r="M17">
-        <v>-1.24</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1376,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>98700</v>
+        <v>81600</v>
       </c>
       <c r="D18" s="3">
-        <v>-1.7899999999999999E-2</v>
+        <v>-0.13739999999999999</v>
       </c>
       <c r="E18">
         <v>14.42</v>
@@ -1394,19 +1394,19 @@
         <v>36460.550000000003</v>
       </c>
       <c r="I18">
-        <v>5.57</v>
+        <v>6.74</v>
       </c>
       <c r="J18">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="K18">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="L18">
-        <v>97.6</v>
+        <v>80.930000000000007</v>
       </c>
       <c r="M18">
-        <v>-10.44</v>
+        <v>-17.329999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1417,10 +1417,10 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>25750</v>
+        <v>22400</v>
       </c>
       <c r="D19" s="3">
-        <v>-2.8299999999999999E-2</v>
+        <v>-0.1076</v>
       </c>
       <c r="E19">
         <v>8.06</v>
@@ -1435,19 +1435,19 @@
         <v>44443.18</v>
       </c>
       <c r="I19">
-        <v>4.1399999999999997</v>
+        <v>4.75</v>
       </c>
       <c r="J19">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="K19">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="L19">
-        <v>104.82</v>
+        <v>90.5</v>
       </c>
       <c r="M19">
-        <v>-9.81</v>
+        <v>-13.01</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1458,10 +1458,10 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>63000</v>
+        <v>57300</v>
       </c>
       <c r="D20" s="3">
-        <v>-1.6000000000000001E-3</v>
+        <v>-7.4300000000000005E-2</v>
       </c>
       <c r="E20">
         <v>7.45</v>
@@ -1476,19 +1476,19 @@
         <v>79986.48</v>
       </c>
       <c r="I20">
-        <v>4.4400000000000004</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="J20">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="K20">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="L20">
-        <v>103.99</v>
+        <v>94.14</v>
       </c>
       <c r="M20">
-        <v>-6.53</v>
+        <v>-9.0500000000000007</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1499,10 +1499,10 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>21950</v>
+        <v>19790</v>
       </c>
       <c r="D21" s="3">
-        <v>-4.4999999999999997E-3</v>
+        <v>-7.3099999999999998E-2</v>
       </c>
       <c r="E21">
         <v>15.12</v>
@@ -1517,19 +1517,19 @@
         <v>15310.06</v>
       </c>
       <c r="I21">
-        <v>5.6</v>
+        <v>6.22</v>
       </c>
       <c r="J21">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="K21">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="L21">
-        <v>101.34</v>
+        <v>91.69</v>
       </c>
       <c r="M21">
-        <v>-2.23</v>
+        <v>-9.84</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1540,10 +1540,10 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>63800</v>
+        <v>54900</v>
       </c>
       <c r="D22" s="3">
-        <v>-1.24E-2</v>
+        <v>-0.12859999999999999</v>
       </c>
       <c r="E22">
         <v>2.85</v>
@@ -1558,19 +1558,19 @@
         <v>71073.47</v>
       </c>
       <c r="I22">
-        <v>3.13</v>
+        <v>3.64</v>
       </c>
       <c r="J22">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="K22">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="L22">
-        <v>104.27</v>
+        <v>89.29</v>
       </c>
       <c r="M22">
-        <v>-7.4</v>
+        <v>-13.95</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1581,10 +1581,10 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>16540</v>
+        <v>14580</v>
       </c>
       <c r="D23" s="3">
-        <v>-7.1300000000000002E-2</v>
+        <v>-9.5000000000000001E-2</v>
       </c>
       <c r="E23">
         <v>4.4000000000000004</v>
@@ -1599,19 +1599,19 @@
         <v>20394.86</v>
       </c>
       <c r="I23">
-        <v>3.93</v>
+        <v>4.46</v>
       </c>
       <c r="J23">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="K23">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="L23">
-        <v>99.82</v>
+        <v>88.38</v>
       </c>
       <c r="M23">
-        <v>-5.49</v>
+        <v>-11.85</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1622,10 +1622,10 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>230000</v>
+        <v>197500</v>
       </c>
       <c r="D24" s="3">
-        <v>-3.7699999999999997E-2</v>
+        <v>-0.1084</v>
       </c>
       <c r="E24">
         <v>4.66</v>
@@ -1640,19 +1640,19 @@
         <v>324173.33</v>
       </c>
       <c r="I24">
-        <v>2.2999999999999998</v>
+        <v>2.68</v>
       </c>
       <c r="J24">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K24">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L24">
-        <v>111.88</v>
+        <v>95.27</v>
       </c>
       <c r="M24">
-        <v>5.0199999999999996</v>
+        <v>-14.13</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1663,10 +1663,10 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>163100</v>
+        <v>151600</v>
       </c>
       <c r="D25" s="3">
-        <v>-3.8899999999999997E-2</v>
+        <v>-6.59E-2</v>
       </c>
       <c r="E25">
         <v>12.66</v>
@@ -1681,19 +1681,19 @@
         <v>83639.03</v>
       </c>
       <c r="I25">
-        <v>3.31</v>
+        <v>3.56</v>
       </c>
       <c r="J25">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="K25">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="L25">
-        <v>98.41</v>
+        <v>90.79</v>
       </c>
       <c r="M25">
-        <v>-7.91</v>
+        <v>-7.05</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1704,10 +1704,10 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>19050</v>
+        <v>17370</v>
       </c>
       <c r="D26" s="3">
-        <v>-1.7999999999999999E-2</v>
+        <v>-7.3099999999999998E-2</v>
       </c>
       <c r="E26">
         <v>12.08</v>
@@ -1722,19 +1722,19 @@
         <v>19234.22</v>
       </c>
       <c r="I26">
-        <v>6.14</v>
+        <v>6.74</v>
       </c>
       <c r="J26">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K26">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L26">
-        <v>103.52</v>
+        <v>94.13</v>
       </c>
       <c r="M26">
-        <v>-1.75</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1745,10 +1745,10 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>41200</v>
+        <v>36150</v>
       </c>
       <c r="D27" s="3">
-        <v>-6.1499999999999999E-2</v>
+        <v>-0.1096</v>
       </c>
       <c r="E27">
         <v>11.21</v>
@@ -1763,19 +1763,19 @@
         <v>122131.86</v>
       </c>
       <c r="I27">
-        <v>3.53</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J27">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="K27">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L27">
-        <v>97.96</v>
+        <v>86.36</v>
       </c>
       <c r="M27">
-        <v>-9.65</v>
+        <v>-12.26</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1786,10 +1786,10 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>96900</v>
+        <v>88800</v>
       </c>
       <c r="D28" s="3">
-        <v>-0.03</v>
+        <v>-8.1699999999999995E-2</v>
       </c>
       <c r="E28">
         <v>8.11</v>
@@ -1804,19 +1804,19 @@
         <v>119742.76</v>
       </c>
       <c r="I28">
-        <v>2.23</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="J28">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K28">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="L28">
-        <v>101.97</v>
+        <v>92.64</v>
       </c>
       <c r="M28">
-        <v>-5</v>
+        <v>-8.36</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1827,10 +1827,10 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>258500</v>
+        <v>206500</v>
       </c>
       <c r="D29" s="3">
-        <v>-3.1800000000000002E-2</v>
+        <v>-0.1414</v>
       </c>
       <c r="E29">
         <v>11.54</v>
@@ -1845,19 +1845,19 @@
         <v>189057.03</v>
       </c>
       <c r="I29">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="J29">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="K29">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="L29">
-        <v>107.8</v>
+        <v>85.71</v>
       </c>
       <c r="M29">
-        <v>-11.62</v>
+        <v>-20.12</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1868,10 +1868,10 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>68700</v>
+        <v>61400</v>
       </c>
       <c r="D30" s="3">
-        <v>-2.1399999999999999E-2</v>
+        <v>-0.12909999999999999</v>
       </c>
       <c r="E30">
         <v>4.12</v>
@@ -1886,19 +1886,19 @@
         <v>151788</v>
       </c>
       <c r="I30">
-        <v>3.93</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J30">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="K30">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="L30">
-        <v>98.27</v>
+        <v>87.75</v>
       </c>
       <c r="M30">
-        <v>-9.25</v>
+        <v>-10.63</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1909,10 +1909,10 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>121800</v>
+        <v>105500</v>
       </c>
       <c r="D31" s="3">
-        <v>-2.4799999999999999E-2</v>
+        <v>-0.1216</v>
       </c>
       <c r="E31">
         <v>9.11</v>
@@ -1927,19 +1927,19 @@
         <v>159337.74</v>
       </c>
       <c r="I31">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="J31">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="K31">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="L31">
-        <v>102.74</v>
+        <v>88.27</v>
       </c>
       <c r="M31">
-        <v>-7.24</v>
+        <v>-13.38</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1950,10 +1950,10 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>159000</v>
+        <v>137700</v>
       </c>
       <c r="D32" s="3">
-        <v>-3.8100000000000002E-2</v>
+        <v>-0.10290000000000001</v>
       </c>
       <c r="E32">
         <v>8.86</v>
@@ -1968,19 +1968,19 @@
         <v>160038.65</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="J32">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K32">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="L32">
-        <v>103.09</v>
+        <v>88.83</v>
       </c>
       <c r="M32">
-        <v>-5.81</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -1991,10 +1991,10 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>19930</v>
+        <v>17640</v>
       </c>
       <c r="D33" s="3">
-        <v>-2.7799999999999998E-2</v>
+        <v>-0.1037</v>
       </c>
       <c r="E33">
         <v>6.96</v>
@@ -2009,19 +2009,19 @@
         <v>34223.949999999997</v>
       </c>
       <c r="I33">
-        <v>3.26</v>
+        <v>3.68</v>
       </c>
       <c r="J33">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="K33">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="L33">
-        <v>101.69</v>
+        <v>89.04</v>
       </c>
       <c r="M33">
-        <v>-12.01</v>
+        <v>-11.49</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2032,10 +2032,10 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>18390</v>
+        <v>16280</v>
       </c>
       <c r="D34" s="3">
-        <v>-3.6700000000000003E-2</v>
+        <v>-0.10059999999999999</v>
       </c>
       <c r="E34">
         <v>3.6</v>
@@ -2050,19 +2050,19 @@
         <v>38541.279999999999</v>
       </c>
       <c r="I34">
-        <v>2.72</v>
+        <v>3.07</v>
       </c>
       <c r="J34">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="K34">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="L34">
-        <v>100.32</v>
+        <v>87.8</v>
       </c>
       <c r="M34">
-        <v>-15.06</v>
+        <v>-11.47</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2073,10 +2073,10 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>72900</v>
+        <v>58200</v>
       </c>
       <c r="D35" s="3">
-        <v>-3.95E-2</v>
+        <v>-0.12870000000000001</v>
       </c>
       <c r="E35">
         <v>10.79</v>
@@ -2091,19 +2091,19 @@
         <v>92723.77</v>
       </c>
       <c r="I35">
-        <v>2.74</v>
+        <v>3.44</v>
       </c>
       <c r="J35">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="K35">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="L35">
-        <v>104.03</v>
+        <v>83.35</v>
       </c>
       <c r="M35">
-        <v>-3.57</v>
+        <v>-20.16</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2114,10 +2114,10 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>31750</v>
+        <v>28300</v>
       </c>
       <c r="D36" s="3">
-        <v>-1.7000000000000001E-2</v>
+        <v>-9.1499999999999998E-2</v>
       </c>
       <c r="E36">
         <v>12.8</v>
@@ -2132,19 +2132,19 @@
         <v>31004.78</v>
       </c>
       <c r="I36">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="J36">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="K36">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="L36">
-        <v>103.53</v>
+        <v>90.75</v>
       </c>
       <c r="M36">
-        <v>-15.33</v>
+        <v>-10.87</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2155,10 +2155,10 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>53000</v>
+        <v>47300</v>
       </c>
       <c r="D37" s="3">
-        <v>-2.75E-2</v>
+        <v>-8.8599999999999998E-2</v>
       </c>
       <c r="E37">
         <v>18.690000000000001</v>
@@ -2173,19 +2173,19 @@
         <v>57293.3</v>
       </c>
       <c r="I37">
-        <v>2.2599999999999998</v>
+        <v>2.54</v>
       </c>
       <c r="J37">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K37">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="L37">
-        <v>97.48</v>
+        <v>87.53</v>
       </c>
       <c r="M37">
-        <v>-2.93</v>
+        <v>-10.75</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2196,10 +2196,10 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>36000</v>
+        <v>31800</v>
       </c>
       <c r="D38" s="3">
-        <v>-4.8899999999999999E-2</v>
+        <v>-9.9199999999999997E-2</v>
       </c>
       <c r="E38">
         <v>9.39</v>
@@ -2214,19 +2214,19 @@
         <v>48211.77</v>
       </c>
       <c r="I38">
-        <v>3.33</v>
+        <v>3.77</v>
       </c>
       <c r="J38">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="K38">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="L38">
-        <v>101.8</v>
+        <v>89.11</v>
       </c>
       <c r="M38">
-        <v>-11.76</v>
+        <v>-11.67</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25320D90-7848-4234-9667-B18561844C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AC5C209-EC2B-475A-9C30-1C630691E0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B352F64F-BC69-454B-9BB0-98056DB1768D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{258F7C3A-C8F0-4560-9D3E-7CAADC7ACC95}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
   <si>
     <t>종목코드</t>
   </si>
@@ -58,12 +58,6 @@
   </si>
   <si>
     <t>해당등락률</t>
-  </si>
-  <si>
-    <t>000240</t>
-  </si>
-  <si>
-    <t>한국앤컴퍼니</t>
   </si>
   <si>
     <t>000270</t>
@@ -654,14 +648,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8A8F70-21E5-430F-8ADA-06281722AF1F}">
-  <dimension ref="A1:M38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E54594-4072-4D42-BF2A-E6100C2614FB}">
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.296875" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -720,37 +714,37 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>24350</v>
+        <v>166400</v>
       </c>
       <c r="D2" s="3">
-        <v>-0.15160000000000001</v>
+        <v>6.1899999999999997E-2</v>
       </c>
       <c r="E2">
-        <v>8.2799999999999994</v>
+        <v>19.09</v>
       </c>
       <c r="F2">
-        <v>8.9</v>
+        <v>14.17</v>
       </c>
       <c r="G2">
-        <v>5.8</v>
+        <v>18.03</v>
       </c>
       <c r="H2" s="4">
-        <v>48390.96</v>
+        <v>150938.41</v>
       </c>
       <c r="I2">
-        <v>4.1100000000000003</v>
+        <v>3.91</v>
       </c>
       <c r="J2">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="L2">
-        <v>81.84</v>
+        <v>98.72</v>
       </c>
       <c r="M2">
-        <v>-22.2</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -761,37 +755,37 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>156700</v>
+        <v>491500</v>
       </c>
       <c r="D3" s="3">
-        <v>-0.1404</v>
+        <v>5.0200000000000002E-2</v>
       </c>
       <c r="E3">
-        <v>19.09</v>
+        <v>13.09</v>
       </c>
       <c r="F3">
-        <v>14.17</v>
+        <v>13.88</v>
       </c>
       <c r="G3">
-        <v>18.03</v>
+        <v>12.47</v>
       </c>
       <c r="H3" s="4">
-        <v>150938.41</v>
+        <v>405451.96</v>
       </c>
       <c r="I3">
-        <v>4.1500000000000004</v>
+        <v>3.87</v>
       </c>
       <c r="J3">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K3">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L3">
-        <v>93.35</v>
+        <v>92.05</v>
       </c>
       <c r="M3">
-        <v>-23.75</v>
+        <v>-7.26</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -802,37 +796,37 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>468000</v>
+        <v>39750</v>
       </c>
       <c r="D4" s="3">
-        <v>-0.10340000000000001</v>
+        <v>3.2500000000000001E-2</v>
       </c>
       <c r="E4">
-        <v>13.09</v>
+        <v>7.12</v>
       </c>
       <c r="F4">
-        <v>13.88</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="G4">
-        <v>12.47</v>
+        <v>12.61</v>
       </c>
       <c r="H4" s="4">
-        <v>405451.96</v>
+        <v>72041.39</v>
       </c>
       <c r="I4">
-        <v>4.0599999999999996</v>
+        <v>5.03</v>
       </c>
       <c r="J4">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K4">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L4">
-        <v>87.57</v>
+        <v>91.5</v>
       </c>
       <c r="M4">
-        <v>-11.7</v>
+        <v>-6.69</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -843,37 +837,37 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>38500</v>
+        <v>77200</v>
       </c>
       <c r="D5" s="3">
-        <v>-0.10879999999999999</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="E5">
-        <v>7.12</v>
+        <v>4.05</v>
       </c>
       <c r="F5">
-        <v>9.6199999999999992</v>
+        <v>7.82</v>
       </c>
       <c r="G5">
-        <v>12.61</v>
+        <v>6.06</v>
       </c>
       <c r="H5" s="4">
-        <v>72041.39</v>
+        <v>65679.45</v>
       </c>
       <c r="I5">
-        <v>5.19</v>
+        <v>1.94</v>
       </c>
       <c r="J5">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="K5">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L5">
-        <v>88.78</v>
+        <v>95.16</v>
       </c>
       <c r="M5">
-        <v>-9.6199999999999992</v>
+        <v>-14.51</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -884,37 +878,37 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>67900</v>
+        <v>61000</v>
       </c>
       <c r="D6" s="3">
-        <v>-0.14810000000000001</v>
+        <v>4.2700000000000002E-2</v>
       </c>
       <c r="E6">
-        <v>4.05</v>
+        <v>1.04</v>
       </c>
       <c r="F6">
-        <v>7.82</v>
+        <v>3.97</v>
       </c>
       <c r="G6">
-        <v>6.06</v>
+        <v>4.21</v>
       </c>
       <c r="H6" s="4">
-        <v>65679.45</v>
+        <v>53899.69</v>
       </c>
       <c r="I6">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="J6">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K6">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L6">
-        <v>83.97</v>
+        <v>82.46</v>
       </c>
       <c r="M6">
-        <v>-24.81</v>
+        <v>-11.72</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -925,37 +919,37 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>58500</v>
+        <v>39900</v>
       </c>
       <c r="D7" s="3">
-        <v>-0.12690000000000001</v>
+        <v>0.10680000000000001</v>
       </c>
       <c r="E7">
-        <v>1.04</v>
+        <v>4.57</v>
       </c>
       <c r="F7">
-        <v>3.97</v>
+        <v>7.42</v>
       </c>
       <c r="G7">
-        <v>4.21</v>
+        <v>4.55</v>
       </c>
       <c r="H7" s="4">
-        <v>53899.69</v>
+        <v>42814.52</v>
       </c>
       <c r="I7">
-        <v>2.0499999999999998</v>
+        <v>3.01</v>
       </c>
       <c r="J7">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="K7">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="L7">
-        <v>78.459999999999994</v>
+        <v>102.91</v>
       </c>
       <c r="M7">
-        <v>-15.34</v>
+        <v>-11.04</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -966,37 +960,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>36050</v>
+        <v>96800</v>
       </c>
       <c r="D8" s="3">
-        <v>-0.12920000000000001</v>
+        <v>6.0199999999999997E-2</v>
       </c>
       <c r="E8">
-        <v>4.57</v>
+        <v>2.16</v>
       </c>
       <c r="F8">
-        <v>7.42</v>
+        <v>5.36</v>
       </c>
       <c r="G8">
-        <v>4.55</v>
+        <v>5.18</v>
       </c>
       <c r="H8" s="4">
-        <v>42814.52</v>
+        <v>177736.27</v>
       </c>
       <c r="I8">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="J8">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K8">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L8">
-        <v>94.03</v>
+        <v>100.55</v>
       </c>
       <c r="M8">
-        <v>-19.62</v>
+        <v>-10.119999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1007,37 +1001,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>91300</v>
+        <v>13110</v>
       </c>
       <c r="D9" s="3">
-        <v>-0.10929999999999999</v>
+        <v>6.0699999999999997E-2</v>
       </c>
       <c r="E9">
-        <v>2.16</v>
+        <v>9.44</v>
       </c>
       <c r="F9">
-        <v>5.36</v>
+        <v>10.67</v>
       </c>
       <c r="G9">
-        <v>5.18</v>
+        <v>9.86</v>
       </c>
       <c r="H9" s="4">
-        <v>177736.27</v>
+        <v>19219.419999999998</v>
       </c>
       <c r="I9">
-        <v>3.4</v>
+        <v>3.93</v>
       </c>
       <c r="J9">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="K9">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="L9">
-        <v>95.08</v>
+        <v>99.59</v>
       </c>
       <c r="M9">
-        <v>-15.23</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1048,37 +1042,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>12360</v>
+        <v>548000</v>
       </c>
       <c r="D10" s="3">
-        <v>-8.1000000000000003E-2</v>
+        <v>9.3799999999999994E-2</v>
       </c>
       <c r="E10">
-        <v>9.44</v>
+        <v>12.43</v>
       </c>
       <c r="F10">
-        <v>10.67</v>
+        <v>10.08</v>
       </c>
       <c r="G10">
-        <v>9.86</v>
+        <v>11.82</v>
       </c>
       <c r="H10" s="4">
-        <v>19219.419999999998</v>
+        <v>429918.88</v>
       </c>
       <c r="I10">
-        <v>4.17</v>
+        <v>2.19</v>
       </c>
       <c r="J10">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K10">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L10">
-        <v>94.37</v>
+        <v>104.68</v>
       </c>
       <c r="M10">
-        <v>-11.21</v>
+        <v>-18.690000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1089,37 +1083,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>501000</v>
+        <v>190600</v>
       </c>
       <c r="D11" s="3">
-        <v>-0.158</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="E11">
-        <v>12.43</v>
+        <v>18.96</v>
       </c>
       <c r="F11">
-        <v>10.08</v>
+        <v>19.43</v>
       </c>
       <c r="G11">
-        <v>11.82</v>
+        <v>18.8</v>
       </c>
       <c r="H11" s="4">
-        <v>429918.88</v>
+        <v>144109.65</v>
       </c>
       <c r="I11">
-        <v>2.4</v>
+        <v>3.57</v>
       </c>
       <c r="J11">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="K11">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="L11">
-        <v>96.14</v>
+        <v>107.2</v>
       </c>
       <c r="M11">
-        <v>-25.67</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1130,37 +1124,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>175500</v>
+        <v>32050</v>
       </c>
       <c r="D12" s="3">
-        <v>-0.06</v>
+        <v>0.1128</v>
       </c>
       <c r="E12">
-        <v>18.96</v>
+        <v>8.73</v>
       </c>
       <c r="F12">
-        <v>19.43</v>
+        <v>11.57</v>
       </c>
       <c r="G12">
-        <v>18.8</v>
+        <v>6.85</v>
       </c>
       <c r="H12" s="4">
-        <v>144109.65</v>
+        <v>24348.21</v>
       </c>
       <c r="I12">
-        <v>3.87</v>
+        <v>2.96</v>
       </c>
       <c r="J12">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K12">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L12">
-        <v>100.06</v>
+        <v>101.9</v>
       </c>
       <c r="M12">
-        <v>-4.1500000000000004</v>
+        <v>-9.7200000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1171,37 +1165,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>28800</v>
+        <v>24500</v>
       </c>
       <c r="D13" s="3">
-        <v>-0.1351</v>
+        <v>4.9299999999999997E-2</v>
       </c>
       <c r="E13">
-        <v>8.73</v>
+        <v>19.78</v>
       </c>
       <c r="F13">
-        <v>11.57</v>
+        <v>13.82</v>
       </c>
       <c r="G13">
-        <v>6.85</v>
+        <v>23.29</v>
       </c>
       <c r="H13" s="4">
-        <v>24348.21</v>
+        <v>32624.26</v>
       </c>
       <c r="I13">
-        <v>3.3</v>
+        <v>4.08</v>
       </c>
       <c r="J13">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K13">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L13">
-        <v>92.3</v>
+        <v>86.93</v>
       </c>
       <c r="M13">
-        <v>-18.87</v>
+        <v>-9.93</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1212,37 +1206,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>23350</v>
+        <v>227000</v>
       </c>
       <c r="D14" s="3">
-        <v>-0.11890000000000001</v>
+        <v>6.0699999999999997E-2</v>
       </c>
       <c r="E14">
-        <v>19.78</v>
+        <v>13.17</v>
       </c>
       <c r="F14">
-        <v>13.82</v>
+        <v>11.69</v>
       </c>
       <c r="G14">
-        <v>23.29</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H14" s="4">
-        <v>32624.26</v>
+        <v>207156.6</v>
       </c>
       <c r="I14">
-        <v>4.28</v>
+        <v>2.36</v>
       </c>
       <c r="J14">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="K14">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="L14">
-        <v>82.76</v>
+        <v>100.17</v>
       </c>
       <c r="M14">
-        <v>-14.15</v>
+        <v>-9.02</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1253,37 +1247,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>214000</v>
+        <v>95200</v>
       </c>
       <c r="D15" s="3">
-        <v>-0.123</v>
+        <v>8.1799999999999998E-2</v>
       </c>
       <c r="E15">
-        <v>13.17</v>
+        <v>12.89</v>
       </c>
       <c r="F15">
-        <v>11.69</v>
+        <v>13.94</v>
       </c>
       <c r="G15">
-        <v>18.010000000000002</v>
+        <v>9.44</v>
       </c>
       <c r="H15" s="4">
-        <v>207156.6</v>
+        <v>87743.72</v>
       </c>
       <c r="I15">
-        <v>2.5</v>
+        <v>3.68</v>
       </c>
       <c r="J15">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K15">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L15">
-        <v>94.85</v>
+        <v>95.93</v>
       </c>
       <c r="M15">
-        <v>-14.23</v>
+        <v>-10.86</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1294,37 +1288,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>88000</v>
+        <v>77900</v>
       </c>
       <c r="D16" s="3">
-        <v>-0.1244</v>
+        <v>0.1081</v>
       </c>
       <c r="E16">
-        <v>12.89</v>
+        <v>10.83</v>
       </c>
       <c r="F16">
-        <v>13.94</v>
+        <v>3.37</v>
       </c>
       <c r="G16">
-        <v>9.44</v>
+        <v>9.48</v>
       </c>
       <c r="H16" s="4">
-        <v>87743.72</v>
+        <v>54894.12</v>
       </c>
       <c r="I16">
-        <v>3.98</v>
+        <v>4.54</v>
       </c>
       <c r="J16">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="K16">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="L16">
-        <v>88.88</v>
+        <v>100.7</v>
       </c>
       <c r="M16">
-        <v>-17.600000000000001</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1335,37 +1329,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>70300</v>
+        <v>86000</v>
       </c>
       <c r="D17" s="3">
-        <v>-0.10100000000000001</v>
+        <v>5.3900000000000003E-2</v>
       </c>
       <c r="E17">
-        <v>10.83</v>
+        <v>14.42</v>
       </c>
       <c r="F17">
-        <v>3.37</v>
+        <v>24.2</v>
       </c>
       <c r="G17">
-        <v>9.48</v>
+        <v>15.82</v>
       </c>
       <c r="H17" s="4">
-        <v>54894.12</v>
+        <v>36460.550000000003</v>
       </c>
       <c r="I17">
-        <v>5.04</v>
+        <v>6.4</v>
       </c>
       <c r="J17">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K17">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L17">
-        <v>91.2</v>
+        <v>85.65</v>
       </c>
       <c r="M17">
-        <v>-11.9</v>
+        <v>-12.87</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1376,37 +1370,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>81600</v>
+        <v>23800</v>
       </c>
       <c r="D18" s="3">
-        <v>-0.13739999999999999</v>
+        <v>6.25E-2</v>
       </c>
       <c r="E18">
-        <v>14.42</v>
+        <v>8.06</v>
       </c>
       <c r="F18">
-        <v>24.2</v>
+        <v>8.64</v>
       </c>
       <c r="G18">
-        <v>15.82</v>
+        <v>8.77</v>
       </c>
       <c r="H18" s="4">
-        <v>36460.550000000003</v>
+        <v>44443.18</v>
       </c>
       <c r="I18">
-        <v>6.74</v>
+        <v>4.47</v>
       </c>
       <c r="J18">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K18">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="L18">
-        <v>80.930000000000007</v>
+        <v>95.83</v>
       </c>
       <c r="M18">
-        <v>-17.329999999999998</v>
+        <v>-7.57</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1417,37 +1411,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>22400</v>
+        <v>59500</v>
       </c>
       <c r="D19" s="3">
-        <v>-0.1076</v>
+        <v>3.8399999999999997E-2</v>
       </c>
       <c r="E19">
-        <v>8.06</v>
+        <v>7.45</v>
       </c>
       <c r="F19">
-        <v>8.64</v>
+        <v>7.45</v>
       </c>
       <c r="G19">
-        <v>8.77</v>
+        <v>7.69</v>
       </c>
       <c r="H19" s="4">
-        <v>44443.18</v>
+        <v>79986.48</v>
       </c>
       <c r="I19">
-        <v>4.75</v>
+        <v>4.71</v>
       </c>
       <c r="J19">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K19">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L19">
-        <v>90.5</v>
+        <v>97.54</v>
       </c>
       <c r="M19">
-        <v>-13.01</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1458,37 +1452,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>57300</v>
+        <v>20400</v>
       </c>
       <c r="D20" s="3">
-        <v>-7.4300000000000005E-2</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="E20">
-        <v>7.45</v>
+        <v>15.12</v>
       </c>
       <c r="F20">
-        <v>7.45</v>
+        <v>13.07</v>
       </c>
       <c r="G20">
-        <v>7.69</v>
+        <v>15.58</v>
       </c>
       <c r="H20" s="4">
-        <v>79986.48</v>
+        <v>15310.06</v>
       </c>
       <c r="I20">
-        <v>4.8899999999999997</v>
+        <v>6.03</v>
       </c>
       <c r="J20">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="K20">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="L20">
-        <v>94.14</v>
+        <v>94.85</v>
       </c>
       <c r="M20">
-        <v>-9.0500000000000007</v>
+        <v>-7.06</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1499,37 +1493,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>19790</v>
+        <v>57800</v>
       </c>
       <c r="D21" s="3">
-        <v>-7.3099999999999998E-2</v>
+        <v>5.28E-2</v>
       </c>
       <c r="E21">
-        <v>15.12</v>
+        <v>2.85</v>
       </c>
       <c r="F21">
-        <v>13.07</v>
+        <v>12.83</v>
       </c>
       <c r="G21">
-        <v>15.58</v>
+        <v>5.63</v>
       </c>
       <c r="H21" s="4">
-        <v>15310.06</v>
+        <v>71073.47</v>
       </c>
       <c r="I21">
-        <v>6.22</v>
+        <v>3.46</v>
       </c>
       <c r="J21">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="K21">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="L21">
-        <v>91.69</v>
+        <v>93.94</v>
       </c>
       <c r="M21">
-        <v>-9.84</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1540,25 +1534,25 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>54900</v>
+        <v>15010</v>
       </c>
       <c r="D22" s="3">
-        <v>-0.12859999999999999</v>
+        <v>2.9499999999999998E-2</v>
       </c>
       <c r="E22">
-        <v>2.85</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F22">
-        <v>12.83</v>
+        <v>6.71</v>
       </c>
       <c r="G22">
-        <v>5.63</v>
+        <v>6.75</v>
       </c>
       <c r="H22" s="4">
-        <v>71073.47</v>
+        <v>20394.86</v>
       </c>
       <c r="I22">
-        <v>3.64</v>
+        <v>4.33</v>
       </c>
       <c r="J22">
         <v>65</v>
@@ -1567,10 +1561,10 @@
         <v>65</v>
       </c>
       <c r="L22">
-        <v>89.29</v>
+        <v>91.26</v>
       </c>
       <c r="M22">
-        <v>-13.95</v>
+        <v>-9.25</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1581,37 +1575,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>14580</v>
+        <v>214000</v>
       </c>
       <c r="D23" s="3">
-        <v>-9.5000000000000001E-2</v>
+        <v>8.3500000000000005E-2</v>
       </c>
       <c r="E23">
-        <v>4.4000000000000004</v>
+        <v>4.66</v>
       </c>
       <c r="F23">
-        <v>6.71</v>
+        <v>4.66</v>
       </c>
       <c r="G23">
-        <v>6.75</v>
+        <v>4.88</v>
       </c>
       <c r="H23" s="4">
-        <v>20394.86</v>
+        <v>324173.33</v>
       </c>
       <c r="I23">
-        <v>4.46</v>
+        <v>2.48</v>
       </c>
       <c r="J23">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K23">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="L23">
-        <v>88.38</v>
+        <v>102.59</v>
       </c>
       <c r="M23">
-        <v>-11.85</v>
+        <v>-6.96</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1622,37 +1616,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>197500</v>
+        <v>156600</v>
       </c>
       <c r="D24" s="3">
-        <v>-0.1084</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="E24">
-        <v>4.66</v>
+        <v>12.66</v>
       </c>
       <c r="F24">
-        <v>4.66</v>
+        <v>11.88</v>
       </c>
       <c r="G24">
-        <v>4.88</v>
+        <v>11.14</v>
       </c>
       <c r="H24" s="4">
-        <v>324173.33</v>
+        <v>83639.03</v>
       </c>
       <c r="I24">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="J24">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K24">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L24">
-        <v>95.27</v>
+        <v>93.71</v>
       </c>
       <c r="M24">
-        <v>-14.13</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1663,37 +1657,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>151600</v>
+        <v>17830</v>
       </c>
       <c r="D25" s="3">
-        <v>-6.59E-2</v>
+        <v>2.6499999999999999E-2</v>
       </c>
       <c r="E25">
-        <v>12.66</v>
+        <v>12.08</v>
       </c>
       <c r="F25">
-        <v>11.88</v>
+        <v>8.58</v>
       </c>
       <c r="G25">
-        <v>11.14</v>
+        <v>8.39</v>
       </c>
       <c r="H25" s="4">
-        <v>83639.03</v>
+        <v>19234.22</v>
       </c>
       <c r="I25">
-        <v>3.56</v>
+        <v>6.56</v>
       </c>
       <c r="J25">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="K25">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="L25">
-        <v>90.79</v>
+        <v>96.52</v>
       </c>
       <c r="M25">
-        <v>-7.05</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1704,37 +1698,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>17370</v>
+        <v>37100</v>
       </c>
       <c r="D26" s="3">
-        <v>-7.3099999999999998E-2</v>
+        <v>2.63E-2</v>
       </c>
       <c r="E26">
-        <v>12.08</v>
+        <v>11.21</v>
       </c>
       <c r="F26">
-        <v>8.58</v>
+        <v>6.55</v>
       </c>
       <c r="G26">
-        <v>8.39</v>
+        <v>6.4</v>
       </c>
       <c r="H26" s="4">
-        <v>19234.22</v>
+        <v>122131.86</v>
       </c>
       <c r="I26">
-        <v>6.74</v>
+        <v>3.92</v>
       </c>
       <c r="J26">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K26">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L26">
-        <v>94.13</v>
+        <v>88.95</v>
       </c>
       <c r="M26">
-        <v>-8.82</v>
+        <v>-9.9499999999999993</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1745,37 +1739,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>36150</v>
+        <v>92900</v>
       </c>
       <c r="D27" s="3">
-        <v>-0.1096</v>
+        <v>4.6199999999999998E-2</v>
       </c>
       <c r="E27">
-        <v>11.21</v>
+        <v>8.11</v>
       </c>
       <c r="F27">
-        <v>6.55</v>
+        <v>10.44</v>
       </c>
       <c r="G27">
-        <v>6.4</v>
+        <v>8.66</v>
       </c>
       <c r="H27" s="4">
-        <v>122131.86</v>
+        <v>119742.76</v>
       </c>
       <c r="I27">
-        <v>4.0199999999999996</v>
+        <v>2.33</v>
       </c>
       <c r="J27">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="K27">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="L27">
-        <v>86.36</v>
+        <v>96.48</v>
       </c>
       <c r="M27">
-        <v>-12.26</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1786,37 +1780,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>88800</v>
+        <v>230500</v>
       </c>
       <c r="D28" s="3">
-        <v>-8.1699999999999995E-2</v>
+        <v>0.1162</v>
       </c>
       <c r="E28">
-        <v>8.11</v>
+        <v>11.54</v>
       </c>
       <c r="F28">
-        <v>10.44</v>
+        <v>20.98</v>
       </c>
       <c r="G28">
-        <v>8.66</v>
+        <v>9.6</v>
       </c>
       <c r="H28" s="4">
-        <v>119742.76</v>
+        <v>189057.03</v>
       </c>
       <c r="I28">
-        <v>2.4300000000000002</v>
+        <v>1.73</v>
       </c>
       <c r="J28">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K28">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L28">
-        <v>92.64</v>
+        <v>95.37</v>
       </c>
       <c r="M28">
-        <v>-8.36</v>
+        <v>-10.83</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1827,37 +1821,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>206500</v>
+        <v>66600</v>
       </c>
       <c r="D29" s="3">
-        <v>-0.1414</v>
+        <v>8.4699999999999998E-2</v>
       </c>
       <c r="E29">
-        <v>11.54</v>
+        <v>4.12</v>
       </c>
       <c r="F29">
-        <v>20.98</v>
+        <v>5.22</v>
       </c>
       <c r="G29">
-        <v>9.6</v>
+        <v>11.01</v>
       </c>
       <c r="H29" s="4">
-        <v>189057.03</v>
+        <v>151788</v>
       </c>
       <c r="I29">
-        <v>1.93</v>
+        <v>4.05</v>
       </c>
       <c r="J29">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K29">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L29">
-        <v>85.71</v>
+        <v>95.32</v>
       </c>
       <c r="M29">
-        <v>-20.12</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1868,37 +1862,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>61400</v>
+        <v>111200</v>
       </c>
       <c r="D30" s="3">
-        <v>-0.12909999999999999</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="E30">
-        <v>4.12</v>
+        <v>9.11</v>
       </c>
       <c r="F30">
-        <v>5.22</v>
+        <v>10.57</v>
       </c>
       <c r="G30">
-        <v>11.01</v>
+        <v>9.4</v>
       </c>
       <c r="H30" s="4">
-        <v>151788</v>
+        <v>159337.74</v>
       </c>
       <c r="I30">
-        <v>4.4000000000000004</v>
+        <v>3.24</v>
       </c>
       <c r="J30">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="K30">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="L30">
-        <v>87.75</v>
+        <v>92.61</v>
       </c>
       <c r="M30">
-        <v>-10.63</v>
+        <v>-8.6999999999999993</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1909,37 +1903,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>105500</v>
+        <v>149000</v>
       </c>
       <c r="D31" s="3">
-        <v>-0.1216</v>
+        <v>8.2100000000000006E-2</v>
       </c>
       <c r="E31">
-        <v>9.11</v>
+        <v>8.86</v>
       </c>
       <c r="F31">
-        <v>10.57</v>
+        <v>11.63</v>
       </c>
       <c r="G31">
-        <v>9.4</v>
+        <v>8.51</v>
       </c>
       <c r="H31" s="4">
-        <v>159337.74</v>
+        <v>160038.65</v>
       </c>
       <c r="I31">
-        <v>3.41</v>
+        <v>2.13</v>
       </c>
       <c r="J31">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="K31">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="L31">
-        <v>88.27</v>
+        <v>95.69</v>
       </c>
       <c r="M31">
-        <v>-13.38</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1950,37 +1944,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>137700</v>
+        <v>18800</v>
       </c>
       <c r="D32" s="3">
-        <v>-0.10290000000000001</v>
+        <v>6.5799999999999997E-2</v>
       </c>
       <c r="E32">
-        <v>8.86</v>
+        <v>6.96</v>
       </c>
       <c r="F32">
-        <v>11.63</v>
+        <v>9.58</v>
       </c>
       <c r="G32">
-        <v>8.51</v>
+        <v>7.18</v>
       </c>
       <c r="H32" s="4">
-        <v>160038.65</v>
+        <v>34223.949999999997</v>
       </c>
       <c r="I32">
-        <v>2.31</v>
+        <v>3.46</v>
       </c>
       <c r="J32">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K32">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L32">
-        <v>88.83</v>
+        <v>94.38</v>
       </c>
       <c r="M32">
-        <v>-13.4</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -1991,37 +1985,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>17640</v>
+        <v>17250</v>
       </c>
       <c r="D33" s="3">
-        <v>-0.1037</v>
+        <v>5.96E-2</v>
       </c>
       <c r="E33">
-        <v>6.96</v>
+        <v>3.6</v>
       </c>
       <c r="F33">
-        <v>9.58</v>
+        <v>9.42</v>
       </c>
       <c r="G33">
-        <v>7.18</v>
+        <v>5.91</v>
       </c>
       <c r="H33" s="4">
-        <v>34223.949999999997</v>
+        <v>38541.279999999999</v>
       </c>
       <c r="I33">
-        <v>3.68</v>
+        <v>2.9</v>
       </c>
       <c r="J33">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K33">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L33">
-        <v>89.04</v>
+        <v>92.6</v>
       </c>
       <c r="M33">
-        <v>-11.49</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2032,37 +2026,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>16280</v>
+        <v>61700</v>
       </c>
       <c r="D34" s="3">
-        <v>-0.10059999999999999</v>
+        <v>6.0100000000000001E-2</v>
       </c>
       <c r="E34">
-        <v>3.6</v>
+        <v>10.79</v>
       </c>
       <c r="F34">
-        <v>9.42</v>
+        <v>10.55</v>
       </c>
       <c r="G34">
-        <v>5.91</v>
+        <v>8.93</v>
       </c>
       <c r="H34" s="4">
-        <v>38541.279999999999</v>
+        <v>92723.77</v>
       </c>
       <c r="I34">
-        <v>3.07</v>
+        <v>3.24</v>
       </c>
       <c r="J34">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K34">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L34">
-        <v>87.8</v>
+        <v>88.48</v>
       </c>
       <c r="M34">
-        <v>-11.47</v>
+        <v>-15.36</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2073,37 +2067,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>58200</v>
+        <v>29250</v>
       </c>
       <c r="D35" s="3">
-        <v>-0.12870000000000001</v>
+        <v>3.3599999999999998E-2</v>
       </c>
       <c r="E35">
-        <v>10.79</v>
+        <v>12.8</v>
       </c>
       <c r="F35">
-        <v>10.55</v>
+        <v>13.49</v>
       </c>
       <c r="G35">
-        <v>8.93</v>
+        <v>12.93</v>
       </c>
       <c r="H35" s="4">
-        <v>92723.77</v>
+        <v>31004.78</v>
       </c>
       <c r="I35">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="J35">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="K35">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="L35">
-        <v>83.35</v>
+        <v>93.18</v>
       </c>
       <c r="M35">
-        <v>-20.16</v>
+        <v>-7.87</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2114,37 +2108,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>28300</v>
+        <v>49250</v>
       </c>
       <c r="D36" s="3">
-        <v>-9.1499999999999998E-2</v>
+        <v>4.1200000000000001E-2</v>
       </c>
       <c r="E36">
-        <v>12.8</v>
+        <v>18.690000000000001</v>
       </c>
       <c r="F36">
-        <v>13.49</v>
+        <v>11.56</v>
       </c>
       <c r="G36">
-        <v>12.93</v>
+        <v>6.83</v>
       </c>
       <c r="H36" s="4">
-        <v>31004.78</v>
+        <v>57293.3</v>
       </c>
       <c r="I36">
-        <v>3.52</v>
+        <v>2.44</v>
       </c>
       <c r="J36">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="K36">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="L36">
-        <v>90.75</v>
+        <v>91.5</v>
       </c>
       <c r="M36">
-        <v>-10.87</v>
+        <v>-7.08</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2155,78 +2149,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>47300</v>
+        <v>33750</v>
       </c>
       <c r="D37" s="3">
-        <v>-8.8599999999999998E-2</v>
+        <v>6.13E-2</v>
       </c>
       <c r="E37">
-        <v>18.690000000000001</v>
+        <v>9.39</v>
       </c>
       <c r="F37">
-        <v>11.56</v>
+        <v>10.74</v>
       </c>
       <c r="G37">
-        <v>6.83</v>
+        <v>9.73</v>
       </c>
       <c r="H37" s="4">
-        <v>57293.3</v>
+        <v>48211.77</v>
       </c>
       <c r="I37">
-        <v>2.54</v>
+        <v>3.56</v>
       </c>
       <c r="J37">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="K37">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="L37">
-        <v>87.53</v>
+        <v>94.12</v>
       </c>
       <c r="M37">
-        <v>-10.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A38" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B38" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="2">
-        <v>31800</v>
-      </c>
-      <c r="D38" s="3">
-        <v>-9.9199999999999997E-2</v>
-      </c>
-      <c r="E38">
-        <v>9.39</v>
-      </c>
-      <c r="F38">
-        <v>10.74</v>
-      </c>
-      <c r="G38">
-        <v>9.73</v>
-      </c>
-      <c r="H38" s="4">
-        <v>48211.77</v>
-      </c>
-      <c r="I38">
-        <v>3.77</v>
-      </c>
-      <c r="J38">
-        <v>69</v>
-      </c>
-      <c r="K38">
-        <v>69</v>
-      </c>
-      <c r="L38">
-        <v>89.11</v>
-      </c>
-      <c r="M38">
-        <v>-11.67</v>
+        <v>-6.25</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AC5C209-EC2B-475A-9C30-1C630691E0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CDB591C-AFDD-499B-90F4-BB61D0232764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{258F7C3A-C8F0-4560-9D3E-7CAADC7ACC95}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A61DE496-9D22-49D4-A609-5B286738B57C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
   <si>
     <t>종목코드</t>
   </si>
@@ -58,6 +58,12 @@
   </si>
   <si>
     <t>해당등락률</t>
+  </si>
+  <si>
+    <t>000240</t>
+  </si>
+  <si>
+    <t>한국앤컴퍼니</t>
   </si>
   <si>
     <t>000270</t>
@@ -648,14 +654,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E54594-4072-4D42-BF2A-E6100C2614FB}">
-  <dimension ref="A1:M37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD5A887-DB7F-4FF5-B356-BC4D28057A2A}">
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -714,37 +720,37 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>166400</v>
+        <v>26000</v>
       </c>
       <c r="D2" s="3">
-        <v>6.1899999999999997E-2</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="E2">
-        <v>19.09</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="F2">
-        <v>14.17</v>
+        <v>8.9</v>
       </c>
       <c r="G2">
-        <v>18.03</v>
+        <v>5.8</v>
       </c>
       <c r="H2" s="4">
-        <v>150938.41</v>
+        <v>48390.96</v>
       </c>
       <c r="I2">
-        <v>3.91</v>
+        <v>3.85</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="K2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="L2">
-        <v>98.72</v>
+        <v>87.53</v>
       </c>
       <c r="M2">
-        <v>-19.03</v>
+        <v>-9.41</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -755,37 +761,37 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>491500</v>
+        <v>167000</v>
       </c>
       <c r="D3" s="3">
-        <v>5.0200000000000002E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="E3">
-        <v>13.09</v>
+        <v>19.09</v>
       </c>
       <c r="F3">
-        <v>13.88</v>
+        <v>14.17</v>
       </c>
       <c r="G3">
-        <v>12.47</v>
+        <v>18.03</v>
       </c>
       <c r="H3" s="4">
-        <v>405451.96</v>
+        <v>150938.41</v>
       </c>
       <c r="I3">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="J3">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L3">
-        <v>92.05</v>
+        <v>98.58</v>
       </c>
       <c r="M3">
-        <v>-7.26</v>
+        <v>-8.39</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -796,37 +802,37 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>39750</v>
+        <v>496500</v>
       </c>
       <c r="D4" s="3">
-        <v>3.2500000000000001E-2</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="E4">
-        <v>7.12</v>
+        <v>13.09</v>
       </c>
       <c r="F4">
-        <v>9.6199999999999992</v>
+        <v>13.88</v>
       </c>
       <c r="G4">
-        <v>12.61</v>
+        <v>12.47</v>
       </c>
       <c r="H4" s="4">
-        <v>72041.39</v>
+        <v>405451.96</v>
       </c>
       <c r="I4">
-        <v>5.03</v>
+        <v>3.83</v>
       </c>
       <c r="J4">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K4">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L4">
-        <v>91.5</v>
+        <v>92.86</v>
       </c>
       <c r="M4">
-        <v>-6.69</v>
+        <v>-4.8899999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -837,37 +843,37 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>77200</v>
+        <v>39500</v>
       </c>
       <c r="D5" s="3">
-        <v>0.13700000000000001</v>
+        <v>-6.3E-3</v>
       </c>
       <c r="E5">
-        <v>4.05</v>
+        <v>7.12</v>
       </c>
       <c r="F5">
-        <v>7.82</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="G5">
-        <v>6.06</v>
+        <v>12.61</v>
       </c>
       <c r="H5" s="4">
-        <v>65679.45</v>
+        <v>72041.39</v>
       </c>
       <c r="I5">
-        <v>1.94</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="J5">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K5">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="L5">
-        <v>95.16</v>
+        <v>90.75</v>
       </c>
       <c r="M5">
-        <v>-14.51</v>
+        <v>-8.56</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -878,37 +884,37 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>61000</v>
+        <v>78800</v>
       </c>
       <c r="D6" s="3">
-        <v>4.2700000000000002E-2</v>
+        <v>2.07E-2</v>
       </c>
       <c r="E6">
-        <v>1.04</v>
+        <v>4.05</v>
       </c>
       <c r="F6">
-        <v>3.97</v>
+        <v>7.82</v>
       </c>
       <c r="G6">
-        <v>4.21</v>
+        <v>6.06</v>
       </c>
       <c r="H6" s="4">
-        <v>53899.69</v>
+        <v>65679.45</v>
       </c>
       <c r="I6">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="J6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L6">
-        <v>82.46</v>
+        <v>96.7</v>
       </c>
       <c r="M6">
-        <v>-11.72</v>
+        <v>-1.1299999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -919,37 +925,37 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>39900</v>
+        <v>61900</v>
       </c>
       <c r="D7" s="3">
-        <v>0.10680000000000001</v>
+        <v>1.4800000000000001E-2</v>
       </c>
       <c r="E7">
-        <v>4.57</v>
+        <v>1.04</v>
       </c>
       <c r="F7">
-        <v>7.42</v>
+        <v>3.97</v>
       </c>
       <c r="G7">
-        <v>4.55</v>
+        <v>4.21</v>
       </c>
       <c r="H7" s="4">
-        <v>42814.52</v>
+        <v>53899.69</v>
       </c>
       <c r="I7">
-        <v>3.01</v>
+        <v>1.94</v>
       </c>
       <c r="J7">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="K7">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="L7">
-        <v>102.91</v>
+        <v>84.19</v>
       </c>
       <c r="M7">
-        <v>-11.04</v>
+        <v>-7.61</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -960,37 +966,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>96800</v>
+        <v>40000</v>
       </c>
       <c r="D8" s="3">
-        <v>6.0199999999999997E-2</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="E8">
-        <v>2.16</v>
+        <v>4.57</v>
       </c>
       <c r="F8">
-        <v>5.36</v>
+        <v>7.42</v>
       </c>
       <c r="G8">
-        <v>5.18</v>
+        <v>4.55</v>
       </c>
       <c r="H8" s="4">
-        <v>177736.27</v>
+        <v>42814.52</v>
       </c>
       <c r="I8">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="K8">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="L8">
-        <v>100.55</v>
+        <v>101.79</v>
       </c>
       <c r="M8">
-        <v>-10.119999999999999</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1001,37 +1007,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>13110</v>
+        <v>94000</v>
       </c>
       <c r="D9" s="3">
-        <v>6.0699999999999997E-2</v>
+        <v>-2.8899999999999999E-2</v>
       </c>
       <c r="E9">
-        <v>9.44</v>
+        <v>2.16</v>
       </c>
       <c r="F9">
-        <v>10.67</v>
+        <v>5.36</v>
       </c>
       <c r="G9">
-        <v>9.86</v>
+        <v>5.18</v>
       </c>
       <c r="H9" s="4">
-        <v>19219.419999999998</v>
+        <v>177736.27</v>
       </c>
       <c r="I9">
-        <v>3.93</v>
+        <v>3.3</v>
       </c>
       <c r="J9">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="K9">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="L9">
-        <v>99.59</v>
+        <v>97.33</v>
       </c>
       <c r="M9">
-        <v>-5.82</v>
+        <v>-8.2899999999999991</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1042,37 +1048,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>548000</v>
+        <v>12790</v>
       </c>
       <c r="D10" s="3">
-        <v>9.3799999999999994E-2</v>
+        <v>-2.4400000000000002E-2</v>
       </c>
       <c r="E10">
-        <v>12.43</v>
+        <v>9.44</v>
       </c>
       <c r="F10">
-        <v>10.08</v>
+        <v>10.67</v>
       </c>
       <c r="G10">
-        <v>11.82</v>
+        <v>9.86</v>
       </c>
       <c r="H10" s="4">
-        <v>429918.88</v>
+        <v>19219.419999999998</v>
       </c>
       <c r="I10">
-        <v>2.19</v>
+        <v>4.03</v>
       </c>
       <c r="J10">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K10">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L10">
-        <v>104.68</v>
+        <v>96.67</v>
       </c>
       <c r="M10">
-        <v>-18.690000000000001</v>
+        <v>-4.91</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1083,37 +1089,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>190600</v>
+        <v>553000</v>
       </c>
       <c r="D11" s="3">
-        <v>8.5999999999999993E-2</v>
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="E11">
-        <v>18.96</v>
+        <v>12.43</v>
       </c>
       <c r="F11">
-        <v>19.43</v>
+        <v>10.08</v>
       </c>
       <c r="G11">
-        <v>18.8</v>
+        <v>11.82</v>
       </c>
       <c r="H11" s="4">
-        <v>144109.65</v>
+        <v>429918.88</v>
       </c>
       <c r="I11">
-        <v>3.57</v>
+        <v>2.17</v>
       </c>
       <c r="J11">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K11">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="L11">
-        <v>107.2</v>
+        <v>104.88</v>
       </c>
       <c r="M11">
-        <v>4.0999999999999996</v>
+        <v>-7.06</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1124,37 +1130,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>32050</v>
+        <v>188400</v>
       </c>
       <c r="D12" s="3">
-        <v>0.1128</v>
+        <v>-1.15E-2</v>
       </c>
       <c r="E12">
-        <v>8.73</v>
+        <v>18.96</v>
       </c>
       <c r="F12">
-        <v>11.57</v>
+        <v>19.43</v>
       </c>
       <c r="G12">
-        <v>6.85</v>
+        <v>18.8</v>
       </c>
       <c r="H12" s="4">
-        <v>24348.21</v>
+        <v>144109.65</v>
       </c>
       <c r="I12">
-        <v>2.96</v>
+        <v>3.61</v>
       </c>
       <c r="J12">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="K12">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="L12">
-        <v>101.9</v>
+        <v>104.57</v>
       </c>
       <c r="M12">
-        <v>-9.7200000000000006</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1165,37 +1171,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>24500</v>
+        <v>32200</v>
       </c>
       <c r="D13" s="3">
-        <v>4.9299999999999997E-2</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="E13">
-        <v>19.78</v>
+        <v>8.73</v>
       </c>
       <c r="F13">
-        <v>13.82</v>
+        <v>11.57</v>
       </c>
       <c r="G13">
-        <v>23.29</v>
+        <v>6.85</v>
       </c>
       <c r="H13" s="4">
-        <v>32624.26</v>
+        <v>24348.21</v>
       </c>
       <c r="I13">
-        <v>4.08</v>
+        <v>2.95</v>
       </c>
       <c r="J13">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K13">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L13">
-        <v>86.93</v>
+        <v>101.24</v>
       </c>
       <c r="M13">
-        <v>-9.93</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1206,37 +1212,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>227000</v>
+        <v>25100</v>
       </c>
       <c r="D14" s="3">
-        <v>6.0699999999999997E-2</v>
+        <v>2.4500000000000001E-2</v>
       </c>
       <c r="E14">
-        <v>13.17</v>
+        <v>19.78</v>
       </c>
       <c r="F14">
-        <v>11.69</v>
+        <v>13.82</v>
       </c>
       <c r="G14">
-        <v>18.010000000000002</v>
+        <v>23.29</v>
       </c>
       <c r="H14" s="4">
-        <v>207156.6</v>
+        <v>32624.26</v>
       </c>
       <c r="I14">
-        <v>2.36</v>
+        <v>3.98</v>
       </c>
       <c r="J14">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="K14">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="L14">
-        <v>100.17</v>
+        <v>88.92</v>
       </c>
       <c r="M14">
-        <v>-9.02</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1247,37 +1253,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>95200</v>
+        <v>230500</v>
       </c>
       <c r="D15" s="3">
-        <v>8.1799999999999998E-2</v>
+        <v>1.54E-2</v>
       </c>
       <c r="E15">
-        <v>12.89</v>
+        <v>13.17</v>
       </c>
       <c r="F15">
-        <v>13.94</v>
+        <v>11.69</v>
       </c>
       <c r="G15">
-        <v>9.44</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H15" s="4">
-        <v>87743.72</v>
+        <v>207156.6</v>
       </c>
       <c r="I15">
-        <v>3.68</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="J15">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K15">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L15">
-        <v>95.93</v>
+        <v>101.07</v>
       </c>
       <c r="M15">
-        <v>-10.86</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1288,37 +1294,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>77900</v>
+        <v>95900</v>
       </c>
       <c r="D16" s="3">
-        <v>0.1081</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="E16">
-        <v>10.83</v>
+        <v>12.89</v>
       </c>
       <c r="F16">
-        <v>3.37</v>
+        <v>13.94</v>
       </c>
       <c r="G16">
-        <v>9.48</v>
+        <v>9.44</v>
       </c>
       <c r="H16" s="4">
-        <v>54894.12</v>
+        <v>87743.72</v>
       </c>
       <c r="I16">
-        <v>4.54</v>
+        <v>3.65</v>
       </c>
       <c r="J16">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K16">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L16">
-        <v>100.7</v>
+        <v>96.04</v>
       </c>
       <c r="M16">
-        <v>-2.38</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1329,37 +1335,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>86000</v>
+        <v>76500</v>
       </c>
       <c r="D17" s="3">
-        <v>5.3900000000000003E-2</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="E17">
-        <v>14.42</v>
+        <v>10.83</v>
       </c>
       <c r="F17">
-        <v>24.2</v>
+        <v>3.37</v>
       </c>
       <c r="G17">
-        <v>15.82</v>
+        <v>9.48</v>
       </c>
       <c r="H17" s="4">
-        <v>36460.550000000003</v>
+        <v>54894.12</v>
       </c>
       <c r="I17">
-        <v>6.4</v>
+        <v>4.63</v>
       </c>
       <c r="J17">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K17">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L17">
-        <v>85.65</v>
+        <v>98.42</v>
       </c>
       <c r="M17">
-        <v>-12.87</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1370,37 +1376,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>23800</v>
+        <v>87000</v>
       </c>
       <c r="D18" s="3">
-        <v>6.25E-2</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="E18">
-        <v>8.06</v>
+        <v>14.42</v>
       </c>
       <c r="F18">
-        <v>8.64</v>
+        <v>24.2</v>
       </c>
       <c r="G18">
-        <v>8.77</v>
+        <v>15.82</v>
       </c>
       <c r="H18" s="4">
-        <v>44443.18</v>
+        <v>36460.550000000003</v>
       </c>
       <c r="I18">
-        <v>4.47</v>
+        <v>6.32</v>
       </c>
       <c r="J18">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K18">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L18">
-        <v>95.83</v>
+        <v>86.93</v>
       </c>
       <c r="M18">
-        <v>-7.57</v>
+        <v>-8.0299999999999994</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1411,37 +1417,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>59500</v>
+        <v>23650</v>
       </c>
       <c r="D19" s="3">
-        <v>3.8399999999999997E-2</v>
+        <v>-6.3E-3</v>
       </c>
       <c r="E19">
-        <v>7.45</v>
+        <v>8.06</v>
       </c>
       <c r="F19">
-        <v>7.45</v>
+        <v>8.64</v>
       </c>
       <c r="G19">
-        <v>7.69</v>
+        <v>8.77</v>
       </c>
       <c r="H19" s="4">
-        <v>79986.48</v>
+        <v>44443.18</v>
       </c>
       <c r="I19">
-        <v>4.71</v>
+        <v>4.5</v>
       </c>
       <c r="J19">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K19">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L19">
-        <v>97.54</v>
+        <v>94.88</v>
       </c>
       <c r="M19">
-        <v>-5.56</v>
+        <v>-5.78</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1452,37 +1458,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>20400</v>
+        <v>59300</v>
       </c>
       <c r="D20" s="3">
-        <v>3.0800000000000001E-2</v>
+        <v>-3.3999999999999998E-3</v>
       </c>
       <c r="E20">
-        <v>15.12</v>
+        <v>7.45</v>
       </c>
       <c r="F20">
-        <v>13.07</v>
+        <v>7.45</v>
       </c>
       <c r="G20">
-        <v>15.58</v>
+        <v>7.69</v>
       </c>
       <c r="H20" s="4">
-        <v>15310.06</v>
+        <v>79986.48</v>
       </c>
       <c r="I20">
-        <v>6.03</v>
+        <v>4.72</v>
       </c>
       <c r="J20">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="K20">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="L20">
-        <v>94.85</v>
+        <v>96.86</v>
       </c>
       <c r="M20">
-        <v>-7.06</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1493,37 +1499,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>57800</v>
+        <v>20200</v>
       </c>
       <c r="D21" s="3">
-        <v>5.28E-2</v>
+        <v>-9.7999999999999997E-3</v>
       </c>
       <c r="E21">
-        <v>2.85</v>
+        <v>15.12</v>
       </c>
       <c r="F21">
-        <v>12.83</v>
+        <v>13.07</v>
       </c>
       <c r="G21">
-        <v>5.63</v>
+        <v>15.58</v>
       </c>
       <c r="H21" s="4">
-        <v>71073.47</v>
+        <v>15310.06</v>
       </c>
       <c r="I21">
-        <v>3.46</v>
+        <v>6.09</v>
       </c>
       <c r="J21">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="K21">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="L21">
-        <v>93.94</v>
+        <v>94.12</v>
       </c>
       <c r="M21">
-        <v>-9.4</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1534,37 +1540,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>15010</v>
+        <v>59000</v>
       </c>
       <c r="D22" s="3">
-        <v>2.9499999999999998E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="E22">
-        <v>4.4000000000000004</v>
+        <v>2.85</v>
       </c>
       <c r="F22">
-        <v>6.71</v>
+        <v>12.83</v>
       </c>
       <c r="G22">
-        <v>6.75</v>
+        <v>5.63</v>
       </c>
       <c r="H22" s="4">
-        <v>20394.86</v>
+        <v>71073.47</v>
       </c>
       <c r="I22">
-        <v>4.33</v>
+        <v>3.39</v>
       </c>
       <c r="J22">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K22">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L22">
-        <v>91.26</v>
+        <v>95.59</v>
       </c>
       <c r="M22">
-        <v>-9.25</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1575,37 +1581,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>214000</v>
+        <v>15090</v>
       </c>
       <c r="D23" s="3">
-        <v>8.3500000000000005E-2</v>
+        <v>5.3E-3</v>
       </c>
       <c r="E23">
-        <v>4.66</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F23">
-        <v>4.66</v>
+        <v>6.71</v>
       </c>
       <c r="G23">
-        <v>4.88</v>
+        <v>6.75</v>
       </c>
       <c r="H23" s="4">
-        <v>324173.33</v>
+        <v>20394.86</v>
       </c>
       <c r="I23">
-        <v>2.48</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="J23">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="K23">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="L23">
-        <v>102.59</v>
+        <v>91.97</v>
       </c>
       <c r="M23">
-        <v>-6.96</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1616,25 +1622,25 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>156600</v>
+        <v>210000</v>
       </c>
       <c r="D24" s="3">
-        <v>3.3000000000000002E-2</v>
+        <v>-1.8700000000000001E-2</v>
       </c>
       <c r="E24">
-        <v>12.66</v>
+        <v>4.66</v>
       </c>
       <c r="F24">
-        <v>11.88</v>
+        <v>4.66</v>
       </c>
       <c r="G24">
-        <v>11.14</v>
+        <v>4.88</v>
       </c>
       <c r="H24" s="4">
-        <v>83639.03</v>
+        <v>324173.33</v>
       </c>
       <c r="I24">
-        <v>3.45</v>
+        <v>2.52</v>
       </c>
       <c r="J24">
         <v>76</v>
@@ -1643,10 +1649,10 @@
         <v>76</v>
       </c>
       <c r="L24">
-        <v>93.71</v>
+        <v>99.93</v>
       </c>
       <c r="M24">
-        <v>-3.99</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1657,37 +1663,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>17830</v>
+        <v>154700</v>
       </c>
       <c r="D25" s="3">
-        <v>2.6499999999999999E-2</v>
+        <v>-1.21E-2</v>
       </c>
       <c r="E25">
-        <v>12.08</v>
+        <v>12.66</v>
       </c>
       <c r="F25">
-        <v>8.58</v>
+        <v>11.88</v>
       </c>
       <c r="G25">
-        <v>8.39</v>
+        <v>11.14</v>
       </c>
       <c r="H25" s="4">
-        <v>19234.22</v>
+        <v>83639.03</v>
       </c>
       <c r="I25">
-        <v>6.56</v>
+        <v>3.49</v>
       </c>
       <c r="J25">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="K25">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="L25">
-        <v>96.52</v>
+        <v>92.57</v>
       </c>
       <c r="M25">
-        <v>-6.4</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1698,37 +1704,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>37100</v>
+        <v>18080</v>
       </c>
       <c r="D26" s="3">
-        <v>2.63E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="E26">
-        <v>11.21</v>
+        <v>12.08</v>
       </c>
       <c r="F26">
-        <v>6.55</v>
+        <v>8.58</v>
       </c>
       <c r="G26">
-        <v>6.4</v>
+        <v>8.39</v>
       </c>
       <c r="H26" s="4">
-        <v>122131.86</v>
+        <v>19234.22</v>
       </c>
       <c r="I26">
-        <v>3.92</v>
+        <v>6.47</v>
       </c>
       <c r="J26">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K26">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L26">
-        <v>88.95</v>
+        <v>97.6</v>
       </c>
       <c r="M26">
-        <v>-9.9499999999999993</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1739,37 +1745,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>92900</v>
+        <v>36900</v>
       </c>
       <c r="D27" s="3">
-        <v>4.6199999999999998E-2</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="E27">
-        <v>8.11</v>
+        <v>11.21</v>
       </c>
       <c r="F27">
-        <v>10.44</v>
+        <v>6.55</v>
       </c>
       <c r="G27">
-        <v>8.66</v>
+        <v>6.4</v>
       </c>
       <c r="H27" s="4">
-        <v>119742.76</v>
+        <v>122131.86</v>
       </c>
       <c r="I27">
-        <v>2.33</v>
+        <v>3.94</v>
       </c>
       <c r="J27">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="K27">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="L27">
-        <v>96.48</v>
+        <v>88.74</v>
       </c>
       <c r="M27">
-        <v>-4.13</v>
+        <v>-9.11</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1780,37 +1786,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>230500</v>
+        <v>91800</v>
       </c>
       <c r="D28" s="3">
-        <v>0.1162</v>
+        <v>-1.18E-2</v>
       </c>
       <c r="E28">
-        <v>11.54</v>
+        <v>8.11</v>
       </c>
       <c r="F28">
-        <v>20.98</v>
+        <v>10.44</v>
       </c>
       <c r="G28">
-        <v>9.6</v>
+        <v>8.66</v>
       </c>
       <c r="H28" s="4">
-        <v>189057.03</v>
+        <v>119742.76</v>
       </c>
       <c r="I28">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="J28">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="K28">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="L28">
-        <v>95.37</v>
+        <v>94.88</v>
       </c>
       <c r="M28">
-        <v>-10.83</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1821,37 +1827,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>66600</v>
+        <v>230000</v>
       </c>
       <c r="D29" s="3">
-        <v>8.4699999999999998E-2</v>
+        <v>-2.2000000000000001E-3</v>
       </c>
       <c r="E29">
-        <v>4.12</v>
+        <v>11.54</v>
       </c>
       <c r="F29">
-        <v>5.22</v>
+        <v>20.98</v>
       </c>
       <c r="G29">
-        <v>11.01</v>
+        <v>9.6</v>
       </c>
       <c r="H29" s="4">
-        <v>151788</v>
+        <v>189057.03</v>
       </c>
       <c r="I29">
-        <v>4.05</v>
+        <v>1.73</v>
       </c>
       <c r="J29">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K29">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L29">
-        <v>95.32</v>
+        <v>94.57</v>
       </c>
       <c r="M29">
-        <v>-3.06</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1862,37 +1868,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>111200</v>
+        <v>65600</v>
       </c>
       <c r="D30" s="3">
-        <v>5.3999999999999999E-2</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="E30">
-        <v>9.11</v>
+        <v>4.12</v>
       </c>
       <c r="F30">
-        <v>10.57</v>
+        <v>5.22</v>
       </c>
       <c r="G30">
-        <v>9.4</v>
+        <v>11.01</v>
       </c>
       <c r="H30" s="4">
-        <v>159337.74</v>
+        <v>151788</v>
       </c>
       <c r="I30">
-        <v>3.24</v>
+        <v>4.12</v>
       </c>
       <c r="J30">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="K30">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="L30">
-        <v>92.61</v>
+        <v>93.81</v>
       </c>
       <c r="M30">
-        <v>-8.6999999999999993</v>
+        <v>-6.95</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1903,37 +1909,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>149000</v>
+        <v>110300</v>
       </c>
       <c r="D31" s="3">
-        <v>8.2100000000000006E-2</v>
+        <v>-8.0999999999999996E-3</v>
       </c>
       <c r="E31">
-        <v>8.86</v>
+        <v>9.11</v>
       </c>
       <c r="F31">
-        <v>11.63</v>
+        <v>10.57</v>
       </c>
       <c r="G31">
-        <v>8.51</v>
+        <v>9.4</v>
       </c>
       <c r="H31" s="4">
-        <v>160038.65</v>
+        <v>159337.74</v>
       </c>
       <c r="I31">
-        <v>2.13</v>
+        <v>3.26</v>
       </c>
       <c r="J31">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K31">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="L31">
-        <v>95.69</v>
+        <v>91.6</v>
       </c>
       <c r="M31">
-        <v>-6.29</v>
+        <v>-8.16</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1944,37 +1950,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>18800</v>
+        <v>147400</v>
       </c>
       <c r="D32" s="3">
-        <v>6.5799999999999997E-2</v>
+        <v>-1.0699999999999999E-2</v>
       </c>
       <c r="E32">
-        <v>6.96</v>
+        <v>8.86</v>
       </c>
       <c r="F32">
-        <v>9.58</v>
+        <v>11.63</v>
       </c>
       <c r="G32">
-        <v>7.18</v>
+        <v>8.51</v>
       </c>
       <c r="H32" s="4">
-        <v>34223.949999999997</v>
+        <v>160038.65</v>
       </c>
       <c r="I32">
-        <v>3.46</v>
+        <v>2.15</v>
       </c>
       <c r="J32">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K32">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L32">
-        <v>94.38</v>
+        <v>94.25</v>
       </c>
       <c r="M32">
-        <v>-5.67</v>
+        <v>-3.97</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -1985,37 +1991,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>17250</v>
+        <v>18420</v>
       </c>
       <c r="D33" s="3">
-        <v>5.96E-2</v>
+        <v>-2.0199999999999999E-2</v>
       </c>
       <c r="E33">
-        <v>3.6</v>
+        <v>6.96</v>
       </c>
       <c r="F33">
-        <v>9.42</v>
+        <v>9.58</v>
       </c>
       <c r="G33">
-        <v>5.91</v>
+        <v>7.18</v>
       </c>
       <c r="H33" s="4">
-        <v>38541.279999999999</v>
+        <v>34223.949999999997</v>
       </c>
       <c r="I33">
-        <v>2.9</v>
+        <v>3.53</v>
       </c>
       <c r="J33">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K33">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L33">
-        <v>92.6</v>
+        <v>92.02</v>
       </c>
       <c r="M33">
-        <v>-6.2</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2026,37 +2032,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>61700</v>
+        <v>17050</v>
       </c>
       <c r="D34" s="3">
-        <v>6.0100000000000001E-2</v>
+        <v>-1.1599999999999999E-2</v>
       </c>
       <c r="E34">
-        <v>10.79</v>
+        <v>3.6</v>
       </c>
       <c r="F34">
-        <v>10.55</v>
+        <v>9.42</v>
       </c>
       <c r="G34">
-        <v>8.93</v>
+        <v>5.91</v>
       </c>
       <c r="H34" s="4">
-        <v>92723.77</v>
+        <v>38541.279999999999</v>
       </c>
       <c r="I34">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="J34">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K34">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L34">
-        <v>88.48</v>
+        <v>91.11</v>
       </c>
       <c r="M34">
-        <v>-15.36</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2067,37 +2073,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>29250</v>
+        <v>59300</v>
       </c>
       <c r="D35" s="3">
-        <v>3.3599999999999998E-2</v>
+        <v>-3.8899999999999997E-2</v>
       </c>
       <c r="E35">
-        <v>12.8</v>
+        <v>10.79</v>
       </c>
       <c r="F35">
-        <v>13.49</v>
+        <v>10.55</v>
       </c>
       <c r="G35">
-        <v>12.93</v>
+        <v>8.93</v>
       </c>
       <c r="H35" s="4">
-        <v>31004.78</v>
+        <v>92723.77</v>
       </c>
       <c r="I35">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="J35">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="K35">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="L35">
-        <v>93.18</v>
+        <v>85.21</v>
       </c>
       <c r="M35">
-        <v>-7.87</v>
+        <v>-11.23</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2108,37 +2114,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>49250</v>
+        <v>29400</v>
       </c>
       <c r="D36" s="3">
-        <v>4.1200000000000001E-2</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="E36">
-        <v>18.690000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="F36">
-        <v>11.56</v>
+        <v>13.49</v>
       </c>
       <c r="G36">
-        <v>6.83</v>
+        <v>12.93</v>
       </c>
       <c r="H36" s="4">
-        <v>57293.3</v>
+        <v>31004.78</v>
       </c>
       <c r="I36">
-        <v>2.44</v>
+        <v>3.38</v>
       </c>
       <c r="J36">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="K36">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L36">
-        <v>91.5</v>
+        <v>93.05</v>
       </c>
       <c r="M36">
-        <v>-7.08</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2149,37 +2155,78 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>33750</v>
+        <v>50000</v>
       </c>
       <c r="D37" s="3">
-        <v>6.13E-2</v>
+        <v>1.52E-2</v>
       </c>
       <c r="E37">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="F37">
+        <v>11.56</v>
+      </c>
+      <c r="G37">
+        <v>6.83</v>
+      </c>
+      <c r="H37" s="4">
+        <v>57293.3</v>
+      </c>
+      <c r="I37">
+        <v>2.4</v>
+      </c>
+      <c r="J37">
+        <v>45</v>
+      </c>
+      <c r="K37">
+        <v>45</v>
+      </c>
+      <c r="L37">
+        <v>92.98</v>
+      </c>
+      <c r="M37">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="2">
+        <v>33050</v>
+      </c>
+      <c r="D38" s="3">
+        <v>-2.07E-2</v>
+      </c>
+      <c r="E38">
         <v>9.39</v>
       </c>
-      <c r="F37">
+      <c r="F38">
         <v>10.74</v>
       </c>
-      <c r="G37">
+      <c r="G38">
         <v>9.73</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H38" s="4">
         <v>48211.77</v>
       </c>
-      <c r="I37">
-        <v>3.56</v>
-      </c>
-      <c r="J37">
-        <v>75</v>
-      </c>
-      <c r="K37">
-        <v>75</v>
-      </c>
-      <c r="L37">
-        <v>94.12</v>
-      </c>
-      <c r="M37">
-        <v>-6.25</v>
+      <c r="I38">
+        <v>3.63</v>
+      </c>
+      <c r="J38">
+        <v>73</v>
+      </c>
+      <c r="K38">
+        <v>73</v>
+      </c>
+      <c r="L38">
+        <v>91.79</v>
+      </c>
+      <c r="M38">
+        <v>-6.37</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CDB591C-AFDD-499B-90F4-BB61D0232764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B1D2F8D-190A-4287-9E51-34C9AFA571E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A61DE496-9D22-49D4-A609-5B286738B57C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{2B39F4A7-1B7A-4A0E-957A-C7A9CC6A2640}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
   <si>
     <t>종목코드</t>
   </si>
@@ -96,6 +96,18 @@
     <t>세아베스틸지주</t>
   </si>
   <si>
+    <t>001680</t>
+  </si>
+  <si>
+    <t>대상</t>
+  </si>
+  <si>
+    <t>002310</t>
+  </si>
+  <si>
+    <t>아세아제지</t>
+  </si>
+  <si>
     <t>003540</t>
   </si>
   <si>
@@ -114,6 +126,24 @@
     <t>코리안리</t>
   </si>
   <si>
+    <t>004370</t>
+  </si>
+  <si>
+    <t>농심</t>
+  </si>
+  <si>
+    <t>004980</t>
+  </si>
+  <si>
+    <t>성신양회</t>
+  </si>
+  <si>
+    <t>005180</t>
+  </si>
+  <si>
+    <t>빙그레</t>
+  </si>
+  <si>
     <t>005380</t>
   </si>
   <si>
@@ -132,6 +162,12 @@
     <t>NH투자증권</t>
   </si>
   <si>
+    <t>007310</t>
+  </si>
+  <si>
+    <t>오뚜기</t>
+  </si>
+  <si>
     <t>007340</t>
   </si>
   <si>
@@ -144,6 +180,12 @@
     <t>영원무역홀딩스</t>
   </si>
   <si>
+    <t>011780</t>
+  </si>
+  <si>
+    <t>금호석유화학</t>
+  </si>
+  <si>
     <t>016360</t>
   </si>
   <si>
@@ -216,6 +258,12 @@
     <t>한국가스공사</t>
   </si>
   <si>
+    <t>038500</t>
+  </si>
+  <si>
+    <t>삼표시멘트</t>
+  </si>
+  <si>
     <t>055550</t>
   </si>
   <si>
@@ -270,10 +318,28 @@
     <t>JB금융지주</t>
   </si>
   <si>
+    <t>183190</t>
+  </si>
+  <si>
+    <t>아세아시멘트</t>
+  </si>
+  <si>
     <t>192080</t>
   </si>
   <si>
     <t>더블유게임즈</t>
+  </si>
+  <si>
+    <t>214320</t>
+  </si>
+  <si>
+    <t>이노션</t>
+  </si>
+  <si>
+    <t>300720</t>
+  </si>
+  <si>
+    <t>한일시멘트</t>
   </si>
   <si>
     <t>316140</t>
@@ -654,8 +720,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD5A887-DB7F-4FF5-B356-BC4D28057A2A}">
-  <dimension ref="A1:M38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364AA57A-DA09-4B5E-A948-31004EAD14B2}">
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
@@ -966,37 +1032,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>40000</v>
+        <v>20650</v>
       </c>
       <c r="D8" s="3">
-        <v>2.5000000000000001E-3</v>
+        <v>-9.5999999999999992E-3</v>
       </c>
       <c r="E8">
-        <v>4.57</v>
+        <v>6.94</v>
       </c>
       <c r="F8">
-        <v>7.42</v>
+        <v>6.38</v>
       </c>
       <c r="G8">
-        <v>4.55</v>
+        <v>6.21</v>
       </c>
       <c r="H8" s="4">
-        <v>42814.52</v>
+        <v>39784.050000000003</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>4.12</v>
       </c>
       <c r="J8">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="K8">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="L8">
-        <v>101.79</v>
+        <v>91.56</v>
       </c>
       <c r="M8">
-        <v>-3.38</v>
+        <v>-5.92</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1007,37 +1073,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>94000</v>
+        <v>9430</v>
       </c>
       <c r="D9" s="3">
-        <v>-2.8899999999999999E-2</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="E9">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="F9">
-        <v>5.36</v>
+        <v>4.16</v>
       </c>
       <c r="G9">
-        <v>5.18</v>
+        <v>8.36</v>
       </c>
       <c r="H9" s="4">
-        <v>177736.27</v>
+        <v>20859.37</v>
       </c>
       <c r="I9">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="J9">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K9">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L9">
-        <v>97.33</v>
+        <v>97.4</v>
       </c>
       <c r="M9">
-        <v>-8.2899999999999991</v>
+        <v>-8.98</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1048,37 +1114,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>12790</v>
+        <v>40000</v>
       </c>
       <c r="D10" s="3">
-        <v>-2.4400000000000002E-2</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="E10">
-        <v>9.44</v>
+        <v>4.57</v>
       </c>
       <c r="F10">
-        <v>10.67</v>
+        <v>7.42</v>
       </c>
       <c r="G10">
-        <v>9.86</v>
+        <v>4.55</v>
       </c>
       <c r="H10" s="4">
-        <v>19219.419999999998</v>
+        <v>42814.52</v>
       </c>
       <c r="I10">
-        <v>4.03</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K10">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L10">
-        <v>96.67</v>
+        <v>101.79</v>
       </c>
       <c r="M10">
-        <v>-4.91</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1089,37 +1155,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>553000</v>
+        <v>94000</v>
       </c>
       <c r="D11" s="3">
-        <v>9.1000000000000004E-3</v>
+        <v>-2.8899999999999999E-2</v>
       </c>
       <c r="E11">
-        <v>12.43</v>
+        <v>2.16</v>
       </c>
       <c r="F11">
-        <v>10.08</v>
+        <v>5.36</v>
       </c>
       <c r="G11">
-        <v>11.82</v>
+        <v>5.18</v>
       </c>
       <c r="H11" s="4">
-        <v>429918.88</v>
+        <v>177736.27</v>
       </c>
       <c r="I11">
-        <v>2.17</v>
+        <v>3.3</v>
       </c>
       <c r="J11">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="K11">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="L11">
-        <v>104.88</v>
+        <v>97.33</v>
       </c>
       <c r="M11">
-        <v>-7.06</v>
+        <v>-8.2899999999999991</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1130,37 +1196,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>188400</v>
+        <v>12790</v>
       </c>
       <c r="D12" s="3">
-        <v>-1.15E-2</v>
+        <v>-2.4400000000000002E-2</v>
       </c>
       <c r="E12">
-        <v>18.96</v>
+        <v>9.44</v>
       </c>
       <c r="F12">
-        <v>19.43</v>
+        <v>10.67</v>
       </c>
       <c r="G12">
-        <v>18.8</v>
+        <v>9.86</v>
       </c>
       <c r="H12" s="4">
-        <v>144109.65</v>
+        <v>19219.419999999998</v>
       </c>
       <c r="I12">
-        <v>3.61</v>
+        <v>4.03</v>
       </c>
       <c r="J12">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K12">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="L12">
-        <v>104.57</v>
+        <v>96.67</v>
       </c>
       <c r="M12">
-        <v>0.91</v>
+        <v>-4.91</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1171,37 +1237,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>32200</v>
+        <v>394500</v>
       </c>
       <c r="D13" s="3">
-        <v>4.7000000000000002E-3</v>
+        <v>-6.3E-3</v>
       </c>
       <c r="E13">
-        <v>8.73</v>
+        <v>6.17</v>
       </c>
       <c r="F13">
-        <v>11.57</v>
+        <v>6.83</v>
       </c>
       <c r="G13">
-        <v>6.85</v>
+        <v>6.2</v>
       </c>
       <c r="H13" s="4">
-        <v>24348.21</v>
+        <v>466289.71</v>
       </c>
       <c r="I13">
-        <v>2.95</v>
+        <v>1.27</v>
       </c>
       <c r="J13">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="K13">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L13">
-        <v>101.24</v>
+        <v>91.74</v>
       </c>
       <c r="M13">
-        <v>-3.3</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1212,37 +1278,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>25100</v>
+        <v>9530</v>
       </c>
       <c r="D14" s="3">
-        <v>2.4500000000000001E-2</v>
+        <v>-2.0999999999999999E-3</v>
       </c>
       <c r="E14">
-        <v>19.78</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="F14">
-        <v>13.82</v>
+        <v>3.26</v>
       </c>
       <c r="G14">
-        <v>23.29</v>
+        <v>5.34</v>
       </c>
       <c r="H14" s="4">
-        <v>32624.26</v>
+        <v>22736.17</v>
       </c>
       <c r="I14">
-        <v>3.98</v>
+        <v>3.67</v>
       </c>
       <c r="J14">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="K14">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="L14">
-        <v>88.92</v>
+        <v>93.84</v>
       </c>
       <c r="M14">
-        <v>-5.28</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1253,37 +1319,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>230500</v>
+        <v>76400</v>
       </c>
       <c r="D15" s="3">
-        <v>1.54E-2</v>
+        <v>-1.29E-2</v>
       </c>
       <c r="E15">
-        <v>13.17</v>
+        <v>15.14</v>
       </c>
       <c r="F15">
-        <v>11.69</v>
+        <v>14.47</v>
       </c>
       <c r="G15">
-        <v>18.010000000000002</v>
+        <v>11.28</v>
       </c>
       <c r="H15" s="4">
-        <v>207156.6</v>
+        <v>82759.37</v>
       </c>
       <c r="I15">
-        <v>2.3199999999999998</v>
+        <v>4.32</v>
       </c>
       <c r="J15">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="K15">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="L15">
-        <v>101.07</v>
+        <v>94.26</v>
       </c>
       <c r="M15">
-        <v>-5.53</v>
+        <v>-2.2999999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1294,37 +1360,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>95900</v>
+        <v>553000</v>
       </c>
       <c r="D16" s="3">
-        <v>7.4000000000000003E-3</v>
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="E16">
-        <v>12.89</v>
+        <v>12.43</v>
       </c>
       <c r="F16">
-        <v>13.94</v>
+        <v>10.08</v>
       </c>
       <c r="G16">
-        <v>9.44</v>
+        <v>11.82</v>
       </c>
       <c r="H16" s="4">
-        <v>87743.72</v>
+        <v>429918.88</v>
       </c>
       <c r="I16">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="J16">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K16">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L16">
-        <v>96.04</v>
+        <v>104.88</v>
       </c>
       <c r="M16">
-        <v>-4.58</v>
+        <v>-7.06</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1335,37 +1401,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>76500</v>
+        <v>188400</v>
       </c>
       <c r="D17" s="3">
-        <v>-1.7999999999999999E-2</v>
+        <v>-1.15E-2</v>
       </c>
       <c r="E17">
-        <v>10.83</v>
+        <v>18.96</v>
       </c>
       <c r="F17">
-        <v>3.37</v>
+        <v>19.43</v>
       </c>
       <c r="G17">
-        <v>9.48</v>
+        <v>18.8</v>
       </c>
       <c r="H17" s="4">
-        <v>54894.12</v>
+        <v>144109.65</v>
       </c>
       <c r="I17">
-        <v>4.63</v>
+        <v>3.61</v>
       </c>
       <c r="J17">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="K17">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="L17">
-        <v>98.42</v>
+        <v>104.57</v>
       </c>
       <c r="M17">
-        <v>-2.17</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1376,37 +1442,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>87000</v>
+        <v>32200</v>
       </c>
       <c r="D18" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="E18">
-        <v>14.42</v>
+        <v>8.73</v>
       </c>
       <c r="F18">
-        <v>24.2</v>
+        <v>11.57</v>
       </c>
       <c r="G18">
-        <v>15.82</v>
+        <v>6.85</v>
       </c>
       <c r="H18" s="4">
-        <v>36460.550000000003</v>
+        <v>24348.21</v>
       </c>
       <c r="I18">
-        <v>6.32</v>
+        <v>2.95</v>
       </c>
       <c r="J18">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K18">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L18">
-        <v>86.93</v>
+        <v>101.24</v>
       </c>
       <c r="M18">
-        <v>-8.0299999999999994</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1417,37 +1483,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>23650</v>
+        <v>367000</v>
       </c>
       <c r="D19" s="3">
-        <v>-6.3E-3</v>
+        <v>-1.4800000000000001E-2</v>
       </c>
       <c r="E19">
-        <v>8.06</v>
+        <v>6.85</v>
       </c>
       <c r="F19">
-        <v>8.64</v>
+        <v>6.19</v>
       </c>
       <c r="G19">
-        <v>8.77</v>
+        <v>10.64</v>
       </c>
       <c r="H19" s="4">
-        <v>44443.18</v>
+        <v>605494.72</v>
       </c>
       <c r="I19">
-        <v>4.5</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="J19">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>94.88</v>
+        <v>93.41</v>
       </c>
       <c r="M19">
-        <v>-5.78</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1458,37 +1524,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>59300</v>
+        <v>25100</v>
       </c>
       <c r="D20" s="3">
-        <v>-3.3999999999999998E-3</v>
+        <v>2.4500000000000001E-2</v>
       </c>
       <c r="E20">
-        <v>7.45</v>
+        <v>19.78</v>
       </c>
       <c r="F20">
-        <v>7.45</v>
+        <v>13.82</v>
       </c>
       <c r="G20">
-        <v>7.69</v>
+        <v>23.29</v>
       </c>
       <c r="H20" s="4">
-        <v>79986.48</v>
+        <v>32624.26</v>
       </c>
       <c r="I20">
-        <v>4.72</v>
+        <v>3.98</v>
       </c>
       <c r="J20">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K20">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="L20">
-        <v>96.86</v>
+        <v>88.92</v>
       </c>
       <c r="M20">
-        <v>-4.2</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1499,37 +1565,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>20200</v>
+        <v>230500</v>
       </c>
       <c r="D21" s="3">
-        <v>-9.7999999999999997E-3</v>
+        <v>1.54E-2</v>
       </c>
       <c r="E21">
-        <v>15.12</v>
+        <v>13.17</v>
       </c>
       <c r="F21">
-        <v>13.07</v>
+        <v>11.69</v>
       </c>
       <c r="G21">
-        <v>15.58</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H21" s="4">
-        <v>15310.06</v>
+        <v>207156.6</v>
       </c>
       <c r="I21">
-        <v>6.09</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="J21">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="K21">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="L21">
-        <v>94.12</v>
+        <v>101.07</v>
       </c>
       <c r="M21">
-        <v>-5.39</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1540,37 +1606,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>59000</v>
+        <v>122500</v>
       </c>
       <c r="D22" s="3">
-        <v>2.0799999999999999E-2</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="E22">
-        <v>2.85</v>
+        <v>5.88</v>
       </c>
       <c r="F22">
-        <v>12.83</v>
+        <v>6.29</v>
       </c>
       <c r="G22">
-        <v>5.63</v>
+        <v>10.87</v>
       </c>
       <c r="H22" s="4">
-        <v>71073.47</v>
+        <v>215382.39999999999</v>
       </c>
       <c r="I22">
-        <v>3.39</v>
+        <v>1.8</v>
       </c>
       <c r="J22">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="K22">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="L22">
-        <v>95.59</v>
+        <v>87.14</v>
       </c>
       <c r="M22">
-        <v>-6.35</v>
+        <v>-11.55</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1581,37 +1647,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>15090</v>
+        <v>95900</v>
       </c>
       <c r="D23" s="3">
-        <v>5.3E-3</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="E23">
-        <v>4.4000000000000004</v>
+        <v>12.89</v>
       </c>
       <c r="F23">
-        <v>6.71</v>
+        <v>13.94</v>
       </c>
       <c r="G23">
-        <v>6.75</v>
+        <v>9.44</v>
       </c>
       <c r="H23" s="4">
-        <v>20394.86</v>
+        <v>87743.72</v>
       </c>
       <c r="I23">
-        <v>4.3099999999999996</v>
+        <v>3.65</v>
       </c>
       <c r="J23">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K23">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L23">
-        <v>91.97</v>
+        <v>96.04</v>
       </c>
       <c r="M23">
-        <v>-6.33</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1622,37 +1688,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>210000</v>
+        <v>76500</v>
       </c>
       <c r="D24" s="3">
-        <v>-1.8700000000000001E-2</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="E24">
-        <v>4.66</v>
+        <v>10.83</v>
       </c>
       <c r="F24">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="G24">
-        <v>4.88</v>
+        <v>9.48</v>
       </c>
       <c r="H24" s="4">
-        <v>324173.33</v>
+        <v>54894.12</v>
       </c>
       <c r="I24">
-        <v>2.52</v>
+        <v>4.63</v>
       </c>
       <c r="J24">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K24">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L24">
-        <v>99.93</v>
+        <v>98.42</v>
       </c>
       <c r="M24">
-        <v>-5.19</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1663,37 +1729,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>154700</v>
+        <v>87000</v>
       </c>
       <c r="D25" s="3">
-        <v>-1.21E-2</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="E25">
-        <v>12.66</v>
+        <v>14.42</v>
       </c>
       <c r="F25">
-        <v>11.88</v>
+        <v>24.2</v>
       </c>
       <c r="G25">
-        <v>11.14</v>
+        <v>15.82</v>
       </c>
       <c r="H25" s="4">
-        <v>83639.03</v>
+        <v>36460.550000000003</v>
       </c>
       <c r="I25">
-        <v>3.49</v>
+        <v>6.32</v>
       </c>
       <c r="J25">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K25">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L25">
-        <v>92.57</v>
+        <v>86.93</v>
       </c>
       <c r="M25">
-        <v>-4.68</v>
+        <v>-8.0299999999999994</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1704,37 +1770,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>18080</v>
+        <v>23650</v>
       </c>
       <c r="D26" s="3">
-        <v>1.4E-2</v>
+        <v>-6.3E-3</v>
       </c>
       <c r="E26">
-        <v>12.08</v>
+        <v>8.06</v>
       </c>
       <c r="F26">
-        <v>8.58</v>
+        <v>8.64</v>
       </c>
       <c r="G26">
-        <v>8.39</v>
+        <v>8.77</v>
       </c>
       <c r="H26" s="4">
-        <v>19234.22</v>
+        <v>44443.18</v>
       </c>
       <c r="I26">
-        <v>6.47</v>
+        <v>4.5</v>
       </c>
       <c r="J26">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="K26">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="L26">
-        <v>97.6</v>
+        <v>94.88</v>
       </c>
       <c r="M26">
-        <v>-3.52</v>
+        <v>-5.78</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1745,37 +1811,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>36900</v>
+        <v>59300</v>
       </c>
       <c r="D27" s="3">
-        <v>-5.4000000000000003E-3</v>
+        <v>-3.3999999999999998E-3</v>
       </c>
       <c r="E27">
-        <v>11.21</v>
+        <v>7.45</v>
       </c>
       <c r="F27">
-        <v>6.55</v>
+        <v>7.45</v>
       </c>
       <c r="G27">
-        <v>6.4</v>
+        <v>7.69</v>
       </c>
       <c r="H27" s="4">
-        <v>122131.86</v>
+        <v>79986.48</v>
       </c>
       <c r="I27">
-        <v>3.94</v>
+        <v>4.72</v>
       </c>
       <c r="J27">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="K27">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="L27">
-        <v>88.74</v>
+        <v>96.86</v>
       </c>
       <c r="M27">
-        <v>-9.11</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1786,37 +1852,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>91800</v>
+        <v>20200</v>
       </c>
       <c r="D28" s="3">
-        <v>-1.18E-2</v>
+        <v>-9.7999999999999997E-3</v>
       </c>
       <c r="E28">
-        <v>8.11</v>
+        <v>15.12</v>
       </c>
       <c r="F28">
-        <v>10.44</v>
+        <v>13.07</v>
       </c>
       <c r="G28">
-        <v>8.66</v>
+        <v>15.58</v>
       </c>
       <c r="H28" s="4">
-        <v>119742.76</v>
+        <v>15310.06</v>
       </c>
       <c r="I28">
-        <v>2.35</v>
+        <v>6.09</v>
       </c>
       <c r="J28">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="K28">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="L28">
-        <v>94.88</v>
+        <v>94.12</v>
       </c>
       <c r="M28">
-        <v>-5.07</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1827,37 +1893,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>230000</v>
+        <v>59000</v>
       </c>
       <c r="D29" s="3">
-        <v>-2.2000000000000001E-3</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="E29">
-        <v>11.54</v>
+        <v>2.85</v>
       </c>
       <c r="F29">
-        <v>20.98</v>
+        <v>12.83</v>
       </c>
       <c r="G29">
-        <v>9.6</v>
+        <v>5.63</v>
       </c>
       <c r="H29" s="4">
-        <v>189057.03</v>
+        <v>71073.47</v>
       </c>
       <c r="I29">
-        <v>1.73</v>
+        <v>3.39</v>
       </c>
       <c r="J29">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K29">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L29">
-        <v>94.57</v>
+        <v>95.59</v>
       </c>
       <c r="M29">
-        <v>-4.37</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1868,37 +1934,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>65600</v>
+        <v>15090</v>
       </c>
       <c r="D30" s="3">
-        <v>-1.4999999999999999E-2</v>
+        <v>5.3E-3</v>
       </c>
       <c r="E30">
-        <v>4.12</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F30">
-        <v>5.22</v>
+        <v>6.71</v>
       </c>
       <c r="G30">
-        <v>11.01</v>
+        <v>6.75</v>
       </c>
       <c r="H30" s="4">
-        <v>151788</v>
+        <v>20394.86</v>
       </c>
       <c r="I30">
-        <v>4.12</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="J30">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K30">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L30">
-        <v>93.81</v>
+        <v>91.97</v>
       </c>
       <c r="M30">
-        <v>-6.95</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1909,37 +1975,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>110300</v>
+        <v>210000</v>
       </c>
       <c r="D31" s="3">
-        <v>-8.0999999999999996E-3</v>
+        <v>-1.8700000000000001E-2</v>
       </c>
       <c r="E31">
-        <v>9.11</v>
+        <v>4.66</v>
       </c>
       <c r="F31">
-        <v>10.57</v>
+        <v>4.66</v>
       </c>
       <c r="G31">
-        <v>9.4</v>
+        <v>4.88</v>
       </c>
       <c r="H31" s="4">
-        <v>159337.74</v>
+        <v>324173.33</v>
       </c>
       <c r="I31">
-        <v>3.26</v>
+        <v>2.52</v>
       </c>
       <c r="J31">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K31">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L31">
-        <v>91.6</v>
+        <v>99.93</v>
       </c>
       <c r="M31">
-        <v>-8.16</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1950,37 +2016,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>147400</v>
+        <v>154700</v>
       </c>
       <c r="D32" s="3">
-        <v>-1.0699999999999999E-2</v>
+        <v>-1.21E-2</v>
       </c>
       <c r="E32">
-        <v>8.86</v>
+        <v>12.66</v>
       </c>
       <c r="F32">
-        <v>11.63</v>
+        <v>11.88</v>
       </c>
       <c r="G32">
-        <v>8.51</v>
+        <v>11.14</v>
       </c>
       <c r="H32" s="4">
-        <v>160038.65</v>
+        <v>83639.03</v>
       </c>
       <c r="I32">
-        <v>2.15</v>
+        <v>3.49</v>
       </c>
       <c r="J32">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="K32">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="L32">
-        <v>94.25</v>
+        <v>92.57</v>
       </c>
       <c r="M32">
-        <v>-3.97</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -1991,37 +2057,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>18420</v>
+        <v>18080</v>
       </c>
       <c r="D33" s="3">
-        <v>-2.0199999999999999E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="E33">
-        <v>6.96</v>
+        <v>12.08</v>
       </c>
       <c r="F33">
-        <v>9.58</v>
+        <v>8.58</v>
       </c>
       <c r="G33">
-        <v>7.18</v>
+        <v>8.39</v>
       </c>
       <c r="H33" s="4">
-        <v>34223.949999999997</v>
+        <v>19234.22</v>
       </c>
       <c r="I33">
-        <v>3.53</v>
+        <v>6.47</v>
       </c>
       <c r="J33">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="K33">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="L33">
-        <v>92.02</v>
+        <v>97.6</v>
       </c>
       <c r="M33">
-        <v>-6.4</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2032,37 +2098,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>17050</v>
+        <v>36900</v>
       </c>
       <c r="D34" s="3">
-        <v>-1.1599999999999999E-2</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="E34">
-        <v>3.6</v>
+        <v>11.21</v>
       </c>
       <c r="F34">
-        <v>9.42</v>
+        <v>6.55</v>
       </c>
       <c r="G34">
-        <v>5.91</v>
+        <v>6.4</v>
       </c>
       <c r="H34" s="4">
-        <v>38541.279999999999</v>
+        <v>122131.86</v>
       </c>
       <c r="I34">
-        <v>2.93</v>
+        <v>3.94</v>
       </c>
       <c r="J34">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="K34">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="L34">
-        <v>91.11</v>
+        <v>88.74</v>
       </c>
       <c r="M34">
-        <v>-5.8</v>
+        <v>-9.11</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2073,37 +2139,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>59300</v>
+        <v>14770</v>
       </c>
       <c r="D35" s="3">
-        <v>-3.8899999999999997E-2</v>
+        <v>3.0700000000000002E-2</v>
       </c>
       <c r="E35">
-        <v>10.79</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="F35">
-        <v>10.55</v>
+        <v>3.02</v>
       </c>
       <c r="G35">
-        <v>8.93</v>
+        <v>6.13</v>
       </c>
       <c r="H35" s="4">
-        <v>92723.77</v>
+        <v>7055.63</v>
       </c>
       <c r="I35">
-        <v>3.37</v>
+        <v>0.74</v>
       </c>
       <c r="J35">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K35">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L35">
-        <v>85.21</v>
+        <v>93.64</v>
       </c>
       <c r="M35">
-        <v>-11.23</v>
+        <v>-13.12</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2114,37 +2180,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>29400</v>
+        <v>91800</v>
       </c>
       <c r="D36" s="3">
-        <v>5.1000000000000004E-3</v>
+        <v>-1.18E-2</v>
       </c>
       <c r="E36">
-        <v>12.8</v>
+        <v>8.11</v>
       </c>
       <c r="F36">
-        <v>13.49</v>
+        <v>10.44</v>
       </c>
       <c r="G36">
-        <v>12.93</v>
+        <v>8.66</v>
       </c>
       <c r="H36" s="4">
-        <v>31004.78</v>
+        <v>119742.76</v>
       </c>
       <c r="I36">
-        <v>3.38</v>
+        <v>2.35</v>
       </c>
       <c r="J36">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="K36">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="L36">
-        <v>93.05</v>
+        <v>94.88</v>
       </c>
       <c r="M36">
-        <v>-5.62</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2155,37 +2221,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>50000</v>
+        <v>230000</v>
       </c>
       <c r="D37" s="3">
-        <v>1.52E-2</v>
+        <v>-2.2000000000000001E-3</v>
       </c>
       <c r="E37">
-        <v>18.690000000000001</v>
+        <v>11.54</v>
       </c>
       <c r="F37">
-        <v>11.56</v>
+        <v>20.98</v>
       </c>
       <c r="G37">
-        <v>6.83</v>
+        <v>9.6</v>
       </c>
       <c r="H37" s="4">
-        <v>57293.3</v>
+        <v>189057.03</v>
       </c>
       <c r="I37">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="J37">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="K37">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="L37">
-        <v>92.98</v>
+        <v>94.57</v>
       </c>
       <c r="M37">
-        <v>-3.66</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2196,36 +2262,487 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
+        <v>65600</v>
+      </c>
+      <c r="D38" s="3">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="E38">
+        <v>4.12</v>
+      </c>
+      <c r="F38">
+        <v>5.22</v>
+      </c>
+      <c r="G38">
+        <v>11.01</v>
+      </c>
+      <c r="H38" s="4">
+        <v>151788</v>
+      </c>
+      <c r="I38">
+        <v>4.12</v>
+      </c>
+      <c r="J38">
+        <v>67</v>
+      </c>
+      <c r="K38">
+        <v>67</v>
+      </c>
+      <c r="L38">
+        <v>93.81</v>
+      </c>
+      <c r="M38">
+        <v>-6.95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="2">
+        <v>110300</v>
+      </c>
+      <c r="D39" s="3">
+        <v>-8.0999999999999996E-3</v>
+      </c>
+      <c r="E39">
+        <v>9.11</v>
+      </c>
+      <c r="F39">
+        <v>10.57</v>
+      </c>
+      <c r="G39">
+        <v>9.4</v>
+      </c>
+      <c r="H39" s="4">
+        <v>159337.74</v>
+      </c>
+      <c r="I39">
+        <v>3.26</v>
+      </c>
+      <c r="J39">
+        <v>77</v>
+      </c>
+      <c r="K39">
+        <v>77</v>
+      </c>
+      <c r="L39">
+        <v>91.6</v>
+      </c>
+      <c r="M39">
+        <v>-8.16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="2">
+        <v>147400</v>
+      </c>
+      <c r="D40" s="3">
+        <v>-1.0699999999999999E-2</v>
+      </c>
+      <c r="E40">
+        <v>8.86</v>
+      </c>
+      <c r="F40">
+        <v>11.63</v>
+      </c>
+      <c r="G40">
+        <v>8.51</v>
+      </c>
+      <c r="H40" s="4">
+        <v>160038.65</v>
+      </c>
+      <c r="I40">
+        <v>2.15</v>
+      </c>
+      <c r="J40">
+        <v>81</v>
+      </c>
+      <c r="K40">
+        <v>81</v>
+      </c>
+      <c r="L40">
+        <v>94.25</v>
+      </c>
+      <c r="M40">
+        <v>-3.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="2">
+        <v>18420</v>
+      </c>
+      <c r="D41" s="3">
+        <v>-2.0199999999999999E-2</v>
+      </c>
+      <c r="E41">
+        <v>6.96</v>
+      </c>
+      <c r="F41">
+        <v>9.58</v>
+      </c>
+      <c r="G41">
+        <v>7.18</v>
+      </c>
+      <c r="H41" s="4">
+        <v>34223.949999999997</v>
+      </c>
+      <c r="I41">
+        <v>3.53</v>
+      </c>
+      <c r="J41">
+        <v>73</v>
+      </c>
+      <c r="K41">
+        <v>73</v>
+      </c>
+      <c r="L41">
+        <v>92.02</v>
+      </c>
+      <c r="M41">
+        <v>-6.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="2">
+        <v>17050</v>
+      </c>
+      <c r="D42" s="3">
+        <v>-1.1599999999999999E-2</v>
+      </c>
+      <c r="E42">
+        <v>3.6</v>
+      </c>
+      <c r="F42">
+        <v>9.42</v>
+      </c>
+      <c r="G42">
+        <v>5.91</v>
+      </c>
+      <c r="H42" s="4">
+        <v>38541.279999999999</v>
+      </c>
+      <c r="I42">
+        <v>2.93</v>
+      </c>
+      <c r="J42">
+        <v>68</v>
+      </c>
+      <c r="K42">
+        <v>68</v>
+      </c>
+      <c r="L42">
+        <v>91.11</v>
+      </c>
+      <c r="M42">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="2">
+        <v>59300</v>
+      </c>
+      <c r="D43" s="3">
+        <v>-3.8899999999999997E-2</v>
+      </c>
+      <c r="E43">
+        <v>10.79</v>
+      </c>
+      <c r="F43">
+        <v>10.55</v>
+      </c>
+      <c r="G43">
+        <v>8.93</v>
+      </c>
+      <c r="H43" s="4">
+        <v>92723.77</v>
+      </c>
+      <c r="I43">
+        <v>3.37</v>
+      </c>
+      <c r="J43">
+        <v>60</v>
+      </c>
+      <c r="K43">
+        <v>60</v>
+      </c>
+      <c r="L43">
+        <v>85.21</v>
+      </c>
+      <c r="M43">
+        <v>-11.23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="2">
+        <v>29400</v>
+      </c>
+      <c r="D44" s="3">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="E44">
+        <v>12.8</v>
+      </c>
+      <c r="F44">
+        <v>13.49</v>
+      </c>
+      <c r="G44">
+        <v>12.93</v>
+      </c>
+      <c r="H44" s="4">
+        <v>31004.78</v>
+      </c>
+      <c r="I44">
+        <v>3.38</v>
+      </c>
+      <c r="J44">
+        <v>72</v>
+      </c>
+      <c r="K44">
+        <v>72</v>
+      </c>
+      <c r="L44">
+        <v>93.05</v>
+      </c>
+      <c r="M44">
+        <v>-5.62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="2">
+        <v>11810</v>
+      </c>
+      <c r="D45" s="3">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="E45">
+        <v>7.65</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45">
+        <v>7.8</v>
+      </c>
+      <c r="H45" s="4">
+        <v>30039.25</v>
+      </c>
+      <c r="I45">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J45">
+        <v>36</v>
+      </c>
+      <c r="K45">
+        <v>36</v>
+      </c>
+      <c r="L45">
+        <v>91.01</v>
+      </c>
+      <c r="M45">
+        <v>-4.22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="2">
+        <v>50000</v>
+      </c>
+      <c r="D46" s="3">
+        <v>1.52E-2</v>
+      </c>
+      <c r="E46">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="F46">
+        <v>11.56</v>
+      </c>
+      <c r="G46">
+        <v>6.83</v>
+      </c>
+      <c r="H46" s="4">
+        <v>57293.3</v>
+      </c>
+      <c r="I46">
+        <v>2.4</v>
+      </c>
+      <c r="J46">
+        <v>45</v>
+      </c>
+      <c r="K46">
+        <v>45</v>
+      </c>
+      <c r="L46">
+        <v>92.98</v>
+      </c>
+      <c r="M46">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="2">
+        <v>19300</v>
+      </c>
+      <c r="D47" s="3">
+        <v>-3.5999999999999999E-3</v>
+      </c>
+      <c r="E47">
+        <v>10.48</v>
+      </c>
+      <c r="F47">
+        <v>7.97</v>
+      </c>
+      <c r="G47">
+        <v>10.17</v>
+      </c>
+      <c r="H47" s="4">
+        <v>25607.22</v>
+      </c>
+      <c r="I47">
+        <v>6.09</v>
+      </c>
+      <c r="J47">
+        <v>17</v>
+      </c>
+      <c r="K47">
+        <v>17</v>
+      </c>
+      <c r="L47">
+        <v>97.44</v>
+      </c>
+      <c r="M47">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B48" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="2">
+        <v>16640</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1.09E-2</v>
+      </c>
+      <c r="E48">
+        <v>11.13</v>
+      </c>
+      <c r="F48">
+        <v>5.01</v>
+      </c>
+      <c r="G48">
+        <v>9.31</v>
+      </c>
+      <c r="H48" s="4">
+        <v>24921.41</v>
+      </c>
+      <c r="I48">
+        <v>6.01</v>
+      </c>
+      <c r="J48">
+        <v>39</v>
+      </c>
+      <c r="K48">
+        <v>39</v>
+      </c>
+      <c r="L48">
+        <v>93.49</v>
+      </c>
+      <c r="M48">
+        <v>-4.97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="2">
         <v>33050</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D49" s="3">
         <v>-2.07E-2</v>
       </c>
-      <c r="E38">
+      <c r="E49">
         <v>9.39</v>
       </c>
-      <c r="F38">
+      <c r="F49">
         <v>10.74</v>
       </c>
-      <c r="G38">
+      <c r="G49">
         <v>9.73</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H49" s="4">
         <v>48211.77</v>
       </c>
-      <c r="I38">
+      <c r="I49">
         <v>3.63</v>
       </c>
-      <c r="J38">
+      <c r="J49">
         <v>73</v>
       </c>
-      <c r="K38">
+      <c r="K49">
         <v>73</v>
       </c>
-      <c r="L38">
+      <c r="L49">
         <v>91.79</v>
       </c>
-      <c r="M38">
+      <c r="M49">
         <v>-6.37</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B1D2F8D-190A-4287-9E51-34C9AFA571E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DECEC3B5-B0F3-4E03-83AE-DCD047D0A36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{2B39F4A7-1B7A-4A0E-957A-C7A9CC6A2640}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C5659A2F-D2DE-42A2-9282-AD29FA24D0C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -720,7 +720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364AA57A-DA09-4B5E-A948-31004EAD14B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED37218-3DB0-4137-BD56-C7A6FE88A6F0}">
   <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DECEC3B5-B0F3-4E03-83AE-DCD047D0A36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26F0AFE9-0261-48E4-99BA-93D62D96146F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C5659A2F-D2DE-42A2-9282-AD29FA24D0C5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E82C1798-5FEC-4409-A1D4-CF43A6D3A27C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
   <si>
     <t>종목코드</t>
   </si>
@@ -154,6 +154,12 @@
   </si>
   <si>
     <t>DB손해보험</t>
+  </si>
+  <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>삼성전자</t>
   </si>
   <si>
     <t>005940</t>
@@ -720,8 +726,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED37218-3DB0-4137-BD56-C7A6FE88A6F0}">
-  <dimension ref="A1:M49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22EB960-1165-4894-B7EE-9E86913D46FA}">
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
@@ -1442,37 +1448,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>32200</v>
+        <v>188200</v>
       </c>
       <c r="D18" s="3">
-        <v>4.7000000000000002E-3</v>
+        <v>-1.77E-2</v>
       </c>
       <c r="E18">
-        <v>8.73</v>
+        <v>10.85</v>
       </c>
       <c r="F18">
-        <v>11.57</v>
+        <v>10.85</v>
       </c>
       <c r="G18">
-        <v>6.85</v>
+        <v>8.01</v>
       </c>
       <c r="H18" s="4">
-        <v>24348.21</v>
+        <v>63976.31</v>
       </c>
       <c r="I18">
-        <v>2.95</v>
+        <v>0.89</v>
       </c>
       <c r="J18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L18">
-        <v>101.24</v>
+        <v>102.49</v>
       </c>
       <c r="M18">
-        <v>-3.3</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1483,37 +1489,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>367000</v>
+        <v>32200</v>
       </c>
       <c r="D19" s="3">
-        <v>-1.4800000000000001E-2</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="E19">
+        <v>8.73</v>
+      </c>
+      <c r="F19">
+        <v>11.57</v>
+      </c>
+      <c r="G19">
         <v>6.85</v>
       </c>
-      <c r="F19">
-        <v>6.19</v>
-      </c>
-      <c r="G19">
-        <v>10.64</v>
-      </c>
       <c r="H19" s="4">
-        <v>605494.72</v>
+        <v>24348.21</v>
       </c>
       <c r="I19">
-        <v>2.4500000000000002</v>
+        <v>2.95</v>
       </c>
       <c r="J19">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="K19">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="L19">
-        <v>93.41</v>
+        <v>101.24</v>
       </c>
       <c r="M19">
-        <v>-5.53</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1524,37 +1530,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>25100</v>
+        <v>367000</v>
       </c>
       <c r="D20" s="3">
-        <v>2.4500000000000001E-2</v>
+        <v>-1.4800000000000001E-2</v>
       </c>
       <c r="E20">
-        <v>19.78</v>
+        <v>6.85</v>
       </c>
       <c r="F20">
-        <v>13.82</v>
+        <v>6.19</v>
       </c>
       <c r="G20">
-        <v>23.29</v>
+        <v>10.64</v>
       </c>
       <c r="H20" s="4">
-        <v>32624.26</v>
+        <v>605494.72</v>
       </c>
       <c r="I20">
-        <v>3.98</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="J20">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>88.92</v>
+        <v>93.41</v>
       </c>
       <c r="M20">
-        <v>-5.28</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1565,37 +1571,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>230500</v>
+        <v>25100</v>
       </c>
       <c r="D21" s="3">
-        <v>1.54E-2</v>
+        <v>2.4500000000000001E-2</v>
       </c>
       <c r="E21">
-        <v>13.17</v>
+        <v>19.78</v>
       </c>
       <c r="F21">
-        <v>11.69</v>
+        <v>13.82</v>
       </c>
       <c r="G21">
-        <v>18.010000000000002</v>
+        <v>23.29</v>
       </c>
       <c r="H21" s="4">
-        <v>207156.6</v>
+        <v>32624.26</v>
       </c>
       <c r="I21">
-        <v>2.3199999999999998</v>
+        <v>3.98</v>
       </c>
       <c r="J21">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="K21">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="L21">
-        <v>101.07</v>
+        <v>88.92</v>
       </c>
       <c r="M21">
-        <v>-5.53</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1606,37 +1612,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>122500</v>
+        <v>230500</v>
       </c>
       <c r="D22" s="3">
-        <v>4.1000000000000003E-3</v>
+        <v>1.54E-2</v>
       </c>
       <c r="E22">
-        <v>5.88</v>
+        <v>13.17</v>
       </c>
       <c r="F22">
-        <v>6.29</v>
+        <v>11.69</v>
       </c>
       <c r="G22">
-        <v>10.87</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H22" s="4">
-        <v>215382.39999999999</v>
+        <v>207156.6</v>
       </c>
       <c r="I22">
-        <v>1.8</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="J22">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="K22">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="L22">
-        <v>87.14</v>
+        <v>101.07</v>
       </c>
       <c r="M22">
-        <v>-11.55</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1647,37 +1653,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>95900</v>
+        <v>122500</v>
       </c>
       <c r="D23" s="3">
-        <v>7.4000000000000003E-3</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="E23">
-        <v>12.89</v>
+        <v>5.88</v>
       </c>
       <c r="F23">
-        <v>13.94</v>
+        <v>6.29</v>
       </c>
       <c r="G23">
-        <v>9.44</v>
+        <v>10.87</v>
       </c>
       <c r="H23" s="4">
-        <v>87743.72</v>
+        <v>215382.39999999999</v>
       </c>
       <c r="I23">
-        <v>3.65</v>
+        <v>1.8</v>
       </c>
       <c r="J23">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="K23">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="L23">
-        <v>96.04</v>
+        <v>87.14</v>
       </c>
       <c r="M23">
-        <v>-4.58</v>
+        <v>-11.55</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1688,37 +1694,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>76500</v>
+        <v>95900</v>
       </c>
       <c r="D24" s="3">
-        <v>-1.7999999999999999E-2</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="E24">
-        <v>10.83</v>
+        <v>12.89</v>
       </c>
       <c r="F24">
-        <v>3.37</v>
+        <v>13.94</v>
       </c>
       <c r="G24">
-        <v>9.48</v>
+        <v>9.44</v>
       </c>
       <c r="H24" s="4">
-        <v>54894.12</v>
+        <v>87743.72</v>
       </c>
       <c r="I24">
-        <v>4.63</v>
+        <v>3.65</v>
       </c>
       <c r="J24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L24">
-        <v>98.42</v>
+        <v>96.04</v>
       </c>
       <c r="M24">
-        <v>-2.17</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1729,37 +1735,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>87000</v>
+        <v>76500</v>
       </c>
       <c r="D25" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="E25">
-        <v>14.42</v>
+        <v>10.83</v>
       </c>
       <c r="F25">
-        <v>24.2</v>
+        <v>3.37</v>
       </c>
       <c r="G25">
-        <v>15.82</v>
+        <v>9.48</v>
       </c>
       <c r="H25" s="4">
-        <v>36460.550000000003</v>
+        <v>54894.12</v>
       </c>
       <c r="I25">
-        <v>6.32</v>
+        <v>4.63</v>
       </c>
       <c r="J25">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K25">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L25">
-        <v>86.93</v>
+        <v>98.42</v>
       </c>
       <c r="M25">
-        <v>-8.0299999999999994</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1770,37 +1776,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>23650</v>
+        <v>87000</v>
       </c>
       <c r="D26" s="3">
-        <v>-6.3E-3</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="E26">
-        <v>8.06</v>
+        <v>14.42</v>
       </c>
       <c r="F26">
-        <v>8.64</v>
+        <v>24.2</v>
       </c>
       <c r="G26">
-        <v>8.77</v>
+        <v>15.82</v>
       </c>
       <c r="H26" s="4">
-        <v>44443.18</v>
+        <v>36460.550000000003</v>
       </c>
       <c r="I26">
-        <v>4.5</v>
+        <v>6.32</v>
       </c>
       <c r="J26">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K26">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L26">
-        <v>94.88</v>
+        <v>86.93</v>
       </c>
       <c r="M26">
-        <v>-5.78</v>
+        <v>-8.0299999999999994</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1811,37 +1817,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>59300</v>
+        <v>23650</v>
       </c>
       <c r="D27" s="3">
-        <v>-3.3999999999999998E-3</v>
+        <v>-6.3E-3</v>
       </c>
       <c r="E27">
-        <v>7.45</v>
+        <v>8.06</v>
       </c>
       <c r="F27">
-        <v>7.45</v>
+        <v>8.64</v>
       </c>
       <c r="G27">
-        <v>7.69</v>
+        <v>8.77</v>
       </c>
       <c r="H27" s="4">
-        <v>79986.48</v>
+        <v>44443.18</v>
       </c>
       <c r="I27">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="J27">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K27">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L27">
-        <v>96.86</v>
+        <v>94.88</v>
       </c>
       <c r="M27">
-        <v>-4.2</v>
+        <v>-5.78</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1852,37 +1858,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>20200</v>
+        <v>59300</v>
       </c>
       <c r="D28" s="3">
-        <v>-9.7999999999999997E-3</v>
+        <v>-3.3999999999999998E-3</v>
       </c>
       <c r="E28">
-        <v>15.12</v>
+        <v>7.45</v>
       </c>
       <c r="F28">
-        <v>13.07</v>
+        <v>7.45</v>
       </c>
       <c r="G28">
-        <v>15.58</v>
+        <v>7.69</v>
       </c>
       <c r="H28" s="4">
-        <v>15310.06</v>
+        <v>79986.48</v>
       </c>
       <c r="I28">
-        <v>6.09</v>
+        <v>4.72</v>
       </c>
       <c r="J28">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="K28">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="L28">
-        <v>94.12</v>
+        <v>96.86</v>
       </c>
       <c r="M28">
-        <v>-5.39</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1893,37 +1899,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>59000</v>
+        <v>20200</v>
       </c>
       <c r="D29" s="3">
-        <v>2.0799999999999999E-2</v>
+        <v>-9.7999999999999997E-3</v>
       </c>
       <c r="E29">
-        <v>2.85</v>
+        <v>15.12</v>
       </c>
       <c r="F29">
-        <v>12.83</v>
+        <v>13.07</v>
       </c>
       <c r="G29">
-        <v>5.63</v>
+        <v>15.58</v>
       </c>
       <c r="H29" s="4">
-        <v>71073.47</v>
+        <v>15310.06</v>
       </c>
       <c r="I29">
-        <v>3.39</v>
+        <v>6.09</v>
       </c>
       <c r="J29">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="K29">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="L29">
-        <v>95.59</v>
+        <v>94.12</v>
       </c>
       <c r="M29">
-        <v>-6.35</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1934,37 +1940,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>15090</v>
+        <v>59000</v>
       </c>
       <c r="D30" s="3">
-        <v>5.3E-3</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="E30">
-        <v>4.4000000000000004</v>
+        <v>2.85</v>
       </c>
       <c r="F30">
-        <v>6.71</v>
+        <v>12.83</v>
       </c>
       <c r="G30">
-        <v>6.75</v>
+        <v>5.63</v>
       </c>
       <c r="H30" s="4">
-        <v>20394.86</v>
+        <v>71073.47</v>
       </c>
       <c r="I30">
-        <v>4.3099999999999996</v>
+        <v>3.39</v>
       </c>
       <c r="J30">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K30">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L30">
-        <v>91.97</v>
+        <v>95.59</v>
       </c>
       <c r="M30">
-        <v>-6.33</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1975,37 +1981,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>210000</v>
+        <v>15090</v>
       </c>
       <c r="D31" s="3">
-        <v>-1.8700000000000001E-2</v>
+        <v>5.3E-3</v>
       </c>
       <c r="E31">
-        <v>4.66</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F31">
-        <v>4.66</v>
+        <v>6.71</v>
       </c>
       <c r="G31">
-        <v>4.88</v>
+        <v>6.75</v>
       </c>
       <c r="H31" s="4">
-        <v>324173.33</v>
+        <v>20394.86</v>
       </c>
       <c r="I31">
-        <v>2.52</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="J31">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="K31">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="L31">
-        <v>99.93</v>
+        <v>91.97</v>
       </c>
       <c r="M31">
-        <v>-5.19</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -2016,37 +2022,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>154700</v>
+        <v>210000</v>
       </c>
       <c r="D32" s="3">
-        <v>-1.21E-2</v>
+        <v>-1.8700000000000001E-2</v>
       </c>
       <c r="E32">
-        <v>12.66</v>
+        <v>4.66</v>
       </c>
       <c r="F32">
-        <v>11.88</v>
+        <v>4.66</v>
       </c>
       <c r="G32">
-        <v>11.14</v>
+        <v>4.88</v>
       </c>
       <c r="H32" s="4">
-        <v>83639.03</v>
+        <v>324173.33</v>
       </c>
       <c r="I32">
-        <v>3.49</v>
+        <v>2.52</v>
       </c>
       <c r="J32">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K32">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L32">
-        <v>92.57</v>
+        <v>99.93</v>
       </c>
       <c r="M32">
-        <v>-4.68</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2057,37 +2063,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>18080</v>
+        <v>154700</v>
       </c>
       <c r="D33" s="3">
-        <v>1.4E-2</v>
+        <v>-1.21E-2</v>
       </c>
       <c r="E33">
-        <v>12.08</v>
+        <v>12.66</v>
       </c>
       <c r="F33">
-        <v>8.58</v>
+        <v>11.88</v>
       </c>
       <c r="G33">
-        <v>8.39</v>
+        <v>11.14</v>
       </c>
       <c r="H33" s="4">
-        <v>19234.22</v>
+        <v>83639.03</v>
       </c>
       <c r="I33">
-        <v>6.47</v>
+        <v>3.49</v>
       </c>
       <c r="J33">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="K33">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="L33">
-        <v>97.6</v>
+        <v>92.57</v>
       </c>
       <c r="M33">
-        <v>-3.52</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2098,37 +2104,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>36900</v>
+        <v>18080</v>
       </c>
       <c r="D34" s="3">
-        <v>-5.4000000000000003E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="E34">
-        <v>11.21</v>
+        <v>12.08</v>
       </c>
       <c r="F34">
-        <v>6.55</v>
+        <v>8.58</v>
       </c>
       <c r="G34">
-        <v>6.4</v>
+        <v>8.39</v>
       </c>
       <c r="H34" s="4">
-        <v>122131.86</v>
+        <v>19234.22</v>
       </c>
       <c r="I34">
-        <v>3.94</v>
+        <v>6.47</v>
       </c>
       <c r="J34">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K34">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L34">
-        <v>88.74</v>
+        <v>97.6</v>
       </c>
       <c r="M34">
-        <v>-9.11</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2139,37 +2145,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>14770</v>
+        <v>36900</v>
       </c>
       <c r="D35" s="3">
-        <v>3.0700000000000002E-2</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="E35">
-        <v>9.0399999999999991</v>
+        <v>11.21</v>
       </c>
       <c r="F35">
-        <v>3.02</v>
+        <v>6.55</v>
       </c>
       <c r="G35">
-        <v>6.13</v>
+        <v>6.4</v>
       </c>
       <c r="H35" s="4">
-        <v>7055.63</v>
+        <v>122131.86</v>
       </c>
       <c r="I35">
-        <v>0.74</v>
+        <v>3.94</v>
       </c>
       <c r="J35">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="K35">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L35">
-        <v>93.64</v>
+        <v>88.74</v>
       </c>
       <c r="M35">
-        <v>-13.12</v>
+        <v>-9.11</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2180,37 +2186,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>91800</v>
+        <v>14770</v>
       </c>
       <c r="D36" s="3">
-        <v>-1.18E-2</v>
+        <v>3.0700000000000002E-2</v>
       </c>
       <c r="E36">
-        <v>8.11</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="F36">
-        <v>10.44</v>
+        <v>3.02</v>
       </c>
       <c r="G36">
-        <v>8.66</v>
+        <v>6.13</v>
       </c>
       <c r="H36" s="4">
-        <v>119742.76</v>
+        <v>7055.63</v>
       </c>
       <c r="I36">
-        <v>2.35</v>
+        <v>0.74</v>
       </c>
       <c r="J36">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="K36">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="L36">
-        <v>94.88</v>
+        <v>93.64</v>
       </c>
       <c r="M36">
-        <v>-5.07</v>
+        <v>-13.12</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2221,37 +2227,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>230000</v>
+        <v>91800</v>
       </c>
       <c r="D37" s="3">
-        <v>-2.2000000000000001E-3</v>
+        <v>-1.18E-2</v>
       </c>
       <c r="E37">
-        <v>11.54</v>
+        <v>8.11</v>
       </c>
       <c r="F37">
-        <v>20.98</v>
+        <v>10.44</v>
       </c>
       <c r="G37">
-        <v>9.6</v>
+        <v>8.66</v>
       </c>
       <c r="H37" s="4">
-        <v>189057.03</v>
+        <v>119742.76</v>
       </c>
       <c r="I37">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="J37">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="K37">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="L37">
-        <v>94.57</v>
+        <v>94.88</v>
       </c>
       <c r="M37">
-        <v>-4.37</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2262,37 +2268,37 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>65600</v>
+        <v>230000</v>
       </c>
       <c r="D38" s="3">
-        <v>-1.4999999999999999E-2</v>
+        <v>-2.2000000000000001E-3</v>
       </c>
       <c r="E38">
-        <v>4.12</v>
+        <v>11.54</v>
       </c>
       <c r="F38">
-        <v>5.22</v>
+        <v>20.98</v>
       </c>
       <c r="G38">
-        <v>11.01</v>
+        <v>9.6</v>
       </c>
       <c r="H38" s="4">
-        <v>151788</v>
+        <v>189057.03</v>
       </c>
       <c r="I38">
-        <v>4.12</v>
+        <v>1.73</v>
       </c>
       <c r="J38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L38">
-        <v>93.81</v>
+        <v>94.57</v>
       </c>
       <c r="M38">
-        <v>-6.95</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2303,37 +2309,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>110300</v>
+        <v>65600</v>
       </c>
       <c r="D39" s="3">
-        <v>-8.0999999999999996E-3</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="E39">
-        <v>9.11</v>
+        <v>4.12</v>
       </c>
       <c r="F39">
-        <v>10.57</v>
+        <v>5.22</v>
       </c>
       <c r="G39">
-        <v>9.4</v>
+        <v>11.01</v>
       </c>
       <c r="H39" s="4">
-        <v>159337.74</v>
+        <v>151788</v>
       </c>
       <c r="I39">
-        <v>3.26</v>
+        <v>4.12</v>
       </c>
       <c r="J39">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="K39">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="L39">
-        <v>91.6</v>
+        <v>93.81</v>
       </c>
       <c r="M39">
-        <v>-8.16</v>
+        <v>-6.95</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2344,37 +2350,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>147400</v>
+        <v>110300</v>
       </c>
       <c r="D40" s="3">
-        <v>-1.0699999999999999E-2</v>
+        <v>-8.0999999999999996E-3</v>
       </c>
       <c r="E40">
-        <v>8.86</v>
+        <v>9.11</v>
       </c>
       <c r="F40">
-        <v>11.63</v>
+        <v>10.57</v>
       </c>
       <c r="G40">
-        <v>8.51</v>
+        <v>9.4</v>
       </c>
       <c r="H40" s="4">
-        <v>160038.65</v>
+        <v>159337.74</v>
       </c>
       <c r="I40">
-        <v>2.15</v>
+        <v>3.26</v>
       </c>
       <c r="J40">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K40">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L40">
-        <v>94.25</v>
+        <v>91.6</v>
       </c>
       <c r="M40">
-        <v>-3.97</v>
+        <v>-8.16</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2385,37 +2391,37 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>18420</v>
+        <v>147400</v>
       </c>
       <c r="D41" s="3">
-        <v>-2.0199999999999999E-2</v>
+        <v>-1.0699999999999999E-2</v>
       </c>
       <c r="E41">
-        <v>6.96</v>
+        <v>8.86</v>
       </c>
       <c r="F41">
-        <v>9.58</v>
+        <v>11.63</v>
       </c>
       <c r="G41">
-        <v>7.18</v>
+        <v>8.51</v>
       </c>
       <c r="H41" s="4">
-        <v>34223.949999999997</v>
+        <v>160038.65</v>
       </c>
       <c r="I41">
-        <v>3.53</v>
+        <v>2.15</v>
       </c>
       <c r="J41">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="K41">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L41">
-        <v>92.02</v>
+        <v>94.25</v>
       </c>
       <c r="M41">
-        <v>-6.4</v>
+        <v>-3.97</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2426,37 +2432,37 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>17050</v>
+        <v>18420</v>
       </c>
       <c r="D42" s="3">
-        <v>-1.1599999999999999E-2</v>
+        <v>-2.0199999999999999E-2</v>
       </c>
       <c r="E42">
-        <v>3.6</v>
+        <v>6.96</v>
       </c>
       <c r="F42">
-        <v>9.42</v>
+        <v>9.58</v>
       </c>
       <c r="G42">
-        <v>5.91</v>
+        <v>7.18</v>
       </c>
       <c r="H42" s="4">
-        <v>38541.279999999999</v>
+        <v>34223.949999999997</v>
       </c>
       <c r="I42">
-        <v>2.93</v>
+        <v>3.53</v>
       </c>
       <c r="J42">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K42">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L42">
-        <v>91.11</v>
+        <v>92.02</v>
       </c>
       <c r="M42">
-        <v>-5.8</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2467,37 +2473,37 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>59300</v>
+        <v>17050</v>
       </c>
       <c r="D43" s="3">
-        <v>-3.8899999999999997E-2</v>
+        <v>-1.1599999999999999E-2</v>
       </c>
       <c r="E43">
-        <v>10.79</v>
+        <v>3.6</v>
       </c>
       <c r="F43">
-        <v>10.55</v>
+        <v>9.42</v>
       </c>
       <c r="G43">
-        <v>8.93</v>
+        <v>5.91</v>
       </c>
       <c r="H43" s="4">
-        <v>92723.77</v>
+        <v>38541.279999999999</v>
       </c>
       <c r="I43">
-        <v>3.37</v>
+        <v>2.93</v>
       </c>
       <c r="J43">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="K43">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="L43">
-        <v>85.21</v>
+        <v>91.11</v>
       </c>
       <c r="M43">
-        <v>-11.23</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
@@ -2508,37 +2514,37 @@
         <v>96</v>
       </c>
       <c r="C44" s="2">
-        <v>29400</v>
+        <v>59300</v>
       </c>
       <c r="D44" s="3">
-        <v>5.1000000000000004E-3</v>
+        <v>-3.8899999999999997E-2</v>
       </c>
       <c r="E44">
-        <v>12.8</v>
+        <v>10.79</v>
       </c>
       <c r="F44">
-        <v>13.49</v>
+        <v>10.55</v>
       </c>
       <c r="G44">
-        <v>12.93</v>
+        <v>8.93</v>
       </c>
       <c r="H44" s="4">
-        <v>31004.78</v>
+        <v>92723.77</v>
       </c>
       <c r="I44">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="J44">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="K44">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="L44">
-        <v>93.05</v>
+        <v>85.21</v>
       </c>
       <c r="M44">
-        <v>-5.62</v>
+        <v>-11.23</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
@@ -2549,37 +2555,37 @@
         <v>98</v>
       </c>
       <c r="C45" s="2">
-        <v>11810</v>
+        <v>29400</v>
       </c>
       <c r="D45" s="3">
-        <v>1.6999999999999999E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="E45">
-        <v>7.65</v>
+        <v>12.8</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>13.49</v>
       </c>
       <c r="G45">
-        <v>7.8</v>
+        <v>12.93</v>
       </c>
       <c r="H45" s="4">
-        <v>30039.25</v>
+        <v>31004.78</v>
       </c>
       <c r="I45">
-        <v>2.2000000000000002</v>
+        <v>3.38</v>
       </c>
       <c r="J45">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="K45">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="L45">
-        <v>91.01</v>
+        <v>93.05</v>
       </c>
       <c r="M45">
-        <v>-4.22</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
@@ -2590,37 +2596,37 @@
         <v>100</v>
       </c>
       <c r="C46" s="2">
-        <v>50000</v>
+        <v>11810</v>
       </c>
       <c r="D46" s="3">
-        <v>1.52E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="E46">
-        <v>18.690000000000001</v>
+        <v>7.65</v>
       </c>
       <c r="F46">
-        <v>11.56</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>6.83</v>
+        <v>7.8</v>
       </c>
       <c r="H46" s="4">
-        <v>57293.3</v>
+        <v>30039.25</v>
       </c>
       <c r="I46">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J46">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K46">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L46">
-        <v>92.98</v>
+        <v>91.01</v>
       </c>
       <c r="M46">
-        <v>-3.66</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
@@ -2631,37 +2637,37 @@
         <v>102</v>
       </c>
       <c r="C47" s="2">
-        <v>19300</v>
+        <v>50000</v>
       </c>
       <c r="D47" s="3">
-        <v>-3.5999999999999999E-3</v>
+        <v>1.52E-2</v>
       </c>
       <c r="E47">
-        <v>10.48</v>
+        <v>18.690000000000001</v>
       </c>
       <c r="F47">
-        <v>7.97</v>
+        <v>11.56</v>
       </c>
       <c r="G47">
-        <v>10.17</v>
+        <v>6.83</v>
       </c>
       <c r="H47" s="4">
-        <v>25607.22</v>
+        <v>57293.3</v>
       </c>
       <c r="I47">
-        <v>6.09</v>
+        <v>2.4</v>
       </c>
       <c r="J47">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="K47">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="L47">
-        <v>97.44</v>
+        <v>92.98</v>
       </c>
       <c r="M47">
-        <v>-2.57</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
@@ -2672,37 +2678,37 @@
         <v>104</v>
       </c>
       <c r="C48" s="2">
-        <v>16640</v>
+        <v>19300</v>
       </c>
       <c r="D48" s="3">
-        <v>1.09E-2</v>
+        <v>-3.5999999999999999E-3</v>
       </c>
       <c r="E48">
-        <v>11.13</v>
+        <v>10.48</v>
       </c>
       <c r="F48">
-        <v>5.01</v>
+        <v>7.97</v>
       </c>
       <c r="G48">
-        <v>9.31</v>
+        <v>10.17</v>
       </c>
       <c r="H48" s="4">
-        <v>24921.41</v>
+        <v>25607.22</v>
       </c>
       <c r="I48">
-        <v>6.01</v>
+        <v>6.09</v>
       </c>
       <c r="J48">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K48">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="L48">
-        <v>93.49</v>
+        <v>97.44</v>
       </c>
       <c r="M48">
-        <v>-4.97</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.4">
@@ -2713,36 +2719,77 @@
         <v>106</v>
       </c>
       <c r="C49" s="2">
+        <v>16640</v>
+      </c>
+      <c r="D49" s="3">
+        <v>1.09E-2</v>
+      </c>
+      <c r="E49">
+        <v>11.13</v>
+      </c>
+      <c r="F49">
+        <v>5.01</v>
+      </c>
+      <c r="G49">
+        <v>9.31</v>
+      </c>
+      <c r="H49" s="4">
+        <v>24921.41</v>
+      </c>
+      <c r="I49">
+        <v>6.01</v>
+      </c>
+      <c r="J49">
+        <v>39</v>
+      </c>
+      <c r="K49">
+        <v>39</v>
+      </c>
+      <c r="L49">
+        <v>93.49</v>
+      </c>
+      <c r="M49">
+        <v>-4.97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="2">
         <v>33050</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D50" s="3">
         <v>-2.07E-2</v>
       </c>
-      <c r="E49">
+      <c r="E50">
         <v>9.39</v>
       </c>
-      <c r="F49">
+      <c r="F50">
         <v>10.74</v>
       </c>
-      <c r="G49">
+      <c r="G50">
         <v>9.73</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H50" s="4">
         <v>48211.77</v>
       </c>
-      <c r="I49">
+      <c r="I50">
         <v>3.63</v>
       </c>
-      <c r="J49">
+      <c r="J50">
         <v>73</v>
       </c>
-      <c r="K49">
+      <c r="K50">
         <v>73</v>
       </c>
-      <c r="L49">
+      <c r="L50">
         <v>91.79</v>
       </c>
-      <c r="M49">
+      <c r="M50">
         <v>-6.37</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26F0AFE9-0261-48E4-99BA-93D62D96146F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A99AF20-6250-4C7E-89DB-556622AB0F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E82C1798-5FEC-4409-A1D4-CF43A6D3A27C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5359FB59-5135-435A-B52C-C48AF17DDD08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
   <si>
     <t>종목코드</t>
   </si>
@@ -352,6 +352,14 @@
   </si>
   <si>
     <t>우리금융지주</t>
+  </si>
+  <si>
+    <t>현대차2우B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>005387</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -726,8 +734,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22EB960-1165-4894-B7EE-9E86913D46FA}">
-  <dimension ref="A1:M50"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CF93E0-8A6D-4D2A-9CB9-0B63E9192EC2}">
+  <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
@@ -2793,6 +2801,47 @@
         <v>-6.37</v>
       </c>
     </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="2">
+        <v>275500</v>
+      </c>
+      <c r="D51" s="3">
+        <v>1.29E-2</v>
+      </c>
+      <c r="E51">
+        <v>12.43</v>
+      </c>
+      <c r="F51">
+        <v>10.08</v>
+      </c>
+      <c r="G51">
+        <v>11.82</v>
+      </c>
+      <c r="H51" s="4">
+        <v>429918.88</v>
+      </c>
+      <c r="I51">
+        <v>3.8</v>
+      </c>
+      <c r="J51">
+        <v>78</v>
+      </c>
+      <c r="K51">
+        <v>78</v>
+      </c>
+      <c r="L51">
+        <v>104.88</v>
+      </c>
+      <c r="M51">
+        <v>-7.06</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A99AF20-6250-4C7E-89DB-556622AB0F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE6ABC09-10E3-4EF7-BE00-67649940381F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5359FB59-5135-435A-B52C-C48AF17DDD08}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D0D8E6B3-ABD5-46F0-B461-3A2E48810120}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
   <si>
     <t>종목코드</t>
   </si>
@@ -156,12 +156,6 @@
     <t>DB손해보험</t>
   </si>
   <si>
-    <t>005930</t>
-  </si>
-  <si>
-    <t>삼성전자</t>
-  </si>
-  <si>
     <t>005940</t>
   </si>
   <si>
@@ -352,14 +346,6 @@
   </si>
   <si>
     <t>우리금융지주</t>
-  </si>
-  <si>
-    <t>현대차2우B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>005387</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -734,14 +720,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CF93E0-8A6D-4D2A-9CB9-0B63E9192EC2}">
-  <dimension ref="A1:M51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24CE32F9-E0FD-4470-AB75-91C19A07D619}">
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.296875" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -800,10 +786,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>26000</v>
+        <v>25950</v>
       </c>
       <c r="D2" s="3">
-        <v>7.7999999999999996E-3</v>
+        <v>3.39E-2</v>
       </c>
       <c r="E2">
         <v>8.2799999999999994</v>
@@ -827,10 +813,10 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>87.53</v>
+        <v>88.23</v>
       </c>
       <c r="M2">
-        <v>-9.41</v>
+        <v>-9.58</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -841,10 +827,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>167000</v>
+        <v>166600</v>
       </c>
       <c r="D3" s="3">
-        <v>3.5999999999999999E-3</v>
+        <v>3.4799999999999998E-2</v>
       </c>
       <c r="E3">
         <v>19.09</v>
@@ -859,7 +845,7 @@
         <v>150938.41</v>
       </c>
       <c r="I3">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="J3">
         <v>70</v>
@@ -868,10 +854,10 @@
         <v>70</v>
       </c>
       <c r="L3">
-        <v>98.58</v>
+        <v>97.94</v>
       </c>
       <c r="M3">
-        <v>-8.39</v>
+        <v>-8.61</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -882,10 +868,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>496500</v>
+        <v>504000</v>
       </c>
       <c r="D4" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>3.1699999999999999E-2</v>
       </c>
       <c r="E4">
         <v>13.09</v>
@@ -900,19 +886,19 @@
         <v>405451.96</v>
       </c>
       <c r="I4">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="J4">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K4">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L4">
-        <v>92.86</v>
+        <v>94.65</v>
       </c>
       <c r="M4">
-        <v>-4.8899999999999997</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -923,10 +909,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>39500</v>
+        <v>42250</v>
       </c>
       <c r="D5" s="3">
-        <v>-6.3E-3</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="E5">
         <v>7.12</v>
@@ -941,19 +927,19 @@
         <v>72041.39</v>
       </c>
       <c r="I5">
-        <v>5.0599999999999996</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="J5">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K5">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="L5">
-        <v>90.75</v>
+        <v>96.64</v>
       </c>
       <c r="M5">
-        <v>-8.56</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -964,10 +950,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>78800</v>
+        <v>81400</v>
       </c>
       <c r="D6" s="3">
-        <v>2.07E-2</v>
+        <v>5.4399999999999997E-2</v>
       </c>
       <c r="E6">
         <v>4.05</v>
@@ -982,19 +968,19 @@
         <v>65679.45</v>
       </c>
       <c r="I6">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="J6">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K6">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L6">
-        <v>96.7</v>
+        <v>99.39</v>
       </c>
       <c r="M6">
-        <v>-1.1299999999999999</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -1005,10 +991,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>61900</v>
+        <v>70200</v>
       </c>
       <c r="D7" s="3">
-        <v>1.4800000000000001E-2</v>
+        <v>0.1341</v>
       </c>
       <c r="E7">
         <v>1.04</v>
@@ -1023,19 +1009,19 @@
         <v>53899.69</v>
       </c>
       <c r="I7">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="J7">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="K7">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="L7">
-        <v>84.19</v>
+        <v>99.65</v>
       </c>
       <c r="M7">
-        <v>-7.61</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -1046,10 +1032,10 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>20650</v>
+        <v>20950</v>
       </c>
       <c r="D8" s="3">
-        <v>-9.5999999999999992E-3</v>
+        <v>2.4400000000000002E-2</v>
       </c>
       <c r="E8">
         <v>6.94</v>
@@ -1064,19 +1050,19 @@
         <v>39784.050000000003</v>
       </c>
       <c r="I8">
-        <v>4.12</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L8">
-        <v>91.56</v>
+        <v>93.94</v>
       </c>
       <c r="M8">
-        <v>-5.92</v>
+        <v>-4.5599999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1087,10 +1073,10 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>9430</v>
+        <v>9410</v>
       </c>
       <c r="D9" s="3">
-        <v>2.7199999999999998E-2</v>
+        <v>9.7000000000000003E-3</v>
       </c>
       <c r="E9">
         <v>2.84</v>
@@ -1105,7 +1091,7 @@
         <v>20859.37</v>
       </c>
       <c r="I9">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="J9">
         <v>53</v>
@@ -1114,10 +1100,10 @@
         <v>53</v>
       </c>
       <c r="L9">
-        <v>97.4</v>
+        <v>95.67</v>
       </c>
       <c r="M9">
-        <v>-8.98</v>
+        <v>-9.17</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1128,10 +1114,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>40000</v>
+        <v>40950</v>
       </c>
       <c r="D10" s="3">
-        <v>2.5000000000000001E-3</v>
+        <v>5.1299999999999998E-2</v>
       </c>
       <c r="E10">
         <v>4.57</v>
@@ -1146,19 +1132,19 @@
         <v>42814.52</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="J10">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K10">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L10">
-        <v>101.79</v>
+        <v>101.18</v>
       </c>
       <c r="M10">
-        <v>-3.38</v>
+        <v>-1.0900000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1169,10 +1155,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>94000</v>
+        <v>95100</v>
       </c>
       <c r="D11" s="3">
-        <v>-2.8899999999999999E-2</v>
+        <v>1.06E-2</v>
       </c>
       <c r="E11">
         <v>2.16</v>
@@ -1187,19 +1173,19 @@
         <v>177736.27</v>
       </c>
       <c r="I11">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="J11">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K11">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L11">
-        <v>97.33</v>
+        <v>98.43</v>
       </c>
       <c r="M11">
-        <v>-8.2899999999999991</v>
+        <v>-7.22</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1210,10 +1196,10 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>12790</v>
+        <v>13300</v>
       </c>
       <c r="D12" s="3">
-        <v>-2.4400000000000002E-2</v>
+        <v>3.5799999999999998E-2</v>
       </c>
       <c r="E12">
         <v>9.44</v>
@@ -1228,19 +1214,19 @@
         <v>19219.419999999998</v>
       </c>
       <c r="I12">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="J12">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="K12">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L12">
-        <v>96.67</v>
+        <v>99.59</v>
       </c>
       <c r="M12">
-        <v>-4.91</v>
+        <v>-1.1200000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1251,10 +1237,10 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>394500</v>
+        <v>400500</v>
       </c>
       <c r="D13" s="3">
-        <v>-6.3E-3</v>
+        <v>3.3500000000000002E-2</v>
       </c>
       <c r="E13">
         <v>6.17</v>
@@ -1269,19 +1255,19 @@
         <v>466289.71</v>
       </c>
       <c r="I13">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="J13">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K13">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L13">
-        <v>91.74</v>
+        <v>94.05</v>
       </c>
       <c r="M13">
-        <v>-5.85</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1292,10 +1278,10 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>9530</v>
+        <v>9490</v>
       </c>
       <c r="D14" s="3">
-        <v>-2.0999999999999999E-3</v>
+        <v>2.3699999999999999E-2</v>
       </c>
       <c r="E14">
         <v>8.2100000000000009</v>
@@ -1310,7 +1296,7 @@
         <v>22736.17</v>
       </c>
       <c r="I14">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="J14">
         <v>20</v>
@@ -1319,10 +1305,10 @@
         <v>20</v>
       </c>
       <c r="L14">
-        <v>93.84</v>
+        <v>94.76</v>
       </c>
       <c r="M14">
-        <v>-0.73</v>
+        <v>-1.1499999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1333,10 +1319,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>76400</v>
+        <v>76600</v>
       </c>
       <c r="D15" s="3">
-        <v>-1.29E-2</v>
+        <v>2.5399999999999999E-2</v>
       </c>
       <c r="E15">
         <v>15.14</v>
@@ -1351,7 +1337,7 @@
         <v>82759.37</v>
       </c>
       <c r="I15">
-        <v>4.32</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="J15">
         <v>49</v>
@@ -1360,10 +1346,10 @@
         <v>49</v>
       </c>
       <c r="L15">
-        <v>94.26</v>
+        <v>94.93</v>
       </c>
       <c r="M15">
-        <v>-2.2999999999999998</v>
+        <v>-2.0499999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1374,10 +1360,10 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>553000</v>
+        <v>543500</v>
       </c>
       <c r="D16" s="3">
-        <v>9.1000000000000004E-3</v>
+        <v>3.5200000000000002E-2</v>
       </c>
       <c r="E16">
         <v>12.43</v>
@@ -1392,19 +1378,19 @@
         <v>429918.88</v>
       </c>
       <c r="I16">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="J16">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K16">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L16">
-        <v>104.88</v>
+        <v>102.2</v>
       </c>
       <c r="M16">
-        <v>-7.06</v>
+        <v>-8.66</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1415,10 +1401,10 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>188400</v>
+        <v>189600</v>
       </c>
       <c r="D17" s="3">
-        <v>-1.15E-2</v>
+        <v>3.32E-2</v>
       </c>
       <c r="E17">
         <v>18.96</v>
@@ -1433,19 +1419,19 @@
         <v>144109.65</v>
       </c>
       <c r="I17">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="J17">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K17">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L17">
-        <v>104.57</v>
+        <v>102.41</v>
       </c>
       <c r="M17">
-        <v>0.91</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1456,37 +1442,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>188200</v>
+        <v>33500</v>
       </c>
       <c r="D18" s="3">
-        <v>-1.77E-2</v>
+        <v>6.6900000000000001E-2</v>
       </c>
       <c r="E18">
-        <v>10.85</v>
+        <v>8.73</v>
       </c>
       <c r="F18">
-        <v>10.85</v>
+        <v>11.57</v>
       </c>
       <c r="G18">
-        <v>8.01</v>
+        <v>6.85</v>
       </c>
       <c r="H18" s="4">
-        <v>63976.31</v>
+        <v>24348.21</v>
       </c>
       <c r="I18">
-        <v>0.89</v>
+        <v>2.84</v>
       </c>
       <c r="J18">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K18">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L18">
-        <v>102.49</v>
+        <v>102.9</v>
       </c>
       <c r="M18">
-        <v>-3.54</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1497,37 +1483,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>32200</v>
+        <v>372000</v>
       </c>
       <c r="D19" s="3">
-        <v>4.7000000000000002E-3</v>
+        <v>3.3300000000000003E-2</v>
       </c>
       <c r="E19">
-        <v>8.73</v>
+        <v>6.85</v>
       </c>
       <c r="F19">
-        <v>11.57</v>
+        <v>6.19</v>
       </c>
       <c r="G19">
-        <v>6.85</v>
+        <v>10.64</v>
       </c>
       <c r="H19" s="4">
-        <v>24348.21</v>
+        <v>605494.72</v>
       </c>
       <c r="I19">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="J19">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="K19">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="L19">
-        <v>101.24</v>
+        <v>95.57</v>
       </c>
       <c r="M19">
-        <v>-3.3</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1538,37 +1524,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>367000</v>
+        <v>28450</v>
       </c>
       <c r="D20" s="3">
-        <v>-1.4800000000000001E-2</v>
+        <v>2.52E-2</v>
       </c>
       <c r="E20">
-        <v>6.85</v>
+        <v>19.78</v>
       </c>
       <c r="F20">
-        <v>6.19</v>
+        <v>13.82</v>
       </c>
       <c r="G20">
-        <v>10.64</v>
+        <v>23.29</v>
       </c>
       <c r="H20" s="4">
-        <v>605494.72</v>
+        <v>32624.26</v>
       </c>
       <c r="I20">
-        <v>2.4500000000000002</v>
+        <v>3.51</v>
       </c>
       <c r="J20">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="L20">
-        <v>93.41</v>
+        <v>100.06</v>
       </c>
       <c r="M20">
-        <v>-5.53</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1579,37 +1565,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>25100</v>
+        <v>236500</v>
       </c>
       <c r="D21" s="3">
-        <v>2.4500000000000001E-2</v>
+        <v>6.2899999999999998E-2</v>
       </c>
       <c r="E21">
-        <v>19.78</v>
+        <v>13.17</v>
       </c>
       <c r="F21">
-        <v>13.82</v>
+        <v>11.69</v>
       </c>
       <c r="G21">
-        <v>23.29</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H21" s="4">
-        <v>32624.26</v>
+        <v>207156.6</v>
       </c>
       <c r="I21">
-        <v>3.98</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J21">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="K21">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="L21">
-        <v>88.92</v>
+        <v>102.77</v>
       </c>
       <c r="M21">
-        <v>-5.28</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1620,37 +1606,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>230500</v>
+        <v>125800</v>
       </c>
       <c r="D22" s="3">
-        <v>1.54E-2</v>
+        <v>3.2800000000000003E-2</v>
       </c>
       <c r="E22">
-        <v>13.17</v>
+        <v>5.88</v>
       </c>
       <c r="F22">
-        <v>11.69</v>
+        <v>6.29</v>
       </c>
       <c r="G22">
-        <v>18.010000000000002</v>
+        <v>10.87</v>
       </c>
       <c r="H22" s="4">
-        <v>207156.6</v>
+        <v>215382.39999999999</v>
       </c>
       <c r="I22">
-        <v>2.3199999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="J22">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K22">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="L22">
-        <v>101.07</v>
+        <v>91.27</v>
       </c>
       <c r="M22">
-        <v>-5.53</v>
+        <v>-9.17</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1661,37 +1647,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>122500</v>
+        <v>99800</v>
       </c>
       <c r="D23" s="3">
-        <v>4.1000000000000003E-3</v>
+        <v>6.8500000000000005E-2</v>
       </c>
       <c r="E23">
-        <v>5.88</v>
+        <v>12.89</v>
       </c>
       <c r="F23">
-        <v>6.29</v>
+        <v>13.94</v>
       </c>
       <c r="G23">
-        <v>10.87</v>
+        <v>9.44</v>
       </c>
       <c r="H23" s="4">
-        <v>215382.39999999999</v>
+        <v>87743.72</v>
       </c>
       <c r="I23">
-        <v>1.8</v>
+        <v>3.51</v>
       </c>
       <c r="J23">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="K23">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="L23">
-        <v>87.14</v>
+        <v>99.47</v>
       </c>
       <c r="M23">
-        <v>-11.55</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1702,37 +1688,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>95900</v>
+        <v>79200</v>
       </c>
       <c r="D24" s="3">
-        <v>7.4000000000000003E-3</v>
+        <v>2.5899999999999999E-2</v>
       </c>
       <c r="E24">
-        <v>12.89</v>
+        <v>10.83</v>
       </c>
       <c r="F24">
-        <v>13.94</v>
+        <v>3.37</v>
       </c>
       <c r="G24">
-        <v>9.44</v>
+        <v>9.48</v>
       </c>
       <c r="H24" s="4">
-        <v>87743.72</v>
+        <v>54894.12</v>
       </c>
       <c r="I24">
-        <v>3.65</v>
+        <v>4.47</v>
       </c>
       <c r="J24">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K24">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L24">
-        <v>96.04</v>
+        <v>101.69</v>
       </c>
       <c r="M24">
-        <v>-4.58</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1743,37 +1729,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>76500</v>
+        <v>89800</v>
       </c>
       <c r="D25" s="3">
-        <v>-1.7999999999999999E-2</v>
+        <v>1.01E-2</v>
       </c>
       <c r="E25">
-        <v>10.83</v>
+        <v>14.42</v>
       </c>
       <c r="F25">
-        <v>3.37</v>
+        <v>24.2</v>
       </c>
       <c r="G25">
-        <v>9.48</v>
+        <v>15.82</v>
       </c>
       <c r="H25" s="4">
-        <v>54894.12</v>
+        <v>36460.550000000003</v>
       </c>
       <c r="I25">
-        <v>4.63</v>
+        <v>6.12</v>
       </c>
       <c r="J25">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K25">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L25">
-        <v>98.42</v>
+        <v>90.84</v>
       </c>
       <c r="M25">
-        <v>-2.17</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1784,37 +1770,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>87000</v>
+        <v>23950</v>
       </c>
       <c r="D26" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>3.6799999999999999E-2</v>
       </c>
       <c r="E26">
-        <v>14.42</v>
+        <v>8.06</v>
       </c>
       <c r="F26">
-        <v>24.2</v>
+        <v>8.64</v>
       </c>
       <c r="G26">
-        <v>15.82</v>
+        <v>8.77</v>
       </c>
       <c r="H26" s="4">
-        <v>36460.550000000003</v>
+        <v>44443.18</v>
       </c>
       <c r="I26">
-        <v>6.32</v>
+        <v>4.45</v>
       </c>
       <c r="J26">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K26">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L26">
-        <v>86.93</v>
+        <v>95.75</v>
       </c>
       <c r="M26">
-        <v>-8.0299999999999994</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1825,37 +1811,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>23650</v>
+        <v>60100</v>
       </c>
       <c r="D27" s="3">
-        <v>-6.3E-3</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="E27">
-        <v>8.06</v>
+        <v>7.45</v>
       </c>
       <c r="F27">
-        <v>8.64</v>
+        <v>7.45</v>
       </c>
       <c r="G27">
-        <v>8.77</v>
+        <v>7.69</v>
       </c>
       <c r="H27" s="4">
-        <v>44443.18</v>
+        <v>79986.48</v>
       </c>
       <c r="I27">
-        <v>4.5</v>
+        <v>4.66</v>
       </c>
       <c r="J27">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K27">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L27">
-        <v>94.88</v>
+        <v>97.76</v>
       </c>
       <c r="M27">
-        <v>-5.78</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1866,37 +1852,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>59300</v>
+        <v>20750</v>
       </c>
       <c r="D28" s="3">
-        <v>-3.3999999999999998E-3</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="E28">
-        <v>7.45</v>
+        <v>15.12</v>
       </c>
       <c r="F28">
-        <v>7.45</v>
+        <v>13.07</v>
       </c>
       <c r="G28">
-        <v>7.69</v>
+        <v>15.58</v>
       </c>
       <c r="H28" s="4">
-        <v>79986.48</v>
+        <v>15310.06</v>
       </c>
       <c r="I28">
-        <v>4.72</v>
+        <v>5.93</v>
       </c>
       <c r="J28">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="K28">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="L28">
-        <v>96.86</v>
+        <v>96.84</v>
       </c>
       <c r="M28">
-        <v>-4.2</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1907,37 +1893,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>20200</v>
+        <v>61100</v>
       </c>
       <c r="D29" s="3">
-        <v>-9.7999999999999997E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="E29">
-        <v>15.12</v>
+        <v>2.85</v>
       </c>
       <c r="F29">
-        <v>13.07</v>
+        <v>12.83</v>
       </c>
       <c r="G29">
-        <v>15.58</v>
+        <v>5.63</v>
       </c>
       <c r="H29" s="4">
-        <v>15310.06</v>
+        <v>71073.47</v>
       </c>
       <c r="I29">
-        <v>6.09</v>
+        <v>3.27</v>
       </c>
       <c r="J29">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="K29">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="L29">
-        <v>94.12</v>
+        <v>98.07</v>
       </c>
       <c r="M29">
-        <v>-5.39</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1948,37 +1934,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>59000</v>
+        <v>15220</v>
       </c>
       <c r="D30" s="3">
-        <v>2.0799999999999999E-2</v>
+        <v>3.1199999999999999E-2</v>
       </c>
       <c r="E30">
-        <v>2.85</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F30">
-        <v>12.83</v>
+        <v>6.71</v>
       </c>
       <c r="G30">
-        <v>5.63</v>
+        <v>6.75</v>
       </c>
       <c r="H30" s="4">
-        <v>71073.47</v>
+        <v>20394.86</v>
       </c>
       <c r="I30">
-        <v>3.39</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J30">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="K30">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="L30">
-        <v>95.59</v>
+        <v>93.7</v>
       </c>
       <c r="M30">
-        <v>-6.35</v>
+        <v>-5.52</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1989,37 +1975,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>15090</v>
+        <v>221500</v>
       </c>
       <c r="D31" s="3">
-        <v>5.3E-3</v>
+        <v>4.7300000000000002E-2</v>
       </c>
       <c r="E31">
-        <v>4.4000000000000004</v>
+        <v>4.66</v>
       </c>
       <c r="F31">
-        <v>6.71</v>
+        <v>4.66</v>
       </c>
       <c r="G31">
-        <v>6.75</v>
+        <v>4.88</v>
       </c>
       <c r="H31" s="4">
-        <v>20394.86</v>
+        <v>324173.33</v>
       </c>
       <c r="I31">
-        <v>4.3099999999999996</v>
+        <v>2.39</v>
       </c>
       <c r="J31">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="K31">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="L31">
-        <v>91.97</v>
+        <v>103.97</v>
       </c>
       <c r="M31">
-        <v>-6.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -2030,25 +2016,25 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>210000</v>
+        <v>156800</v>
       </c>
       <c r="D32" s="3">
-        <v>-1.8700000000000001E-2</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="E32">
-        <v>4.66</v>
+        <v>12.66</v>
       </c>
       <c r="F32">
-        <v>4.66</v>
+        <v>11.88</v>
       </c>
       <c r="G32">
-        <v>4.88</v>
+        <v>11.14</v>
       </c>
       <c r="H32" s="4">
-        <v>324173.33</v>
+        <v>83639.03</v>
       </c>
       <c r="I32">
-        <v>2.52</v>
+        <v>3.44</v>
       </c>
       <c r="J32">
         <v>76</v>
@@ -2057,10 +2043,10 @@
         <v>76</v>
       </c>
       <c r="L32">
-        <v>99.93</v>
+        <v>94.29</v>
       </c>
       <c r="M32">
-        <v>-5.19</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2071,37 +2057,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>154700</v>
+        <v>18130</v>
       </c>
       <c r="D33" s="3">
-        <v>-1.21E-2</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="E33">
-        <v>12.66</v>
+        <v>12.08</v>
       </c>
       <c r="F33">
-        <v>11.88</v>
+        <v>8.58</v>
       </c>
       <c r="G33">
-        <v>11.14</v>
+        <v>8.39</v>
       </c>
       <c r="H33" s="4">
-        <v>83639.03</v>
+        <v>19234.22</v>
       </c>
       <c r="I33">
-        <v>3.49</v>
+        <v>6.45</v>
       </c>
       <c r="J33">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="K33">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="L33">
-        <v>92.57</v>
+        <v>97.57</v>
       </c>
       <c r="M33">
-        <v>-4.68</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2112,37 +2098,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>18080</v>
+        <v>36550</v>
       </c>
       <c r="D34" s="3">
-        <v>1.4E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="E34">
-        <v>12.08</v>
+        <v>11.21</v>
       </c>
       <c r="F34">
-        <v>8.58</v>
+        <v>6.55</v>
       </c>
       <c r="G34">
-        <v>8.39</v>
+        <v>6.4</v>
       </c>
       <c r="H34" s="4">
-        <v>19234.22</v>
+        <v>122131.86</v>
       </c>
       <c r="I34">
-        <v>6.47</v>
+        <v>3.98</v>
       </c>
       <c r="J34">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K34">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L34">
-        <v>97.6</v>
+        <v>89.4</v>
       </c>
       <c r="M34">
-        <v>-3.52</v>
+        <v>-9.98</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2153,37 +2139,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>36900</v>
+        <v>16980</v>
       </c>
       <c r="D35" s="3">
-        <v>-5.4000000000000003E-3</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="E35">
-        <v>11.21</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="F35">
-        <v>6.55</v>
+        <v>3.02</v>
       </c>
       <c r="G35">
-        <v>6.4</v>
+        <v>6.13</v>
       </c>
       <c r="H35" s="4">
-        <v>122131.86</v>
+        <v>7055.63</v>
       </c>
       <c r="I35">
-        <v>3.94</v>
+        <v>0.65</v>
       </c>
       <c r="J35">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="K35">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="L35">
-        <v>88.74</v>
+        <v>109.86</v>
       </c>
       <c r="M35">
-        <v>-9.11</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2194,37 +2180,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>14770</v>
+        <v>92600</v>
       </c>
       <c r="D36" s="3">
-        <v>3.0700000000000002E-2</v>
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="E36">
-        <v>9.0399999999999991</v>
+        <v>8.11</v>
       </c>
       <c r="F36">
-        <v>3.02</v>
+        <v>10.44</v>
       </c>
       <c r="G36">
-        <v>6.13</v>
+        <v>8.66</v>
       </c>
       <c r="H36" s="4">
-        <v>7055.63</v>
+        <v>119742.76</v>
       </c>
       <c r="I36">
-        <v>0.74</v>
+        <v>2.33</v>
       </c>
       <c r="J36">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="K36">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="L36">
-        <v>93.64</v>
+        <v>95.66</v>
       </c>
       <c r="M36">
-        <v>-13.12</v>
+        <v>-4.24</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2235,37 +2221,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>91800</v>
+        <v>236000</v>
       </c>
       <c r="D37" s="3">
-        <v>-1.18E-2</v>
+        <v>7.2700000000000001E-2</v>
       </c>
       <c r="E37">
-        <v>8.11</v>
+        <v>11.54</v>
       </c>
       <c r="F37">
-        <v>10.44</v>
+        <v>20.98</v>
       </c>
       <c r="G37">
-        <v>8.66</v>
+        <v>9.6</v>
       </c>
       <c r="H37" s="4">
-        <v>119742.76</v>
+        <v>189057.03</v>
       </c>
       <c r="I37">
-        <v>2.35</v>
+        <v>1.69</v>
       </c>
       <c r="J37">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K37">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L37">
-        <v>94.88</v>
+        <v>96.42</v>
       </c>
       <c r="M37">
-        <v>-5.07</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2276,37 +2262,37 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>230000</v>
+        <v>66600</v>
       </c>
       <c r="D38" s="3">
-        <v>-2.2000000000000001E-3</v>
+        <v>4.0599999999999997E-2</v>
       </c>
       <c r="E38">
-        <v>11.54</v>
+        <v>4.12</v>
       </c>
       <c r="F38">
-        <v>20.98</v>
+        <v>5.22</v>
       </c>
       <c r="G38">
-        <v>9.6</v>
+        <v>11.01</v>
       </c>
       <c r="H38" s="4">
-        <v>189057.03</v>
+        <v>151788</v>
       </c>
       <c r="I38">
-        <v>1.73</v>
+        <v>4.05</v>
       </c>
       <c r="J38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L38">
-        <v>94.57</v>
+        <v>96.04</v>
       </c>
       <c r="M38">
-        <v>-4.37</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2317,37 +2303,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>65600</v>
+        <v>115200</v>
       </c>
       <c r="D39" s="3">
-        <v>-1.4999999999999999E-2</v>
+        <v>4.82E-2</v>
       </c>
       <c r="E39">
-        <v>4.12</v>
+        <v>9.11</v>
       </c>
       <c r="F39">
-        <v>5.22</v>
+        <v>10.57</v>
       </c>
       <c r="G39">
-        <v>11.01</v>
+        <v>9.4</v>
       </c>
       <c r="H39" s="4">
-        <v>151788</v>
+        <v>159337.74</v>
       </c>
       <c r="I39">
-        <v>4.12</v>
+        <v>3.13</v>
       </c>
       <c r="J39">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="K39">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="L39">
-        <v>93.81</v>
+        <v>95.82</v>
       </c>
       <c r="M39">
-        <v>-6.95</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2358,37 +2344,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>110300</v>
+        <v>154600</v>
       </c>
       <c r="D40" s="3">
-        <v>-8.0999999999999996E-3</v>
+        <v>4.8800000000000003E-2</v>
       </c>
       <c r="E40">
-        <v>9.11</v>
+        <v>8.86</v>
       </c>
       <c r="F40">
-        <v>10.57</v>
+        <v>11.63</v>
       </c>
       <c r="G40">
-        <v>9.4</v>
+        <v>8.51</v>
       </c>
       <c r="H40" s="4">
-        <v>159337.74</v>
+        <v>160038.65</v>
       </c>
       <c r="I40">
-        <v>3.26</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="J40">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K40">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="L40">
-        <v>91.6</v>
+        <v>98.1</v>
       </c>
       <c r="M40">
-        <v>-8.16</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2399,37 +2385,37 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>147400</v>
+        <v>19150</v>
       </c>
       <c r="D41" s="3">
-        <v>-1.0699999999999999E-2</v>
+        <v>4.4699999999999997E-2</v>
       </c>
       <c r="E41">
-        <v>8.86</v>
+        <v>6.96</v>
       </c>
       <c r="F41">
-        <v>11.63</v>
+        <v>9.58</v>
       </c>
       <c r="G41">
-        <v>8.51</v>
+        <v>7.18</v>
       </c>
       <c r="H41" s="4">
-        <v>160038.65</v>
+        <v>34223.949999999997</v>
       </c>
       <c r="I41">
-        <v>2.15</v>
+        <v>3.39</v>
       </c>
       <c r="J41">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K41">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L41">
-        <v>94.25</v>
+        <v>95.15</v>
       </c>
       <c r="M41">
-        <v>-3.97</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2440,37 +2426,37 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>18420</v>
+        <v>17500</v>
       </c>
       <c r="D42" s="3">
-        <v>-2.0199999999999999E-2</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="E42">
-        <v>6.96</v>
+        <v>3.6</v>
       </c>
       <c r="F42">
-        <v>9.58</v>
+        <v>9.42</v>
       </c>
       <c r="G42">
-        <v>7.18</v>
+        <v>5.91</v>
       </c>
       <c r="H42" s="4">
-        <v>34223.949999999997</v>
+        <v>38541.279999999999</v>
       </c>
       <c r="I42">
-        <v>3.53</v>
+        <v>2.86</v>
       </c>
       <c r="J42">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K42">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L42">
-        <v>92.02</v>
+        <v>93.09</v>
       </c>
       <c r="M42">
-        <v>-6.4</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2481,37 +2467,37 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>17050</v>
+        <v>60200</v>
       </c>
       <c r="D43" s="3">
-        <v>-1.1599999999999999E-2</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="E43">
-        <v>3.6</v>
+        <v>10.79</v>
       </c>
       <c r="F43">
-        <v>9.42</v>
+        <v>10.55</v>
       </c>
       <c r="G43">
-        <v>5.91</v>
+        <v>8.93</v>
       </c>
       <c r="H43" s="4">
-        <v>38541.279999999999</v>
+        <v>92723.77</v>
       </c>
       <c r="I43">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="J43">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="K43">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L43">
-        <v>91.11</v>
+        <v>87.68</v>
       </c>
       <c r="M43">
-        <v>-5.8</v>
+        <v>-9.8800000000000008</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
@@ -2522,37 +2508,37 @@
         <v>96</v>
       </c>
       <c r="C44" s="2">
-        <v>59300</v>
+        <v>31750</v>
       </c>
       <c r="D44" s="3">
-        <v>-3.8899999999999997E-2</v>
+        <v>3.7600000000000001E-2</v>
       </c>
       <c r="E44">
-        <v>10.79</v>
+        <v>12.8</v>
       </c>
       <c r="F44">
-        <v>10.55</v>
+        <v>13.49</v>
       </c>
       <c r="G44">
-        <v>8.93</v>
+        <v>12.93</v>
       </c>
       <c r="H44" s="4">
-        <v>92723.77</v>
+        <v>31004.78</v>
       </c>
       <c r="I44">
-        <v>3.37</v>
+        <v>3.13</v>
       </c>
       <c r="J44">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="K44">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="L44">
-        <v>85.21</v>
+        <v>99.21</v>
       </c>
       <c r="M44">
-        <v>-11.23</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
@@ -2563,37 +2549,37 @@
         <v>98</v>
       </c>
       <c r="C45" s="2">
-        <v>29400</v>
+        <v>12070</v>
       </c>
       <c r="D45" s="3">
-        <v>5.1000000000000004E-3</v>
+        <v>1.17E-2</v>
       </c>
       <c r="E45">
-        <v>12.8</v>
+        <v>7.65</v>
       </c>
       <c r="F45">
-        <v>13.49</v>
+        <v>4</v>
       </c>
       <c r="G45">
-        <v>12.93</v>
+        <v>7.8</v>
       </c>
       <c r="H45" s="4">
-        <v>31004.78</v>
+        <v>30039.25</v>
       </c>
       <c r="I45">
-        <v>3.38</v>
+        <v>2.15</v>
       </c>
       <c r="J45">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="K45">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L45">
-        <v>93.05</v>
+        <v>94.49</v>
       </c>
       <c r="M45">
-        <v>-5.62</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
@@ -2604,37 +2590,37 @@
         <v>100</v>
       </c>
       <c r="C46" s="2">
-        <v>11810</v>
+        <v>50100</v>
       </c>
       <c r="D46" s="3">
-        <v>1.6999999999999999E-3</v>
+        <v>1.83E-2</v>
       </c>
       <c r="E46">
-        <v>7.65</v>
+        <v>18.690000000000001</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>11.56</v>
       </c>
       <c r="G46">
-        <v>7.8</v>
+        <v>6.83</v>
       </c>
       <c r="H46" s="4">
-        <v>30039.25</v>
+        <v>57293.3</v>
       </c>
       <c r="I46">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="J46">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K46">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L46">
-        <v>91.01</v>
+        <v>93.96</v>
       </c>
       <c r="M46">
-        <v>-4.22</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
@@ -2645,37 +2631,37 @@
         <v>102</v>
       </c>
       <c r="C47" s="2">
-        <v>50000</v>
+        <v>19590</v>
       </c>
       <c r="D47" s="3">
-        <v>1.52E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="E47">
-        <v>18.690000000000001</v>
+        <v>10.48</v>
       </c>
       <c r="F47">
-        <v>11.56</v>
+        <v>7.97</v>
       </c>
       <c r="G47">
-        <v>6.83</v>
+        <v>10.17</v>
       </c>
       <c r="H47" s="4">
-        <v>57293.3</v>
+        <v>25607.22</v>
       </c>
       <c r="I47">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="J47">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="K47">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="L47">
-        <v>92.98</v>
+        <v>98.89</v>
       </c>
       <c r="M47">
-        <v>-3.66</v>
+        <v>-1.1100000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
@@ -2686,37 +2672,37 @@
         <v>104</v>
       </c>
       <c r="C48" s="2">
-        <v>19300</v>
+        <v>16850</v>
       </c>
       <c r="D48" s="3">
-        <v>-3.5999999999999999E-3</v>
+        <v>3.56E-2</v>
       </c>
       <c r="E48">
-        <v>10.48</v>
+        <v>11.13</v>
       </c>
       <c r="F48">
-        <v>7.97</v>
+        <v>5.01</v>
       </c>
       <c r="G48">
-        <v>10.17</v>
+        <v>9.31</v>
       </c>
       <c r="H48" s="4">
-        <v>25607.22</v>
+        <v>24921.41</v>
       </c>
       <c r="I48">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="J48">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="K48">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="L48">
-        <v>97.44</v>
+        <v>95.74</v>
       </c>
       <c r="M48">
-        <v>-2.57</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.4">
@@ -2727,119 +2713,37 @@
         <v>106</v>
       </c>
       <c r="C49" s="2">
-        <v>16640</v>
+        <v>33650</v>
       </c>
       <c r="D49" s="3">
-        <v>1.09E-2</v>
+        <v>4.8300000000000003E-2</v>
       </c>
       <c r="E49">
-        <v>11.13</v>
+        <v>9.39</v>
       </c>
       <c r="F49">
-        <v>5.01</v>
+        <v>10.74</v>
       </c>
       <c r="G49">
-        <v>9.31</v>
+        <v>9.73</v>
       </c>
       <c r="H49" s="4">
-        <v>24921.41</v>
+        <v>48211.77</v>
       </c>
       <c r="I49">
-        <v>6.01</v>
+        <v>3.57</v>
       </c>
       <c r="J49">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="K49">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="L49">
-        <v>93.49</v>
+        <v>93.19</v>
       </c>
       <c r="M49">
-        <v>-4.97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A50" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B50" t="s">
-        <v>108</v>
-      </c>
-      <c r="C50" s="2">
-        <v>33050</v>
-      </c>
-      <c r="D50" s="3">
-        <v>-2.07E-2</v>
-      </c>
-      <c r="E50">
-        <v>9.39</v>
-      </c>
-      <c r="F50">
-        <v>10.74</v>
-      </c>
-      <c r="G50">
-        <v>9.73</v>
-      </c>
-      <c r="H50" s="4">
-        <v>48211.77</v>
-      </c>
-      <c r="I50">
-        <v>3.63</v>
-      </c>
-      <c r="J50">
-        <v>73</v>
-      </c>
-      <c r="K50">
-        <v>73</v>
-      </c>
-      <c r="L50">
-        <v>91.79</v>
-      </c>
-      <c r="M50">
-        <v>-6.37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A51" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B51" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" s="2">
-        <v>275500</v>
-      </c>
-      <c r="D51" s="3">
-        <v>1.29E-2</v>
-      </c>
-      <c r="E51">
-        <v>12.43</v>
-      </c>
-      <c r="F51">
-        <v>10.08</v>
-      </c>
-      <c r="G51">
-        <v>11.82</v>
-      </c>
-      <c r="H51" s="4">
-        <v>429918.88</v>
-      </c>
-      <c r="I51">
-        <v>3.8</v>
-      </c>
-      <c r="J51">
-        <v>78</v>
-      </c>
-      <c r="K51">
-        <v>78</v>
-      </c>
-      <c r="L51">
-        <v>104.88</v>
-      </c>
-      <c r="M51">
-        <v>-7.06</v>
+        <v>-4.67</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE6ABC09-10E3-4EF7-BE00-67649940381F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09702678-E96D-485A-90E8-C12FD302C229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D0D8E6B3-ABD5-46F0-B461-3A2E48810120}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{192E0C0B-58FF-4559-905F-66C1C805FB95}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,6 +60,264 @@
     <t>해당등락률</t>
   </si>
   <si>
+    <t>038500</t>
+  </si>
+  <si>
+    <t>삼표시멘트</t>
+  </si>
+  <si>
+    <t>001430</t>
+  </si>
+  <si>
+    <t>세아베스틸지주</t>
+  </si>
+  <si>
+    <t>001120</t>
+  </si>
+  <si>
+    <t>LX인터내셔널</t>
+  </si>
+  <si>
+    <t>007340</t>
+  </si>
+  <si>
+    <t>DN오토모티브</t>
+  </si>
+  <si>
+    <t>003690</t>
+  </si>
+  <si>
+    <t>코리안리</t>
+  </si>
+  <si>
+    <t>175330</t>
+  </si>
+  <si>
+    <t>JB금융지주</t>
+  </si>
+  <si>
+    <t>214320</t>
+  </si>
+  <si>
+    <t>이노션</t>
+  </si>
+  <si>
+    <t>005830</t>
+  </si>
+  <si>
+    <t>DB손해보험</t>
+  </si>
+  <si>
+    <t>004980</t>
+  </si>
+  <si>
+    <t>성신양회</t>
+  </si>
+  <si>
+    <t>078930</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>030200</t>
+  </si>
+  <si>
+    <t>KT</t>
+  </si>
+  <si>
+    <t>029780</t>
+  </si>
+  <si>
+    <t>삼성카드</t>
+  </si>
+  <si>
+    <t>001270</t>
+  </si>
+  <si>
+    <t>부국증권</t>
+  </si>
+  <si>
+    <t>035250</t>
+  </si>
+  <si>
+    <t>강원랜드</t>
+  </si>
+  <si>
+    <t>017670</t>
+  </si>
+  <si>
+    <t>SK텔레콤</t>
+  </si>
+  <si>
+    <t>033780</t>
+  </si>
+  <si>
+    <t>KT&amp;G</t>
+  </si>
+  <si>
+    <t>009970</t>
+  </si>
+  <si>
+    <t>영원무역홀딩스</t>
+  </si>
+  <si>
+    <t>032830</t>
+  </si>
+  <si>
+    <t>삼성생명</t>
+  </si>
+  <si>
+    <t>183190</t>
+  </si>
+  <si>
+    <t>아세아시멘트</t>
+  </si>
+  <si>
+    <t>055550</t>
+  </si>
+  <si>
+    <t>신한지주</t>
+  </si>
+  <si>
+    <t>030000</t>
+  </si>
+  <si>
+    <t>제일기획</t>
+  </si>
+  <si>
+    <t>007310</t>
+  </si>
+  <si>
+    <t>오뚜기</t>
+  </si>
+  <si>
+    <t>192080</t>
+  </si>
+  <si>
+    <t>더블유게임즈</t>
+  </si>
+  <si>
+    <t>005180</t>
+  </si>
+  <si>
+    <t>빙그레</t>
+  </si>
+  <si>
+    <t>105560</t>
+  </si>
+  <si>
+    <t>KB금융</t>
+  </si>
+  <si>
+    <t>300720</t>
+  </si>
+  <si>
+    <t>한일시멘트</t>
+  </si>
+  <si>
+    <t>138930</t>
+  </si>
+  <si>
+    <t>BNK금융지주</t>
+  </si>
+  <si>
+    <t>000810</t>
+  </si>
+  <si>
+    <t>삼성화재</t>
+  </si>
+  <si>
+    <t>086790</t>
+  </si>
+  <si>
+    <t>하나금융지주</t>
+  </si>
+  <si>
+    <t>032640</t>
+  </si>
+  <si>
+    <t>LG유플러스</t>
+  </si>
+  <si>
+    <t>001680</t>
+  </si>
+  <si>
+    <t>대상</t>
+  </si>
+  <si>
+    <t>005940</t>
+  </si>
+  <si>
+    <t>NH투자증권</t>
+  </si>
+  <si>
+    <t>139130</t>
+  </si>
+  <si>
+    <t>iM금융지주</t>
+  </si>
+  <si>
+    <t>024110</t>
+  </si>
+  <si>
+    <t>기업은행</t>
+  </si>
+  <si>
+    <t>316140</t>
+  </si>
+  <si>
+    <t>우리금융지주</t>
+  </si>
+  <si>
+    <t>016360</t>
+  </si>
+  <si>
+    <t>삼성증권</t>
+  </si>
+  <si>
+    <t>017800</t>
+  </si>
+  <si>
+    <t>현대엘리베이터</t>
+  </si>
+  <si>
+    <t>003540</t>
+  </si>
+  <si>
+    <t>대신증권</t>
+  </si>
+  <si>
+    <t>071050</t>
+  </si>
+  <si>
+    <t>한국금융지주</t>
+  </si>
+  <si>
+    <t>036460</t>
+  </si>
+  <si>
+    <t>한국가스공사</t>
+  </si>
+  <si>
+    <t>004370</t>
+  </si>
+  <si>
+    <t>농심</t>
+  </si>
+  <si>
+    <t>002310</t>
+  </si>
+  <si>
+    <t>아세아제지</t>
+  </si>
+  <si>
+    <t>003550</t>
+  </si>
+  <si>
+    <t>LG</t>
+  </si>
+  <si>
     <t>000240</t>
   </si>
   <si>
@@ -72,280 +330,22 @@
     <t>기아</t>
   </si>
   <si>
-    <t>000810</t>
-  </si>
-  <si>
-    <t>삼성화재</t>
-  </si>
-  <si>
-    <t>001120</t>
-  </si>
-  <si>
-    <t>LX인터내셔널</t>
-  </si>
-  <si>
-    <t>001270</t>
-  </si>
-  <si>
-    <t>부국증권</t>
-  </si>
-  <si>
-    <t>001430</t>
-  </si>
-  <si>
-    <t>세아베스틸지주</t>
-  </si>
-  <si>
-    <t>001680</t>
-  </si>
-  <si>
-    <t>대상</t>
-  </si>
-  <si>
-    <t>002310</t>
-  </si>
-  <si>
-    <t>아세아제지</t>
-  </si>
-  <si>
-    <t>003540</t>
-  </si>
-  <si>
-    <t>대신증권</t>
-  </si>
-  <si>
-    <t>003550</t>
-  </si>
-  <si>
-    <t>LG</t>
-  </si>
-  <si>
-    <t>003690</t>
-  </si>
-  <si>
-    <t>코리안리</t>
-  </si>
-  <si>
-    <t>004370</t>
-  </si>
-  <si>
-    <t>농심</t>
-  </si>
-  <si>
-    <t>004980</t>
-  </si>
-  <si>
-    <t>성신양회</t>
-  </si>
-  <si>
-    <t>005180</t>
-  </si>
-  <si>
-    <t>빙그레</t>
+    <t>161390</t>
+  </si>
+  <si>
+    <t>한국타이어앤테크놀로</t>
+  </si>
+  <si>
+    <t>011780</t>
+  </si>
+  <si>
+    <t>금호석유화학</t>
   </si>
   <si>
     <t>005380</t>
   </si>
   <si>
     <t>현대차</t>
-  </si>
-  <si>
-    <t>005830</t>
-  </si>
-  <si>
-    <t>DB손해보험</t>
-  </si>
-  <si>
-    <t>005940</t>
-  </si>
-  <si>
-    <t>NH투자증권</t>
-  </si>
-  <si>
-    <t>007310</t>
-  </si>
-  <si>
-    <t>오뚜기</t>
-  </si>
-  <si>
-    <t>007340</t>
-  </si>
-  <si>
-    <t>DN오토모티브</t>
-  </si>
-  <si>
-    <t>009970</t>
-  </si>
-  <si>
-    <t>영원무역홀딩스</t>
-  </si>
-  <si>
-    <t>011780</t>
-  </si>
-  <si>
-    <t>금호석유화학</t>
-  </si>
-  <si>
-    <t>016360</t>
-  </si>
-  <si>
-    <t>삼성증권</t>
-  </si>
-  <si>
-    <t>017670</t>
-  </si>
-  <si>
-    <t>SK텔레콤</t>
-  </si>
-  <si>
-    <t>017800</t>
-  </si>
-  <si>
-    <t>현대엘리베이터</t>
-  </si>
-  <si>
-    <t>024110</t>
-  </si>
-  <si>
-    <t>기업은행</t>
-  </si>
-  <si>
-    <t>029780</t>
-  </si>
-  <si>
-    <t>삼성카드</t>
-  </si>
-  <si>
-    <t>030000</t>
-  </si>
-  <si>
-    <t>제일기획</t>
-  </si>
-  <si>
-    <t>030200</t>
-  </si>
-  <si>
-    <t>KT</t>
-  </si>
-  <si>
-    <t>032640</t>
-  </si>
-  <si>
-    <t>LG유플러스</t>
-  </si>
-  <si>
-    <t>032830</t>
-  </si>
-  <si>
-    <t>삼성생명</t>
-  </si>
-  <si>
-    <t>033780</t>
-  </si>
-  <si>
-    <t>KT&amp;G</t>
-  </si>
-  <si>
-    <t>035250</t>
-  </si>
-  <si>
-    <t>강원랜드</t>
-  </si>
-  <si>
-    <t>036460</t>
-  </si>
-  <si>
-    <t>한국가스공사</t>
-  </si>
-  <si>
-    <t>038500</t>
-  </si>
-  <si>
-    <t>삼표시멘트</t>
-  </si>
-  <si>
-    <t>055550</t>
-  </si>
-  <si>
-    <t>신한지주</t>
-  </si>
-  <si>
-    <t>071050</t>
-  </si>
-  <si>
-    <t>한국금융지주</t>
-  </si>
-  <si>
-    <t>078930</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>086790</t>
-  </si>
-  <si>
-    <t>하나금융지주</t>
-  </si>
-  <si>
-    <t>105560</t>
-  </si>
-  <si>
-    <t>KB금융</t>
-  </si>
-  <si>
-    <t>138930</t>
-  </si>
-  <si>
-    <t>BNK금융지주</t>
-  </si>
-  <si>
-    <t>139130</t>
-  </si>
-  <si>
-    <t>iM금융지주</t>
-  </si>
-  <si>
-    <t>161390</t>
-  </si>
-  <si>
-    <t>한국타이어앤테크놀로</t>
-  </si>
-  <si>
-    <t>175330</t>
-  </si>
-  <si>
-    <t>JB금융지주</t>
-  </si>
-  <si>
-    <t>183190</t>
-  </si>
-  <si>
-    <t>아세아시멘트</t>
-  </si>
-  <si>
-    <t>192080</t>
-  </si>
-  <si>
-    <t>더블유게임즈</t>
-  </si>
-  <si>
-    <t>214320</t>
-  </si>
-  <si>
-    <t>이노션</t>
-  </si>
-  <si>
-    <t>300720</t>
-  </si>
-  <si>
-    <t>한일시멘트</t>
-  </si>
-  <si>
-    <t>316140</t>
-  </si>
-  <si>
-    <t>우리금융지주</t>
   </si>
 </sst>
 </file>
@@ -720,7 +720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24CE32F9-E0FD-4470-AB75-91C19A07D619}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3F1FE7-34C6-431A-A8BE-3EF5DFF5DC58}">
   <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -786,37 +786,37 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>25950</v>
+        <v>20200</v>
       </c>
       <c r="D2" s="3">
-        <v>3.39E-2</v>
+        <v>0.11360000000000001</v>
       </c>
       <c r="E2">
-        <v>8.2799999999999994</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="F2">
-        <v>8.9</v>
+        <v>3.02</v>
       </c>
       <c r="G2">
-        <v>5.8</v>
+        <v>6.13</v>
       </c>
       <c r="H2" s="4">
-        <v>48390.96</v>
+        <v>7055.63</v>
       </c>
       <c r="I2">
-        <v>3.85</v>
+        <v>0.54</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="L2">
-        <v>88.23</v>
+        <v>129.97999999999999</v>
       </c>
       <c r="M2">
-        <v>-9.58</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -827,37 +827,37 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>166600</v>
+        <v>71300</v>
       </c>
       <c r="D3" s="3">
-        <v>3.4799999999999998E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="E3">
-        <v>19.09</v>
+        <v>1.04</v>
       </c>
       <c r="F3">
-        <v>14.17</v>
+        <v>3.97</v>
       </c>
       <c r="G3">
-        <v>18.03</v>
+        <v>4.21</v>
       </c>
       <c r="H3" s="4">
-        <v>150938.41</v>
+        <v>53899.69</v>
       </c>
       <c r="I3">
-        <v>3.9</v>
+        <v>1.68</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L3">
-        <v>97.94</v>
+        <v>102.15</v>
       </c>
       <c r="M3">
-        <v>-8.61</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -868,37 +868,37 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>504000</v>
+        <v>43750</v>
       </c>
       <c r="D4" s="3">
-        <v>3.1699999999999999E-2</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="E4">
-        <v>13.09</v>
+        <v>7.12</v>
       </c>
       <c r="F4">
-        <v>13.88</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="G4">
-        <v>12.47</v>
+        <v>12.61</v>
       </c>
       <c r="H4" s="4">
-        <v>405451.96</v>
+        <v>72041.39</v>
       </c>
       <c r="I4">
-        <v>3.77</v>
+        <v>4.57</v>
       </c>
       <c r="J4">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K4">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="L4">
-        <v>94.65</v>
+        <v>99.88</v>
       </c>
       <c r="M4">
-        <v>-3.45</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -909,37 +909,37 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>42250</v>
+        <v>27650</v>
       </c>
       <c r="D5" s="3">
-        <v>2.8000000000000001E-2</v>
+        <v>-1.2500000000000001E-2</v>
       </c>
       <c r="E5">
-        <v>7.12</v>
+        <v>19.78</v>
       </c>
       <c r="F5">
-        <v>9.6199999999999992</v>
+        <v>13.82</v>
       </c>
       <c r="G5">
-        <v>12.61</v>
+        <v>23.29</v>
       </c>
       <c r="H5" s="4">
-        <v>72041.39</v>
+        <v>32624.26</v>
       </c>
       <c r="I5">
-        <v>4.7300000000000004</v>
+        <v>3.62</v>
       </c>
       <c r="J5">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K5">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L5">
-        <v>96.64</v>
+        <v>97.1</v>
       </c>
       <c r="M5">
-        <v>-2.2000000000000002</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -950,37 +950,37 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>81400</v>
+        <v>13710</v>
       </c>
       <c r="D6" s="3">
-        <v>5.4399999999999997E-2</v>
+        <v>1.11E-2</v>
       </c>
       <c r="E6">
-        <v>4.05</v>
+        <v>9.44</v>
       </c>
       <c r="F6">
-        <v>7.82</v>
+        <v>10.67</v>
       </c>
       <c r="G6">
-        <v>6.06</v>
+        <v>9.86</v>
       </c>
       <c r="H6" s="4">
-        <v>65679.45</v>
+        <v>19219.419999999998</v>
       </c>
       <c r="I6">
-        <v>1.84</v>
+        <v>3.76</v>
       </c>
       <c r="J6">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="K6">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="L6">
-        <v>99.39</v>
+        <v>101.99</v>
       </c>
       <c r="M6">
-        <v>2.13</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -991,37 +991,37 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>70200</v>
+        <v>31200</v>
       </c>
       <c r="D7" s="3">
-        <v>0.1341</v>
+        <v>-3.2000000000000002E-3</v>
       </c>
       <c r="E7">
-        <v>1.04</v>
+        <v>12.8</v>
       </c>
       <c r="F7">
-        <v>3.97</v>
+        <v>13.49</v>
       </c>
       <c r="G7">
-        <v>4.21</v>
+        <v>12.93</v>
       </c>
       <c r="H7" s="4">
-        <v>53899.69</v>
+        <v>31004.78</v>
       </c>
       <c r="I7">
-        <v>1.71</v>
+        <v>3.19</v>
       </c>
       <c r="J7">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K7">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L7">
-        <v>99.65</v>
+        <v>97.14</v>
       </c>
       <c r="M7">
-        <v>4.78</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -1032,37 +1032,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>20950</v>
+        <v>19550</v>
       </c>
       <c r="D8" s="3">
-        <v>2.4400000000000002E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="E8">
-        <v>6.94</v>
+        <v>10.48</v>
       </c>
       <c r="F8">
-        <v>6.38</v>
+        <v>7.97</v>
       </c>
       <c r="G8">
-        <v>6.21</v>
+        <v>10.17</v>
       </c>
       <c r="H8" s="4">
-        <v>39784.050000000003</v>
+        <v>25607.22</v>
       </c>
       <c r="I8">
-        <v>4.0599999999999996</v>
+        <v>6.01</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K8">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="L8">
-        <v>93.94</v>
+        <v>98.71</v>
       </c>
       <c r="M8">
-        <v>-4.5599999999999996</v>
+        <v>-2.4900000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1073,37 +1073,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>9410</v>
+        <v>178000</v>
       </c>
       <c r="D9" s="3">
-        <v>9.7000000000000003E-3</v>
+        <v>-2.8400000000000002E-2</v>
       </c>
       <c r="E9">
-        <v>2.84</v>
+        <v>18.96</v>
       </c>
       <c r="F9">
-        <v>4.16</v>
+        <v>19.43</v>
       </c>
       <c r="G9">
-        <v>8.36</v>
+        <v>18.8</v>
       </c>
       <c r="H9" s="4">
-        <v>20859.37</v>
+        <v>144109.65</v>
       </c>
       <c r="I9">
-        <v>2.34</v>
+        <v>3.82</v>
       </c>
       <c r="J9">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="K9">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="L9">
-        <v>95.67</v>
+        <v>95.95</v>
       </c>
       <c r="M9">
-        <v>-9.17</v>
+        <v>-2.79</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1114,37 +1114,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>40950</v>
+        <v>9510</v>
       </c>
       <c r="D10" s="3">
-        <v>5.1299999999999998E-2</v>
+        <v>-5.1999999999999998E-3</v>
       </c>
       <c r="E10">
-        <v>4.57</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="F10">
-        <v>7.42</v>
+        <v>3.26</v>
       </c>
       <c r="G10">
-        <v>4.55</v>
+        <v>5.34</v>
       </c>
       <c r="H10" s="4">
-        <v>42814.52</v>
+        <v>22736.17</v>
       </c>
       <c r="I10">
-        <v>2.93</v>
+        <v>3.68</v>
       </c>
       <c r="J10">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="K10">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="L10">
-        <v>101.18</v>
+        <v>95.27</v>
       </c>
       <c r="M10">
-        <v>-1.0900000000000001</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1155,37 +1155,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>95100</v>
+        <v>66300</v>
       </c>
       <c r="D11" s="3">
-        <v>1.06E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="E11">
-        <v>2.16</v>
+        <v>4.12</v>
       </c>
       <c r="F11">
-        <v>5.36</v>
+        <v>5.22</v>
       </c>
       <c r="G11">
-        <v>5.18</v>
+        <v>11.01</v>
       </c>
       <c r="H11" s="4">
-        <v>177736.27</v>
+        <v>151788</v>
       </c>
       <c r="I11">
-        <v>3.26</v>
+        <v>4.07</v>
       </c>
       <c r="J11">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="K11">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="L11">
-        <v>98.43</v>
+        <v>95.8</v>
       </c>
       <c r="M11">
-        <v>-7.22</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1196,25 +1196,25 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>13300</v>
+        <v>61500</v>
       </c>
       <c r="D12" s="3">
-        <v>3.5799999999999998E-2</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="E12">
-        <v>9.44</v>
+        <v>2.85</v>
       </c>
       <c r="F12">
-        <v>10.67</v>
+        <v>12.83</v>
       </c>
       <c r="G12">
-        <v>9.86</v>
+        <v>5.63</v>
       </c>
       <c r="H12" s="4">
-        <v>19219.419999999998</v>
+        <v>71073.47</v>
       </c>
       <c r="I12">
-        <v>3.87</v>
+        <v>3.25</v>
       </c>
       <c r="J12">
         <v>81</v>
@@ -1223,10 +1223,10 @@
         <v>81</v>
       </c>
       <c r="L12">
-        <v>99.59</v>
+        <v>98.4</v>
       </c>
       <c r="M12">
-        <v>-1.1200000000000001</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1237,37 +1237,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>400500</v>
+        <v>60700</v>
       </c>
       <c r="D13" s="3">
-        <v>3.3500000000000002E-2</v>
+        <v>2.0199999999999999E-2</v>
       </c>
       <c r="E13">
-        <v>6.17</v>
+        <v>7.45</v>
       </c>
       <c r="F13">
-        <v>6.83</v>
+        <v>7.45</v>
       </c>
       <c r="G13">
-        <v>6.2</v>
+        <v>7.69</v>
       </c>
       <c r="H13" s="4">
-        <v>466289.71</v>
+        <v>79986.48</v>
       </c>
       <c r="I13">
-        <v>1.25</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="J13">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="K13">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="L13">
-        <v>94.05</v>
+        <v>98.64</v>
       </c>
       <c r="M13">
-        <v>-4.42</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1278,37 +1278,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>9490</v>
+        <v>86800</v>
       </c>
       <c r="D14" s="3">
-        <v>2.3699999999999999E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E14">
-        <v>8.2100000000000009</v>
+        <v>4.05</v>
       </c>
       <c r="F14">
-        <v>3.26</v>
+        <v>7.82</v>
       </c>
       <c r="G14">
-        <v>5.34</v>
+        <v>6.06</v>
       </c>
       <c r="H14" s="4">
-        <v>22736.17</v>
+        <v>65679.45</v>
       </c>
       <c r="I14">
-        <v>3.69</v>
+        <v>1.73</v>
       </c>
       <c r="J14">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="K14">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L14">
-        <v>94.76</v>
+        <v>104.9</v>
       </c>
       <c r="M14">
-        <v>-1.1499999999999999</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1319,37 +1319,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>76600</v>
+        <v>18280</v>
       </c>
       <c r="D15" s="3">
-        <v>2.5399999999999999E-2</v>
+        <v>1.67E-2</v>
       </c>
       <c r="E15">
-        <v>15.14</v>
+        <v>12.08</v>
       </c>
       <c r="F15">
-        <v>14.47</v>
+        <v>8.58</v>
       </c>
       <c r="G15">
-        <v>11.28</v>
+        <v>8.39</v>
       </c>
       <c r="H15" s="4">
-        <v>82759.37</v>
+        <v>19234.22</v>
       </c>
       <c r="I15">
-        <v>4.3099999999999996</v>
+        <v>6.4</v>
       </c>
       <c r="J15">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="K15">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="L15">
-        <v>94.93</v>
+        <v>98.26</v>
       </c>
       <c r="M15">
-        <v>-2.0499999999999998</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1360,25 +1360,25 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>543500</v>
+        <v>76200</v>
       </c>
       <c r="D16" s="3">
-        <v>3.5200000000000002E-2</v>
+        <v>-2.18E-2</v>
       </c>
       <c r="E16">
-        <v>12.43</v>
+        <v>10.83</v>
       </c>
       <c r="F16">
-        <v>10.08</v>
+        <v>3.37</v>
       </c>
       <c r="G16">
-        <v>11.82</v>
+        <v>9.48</v>
       </c>
       <c r="H16" s="4">
-        <v>429918.88</v>
+        <v>54894.12</v>
       </c>
       <c r="I16">
-        <v>2.21</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="J16">
         <v>73</v>
@@ -1387,10 +1387,10 @@
         <v>73</v>
       </c>
       <c r="L16">
-        <v>102.2</v>
+        <v>97.48</v>
       </c>
       <c r="M16">
-        <v>-8.66</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1401,37 +1401,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>189600</v>
+        <v>155600</v>
       </c>
       <c r="D17" s="3">
-        <v>3.32E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="E17">
-        <v>18.96</v>
+        <v>12.66</v>
       </c>
       <c r="F17">
-        <v>19.43</v>
+        <v>11.88</v>
       </c>
       <c r="G17">
-        <v>18.8</v>
+        <v>11.14</v>
       </c>
       <c r="H17" s="4">
-        <v>144109.65</v>
+        <v>83639.03</v>
       </c>
       <c r="I17">
-        <v>3.59</v>
+        <v>3.47</v>
       </c>
       <c r="J17">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K17">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="L17">
-        <v>102.41</v>
+        <v>93.85</v>
       </c>
       <c r="M17">
-        <v>1.55</v>
+        <v>-4.5999999999999996</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1442,37 +1442,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>33500</v>
+        <v>238000</v>
       </c>
       <c r="D18" s="3">
-        <v>6.6900000000000001E-2</v>
+        <v>3.2500000000000001E-2</v>
       </c>
       <c r="E18">
-        <v>8.73</v>
+        <v>13.17</v>
       </c>
       <c r="F18">
-        <v>11.57</v>
+        <v>11.69</v>
       </c>
       <c r="G18">
-        <v>6.85</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H18" s="4">
-        <v>24348.21</v>
+        <v>207156.6</v>
       </c>
       <c r="I18">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="J18">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="K18">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="L18">
-        <v>102.9</v>
+        <v>102.87</v>
       </c>
       <c r="M18">
-        <v>0.6</v>
+        <v>-4.6100000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1483,37 +1483,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>372000</v>
+        <v>218500</v>
       </c>
       <c r="D19" s="3">
-        <v>3.3300000000000003E-2</v>
+        <v>-3.5299999999999998E-2</v>
       </c>
       <c r="E19">
-        <v>6.85</v>
+        <v>4.66</v>
       </c>
       <c r="F19">
-        <v>6.19</v>
+        <v>4.66</v>
       </c>
       <c r="G19">
-        <v>10.64</v>
+        <v>4.88</v>
       </c>
       <c r="H19" s="4">
-        <v>605494.72</v>
+        <v>324173.33</v>
       </c>
       <c r="I19">
-        <v>2.42</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="J19">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="K19">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="L19">
-        <v>95.57</v>
+        <v>101.62</v>
       </c>
       <c r="M19">
-        <v>-4.25</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1524,37 +1524,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>28450</v>
+        <v>12040</v>
       </c>
       <c r="D20" s="3">
-        <v>2.52E-2</v>
+        <v>-8.0000000000000004E-4</v>
       </c>
       <c r="E20">
-        <v>19.78</v>
+        <v>7.65</v>
       </c>
       <c r="F20">
-        <v>13.82</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>23.29</v>
+        <v>7.8</v>
       </c>
       <c r="H20" s="4">
-        <v>32624.26</v>
+        <v>30039.25</v>
       </c>
       <c r="I20">
-        <v>3.51</v>
+        <v>2.16</v>
       </c>
       <c r="J20">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="K20">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="L20">
-        <v>100.06</v>
+        <v>94.57</v>
       </c>
       <c r="M20">
-        <v>7.36</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1565,37 +1565,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>236500</v>
+        <v>91900</v>
       </c>
       <c r="D21" s="3">
-        <v>6.2899999999999998E-2</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="E21">
-        <v>13.17</v>
+        <v>8.11</v>
       </c>
       <c r="F21">
-        <v>11.69</v>
+        <v>10.44</v>
       </c>
       <c r="G21">
-        <v>18.010000000000002</v>
+        <v>8.66</v>
       </c>
       <c r="H21" s="4">
-        <v>207156.6</v>
+        <v>119742.76</v>
       </c>
       <c r="I21">
-        <v>2.2599999999999998</v>
+        <v>2.35</v>
       </c>
       <c r="J21">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K21">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="L21">
-        <v>102.77</v>
+        <v>95.09</v>
       </c>
       <c r="M21">
-        <v>-3.07</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1606,37 +1606,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>125800</v>
+        <v>20800</v>
       </c>
       <c r="D22" s="3">
-        <v>3.2800000000000003E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="E22">
-        <v>5.88</v>
+        <v>15.12</v>
       </c>
       <c r="F22">
-        <v>6.29</v>
+        <v>13.07</v>
       </c>
       <c r="G22">
-        <v>10.87</v>
+        <v>15.58</v>
       </c>
       <c r="H22" s="4">
-        <v>215382.39999999999</v>
+        <v>15310.06</v>
       </c>
       <c r="I22">
-        <v>1.75</v>
+        <v>5.91</v>
       </c>
       <c r="J22">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="K22">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="L22">
-        <v>91.27</v>
+        <v>97.12</v>
       </c>
       <c r="M22">
-        <v>-9.17</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1647,37 +1647,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>99800</v>
+        <v>376500</v>
       </c>
       <c r="D23" s="3">
-        <v>6.8500000000000005E-2</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="E23">
-        <v>12.89</v>
+        <v>6.85</v>
       </c>
       <c r="F23">
-        <v>13.94</v>
+        <v>6.19</v>
       </c>
       <c r="G23">
-        <v>9.44</v>
+        <v>10.64</v>
       </c>
       <c r="H23" s="4">
-        <v>87743.72</v>
+        <v>605494.72</v>
       </c>
       <c r="I23">
-        <v>3.51</v>
+        <v>2.39</v>
       </c>
       <c r="J23">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="K23">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="L23">
-        <v>99.47</v>
+        <v>96.9</v>
       </c>
       <c r="M23">
-        <v>-0.7</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1688,37 +1688,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>79200</v>
+        <v>50200</v>
       </c>
       <c r="D24" s="3">
-        <v>2.5899999999999999E-2</v>
+        <v>1.01E-2</v>
       </c>
       <c r="E24">
-        <v>10.83</v>
+        <v>18.690000000000001</v>
       </c>
       <c r="F24">
-        <v>3.37</v>
+        <v>11.56</v>
       </c>
       <c r="G24">
-        <v>9.48</v>
+        <v>6.83</v>
       </c>
       <c r="H24" s="4">
-        <v>54894.12</v>
+        <v>57293.3</v>
       </c>
       <c r="I24">
-        <v>4.47</v>
+        <v>2.39</v>
       </c>
       <c r="J24">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="K24">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="L24">
-        <v>101.69</v>
+        <v>94.66</v>
       </c>
       <c r="M24">
-        <v>1.28</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1729,37 +1729,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>89800</v>
+        <v>77100</v>
       </c>
       <c r="D25" s="3">
-        <v>1.01E-2</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="E25">
-        <v>14.42</v>
+        <v>15.14</v>
       </c>
       <c r="F25">
-        <v>24.2</v>
+        <v>14.47</v>
       </c>
       <c r="G25">
-        <v>15.82</v>
+        <v>11.28</v>
       </c>
       <c r="H25" s="4">
-        <v>36460.550000000003</v>
+        <v>82759.37</v>
       </c>
       <c r="I25">
-        <v>6.12</v>
+        <v>4.28</v>
       </c>
       <c r="J25">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="K25">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L25">
-        <v>90.84</v>
+        <v>95.64</v>
       </c>
       <c r="M25">
-        <v>-5.07</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1770,37 +1770,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>23950</v>
+        <v>149200</v>
       </c>
       <c r="D26" s="3">
-        <v>3.6799999999999999E-2</v>
+        <v>-1.3899999999999999E-2</v>
       </c>
       <c r="E26">
-        <v>8.06</v>
+        <v>8.86</v>
       </c>
       <c r="F26">
-        <v>8.64</v>
+        <v>11.63</v>
       </c>
       <c r="G26">
-        <v>8.77</v>
+        <v>8.51</v>
       </c>
       <c r="H26" s="4">
-        <v>44443.18</v>
+        <v>160038.65</v>
       </c>
       <c r="I26">
-        <v>4.45</v>
+        <v>2.13</v>
       </c>
       <c r="J26">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K26">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L26">
-        <v>95.75</v>
+        <v>94.77</v>
       </c>
       <c r="M26">
-        <v>-4.58</v>
+        <v>-6.16</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1811,37 +1811,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>60100</v>
+        <v>17050</v>
       </c>
       <c r="D27" s="3">
-        <v>2.2100000000000002E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="E27">
-        <v>7.45</v>
+        <v>11.13</v>
       </c>
       <c r="F27">
-        <v>7.45</v>
+        <v>5.01</v>
       </c>
       <c r="G27">
-        <v>7.69</v>
+        <v>9.31</v>
       </c>
       <c r="H27" s="4">
-        <v>79986.48</v>
+        <v>24921.41</v>
       </c>
       <c r="I27">
-        <v>4.66</v>
+        <v>5.87</v>
       </c>
       <c r="J27">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="K27">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="L27">
-        <v>97.76</v>
+        <v>97.06</v>
       </c>
       <c r="M27">
-        <v>-2.91</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1852,37 +1852,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>20750</v>
+        <v>18650</v>
       </c>
       <c r="D28" s="3">
-        <v>7.3000000000000001E-3</v>
+        <v>-2.1000000000000001E-2</v>
       </c>
       <c r="E28">
-        <v>15.12</v>
+        <v>6.96</v>
       </c>
       <c r="F28">
-        <v>13.07</v>
+        <v>9.58</v>
       </c>
       <c r="G28">
-        <v>15.58</v>
+        <v>7.18</v>
       </c>
       <c r="H28" s="4">
-        <v>15310.06</v>
+        <v>34223.949999999997</v>
       </c>
       <c r="I28">
-        <v>5.93</v>
+        <v>3.49</v>
       </c>
       <c r="J28">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="K28">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="L28">
-        <v>96.84</v>
+        <v>92.65</v>
       </c>
       <c r="M28">
-        <v>-2.81</v>
+        <v>-6.42</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1893,37 +1893,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>61100</v>
+        <v>490000</v>
       </c>
       <c r="D29" s="3">
-        <v>4.8999999999999998E-3</v>
+        <v>-1.5100000000000001E-2</v>
       </c>
       <c r="E29">
-        <v>2.85</v>
+        <v>13.09</v>
       </c>
       <c r="F29">
-        <v>12.83</v>
+        <v>13.88</v>
       </c>
       <c r="G29">
-        <v>5.63</v>
+        <v>12.47</v>
       </c>
       <c r="H29" s="4">
-        <v>71073.47</v>
+        <v>405451.96</v>
       </c>
       <c r="I29">
-        <v>3.27</v>
+        <v>3.88</v>
       </c>
       <c r="J29">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="K29">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="L29">
-        <v>98.07</v>
+        <v>92.33</v>
       </c>
       <c r="M29">
-        <v>-3.02</v>
+        <v>-7.55</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1934,37 +1934,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>15220</v>
+        <v>112500</v>
       </c>
       <c r="D30" s="3">
-        <v>3.1199999999999999E-2</v>
+        <v>-7.9000000000000008E-3</v>
       </c>
       <c r="E30">
-        <v>4.4000000000000004</v>
+        <v>9.11</v>
       </c>
       <c r="F30">
-        <v>6.71</v>
+        <v>10.57</v>
       </c>
       <c r="G30">
-        <v>6.75</v>
+        <v>9.4</v>
       </c>
       <c r="H30" s="4">
-        <v>20394.86</v>
+        <v>159337.74</v>
       </c>
       <c r="I30">
-        <v>4.2699999999999996</v>
+        <v>3.2</v>
       </c>
       <c r="J30">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K30">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="L30">
-        <v>93.7</v>
+        <v>93.72</v>
       </c>
       <c r="M30">
-        <v>-5.52</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1975,37 +1975,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>221500</v>
+        <v>15260</v>
       </c>
       <c r="D31" s="3">
-        <v>4.7300000000000002E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="E31">
-        <v>4.66</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F31">
-        <v>4.66</v>
+        <v>6.71</v>
       </c>
       <c r="G31">
-        <v>4.88</v>
+        <v>6.75</v>
       </c>
       <c r="H31" s="4">
-        <v>324173.33</v>
+        <v>20394.86</v>
       </c>
       <c r="I31">
-        <v>2.39</v>
+        <v>4.26</v>
       </c>
       <c r="J31">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="K31">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="L31">
-        <v>103.97</v>
+        <v>94.07</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -2016,37 +2016,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>156800</v>
+        <v>20800</v>
       </c>
       <c r="D32" s="3">
-        <v>1.4200000000000001E-2</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="E32">
-        <v>12.66</v>
+        <v>6.94</v>
       </c>
       <c r="F32">
-        <v>11.88</v>
+        <v>6.38</v>
       </c>
       <c r="G32">
-        <v>11.14</v>
+        <v>6.21</v>
       </c>
       <c r="H32" s="4">
-        <v>83639.03</v>
+        <v>39784.050000000003</v>
       </c>
       <c r="I32">
-        <v>3.44</v>
+        <v>4.09</v>
       </c>
       <c r="J32">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="K32">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="L32">
-        <v>94.29</v>
+        <v>93.62</v>
       </c>
       <c r="M32">
-        <v>-3.39</v>
+        <v>-7.96</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2057,37 +2057,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>18130</v>
+        <v>32550</v>
       </c>
       <c r="D33" s="3">
-        <v>1.5699999999999999E-2</v>
+        <v>-2.2499999999999999E-2</v>
       </c>
       <c r="E33">
-        <v>12.08</v>
+        <v>8.73</v>
       </c>
       <c r="F33">
-        <v>8.58</v>
+        <v>11.57</v>
       </c>
       <c r="G33">
-        <v>8.39</v>
+        <v>6.85</v>
       </c>
       <c r="H33" s="4">
-        <v>19234.22</v>
+        <v>24348.21</v>
       </c>
       <c r="I33">
-        <v>6.45</v>
+        <v>2.92</v>
       </c>
       <c r="J33">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="K33">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="L33">
-        <v>97.57</v>
+        <v>99.01</v>
       </c>
       <c r="M33">
-        <v>-3.26</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2098,37 +2098,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>36550</v>
+        <v>16860</v>
       </c>
       <c r="D34" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>-2.4299999999999999E-2</v>
       </c>
       <c r="E34">
-        <v>11.21</v>
+        <v>3.6</v>
       </c>
       <c r="F34">
-        <v>6.55</v>
+        <v>9.42</v>
       </c>
       <c r="G34">
-        <v>6.4</v>
+        <v>5.91</v>
       </c>
       <c r="H34" s="4">
-        <v>122131.86</v>
+        <v>38541.279999999999</v>
       </c>
       <c r="I34">
-        <v>3.98</v>
+        <v>2.97</v>
       </c>
       <c r="J34">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="K34">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="L34">
-        <v>89.4</v>
+        <v>89.89</v>
       </c>
       <c r="M34">
-        <v>-9.98</v>
+        <v>-8.32</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2139,37 +2139,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>16980</v>
+        <v>23450</v>
       </c>
       <c r="D35" s="3">
-        <v>0.21629999999999999</v>
+        <v>-6.4000000000000003E-3</v>
       </c>
       <c r="E35">
-        <v>9.0399999999999991</v>
+        <v>8.06</v>
       </c>
       <c r="F35">
-        <v>3.02</v>
+        <v>8.64</v>
       </c>
       <c r="G35">
-        <v>6.13</v>
+        <v>8.77</v>
       </c>
       <c r="H35" s="4">
-        <v>7055.63</v>
+        <v>44443.18</v>
       </c>
       <c r="I35">
-        <v>0.65</v>
+        <v>4.54</v>
       </c>
       <c r="J35">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K35">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L35">
-        <v>109.86</v>
+        <v>93.73</v>
       </c>
       <c r="M35">
-        <v>-0.12</v>
+        <v>-8.93</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2180,37 +2180,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>92600</v>
+        <v>32500</v>
       </c>
       <c r="D36" s="3">
-        <v>3.8100000000000002E-2</v>
+        <v>-2.5499999999999998E-2</v>
       </c>
       <c r="E36">
-        <v>8.11</v>
+        <v>9.39</v>
       </c>
       <c r="F36">
-        <v>10.44</v>
+        <v>10.74</v>
       </c>
       <c r="G36">
-        <v>8.66</v>
+        <v>9.73</v>
       </c>
       <c r="H36" s="4">
-        <v>119742.76</v>
+        <v>48211.77</v>
       </c>
       <c r="I36">
-        <v>2.33</v>
+        <v>3.69</v>
       </c>
       <c r="J36">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K36">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="L36">
-        <v>95.66</v>
+        <v>90.03</v>
       </c>
       <c r="M36">
-        <v>-4.24</v>
+        <v>-9.7200000000000006</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2221,37 +2221,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>236000</v>
+        <v>96000</v>
       </c>
       <c r="D37" s="3">
-        <v>7.2700000000000001E-2</v>
+        <v>-1.84E-2</v>
       </c>
       <c r="E37">
-        <v>11.54</v>
+        <v>12.89</v>
       </c>
       <c r="F37">
-        <v>20.98</v>
+        <v>13.94</v>
       </c>
       <c r="G37">
-        <v>9.6</v>
+        <v>9.44</v>
       </c>
       <c r="H37" s="4">
-        <v>189057.03</v>
+        <v>87743.72</v>
       </c>
       <c r="I37">
-        <v>1.69</v>
+        <v>3.65</v>
       </c>
       <c r="J37">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K37">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L37">
-        <v>96.42</v>
+        <v>95.43</v>
       </c>
       <c r="M37">
-        <v>-1.87</v>
+        <v>-10.11</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2262,37 +2262,37 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>66600</v>
+        <v>88100</v>
       </c>
       <c r="D38" s="3">
-        <v>4.0599999999999997E-2</v>
+        <v>-3.3999999999999998E-3</v>
       </c>
       <c r="E38">
-        <v>4.12</v>
+        <v>14.42</v>
       </c>
       <c r="F38">
-        <v>5.22</v>
+        <v>24.2</v>
       </c>
       <c r="G38">
-        <v>11.01</v>
+        <v>15.82</v>
       </c>
       <c r="H38" s="4">
-        <v>151788</v>
+        <v>36460.550000000003</v>
       </c>
       <c r="I38">
-        <v>4.05</v>
+        <v>6.24</v>
       </c>
       <c r="J38">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K38">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L38">
-        <v>96.04</v>
+        <v>89.82</v>
       </c>
       <c r="M38">
-        <v>-5.53</v>
+        <v>-10.74</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2303,37 +2303,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>115200</v>
+        <v>39900</v>
       </c>
       <c r="D39" s="3">
-        <v>4.82E-2</v>
+        <v>-1.6E-2</v>
       </c>
       <c r="E39">
-        <v>9.11</v>
+        <v>4.57</v>
       </c>
       <c r="F39">
-        <v>10.57</v>
+        <v>7.42</v>
       </c>
       <c r="G39">
-        <v>9.4</v>
+        <v>4.55</v>
       </c>
       <c r="H39" s="4">
-        <v>159337.74</v>
+        <v>42814.52</v>
       </c>
       <c r="I39">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="J39">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="K39">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="L39">
-        <v>95.82</v>
+        <v>97.44</v>
       </c>
       <c r="M39">
-        <v>-4.08</v>
+        <v>-11.04</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2344,37 +2344,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>154600</v>
+        <v>227000</v>
       </c>
       <c r="D40" s="3">
-        <v>4.8800000000000003E-2</v>
+        <v>-1.09E-2</v>
       </c>
       <c r="E40">
-        <v>8.86</v>
+        <v>11.54</v>
       </c>
       <c r="F40">
-        <v>11.63</v>
+        <v>20.98</v>
       </c>
       <c r="G40">
-        <v>8.51</v>
+        <v>9.6</v>
       </c>
       <c r="H40" s="4">
-        <v>160038.65</v>
+        <v>189057.03</v>
       </c>
       <c r="I40">
-        <v>2.0499999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="J40">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="K40">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="L40">
-        <v>98.1</v>
+        <v>92.46</v>
       </c>
       <c r="M40">
-        <v>0.72</v>
+        <v>-12.19</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2385,37 +2385,37 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>19150</v>
+        <v>36100</v>
       </c>
       <c r="D41" s="3">
-        <v>4.4699999999999997E-2</v>
+        <v>-1.4E-3</v>
       </c>
       <c r="E41">
-        <v>6.96</v>
+        <v>11.21</v>
       </c>
       <c r="F41">
-        <v>9.58</v>
+        <v>6.55</v>
       </c>
       <c r="G41">
-        <v>7.18</v>
+        <v>6.4</v>
       </c>
       <c r="H41" s="4">
-        <v>34223.949999999997</v>
+        <v>122131.86</v>
       </c>
       <c r="I41">
-        <v>3.39</v>
+        <v>4.03</v>
       </c>
       <c r="J41">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="K41">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="L41">
-        <v>95.15</v>
+        <v>88.85</v>
       </c>
       <c r="M41">
-        <v>-2.69</v>
+        <v>-12.38</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2426,37 +2426,37 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>17500</v>
+        <v>374000</v>
       </c>
       <c r="D42" s="3">
-        <v>2.2800000000000001E-2</v>
+        <v>-5.0799999999999998E-2</v>
       </c>
       <c r="E42">
-        <v>3.6</v>
+        <v>6.17</v>
       </c>
       <c r="F42">
-        <v>9.42</v>
+        <v>6.83</v>
       </c>
       <c r="G42">
-        <v>5.91</v>
+        <v>6.2</v>
       </c>
       <c r="H42" s="4">
-        <v>38541.279999999999</v>
+        <v>466289.71</v>
       </c>
       <c r="I42">
-        <v>2.86</v>
+        <v>1.34</v>
       </c>
       <c r="J42">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="K42">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="L42">
-        <v>93.09</v>
+        <v>88.37</v>
       </c>
       <c r="M42">
-        <v>-3.31</v>
+        <v>-13.02</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2467,37 +2467,37 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>60200</v>
+        <v>9290</v>
       </c>
       <c r="D43" s="3">
-        <v>1.8599999999999998E-2</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="E43">
-        <v>10.79</v>
+        <v>2.84</v>
       </c>
       <c r="F43">
-        <v>10.55</v>
+        <v>4.16</v>
       </c>
       <c r="G43">
-        <v>8.93</v>
+        <v>8.36</v>
       </c>
       <c r="H43" s="4">
-        <v>92723.77</v>
+        <v>20859.37</v>
       </c>
       <c r="I43">
-        <v>3.32</v>
+        <v>2.37</v>
       </c>
       <c r="J43">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="K43">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="L43">
-        <v>87.68</v>
+        <v>94.09</v>
       </c>
       <c r="M43">
-        <v>-9.8800000000000008</v>
+        <v>-13.42</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
@@ -2508,37 +2508,37 @@
         <v>96</v>
       </c>
       <c r="C44" s="2">
-        <v>31750</v>
+        <v>92800</v>
       </c>
       <c r="D44" s="3">
-        <v>3.7600000000000001E-2</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="E44">
-        <v>12.8</v>
+        <v>2.16</v>
       </c>
       <c r="F44">
-        <v>13.49</v>
+        <v>5.36</v>
       </c>
       <c r="G44">
-        <v>12.93</v>
+        <v>5.18</v>
       </c>
       <c r="H44" s="4">
-        <v>31004.78</v>
+        <v>177736.27</v>
       </c>
       <c r="I44">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="J44">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="K44">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L44">
-        <v>99.21</v>
+        <v>95.99</v>
       </c>
       <c r="M44">
-        <v>1.93</v>
+        <v>-13.83</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
@@ -2549,37 +2549,37 @@
         <v>98</v>
       </c>
       <c r="C45" s="2">
-        <v>12070</v>
+        <v>25850</v>
       </c>
       <c r="D45" s="3">
-        <v>1.17E-2</v>
+        <v>1.37E-2</v>
       </c>
       <c r="E45">
-        <v>7.65</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>8.9</v>
       </c>
       <c r="G45">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="H45" s="4">
-        <v>30039.25</v>
+        <v>48390.96</v>
       </c>
       <c r="I45">
-        <v>2.15</v>
+        <v>3.87</v>
       </c>
       <c r="J45">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="K45">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="L45">
-        <v>94.49</v>
+        <v>88.1</v>
       </c>
       <c r="M45">
-        <v>-2.11</v>
+        <v>-17.41</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
@@ -2590,37 +2590,37 @@
         <v>100</v>
       </c>
       <c r="C46" s="2">
-        <v>50100</v>
+        <v>167000</v>
       </c>
       <c r="D46" s="3">
-        <v>1.83E-2</v>
+        <v>3.09E-2</v>
       </c>
       <c r="E46">
-        <v>18.690000000000001</v>
+        <v>19.09</v>
       </c>
       <c r="F46">
-        <v>11.56</v>
+        <v>14.17</v>
       </c>
       <c r="G46">
-        <v>6.83</v>
+        <v>18.03</v>
       </c>
       <c r="H46" s="4">
-        <v>57293.3</v>
+        <v>150938.41</v>
       </c>
       <c r="I46">
-        <v>2.4</v>
+        <v>3.89</v>
       </c>
       <c r="J46">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="K46">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="L46">
-        <v>93.96</v>
+        <v>97.87</v>
       </c>
       <c r="M46">
-        <v>-3.47</v>
+        <v>-18.73</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
@@ -2631,37 +2631,37 @@
         <v>102</v>
       </c>
       <c r="C47" s="2">
-        <v>19590</v>
+        <v>57600</v>
       </c>
       <c r="D47" s="3">
-        <v>1.4E-2</v>
+        <v>-2.3699999999999999E-2</v>
       </c>
       <c r="E47">
-        <v>10.48</v>
+        <v>10.79</v>
       </c>
       <c r="F47">
-        <v>7.97</v>
+        <v>10.55</v>
       </c>
       <c r="G47">
-        <v>10.17</v>
+        <v>8.93</v>
       </c>
       <c r="H47" s="4">
-        <v>25607.22</v>
+        <v>92723.77</v>
       </c>
       <c r="I47">
-        <v>6</v>
+        <v>3.47</v>
       </c>
       <c r="J47">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="K47">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="L47">
-        <v>98.89</v>
+        <v>84.56</v>
       </c>
       <c r="M47">
-        <v>-1.1100000000000001</v>
+        <v>-20.99</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
@@ -2672,37 +2672,37 @@
         <v>104</v>
       </c>
       <c r="C48" s="2">
-        <v>16850</v>
+        <v>120000</v>
       </c>
       <c r="D48" s="3">
-        <v>3.56E-2</v>
+        <v>-4.2299999999999997E-2</v>
       </c>
       <c r="E48">
-        <v>11.13</v>
+        <v>5.88</v>
       </c>
       <c r="F48">
-        <v>5.01</v>
+        <v>6.29</v>
       </c>
       <c r="G48">
-        <v>9.31</v>
+        <v>10.87</v>
       </c>
       <c r="H48" s="4">
-        <v>24921.41</v>
+        <v>215382.39999999999</v>
       </c>
       <c r="I48">
-        <v>5.93</v>
+        <v>1.83</v>
       </c>
       <c r="J48">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="K48">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="L48">
-        <v>95.74</v>
+        <v>87.56</v>
       </c>
       <c r="M48">
-        <v>-3.77</v>
+        <v>-21.77</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.4">
@@ -2713,37 +2713,37 @@
         <v>106</v>
       </c>
       <c r="C49" s="2">
-        <v>33650</v>
+        <v>521000</v>
       </c>
       <c r="D49" s="3">
-        <v>4.8300000000000003E-2</v>
+        <v>-1.7000000000000001E-2</v>
       </c>
       <c r="E49">
-        <v>9.39</v>
+        <v>12.43</v>
       </c>
       <c r="F49">
-        <v>10.74</v>
+        <v>10.08</v>
       </c>
       <c r="G49">
-        <v>9.73</v>
+        <v>11.82</v>
       </c>
       <c r="H49" s="4">
-        <v>48211.77</v>
+        <v>429918.88</v>
       </c>
       <c r="I49">
-        <v>3.57</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J49">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="K49">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L49">
-        <v>93.19</v>
+        <v>97.6</v>
       </c>
       <c r="M49">
-        <v>-4.67</v>
+        <v>-22.7</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09702678-E96D-485A-90E8-C12FD302C229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D915FBE-EECE-4D70-B665-5AA2D8F19747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{192E0C0B-58FF-4559-905F-66C1C805FB95}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{483BA26C-6031-4CD8-9BD9-1735F0EE164A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
   <si>
     <t>종목코드</t>
   </si>
@@ -60,10 +60,34 @@
     <t>해당등락률</t>
   </si>
   <si>
-    <t>038500</t>
-  </si>
-  <si>
-    <t>삼표시멘트</t>
+    <t>000240</t>
+  </si>
+  <si>
+    <t>한국앤컴퍼니</t>
+  </si>
+  <si>
+    <t>000270</t>
+  </si>
+  <si>
+    <t>기아</t>
+  </si>
+  <si>
+    <t>000810</t>
+  </si>
+  <si>
+    <t>삼성화재</t>
+  </si>
+  <si>
+    <t>001120</t>
+  </si>
+  <si>
+    <t>LX인터내셔널</t>
+  </si>
+  <si>
+    <t>001270</t>
+  </si>
+  <si>
+    <t>부국증권</t>
   </si>
   <si>
     <t>001430</t>
@@ -72,10 +96,76 @@
     <t>세아베스틸지주</t>
   </si>
   <si>
-    <t>001120</t>
-  </si>
-  <si>
-    <t>LX인터내셔널</t>
+    <t>001680</t>
+  </si>
+  <si>
+    <t>대상</t>
+  </si>
+  <si>
+    <t>002310</t>
+  </si>
+  <si>
+    <t>아세아제지</t>
+  </si>
+  <si>
+    <t>003540</t>
+  </si>
+  <si>
+    <t>대신증권</t>
+  </si>
+  <si>
+    <t>003550</t>
+  </si>
+  <si>
+    <t>LG</t>
+  </si>
+  <si>
+    <t>003690</t>
+  </si>
+  <si>
+    <t>코리안리</t>
+  </si>
+  <si>
+    <t>004370</t>
+  </si>
+  <si>
+    <t>농심</t>
+  </si>
+  <si>
+    <t>004980</t>
+  </si>
+  <si>
+    <t>성신양회</t>
+  </si>
+  <si>
+    <t>005180</t>
+  </si>
+  <si>
+    <t>빙그레</t>
+  </si>
+  <si>
+    <t>005380</t>
+  </si>
+  <si>
+    <t>현대차</t>
+  </si>
+  <si>
+    <t>005830</t>
+  </si>
+  <si>
+    <t>DB손해보험</t>
+  </si>
+  <si>
+    <t>005940</t>
+  </si>
+  <si>
+    <t>NH투자증권</t>
+  </si>
+  <si>
+    <t>007310</t>
+  </si>
+  <si>
+    <t>오뚜기</t>
   </si>
   <si>
     <t>007340</t>
@@ -84,10 +174,136 @@
     <t>DN오토모티브</t>
   </si>
   <si>
-    <t>003690</t>
-  </si>
-  <si>
-    <t>코리안리</t>
+    <t>009970</t>
+  </si>
+  <si>
+    <t>영원무역홀딩스</t>
+  </si>
+  <si>
+    <t>011780</t>
+  </si>
+  <si>
+    <t>금호석유화학</t>
+  </si>
+  <si>
+    <t>016360</t>
+  </si>
+  <si>
+    <t>삼성증권</t>
+  </si>
+  <si>
+    <t>017670</t>
+  </si>
+  <si>
+    <t>SK텔레콤</t>
+  </si>
+  <si>
+    <t>017800</t>
+  </si>
+  <si>
+    <t>현대엘리베이터</t>
+  </si>
+  <si>
+    <t>024110</t>
+  </si>
+  <si>
+    <t>기업은행</t>
+  </si>
+  <si>
+    <t>029780</t>
+  </si>
+  <si>
+    <t>삼성카드</t>
+  </si>
+  <si>
+    <t>030000</t>
+  </si>
+  <si>
+    <t>제일기획</t>
+  </si>
+  <si>
+    <t>030200</t>
+  </si>
+  <si>
+    <t>KT</t>
+  </si>
+  <si>
+    <t>032640</t>
+  </si>
+  <si>
+    <t>LG유플러스</t>
+  </si>
+  <si>
+    <t>032830</t>
+  </si>
+  <si>
+    <t>삼성생명</t>
+  </si>
+  <si>
+    <t>033780</t>
+  </si>
+  <si>
+    <t>KT&amp;G</t>
+  </si>
+  <si>
+    <t>035250</t>
+  </si>
+  <si>
+    <t>강원랜드</t>
+  </si>
+  <si>
+    <t>036460</t>
+  </si>
+  <si>
+    <t>한국가스공사</t>
+  </si>
+  <si>
+    <t>055550</t>
+  </si>
+  <si>
+    <t>신한지주</t>
+  </si>
+  <si>
+    <t>071050</t>
+  </si>
+  <si>
+    <t>한국금융지주</t>
+  </si>
+  <si>
+    <t>078930</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>086790</t>
+  </si>
+  <si>
+    <t>하나금융지주</t>
+  </si>
+  <si>
+    <t>105560</t>
+  </si>
+  <si>
+    <t>KB금융</t>
+  </si>
+  <si>
+    <t>138930</t>
+  </si>
+  <si>
+    <t>BNK금융지주</t>
+  </si>
+  <si>
+    <t>139130</t>
+  </si>
+  <si>
+    <t>iM금융지주</t>
+  </si>
+  <si>
+    <t>161390</t>
+  </si>
+  <si>
+    <t>한국타이어앤테크놀로</t>
   </si>
   <si>
     <t>175330</t>
@@ -96,256 +312,34 @@
     <t>JB금융지주</t>
   </si>
   <si>
+    <t>183190</t>
+  </si>
+  <si>
+    <t>아세아시멘트</t>
+  </si>
+  <si>
+    <t>192080</t>
+  </si>
+  <si>
+    <t>더블유게임즈</t>
+  </si>
+  <si>
     <t>214320</t>
   </si>
   <si>
     <t>이노션</t>
   </si>
   <si>
-    <t>005830</t>
-  </si>
-  <si>
-    <t>DB손해보험</t>
-  </si>
-  <si>
-    <t>004980</t>
-  </si>
-  <si>
-    <t>성신양회</t>
-  </si>
-  <si>
-    <t>078930</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>030200</t>
-  </si>
-  <si>
-    <t>KT</t>
-  </si>
-  <si>
-    <t>029780</t>
-  </si>
-  <si>
-    <t>삼성카드</t>
-  </si>
-  <si>
-    <t>001270</t>
-  </si>
-  <si>
-    <t>부국증권</t>
-  </si>
-  <si>
-    <t>035250</t>
-  </si>
-  <si>
-    <t>강원랜드</t>
-  </si>
-  <si>
-    <t>017670</t>
-  </si>
-  <si>
-    <t>SK텔레콤</t>
-  </si>
-  <si>
-    <t>033780</t>
-  </si>
-  <si>
-    <t>KT&amp;G</t>
-  </si>
-  <si>
-    <t>009970</t>
-  </si>
-  <si>
-    <t>영원무역홀딩스</t>
-  </si>
-  <si>
-    <t>032830</t>
-  </si>
-  <si>
-    <t>삼성생명</t>
-  </si>
-  <si>
-    <t>183190</t>
-  </si>
-  <si>
-    <t>아세아시멘트</t>
-  </si>
-  <si>
-    <t>055550</t>
-  </si>
-  <si>
-    <t>신한지주</t>
-  </si>
-  <si>
-    <t>030000</t>
-  </si>
-  <si>
-    <t>제일기획</t>
-  </si>
-  <si>
-    <t>007310</t>
-  </si>
-  <si>
-    <t>오뚜기</t>
-  </si>
-  <si>
-    <t>192080</t>
-  </si>
-  <si>
-    <t>더블유게임즈</t>
-  </si>
-  <si>
-    <t>005180</t>
-  </si>
-  <si>
-    <t>빙그레</t>
-  </si>
-  <si>
-    <t>105560</t>
-  </si>
-  <si>
-    <t>KB금융</t>
-  </si>
-  <si>
     <t>300720</t>
   </si>
   <si>
     <t>한일시멘트</t>
   </si>
   <si>
-    <t>138930</t>
-  </si>
-  <si>
-    <t>BNK금융지주</t>
-  </si>
-  <si>
-    <t>000810</t>
-  </si>
-  <si>
-    <t>삼성화재</t>
-  </si>
-  <si>
-    <t>086790</t>
-  </si>
-  <si>
-    <t>하나금융지주</t>
-  </si>
-  <si>
-    <t>032640</t>
-  </si>
-  <si>
-    <t>LG유플러스</t>
-  </si>
-  <si>
-    <t>001680</t>
-  </si>
-  <si>
-    <t>대상</t>
-  </si>
-  <si>
-    <t>005940</t>
-  </si>
-  <si>
-    <t>NH투자증권</t>
-  </si>
-  <si>
-    <t>139130</t>
-  </si>
-  <si>
-    <t>iM금융지주</t>
-  </si>
-  <si>
-    <t>024110</t>
-  </si>
-  <si>
-    <t>기업은행</t>
-  </si>
-  <si>
     <t>316140</t>
   </si>
   <si>
     <t>우리금융지주</t>
-  </si>
-  <si>
-    <t>016360</t>
-  </si>
-  <si>
-    <t>삼성증권</t>
-  </si>
-  <si>
-    <t>017800</t>
-  </si>
-  <si>
-    <t>현대엘리베이터</t>
-  </si>
-  <si>
-    <t>003540</t>
-  </si>
-  <si>
-    <t>대신증권</t>
-  </si>
-  <si>
-    <t>071050</t>
-  </si>
-  <si>
-    <t>한국금융지주</t>
-  </si>
-  <si>
-    <t>036460</t>
-  </si>
-  <si>
-    <t>한국가스공사</t>
-  </si>
-  <si>
-    <t>004370</t>
-  </si>
-  <si>
-    <t>농심</t>
-  </si>
-  <si>
-    <t>002310</t>
-  </si>
-  <si>
-    <t>아세아제지</t>
-  </si>
-  <si>
-    <t>003550</t>
-  </si>
-  <si>
-    <t>LG</t>
-  </si>
-  <si>
-    <t>000240</t>
-  </si>
-  <si>
-    <t>한국앤컴퍼니</t>
-  </si>
-  <si>
-    <t>000270</t>
-  </si>
-  <si>
-    <t>기아</t>
-  </si>
-  <si>
-    <t>161390</t>
-  </si>
-  <si>
-    <t>한국타이어앤테크놀로</t>
-  </si>
-  <si>
-    <t>011780</t>
-  </si>
-  <si>
-    <t>금호석유화학</t>
-  </si>
-  <si>
-    <t>005380</t>
-  </si>
-  <si>
-    <t>현대차</t>
   </si>
 </sst>
 </file>
@@ -720,14 +714,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3F1FE7-34C6-431A-A8BE-3EF5DFF5DC58}">
-  <dimension ref="A1:M49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBFF365F-02C7-405D-A82B-25D49A7A0AEA}">
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -786,37 +780,37 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>20200</v>
+        <v>25250</v>
       </c>
       <c r="D2" s="3">
-        <v>0.11360000000000001</v>
+        <v>-2.3199999999999998E-2</v>
       </c>
       <c r="E2">
-        <v>9.0399999999999991</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="F2">
-        <v>3.02</v>
+        <v>8.9</v>
       </c>
       <c r="G2">
-        <v>6.13</v>
+        <v>5.8</v>
       </c>
       <c r="H2" s="4">
-        <v>7055.63</v>
+        <v>48390.96</v>
       </c>
       <c r="I2">
-        <v>0.54</v>
+        <v>3.96</v>
       </c>
       <c r="J2">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="K2">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="L2">
-        <v>129.97999999999999</v>
+        <v>86.45</v>
       </c>
       <c r="M2">
-        <v>16.43</v>
+        <v>-12.02</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -827,37 +821,37 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>71300</v>
+        <v>164300</v>
       </c>
       <c r="D3" s="3">
-        <v>2.3E-2</v>
+        <v>-1.6199999999999999E-2</v>
       </c>
       <c r="E3">
-        <v>1.04</v>
+        <v>19.09</v>
       </c>
       <c r="F3">
-        <v>3.97</v>
+        <v>14.17</v>
       </c>
       <c r="G3">
-        <v>4.21</v>
+        <v>18.03</v>
       </c>
       <c r="H3" s="4">
-        <v>53899.69</v>
+        <v>150938.41</v>
       </c>
       <c r="I3">
-        <v>1.68</v>
+        <v>3.96</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K3">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="L3">
-        <v>102.15</v>
+        <v>95.99</v>
       </c>
       <c r="M3">
-        <v>3.18</v>
+        <v>-9.8699999999999992</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -868,37 +862,37 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>43750</v>
+        <v>474000</v>
       </c>
       <c r="D4" s="3">
-        <v>6.4500000000000002E-2</v>
+        <v>-3.27E-2</v>
       </c>
       <c r="E4">
-        <v>7.12</v>
+        <v>13.09</v>
       </c>
       <c r="F4">
-        <v>9.6199999999999992</v>
+        <v>13.88</v>
       </c>
       <c r="G4">
-        <v>12.61</v>
+        <v>12.47</v>
       </c>
       <c r="H4" s="4">
-        <v>72041.39</v>
+        <v>405451.96</v>
       </c>
       <c r="I4">
-        <v>4.57</v>
+        <v>4.01</v>
       </c>
       <c r="J4">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="K4">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="L4">
-        <v>99.88</v>
+        <v>89.79</v>
       </c>
       <c r="M4">
-        <v>2.7</v>
+        <v>-9.1999999999999993</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -909,37 +903,37 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>27650</v>
+        <v>43300</v>
       </c>
       <c r="D5" s="3">
-        <v>-1.2500000000000001E-2</v>
+        <v>-1.03E-2</v>
       </c>
       <c r="E5">
-        <v>19.78</v>
+        <v>7.12</v>
       </c>
       <c r="F5">
-        <v>13.82</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="G5">
-        <v>23.29</v>
+        <v>12.61</v>
       </c>
       <c r="H5" s="4">
-        <v>32624.26</v>
+        <v>72041.39</v>
       </c>
       <c r="I5">
-        <v>3.62</v>
+        <v>4.62</v>
       </c>
       <c r="J5">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K5">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L5">
-        <v>97.1</v>
+        <v>98.79</v>
       </c>
       <c r="M5">
-        <v>1.65</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -950,37 +944,37 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>13710</v>
+        <v>81500</v>
       </c>
       <c r="D6" s="3">
-        <v>1.11E-2</v>
+        <v>-6.1100000000000002E-2</v>
       </c>
       <c r="E6">
-        <v>9.44</v>
+        <v>4.05</v>
       </c>
       <c r="F6">
-        <v>10.67</v>
+        <v>7.82</v>
       </c>
       <c r="G6">
-        <v>9.86</v>
+        <v>6.06</v>
       </c>
       <c r="H6" s="4">
-        <v>19219.419999999998</v>
+        <v>65679.45</v>
       </c>
       <c r="I6">
-        <v>3.76</v>
+        <v>1.84</v>
       </c>
       <c r="J6">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="K6">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="L6">
-        <v>101.99</v>
+        <v>97.95</v>
       </c>
       <c r="M6">
-        <v>-1.51</v>
+        <v>2.2599999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -991,37 +985,37 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>31200</v>
+        <v>70500</v>
       </c>
       <c r="D7" s="3">
-        <v>-3.2000000000000002E-3</v>
+        <v>-1.12E-2</v>
       </c>
       <c r="E7">
-        <v>12.8</v>
+        <v>1.04</v>
       </c>
       <c r="F7">
-        <v>13.49</v>
+        <v>3.97</v>
       </c>
       <c r="G7">
-        <v>12.93</v>
+        <v>4.21</v>
       </c>
       <c r="H7" s="4">
-        <v>31004.78</v>
+        <v>53899.69</v>
       </c>
       <c r="I7">
-        <v>3.19</v>
+        <v>1.7</v>
       </c>
       <c r="J7">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K7">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="L7">
-        <v>97.14</v>
+        <v>102.02</v>
       </c>
       <c r="M7">
-        <v>-1.73</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -1032,37 +1026,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>19550</v>
+        <v>20550</v>
       </c>
       <c r="D8" s="3">
-        <v>1.2999999999999999E-2</v>
+        <v>-1.2E-2</v>
       </c>
       <c r="E8">
-        <v>10.48</v>
+        <v>6.94</v>
       </c>
       <c r="F8">
-        <v>7.97</v>
+        <v>6.38</v>
       </c>
       <c r="G8">
-        <v>10.17</v>
+        <v>6.21</v>
       </c>
       <c r="H8" s="4">
-        <v>25607.22</v>
+        <v>39784.050000000003</v>
       </c>
       <c r="I8">
-        <v>6.01</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="J8">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K8">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L8">
-        <v>98.71</v>
+        <v>92.92</v>
       </c>
       <c r="M8">
-        <v>-2.4900000000000002</v>
+        <v>-6.38</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1073,37 +1067,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>178000</v>
+        <v>9160</v>
       </c>
       <c r="D9" s="3">
-        <v>-2.8400000000000002E-2</v>
+        <v>-1.4E-2</v>
       </c>
       <c r="E9">
-        <v>18.96</v>
+        <v>2.84</v>
       </c>
       <c r="F9">
-        <v>19.43</v>
+        <v>4.16</v>
       </c>
       <c r="G9">
-        <v>18.8</v>
+        <v>8.36</v>
       </c>
       <c r="H9" s="4">
-        <v>144109.65</v>
+        <v>20859.37</v>
       </c>
       <c r="I9">
-        <v>3.82</v>
+        <v>2.4</v>
       </c>
       <c r="J9">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="K9">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="L9">
-        <v>95.95</v>
+        <v>92.74</v>
       </c>
       <c r="M9">
-        <v>-2.79</v>
+        <v>-11.58</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1114,37 +1108,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>9510</v>
+        <v>39850</v>
       </c>
       <c r="D10" s="3">
-        <v>-5.1999999999999998E-3</v>
+        <v>-1.2999999999999999E-3</v>
       </c>
       <c r="E10">
-        <v>8.2100000000000009</v>
+        <v>4.57</v>
       </c>
       <c r="F10">
-        <v>3.26</v>
+        <v>7.42</v>
       </c>
       <c r="G10">
-        <v>5.34</v>
+        <v>4.55</v>
       </c>
       <c r="H10" s="4">
-        <v>22736.17</v>
+        <v>42814.52</v>
       </c>
       <c r="I10">
-        <v>3.68</v>
+        <v>3.01</v>
       </c>
       <c r="J10">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="K10">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="L10">
-        <v>95.27</v>
+        <v>96.31</v>
       </c>
       <c r="M10">
-        <v>-3.45</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1155,37 +1149,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>66300</v>
+        <v>90000</v>
       </c>
       <c r="D11" s="3">
-        <v>1.6899999999999998E-2</v>
+        <v>-3.0200000000000001E-2</v>
       </c>
       <c r="E11">
-        <v>4.12</v>
+        <v>2.16</v>
       </c>
       <c r="F11">
-        <v>5.22</v>
+        <v>5.36</v>
       </c>
       <c r="G11">
-        <v>11.01</v>
+        <v>5.18</v>
       </c>
       <c r="H11" s="4">
-        <v>151788</v>
+        <v>177736.27</v>
       </c>
       <c r="I11">
-        <v>4.07</v>
+        <v>3.44</v>
       </c>
       <c r="J11">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="K11">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="L11">
-        <v>95.8</v>
+        <v>93.17</v>
       </c>
       <c r="M11">
-        <v>-3.49</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1196,37 +1190,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>61500</v>
+        <v>13160</v>
       </c>
       <c r="D12" s="3">
-        <v>2.6700000000000002E-2</v>
+        <v>-4.0099999999999997E-2</v>
       </c>
       <c r="E12">
-        <v>2.85</v>
+        <v>9.44</v>
       </c>
       <c r="F12">
-        <v>12.83</v>
+        <v>10.67</v>
       </c>
       <c r="G12">
-        <v>5.63</v>
+        <v>9.86</v>
       </c>
       <c r="H12" s="4">
-        <v>71073.47</v>
+        <v>19219.419999999998</v>
       </c>
       <c r="I12">
-        <v>3.25</v>
+        <v>3.91</v>
       </c>
       <c r="J12">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K12">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L12">
-        <v>98.4</v>
+        <v>97.7</v>
       </c>
       <c r="M12">
-        <v>-3.61</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1237,37 +1231,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>60700</v>
+        <v>369000</v>
       </c>
       <c r="D13" s="3">
-        <v>2.0199999999999999E-2</v>
+        <v>-1.34E-2</v>
       </c>
       <c r="E13">
-        <v>7.45</v>
+        <v>6.17</v>
       </c>
       <c r="F13">
-        <v>7.45</v>
+        <v>6.83</v>
       </c>
       <c r="G13">
-        <v>7.69</v>
+        <v>6.2</v>
       </c>
       <c r="H13" s="4">
-        <v>79986.48</v>
+        <v>466289.71</v>
       </c>
       <c r="I13">
-        <v>4.6100000000000003</v>
+        <v>1.36</v>
       </c>
       <c r="J13">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="K13">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="L13">
-        <v>98.64</v>
+        <v>87.8</v>
       </c>
       <c r="M13">
-        <v>-3.65</v>
+        <v>-11.93</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1278,37 +1272,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>86800</v>
+        <v>9320</v>
       </c>
       <c r="D14" s="3">
-        <v>6.9000000000000006E-2</v>
+        <v>-0.02</v>
       </c>
       <c r="E14">
-        <v>4.05</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="F14">
-        <v>7.82</v>
+        <v>3.26</v>
       </c>
       <c r="G14">
-        <v>6.06</v>
+        <v>5.34</v>
       </c>
       <c r="H14" s="4">
-        <v>65679.45</v>
+        <v>22736.17</v>
       </c>
       <c r="I14">
-        <v>1.73</v>
+        <v>3.76</v>
       </c>
       <c r="J14">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="K14">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="L14">
-        <v>104.9</v>
+        <v>93.83</v>
       </c>
       <c r="M14">
-        <v>-3.88</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1319,37 +1313,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>18280</v>
+        <v>77200</v>
       </c>
       <c r="D15" s="3">
-        <v>1.67E-2</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="E15">
-        <v>12.08</v>
+        <v>7.58</v>
       </c>
       <c r="F15">
-        <v>8.58</v>
+        <v>7.58</v>
       </c>
       <c r="G15">
-        <v>8.39</v>
+        <v>12.29</v>
       </c>
       <c r="H15" s="4">
-        <v>19234.22</v>
+        <v>79498.27</v>
       </c>
       <c r="I15">
-        <v>6.4</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K15">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L15">
-        <v>98.26</v>
+        <v>95.88</v>
       </c>
       <c r="M15">
-        <v>-4.04</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1360,37 +1354,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>76200</v>
+        <v>517000</v>
       </c>
       <c r="D16" s="3">
-        <v>-2.18E-2</v>
+        <v>-7.7000000000000002E-3</v>
       </c>
       <c r="E16">
-        <v>10.83</v>
+        <v>12.43</v>
       </c>
       <c r="F16">
-        <v>3.37</v>
+        <v>10.08</v>
       </c>
       <c r="G16">
-        <v>9.48</v>
+        <v>11.82</v>
       </c>
       <c r="H16" s="4">
-        <v>54894.12</v>
+        <v>429918.88</v>
       </c>
       <c r="I16">
-        <v>4.6500000000000004</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="J16">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K16">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L16">
-        <v>97.48</v>
+        <v>96.5</v>
       </c>
       <c r="M16">
-        <v>-4.51</v>
+        <v>-13.11</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1401,37 +1395,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>155600</v>
+        <v>177300</v>
       </c>
       <c r="D17" s="3">
-        <v>6.4999999999999997E-3</v>
+        <v>-3.8999999999999998E-3</v>
       </c>
       <c r="E17">
-        <v>12.66</v>
+        <v>18.96</v>
       </c>
       <c r="F17">
-        <v>11.88</v>
+        <v>19.43</v>
       </c>
       <c r="G17">
-        <v>11.14</v>
+        <v>18.8</v>
       </c>
       <c r="H17" s="4">
-        <v>83639.03</v>
+        <v>144109.65</v>
       </c>
       <c r="I17">
-        <v>3.47</v>
+        <v>3.84</v>
       </c>
       <c r="J17">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K17">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L17">
-        <v>93.85</v>
+        <v>95.35</v>
       </c>
       <c r="M17">
-        <v>-4.5999999999999996</v>
+        <v>-5.03</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1442,37 +1436,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>238000</v>
+        <v>31700</v>
       </c>
       <c r="D18" s="3">
-        <v>3.2500000000000001E-2</v>
+        <v>-2.6100000000000002E-2</v>
       </c>
       <c r="E18">
-        <v>13.17</v>
+        <v>8.73</v>
       </c>
       <c r="F18">
-        <v>11.69</v>
+        <v>11.57</v>
       </c>
       <c r="G18">
-        <v>18.010000000000002</v>
+        <v>6.85</v>
       </c>
       <c r="H18" s="4">
-        <v>207156.6</v>
+        <v>24348.21</v>
       </c>
       <c r="I18">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="J18">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="K18">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="L18">
-        <v>102.87</v>
+        <v>95.71</v>
       </c>
       <c r="M18">
-        <v>-4.6100000000000003</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1483,37 +1477,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>218500</v>
+        <v>365500</v>
       </c>
       <c r="D19" s="3">
-        <v>-3.5299999999999998E-2</v>
+        <v>-2.92E-2</v>
       </c>
       <c r="E19">
-        <v>4.66</v>
+        <v>6.85</v>
       </c>
       <c r="F19">
-        <v>4.66</v>
+        <v>6.19</v>
       </c>
       <c r="G19">
-        <v>4.88</v>
+        <v>10.64</v>
       </c>
       <c r="H19" s="4">
-        <v>324173.33</v>
+        <v>605494.72</v>
       </c>
       <c r="I19">
-        <v>2.4300000000000002</v>
+        <v>2.46</v>
       </c>
       <c r="J19">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>101.62</v>
+        <v>94.38</v>
       </c>
       <c r="M19">
-        <v>-5</v>
+        <v>-5.92</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1524,37 +1518,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>12040</v>
+        <v>27600</v>
       </c>
       <c r="D20" s="3">
-        <v>-8.0000000000000004E-4</v>
+        <v>-1.8E-3</v>
       </c>
       <c r="E20">
-        <v>7.65</v>
+        <v>19.78</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>13.82</v>
       </c>
       <c r="G20">
-        <v>7.8</v>
+        <v>23.29</v>
       </c>
       <c r="H20" s="4">
-        <v>30039.25</v>
+        <v>32624.26</v>
       </c>
       <c r="I20">
-        <v>2.16</v>
+        <v>3.62</v>
       </c>
       <c r="J20">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="K20">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="L20">
-        <v>94.57</v>
+        <v>97</v>
       </c>
       <c r="M20">
-        <v>-5.05</v>
+        <v>4.1500000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1565,37 +1559,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>91900</v>
+        <v>223000</v>
       </c>
       <c r="D21" s="3">
-        <v>8.8000000000000005E-3</v>
+        <v>-6.3E-2</v>
       </c>
       <c r="E21">
-        <v>8.11</v>
+        <v>13.17</v>
       </c>
       <c r="F21">
-        <v>10.44</v>
+        <v>11.69</v>
       </c>
       <c r="G21">
-        <v>8.66</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H21" s="4">
-        <v>119742.76</v>
+        <v>207156.6</v>
       </c>
       <c r="I21">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="J21">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K21">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L21">
-        <v>95.09</v>
+        <v>96.22</v>
       </c>
       <c r="M21">
-        <v>-5.16</v>
+        <v>-8.61</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1606,37 +1600,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>20800</v>
+        <v>116300</v>
       </c>
       <c r="D22" s="3">
-        <v>1.46E-2</v>
+        <v>-3.0800000000000001E-2</v>
       </c>
       <c r="E22">
-        <v>15.12</v>
+        <v>5.88</v>
       </c>
       <c r="F22">
-        <v>13.07</v>
+        <v>6.29</v>
       </c>
       <c r="G22">
-        <v>15.58</v>
+        <v>10.87</v>
       </c>
       <c r="H22" s="4">
-        <v>15310.06</v>
+        <v>215382.39999999999</v>
       </c>
       <c r="I22">
-        <v>5.91</v>
+        <v>1.89</v>
       </c>
       <c r="J22">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K22">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="L22">
-        <v>97.12</v>
+        <v>85.55</v>
       </c>
       <c r="M22">
-        <v>-5.24</v>
+        <v>-16.03</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1647,37 +1641,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>376500</v>
+        <v>95300</v>
       </c>
       <c r="D23" s="3">
-        <v>1.7600000000000001E-2</v>
+        <v>-7.3000000000000001E-3</v>
       </c>
       <c r="E23">
-        <v>6.85</v>
+        <v>12.89</v>
       </c>
       <c r="F23">
-        <v>6.19</v>
+        <v>13.94</v>
       </c>
       <c r="G23">
-        <v>10.64</v>
+        <v>9.44</v>
       </c>
       <c r="H23" s="4">
-        <v>605494.72</v>
+        <v>87743.72</v>
       </c>
       <c r="I23">
-        <v>2.39</v>
+        <v>3.67</v>
       </c>
       <c r="J23">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="K23">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="L23">
-        <v>96.9</v>
+        <v>94.61</v>
       </c>
       <c r="M23">
-        <v>-5.28</v>
+        <v>-5.17</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1688,37 +1682,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>50200</v>
+        <v>75000</v>
       </c>
       <c r="D24" s="3">
-        <v>1.01E-2</v>
+        <v>-1.5699999999999999E-2</v>
       </c>
       <c r="E24">
-        <v>18.690000000000001</v>
+        <v>10.83</v>
       </c>
       <c r="F24">
-        <v>11.56</v>
+        <v>3.37</v>
       </c>
       <c r="G24">
-        <v>6.83</v>
+        <v>9.48</v>
       </c>
       <c r="H24" s="4">
-        <v>57293.3</v>
+        <v>54894.12</v>
       </c>
       <c r="I24">
-        <v>2.39</v>
+        <v>4.72</v>
       </c>
       <c r="J24">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="K24">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="L24">
-        <v>94.66</v>
+        <v>95.85</v>
       </c>
       <c r="M24">
-        <v>-5.28</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1729,37 +1723,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>77100</v>
+        <v>87900</v>
       </c>
       <c r="D25" s="3">
-        <v>1.0500000000000001E-2</v>
+        <v>-2.3E-3</v>
       </c>
       <c r="E25">
-        <v>15.14</v>
+        <v>14.42</v>
       </c>
       <c r="F25">
-        <v>14.47</v>
+        <v>24.2</v>
       </c>
       <c r="G25">
-        <v>11.28</v>
+        <v>15.82</v>
       </c>
       <c r="H25" s="4">
-        <v>82759.37</v>
+        <v>36460.550000000003</v>
       </c>
       <c r="I25">
-        <v>4.28</v>
+        <v>6.26</v>
       </c>
       <c r="J25">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="K25">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L25">
-        <v>95.64</v>
+        <v>90.33</v>
       </c>
       <c r="M25">
-        <v>-5.86</v>
+        <v>-7.08</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1770,37 +1764,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>149200</v>
+        <v>23100</v>
       </c>
       <c r="D26" s="3">
-        <v>-1.3899999999999999E-2</v>
+        <v>-1.49E-2</v>
       </c>
       <c r="E26">
-        <v>8.86</v>
+        <v>8.06</v>
       </c>
       <c r="F26">
-        <v>11.63</v>
+        <v>8.64</v>
       </c>
       <c r="G26">
-        <v>8.51</v>
+        <v>8.77</v>
       </c>
       <c r="H26" s="4">
-        <v>160038.65</v>
+        <v>44443.18</v>
       </c>
       <c r="I26">
-        <v>2.13</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="J26">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K26">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="L26">
-        <v>94.77</v>
+        <v>92.41</v>
       </c>
       <c r="M26">
-        <v>-6.16</v>
+        <v>-7.97</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1811,37 +1805,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>17050</v>
+        <v>59100</v>
       </c>
       <c r="D27" s="3">
-        <v>2.1000000000000001E-2</v>
+        <v>-2.64E-2</v>
       </c>
       <c r="E27">
-        <v>11.13</v>
+        <v>7.45</v>
       </c>
       <c r="F27">
-        <v>5.01</v>
+        <v>7.45</v>
       </c>
       <c r="G27">
-        <v>9.31</v>
+        <v>7.69</v>
       </c>
       <c r="H27" s="4">
-        <v>24921.41</v>
+        <v>79986.48</v>
       </c>
       <c r="I27">
-        <v>5.87</v>
+        <v>4.74</v>
       </c>
       <c r="J27">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="K27">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="L27">
-        <v>97.06</v>
+        <v>96.05</v>
       </c>
       <c r="M27">
-        <v>-6.37</v>
+        <v>-4.5199999999999996</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1852,37 +1846,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>18650</v>
+        <v>20700</v>
       </c>
       <c r="D28" s="3">
-        <v>-2.1000000000000001E-2</v>
+        <v>-4.7999999999999996E-3</v>
       </c>
       <c r="E28">
-        <v>6.96</v>
+        <v>15.12</v>
       </c>
       <c r="F28">
-        <v>9.58</v>
+        <v>13.07</v>
       </c>
       <c r="G28">
-        <v>7.18</v>
+        <v>15.58</v>
       </c>
       <c r="H28" s="4">
-        <v>34223.949999999997</v>
+        <v>15310.06</v>
       </c>
       <c r="I28">
-        <v>3.49</v>
+        <v>5.94</v>
       </c>
       <c r="J28">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="K28">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="L28">
-        <v>92.65</v>
+        <v>96.79</v>
       </c>
       <c r="M28">
-        <v>-6.42</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1893,37 +1887,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>490000</v>
+        <v>59600</v>
       </c>
       <c r="D29" s="3">
-        <v>-1.5100000000000001E-2</v>
+        <v>-3.09E-2</v>
       </c>
       <c r="E29">
-        <v>13.09</v>
+        <v>2.85</v>
       </c>
       <c r="F29">
-        <v>13.88</v>
+        <v>12.83</v>
       </c>
       <c r="G29">
-        <v>12.47</v>
+        <v>5.63</v>
       </c>
       <c r="H29" s="4">
-        <v>405451.96</v>
+        <v>71073.47</v>
       </c>
       <c r="I29">
-        <v>3.88</v>
+        <v>3.36</v>
       </c>
       <c r="J29">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K29">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L29">
-        <v>92.33</v>
+        <v>95.34</v>
       </c>
       <c r="M29">
-        <v>-7.55</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1934,37 +1928,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>112500</v>
+        <v>14950</v>
       </c>
       <c r="D30" s="3">
-        <v>-7.9000000000000008E-3</v>
+        <v>-2.0299999999999999E-2</v>
       </c>
       <c r="E30">
-        <v>9.11</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F30">
-        <v>10.57</v>
+        <v>6.71</v>
       </c>
       <c r="G30">
-        <v>9.4</v>
+        <v>6.75</v>
       </c>
       <c r="H30" s="4">
-        <v>159337.74</v>
+        <v>20394.86</v>
       </c>
       <c r="I30">
-        <v>3.2</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="J30">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="K30">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="L30">
-        <v>93.72</v>
+        <v>92.39</v>
       </c>
       <c r="M30">
-        <v>-7.64</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1975,37 +1969,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>15260</v>
+        <v>216000</v>
       </c>
       <c r="D31" s="3">
-        <v>1.46E-2</v>
+        <v>-1.14E-2</v>
       </c>
       <c r="E31">
-        <v>4.4000000000000004</v>
+        <v>4.66</v>
       </c>
       <c r="F31">
-        <v>6.71</v>
+        <v>4.66</v>
       </c>
       <c r="G31">
-        <v>6.75</v>
+        <v>4.88</v>
       </c>
       <c r="H31" s="4">
-        <v>20394.86</v>
+        <v>324173.33</v>
       </c>
       <c r="I31">
-        <v>4.26</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="J31">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="K31">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L31">
-        <v>94.07</v>
+        <v>99.93</v>
       </c>
       <c r="M31">
-        <v>-7.74</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -2016,37 +2010,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>20800</v>
+        <v>153000</v>
       </c>
       <c r="D32" s="3">
-        <v>4.7999999999999996E-3</v>
+        <v>-1.67E-2</v>
       </c>
       <c r="E32">
-        <v>6.94</v>
+        <v>12.66</v>
       </c>
       <c r="F32">
-        <v>6.38</v>
+        <v>11.88</v>
       </c>
       <c r="G32">
-        <v>6.21</v>
+        <v>11.14</v>
       </c>
       <c r="H32" s="4">
-        <v>39784.050000000003</v>
+        <v>83639.03</v>
       </c>
       <c r="I32">
-        <v>4.09</v>
+        <v>3.53</v>
       </c>
       <c r="J32">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="K32">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="L32">
-        <v>93.62</v>
+        <v>92.71</v>
       </c>
       <c r="M32">
-        <v>-7.96</v>
+        <v>-5.73</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2057,37 +2051,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>32550</v>
+        <v>18140</v>
       </c>
       <c r="D33" s="3">
-        <v>-2.2499999999999999E-2</v>
+        <v>-7.7000000000000002E-3</v>
       </c>
       <c r="E33">
-        <v>8.73</v>
+        <v>12.08</v>
       </c>
       <c r="F33">
-        <v>11.57</v>
+        <v>8.58</v>
       </c>
       <c r="G33">
-        <v>6.85</v>
+        <v>8.39</v>
       </c>
       <c r="H33" s="4">
-        <v>24348.21</v>
+        <v>19234.22</v>
       </c>
       <c r="I33">
-        <v>2.92</v>
+        <v>6.45</v>
       </c>
       <c r="J33">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="K33">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="L33">
-        <v>99.01</v>
+        <v>97.47</v>
       </c>
       <c r="M33">
-        <v>-8.31</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2098,37 +2092,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>16860</v>
+        <v>35450</v>
       </c>
       <c r="D34" s="3">
-        <v>-2.4299999999999999E-2</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="E34">
-        <v>3.6</v>
+        <v>11.21</v>
       </c>
       <c r="F34">
-        <v>9.42</v>
+        <v>6.55</v>
       </c>
       <c r="G34">
-        <v>5.91</v>
+        <v>6.4</v>
       </c>
       <c r="H34" s="4">
-        <v>38541.279999999999</v>
+        <v>122131.86</v>
       </c>
       <c r="I34">
-        <v>2.97</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="J34">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="K34">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="L34">
-        <v>89.89</v>
+        <v>87.89</v>
       </c>
       <c r="M34">
-        <v>-8.32</v>
+        <v>-12.68</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2139,37 +2133,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>23450</v>
+        <v>90800</v>
       </c>
       <c r="D35" s="3">
-        <v>-6.4000000000000003E-3</v>
+        <v>-1.2E-2</v>
       </c>
       <c r="E35">
-        <v>8.06</v>
+        <v>8.11</v>
       </c>
       <c r="F35">
-        <v>8.64</v>
+        <v>10.44</v>
       </c>
       <c r="G35">
-        <v>8.77</v>
+        <v>8.66</v>
       </c>
       <c r="H35" s="4">
-        <v>44443.18</v>
+        <v>119742.76</v>
       </c>
       <c r="I35">
-        <v>4.54</v>
+        <v>2.38</v>
       </c>
       <c r="J35">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K35">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="L35">
-        <v>93.73</v>
+        <v>94.08</v>
       </c>
       <c r="M35">
-        <v>-8.93</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2180,37 +2174,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>32500</v>
+        <v>219500</v>
       </c>
       <c r="D36" s="3">
-        <v>-2.5499999999999998E-2</v>
+        <v>-3.3000000000000002E-2</v>
       </c>
       <c r="E36">
-        <v>9.39</v>
+        <v>11.54</v>
       </c>
       <c r="F36">
-        <v>10.74</v>
+        <v>20.98</v>
       </c>
       <c r="G36">
-        <v>9.73</v>
+        <v>9.6</v>
       </c>
       <c r="H36" s="4">
-        <v>48211.77</v>
+        <v>189057.03</v>
       </c>
       <c r="I36">
-        <v>3.69</v>
+        <v>1.81</v>
       </c>
       <c r="J36">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K36">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L36">
-        <v>90.03</v>
+        <v>89.48</v>
       </c>
       <c r="M36">
-        <v>-9.7200000000000006</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2221,37 +2215,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>96000</v>
+        <v>63800</v>
       </c>
       <c r="D37" s="3">
-        <v>-1.84E-2</v>
+        <v>-3.7699999999999997E-2</v>
       </c>
       <c r="E37">
-        <v>12.89</v>
+        <v>4.12</v>
       </c>
       <c r="F37">
-        <v>13.94</v>
+        <v>5.22</v>
       </c>
       <c r="G37">
-        <v>9.44</v>
+        <v>11.01</v>
       </c>
       <c r="H37" s="4">
-        <v>87743.72</v>
+        <v>151788</v>
       </c>
       <c r="I37">
-        <v>3.65</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="J37">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="K37">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="L37">
-        <v>95.43</v>
+        <v>92.69</v>
       </c>
       <c r="M37">
-        <v>-10.11</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2262,37 +2256,37 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>88100</v>
+        <v>108900</v>
       </c>
       <c r="D38" s="3">
-        <v>-3.3999999999999998E-3</v>
+        <v>-3.2000000000000001E-2</v>
       </c>
       <c r="E38">
-        <v>14.42</v>
+        <v>9.11</v>
       </c>
       <c r="F38">
-        <v>24.2</v>
+        <v>10.57</v>
       </c>
       <c r="G38">
-        <v>15.82</v>
+        <v>9.4</v>
       </c>
       <c r="H38" s="4">
-        <v>36460.550000000003</v>
+        <v>159337.74</v>
       </c>
       <c r="I38">
-        <v>6.24</v>
+        <v>3.31</v>
       </c>
       <c r="J38">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K38">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L38">
-        <v>89.82</v>
+        <v>91.1</v>
       </c>
       <c r="M38">
-        <v>-10.74</v>
+        <v>-9.33</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2303,37 +2297,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>39900</v>
+        <v>148900</v>
       </c>
       <c r="D39" s="3">
-        <v>-1.6E-2</v>
+        <v>-2E-3</v>
       </c>
       <c r="E39">
-        <v>4.57</v>
+        <v>8.86</v>
       </c>
       <c r="F39">
-        <v>7.42</v>
+        <v>11.63</v>
       </c>
       <c r="G39">
-        <v>4.55</v>
+        <v>8.51</v>
       </c>
       <c r="H39" s="4">
-        <v>42814.52</v>
+        <v>160038.65</v>
       </c>
       <c r="I39">
-        <v>3.01</v>
+        <v>2.13</v>
       </c>
       <c r="J39">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="K39">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L39">
-        <v>97.44</v>
+        <v>94.66</v>
       </c>
       <c r="M39">
-        <v>-11.04</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2344,37 +2338,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>227000</v>
+        <v>18270</v>
       </c>
       <c r="D40" s="3">
-        <v>-1.09E-2</v>
+        <v>-2.0400000000000001E-2</v>
       </c>
       <c r="E40">
-        <v>11.54</v>
+        <v>6.96</v>
       </c>
       <c r="F40">
-        <v>20.98</v>
+        <v>9.58</v>
       </c>
       <c r="G40">
-        <v>9.6</v>
+        <v>7.18</v>
       </c>
       <c r="H40" s="4">
-        <v>189057.03</v>
+        <v>34223.949999999997</v>
       </c>
       <c r="I40">
-        <v>1.75</v>
+        <v>3.56</v>
       </c>
       <c r="J40">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K40">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L40">
-        <v>92.46</v>
+        <v>91.03</v>
       </c>
       <c r="M40">
-        <v>-12.19</v>
+        <v>-7.16</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2385,37 +2379,37 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>36100</v>
+        <v>16660</v>
       </c>
       <c r="D41" s="3">
-        <v>-1.4E-3</v>
+        <v>-1.1900000000000001E-2</v>
       </c>
       <c r="E41">
-        <v>11.21</v>
+        <v>3.6</v>
       </c>
       <c r="F41">
-        <v>6.55</v>
+        <v>9.42</v>
       </c>
       <c r="G41">
-        <v>6.4</v>
+        <v>5.91</v>
       </c>
       <c r="H41" s="4">
-        <v>122131.86</v>
+        <v>38541.279999999999</v>
       </c>
       <c r="I41">
-        <v>4.03</v>
+        <v>3</v>
       </c>
       <c r="J41">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="K41">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="L41">
-        <v>88.85</v>
+        <v>89.11</v>
       </c>
       <c r="M41">
-        <v>-12.38</v>
+        <v>-7.96</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2426,37 +2420,37 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>374000</v>
+        <v>55300</v>
       </c>
       <c r="D42" s="3">
-        <v>-5.0799999999999998E-2</v>
+        <v>-3.9899999999999998E-2</v>
       </c>
       <c r="E42">
-        <v>6.17</v>
+        <v>10.79</v>
       </c>
       <c r="F42">
-        <v>6.83</v>
+        <v>10.55</v>
       </c>
       <c r="G42">
-        <v>6.2</v>
+        <v>8.93</v>
       </c>
       <c r="H42" s="4">
-        <v>466289.71</v>
+        <v>92723.77</v>
       </c>
       <c r="I42">
-        <v>1.34</v>
+        <v>3.62</v>
       </c>
       <c r="J42">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="K42">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="L42">
-        <v>88.37</v>
+        <v>82.06</v>
       </c>
       <c r="M42">
-        <v>-13.02</v>
+        <v>-17.22</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2467,37 +2461,37 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>9290</v>
+        <v>30500</v>
       </c>
       <c r="D43" s="3">
-        <v>5.4000000000000003E-3</v>
+        <v>-2.24E-2</v>
       </c>
       <c r="E43">
-        <v>2.84</v>
+        <v>12.8</v>
       </c>
       <c r="F43">
-        <v>4.16</v>
+        <v>13.49</v>
       </c>
       <c r="G43">
-        <v>8.36</v>
+        <v>12.93</v>
       </c>
       <c r="H43" s="4">
-        <v>20859.37</v>
+        <v>31004.78</v>
       </c>
       <c r="I43">
-        <v>2.37</v>
+        <v>3.26</v>
       </c>
       <c r="J43">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="K43">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="L43">
-        <v>94.09</v>
+        <v>94.82</v>
       </c>
       <c r="M43">
-        <v>-13.42</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
@@ -2508,37 +2502,37 @@
         <v>96</v>
       </c>
       <c r="C44" s="2">
-        <v>92800</v>
+        <v>12030</v>
       </c>
       <c r="D44" s="3">
-        <v>-5.4000000000000003E-3</v>
+        <v>-8.0000000000000004E-4</v>
       </c>
       <c r="E44">
+        <v>7.65</v>
+      </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
+      <c r="G44">
+        <v>7.8</v>
+      </c>
+      <c r="H44" s="4">
+        <v>30039.25</v>
+      </c>
+      <c r="I44">
         <v>2.16</v>
       </c>
-      <c r="F44">
-        <v>5.36</v>
-      </c>
-      <c r="G44">
-        <v>5.18</v>
-      </c>
-      <c r="H44" s="4">
-        <v>177736.27</v>
-      </c>
-      <c r="I44">
-        <v>3.34</v>
-      </c>
       <c r="J44">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="K44">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="L44">
-        <v>95.99</v>
+        <v>94.85</v>
       </c>
       <c r="M44">
-        <v>-13.83</v>
+        <v>-2.4300000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
@@ -2549,37 +2543,37 @@
         <v>98</v>
       </c>
       <c r="C45" s="2">
-        <v>25850</v>
+        <v>50500</v>
       </c>
       <c r="D45" s="3">
-        <v>1.37E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E45">
-        <v>8.2799999999999994</v>
+        <v>18.690000000000001</v>
       </c>
       <c r="F45">
-        <v>8.9</v>
+        <v>11.56</v>
       </c>
       <c r="G45">
-        <v>5.8</v>
+        <v>6.83</v>
       </c>
       <c r="H45" s="4">
-        <v>48390.96</v>
+        <v>57293.3</v>
       </c>
       <c r="I45">
-        <v>3.87</v>
+        <v>2.38</v>
       </c>
       <c r="J45">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="K45">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="L45">
-        <v>88.1</v>
+        <v>95.78</v>
       </c>
       <c r="M45">
-        <v>-17.41</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
@@ -2590,37 +2584,37 @@
         <v>100</v>
       </c>
       <c r="C46" s="2">
-        <v>167000</v>
+        <v>19590</v>
       </c>
       <c r="D46" s="3">
-        <v>3.09E-2</v>
+        <v>2E-3</v>
       </c>
       <c r="E46">
-        <v>19.09</v>
+        <v>10.48</v>
       </c>
       <c r="F46">
-        <v>14.17</v>
+        <v>7.97</v>
       </c>
       <c r="G46">
-        <v>18.03</v>
+        <v>10.17</v>
       </c>
       <c r="H46" s="4">
-        <v>150938.41</v>
+        <v>25607.22</v>
       </c>
       <c r="I46">
-        <v>3.89</v>
+        <v>6</v>
       </c>
       <c r="J46">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="K46">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="L46">
-        <v>97.87</v>
+        <v>98.95</v>
       </c>
       <c r="M46">
-        <v>-18.73</v>
+        <v>-1.1100000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
@@ -2631,37 +2625,37 @@
         <v>102</v>
       </c>
       <c r="C47" s="2">
-        <v>57600</v>
+        <v>16800</v>
       </c>
       <c r="D47" s="3">
-        <v>-2.3699999999999999E-2</v>
+        <v>-1.47E-2</v>
       </c>
       <c r="E47">
-        <v>10.79</v>
+        <v>11.13</v>
       </c>
       <c r="F47">
-        <v>10.55</v>
+        <v>5.01</v>
       </c>
       <c r="G47">
-        <v>8.93</v>
+        <v>9.31</v>
       </c>
       <c r="H47" s="4">
-        <v>92723.77</v>
+        <v>24921.41</v>
       </c>
       <c r="I47">
-        <v>3.47</v>
+        <v>5.95</v>
       </c>
       <c r="J47">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="K47">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="L47">
-        <v>84.56</v>
+        <v>95.91</v>
       </c>
       <c r="M47">
-        <v>-20.99</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
@@ -2672,78 +2666,37 @@
         <v>104</v>
       </c>
       <c r="C48" s="2">
-        <v>120000</v>
+        <v>32200</v>
       </c>
       <c r="D48" s="3">
-        <v>-4.2299999999999997E-2</v>
+        <v>-9.1999999999999998E-3</v>
       </c>
       <c r="E48">
-        <v>5.88</v>
+        <v>9.39</v>
       </c>
       <c r="F48">
-        <v>6.29</v>
+        <v>10.74</v>
       </c>
       <c r="G48">
-        <v>10.87</v>
+        <v>9.73</v>
       </c>
       <c r="H48" s="4">
-        <v>215382.39999999999</v>
+        <v>48211.77</v>
       </c>
       <c r="I48">
-        <v>1.83</v>
+        <v>3.73</v>
       </c>
       <c r="J48">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="K48">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="L48">
-        <v>87.56</v>
+        <v>89.49</v>
       </c>
       <c r="M48">
-        <v>-21.77</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A49" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B49" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" s="2">
-        <v>521000</v>
-      </c>
-      <c r="D49" s="3">
-        <v>-1.7000000000000001E-2</v>
-      </c>
-      <c r="E49">
-        <v>12.43</v>
-      </c>
-      <c r="F49">
-        <v>10.08</v>
-      </c>
-      <c r="G49">
-        <v>11.82</v>
-      </c>
-      <c r="H49" s="4">
-        <v>429918.88</v>
-      </c>
-      <c r="I49">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="J49">
-        <v>69</v>
-      </c>
-      <c r="K49">
-        <v>69</v>
-      </c>
-      <c r="L49">
-        <v>97.6</v>
-      </c>
-      <c r="M49">
-        <v>-22.7</v>
+        <v>-8.7799999999999994</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D915FBE-EECE-4D70-B665-5AA2D8F19747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E823FAB5-372C-4567-80AA-C747605F1500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{483BA26C-6031-4CD8-9BD9-1735F0EE164A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{22A44216-7F7E-41A0-96E1-E4AAA6A3C645}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
   <si>
     <t>종목코드</t>
   </si>
@@ -96,18 +96,6 @@
     <t>세아베스틸지주</t>
   </si>
   <si>
-    <t>001680</t>
-  </si>
-  <si>
-    <t>대상</t>
-  </si>
-  <si>
-    <t>002310</t>
-  </si>
-  <si>
-    <t>아세아제지</t>
-  </si>
-  <si>
     <t>003540</t>
   </si>
   <si>
@@ -126,24 +114,6 @@
     <t>코리안리</t>
   </si>
   <si>
-    <t>004370</t>
-  </si>
-  <si>
-    <t>농심</t>
-  </si>
-  <si>
-    <t>004980</t>
-  </si>
-  <si>
-    <t>성신양회</t>
-  </si>
-  <si>
-    <t>005180</t>
-  </si>
-  <si>
-    <t>빙그레</t>
-  </si>
-  <si>
     <t>005380</t>
   </si>
   <si>
@@ -162,12 +132,6 @@
     <t>NH투자증권</t>
   </si>
   <si>
-    <t>007310</t>
-  </si>
-  <si>
-    <t>오뚜기</t>
-  </si>
-  <si>
     <t>007340</t>
   </si>
   <si>
@@ -180,12 +144,6 @@
     <t>영원무역홀딩스</t>
   </si>
   <si>
-    <t>011780</t>
-  </si>
-  <si>
-    <t>금호석유화학</t>
-  </si>
-  <si>
     <t>016360</t>
   </si>
   <si>
@@ -312,28 +270,10 @@
     <t>JB금융지주</t>
   </si>
   <si>
-    <t>183190</t>
-  </si>
-  <si>
-    <t>아세아시멘트</t>
-  </si>
-  <si>
     <t>192080</t>
   </si>
   <si>
     <t>더블유게임즈</t>
-  </si>
-  <si>
-    <t>214320</t>
-  </si>
-  <si>
-    <t>이노션</t>
-  </si>
-  <si>
-    <t>300720</t>
-  </si>
-  <si>
-    <t>한일시멘트</t>
   </si>
   <si>
     <t>316140</t>
@@ -714,8 +654,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBFF365F-02C7-405D-A82B-25D49A7A0AEA}">
-  <dimension ref="A1:M48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27312FCD-872D-4C85-BA66-81C56918FE28}">
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
@@ -1026,37 +966,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>20550</v>
+        <v>39850</v>
       </c>
       <c r="D8" s="3">
-        <v>-1.2E-2</v>
+        <v>-1.2999999999999999E-3</v>
       </c>
       <c r="E8">
-        <v>6.94</v>
+        <v>4.57</v>
       </c>
       <c r="F8">
-        <v>6.38</v>
+        <v>7.42</v>
       </c>
       <c r="G8">
-        <v>6.21</v>
+        <v>4.55</v>
       </c>
       <c r="H8" s="4">
-        <v>39784.050000000003</v>
+        <v>42814.52</v>
       </c>
       <c r="I8">
-        <v>4.1399999999999997</v>
+        <v>3.01</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="K8">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="L8">
-        <v>92.92</v>
+        <v>96.31</v>
       </c>
       <c r="M8">
-        <v>-6.38</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1067,25 +1007,25 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>9160</v>
+        <v>90000</v>
       </c>
       <c r="D9" s="3">
-        <v>-1.4E-2</v>
+        <v>-3.0200000000000001E-2</v>
       </c>
       <c r="E9">
-        <v>2.84</v>
+        <v>2.16</v>
       </c>
       <c r="F9">
-        <v>4.16</v>
+        <v>5.36</v>
       </c>
       <c r="G9">
-        <v>8.36</v>
+        <v>5.18</v>
       </c>
       <c r="H9" s="4">
-        <v>20859.37</v>
+        <v>177736.27</v>
       </c>
       <c r="I9">
-        <v>2.4</v>
+        <v>3.44</v>
       </c>
       <c r="J9">
         <v>49</v>
@@ -1094,10 +1034,10 @@
         <v>49</v>
       </c>
       <c r="L9">
-        <v>92.74</v>
+        <v>93.17</v>
       </c>
       <c r="M9">
-        <v>-11.58</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1108,37 +1048,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>39850</v>
+        <v>13160</v>
       </c>
       <c r="D10" s="3">
-        <v>-1.2999999999999999E-3</v>
+        <v>-4.0099999999999997E-2</v>
       </c>
       <c r="E10">
-        <v>4.57</v>
+        <v>9.44</v>
       </c>
       <c r="F10">
-        <v>7.42</v>
+        <v>10.67</v>
       </c>
       <c r="G10">
-        <v>4.55</v>
+        <v>9.86</v>
       </c>
       <c r="H10" s="4">
-        <v>42814.52</v>
+        <v>19219.419999999998</v>
       </c>
       <c r="I10">
-        <v>3.01</v>
+        <v>3.91</v>
       </c>
       <c r="J10">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K10">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L10">
-        <v>96.31</v>
+        <v>97.7</v>
       </c>
       <c r="M10">
-        <v>-3.74</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1149,37 +1089,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>90000</v>
+        <v>517000</v>
       </c>
       <c r="D11" s="3">
-        <v>-3.0200000000000001E-2</v>
+        <v>-7.7000000000000002E-3</v>
       </c>
       <c r="E11">
-        <v>2.16</v>
+        <v>12.43</v>
       </c>
       <c r="F11">
-        <v>5.36</v>
+        <v>10.08</v>
       </c>
       <c r="G11">
-        <v>5.18</v>
+        <v>11.82</v>
       </c>
       <c r="H11" s="4">
-        <v>177736.27</v>
+        <v>429918.88</v>
       </c>
       <c r="I11">
-        <v>3.44</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="J11">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="K11">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="L11">
-        <v>93.17</v>
+        <v>96.5</v>
       </c>
       <c r="M11">
-        <v>-12.2</v>
+        <v>-13.11</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1190,37 +1130,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>13160</v>
+        <v>177300</v>
       </c>
       <c r="D12" s="3">
-        <v>-4.0099999999999997E-2</v>
+        <v>-3.8999999999999998E-3</v>
       </c>
       <c r="E12">
-        <v>9.44</v>
+        <v>18.96</v>
       </c>
       <c r="F12">
-        <v>10.67</v>
+        <v>19.43</v>
       </c>
       <c r="G12">
-        <v>9.86</v>
+        <v>18.8</v>
       </c>
       <c r="H12" s="4">
-        <v>19219.419999999998</v>
+        <v>144109.65</v>
       </c>
       <c r="I12">
-        <v>3.91</v>
+        <v>3.84</v>
       </c>
       <c r="J12">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K12">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L12">
-        <v>97.7</v>
+        <v>95.35</v>
       </c>
       <c r="M12">
-        <v>-2.16</v>
+        <v>-5.03</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1231,37 +1171,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>369000</v>
+        <v>31700</v>
       </c>
       <c r="D13" s="3">
-        <v>-1.34E-2</v>
+        <v>-2.6100000000000002E-2</v>
       </c>
       <c r="E13">
-        <v>6.17</v>
+        <v>8.73</v>
       </c>
       <c r="F13">
-        <v>6.83</v>
+        <v>11.57</v>
       </c>
       <c r="G13">
-        <v>6.2</v>
+        <v>6.85</v>
       </c>
       <c r="H13" s="4">
-        <v>466289.71</v>
+        <v>24348.21</v>
       </c>
       <c r="I13">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="K13">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="L13">
-        <v>87.8</v>
+        <v>95.71</v>
       </c>
       <c r="M13">
-        <v>-11.93</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1272,37 +1212,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>9320</v>
+        <v>27600</v>
       </c>
       <c r="D14" s="3">
-        <v>-0.02</v>
+        <v>-1.8E-3</v>
       </c>
       <c r="E14">
-        <v>8.2100000000000009</v>
+        <v>19.78</v>
       </c>
       <c r="F14">
-        <v>3.26</v>
+        <v>13.82</v>
       </c>
       <c r="G14">
-        <v>5.34</v>
+        <v>23.29</v>
       </c>
       <c r="H14" s="4">
-        <v>22736.17</v>
+        <v>32624.26</v>
       </c>
       <c r="I14">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
       <c r="J14">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="K14">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="L14">
-        <v>93.83</v>
+        <v>97</v>
       </c>
       <c r="M14">
-        <v>-2.92</v>
+        <v>4.1500000000000004</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1313,37 +1253,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>77200</v>
+        <v>223000</v>
       </c>
       <c r="D15" s="3">
-        <v>1.2999999999999999E-3</v>
+        <v>-6.3E-2</v>
       </c>
       <c r="E15">
-        <v>7.58</v>
+        <v>13.17</v>
       </c>
       <c r="F15">
-        <v>7.58</v>
+        <v>11.69</v>
       </c>
       <c r="G15">
-        <v>12.29</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H15" s="4">
-        <v>79498.27</v>
+        <v>207156.6</v>
       </c>
       <c r="I15">
-        <v>4.2699999999999996</v>
+        <v>2.4</v>
       </c>
       <c r="J15">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="K15">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="L15">
-        <v>95.88</v>
+        <v>96.22</v>
       </c>
       <c r="M15">
-        <v>-1.28</v>
+        <v>-8.61</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1354,37 +1294,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>517000</v>
+        <v>95300</v>
       </c>
       <c r="D16" s="3">
-        <v>-7.7000000000000002E-3</v>
+        <v>-7.3000000000000001E-3</v>
       </c>
       <c r="E16">
-        <v>12.43</v>
+        <v>12.89</v>
       </c>
       <c r="F16">
-        <v>10.08</v>
+        <v>13.94</v>
       </c>
       <c r="G16">
-        <v>11.82</v>
+        <v>9.44</v>
       </c>
       <c r="H16" s="4">
-        <v>429918.88</v>
+        <v>87743.72</v>
       </c>
       <c r="I16">
-        <v>2.3199999999999998</v>
+        <v>3.67</v>
       </c>
       <c r="J16">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K16">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L16">
-        <v>96.5</v>
+        <v>94.61</v>
       </c>
       <c r="M16">
-        <v>-13.11</v>
+        <v>-5.17</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1395,37 +1335,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>177300</v>
+        <v>75000</v>
       </c>
       <c r="D17" s="3">
-        <v>-3.8999999999999998E-3</v>
+        <v>-1.5699999999999999E-2</v>
       </c>
       <c r="E17">
-        <v>18.96</v>
+        <v>10.83</v>
       </c>
       <c r="F17">
-        <v>19.43</v>
+        <v>3.37</v>
       </c>
       <c r="G17">
-        <v>18.8</v>
+        <v>9.48</v>
       </c>
       <c r="H17" s="4">
-        <v>144109.65</v>
+        <v>54894.12</v>
       </c>
       <c r="I17">
-        <v>3.84</v>
+        <v>4.72</v>
       </c>
       <c r="J17">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="K17">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="L17">
-        <v>95.35</v>
+        <v>95.85</v>
       </c>
       <c r="M17">
-        <v>-5.03</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1436,37 +1376,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>31700</v>
+        <v>87900</v>
       </c>
       <c r="D18" s="3">
-        <v>-2.6100000000000002E-2</v>
+        <v>-2.3E-3</v>
       </c>
       <c r="E18">
-        <v>8.73</v>
+        <v>14.42</v>
       </c>
       <c r="F18">
-        <v>11.57</v>
+        <v>24.2</v>
       </c>
       <c r="G18">
-        <v>6.85</v>
+        <v>15.82</v>
       </c>
       <c r="H18" s="4">
-        <v>24348.21</v>
+        <v>36460.550000000003</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>6.26</v>
       </c>
       <c r="J18">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K18">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L18">
-        <v>95.71</v>
+        <v>90.33</v>
       </c>
       <c r="M18">
-        <v>-4.8</v>
+        <v>-7.08</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1477,37 +1417,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>365500</v>
+        <v>23100</v>
       </c>
       <c r="D19" s="3">
-        <v>-2.92E-2</v>
+        <v>-1.49E-2</v>
       </c>
       <c r="E19">
-        <v>6.85</v>
+        <v>8.06</v>
       </c>
       <c r="F19">
-        <v>6.19</v>
+        <v>8.64</v>
       </c>
       <c r="G19">
-        <v>10.64</v>
+        <v>8.77</v>
       </c>
       <c r="H19" s="4">
-        <v>605494.72</v>
+        <v>44443.18</v>
       </c>
       <c r="I19">
-        <v>2.46</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="J19">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="K19">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="L19">
-        <v>94.38</v>
+        <v>92.41</v>
       </c>
       <c r="M19">
-        <v>-5.92</v>
+        <v>-7.97</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1518,37 +1458,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>27600</v>
+        <v>59100</v>
       </c>
       <c r="D20" s="3">
-        <v>-1.8E-3</v>
+        <v>-2.64E-2</v>
       </c>
       <c r="E20">
-        <v>19.78</v>
+        <v>7.45</v>
       </c>
       <c r="F20">
-        <v>13.82</v>
+        <v>7.45</v>
       </c>
       <c r="G20">
-        <v>23.29</v>
+        <v>7.69</v>
       </c>
       <c r="H20" s="4">
-        <v>32624.26</v>
+        <v>79986.48</v>
       </c>
       <c r="I20">
-        <v>3.62</v>
+        <v>4.74</v>
       </c>
       <c r="J20">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K20">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L20">
-        <v>97</v>
+        <v>96.05</v>
       </c>
       <c r="M20">
-        <v>4.1500000000000004</v>
+        <v>-4.5199999999999996</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1559,37 +1499,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>223000</v>
+        <v>20700</v>
       </c>
       <c r="D21" s="3">
-        <v>-6.3E-2</v>
+        <v>-4.7999999999999996E-3</v>
       </c>
       <c r="E21">
-        <v>13.17</v>
+        <v>15.12</v>
       </c>
       <c r="F21">
-        <v>11.69</v>
+        <v>13.07</v>
       </c>
       <c r="G21">
-        <v>18.010000000000002</v>
+        <v>15.58</v>
       </c>
       <c r="H21" s="4">
-        <v>207156.6</v>
+        <v>15310.06</v>
       </c>
       <c r="I21">
-        <v>2.4</v>
+        <v>5.94</v>
       </c>
       <c r="J21">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="K21">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="L21">
-        <v>96.22</v>
+        <v>96.79</v>
       </c>
       <c r="M21">
-        <v>-8.61</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1600,37 +1540,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>116300</v>
+        <v>59600</v>
       </c>
       <c r="D22" s="3">
-        <v>-3.0800000000000001E-2</v>
+        <v>-3.09E-2</v>
       </c>
       <c r="E22">
-        <v>5.88</v>
+        <v>2.85</v>
       </c>
       <c r="F22">
-        <v>6.29</v>
+        <v>12.83</v>
       </c>
       <c r="G22">
-        <v>10.87</v>
+        <v>5.63</v>
       </c>
       <c r="H22" s="4">
-        <v>215382.39999999999</v>
+        <v>71073.47</v>
       </c>
       <c r="I22">
-        <v>1.89</v>
+        <v>3.36</v>
       </c>
       <c r="J22">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="K22">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="L22">
-        <v>85.55</v>
+        <v>95.34</v>
       </c>
       <c r="M22">
-        <v>-16.03</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1641,37 +1581,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>95300</v>
+        <v>14950</v>
       </c>
       <c r="D23" s="3">
-        <v>-7.3000000000000001E-3</v>
+        <v>-2.0299999999999999E-2</v>
       </c>
       <c r="E23">
-        <v>12.89</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F23">
-        <v>13.94</v>
+        <v>6.71</v>
       </c>
       <c r="G23">
-        <v>9.44</v>
+        <v>6.75</v>
       </c>
       <c r="H23" s="4">
-        <v>87743.72</v>
+        <v>20394.86</v>
       </c>
       <c r="I23">
-        <v>3.67</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="J23">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K23">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L23">
-        <v>94.61</v>
+        <v>92.39</v>
       </c>
       <c r="M23">
-        <v>-5.17</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1682,37 +1622,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>75000</v>
+        <v>216000</v>
       </c>
       <c r="D24" s="3">
-        <v>-1.5699999999999999E-2</v>
+        <v>-1.14E-2</v>
       </c>
       <c r="E24">
-        <v>10.83</v>
+        <v>4.66</v>
       </c>
       <c r="F24">
-        <v>3.37</v>
+        <v>4.66</v>
       </c>
       <c r="G24">
-        <v>9.48</v>
+        <v>4.88</v>
       </c>
       <c r="H24" s="4">
-        <v>54894.12</v>
+        <v>324173.33</v>
       </c>
       <c r="I24">
-        <v>4.72</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="J24">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K24">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="L24">
-        <v>95.85</v>
+        <v>99.93</v>
       </c>
       <c r="M24">
-        <v>-4.09</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1723,37 +1663,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>87900</v>
+        <v>153000</v>
       </c>
       <c r="D25" s="3">
-        <v>-2.3E-3</v>
+        <v>-1.67E-2</v>
       </c>
       <c r="E25">
-        <v>14.42</v>
+        <v>12.66</v>
       </c>
       <c r="F25">
-        <v>24.2</v>
+        <v>11.88</v>
       </c>
       <c r="G25">
-        <v>15.82</v>
+        <v>11.14</v>
       </c>
       <c r="H25" s="4">
-        <v>36460.550000000003</v>
+        <v>83639.03</v>
       </c>
       <c r="I25">
-        <v>6.26</v>
+        <v>3.53</v>
       </c>
       <c r="J25">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K25">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L25">
-        <v>90.33</v>
+        <v>92.71</v>
       </c>
       <c r="M25">
-        <v>-7.08</v>
+        <v>-5.73</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1764,37 +1704,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>23100</v>
+        <v>18140</v>
       </c>
       <c r="D26" s="3">
-        <v>-1.49E-2</v>
+        <v>-7.7000000000000002E-3</v>
       </c>
       <c r="E26">
-        <v>8.06</v>
+        <v>12.08</v>
       </c>
       <c r="F26">
-        <v>8.64</v>
+        <v>8.58</v>
       </c>
       <c r="G26">
-        <v>8.77</v>
+        <v>8.39</v>
       </c>
       <c r="H26" s="4">
-        <v>44443.18</v>
+        <v>19234.22</v>
       </c>
       <c r="I26">
-        <v>4.6100000000000003</v>
+        <v>6.45</v>
       </c>
       <c r="J26">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="K26">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="L26">
-        <v>92.41</v>
+        <v>97.47</v>
       </c>
       <c r="M26">
-        <v>-7.97</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1805,37 +1745,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>59100</v>
+        <v>35450</v>
       </c>
       <c r="D27" s="3">
-        <v>-2.64E-2</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="E27">
-        <v>7.45</v>
+        <v>11.21</v>
       </c>
       <c r="F27">
-        <v>7.45</v>
+        <v>6.55</v>
       </c>
       <c r="G27">
-        <v>7.69</v>
+        <v>6.4</v>
       </c>
       <c r="H27" s="4">
-        <v>79986.48</v>
+        <v>122131.86</v>
       </c>
       <c r="I27">
-        <v>4.74</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="J27">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="K27">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="L27">
-        <v>96.05</v>
+        <v>87.89</v>
       </c>
       <c r="M27">
-        <v>-4.5199999999999996</v>
+        <v>-12.68</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1846,37 +1786,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>20700</v>
+        <v>90800</v>
       </c>
       <c r="D28" s="3">
-        <v>-4.7999999999999996E-3</v>
+        <v>-1.2E-2</v>
       </c>
       <c r="E28">
-        <v>15.12</v>
+        <v>8.11</v>
       </c>
       <c r="F28">
-        <v>13.07</v>
+        <v>10.44</v>
       </c>
       <c r="G28">
-        <v>15.58</v>
+        <v>8.66</v>
       </c>
       <c r="H28" s="4">
-        <v>15310.06</v>
+        <v>119742.76</v>
       </c>
       <c r="I28">
-        <v>5.94</v>
+        <v>2.38</v>
       </c>
       <c r="J28">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="K28">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="L28">
-        <v>96.79</v>
+        <v>94.08</v>
       </c>
       <c r="M28">
-        <v>-3.04</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1887,37 +1827,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>59600</v>
+        <v>219500</v>
       </c>
       <c r="D29" s="3">
-        <v>-3.09E-2</v>
+        <v>-3.3000000000000002E-2</v>
       </c>
       <c r="E29">
-        <v>2.85</v>
+        <v>11.54</v>
       </c>
       <c r="F29">
-        <v>12.83</v>
+        <v>20.98</v>
       </c>
       <c r="G29">
-        <v>5.63</v>
+        <v>9.6</v>
       </c>
       <c r="H29" s="4">
-        <v>71073.47</v>
+        <v>189057.03</v>
       </c>
       <c r="I29">
-        <v>3.36</v>
+        <v>1.81</v>
       </c>
       <c r="J29">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K29">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L29">
-        <v>95.34</v>
+        <v>89.48</v>
       </c>
       <c r="M29">
-        <v>-5.4</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1928,37 +1868,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>14950</v>
+        <v>63800</v>
       </c>
       <c r="D30" s="3">
-        <v>-2.0299999999999999E-2</v>
+        <v>-3.7699999999999997E-2</v>
       </c>
       <c r="E30">
-        <v>4.4000000000000004</v>
+        <v>4.12</v>
       </c>
       <c r="F30">
-        <v>6.71</v>
+        <v>5.22</v>
       </c>
       <c r="G30">
-        <v>6.75</v>
+        <v>11.01</v>
       </c>
       <c r="H30" s="4">
-        <v>20394.86</v>
+        <v>151788</v>
       </c>
       <c r="I30">
-        <v>4.3499999999999996</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="J30">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K30">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L30">
-        <v>92.39</v>
+        <v>92.69</v>
       </c>
       <c r="M30">
-        <v>-7.2</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1969,37 +1909,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>216000</v>
+        <v>108900</v>
       </c>
       <c r="D31" s="3">
-        <v>-1.14E-2</v>
+        <v>-3.2000000000000001E-2</v>
       </c>
       <c r="E31">
-        <v>4.66</v>
+        <v>9.11</v>
       </c>
       <c r="F31">
-        <v>4.66</v>
+        <v>10.57</v>
       </c>
       <c r="G31">
-        <v>4.88</v>
+        <v>9.4</v>
       </c>
       <c r="H31" s="4">
-        <v>324173.33</v>
+        <v>159337.74</v>
       </c>
       <c r="I31">
-        <v>2.4500000000000002</v>
+        <v>3.31</v>
       </c>
       <c r="J31">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K31">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L31">
-        <v>99.93</v>
+        <v>91.1</v>
       </c>
       <c r="M31">
-        <v>-2.48</v>
+        <v>-9.33</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -2010,37 +1950,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>153000</v>
+        <v>148900</v>
       </c>
       <c r="D32" s="3">
-        <v>-1.67E-2</v>
+        <v>-2E-3</v>
       </c>
       <c r="E32">
-        <v>12.66</v>
+        <v>8.86</v>
       </c>
       <c r="F32">
-        <v>11.88</v>
+        <v>11.63</v>
       </c>
       <c r="G32">
-        <v>11.14</v>
+        <v>8.51</v>
       </c>
       <c r="H32" s="4">
-        <v>83639.03</v>
+        <v>160038.65</v>
       </c>
       <c r="I32">
-        <v>3.53</v>
+        <v>2.13</v>
       </c>
       <c r="J32">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K32">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L32">
-        <v>92.71</v>
+        <v>94.66</v>
       </c>
       <c r="M32">
-        <v>-5.73</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2051,37 +1991,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>18140</v>
+        <v>18270</v>
       </c>
       <c r="D33" s="3">
-        <v>-7.7000000000000002E-3</v>
+        <v>-2.0400000000000001E-2</v>
       </c>
       <c r="E33">
-        <v>12.08</v>
+        <v>6.96</v>
       </c>
       <c r="F33">
-        <v>8.58</v>
+        <v>9.58</v>
       </c>
       <c r="G33">
-        <v>8.39</v>
+        <v>7.18</v>
       </c>
       <c r="H33" s="4">
-        <v>19234.22</v>
+        <v>34223.949999999997</v>
       </c>
       <c r="I33">
-        <v>6.45</v>
+        <v>3.56</v>
       </c>
       <c r="J33">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="K33">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="L33">
-        <v>97.47</v>
+        <v>91.03</v>
       </c>
       <c r="M33">
-        <v>-3.2</v>
+        <v>-7.16</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2092,37 +2032,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>35450</v>
+        <v>16660</v>
       </c>
       <c r="D34" s="3">
-        <v>-1.7999999999999999E-2</v>
+        <v>-1.1900000000000001E-2</v>
       </c>
       <c r="E34">
-        <v>11.21</v>
+        <v>3.6</v>
       </c>
       <c r="F34">
-        <v>6.55</v>
+        <v>9.42</v>
       </c>
       <c r="G34">
-        <v>6.4</v>
+        <v>5.91</v>
       </c>
       <c r="H34" s="4">
-        <v>122131.86</v>
+        <v>38541.279999999999</v>
       </c>
       <c r="I34">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="J34">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="K34">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="L34">
-        <v>87.89</v>
+        <v>89.11</v>
       </c>
       <c r="M34">
-        <v>-12.68</v>
+        <v>-7.96</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2133,37 +2073,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>90800</v>
+        <v>55300</v>
       </c>
       <c r="D35" s="3">
-        <v>-1.2E-2</v>
+        <v>-3.9899999999999998E-2</v>
       </c>
       <c r="E35">
-        <v>8.11</v>
+        <v>10.79</v>
       </c>
       <c r="F35">
-        <v>10.44</v>
+        <v>10.55</v>
       </c>
       <c r="G35">
-        <v>8.66</v>
+        <v>8.93</v>
       </c>
       <c r="H35" s="4">
-        <v>119742.76</v>
+        <v>92723.77</v>
       </c>
       <c r="I35">
-        <v>2.38</v>
+        <v>3.62</v>
       </c>
       <c r="J35">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="K35">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="L35">
-        <v>94.08</v>
+        <v>82.06</v>
       </c>
       <c r="M35">
-        <v>-6.1</v>
+        <v>-17.22</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2174,37 +2114,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>219500</v>
+        <v>30500</v>
       </c>
       <c r="D36" s="3">
-        <v>-3.3000000000000002E-2</v>
+        <v>-2.24E-2</v>
       </c>
       <c r="E36">
-        <v>11.54</v>
+        <v>12.8</v>
       </c>
       <c r="F36">
-        <v>20.98</v>
+        <v>13.49</v>
       </c>
       <c r="G36">
-        <v>9.6</v>
+        <v>12.93</v>
       </c>
       <c r="H36" s="4">
-        <v>189057.03</v>
+        <v>31004.78</v>
       </c>
       <c r="I36">
-        <v>1.81</v>
+        <v>3.26</v>
       </c>
       <c r="J36">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K36">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L36">
-        <v>89.48</v>
+        <v>94.82</v>
       </c>
       <c r="M36">
-        <v>-8.73</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2215,37 +2155,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>63800</v>
+        <v>50500</v>
       </c>
       <c r="D37" s="3">
-        <v>-3.7699999999999997E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E37">
-        <v>4.12</v>
+        <v>18.690000000000001</v>
       </c>
       <c r="F37">
-        <v>5.22</v>
+        <v>11.56</v>
       </c>
       <c r="G37">
-        <v>11.01</v>
+        <v>6.83</v>
       </c>
       <c r="H37" s="4">
-        <v>151788</v>
+        <v>57293.3</v>
       </c>
       <c r="I37">
-        <v>4.2300000000000004</v>
+        <v>2.38</v>
       </c>
       <c r="J37">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="K37">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="L37">
-        <v>92.69</v>
+        <v>95.78</v>
       </c>
       <c r="M37">
-        <v>-9.5</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2256,446 +2196,36 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>108900</v>
+        <v>32200</v>
       </c>
       <c r="D38" s="3">
-        <v>-3.2000000000000001E-2</v>
+        <v>-9.1999999999999998E-3</v>
       </c>
       <c r="E38">
-        <v>9.11</v>
+        <v>9.39</v>
       </c>
       <c r="F38">
-        <v>10.57</v>
+        <v>10.74</v>
       </c>
       <c r="G38">
-        <v>9.4</v>
+        <v>9.73</v>
       </c>
       <c r="H38" s="4">
-        <v>159337.74</v>
+        <v>48211.77</v>
       </c>
       <c r="I38">
-        <v>3.31</v>
+        <v>3.73</v>
       </c>
       <c r="J38">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K38">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L38">
-        <v>91.1</v>
+        <v>89.49</v>
       </c>
       <c r="M38">
-        <v>-9.33</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A39" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="2">
-        <v>148900</v>
-      </c>
-      <c r="D39" s="3">
-        <v>-2E-3</v>
-      </c>
-      <c r="E39">
-        <v>8.86</v>
-      </c>
-      <c r="F39">
-        <v>11.63</v>
-      </c>
-      <c r="G39">
-        <v>8.51</v>
-      </c>
-      <c r="H39" s="4">
-        <v>160038.65</v>
-      </c>
-      <c r="I39">
-        <v>2.13</v>
-      </c>
-      <c r="J39">
-        <v>82</v>
-      </c>
-      <c r="K39">
-        <v>82</v>
-      </c>
-      <c r="L39">
-        <v>94.66</v>
-      </c>
-      <c r="M39">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A40" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="2">
-        <v>18270</v>
-      </c>
-      <c r="D40" s="3">
-        <v>-2.0400000000000001E-2</v>
-      </c>
-      <c r="E40">
-        <v>6.96</v>
-      </c>
-      <c r="F40">
-        <v>9.58</v>
-      </c>
-      <c r="G40">
-        <v>7.18</v>
-      </c>
-      <c r="H40" s="4">
-        <v>34223.949999999997</v>
-      </c>
-      <c r="I40">
-        <v>3.56</v>
-      </c>
-      <c r="J40">
-        <v>72</v>
-      </c>
-      <c r="K40">
-        <v>72</v>
-      </c>
-      <c r="L40">
-        <v>91.03</v>
-      </c>
-      <c r="M40">
-        <v>-7.16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A41" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B41" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="2">
-        <v>16660</v>
-      </c>
-      <c r="D41" s="3">
-        <v>-1.1900000000000001E-2</v>
-      </c>
-      <c r="E41">
-        <v>3.6</v>
-      </c>
-      <c r="F41">
-        <v>9.42</v>
-      </c>
-      <c r="G41">
-        <v>5.91</v>
-      </c>
-      <c r="H41" s="4">
-        <v>38541.279999999999</v>
-      </c>
-      <c r="I41">
-        <v>3</v>
-      </c>
-      <c r="J41">
-        <v>65</v>
-      </c>
-      <c r="K41">
-        <v>65</v>
-      </c>
-      <c r="L41">
-        <v>89.11</v>
-      </c>
-      <c r="M41">
-        <v>-7.96</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A42" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B42" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42" s="2">
-        <v>55300</v>
-      </c>
-      <c r="D42" s="3">
-        <v>-3.9899999999999998E-2</v>
-      </c>
-      <c r="E42">
-        <v>10.79</v>
-      </c>
-      <c r="F42">
-        <v>10.55</v>
-      </c>
-      <c r="G42">
-        <v>8.93</v>
-      </c>
-      <c r="H42" s="4">
-        <v>92723.77</v>
-      </c>
-      <c r="I42">
-        <v>3.62</v>
-      </c>
-      <c r="J42">
-        <v>52</v>
-      </c>
-      <c r="K42">
-        <v>52</v>
-      </c>
-      <c r="L42">
-        <v>82.06</v>
-      </c>
-      <c r="M42">
-        <v>-17.22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A43" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B43" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" s="2">
-        <v>30500</v>
-      </c>
-      <c r="D43" s="3">
-        <v>-2.24E-2</v>
-      </c>
-      <c r="E43">
-        <v>12.8</v>
-      </c>
-      <c r="F43">
-        <v>13.49</v>
-      </c>
-      <c r="G43">
-        <v>12.93</v>
-      </c>
-      <c r="H43" s="4">
-        <v>31004.78</v>
-      </c>
-      <c r="I43">
-        <v>3.26</v>
-      </c>
-      <c r="J43">
-        <v>75</v>
-      </c>
-      <c r="K43">
-        <v>75</v>
-      </c>
-      <c r="L43">
-        <v>94.82</v>
-      </c>
-      <c r="M43">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A44" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B44" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" s="2">
-        <v>12030</v>
-      </c>
-      <c r="D44" s="3">
-        <v>-8.0000000000000004E-4</v>
-      </c>
-      <c r="E44">
-        <v>7.65</v>
-      </c>
-      <c r="F44">
-        <v>4</v>
-      </c>
-      <c r="G44">
-        <v>7.8</v>
-      </c>
-      <c r="H44" s="4">
-        <v>30039.25</v>
-      </c>
-      <c r="I44">
-        <v>2.16</v>
-      </c>
-      <c r="J44">
-        <v>38</v>
-      </c>
-      <c r="K44">
-        <v>38</v>
-      </c>
-      <c r="L44">
-        <v>94.85</v>
-      </c>
-      <c r="M44">
-        <v>-2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A45" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="2">
-        <v>50500</v>
-      </c>
-      <c r="D45" s="3">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="E45">
-        <v>18.690000000000001</v>
-      </c>
-      <c r="F45">
-        <v>11.56</v>
-      </c>
-      <c r="G45">
-        <v>6.83</v>
-      </c>
-      <c r="H45" s="4">
-        <v>57293.3</v>
-      </c>
-      <c r="I45">
-        <v>2.38</v>
-      </c>
-      <c r="J45">
-        <v>46</v>
-      </c>
-      <c r="K45">
-        <v>46</v>
-      </c>
-      <c r="L45">
-        <v>95.78</v>
-      </c>
-      <c r="M45">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A46" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B46" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" s="2">
-        <v>19590</v>
-      </c>
-      <c r="D46" s="3">
-        <v>2E-3</v>
-      </c>
-      <c r="E46">
-        <v>10.48</v>
-      </c>
-      <c r="F46">
-        <v>7.97</v>
-      </c>
-      <c r="G46">
-        <v>10.17</v>
-      </c>
-      <c r="H46" s="4">
-        <v>25607.22</v>
-      </c>
-      <c r="I46">
-        <v>6</v>
-      </c>
-      <c r="J46">
-        <v>19</v>
-      </c>
-      <c r="K46">
-        <v>19</v>
-      </c>
-      <c r="L46">
-        <v>98.95</v>
-      </c>
-      <c r="M46">
-        <v>-1.1100000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A47" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B47" t="s">
-        <v>102</v>
-      </c>
-      <c r="C47" s="2">
-        <v>16800</v>
-      </c>
-      <c r="D47" s="3">
-        <v>-1.47E-2</v>
-      </c>
-      <c r="E47">
-        <v>11.13</v>
-      </c>
-      <c r="F47">
-        <v>5.01</v>
-      </c>
-      <c r="G47">
-        <v>9.31</v>
-      </c>
-      <c r="H47" s="4">
-        <v>24921.41</v>
-      </c>
-      <c r="I47">
-        <v>5.95</v>
-      </c>
-      <c r="J47">
-        <v>40</v>
-      </c>
-      <c r="K47">
-        <v>40</v>
-      </c>
-      <c r="L47">
-        <v>95.91</v>
-      </c>
-      <c r="M47">
-        <v>-4.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A48" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B48" t="s">
-        <v>104</v>
-      </c>
-      <c r="C48" s="2">
-        <v>32200</v>
-      </c>
-      <c r="D48" s="3">
-        <v>-9.1999999999999998E-3</v>
-      </c>
-      <c r="E48">
-        <v>9.39</v>
-      </c>
-      <c r="F48">
-        <v>10.74</v>
-      </c>
-      <c r="G48">
-        <v>9.73</v>
-      </c>
-      <c r="H48" s="4">
-        <v>48211.77</v>
-      </c>
-      <c r="I48">
-        <v>3.73</v>
-      </c>
-      <c r="J48">
-        <v>70</v>
-      </c>
-      <c r="K48">
-        <v>70</v>
-      </c>
-      <c r="L48">
-        <v>89.49</v>
-      </c>
-      <c r="M48">
         <v>-8.7799999999999994</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E823FAB5-372C-4567-80AA-C747605F1500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E4AE669-5DC2-4DB4-9E7E-CAF049F3002C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{22A44216-7F7E-41A0-96E1-E4AAA6A3C645}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C76E860B-E7E0-43BA-9A85-C443069AA07F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -654,7 +654,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27312FCD-872D-4C85-BA66-81C56918FE28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB30139A-664F-4D07-8A37-80CE9D00ECA4}">
   <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -720,10 +720,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>25250</v>
+        <v>26150</v>
       </c>
       <c r="D2" s="3">
-        <v>-2.3199999999999998E-2</v>
+        <v>5.2299999999999999E-2</v>
       </c>
       <c r="E2">
         <v>8.2799999999999994</v>
@@ -738,19 +738,19 @@
         <v>48390.96</v>
       </c>
       <c r="I2">
-        <v>3.96</v>
+        <v>3.82</v>
       </c>
       <c r="J2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L2">
-        <v>86.45</v>
+        <v>91.11</v>
       </c>
       <c r="M2">
-        <v>-12.02</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -761,10 +761,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>164300</v>
+        <v>167300</v>
       </c>
       <c r="D3" s="3">
-        <v>-1.6199999999999999E-2</v>
+        <v>3.27E-2</v>
       </c>
       <c r="E3">
         <v>19.09</v>
@@ -779,19 +779,19 @@
         <v>150938.41</v>
       </c>
       <c r="I3">
-        <v>3.96</v>
+        <v>3.89</v>
       </c>
       <c r="J3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L3">
-        <v>95.99</v>
+        <v>97.38</v>
       </c>
       <c r="M3">
-        <v>-9.8699999999999992</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -802,10 +802,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>474000</v>
+        <v>477500</v>
       </c>
       <c r="D4" s="3">
-        <v>-3.27E-2</v>
+        <v>2.69E-2</v>
       </c>
       <c r="E4">
         <v>13.09</v>
@@ -820,19 +820,19 @@
         <v>405451.96</v>
       </c>
       <c r="I4">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="J4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L4">
-        <v>89.79</v>
+        <v>91.68</v>
       </c>
       <c r="M4">
-        <v>-9.1999999999999993</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -843,10 +843,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>43300</v>
+        <v>45000</v>
       </c>
       <c r="D5" s="3">
-        <v>-1.03E-2</v>
+        <v>-9.9000000000000008E-3</v>
       </c>
       <c r="E5">
         <v>7.12</v>
@@ -861,19 +861,19 @@
         <v>72041.39</v>
       </c>
       <c r="I5">
-        <v>4.62</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="J5">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K5">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L5">
-        <v>98.79</v>
+        <v>102.24</v>
       </c>
       <c r="M5">
-        <v>0.23</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -884,10 +884,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>81500</v>
+        <v>77600</v>
       </c>
       <c r="D6" s="3">
-        <v>-6.1100000000000002E-2</v>
+        <v>-8.8999999999999999E-3</v>
       </c>
       <c r="E6">
         <v>4.05</v>
@@ -902,19 +902,19 @@
         <v>65679.45</v>
       </c>
       <c r="I6">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="J6">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K6">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="L6">
-        <v>97.95</v>
+        <v>92.73</v>
       </c>
       <c r="M6">
-        <v>2.2599999999999998</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -925,10 +925,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>70500</v>
+        <v>68200</v>
       </c>
       <c r="D7" s="3">
-        <v>-1.12E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="E7">
         <v>1.04</v>
@@ -943,19 +943,19 @@
         <v>53899.69</v>
       </c>
       <c r="I7">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="J7">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K7">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L7">
-        <v>102.02</v>
+        <v>100.18</v>
       </c>
       <c r="M7">
-        <v>5.22</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -966,10 +966,10 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>39850</v>
+        <v>39700</v>
       </c>
       <c r="D8" s="3">
-        <v>-1.2999999999999999E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="E8">
         <v>4.57</v>
@@ -984,19 +984,19 @@
         <v>42814.52</v>
       </c>
       <c r="I8">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="J8">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K8">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L8">
-        <v>96.31</v>
+        <v>94.91</v>
       </c>
       <c r="M8">
-        <v>-3.74</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1007,10 +1007,10 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>90000</v>
+        <v>91000</v>
       </c>
       <c r="D9" s="3">
-        <v>-3.0200000000000001E-2</v>
+        <v>2.7099999999999999E-2</v>
       </c>
       <c r="E9">
         <v>2.16</v>
@@ -1025,19 +1025,19 @@
         <v>177736.27</v>
       </c>
       <c r="I9">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="J9">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K9">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L9">
-        <v>93.17</v>
+        <v>94.77</v>
       </c>
       <c r="M9">
-        <v>-12.2</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1048,10 +1048,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>13160</v>
+        <v>13150</v>
       </c>
       <c r="D10" s="3">
-        <v>-4.0099999999999997E-2</v>
+        <v>1.54E-2</v>
       </c>
       <c r="E10">
         <v>9.44</v>
@@ -1066,7 +1066,7 @@
         <v>19219.419999999998</v>
       </c>
       <c r="I10">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="J10">
         <v>80</v>
@@ -1075,10 +1075,10 @@
         <v>80</v>
       </c>
       <c r="L10">
-        <v>97.7</v>
+        <v>97.62</v>
       </c>
       <c r="M10">
-        <v>-2.16</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1089,10 +1089,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>517000</v>
+        <v>522000</v>
       </c>
       <c r="D11" s="3">
-        <v>-7.7000000000000002E-3</v>
+        <v>3.1600000000000003E-2</v>
       </c>
       <c r="E11">
         <v>12.43</v>
@@ -1107,19 +1107,19 @@
         <v>429918.88</v>
       </c>
       <c r="I11">
-        <v>2.3199999999999998</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J11">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K11">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L11">
-        <v>96.5</v>
+        <v>97.08</v>
       </c>
       <c r="M11">
-        <v>-13.11</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1130,10 +1130,10 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>177300</v>
+        <v>179100</v>
       </c>
       <c r="D12" s="3">
-        <v>-3.8999999999999998E-3</v>
+        <v>1.3599999999999999E-2</v>
       </c>
       <c r="E12">
         <v>18.96</v>
@@ -1148,19 +1148,19 @@
         <v>144109.65</v>
       </c>
       <c r="I12">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="J12">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K12">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L12">
-        <v>95.35</v>
+        <v>96.15</v>
       </c>
       <c r="M12">
-        <v>-5.03</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1171,10 +1171,10 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>31700</v>
+        <v>32400</v>
       </c>
       <c r="D13" s="3">
-        <v>-2.6100000000000002E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="E13">
         <v>8.73</v>
@@ -1189,19 +1189,19 @@
         <v>24348.21</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="J13">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K13">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L13">
-        <v>95.71</v>
+        <v>96.84</v>
       </c>
       <c r="M13">
-        <v>-4.8</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1212,10 +1212,10 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>27600</v>
+        <v>35800</v>
       </c>
       <c r="D14" s="3">
-        <v>-1.8E-3</v>
+        <v>-1.4E-3</v>
       </c>
       <c r="E14">
         <v>19.78</v>
@@ -1230,19 +1230,19 @@
         <v>32624.26</v>
       </c>
       <c r="I14">
-        <v>3.62</v>
+        <v>2.79</v>
       </c>
       <c r="J14">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="K14">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="L14">
-        <v>97</v>
+        <v>122.84</v>
       </c>
       <c r="M14">
-        <v>4.1500000000000004</v>
+        <v>46.12</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1253,10 +1253,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>223000</v>
+        <v>225000</v>
       </c>
       <c r="D15" s="3">
-        <v>-6.3E-2</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="E15">
         <v>13.17</v>
@@ -1271,19 +1271,19 @@
         <v>207156.6</v>
       </c>
       <c r="I15">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J15">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K15">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L15">
-        <v>96.22</v>
+        <v>97.31</v>
       </c>
       <c r="M15">
-        <v>-8.61</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1294,10 +1294,10 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>95300</v>
+        <v>97400</v>
       </c>
       <c r="D16" s="3">
-        <v>-7.3000000000000001E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="E16">
         <v>12.89</v>
@@ -1312,19 +1312,19 @@
         <v>87743.72</v>
       </c>
       <c r="I16">
-        <v>3.67</v>
+        <v>3.59</v>
       </c>
       <c r="J16">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K16">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L16">
-        <v>94.61</v>
+        <v>96.57</v>
       </c>
       <c r="M16">
-        <v>-5.17</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1335,10 +1335,10 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>75000</v>
+        <v>79700</v>
       </c>
       <c r="D17" s="3">
-        <v>-1.5699999999999999E-2</v>
+        <v>4.4600000000000001E-2</v>
       </c>
       <c r="E17">
         <v>10.83</v>
@@ -1353,19 +1353,19 @@
         <v>54894.12</v>
       </c>
       <c r="I17">
-        <v>4.72</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="J17">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K17">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L17">
-        <v>95.85</v>
+        <v>101.41</v>
       </c>
       <c r="M17">
-        <v>-4.09</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1376,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>87900</v>
+        <v>87100</v>
       </c>
       <c r="D18" s="3">
-        <v>-2.3E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="E18">
         <v>14.42</v>
@@ -1394,19 +1394,19 @@
         <v>36460.550000000003</v>
       </c>
       <c r="I18">
-        <v>6.26</v>
+        <v>6.31</v>
       </c>
       <c r="J18">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K18">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L18">
-        <v>90.33</v>
+        <v>91.03</v>
       </c>
       <c r="M18">
-        <v>-7.08</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1417,10 +1417,10 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>23100</v>
+        <v>23200</v>
       </c>
       <c r="D19" s="3">
-        <v>-1.49E-2</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="E19">
         <v>8.06</v>
@@ -1435,7 +1435,7 @@
         <v>44443.18</v>
       </c>
       <c r="I19">
-        <v>4.6100000000000003</v>
+        <v>4.59</v>
       </c>
       <c r="J19">
         <v>69</v>
@@ -1444,10 +1444,10 @@
         <v>69</v>
       </c>
       <c r="L19">
-        <v>92.41</v>
+        <v>93.39</v>
       </c>
       <c r="M19">
-        <v>-7.97</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1458,10 +1458,10 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>59100</v>
+        <v>58600</v>
       </c>
       <c r="D20" s="3">
-        <v>-2.64E-2</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="E20">
         <v>7.45</v>
@@ -1476,19 +1476,19 @@
         <v>79986.48</v>
       </c>
       <c r="I20">
-        <v>4.74</v>
+        <v>4.78</v>
       </c>
       <c r="J20">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K20">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L20">
-        <v>96.05</v>
+        <v>95.6</v>
       </c>
       <c r="M20">
-        <v>-4.5199999999999996</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1499,10 +1499,10 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>20700</v>
+        <v>20800</v>
       </c>
       <c r="D21" s="3">
-        <v>-4.7999999999999996E-3</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="E21">
         <v>15.12</v>
@@ -1517,19 +1517,19 @@
         <v>15310.06</v>
       </c>
       <c r="I21">
-        <v>5.94</v>
+        <v>5.91</v>
       </c>
       <c r="J21">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K21">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L21">
-        <v>96.79</v>
+        <v>97.76</v>
       </c>
       <c r="M21">
-        <v>-3.04</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1540,10 +1540,10 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>59600</v>
+        <v>60000</v>
       </c>
       <c r="D22" s="3">
-        <v>-3.09E-2</v>
+        <v>1.8700000000000001E-2</v>
       </c>
       <c r="E22">
         <v>2.85</v>
@@ -1558,19 +1558,19 @@
         <v>71073.47</v>
       </c>
       <c r="I22">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="J22">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K22">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L22">
-        <v>95.34</v>
+        <v>96.32</v>
       </c>
       <c r="M22">
-        <v>-5.4</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1581,10 +1581,10 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>14950</v>
+        <v>15800</v>
       </c>
       <c r="D23" s="3">
-        <v>-2.0299999999999999E-2</v>
+        <v>3.95E-2</v>
       </c>
       <c r="E23">
         <v>4.4000000000000004</v>
@@ -1599,19 +1599,19 @@
         <v>20394.86</v>
       </c>
       <c r="I23">
-        <v>4.3499999999999996</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="J23">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K23">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="L23">
-        <v>92.39</v>
+        <v>98.12</v>
       </c>
       <c r="M23">
-        <v>-7.2</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1622,10 +1622,10 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>216000</v>
+        <v>217000</v>
       </c>
       <c r="D24" s="3">
-        <v>-1.14E-2</v>
+        <v>2.3599999999999999E-2</v>
       </c>
       <c r="E24">
         <v>4.66</v>
@@ -1640,7 +1640,7 @@
         <v>324173.33</v>
       </c>
       <c r="I24">
-        <v>2.4500000000000002</v>
+        <v>2.44</v>
       </c>
       <c r="J24">
         <v>79</v>
@@ -1649,10 +1649,10 @@
         <v>79</v>
       </c>
       <c r="L24">
-        <v>99.93</v>
+        <v>99.67</v>
       </c>
       <c r="M24">
-        <v>-2.48</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1663,10 +1663,10 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>153000</v>
+        <v>155500</v>
       </c>
       <c r="D25" s="3">
-        <v>-1.67E-2</v>
+        <v>1.9699999999999999E-2</v>
       </c>
       <c r="E25">
         <v>12.66</v>
@@ -1681,19 +1681,19 @@
         <v>83639.03</v>
       </c>
       <c r="I25">
-        <v>3.53</v>
+        <v>3.47</v>
       </c>
       <c r="J25">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K25">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L25">
-        <v>92.71</v>
+        <v>95.25</v>
       </c>
       <c r="M25">
-        <v>-5.73</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1704,10 +1704,10 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>18140</v>
+        <v>18100</v>
       </c>
       <c r="D26" s="3">
-        <v>-7.7000000000000002E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="E26">
         <v>12.08</v>
@@ -1722,7 +1722,7 @@
         <v>19234.22</v>
       </c>
       <c r="I26">
-        <v>6.45</v>
+        <v>6.46</v>
       </c>
       <c r="J26">
         <v>29</v>
@@ -1734,7 +1734,7 @@
         <v>97.47</v>
       </c>
       <c r="M26">
-        <v>-3.2</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1745,10 +1745,10 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>35450</v>
+        <v>34800</v>
       </c>
       <c r="D27" s="3">
-        <v>-1.7999999999999999E-2</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="E27">
         <v>11.21</v>
@@ -1763,19 +1763,19 @@
         <v>122131.86</v>
       </c>
       <c r="I27">
-        <v>4.0999999999999996</v>
+        <v>4.18</v>
       </c>
       <c r="J27">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K27">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L27">
-        <v>87.89</v>
+        <v>87.98</v>
       </c>
       <c r="M27">
-        <v>-12.68</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1786,10 +1786,10 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>90800</v>
+        <v>91200</v>
       </c>
       <c r="D28" s="3">
-        <v>-1.2E-2</v>
+        <v>1.3299999999999999E-2</v>
       </c>
       <c r="E28">
         <v>8.11</v>
@@ -1804,19 +1804,19 @@
         <v>119742.76</v>
       </c>
       <c r="I28">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="J28">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K28">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L28">
-        <v>94.08</v>
+        <v>95.36</v>
       </c>
       <c r="M28">
-        <v>-6.1</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1827,10 +1827,10 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>219500</v>
+        <v>233500</v>
       </c>
       <c r="D29" s="3">
-        <v>-3.3000000000000002E-2</v>
+        <v>4.4699999999999997E-2</v>
       </c>
       <c r="E29">
         <v>11.54</v>
@@ -1845,19 +1845,19 @@
         <v>189057.03</v>
       </c>
       <c r="I29">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="J29">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K29">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="L29">
-        <v>89.48</v>
+        <v>95.29</v>
       </c>
       <c r="M29">
-        <v>-8.73</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1868,10 +1868,10 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>63800</v>
+        <v>64200</v>
       </c>
       <c r="D30" s="3">
-        <v>-3.7699999999999997E-2</v>
+        <v>3.0499999999999999E-2</v>
       </c>
       <c r="E30">
         <v>4.12</v>
@@ -1886,19 +1886,19 @@
         <v>151788</v>
       </c>
       <c r="I30">
-        <v>4.2300000000000004</v>
+        <v>4.21</v>
       </c>
       <c r="J30">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K30">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L30">
-        <v>92.69</v>
+        <v>94.18</v>
       </c>
       <c r="M30">
-        <v>-9.5</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1909,10 +1909,10 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>108900</v>
+        <v>109900</v>
       </c>
       <c r="D31" s="3">
-        <v>-3.2000000000000001E-2</v>
+        <v>1.38E-2</v>
       </c>
       <c r="E31">
         <v>9.11</v>
@@ -1927,19 +1927,19 @@
         <v>159337.74</v>
       </c>
       <c r="I31">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="J31">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K31">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L31">
-        <v>91.1</v>
+        <v>93.09</v>
       </c>
       <c r="M31">
-        <v>-9.33</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1950,10 +1950,10 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>148900</v>
+        <v>150700</v>
       </c>
       <c r="D32" s="3">
-        <v>-2E-3</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="E32">
         <v>8.86</v>
@@ -1968,19 +1968,19 @@
         <v>160038.65</v>
       </c>
       <c r="I32">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="J32">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K32">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L32">
-        <v>94.66</v>
+        <v>96.41</v>
       </c>
       <c r="M32">
-        <v>-3</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -1991,10 +1991,10 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>18270</v>
+        <v>18480</v>
       </c>
       <c r="D33" s="3">
-        <v>-2.0400000000000001E-2</v>
+        <v>1.8700000000000001E-2</v>
       </c>
       <c r="E33">
         <v>6.96</v>
@@ -2009,19 +2009,19 @@
         <v>34223.949999999997</v>
       </c>
       <c r="I33">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="J33">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K33">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L33">
-        <v>91.03</v>
+        <v>92.85</v>
       </c>
       <c r="M33">
-        <v>-7.16</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2032,10 +2032,10 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>16660</v>
+        <v>16580</v>
       </c>
       <c r="D34" s="3">
-        <v>-1.1900000000000001E-2</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="E34">
         <v>3.6</v>
@@ -2050,7 +2050,7 @@
         <v>38541.279999999999</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="J34">
         <v>65</v>
@@ -2059,10 +2059,10 @@
         <v>65</v>
       </c>
       <c r="L34">
-        <v>89.11</v>
+        <v>89.87</v>
       </c>
       <c r="M34">
-        <v>-7.96</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2073,10 +2073,10 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>55300</v>
+        <v>56300</v>
       </c>
       <c r="D35" s="3">
-        <v>-3.9899999999999998E-2</v>
+        <v>4.2599999999999999E-2</v>
       </c>
       <c r="E35">
         <v>10.79</v>
@@ -2091,19 +2091,19 @@
         <v>92723.77</v>
       </c>
       <c r="I35">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="J35">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K35">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L35">
-        <v>82.06</v>
+        <v>85.84</v>
       </c>
       <c r="M35">
-        <v>-17.22</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2114,10 +2114,10 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>30500</v>
+        <v>29450</v>
       </c>
       <c r="D36" s="3">
-        <v>-2.24E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="E36">
         <v>12.8</v>
@@ -2132,19 +2132,19 @@
         <v>31004.78</v>
       </c>
       <c r="I36">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="J36">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K36">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L36">
-        <v>94.82</v>
+        <v>92.03</v>
       </c>
       <c r="M36">
-        <v>-2.09</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2158,7 +2158,7 @@
         <v>50500</v>
       </c>
       <c r="D37" s="3">
-        <v>6.0000000000000001E-3</v>
+        <v>1.7100000000000001E-2</v>
       </c>
       <c r="E37">
         <v>18.690000000000001</v>
@@ -2182,10 +2182,10 @@
         <v>46</v>
       </c>
       <c r="L37">
-        <v>95.78</v>
+        <v>96.93</v>
       </c>
       <c r="M37">
-        <v>-2.7</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2196,10 +2196,10 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>32200</v>
+        <v>32600</v>
       </c>
       <c r="D38" s="3">
-        <v>-9.1999999999999998E-3</v>
+        <v>2.1899999999999999E-2</v>
       </c>
       <c r="E38">
         <v>9.39</v>
@@ -2214,19 +2214,19 @@
         <v>48211.77</v>
       </c>
       <c r="I38">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="J38">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K38">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L38">
-        <v>89.49</v>
+        <v>91.75</v>
       </c>
       <c r="M38">
-        <v>-8.7799999999999994</v>
+        <v>-3.41</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E4AE669-5DC2-4DB4-9E7E-CAF049F3002C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABC8D7DC-3D83-4A6A-8ED3-6C60F500471C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C76E860B-E7E0-43BA-9A85-C443069AA07F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{36C78BB6-8F28-4183-9D30-D521DE27668D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -325,7 +325,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -339,6 +339,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -654,7 +657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB30139A-664F-4D07-8A37-80CE9D00ECA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{624B7A42-B1FA-4DA3-9EA1-3E220A9BE1F9}">
   <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -720,10 +723,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>26150</v>
+        <v>27100</v>
       </c>
       <c r="D2" s="3">
-        <v>5.2299999999999999E-2</v>
+        <v>1.8800000000000001E-2</v>
       </c>
       <c r="E2">
         <v>8.2799999999999994</v>
@@ -738,19 +741,19 @@
         <v>48390.96</v>
       </c>
       <c r="I2">
-        <v>3.82</v>
+        <v>3.69</v>
       </c>
       <c r="J2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L2">
-        <v>91.11</v>
+        <v>96.42</v>
       </c>
       <c r="M2">
-        <v>1.36</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -761,37 +764,37 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>167300</v>
+        <v>168500</v>
       </c>
       <c r="D3" s="3">
-        <v>3.27E-2</v>
+        <v>-1.17E-2</v>
       </c>
       <c r="E3">
-        <v>19.09</v>
+        <v>12.92</v>
       </c>
       <c r="F3">
-        <v>14.17</v>
+        <v>12.92</v>
       </c>
       <c r="G3">
-        <v>18.03</v>
+        <v>17.48</v>
       </c>
       <c r="H3" s="4">
-        <v>150938.41</v>
+        <v>157169.68</v>
       </c>
       <c r="I3">
-        <v>3.89</v>
+        <v>4.04</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L3">
-        <v>97.38</v>
+        <v>97.69</v>
       </c>
       <c r="M3">
-        <v>0.54</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -802,10 +805,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>477500</v>
+        <v>474500</v>
       </c>
       <c r="D4" s="3">
-        <v>2.69E-2</v>
+        <v>-8.3999999999999995E-3</v>
       </c>
       <c r="E4">
         <v>13.09</v>
@@ -820,19 +823,19 @@
         <v>405451.96</v>
       </c>
       <c r="I4">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K4">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L4">
-        <v>91.68</v>
+        <v>93.46</v>
       </c>
       <c r="M4">
-        <v>-2.85</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -843,10 +846,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>45000</v>
+        <v>47150</v>
       </c>
       <c r="D5" s="3">
-        <v>-9.9000000000000008E-3</v>
+        <v>5.96E-2</v>
       </c>
       <c r="E5">
         <v>7.12</v>
@@ -861,19 +864,19 @@
         <v>72041.39</v>
       </c>
       <c r="I5">
-        <v>4.4400000000000004</v>
+        <v>4.24</v>
       </c>
       <c r="J5">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K5">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="L5">
-        <v>102.24</v>
+        <v>107.59</v>
       </c>
       <c r="M5">
-        <v>13.21</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -884,10 +887,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>77600</v>
+        <v>78600</v>
       </c>
       <c r="D6" s="3">
-        <v>-8.8999999999999999E-3</v>
+        <v>1.95E-2</v>
       </c>
       <c r="E6">
         <v>4.05</v>
@@ -902,19 +905,19 @@
         <v>65679.45</v>
       </c>
       <c r="I6">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J6">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K6">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L6">
-        <v>92.73</v>
+        <v>94.13</v>
       </c>
       <c r="M6">
-        <v>0.52</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -925,10 +928,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>68200</v>
+        <v>66200</v>
       </c>
       <c r="D7" s="3">
-        <v>1.34E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="E7">
         <v>1.04</v>
@@ -943,19 +946,19 @@
         <v>53899.69</v>
       </c>
       <c r="I7">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="J7">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K7">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L7">
-        <v>100.18</v>
+        <v>98.89</v>
       </c>
       <c r="M7">
-        <v>11.8</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -966,10 +969,10 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>39700</v>
+        <v>40350</v>
       </c>
       <c r="D8" s="3">
-        <v>1.2999999999999999E-3</v>
+        <v>1.77E-2</v>
       </c>
       <c r="E8">
         <v>4.57</v>
@@ -984,19 +987,19 @@
         <v>42814.52</v>
       </c>
       <c r="I8">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="J8">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K8">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L8">
-        <v>94.91</v>
+        <v>96.72</v>
       </c>
       <c r="M8">
-        <v>-0.5</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1007,10 +1010,10 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>91000</v>
+        <v>95500</v>
       </c>
       <c r="D9" s="3">
-        <v>2.7099999999999999E-2</v>
+        <v>5.5199999999999999E-2</v>
       </c>
       <c r="E9">
         <v>2.16</v>
@@ -1025,19 +1028,19 @@
         <v>177736.27</v>
       </c>
       <c r="I9">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="J9">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K9">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="L9">
-        <v>94.77</v>
+        <v>99.9</v>
       </c>
       <c r="M9">
-        <v>-5.99</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1048,10 +1051,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>13150</v>
+        <v>13170</v>
       </c>
       <c r="D10" s="3">
-        <v>1.54E-2</v>
+        <v>5.3E-3</v>
       </c>
       <c r="E10">
         <v>9.44</v>
@@ -1066,7 +1069,7 @@
         <v>19219.419999999998</v>
       </c>
       <c r="I10">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="J10">
         <v>80</v>
@@ -1075,10 +1078,10 @@
         <v>80</v>
       </c>
       <c r="L10">
-        <v>97.62</v>
+        <v>98.16</v>
       </c>
       <c r="M10">
-        <v>0.31</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1089,37 +1092,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>522000</v>
+        <v>517000</v>
       </c>
       <c r="D11" s="3">
-        <v>3.1600000000000003E-2</v>
+        <v>-9.5999999999999992E-3</v>
       </c>
       <c r="E11">
-        <v>12.43</v>
+        <v>8.41</v>
       </c>
       <c r="F11">
-        <v>10.08</v>
+        <v>8.41</v>
       </c>
       <c r="G11">
-        <v>11.82</v>
+        <v>11.51</v>
       </c>
       <c r="H11" s="4">
-        <v>429918.88</v>
+        <v>436418.31</v>
       </c>
       <c r="I11">
-        <v>2.2999999999999998</v>
+        <v>1.93</v>
       </c>
       <c r="J11">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K11">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L11">
-        <v>97.08</v>
+        <v>95.56</v>
       </c>
       <c r="M11">
-        <v>-4.74</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1130,10 +1133,10 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>179100</v>
+        <v>186700</v>
       </c>
       <c r="D12" s="3">
-        <v>1.3599999999999999E-2</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="E12">
         <v>18.96</v>
@@ -1148,19 +1151,19 @@
         <v>144109.65</v>
       </c>
       <c r="I12">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="J12">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K12">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L12">
-        <v>96.15</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>-6.03</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1171,10 +1174,10 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>32400</v>
+        <v>35600</v>
       </c>
       <c r="D13" s="3">
-        <v>2.0500000000000001E-2</v>
+        <v>6.59E-2</v>
       </c>
       <c r="E13">
         <v>8.73</v>
@@ -1189,19 +1192,19 @@
         <v>24348.21</v>
       </c>
       <c r="I13">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="J13">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K13">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L13">
-        <v>96.84</v>
+        <v>105.4</v>
       </c>
       <c r="M13">
-        <v>1.0900000000000001</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1212,37 +1215,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>35800</v>
+        <v>39750</v>
       </c>
       <c r="D14" s="3">
-        <v>-1.4E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="E14">
-        <v>19.78</v>
+        <v>15.02</v>
       </c>
       <c r="F14">
-        <v>13.82</v>
+        <v>15.02</v>
       </c>
       <c r="G14">
-        <v>23.29</v>
+        <v>20.7</v>
       </c>
       <c r="H14" s="4">
-        <v>32624.26</v>
+        <v>34750.239999999998</v>
       </c>
       <c r="I14">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
       <c r="J14">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K14">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L14">
-        <v>122.84</v>
+        <v>131.59</v>
       </c>
       <c r="M14">
-        <v>46.12</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1253,10 +1256,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>225000</v>
+        <v>227000</v>
       </c>
       <c r="D15" s="3">
-        <v>2.7400000000000001E-2</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="E15">
         <v>13.17</v>
@@ -1271,19 +1274,19 @@
         <v>207156.6</v>
       </c>
       <c r="I15">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J15">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K15">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L15">
-        <v>97.31</v>
+        <v>98.43</v>
       </c>
       <c r="M15">
-        <v>-0.88</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1294,10 +1297,10 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>97400</v>
+        <v>102300</v>
       </c>
       <c r="D16" s="3">
-        <v>8.3000000000000001E-3</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="E16">
         <v>12.89</v>
@@ -1312,19 +1315,19 @@
         <v>87743.72</v>
       </c>
       <c r="I16">
-        <v>3.59</v>
+        <v>3.42</v>
       </c>
       <c r="J16">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K16">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L16">
-        <v>96.57</v>
+        <v>101.8</v>
       </c>
       <c r="M16">
-        <v>2.31</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1335,37 +1338,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>79700</v>
+        <v>78800</v>
       </c>
       <c r="D17" s="3">
-        <v>4.4600000000000001E-2</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="E17">
-        <v>10.83</v>
+        <v>3.33</v>
       </c>
       <c r="F17">
-        <v>3.37</v>
+        <v>3.33</v>
       </c>
       <c r="G17">
-        <v>9.48</v>
+        <v>7.93</v>
       </c>
       <c r="H17" s="4">
-        <v>54894.12</v>
+        <v>60299.05</v>
       </c>
       <c r="I17">
-        <v>4.4400000000000004</v>
+        <v>2.11</v>
       </c>
       <c r="J17">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K17">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L17">
-        <v>101.41</v>
+        <v>100.76</v>
       </c>
       <c r="M17">
-        <v>2.31</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1376,10 +1379,10 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>87100</v>
+        <v>88800</v>
       </c>
       <c r="D18" s="3">
-        <v>1.1000000000000001E-3</v>
+        <v>1.6E-2</v>
       </c>
       <c r="E18">
         <v>14.42</v>
@@ -1394,19 +1397,19 @@
         <v>36460.550000000003</v>
       </c>
       <c r="I18">
-        <v>6.31</v>
+        <v>6.19</v>
       </c>
       <c r="J18">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K18">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L18">
-        <v>91.03</v>
+        <v>95.04</v>
       </c>
       <c r="M18">
-        <v>1.28</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1417,10 +1420,10 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>23200</v>
+        <v>24100</v>
       </c>
       <c r="D19" s="3">
-        <v>1.5299999999999999E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="E19">
         <v>8.06</v>
@@ -1435,19 +1438,19 @@
         <v>44443.18</v>
       </c>
       <c r="I19">
-        <v>4.59</v>
+        <v>4.42</v>
       </c>
       <c r="J19">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="K19">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L19">
-        <v>93.39</v>
+        <v>98.45</v>
       </c>
       <c r="M19">
-        <v>-2.52</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1458,10 +1461,10 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>58600</v>
+        <v>59700</v>
       </c>
       <c r="D20" s="3">
-        <v>6.8999999999999999E-3</v>
+        <v>-1.6999999999999999E-3</v>
       </c>
       <c r="E20">
         <v>7.45</v>
@@ -1476,19 +1479,19 @@
         <v>79986.48</v>
       </c>
       <c r="I20">
-        <v>4.78</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="J20">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K20">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L20">
-        <v>95.6</v>
+        <v>98.04</v>
       </c>
       <c r="M20">
-        <v>-1.51</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1499,37 +1502,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>20800</v>
+        <v>21300</v>
       </c>
       <c r="D21" s="3">
-        <v>1.9599999999999999E-2</v>
+        <v>1.67E-2</v>
       </c>
       <c r="E21">
-        <v>15.12</v>
+        <v>13.7</v>
       </c>
       <c r="F21">
-        <v>13.07</v>
+        <v>13.7</v>
       </c>
       <c r="G21">
-        <v>15.58</v>
+        <v>14.6</v>
       </c>
       <c r="H21" s="4">
-        <v>15310.06</v>
+        <v>16125.49</v>
       </c>
       <c r="I21">
-        <v>5.91</v>
+        <v>5.77</v>
       </c>
       <c r="J21">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K21">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L21">
-        <v>97.76</v>
+        <v>100.84</v>
       </c>
       <c r="M21">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1540,37 +1543,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>60000</v>
+        <v>60700</v>
       </c>
       <c r="D22" s="3">
-        <v>1.8700000000000001E-2</v>
+        <v>2.3599999999999999E-2</v>
       </c>
       <c r="E22">
-        <v>2.85</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="F22">
-        <v>12.83</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="G22">
-        <v>5.63</v>
+        <v>6.37</v>
       </c>
       <c r="H22" s="4">
-        <v>71073.47</v>
+        <v>71885.83</v>
       </c>
       <c r="I22">
-        <v>3.33</v>
+        <v>3.95</v>
       </c>
       <c r="J22">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K22">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L22">
-        <v>96.32</v>
+        <v>98.58</v>
       </c>
       <c r="M22">
-        <v>3.81</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1581,25 +1584,25 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>15800</v>
+        <v>15820</v>
       </c>
       <c r="D23" s="3">
-        <v>3.95E-2</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="E23">
-        <v>4.4000000000000004</v>
+        <v>6.01</v>
       </c>
       <c r="F23">
-        <v>6.71</v>
+        <v>6.01</v>
       </c>
       <c r="G23">
-        <v>6.75</v>
+        <v>5.97</v>
       </c>
       <c r="H23" s="4">
-        <v>20394.86</v>
+        <v>20769.650000000001</v>
       </c>
       <c r="I23">
-        <v>4.1100000000000003</v>
+        <v>4.17</v>
       </c>
       <c r="J23">
         <v>74</v>
@@ -1608,10 +1611,10 @@
         <v>74</v>
       </c>
       <c r="L23">
-        <v>98.12</v>
+        <v>99.7</v>
       </c>
       <c r="M23">
-        <v>5.26</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1622,10 +1625,10 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>217000</v>
+        <v>231500</v>
       </c>
       <c r="D24" s="3">
-        <v>2.3599999999999999E-2</v>
+        <v>4.3E-3</v>
       </c>
       <c r="E24">
         <v>4.66</v>
@@ -1640,19 +1643,19 @@
         <v>324173.33</v>
       </c>
       <c r="I24">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="J24">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K24">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="L24">
-        <v>99.67</v>
+        <v>104.47</v>
       </c>
       <c r="M24">
-        <v>1.4</v>
+        <v>9.4600000000000009</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1663,37 +1666,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>155500</v>
+        <v>157500</v>
       </c>
       <c r="D25" s="3">
-        <v>1.9699999999999999E-2</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="E25">
-        <v>12.66</v>
+        <v>11.77</v>
       </c>
       <c r="F25">
-        <v>11.88</v>
+        <v>11.77</v>
       </c>
       <c r="G25">
-        <v>11.14</v>
+        <v>11.4</v>
       </c>
       <c r="H25" s="4">
-        <v>83639.03</v>
+        <v>85735.74</v>
       </c>
       <c r="I25">
-        <v>3.47</v>
+        <v>3.81</v>
       </c>
       <c r="J25">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K25">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L25">
-        <v>95.25</v>
+        <v>97.91</v>
       </c>
       <c r="M25">
-        <v>-0.7</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1704,37 +1707,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>18100</v>
+        <v>18190</v>
       </c>
       <c r="D26" s="3">
-        <v>2.8E-3</v>
+        <v>1.9E-2</v>
       </c>
       <c r="E26">
-        <v>12.08</v>
+        <v>8.11</v>
       </c>
       <c r="F26">
-        <v>8.58</v>
+        <v>8.11</v>
       </c>
       <c r="G26">
-        <v>8.39</v>
+        <v>9.93</v>
       </c>
       <c r="H26" s="4">
-        <v>19234.22</v>
+        <v>19583.27</v>
       </c>
       <c r="I26">
-        <v>6.46</v>
+        <v>5.22</v>
       </c>
       <c r="J26">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K26">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L26">
-        <v>97.47</v>
+        <v>98.7</v>
       </c>
       <c r="M26">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1745,37 +1748,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>34800</v>
+        <v>37700</v>
       </c>
       <c r="D27" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>0.04</v>
       </c>
       <c r="E27">
-        <v>11.21</v>
+        <v>1.23</v>
       </c>
       <c r="F27">
-        <v>6.55</v>
+        <v>1.23</v>
       </c>
       <c r="G27">
-        <v>6.4</v>
+        <v>1.59</v>
       </c>
       <c r="H27" s="4">
-        <v>122131.86</v>
+        <v>118301.94</v>
       </c>
       <c r="I27">
-        <v>4.18</v>
+        <v>3.06</v>
       </c>
       <c r="J27">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K27">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L27">
-        <v>87.98</v>
+        <v>97.4</v>
       </c>
       <c r="M27">
-        <v>-6.2</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1786,10 +1789,10 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>91200</v>
+        <v>97900</v>
       </c>
       <c r="D28" s="3">
-        <v>1.3299999999999999E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="E28">
         <v>8.11</v>
@@ -1804,19 +1807,19 @@
         <v>119742.76</v>
       </c>
       <c r="I28">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="J28">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K28">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="L28">
-        <v>95.36</v>
+        <v>103.42</v>
       </c>
       <c r="M28">
-        <v>-1.83</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1827,10 +1830,10 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>233500</v>
+        <v>234500</v>
       </c>
       <c r="D29" s="3">
-        <v>4.4699999999999997E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="E29">
         <v>11.54</v>
@@ -1854,10 +1857,10 @@
         <v>74</v>
       </c>
       <c r="L29">
-        <v>95.29</v>
+        <v>97.34</v>
       </c>
       <c r="M29">
-        <v>1.3</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1868,10 +1871,10 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>64200</v>
+        <v>69000</v>
       </c>
       <c r="D30" s="3">
-        <v>3.0499999999999999E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E30">
         <v>4.12</v>
@@ -1886,19 +1889,19 @@
         <v>151788</v>
       </c>
       <c r="I30">
-        <v>4.21</v>
+        <v>3.91</v>
       </c>
       <c r="J30">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K30">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="L30">
-        <v>94.18</v>
+        <v>102.23</v>
       </c>
       <c r="M30">
-        <v>-3.6</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1909,37 +1912,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>109900</v>
-      </c>
-      <c r="D31" s="3">
-        <v>1.38E-2</v>
+        <v>113200</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>9.11</v>
+        <v>9.17</v>
       </c>
       <c r="F31">
-        <v>10.57</v>
+        <v>9.17</v>
       </c>
       <c r="G31">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="H31" s="4">
-        <v>159337.74</v>
+        <v>162088.94</v>
       </c>
       <c r="I31">
-        <v>3.28</v>
+        <v>3.63</v>
       </c>
       <c r="J31">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K31">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L31">
-        <v>93.09</v>
+        <v>97.67</v>
       </c>
       <c r="M31">
-        <v>-1.17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1950,10 +1953,10 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>150700</v>
+        <v>155200</v>
       </c>
       <c r="D32" s="3">
-        <v>9.4000000000000004E-3</v>
+        <v>-3.2000000000000002E-3</v>
       </c>
       <c r="E32">
         <v>8.86</v>
@@ -1968,19 +1971,19 @@
         <v>160038.65</v>
       </c>
       <c r="I32">
-        <v>2.11</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="J32">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K32">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L32">
-        <v>96.41</v>
+        <v>100.49</v>
       </c>
       <c r="M32">
-        <v>1.1399999999999999</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -1991,10 +1994,10 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>18480</v>
+        <v>18850</v>
       </c>
       <c r="D33" s="3">
-        <v>1.8700000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E33">
         <v>6.96</v>
@@ -2009,19 +2012,19 @@
         <v>34223.949999999997</v>
       </c>
       <c r="I33">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="J33">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K33">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L33">
-        <v>92.85</v>
+        <v>97.04</v>
       </c>
       <c r="M33">
-        <v>-1.7</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2032,10 +2035,10 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>16580</v>
+        <v>17240</v>
       </c>
       <c r="D34" s="3">
-        <v>4.1999999999999997E-3</v>
+        <v>2.6200000000000001E-2</v>
       </c>
       <c r="E34">
         <v>3.6</v>
@@ -2050,19 +2053,19 @@
         <v>38541.279999999999</v>
       </c>
       <c r="I34">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="J34">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K34">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L34">
-        <v>89.87</v>
+        <v>96.19</v>
       </c>
       <c r="M34">
-        <v>-3.88</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2073,10 +2076,10 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>56300</v>
+        <v>57400</v>
       </c>
       <c r="D35" s="3">
-        <v>4.2599999999999999E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="E35">
         <v>10.79</v>
@@ -2091,19 +2094,19 @@
         <v>92723.77</v>
       </c>
       <c r="I35">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="J35">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K35">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L35">
-        <v>85.84</v>
+        <v>90.82</v>
       </c>
       <c r="M35">
-        <v>-8.75</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2114,10 +2117,10 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>29450</v>
+        <v>30950</v>
       </c>
       <c r="D36" s="3">
-        <v>1.9E-2</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="E36">
         <v>12.8</v>
@@ -2132,19 +2135,19 @@
         <v>31004.78</v>
       </c>
       <c r="I36">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="J36">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K36">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L36">
-        <v>92.03</v>
+        <v>98.82</v>
       </c>
       <c r="M36">
-        <v>0.68</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2155,10 +2158,10 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>50500</v>
+        <v>50900</v>
       </c>
       <c r="D37" s="3">
-        <v>1.7100000000000001E-2</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="E37">
         <v>18.690000000000001</v>
@@ -2173,19 +2176,19 @@
         <v>57293.3</v>
       </c>
       <c r="I37">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J37">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K37">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L37">
-        <v>96.93</v>
+        <v>98.67</v>
       </c>
       <c r="M37">
-        <v>2.54</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2196,10 +2199,10 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>32600</v>
+        <v>33900</v>
       </c>
       <c r="D38" s="3">
-        <v>2.1899999999999999E-2</v>
+        <v>8.8999999999999999E-3</v>
       </c>
       <c r="E38">
         <v>9.39</v>
@@ -2214,19 +2217,19 @@
         <v>48211.77</v>
       </c>
       <c r="I38">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="J38">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K38">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L38">
-        <v>91.75</v>
+        <v>97.67</v>
       </c>
       <c r="M38">
-        <v>-3.41</v>
+        <v>5.61</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABC8D7DC-3D83-4A6A-8ED3-6C60F500471C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B5A4CBF-6AEF-419C-AD08-673C909B37FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{36C78BB6-8F28-4183-9D30-D521DE27668D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9A05698F-BC93-4BB8-8F96-A65965D27E9D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="179">
   <si>
     <t>종목코드</t>
   </si>
@@ -60,6 +60,12 @@
     <t>해당등락률</t>
   </si>
   <si>
+    <t>000100</t>
+  </si>
+  <si>
+    <t>유한양행</t>
+  </si>
+  <si>
     <t>000240</t>
   </si>
   <si>
@@ -72,12 +78,30 @@
     <t>기아</t>
   </si>
   <si>
+    <t>000660</t>
+  </si>
+  <si>
+    <t>SK하이닉스</t>
+  </si>
+  <si>
     <t>000810</t>
   </si>
   <si>
     <t>삼성화재</t>
   </si>
   <si>
+    <t>000880</t>
+  </si>
+  <si>
+    <t>한화</t>
+  </si>
+  <si>
+    <t>001040</t>
+  </si>
+  <si>
+    <t>CJ</t>
+  </si>
+  <si>
     <t>001120</t>
   </si>
   <si>
@@ -96,6 +120,18 @@
     <t>세아베스틸지주</t>
   </si>
   <si>
+    <t>003230</t>
+  </si>
+  <si>
+    <t>삼양식품</t>
+  </si>
+  <si>
+    <t>003490</t>
+  </si>
+  <si>
+    <t>대한항공</t>
+  </si>
+  <si>
     <t>003540</t>
   </si>
   <si>
@@ -120,30 +156,114 @@
     <t>현대차</t>
   </si>
   <si>
+    <t>005490</t>
+  </si>
+  <si>
+    <t>POSCO홀딩스</t>
+  </si>
+  <si>
     <t>005830</t>
   </si>
   <si>
     <t>DB손해보험</t>
   </si>
   <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>삼성전자</t>
+  </si>
+  <si>
     <t>005940</t>
   </si>
   <si>
     <t>NH투자증권</t>
   </si>
   <si>
+    <t>006260</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>006800</t>
+  </si>
+  <si>
+    <t>미래에셋증권</t>
+  </si>
+  <si>
     <t>007340</t>
   </si>
   <si>
     <t>DN오토모티브</t>
   </si>
   <si>
+    <t>007660</t>
+  </si>
+  <si>
+    <t>이수페타시스</t>
+  </si>
+  <si>
+    <t>009150</t>
+  </si>
+  <si>
+    <t>삼성전기</t>
+  </si>
+  <si>
+    <t>009540</t>
+  </si>
+  <si>
+    <t>HD한국조선해양</t>
+  </si>
+  <si>
     <t>009970</t>
   </si>
   <si>
     <t>영원무역홀딩스</t>
   </si>
   <si>
+    <t>010120</t>
+  </si>
+  <si>
+    <t>LS ELECTRIC</t>
+  </si>
+  <si>
+    <t>010130</t>
+  </si>
+  <si>
+    <t>고려아연</t>
+  </si>
+  <si>
+    <t>011070</t>
+  </si>
+  <si>
+    <t>LG이노텍</t>
+  </si>
+  <si>
+    <t>011200</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
+    <t>012330</t>
+  </si>
+  <si>
+    <t>현대모비스</t>
+  </si>
+  <si>
+    <t>012450</t>
+  </si>
+  <si>
+    <t>한화에어로스페이스</t>
+  </si>
+  <si>
+    <t>015760</t>
+  </si>
+  <si>
+    <t>한국전력</t>
+  </si>
+  <si>
     <t>016360</t>
   </si>
   <si>
@@ -162,12 +282,42 @@
     <t>현대엘리베이터</t>
   </si>
   <si>
+    <t>018260</t>
+  </si>
+  <si>
+    <t>삼성에스디에스</t>
+  </si>
+  <si>
+    <t>021240</t>
+  </si>
+  <si>
+    <t>코웨이</t>
+  </si>
+  <si>
+    <t>022100</t>
+  </si>
+  <si>
+    <t>포스코DX</t>
+  </si>
+  <si>
     <t>024110</t>
   </si>
   <si>
     <t>기업은행</t>
   </si>
   <si>
+    <t>028050</t>
+  </si>
+  <si>
+    <t>삼성E&amp;A</t>
+  </si>
+  <si>
+    <t>028260</t>
+  </si>
+  <si>
+    <t>삼성물산</t>
+  </si>
+  <si>
     <t>029780</t>
   </si>
   <si>
@@ -210,18 +360,72 @@
     <t>강원랜드</t>
   </si>
   <si>
+    <t>035420</t>
+  </si>
+  <si>
+    <t>NAVER</t>
+  </si>
+  <si>
+    <t>035720</t>
+  </si>
+  <si>
+    <t>카카오</t>
+  </si>
+  <si>
     <t>036460</t>
   </si>
   <si>
     <t>한국가스공사</t>
   </si>
   <si>
+    <t>039490</t>
+  </si>
+  <si>
+    <t>키움증권</t>
+  </si>
+  <si>
+    <t>042700</t>
+  </si>
+  <si>
+    <t>한미반도체</t>
+  </si>
+  <si>
+    <t>047050</t>
+  </si>
+  <si>
+    <t>포스코인터내셔널</t>
+  </si>
+  <si>
+    <t>047810</t>
+  </si>
+  <si>
+    <t>한국항공우주</t>
+  </si>
+  <si>
     <t>055550</t>
   </si>
   <si>
     <t>신한지주</t>
   </si>
   <si>
+    <t>064350</t>
+  </si>
+  <si>
+    <t>현대로템</t>
+  </si>
+  <si>
+    <t>066570</t>
+  </si>
+  <si>
+    <t>LG전자</t>
+  </si>
+  <si>
+    <t>068270</t>
+  </si>
+  <si>
+    <t>셀트리온</t>
+  </si>
+  <si>
     <t>071050</t>
   </si>
   <si>
@@ -234,18 +438,48 @@
     <t>GS</t>
   </si>
   <si>
+    <t>079550</t>
+  </si>
+  <si>
+    <t>LIG넥스원</t>
+  </si>
+  <si>
+    <t>086280</t>
+  </si>
+  <si>
+    <t>현대글로비스</t>
+  </si>
+  <si>
     <t>086790</t>
   </si>
   <si>
     <t>하나금융지주</t>
   </si>
   <si>
+    <t>090430</t>
+  </si>
+  <si>
+    <t>아모레퍼시픽</t>
+  </si>
+  <si>
     <t>105560</t>
   </si>
   <si>
     <t>KB금융</t>
   </si>
   <si>
+    <t>128940</t>
+  </si>
+  <si>
+    <t>한미약품</t>
+  </si>
+  <si>
+    <t>138040</t>
+  </si>
+  <si>
+    <t>메리츠금융지주</t>
+  </si>
+  <si>
     <t>138930</t>
   </si>
   <si>
@@ -270,10 +504,58 @@
     <t>JB금융지주</t>
   </si>
   <si>
+    <t>180640</t>
+  </si>
+  <si>
+    <t>한진칼</t>
+  </si>
+  <si>
     <t>192080</t>
   </si>
   <si>
     <t>더블유게임즈</t>
+  </si>
+  <si>
+    <t>241560</t>
+  </si>
+  <si>
+    <t>두산밥캣</t>
+  </si>
+  <si>
+    <t>267250</t>
+  </si>
+  <si>
+    <t>HD현대</t>
+  </si>
+  <si>
+    <t>267260</t>
+  </si>
+  <si>
+    <t>HD현대일렉트릭</t>
+  </si>
+  <si>
+    <t>267270</t>
+  </si>
+  <si>
+    <t>HD건설기계</t>
+  </si>
+  <si>
+    <t>272210</t>
+  </si>
+  <si>
+    <t>한화시스템</t>
+  </si>
+  <si>
+    <t>298040</t>
+  </si>
+  <si>
+    <t>효성중공업</t>
+  </si>
+  <si>
+    <t>307950</t>
+  </si>
+  <si>
+    <t>현대오토에버</t>
   </si>
   <si>
     <t>316140</t>
@@ -657,13 +939,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{624B7A42-B1FA-4DA3-9EA1-3E220A9BE1F9}">
-  <dimension ref="A1:M38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A212A883-B510-4B09-A0D5-0BA3DCA570C4}">
+  <dimension ref="A1:M85"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
@@ -723,37 +1005,37 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>27100</v>
+        <v>100300</v>
       </c>
       <c r="D2" s="3">
-        <v>1.8800000000000001E-2</v>
+        <v>1.6199999999999999E-2</v>
       </c>
       <c r="E2">
-        <v>8.2799999999999994</v>
+        <v>8.81</v>
       </c>
       <c r="F2">
-        <v>8.9</v>
+        <v>8.81</v>
       </c>
       <c r="G2">
-        <v>5.8</v>
+        <v>6.32</v>
       </c>
       <c r="H2" s="4">
-        <v>48390.96</v>
+        <v>31276.98</v>
       </c>
       <c r="I2">
-        <v>3.69</v>
+        <v>0.6</v>
       </c>
       <c r="J2">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="K2">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L2">
-        <v>96.42</v>
+        <v>97.45</v>
       </c>
       <c r="M2">
-        <v>7.97</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -764,37 +1046,37 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>168500</v>
+        <v>27100</v>
       </c>
       <c r="D3" s="3">
-        <v>-1.17E-2</v>
+        <v>1.8800000000000001E-2</v>
       </c>
       <c r="E3">
-        <v>12.92</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="F3">
-        <v>12.92</v>
+        <v>8.9</v>
       </c>
       <c r="G3">
-        <v>17.48</v>
+        <v>5.8</v>
       </c>
       <c r="H3" s="4">
-        <v>157169.68</v>
+        <v>48390.96</v>
       </c>
       <c r="I3">
-        <v>4.04</v>
+        <v>3.69</v>
       </c>
       <c r="J3">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="K3">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L3">
-        <v>97.69</v>
+        <v>96.42</v>
       </c>
       <c r="M3">
-        <v>4.66</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -805,37 +1087,37 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>474500</v>
+        <v>168500</v>
       </c>
       <c r="D4" s="3">
-        <v>-8.3999999999999995E-3</v>
+        <v>-1.17E-2</v>
       </c>
       <c r="E4">
-        <v>13.09</v>
+        <v>12.92</v>
       </c>
       <c r="F4">
-        <v>13.88</v>
+        <v>12.92</v>
       </c>
       <c r="G4">
-        <v>12.47</v>
+        <v>17.48</v>
       </c>
       <c r="H4" s="4">
-        <v>405451.96</v>
+        <v>157169.68</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="J4">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="K4">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="L4">
-        <v>93.46</v>
+        <v>97.69</v>
       </c>
       <c r="M4">
-        <v>-2.87</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -846,25 +1128,25 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>47150</v>
+        <v>1007000</v>
       </c>
       <c r="D5" s="3">
-        <v>5.96E-2</v>
+        <v>-5.8999999999999999E-3</v>
       </c>
       <c r="E5">
-        <v>7.12</v>
+        <v>44.15</v>
       </c>
       <c r="F5">
-        <v>9.6199999999999992</v>
+        <v>44.15</v>
       </c>
       <c r="G5">
-        <v>12.61</v>
+        <v>19.87</v>
       </c>
       <c r="H5" s="4">
-        <v>72041.39</v>
+        <v>167604.03</v>
       </c>
       <c r="I5">
-        <v>4.24</v>
+        <v>0.3</v>
       </c>
       <c r="J5">
         <v>91</v>
@@ -873,10 +1155,10 @@
         <v>91</v>
       </c>
       <c r="L5">
-        <v>107.59</v>
+        <v>104.22</v>
       </c>
       <c r="M5">
-        <v>14.72</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -887,37 +1169,37 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>78600</v>
+        <v>474500</v>
       </c>
       <c r="D6" s="3">
-        <v>1.95E-2</v>
+        <v>-8.3999999999999995E-3</v>
       </c>
       <c r="E6">
-        <v>4.05</v>
+        <v>13.09</v>
       </c>
       <c r="F6">
-        <v>7.82</v>
+        <v>13.88</v>
       </c>
       <c r="G6">
-        <v>6.06</v>
+        <v>12.47</v>
       </c>
       <c r="H6" s="4">
-        <v>65679.45</v>
+        <v>405451.96</v>
       </c>
       <c r="I6">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K6">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L6">
-        <v>94.13</v>
+        <v>93.46</v>
       </c>
       <c r="M6">
-        <v>1.81</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -928,37 +1210,37 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>66200</v>
+        <v>120700</v>
       </c>
       <c r="D7" s="3">
-        <v>1.6899999999999998E-2</v>
+        <v>-7.4000000000000003E-3</v>
       </c>
       <c r="E7">
-        <v>1.04</v>
+        <v>7.19</v>
       </c>
       <c r="F7">
-        <v>3.97</v>
+        <v>6.47</v>
       </c>
       <c r="G7">
-        <v>4.21</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="H7" s="4">
-        <v>53899.69</v>
+        <v>117241.22</v>
       </c>
       <c r="I7">
-        <v>1.81</v>
+        <v>0.66</v>
       </c>
       <c r="J7">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="K7">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="L7">
-        <v>98.89</v>
+        <v>94.5</v>
       </c>
       <c r="M7">
-        <v>6.95</v>
+        <v>-4.21</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -969,37 +1251,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>40350</v>
+        <v>207000</v>
       </c>
       <c r="D8" s="3">
-        <v>1.77E-2</v>
+        <v>5.0799999999999998E-2</v>
       </c>
       <c r="E8">
-        <v>4.57</v>
+        <v>1.83</v>
       </c>
       <c r="F8">
-        <v>7.42</v>
+        <v>9.24</v>
       </c>
       <c r="G8">
-        <v>4.55</v>
+        <v>3.14</v>
       </c>
       <c r="H8" s="4">
-        <v>42814.52</v>
+        <v>156275.9</v>
       </c>
       <c r="I8">
-        <v>2.97</v>
+        <v>1.45</v>
       </c>
       <c r="J8">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K8">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L8">
-        <v>96.72</v>
+        <v>104.48</v>
       </c>
       <c r="M8">
-        <v>3.59</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1010,37 +1292,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>95500</v>
+        <v>47150</v>
       </c>
       <c r="D9" s="3">
-        <v>5.5199999999999999E-2</v>
+        <v>5.96E-2</v>
       </c>
       <c r="E9">
-        <v>2.16</v>
+        <v>7.12</v>
       </c>
       <c r="F9">
-        <v>5.36</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="G9">
-        <v>5.18</v>
+        <v>12.61</v>
       </c>
       <c r="H9" s="4">
-        <v>177736.27</v>
+        <v>72041.39</v>
       </c>
       <c r="I9">
-        <v>3.25</v>
+        <v>4.24</v>
       </c>
       <c r="J9">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="K9">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="L9">
-        <v>99.9</v>
+        <v>107.59</v>
       </c>
       <c r="M9">
-        <v>1.49</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1051,37 +1333,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>13170</v>
+        <v>78600</v>
       </c>
       <c r="D10" s="3">
-        <v>5.3E-3</v>
+        <v>1.95E-2</v>
       </c>
       <c r="E10">
-        <v>9.44</v>
+        <v>4.05</v>
       </c>
       <c r="F10">
-        <v>10.67</v>
+        <v>7.82</v>
       </c>
       <c r="G10">
-        <v>9.86</v>
+        <v>6.06</v>
       </c>
       <c r="H10" s="4">
-        <v>19219.419999999998</v>
+        <v>65679.45</v>
       </c>
       <c r="I10">
-        <v>3.91</v>
+        <v>1.91</v>
       </c>
       <c r="J10">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K10">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L10">
-        <v>98.16</v>
+        <v>94.13</v>
       </c>
       <c r="M10">
-        <v>2.57</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1092,37 +1374,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>517000</v>
+        <v>66200</v>
       </c>
       <c r="D11" s="3">
-        <v>-9.5999999999999992E-3</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="E11">
-        <v>8.41</v>
+        <v>1.04</v>
       </c>
       <c r="F11">
-        <v>8.41</v>
+        <v>3.97</v>
       </c>
       <c r="G11">
-        <v>11.51</v>
+        <v>4.21</v>
       </c>
       <c r="H11" s="4">
-        <v>436418.31</v>
+        <v>53899.69</v>
       </c>
       <c r="I11">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="J11">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K11">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L11">
-        <v>95.56</v>
+        <v>98.89</v>
       </c>
       <c r="M11">
-        <v>-1.52</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1133,37 +1415,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>186700</v>
+        <v>1151000</v>
       </c>
       <c r="D12" s="3">
-        <v>1.1900000000000001E-2</v>
+        <v>4.6399999999999997E-2</v>
       </c>
       <c r="E12">
-        <v>18.96</v>
+        <v>39.369999999999997</v>
       </c>
       <c r="F12">
-        <v>19.43</v>
+        <v>41.29</v>
       </c>
       <c r="G12">
-        <v>18.8</v>
+        <v>27.7</v>
       </c>
       <c r="H12" s="4">
-        <v>144109.65</v>
+        <v>144393.44</v>
       </c>
       <c r="I12">
-        <v>3.64</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J12">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="K12">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>102.45</v>
       </c>
       <c r="M12">
-        <v>1.74</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1174,37 +1456,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>35600</v>
+        <v>26350</v>
       </c>
       <c r="D13" s="3">
-        <v>6.59E-2</v>
+        <v>7.3300000000000004E-2</v>
       </c>
       <c r="E13">
-        <v>8.73</v>
+        <v>7.28</v>
       </c>
       <c r="F13">
-        <v>11.57</v>
+        <v>7.28</v>
       </c>
       <c r="G13">
-        <v>6.85</v>
+        <v>10.64</v>
       </c>
       <c r="H13" s="4">
-        <v>24348.21</v>
+        <v>29659.1</v>
       </c>
       <c r="I13">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="J13">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="K13">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="L13">
-        <v>105.4</v>
+        <v>104.06</v>
       </c>
       <c r="M13">
-        <v>13.38</v>
+        <v>8.2100000000000009</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1215,37 +1497,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>39750</v>
+        <v>40350</v>
       </c>
       <c r="D14" s="3">
-        <v>3.8E-3</v>
+        <v>1.77E-2</v>
       </c>
       <c r="E14">
-        <v>15.02</v>
+        <v>4.57</v>
       </c>
       <c r="F14">
-        <v>15.02</v>
+        <v>7.42</v>
       </c>
       <c r="G14">
-        <v>20.7</v>
+        <v>4.55</v>
       </c>
       <c r="H14" s="4">
-        <v>34750.239999999998</v>
+        <v>42814.52</v>
       </c>
       <c r="I14">
-        <v>2.52</v>
+        <v>2.97</v>
       </c>
       <c r="J14">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="K14">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="L14">
-        <v>131.59</v>
+        <v>96.72</v>
       </c>
       <c r="M14">
-        <v>43.24</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1256,37 +1538,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>227000</v>
+        <v>95500</v>
       </c>
       <c r="D15" s="3">
-        <v>2.4799999999999999E-2</v>
+        <v>5.5199999999999999E-2</v>
       </c>
       <c r="E15">
-        <v>13.17</v>
+        <v>2.16</v>
       </c>
       <c r="F15">
-        <v>11.69</v>
+        <v>5.36</v>
       </c>
       <c r="G15">
-        <v>18.010000000000002</v>
+        <v>5.18</v>
       </c>
       <c r="H15" s="4">
-        <v>207156.6</v>
+        <v>177736.27</v>
       </c>
       <c r="I15">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="J15">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="K15">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="L15">
-        <v>98.43</v>
+        <v>99.9</v>
       </c>
       <c r="M15">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1297,37 +1579,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>102300</v>
+        <v>13170</v>
       </c>
       <c r="D16" s="3">
-        <v>3.7499999999999999E-2</v>
+        <v>5.3E-3</v>
       </c>
       <c r="E16">
-        <v>12.89</v>
+        <v>9.44</v>
       </c>
       <c r="F16">
-        <v>13.94</v>
+        <v>10.67</v>
       </c>
       <c r="G16">
-        <v>9.44</v>
+        <v>9.86</v>
       </c>
       <c r="H16" s="4">
-        <v>87743.72</v>
+        <v>19219.419999999998</v>
       </c>
       <c r="I16">
-        <v>3.42</v>
+        <v>3.91</v>
       </c>
       <c r="J16">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K16">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L16">
-        <v>101.8</v>
+        <v>98.16</v>
       </c>
       <c r="M16">
-        <v>9.5299999999999994</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1338,37 +1620,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>78800</v>
+        <v>517000</v>
       </c>
       <c r="D17" s="3">
-        <v>7.7000000000000002E-3</v>
+        <v>-9.5999999999999992E-3</v>
       </c>
       <c r="E17">
-        <v>3.33</v>
+        <v>8.41</v>
       </c>
       <c r="F17">
-        <v>3.33</v>
+        <v>8.41</v>
       </c>
       <c r="G17">
-        <v>7.93</v>
+        <v>11.51</v>
       </c>
       <c r="H17" s="4">
-        <v>60299.05</v>
+        <v>436418.31</v>
       </c>
       <c r="I17">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="J17">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="K17">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="L17">
-        <v>100.76</v>
+        <v>95.56</v>
       </c>
       <c r="M17">
-        <v>2.0699999999999998</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1379,37 +1661,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>88800</v>
+        <v>343500</v>
       </c>
       <c r="D18" s="3">
-        <v>1.6E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="E18">
-        <v>14.42</v>
+        <v>1.18</v>
       </c>
       <c r="F18">
-        <v>24.2</v>
+        <v>1.18</v>
       </c>
       <c r="G18">
-        <v>15.82</v>
+        <v>2.12</v>
       </c>
       <c r="H18" s="4">
-        <v>36460.550000000003</v>
+        <v>703131.42</v>
       </c>
       <c r="I18">
-        <v>6.19</v>
+        <v>2.91</v>
       </c>
       <c r="J18">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="K18">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="L18">
-        <v>95.04</v>
+        <v>95.15</v>
       </c>
       <c r="M18">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1420,37 +1702,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>24100</v>
+        <v>186700</v>
       </c>
       <c r="D19" s="3">
-        <v>1.6899999999999998E-2</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="E19">
-        <v>8.06</v>
+        <v>18.96</v>
       </c>
       <c r="F19">
-        <v>8.64</v>
+        <v>19.43</v>
       </c>
       <c r="G19">
-        <v>8.77</v>
+        <v>18.8</v>
       </c>
       <c r="H19" s="4">
-        <v>44443.18</v>
+        <v>144109.65</v>
       </c>
       <c r="I19">
-        <v>4.42</v>
+        <v>3.64</v>
       </c>
       <c r="J19">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K19">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="L19">
-        <v>98.45</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>4.33</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1461,37 +1743,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>59700</v>
+        <v>199400</v>
       </c>
       <c r="D20" s="3">
-        <v>-1.6999999999999999E-3</v>
+        <v>-5.4999999999999997E-3</v>
       </c>
       <c r="E20">
-        <v>7.45</v>
+        <v>10.85</v>
       </c>
       <c r="F20">
-        <v>7.45</v>
+        <v>10.85</v>
       </c>
       <c r="G20">
-        <v>7.69</v>
+        <v>8.01</v>
       </c>
       <c r="H20" s="4">
-        <v>79986.48</v>
+        <v>63976.31</v>
       </c>
       <c r="I20">
-        <v>4.6900000000000004</v>
+        <v>0.84</v>
       </c>
       <c r="J20">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K20">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="L20">
-        <v>98.04</v>
+        <v>102.73</v>
       </c>
       <c r="M20">
-        <v>1.53</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1502,37 +1784,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>21300</v>
+        <v>35600</v>
       </c>
       <c r="D21" s="3">
-        <v>1.67E-2</v>
+        <v>6.59E-2</v>
       </c>
       <c r="E21">
-        <v>13.7</v>
+        <v>8.73</v>
       </c>
       <c r="F21">
-        <v>13.7</v>
+        <v>11.57</v>
       </c>
       <c r="G21">
-        <v>14.6</v>
+        <v>6.85</v>
       </c>
       <c r="H21" s="4">
-        <v>16125.49</v>
+        <v>24348.21</v>
       </c>
       <c r="I21">
-        <v>5.77</v>
+        <v>2.67</v>
       </c>
       <c r="J21">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="K21">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="L21">
-        <v>100.84</v>
+        <v>105.4</v>
       </c>
       <c r="M21">
-        <v>3.4</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1543,37 +1825,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>60700</v>
+        <v>303500</v>
       </c>
       <c r="D22" s="3">
-        <v>2.3599999999999999E-2</v>
+        <v>4.48E-2</v>
       </c>
       <c r="E22">
-        <v>10.220000000000001</v>
+        <v>5.09</v>
       </c>
       <c r="F22">
-        <v>10.220000000000001</v>
+        <v>7.08</v>
       </c>
       <c r="G22">
-        <v>6.37</v>
+        <v>11.63</v>
       </c>
       <c r="H22" s="4">
-        <v>71885.83</v>
+        <v>158418.68</v>
       </c>
       <c r="I22">
-        <v>3.95</v>
+        <v>0.54</v>
       </c>
       <c r="J22">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="K22">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="L22">
-        <v>98.58</v>
+        <v>114.4</v>
       </c>
       <c r="M22">
-        <v>-0.16</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1584,37 +1866,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>15820</v>
+        <v>67700</v>
       </c>
       <c r="D23" s="3">
-        <v>1.2800000000000001E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E23">
-        <v>6.01</v>
+        <v>7.94</v>
       </c>
       <c r="F23">
-        <v>6.01</v>
+        <v>10.76</v>
       </c>
       <c r="G23">
-        <v>5.97</v>
+        <v>5.75</v>
       </c>
       <c r="H23" s="4">
-        <v>20769.650000000001</v>
+        <v>18036.09</v>
       </c>
       <c r="I23">
-        <v>4.17</v>
+        <v>0.37</v>
       </c>
       <c r="J23">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="K23">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="L23">
-        <v>99.7</v>
+        <v>99.54</v>
       </c>
       <c r="M23">
-        <v>7.18</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1625,37 +1907,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>231500</v>
+        <v>39750</v>
       </c>
       <c r="D24" s="3">
-        <v>4.3E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="E24">
-        <v>4.66</v>
+        <v>15.02</v>
       </c>
       <c r="F24">
-        <v>4.66</v>
+        <v>15.02</v>
       </c>
       <c r="G24">
-        <v>4.88</v>
+        <v>20.7</v>
       </c>
       <c r="H24" s="4">
-        <v>324173.33</v>
+        <v>34750.239999999998</v>
       </c>
       <c r="I24">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="J24">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K24">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L24">
-        <v>104.47</v>
+        <v>131.59</v>
       </c>
       <c r="M24">
-        <v>9.4600000000000009</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1666,37 +1948,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>157500</v>
+        <v>126800</v>
       </c>
       <c r="D25" s="3">
-        <v>3.2000000000000002E-3</v>
+        <v>-2.0799999999999999E-2</v>
       </c>
       <c r="E25">
-        <v>11.77</v>
+        <v>24.91</v>
       </c>
       <c r="F25">
-        <v>11.77</v>
+        <v>29.9</v>
       </c>
       <c r="G25">
-        <v>11.4</v>
+        <v>34.450000000000003</v>
       </c>
       <c r="H25" s="4">
-        <v>85735.74</v>
+        <v>9737.2999999999993</v>
       </c>
       <c r="I25">
-        <v>3.81</v>
+        <v>0.12</v>
       </c>
       <c r="J25">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K25">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L25">
-        <v>97.91</v>
+        <v>111.69</v>
       </c>
       <c r="M25">
-        <v>1.88</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1707,37 +1989,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>18190</v>
+        <v>464500</v>
       </c>
       <c r="D26" s="3">
-        <v>1.9E-2</v>
+        <v>-3.1300000000000001E-2</v>
       </c>
       <c r="E26">
-        <v>8.11</v>
+        <v>7.7</v>
       </c>
       <c r="F26">
-        <v>8.11</v>
+        <v>7.7</v>
       </c>
       <c r="G26">
-        <v>9.93</v>
+        <v>7.12</v>
       </c>
       <c r="H26" s="4">
-        <v>19583.27</v>
+        <v>124850.23</v>
       </c>
       <c r="I26">
-        <v>5.22</v>
+        <v>0.51</v>
       </c>
       <c r="J26">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="K26">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="L26">
-        <v>98.7</v>
+        <v>109.75</v>
       </c>
       <c r="M26">
-        <v>1.9</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1748,37 +2030,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>37700</v>
+        <v>404500</v>
       </c>
       <c r="D27" s="3">
-        <v>0.04</v>
+        <v>-2.18E-2</v>
       </c>
       <c r="E27">
-        <v>1.23</v>
+        <v>11.16</v>
       </c>
       <c r="F27">
-        <v>1.23</v>
+        <v>16.829999999999998</v>
       </c>
       <c r="G27">
-        <v>1.59</v>
+        <v>3.73</v>
       </c>
       <c r="H27" s="4">
-        <v>118301.94</v>
+        <v>175890.96</v>
       </c>
       <c r="I27">
-        <v>3.06</v>
+        <v>1.26</v>
       </c>
       <c r="J27">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="K27">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="L27">
-        <v>97.4</v>
+        <v>94.98</v>
       </c>
       <c r="M27">
-        <v>4.43</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1789,37 +2071,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>97900</v>
+        <v>227000</v>
       </c>
       <c r="D28" s="3">
-        <v>1.4500000000000001E-2</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="E28">
-        <v>8.11</v>
+        <v>13.17</v>
       </c>
       <c r="F28">
-        <v>10.44</v>
+        <v>11.69</v>
       </c>
       <c r="G28">
-        <v>8.66</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H28" s="4">
-        <v>119742.76</v>
+        <v>207156.6</v>
       </c>
       <c r="I28">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="J28">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K28">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L28">
-        <v>103.42</v>
+        <v>98.43</v>
       </c>
       <c r="M28">
-        <v>9.75</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1830,37 +2112,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>234500</v>
+        <v>886000</v>
       </c>
       <c r="D29" s="3">
-        <v>2.4E-2</v>
+        <v>1.49E-2</v>
       </c>
       <c r="E29">
-        <v>11.54</v>
+        <v>13.44</v>
       </c>
       <c r="F29">
-        <v>20.98</v>
+        <v>14.22</v>
       </c>
       <c r="G29">
-        <v>9.6</v>
+        <v>10.67</v>
       </c>
       <c r="H29" s="4">
-        <v>189057.03</v>
+        <v>66213.7</v>
       </c>
       <c r="I29">
-        <v>1.7</v>
+        <v>0.33</v>
       </c>
       <c r="J29">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="K29">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="L29">
-        <v>97.34</v>
+        <v>118.54</v>
       </c>
       <c r="M29">
-        <v>6.59</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1871,37 +2153,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>69000</v>
+        <v>1587000</v>
       </c>
       <c r="D30" s="3">
-        <v>5.5E-2</v>
+        <v>-1.55E-2</v>
       </c>
       <c r="E30">
-        <v>4.12</v>
+        <v>8.48</v>
       </c>
       <c r="F30">
-        <v>5.22</v>
+        <v>8.48</v>
       </c>
       <c r="G30">
-        <v>11.01</v>
+        <v>5.49</v>
       </c>
       <c r="H30" s="4">
-        <v>151788</v>
+        <v>542817.23</v>
       </c>
       <c r="I30">
-        <v>3.91</v>
+        <v>1.26</v>
       </c>
       <c r="J30">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="K30">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="L30">
-        <v>102.23</v>
+        <v>91</v>
       </c>
       <c r="M30">
-        <v>7.81</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1912,37 +2194,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>113200</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0</v>
+        <v>296000</v>
+      </c>
+      <c r="D31" s="3">
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="E31">
-        <v>9.17</v>
+        <v>6.14</v>
       </c>
       <c r="F31">
-        <v>9.17</v>
+        <v>6.14</v>
       </c>
       <c r="G31">
-        <v>9.1</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="H31" s="4">
-        <v>162088.94</v>
+        <v>243518.36</v>
       </c>
       <c r="I31">
-        <v>3.63</v>
+        <v>0.64</v>
       </c>
       <c r="J31">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="K31">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L31">
-        <v>97.67</v>
+        <v>108.56</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1953,37 +2235,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>155200</v>
+        <v>21250</v>
       </c>
       <c r="D32" s="3">
-        <v>-3.2000000000000002E-3</v>
+        <v>1.9199999999999998E-2</v>
       </c>
       <c r="E32">
-        <v>8.86</v>
+        <v>6.9</v>
       </c>
       <c r="F32">
-        <v>11.63</v>
+        <v>6.9</v>
       </c>
       <c r="G32">
-        <v>8.51</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="H32" s="4">
-        <v>160038.65</v>
+        <v>28168.11</v>
       </c>
       <c r="I32">
-        <v>2.0499999999999998</v>
+        <v>3.29</v>
       </c>
       <c r="J32">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K32">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="L32">
-        <v>100.49</v>
+        <v>97.97</v>
       </c>
       <c r="M32">
-        <v>5.29</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -1994,37 +2276,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>18850</v>
+        <v>400500</v>
       </c>
       <c r="D33" s="3">
-        <v>0.02</v>
+        <v>-3.0300000000000001E-2</v>
       </c>
       <c r="E33">
-        <v>6.96</v>
+        <v>7.68</v>
       </c>
       <c r="F33">
-        <v>9.58</v>
+        <v>7.68</v>
       </c>
       <c r="G33">
-        <v>7.18</v>
+        <v>8.59</v>
       </c>
       <c r="H33" s="4">
-        <v>34223.949999999997</v>
+        <v>545786.89</v>
       </c>
       <c r="I33">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="J33">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="K33">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="L33">
-        <v>97.04</v>
+        <v>91.74</v>
       </c>
       <c r="M33">
-        <v>2.84</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2035,37 +2317,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>17240</v>
+        <v>1320000</v>
       </c>
       <c r="D34" s="3">
-        <v>2.6200000000000001E-2</v>
+        <v>-0.04</v>
       </c>
       <c r="E34">
-        <v>3.6</v>
+        <v>53.94</v>
       </c>
       <c r="F34">
-        <v>9.42</v>
+        <v>14.72</v>
       </c>
       <c r="G34">
-        <v>5.91</v>
+        <v>28.78</v>
       </c>
       <c r="H34" s="4">
-        <v>38541.279999999999</v>
+        <v>174991.05</v>
       </c>
       <c r="I34">
-        <v>2.9</v>
+        <v>0.27</v>
       </c>
       <c r="J34">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="K34">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="L34">
-        <v>96.19</v>
+        <v>97.25</v>
       </c>
       <c r="M34">
-        <v>0.76</v>
+        <v>-9.2799999999999994</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2076,37 +2358,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>57400</v>
+        <v>49150</v>
       </c>
       <c r="D35" s="3">
-        <v>7.0000000000000001E-3</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="E35">
-        <v>10.79</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="F35">
-        <v>10.55</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="G35">
-        <v>8.93</v>
+        <v>5.33</v>
       </c>
       <c r="H35" s="4">
-        <v>92723.77</v>
+        <v>75035.259999999995</v>
       </c>
       <c r="I35">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="J35">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K35">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L35">
-        <v>90.82</v>
+        <v>93.91</v>
       </c>
       <c r="M35">
-        <v>-2.88</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2117,37 +2399,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>30950</v>
+        <v>102300</v>
       </c>
       <c r="D36" s="3">
-        <v>2.4799999999999999E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="E36">
-        <v>12.8</v>
+        <v>12.89</v>
       </c>
       <c r="F36">
-        <v>13.49</v>
+        <v>13.94</v>
       </c>
       <c r="G36">
-        <v>12.93</v>
+        <v>9.44</v>
       </c>
       <c r="H36" s="4">
-        <v>31004.78</v>
+        <v>87743.72</v>
       </c>
       <c r="I36">
-        <v>3.21</v>
+        <v>3.42</v>
       </c>
       <c r="J36">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K36">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L36">
-        <v>98.82</v>
+        <v>101.8</v>
       </c>
       <c r="M36">
-        <v>1.1399999999999999</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2158,37 +2440,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>50900</v>
+        <v>78800</v>
       </c>
       <c r="D37" s="3">
-        <v>1.1900000000000001E-2</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="E37">
-        <v>18.690000000000001</v>
+        <v>3.33</v>
       </c>
       <c r="F37">
-        <v>11.56</v>
+        <v>3.33</v>
       </c>
       <c r="G37">
-        <v>6.83</v>
+        <v>7.93</v>
       </c>
       <c r="H37" s="4">
-        <v>57293.3</v>
+        <v>60299.05</v>
       </c>
       <c r="I37">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="J37">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="K37">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="L37">
-        <v>98.67</v>
+        <v>100.76</v>
       </c>
       <c r="M37">
-        <v>3.46</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2199,36 +2481,1963 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
+        <v>88800</v>
+      </c>
+      <c r="D38" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="E38">
+        <v>14.42</v>
+      </c>
+      <c r="F38">
+        <v>24.2</v>
+      </c>
+      <c r="G38">
+        <v>15.82</v>
+      </c>
+      <c r="H38" s="4">
+        <v>36460.550000000003</v>
+      </c>
+      <c r="I38">
+        <v>6.19</v>
+      </c>
+      <c r="J38">
+        <v>73</v>
+      </c>
+      <c r="K38">
+        <v>73</v>
+      </c>
+      <c r="L38">
+        <v>95.04</v>
+      </c>
+      <c r="M38">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="2">
+        <v>162600</v>
+      </c>
+      <c r="D39" s="3">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="E39">
+        <v>7.89</v>
+      </c>
+      <c r="F39">
+        <v>7.89</v>
+      </c>
+      <c r="G39">
+        <v>8.18</v>
+      </c>
+      <c r="H39" s="4">
+        <v>128172.41</v>
+      </c>
+      <c r="I39">
+        <v>1.96</v>
+      </c>
+      <c r="J39">
+        <v>60</v>
+      </c>
+      <c r="K39">
+        <v>60</v>
+      </c>
+      <c r="L39">
+        <v>96.42</v>
+      </c>
+      <c r="M39">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="2">
+        <v>74400</v>
+      </c>
+      <c r="D40" s="3">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="E40">
+        <v>18.14</v>
+      </c>
+      <c r="F40">
+        <v>18.14</v>
+      </c>
+      <c r="G40">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="H40" s="4">
+        <v>51783.79</v>
+      </c>
+      <c r="I40">
+        <v>2.61</v>
+      </c>
+      <c r="J40">
+        <v>46</v>
+      </c>
+      <c r="K40">
+        <v>46</v>
+      </c>
+      <c r="L40">
+        <v>95.93</v>
+      </c>
+      <c r="M40">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="2">
+        <v>32400</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="E41">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="F41">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="G41">
+        <v>16.18</v>
+      </c>
+      <c r="H41" s="4">
+        <v>3753.16</v>
+      </c>
+      <c r="I41">
+        <v>0.39</v>
+      </c>
+      <c r="J41">
+        <v>37</v>
+      </c>
+      <c r="K41">
+        <v>37</v>
+      </c>
+      <c r="L41">
+        <v>95.32</v>
+      </c>
+      <c r="M41">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="2">
+        <v>24100</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="E42">
+        <v>8.06</v>
+      </c>
+      <c r="F42">
+        <v>8.64</v>
+      </c>
+      <c r="G42">
+        <v>8.77</v>
+      </c>
+      <c r="H42" s="4">
+        <v>44443.18</v>
+      </c>
+      <c r="I42">
+        <v>4.42</v>
+      </c>
+      <c r="J42">
+        <v>74</v>
+      </c>
+      <c r="K42">
+        <v>74</v>
+      </c>
+      <c r="L42">
+        <v>98.45</v>
+      </c>
+      <c r="M42">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="2">
+        <v>35300</v>
+      </c>
+      <c r="D43" s="3">
+        <v>8.2799999999999999E-2</v>
+      </c>
+      <c r="E43">
+        <v>13.76</v>
+      </c>
+      <c r="F43">
+        <v>13.76</v>
+      </c>
+      <c r="G43">
+        <v>19.29</v>
+      </c>
+      <c r="H43" s="4">
+        <v>24187.31</v>
+      </c>
+      <c r="I43">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="J43">
+        <v>83</v>
+      </c>
+      <c r="K43">
+        <v>83</v>
+      </c>
+      <c r="L43">
+        <v>104.09</v>
+      </c>
+      <c r="M43">
+        <v>12.96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="2">
+        <v>297500</v>
+      </c>
+      <c r="D44" s="3">
+        <v>2.23E-2</v>
+      </c>
+      <c r="E44">
+        <v>6.02</v>
+      </c>
+      <c r="F44">
+        <v>6.02</v>
+      </c>
+      <c r="G44">
+        <v>6.71</v>
+      </c>
+      <c r="H44" s="4">
+        <v>294896.78000000003</v>
+      </c>
+      <c r="I44">
+        <v>0.94</v>
+      </c>
+      <c r="J44">
+        <v>75</v>
+      </c>
+      <c r="K44">
+        <v>75</v>
+      </c>
+      <c r="L44">
+        <v>98.23</v>
+      </c>
+      <c r="M44">
+        <v>8.9700000000000006</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="2">
+        <v>59700</v>
+      </c>
+      <c r="D45" s="3">
+        <v>-1.6999999999999999E-3</v>
+      </c>
+      <c r="E45">
+        <v>7.45</v>
+      </c>
+      <c r="F45">
+        <v>7.45</v>
+      </c>
+      <c r="G45">
+        <v>7.69</v>
+      </c>
+      <c r="H45" s="4">
+        <v>79986.48</v>
+      </c>
+      <c r="I45">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="J45">
+        <v>77</v>
+      </c>
+      <c r="K45">
+        <v>77</v>
+      </c>
+      <c r="L45">
+        <v>98.04</v>
+      </c>
+      <c r="M45">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="2">
+        <v>21300</v>
+      </c>
+      <c r="D46" s="3">
+        <v>1.67E-2</v>
+      </c>
+      <c r="E46">
+        <v>13.7</v>
+      </c>
+      <c r="F46">
+        <v>13.7</v>
+      </c>
+      <c r="G46">
+        <v>14.6</v>
+      </c>
+      <c r="H46" s="4">
+        <v>16125.49</v>
+      </c>
+      <c r="I46">
+        <v>5.77</v>
+      </c>
+      <c r="J46">
+        <v>48</v>
+      </c>
+      <c r="K46">
+        <v>48</v>
+      </c>
+      <c r="L46">
+        <v>100.84</v>
+      </c>
+      <c r="M46">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="2">
+        <v>60700</v>
+      </c>
+      <c r="D47" s="3">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="E47">
+        <v>10.220000000000001</v>
+      </c>
+      <c r="F47">
+        <v>10.220000000000001</v>
+      </c>
+      <c r="G47">
+        <v>6.37</v>
+      </c>
+      <c r="H47" s="4">
+        <v>71885.83</v>
+      </c>
+      <c r="I47">
+        <v>3.95</v>
+      </c>
+      <c r="J47">
+        <v>79</v>
+      </c>
+      <c r="K47">
+        <v>79</v>
+      </c>
+      <c r="L47">
+        <v>98.58</v>
+      </c>
+      <c r="M47">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B48" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="2">
+        <v>15820</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="E48">
+        <v>6.01</v>
+      </c>
+      <c r="F48">
+        <v>6.01</v>
+      </c>
+      <c r="G48">
+        <v>5.97</v>
+      </c>
+      <c r="H48" s="4">
+        <v>20769.650000000001</v>
+      </c>
+      <c r="I48">
+        <v>4.17</v>
+      </c>
+      <c r="J48">
+        <v>74</v>
+      </c>
+      <c r="K48">
+        <v>74</v>
+      </c>
+      <c r="L48">
+        <v>99.7</v>
+      </c>
+      <c r="M48">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="2">
+        <v>231500</v>
+      </c>
+      <c r="D49" s="3">
+        <v>4.3E-3</v>
+      </c>
+      <c r="E49">
+        <v>4.66</v>
+      </c>
+      <c r="F49">
+        <v>4.66</v>
+      </c>
+      <c r="G49">
+        <v>4.88</v>
+      </c>
+      <c r="H49" s="4">
+        <v>324173.33</v>
+      </c>
+      <c r="I49">
+        <v>2.29</v>
+      </c>
+      <c r="J49">
+        <v>86</v>
+      </c>
+      <c r="K49">
+        <v>86</v>
+      </c>
+      <c r="L49">
+        <v>104.47</v>
+      </c>
+      <c r="M49">
+        <v>9.4600000000000009</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="2">
+        <v>157500</v>
+      </c>
+      <c r="D50" s="3">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="E50">
+        <v>11.77</v>
+      </c>
+      <c r="F50">
+        <v>11.77</v>
+      </c>
+      <c r="G50">
+        <v>11.4</v>
+      </c>
+      <c r="H50" s="4">
+        <v>85735.74</v>
+      </c>
+      <c r="I50">
+        <v>3.81</v>
+      </c>
+      <c r="J50">
+        <v>77</v>
+      </c>
+      <c r="K50">
+        <v>77</v>
+      </c>
+      <c r="L50">
+        <v>97.91</v>
+      </c>
+      <c r="M50">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="2">
+        <v>18190</v>
+      </c>
+      <c r="D51" s="3">
+        <v>1.9E-2</v>
+      </c>
+      <c r="E51">
+        <v>8.11</v>
+      </c>
+      <c r="F51">
+        <v>8.11</v>
+      </c>
+      <c r="G51">
+        <v>9.93</v>
+      </c>
+      <c r="H51" s="4">
+        <v>19583.27</v>
+      </c>
+      <c r="I51">
+        <v>5.22</v>
+      </c>
+      <c r="J51">
+        <v>30</v>
+      </c>
+      <c r="K51">
+        <v>30</v>
+      </c>
+      <c r="L51">
+        <v>98.7</v>
+      </c>
+      <c r="M51">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="2">
+        <v>221500</v>
+      </c>
+      <c r="D52" s="3">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="E52">
+        <v>7.36</v>
+      </c>
+      <c r="F52">
+        <v>7.36</v>
+      </c>
+      <c r="G52">
+        <v>6.56</v>
+      </c>
+      <c r="H52" s="4">
+        <v>180116.6</v>
+      </c>
+      <c r="I52">
+        <v>1.19</v>
+      </c>
+      <c r="J52">
+        <v>22</v>
+      </c>
+      <c r="K52">
+        <v>22</v>
+      </c>
+      <c r="L52">
+        <v>95.56</v>
+      </c>
+      <c r="M52">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="2">
+        <v>50000</v>
+      </c>
+      <c r="D53" s="5">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F53">
+        <v>5.88</v>
+      </c>
+      <c r="G53">
+        <v>1.31</v>
+      </c>
+      <c r="H53" s="4">
+        <v>24000.959999999999</v>
+      </c>
+      <c r="I53">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J53">
+        <v>12</v>
+      </c>
+      <c r="K53">
+        <v>12</v>
+      </c>
+      <c r="L53">
+        <v>93.44</v>
+      </c>
+      <c r="M53">
+        <v>-3.47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="2">
+        <v>37700</v>
+      </c>
+      <c r="D54" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="E54">
+        <v>1.23</v>
+      </c>
+      <c r="F54">
+        <v>1.23</v>
+      </c>
+      <c r="G54">
+        <v>1.59</v>
+      </c>
+      <c r="H54" s="4">
+        <v>118301.94</v>
+      </c>
+      <c r="I54">
+        <v>3.06</v>
+      </c>
+      <c r="J54">
+        <v>36</v>
+      </c>
+      <c r="K54">
+        <v>36</v>
+      </c>
+      <c r="L54">
+        <v>97.4</v>
+      </c>
+      <c r="M54">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B55" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="2">
+        <v>460500</v>
+      </c>
+      <c r="D55" s="3">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="E55">
+        <v>15.98</v>
+      </c>
+      <c r="F55">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="G55">
+        <v>12.25</v>
+      </c>
+      <c r="H55" s="4">
+        <v>238844.91</v>
+      </c>
+      <c r="I55">
+        <v>1.63</v>
+      </c>
+      <c r="J55">
+        <v>87</v>
+      </c>
+      <c r="K55">
+        <v>87</v>
+      </c>
+      <c r="L55">
+        <v>103.17</v>
+      </c>
+      <c r="M55">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A56" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="2">
+        <v>309500</v>
+      </c>
+      <c r="D56" s="3">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="E56">
+        <v>34.76</v>
+      </c>
+      <c r="F56">
+        <v>34.76</v>
+      </c>
+      <c r="G56">
+        <v>39.24</v>
+      </c>
+      <c r="H56" s="4">
+        <v>7523.78</v>
+      </c>
+      <c r="I56">
+        <v>0.26</v>
+      </c>
+      <c r="J56">
+        <v>92</v>
+      </c>
+      <c r="K56">
+        <v>92</v>
+      </c>
+      <c r="L56">
+        <v>108.41</v>
+      </c>
+      <c r="M56">
+        <v>-4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A57" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="2">
+        <v>77000</v>
+      </c>
+      <c r="D57" s="3">
+        <v>7.2400000000000006E-2</v>
+      </c>
+      <c r="E57">
+        <v>9.27</v>
+      </c>
+      <c r="F57">
+        <v>9.27</v>
+      </c>
+      <c r="G57">
+        <v>10.26</v>
+      </c>
+      <c r="H57" s="4">
+        <v>38290.26</v>
+      </c>
+      <c r="I57">
+        <v>2.4</v>
+      </c>
+      <c r="J57">
+        <v>75</v>
+      </c>
+      <c r="K57">
+        <v>75</v>
+      </c>
+      <c r="L57">
+        <v>105.33</v>
+      </c>
+      <c r="M57">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A58" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="2">
+        <v>185700</v>
+      </c>
+      <c r="D58" s="3">
+        <v>-2.47E-2</v>
+      </c>
+      <c r="E58">
+        <v>10.42</v>
+      </c>
+      <c r="F58">
+        <v>9.58</v>
+      </c>
+      <c r="G58">
+        <v>11.34</v>
+      </c>
+      <c r="H58" s="4">
+        <v>18284.689999999999</v>
+      </c>
+      <c r="I58">
+        <v>0.27</v>
+      </c>
+      <c r="J58">
+        <v>84</v>
+      </c>
+      <c r="K58">
+        <v>84</v>
+      </c>
+      <c r="L58">
+        <v>101.39</v>
+      </c>
+      <c r="M58">
+        <v>6.66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A59" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" s="2">
+        <v>97900</v>
+      </c>
+      <c r="D59" s="3">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="E59">
+        <v>8.11</v>
+      </c>
+      <c r="F59">
+        <v>10.44</v>
+      </c>
+      <c r="G59">
+        <v>8.66</v>
+      </c>
+      <c r="H59" s="4">
+        <v>119742.76</v>
+      </c>
+      <c r="I59">
+        <v>2.21</v>
+      </c>
+      <c r="J59">
+        <v>88</v>
+      </c>
+      <c r="K59">
+        <v>88</v>
+      </c>
+      <c r="L59">
+        <v>103.42</v>
+      </c>
+      <c r="M59">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A60" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" s="2">
+        <v>180100</v>
+      </c>
+      <c r="D60" s="3">
+        <v>-3.3300000000000003E-2</v>
+      </c>
+      <c r="E60">
+        <v>30.05</v>
+      </c>
+      <c r="F60">
+        <v>30.05</v>
+      </c>
+      <c r="G60">
+        <v>20.65</v>
+      </c>
+      <c r="H60" s="4">
+        <v>28211.09</v>
+      </c>
+      <c r="I60">
+        <v>0.33</v>
+      </c>
+      <c r="J60">
+        <v>63</v>
+      </c>
+      <c r="K60">
+        <v>63</v>
+      </c>
+      <c r="L60">
+        <v>85.34</v>
+      </c>
+      <c r="M60">
+        <v>-13.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A61" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="2">
+        <v>117900</v>
+      </c>
+      <c r="D61" s="3">
+        <v>1.46E-2</v>
+      </c>
+      <c r="E61">
+        <v>4.28</v>
+      </c>
+      <c r="F61">
+        <v>4.28</v>
+      </c>
+      <c r="G61">
+        <v>3.26</v>
+      </c>
+      <c r="H61" s="4">
+        <v>132655.74</v>
+      </c>
+      <c r="I61">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J61">
+        <v>49</v>
+      </c>
+      <c r="K61">
+        <v>49</v>
+      </c>
+      <c r="L61">
+        <v>96.5</v>
+      </c>
+      <c r="M61">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A62" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="2">
+        <v>202000</v>
+      </c>
+      <c r="D62" s="5">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>2.46</v>
+      </c>
+      <c r="F62">
+        <v>3.92</v>
+      </c>
+      <c r="G62">
+        <v>6.96</v>
+      </c>
+      <c r="H62" s="4">
+        <v>81630.009999999995</v>
+      </c>
+      <c r="I62">
+        <v>0.37</v>
+      </c>
+      <c r="J62">
+        <v>50</v>
+      </c>
+      <c r="K62">
+        <v>50</v>
+      </c>
+      <c r="L62">
+        <v>92.77</v>
+      </c>
+      <c r="M62">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="2">
+        <v>234500</v>
+      </c>
+      <c r="D63" s="3">
+        <v>2.4E-2</v>
+      </c>
+      <c r="E63">
+        <v>11.54</v>
+      </c>
+      <c r="F63">
+        <v>20.98</v>
+      </c>
+      <c r="G63">
+        <v>9.6</v>
+      </c>
+      <c r="H63" s="4">
+        <v>189057.03</v>
+      </c>
+      <c r="I63">
+        <v>1.7</v>
+      </c>
+      <c r="J63">
+        <v>74</v>
+      </c>
+      <c r="K63">
+        <v>74</v>
+      </c>
+      <c r="L63">
+        <v>97.34</v>
+      </c>
+      <c r="M63">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A64" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="2">
+        <v>69000</v>
+      </c>
+      <c r="D64" s="3">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E64">
+        <v>4.12</v>
+      </c>
+      <c r="F64">
+        <v>5.22</v>
+      </c>
+      <c r="G64">
+        <v>11.01</v>
+      </c>
+      <c r="H64" s="4">
+        <v>151788</v>
+      </c>
+      <c r="I64">
+        <v>3.91</v>
+      </c>
+      <c r="J64">
+        <v>74</v>
+      </c>
+      <c r="K64">
+        <v>74</v>
+      </c>
+      <c r="L64">
+        <v>102.23</v>
+      </c>
+      <c r="M64">
+        <v>7.81</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B65" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="2">
+        <v>661000</v>
+      </c>
+      <c r="D65" s="3">
+        <v>-5.8400000000000001E-2</v>
+      </c>
+      <c r="E65">
+        <v>19.59</v>
+      </c>
+      <c r="F65">
+        <v>25.3</v>
+      </c>
+      <c r="G65">
+        <v>17.23</v>
+      </c>
+      <c r="H65" s="4">
+        <v>64298.52</v>
+      </c>
+      <c r="I65">
+        <v>0.36</v>
+      </c>
+      <c r="J65">
+        <v>72</v>
+      </c>
+      <c r="K65">
+        <v>72</v>
+      </c>
+      <c r="L65">
+        <v>100.48</v>
+      </c>
+      <c r="M65">
+        <v>-12.91</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A66" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B66" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="2">
+        <v>230500</v>
+      </c>
+      <c r="D66" s="5">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>13.24</v>
+      </c>
+      <c r="F66">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="G66">
+        <v>15.51</v>
+      </c>
+      <c r="H66" s="4">
+        <v>130762.28</v>
+      </c>
+      <c r="I66">
+        <v>1.61</v>
+      </c>
+      <c r="J66">
+        <v>71</v>
+      </c>
+      <c r="K66">
+        <v>71</v>
+      </c>
+      <c r="L66">
+        <v>93.21</v>
+      </c>
+      <c r="M66">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A67" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="2">
+        <v>113200</v>
+      </c>
+      <c r="D67" s="5">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>9.17</v>
+      </c>
+      <c r="F67">
+        <v>9.17</v>
+      </c>
+      <c r="G67">
+        <v>9.1</v>
+      </c>
+      <c r="H67" s="4">
+        <v>162088.94</v>
+      </c>
+      <c r="I67">
+        <v>3.63</v>
+      </c>
+      <c r="J67">
+        <v>80</v>
+      </c>
+      <c r="K67">
+        <v>80</v>
+      </c>
+      <c r="L67">
+        <v>97.67</v>
+      </c>
+      <c r="M67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A68" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" s="2">
+        <v>140800</v>
+      </c>
+      <c r="D68" s="3">
+        <v>4.53E-2</v>
+      </c>
+      <c r="E68">
+        <v>11.69</v>
+      </c>
+      <c r="F68">
+        <v>5.33</v>
+      </c>
+      <c r="G68">
+        <v>6.07</v>
+      </c>
+      <c r="H68" s="4">
+        <v>77979.460000000006</v>
+      </c>
+      <c r="I68">
+        <v>0.8</v>
+      </c>
+      <c r="J68">
+        <v>25</v>
+      </c>
+      <c r="K68">
+        <v>25</v>
+      </c>
+      <c r="L68">
+        <v>101.19</v>
+      </c>
+      <c r="M68">
+        <v>8.98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="2">
+        <v>155200</v>
+      </c>
+      <c r="D69" s="3">
+        <v>-3.2000000000000002E-3</v>
+      </c>
+      <c r="E69">
+        <v>8.86</v>
+      </c>
+      <c r="F69">
+        <v>11.63</v>
+      </c>
+      <c r="G69">
+        <v>8.51</v>
+      </c>
+      <c r="H69" s="4">
+        <v>160038.65</v>
+      </c>
+      <c r="I69">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="J69">
+        <v>87</v>
+      </c>
+      <c r="K69">
+        <v>87</v>
+      </c>
+      <c r="L69">
+        <v>100.49</v>
+      </c>
+      <c r="M69">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="2">
+        <v>560000</v>
+      </c>
+      <c r="D70" s="3">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="E70">
+        <v>11.89</v>
+      </c>
+      <c r="F70">
+        <v>14.27</v>
+      </c>
+      <c r="G70">
+        <v>12.6</v>
+      </c>
+      <c r="H70" s="4">
+        <v>95809.42</v>
+      </c>
+      <c r="I70">
+        <v>0.22</v>
+      </c>
+      <c r="J70">
+        <v>80</v>
+      </c>
+      <c r="K70">
+        <v>80</v>
+      </c>
+      <c r="L70">
+        <v>103.69</v>
+      </c>
+      <c r="M70">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A71" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" s="2">
+        <v>110100</v>
+      </c>
+      <c r="D71" s="3">
+        <v>-7.1999999999999998E-3</v>
+      </c>
+      <c r="E71">
+        <v>23.44</v>
+      </c>
+      <c r="F71">
+        <v>25.94</v>
+      </c>
+      <c r="G71">
+        <v>27.89</v>
+      </c>
+      <c r="H71" s="4">
+        <v>59980.14</v>
+      </c>
+      <c r="I71">
+        <v>1.23</v>
+      </c>
+      <c r="J71">
+        <v>71</v>
+      </c>
+      <c r="K71">
+        <v>71</v>
+      </c>
+      <c r="L71">
+        <v>91.91</v>
+      </c>
+      <c r="M71">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A72" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" s="2">
+        <v>18850</v>
+      </c>
+      <c r="D72" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="E72">
+        <v>6.96</v>
+      </c>
+      <c r="F72">
+        <v>9.58</v>
+      </c>
+      <c r="G72">
+        <v>7.18</v>
+      </c>
+      <c r="H72" s="4">
+        <v>34223.949999999997</v>
+      </c>
+      <c r="I72">
+        <v>3.45</v>
+      </c>
+      <c r="J72">
+        <v>75</v>
+      </c>
+      <c r="K72">
+        <v>75</v>
+      </c>
+      <c r="L72">
+        <v>97.04</v>
+      </c>
+      <c r="M72">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A73" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" s="2">
+        <v>17240</v>
+      </c>
+      <c r="D73" s="3">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="E73">
+        <v>3.6</v>
+      </c>
+      <c r="F73">
+        <v>9.42</v>
+      </c>
+      <c r="G73">
+        <v>5.91</v>
+      </c>
+      <c r="H73" s="4">
+        <v>38541.279999999999</v>
+      </c>
+      <c r="I73">
+        <v>2.9</v>
+      </c>
+      <c r="J73">
+        <v>69</v>
+      </c>
+      <c r="K73">
+        <v>69</v>
+      </c>
+      <c r="L73">
+        <v>96.19</v>
+      </c>
+      <c r="M73">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A74" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="2">
+        <v>57400</v>
+      </c>
+      <c r="D74" s="3">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="E74">
+        <v>10.79</v>
+      </c>
+      <c r="F74">
+        <v>10.55</v>
+      </c>
+      <c r="G74">
+        <v>8.93</v>
+      </c>
+      <c r="H74" s="4">
+        <v>92723.77</v>
+      </c>
+      <c r="I74">
+        <v>3.48</v>
+      </c>
+      <c r="J74">
+        <v>57</v>
+      </c>
+      <c r="K74">
+        <v>57</v>
+      </c>
+      <c r="L74">
+        <v>90.82</v>
+      </c>
+      <c r="M74">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A75" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75" s="2">
+        <v>30950</v>
+      </c>
+      <c r="D75" s="3">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="E75">
+        <v>12.8</v>
+      </c>
+      <c r="F75">
+        <v>13.49</v>
+      </c>
+      <c r="G75">
+        <v>12.93</v>
+      </c>
+      <c r="H75" s="4">
+        <v>31004.78</v>
+      </c>
+      <c r="I75">
+        <v>3.21</v>
+      </c>
+      <c r="J75">
+        <v>77</v>
+      </c>
+      <c r="K75">
+        <v>77</v>
+      </c>
+      <c r="L75">
+        <v>98.82</v>
+      </c>
+      <c r="M75">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="2">
+        <v>130000</v>
+      </c>
+      <c r="D76" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="E76">
+        <v>16.75</v>
+      </c>
+      <c r="F76">
+        <v>4.34</v>
+      </c>
+      <c r="G76">
+        <v>21.73</v>
+      </c>
+      <c r="H76" s="4">
+        <v>49146.79</v>
+      </c>
+      <c r="I76">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J76">
+        <v>68</v>
+      </c>
+      <c r="K76">
+        <v>68</v>
+      </c>
+      <c r="L76">
+        <v>97.56</v>
+      </c>
+      <c r="M76">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A77" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B77" t="s">
+        <v>162</v>
+      </c>
+      <c r="C77" s="2">
+        <v>50900</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="E77">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="F77">
+        <v>11.56</v>
+      </c>
+      <c r="G77">
+        <v>6.83</v>
+      </c>
+      <c r="H77" s="4">
+        <v>57293.3</v>
+      </c>
+      <c r="I77">
+        <v>2.36</v>
+      </c>
+      <c r="J77">
+        <v>47</v>
+      </c>
+      <c r="K77">
+        <v>47</v>
+      </c>
+      <c r="L77">
+        <v>98.67</v>
+      </c>
+      <c r="M77">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A78" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B78" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" s="2">
+        <v>63100</v>
+      </c>
+      <c r="D78" s="3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E78">
+        <v>8.77</v>
+      </c>
+      <c r="F78">
+        <v>6.11</v>
+      </c>
+      <c r="G78">
+        <v>13.11</v>
+      </c>
+      <c r="H78" s="4">
+        <v>72587.83</v>
+      </c>
+      <c r="I78">
+        <v>2.54</v>
+      </c>
+      <c r="J78">
+        <v>77</v>
+      </c>
+      <c r="K78">
+        <v>77</v>
+      </c>
+      <c r="L78">
+        <v>102.94</v>
+      </c>
+      <c r="M78">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A79" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B79" t="s">
+        <v>166</v>
+      </c>
+      <c r="C79" s="2">
+        <v>265500</v>
+      </c>
+      <c r="D79" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="E79">
+        <v>6.36</v>
+      </c>
+      <c r="F79">
+        <v>7.5</v>
+      </c>
+      <c r="G79">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="H79" s="4">
+        <v>128102.48</v>
+      </c>
+      <c r="I79">
+        <v>1.36</v>
+      </c>
+      <c r="J79">
+        <v>81</v>
+      </c>
+      <c r="K79">
+        <v>81</v>
+      </c>
+      <c r="L79">
+        <v>95.58</v>
+      </c>
+      <c r="M79">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A80" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B80" t="s">
+        <v>168</v>
+      </c>
+      <c r="C80" s="2">
+        <v>959000</v>
+      </c>
+      <c r="D80" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="E80">
+        <v>41.5</v>
+      </c>
+      <c r="F80">
+        <v>41.5</v>
+      </c>
+      <c r="G80">
+        <v>36.18</v>
+      </c>
+      <c r="H80" s="4">
+        <v>56703.88</v>
+      </c>
+      <c r="I80">
+        <v>0.74</v>
+      </c>
+      <c r="J80">
+        <v>86</v>
+      </c>
+      <c r="K80">
+        <v>86</v>
+      </c>
+      <c r="L80">
+        <v>98</v>
+      </c>
+      <c r="M80">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A81" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B81" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" s="2">
+        <v>133000</v>
+      </c>
+      <c r="D81" s="3">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="E81">
+        <v>6.18</v>
+      </c>
+      <c r="F81">
+        <v>5.98</v>
+      </c>
+      <c r="G81">
+        <v>7.78</v>
+      </c>
+      <c r="H81" s="4">
+        <v>102514.49</v>
+      </c>
+      <c r="I81">
+        <v>0.38</v>
+      </c>
+      <c r="J81">
+        <v>87</v>
+      </c>
+      <c r="K81">
+        <v>87</v>
+      </c>
+      <c r="L81">
+        <v>100.4</v>
+      </c>
+      <c r="M81">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A82" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82" s="2">
+        <v>136000</v>
+      </c>
+      <c r="D82" s="3">
+        <v>-3.5499999999999997E-2</v>
+      </c>
+      <c r="E82">
+        <v>6.6</v>
+      </c>
+      <c r="F82">
+        <v>6.6</v>
+      </c>
+      <c r="G82">
+        <v>14.36</v>
+      </c>
+      <c r="H82" s="4">
+        <v>25848.86</v>
+      </c>
+      <c r="I82">
+        <v>0.37</v>
+      </c>
+      <c r="J82">
+        <v>72</v>
+      </c>
+      <c r="K82">
+        <v>72</v>
+      </c>
+      <c r="L82">
+        <v>100.53</v>
+      </c>
+      <c r="M82">
+        <v>-12.93</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A83" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B83" t="s">
+        <v>174</v>
+      </c>
+      <c r="C83" s="2">
+        <v>2735000</v>
+      </c>
+      <c r="D83" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="E83">
+        <v>24.41</v>
+      </c>
+      <c r="F83">
+        <v>24.41</v>
+      </c>
+      <c r="G83">
+        <v>16.87</v>
+      </c>
+      <c r="H83" s="4">
+        <v>252284.7</v>
+      </c>
+      <c r="I83">
+        <v>0.27</v>
+      </c>
+      <c r="J83">
+        <v>93</v>
+      </c>
+      <c r="K83">
+        <v>93</v>
+      </c>
+      <c r="L83">
+        <v>104.52</v>
+      </c>
+      <c r="M83">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A84" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" t="s">
+        <v>176</v>
+      </c>
+      <c r="C84" s="2">
+        <v>430500</v>
+      </c>
+      <c r="D84" s="3">
+        <v>1.06E-2</v>
+      </c>
+      <c r="E84">
+        <v>10.4</v>
+      </c>
+      <c r="F84">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="G84">
+        <v>9.14</v>
+      </c>
+      <c r="H84" s="4">
+        <v>65279.4</v>
+      </c>
+      <c r="I84">
+        <v>0.41</v>
+      </c>
+      <c r="J84">
+        <v>75</v>
+      </c>
+      <c r="K84">
+        <v>75</v>
+      </c>
+      <c r="L84">
+        <v>100.33</v>
+      </c>
+      <c r="M84">
+        <v>7.76</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A85" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B85" t="s">
+        <v>178</v>
+      </c>
+      <c r="C85" s="2">
         <v>33900</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D85" s="3">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="E38">
+      <c r="E85">
         <v>9.39</v>
       </c>
-      <c r="F38">
+      <c r="F85">
         <v>10.74</v>
       </c>
-      <c r="G38">
+      <c r="G85">
         <v>9.73</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H85" s="4">
         <v>48211.77</v>
       </c>
-      <c r="I38">
+      <c r="I85">
         <v>3.54</v>
       </c>
-      <c r="J38">
+      <c r="J85">
         <v>76</v>
       </c>
-      <c r="K38">
+      <c r="K85">
         <v>76</v>
       </c>
-      <c r="L38">
+      <c r="L85">
         <v>97.67</v>
       </c>
-      <c r="M38">
+      <c r="M85">
         <v>5.61</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B5A4CBF-6AEF-419C-AD08-673C909B37FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{992102F2-0DCA-4964-B51B-99F621F8F94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9A05698F-BC93-4BB8-8F96-A65965D27E9D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E524DFF4-9F2F-46DB-97BD-49B189E3F2FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="199">
   <si>
     <t>종목코드</t>
   </si>
@@ -120,6 +120,18 @@
     <t>세아베스틸지주</t>
   </si>
   <si>
+    <t>001680</t>
+  </si>
+  <si>
+    <t>대상</t>
+  </si>
+  <si>
+    <t>002310</t>
+  </si>
+  <si>
+    <t>아세아제지</t>
+  </si>
+  <si>
     <t>003230</t>
   </si>
   <si>
@@ -150,6 +162,24 @@
     <t>코리안리</t>
   </si>
   <si>
+    <t>004370</t>
+  </si>
+  <si>
+    <t>농심</t>
+  </si>
+  <si>
+    <t>004980</t>
+  </si>
+  <si>
+    <t>성신양회</t>
+  </si>
+  <si>
+    <t>005180</t>
+  </si>
+  <si>
+    <t>빙그레</t>
+  </si>
+  <si>
     <t>005380</t>
   </si>
   <si>
@@ -192,6 +222,12 @@
     <t>미래에셋증권</t>
   </si>
   <si>
+    <t>007310</t>
+  </si>
+  <si>
+    <t>오뚜기</t>
+  </si>
+  <si>
     <t>007340</t>
   </si>
   <si>
@@ -246,6 +282,12 @@
     <t>HMM</t>
   </si>
   <si>
+    <t>011780</t>
+  </si>
+  <si>
+    <t>금호석유화학</t>
+  </si>
+  <si>
     <t>012330</t>
   </si>
   <si>
@@ -510,12 +552,24 @@
     <t>한진칼</t>
   </si>
   <si>
+    <t>183190</t>
+  </si>
+  <si>
+    <t>아세아시멘트</t>
+  </si>
+  <si>
     <t>192080</t>
   </si>
   <si>
     <t>더블유게임즈</t>
   </si>
   <si>
+    <t>214320</t>
+  </si>
+  <si>
+    <t>이노션</t>
+  </si>
+  <si>
     <t>241560</t>
   </si>
   <si>
@@ -550,6 +604,12 @@
   </si>
   <si>
     <t>효성중공업</t>
+  </si>
+  <si>
+    <t>300720</t>
+  </si>
+  <si>
+    <t>한일시멘트</t>
   </si>
   <si>
     <t>307950</t>
@@ -939,8 +999,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A212A883-B510-4B09-A0D5-0BA3DCA570C4}">
-  <dimension ref="A1:M85"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2C218F-EC09-4E63-8518-5903438C7951}">
+  <dimension ref="A1:M95"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
@@ -1415,37 +1475,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>1151000</v>
+        <v>20700</v>
       </c>
       <c r="D12" s="3">
-        <v>4.6399999999999997E-2</v>
+        <v>1.9699999999999999E-2</v>
       </c>
       <c r="E12">
-        <v>39.369999999999997</v>
+        <v>6.94</v>
       </c>
       <c r="F12">
-        <v>41.29</v>
+        <v>6.38</v>
       </c>
       <c r="G12">
-        <v>27.7</v>
+        <v>6.21</v>
       </c>
       <c r="H12" s="4">
-        <v>144393.44</v>
+        <v>39784.050000000003</v>
       </c>
       <c r="I12">
-        <v>0.28999999999999998</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="J12">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="K12">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="L12">
-        <v>102.45</v>
+        <v>96.5</v>
       </c>
       <c r="M12">
-        <v>11.75</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1456,37 +1516,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>26350</v>
+        <v>9090</v>
       </c>
       <c r="D13" s="3">
-        <v>7.3300000000000004E-2</v>
+        <v>2.3599999999999999E-2</v>
       </c>
       <c r="E13">
-        <v>7.28</v>
+        <v>2.84</v>
       </c>
       <c r="F13">
-        <v>7.28</v>
+        <v>4.16</v>
       </c>
       <c r="G13">
-        <v>10.64</v>
+        <v>8.36</v>
       </c>
       <c r="H13" s="4">
-        <v>29659.1</v>
+        <v>20859.37</v>
       </c>
       <c r="I13">
-        <v>2.85</v>
+        <v>2.42</v>
       </c>
       <c r="J13">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K13">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L13">
-        <v>104.06</v>
+        <v>94.11</v>
       </c>
       <c r="M13">
-        <v>8.2100000000000009</v>
+        <v>-2.4700000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1497,37 +1557,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>40350</v>
+        <v>1151000</v>
       </c>
       <c r="D14" s="3">
-        <v>1.77E-2</v>
+        <v>4.6399999999999997E-2</v>
       </c>
       <c r="E14">
-        <v>4.57</v>
+        <v>39.369999999999997</v>
       </c>
       <c r="F14">
-        <v>7.42</v>
+        <v>41.29</v>
       </c>
       <c r="G14">
-        <v>4.55</v>
+        <v>27.7</v>
       </c>
       <c r="H14" s="4">
-        <v>42814.52</v>
+        <v>144393.44</v>
       </c>
       <c r="I14">
-        <v>2.97</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J14">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K14">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L14">
-        <v>96.72</v>
+        <v>102.45</v>
       </c>
       <c r="M14">
-        <v>3.59</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1538,37 +1598,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>95500</v>
+        <v>26350</v>
       </c>
       <c r="D15" s="3">
-        <v>5.5199999999999999E-2</v>
+        <v>7.3300000000000004E-2</v>
       </c>
       <c r="E15">
-        <v>2.16</v>
+        <v>7.28</v>
       </c>
       <c r="F15">
-        <v>5.36</v>
+        <v>7.28</v>
       </c>
       <c r="G15">
-        <v>5.18</v>
+        <v>10.64</v>
       </c>
       <c r="H15" s="4">
-        <v>177736.27</v>
+        <v>29659.1</v>
       </c>
       <c r="I15">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="J15">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K15">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="L15">
-        <v>99.9</v>
+        <v>104.06</v>
       </c>
       <c r="M15">
-        <v>1.49</v>
+        <v>8.2100000000000009</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1579,37 +1639,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>13170</v>
+        <v>40350</v>
       </c>
       <c r="D16" s="3">
-        <v>5.3E-3</v>
+        <v>1.77E-2</v>
       </c>
       <c r="E16">
-        <v>9.44</v>
+        <v>4.57</v>
       </c>
       <c r="F16">
-        <v>10.67</v>
+        <v>7.42</v>
       </c>
       <c r="G16">
-        <v>9.86</v>
+        <v>4.55</v>
       </c>
       <c r="H16" s="4">
-        <v>19219.419999999998</v>
+        <v>42814.52</v>
       </c>
       <c r="I16">
-        <v>3.91</v>
+        <v>2.97</v>
       </c>
       <c r="J16">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K16">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L16">
-        <v>98.16</v>
+        <v>96.72</v>
       </c>
       <c r="M16">
-        <v>2.57</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1620,37 +1680,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>517000</v>
+        <v>95500</v>
       </c>
       <c r="D17" s="3">
-        <v>-9.5999999999999992E-3</v>
+        <v>5.5199999999999999E-2</v>
       </c>
       <c r="E17">
-        <v>8.41</v>
+        <v>2.16</v>
       </c>
       <c r="F17">
-        <v>8.41</v>
+        <v>5.36</v>
       </c>
       <c r="G17">
-        <v>11.51</v>
+        <v>5.18</v>
       </c>
       <c r="H17" s="4">
-        <v>436418.31</v>
+        <v>177736.27</v>
       </c>
       <c r="I17">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="J17">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="K17">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="L17">
-        <v>95.56</v>
+        <v>99.9</v>
       </c>
       <c r="M17">
-        <v>-1.52</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1661,37 +1721,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>343500</v>
+        <v>13170</v>
       </c>
       <c r="D18" s="3">
-        <v>1.6299999999999999E-2</v>
+        <v>5.3E-3</v>
       </c>
       <c r="E18">
-        <v>1.18</v>
+        <v>9.44</v>
       </c>
       <c r="F18">
-        <v>1.18</v>
+        <v>10.67</v>
       </c>
       <c r="G18">
-        <v>2.12</v>
+        <v>9.86</v>
       </c>
       <c r="H18" s="4">
-        <v>703131.42</v>
+        <v>19219.419999999998</v>
       </c>
       <c r="I18">
-        <v>2.91</v>
+        <v>3.91</v>
       </c>
       <c r="J18">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="K18">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L18">
-        <v>95.15</v>
+        <v>98.16</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1702,37 +1762,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>186700</v>
+        <v>380500</v>
       </c>
       <c r="D19" s="3">
-        <v>1.1900000000000001E-2</v>
+        <v>2.5600000000000001E-2</v>
       </c>
       <c r="E19">
-        <v>18.96</v>
+        <v>6.18</v>
       </c>
       <c r="F19">
-        <v>19.43</v>
+        <v>6.18</v>
       </c>
       <c r="G19">
-        <v>18.8</v>
+        <v>6.54</v>
       </c>
       <c r="H19" s="4">
-        <v>144109.65</v>
+        <v>476371.16</v>
       </c>
       <c r="I19">
-        <v>3.64</v>
+        <v>1.58</v>
       </c>
       <c r="J19">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="K19">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>94.68</v>
       </c>
       <c r="M19">
-        <v>1.74</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1743,37 +1803,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>199400</v>
+        <v>10090</v>
       </c>
       <c r="D20" s="3">
-        <v>-5.4999999999999997E-3</v>
+        <v>8.3799999999999999E-2</v>
       </c>
       <c r="E20">
-        <v>10.85</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="F20">
-        <v>10.85</v>
+        <v>3.26</v>
       </c>
       <c r="G20">
-        <v>8.01</v>
+        <v>5.34</v>
       </c>
       <c r="H20" s="4">
-        <v>63976.31</v>
+        <v>22736.17</v>
       </c>
       <c r="I20">
-        <v>0.84</v>
+        <v>3.47</v>
       </c>
       <c r="J20">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="K20">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="L20">
-        <v>102.73</v>
+        <v>104.46</v>
       </c>
       <c r="M20">
-        <v>6.12</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1784,37 +1844,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>35600</v>
+        <v>75600</v>
       </c>
       <c r="D21" s="3">
-        <v>6.59E-2</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="E21">
-        <v>8.73</v>
+        <v>7.58</v>
       </c>
       <c r="F21">
-        <v>11.57</v>
+        <v>7.58</v>
       </c>
       <c r="G21">
-        <v>6.85</v>
+        <v>12.29</v>
       </c>
       <c r="H21" s="4">
-        <v>24348.21</v>
+        <v>79498.27</v>
       </c>
       <c r="I21">
-        <v>2.67</v>
+        <v>4.37</v>
       </c>
       <c r="J21">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="K21">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="L21">
-        <v>105.4</v>
+        <v>95.94</v>
       </c>
       <c r="M21">
-        <v>13.38</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1825,37 +1885,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>303500</v>
+        <v>517000</v>
       </c>
       <c r="D22" s="3">
-        <v>4.48E-2</v>
+        <v>-9.5999999999999992E-3</v>
       </c>
       <c r="E22">
-        <v>5.09</v>
+        <v>8.41</v>
       </c>
       <c r="F22">
-        <v>7.08</v>
+        <v>8.41</v>
       </c>
       <c r="G22">
-        <v>11.63</v>
+        <v>11.51</v>
       </c>
       <c r="H22" s="4">
-        <v>158418.68</v>
+        <v>436418.31</v>
       </c>
       <c r="I22">
-        <v>0.54</v>
+        <v>1.93</v>
       </c>
       <c r="J22">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="K22">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="L22">
-        <v>114.4</v>
+        <v>95.56</v>
       </c>
       <c r="M22">
-        <v>24.9</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1866,37 +1926,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>67700</v>
+        <v>343500</v>
       </c>
       <c r="D23" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="E23">
-        <v>7.94</v>
+        <v>1.18</v>
       </c>
       <c r="F23">
-        <v>10.76</v>
+        <v>1.18</v>
       </c>
       <c r="G23">
-        <v>5.75</v>
+        <v>2.12</v>
       </c>
       <c r="H23" s="4">
-        <v>18036.09</v>
+        <v>703131.42</v>
       </c>
       <c r="I23">
-        <v>0.37</v>
+        <v>2.91</v>
       </c>
       <c r="J23">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="K23">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="L23">
-        <v>99.54</v>
+        <v>95.15</v>
       </c>
       <c r="M23">
-        <v>5.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1907,37 +1967,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>39750</v>
+        <v>186700</v>
       </c>
       <c r="D24" s="3">
-        <v>3.8E-3</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="E24">
-        <v>15.02</v>
+        <v>18.96</v>
       </c>
       <c r="F24">
-        <v>15.02</v>
+        <v>19.43</v>
       </c>
       <c r="G24">
-        <v>20.7</v>
+        <v>18.8</v>
       </c>
       <c r="H24" s="4">
-        <v>34750.239999999998</v>
+        <v>144109.65</v>
       </c>
       <c r="I24">
-        <v>2.52</v>
+        <v>3.64</v>
       </c>
       <c r="J24">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K24">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="L24">
-        <v>131.59</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>43.24</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1948,37 +2008,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>126800</v>
+        <v>199400</v>
       </c>
       <c r="D25" s="3">
-        <v>-2.0799999999999999E-2</v>
+        <v>-5.4999999999999997E-3</v>
       </c>
       <c r="E25">
-        <v>24.91</v>
+        <v>10.85</v>
       </c>
       <c r="F25">
-        <v>29.9</v>
+        <v>10.85</v>
       </c>
       <c r="G25">
-        <v>34.450000000000003</v>
+        <v>8.01</v>
       </c>
       <c r="H25" s="4">
-        <v>9737.2999999999993</v>
+        <v>63976.31</v>
       </c>
       <c r="I25">
-        <v>0.12</v>
+        <v>0.84</v>
       </c>
       <c r="J25">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K25">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="L25">
-        <v>111.69</v>
+        <v>102.73</v>
       </c>
       <c r="M25">
-        <v>11.52</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1989,37 +2049,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>464500</v>
+        <v>35600</v>
       </c>
       <c r="D26" s="3">
-        <v>-3.1300000000000001E-2</v>
+        <v>6.59E-2</v>
       </c>
       <c r="E26">
-        <v>7.7</v>
+        <v>8.73</v>
       </c>
       <c r="F26">
-        <v>7.7</v>
+        <v>11.57</v>
       </c>
       <c r="G26">
-        <v>7.12</v>
+        <v>6.85</v>
       </c>
       <c r="H26" s="4">
-        <v>124850.23</v>
+        <v>24348.21</v>
       </c>
       <c r="I26">
-        <v>0.51</v>
+        <v>2.67</v>
       </c>
       <c r="J26">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K26">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L26">
-        <v>109.75</v>
+        <v>105.4</v>
       </c>
       <c r="M26">
-        <v>15.55</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -2030,37 +2090,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>404500</v>
+        <v>303500</v>
       </c>
       <c r="D27" s="3">
-        <v>-2.18E-2</v>
+        <v>4.48E-2</v>
       </c>
       <c r="E27">
-        <v>11.16</v>
+        <v>5.09</v>
       </c>
       <c r="F27">
-        <v>16.829999999999998</v>
+        <v>7.08</v>
       </c>
       <c r="G27">
-        <v>3.73</v>
+        <v>11.63</v>
       </c>
       <c r="H27" s="4">
-        <v>175890.96</v>
+        <v>158418.68</v>
       </c>
       <c r="I27">
-        <v>1.26</v>
+        <v>0.54</v>
       </c>
       <c r="J27">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="K27">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="L27">
-        <v>94.98</v>
+        <v>114.4</v>
       </c>
       <c r="M27">
-        <v>0.12</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -2071,37 +2131,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>227000</v>
+        <v>67700</v>
       </c>
       <c r="D28" s="3">
-        <v>2.4799999999999999E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E28">
-        <v>13.17</v>
+        <v>7.94</v>
       </c>
       <c r="F28">
-        <v>11.69</v>
+        <v>10.76</v>
       </c>
       <c r="G28">
-        <v>18.010000000000002</v>
+        <v>5.75</v>
       </c>
       <c r="H28" s="4">
-        <v>207156.6</v>
+        <v>18036.09</v>
       </c>
       <c r="I28">
-        <v>2.36</v>
+        <v>0.37</v>
       </c>
       <c r="J28">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K28">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L28">
-        <v>98.43</v>
+        <v>99.54</v>
       </c>
       <c r="M28">
-        <v>2.02</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -2112,37 +2172,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>886000</v>
+        <v>368000</v>
       </c>
       <c r="D29" s="3">
-        <v>1.49E-2</v>
+        <v>-1.4E-3</v>
       </c>
       <c r="E29">
-        <v>13.44</v>
+        <v>6.85</v>
       </c>
       <c r="F29">
-        <v>14.22</v>
+        <v>6.19</v>
       </c>
       <c r="G29">
-        <v>10.67</v>
+        <v>10.64</v>
       </c>
       <c r="H29" s="4">
-        <v>66213.7</v>
+        <v>605494.72</v>
       </c>
       <c r="I29">
-        <v>0.33</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="J29">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="K29">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="L29">
-        <v>118.54</v>
+        <v>96.91</v>
       </c>
       <c r="M29">
-        <v>22.38</v>
+        <v>2.2200000000000002</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -2153,37 +2213,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>1587000</v>
+        <v>39750</v>
       </c>
       <c r="D30" s="3">
-        <v>-1.55E-2</v>
+        <v>3.8E-3</v>
       </c>
       <c r="E30">
-        <v>8.48</v>
+        <v>15.02</v>
       </c>
       <c r="F30">
-        <v>8.48</v>
+        <v>15.02</v>
       </c>
       <c r="G30">
-        <v>5.49</v>
+        <v>20.7</v>
       </c>
       <c r="H30" s="4">
-        <v>542817.23</v>
+        <v>34750.239999999998</v>
       </c>
       <c r="I30">
-        <v>1.26</v>
+        <v>2.52</v>
       </c>
       <c r="J30">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="K30">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="L30">
-        <v>91</v>
+        <v>131.59</v>
       </c>
       <c r="M30">
-        <v>-2.34</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -2194,37 +2254,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>296000</v>
+        <v>126800</v>
       </c>
       <c r="D31" s="3">
-        <v>3.5000000000000003E-2</v>
+        <v>-2.0799999999999999E-2</v>
       </c>
       <c r="E31">
-        <v>6.14</v>
+        <v>24.91</v>
       </c>
       <c r="F31">
-        <v>6.14</v>
+        <v>29.9</v>
       </c>
       <c r="G31">
-        <v>9.2200000000000006</v>
+        <v>34.450000000000003</v>
       </c>
       <c r="H31" s="4">
-        <v>243518.36</v>
+        <v>9737.2999999999993</v>
       </c>
       <c r="I31">
-        <v>0.64</v>
+        <v>0.12</v>
       </c>
       <c r="J31">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="K31">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="L31">
-        <v>108.56</v>
+        <v>111.69</v>
       </c>
       <c r="M31">
-        <v>14.73</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -2235,37 +2295,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>21250</v>
+        <v>464500</v>
       </c>
       <c r="D32" s="3">
-        <v>1.9199999999999998E-2</v>
+        <v>-3.1300000000000001E-2</v>
       </c>
       <c r="E32">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="F32">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="G32">
-        <v>8.9499999999999993</v>
+        <v>7.12</v>
       </c>
       <c r="H32" s="4">
-        <v>28168.11</v>
+        <v>124850.23</v>
       </c>
       <c r="I32">
-        <v>3.29</v>
+        <v>0.51</v>
       </c>
       <c r="J32">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K32">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="L32">
-        <v>97.97</v>
+        <v>109.75</v>
       </c>
       <c r="M32">
-        <v>1.67</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2276,37 +2336,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>400500</v>
+        <v>404500</v>
       </c>
       <c r="D33" s="3">
-        <v>-3.0300000000000001E-2</v>
+        <v>-2.18E-2</v>
       </c>
       <c r="E33">
-        <v>7.68</v>
+        <v>11.16</v>
       </c>
       <c r="F33">
-        <v>7.68</v>
+        <v>16.829999999999998</v>
       </c>
       <c r="G33">
-        <v>8.59</v>
+        <v>3.73</v>
       </c>
       <c r="H33" s="4">
-        <v>545786.89</v>
+        <v>175890.96</v>
       </c>
       <c r="I33">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="J33">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="K33">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="L33">
-        <v>91.74</v>
+        <v>94.98</v>
       </c>
       <c r="M33">
-        <v>-5.32</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2317,37 +2377,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>1320000</v>
+        <v>227000</v>
       </c>
       <c r="D34" s="3">
-        <v>-0.04</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="E34">
-        <v>53.94</v>
+        <v>13.17</v>
       </c>
       <c r="F34">
-        <v>14.72</v>
+        <v>11.69</v>
       </c>
       <c r="G34">
-        <v>28.78</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H34" s="4">
-        <v>174991.05</v>
+        <v>207156.6</v>
       </c>
       <c r="I34">
-        <v>0.27</v>
+        <v>2.36</v>
       </c>
       <c r="J34">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K34">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L34">
-        <v>97.25</v>
+        <v>98.43</v>
       </c>
       <c r="M34">
-        <v>-9.2799999999999994</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2358,37 +2418,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>49150</v>
+        <v>886000</v>
       </c>
       <c r="D35" s="3">
-        <v>1.7600000000000001E-2</v>
+        <v>1.49E-2</v>
       </c>
       <c r="E35">
-        <v>19.399999999999999</v>
+        <v>13.44</v>
       </c>
       <c r="F35">
-        <v>19.399999999999999</v>
+        <v>14.22</v>
       </c>
       <c r="G35">
-        <v>5.33</v>
+        <v>10.67</v>
       </c>
       <c r="H35" s="4">
-        <v>75035.259999999995</v>
+        <v>66213.7</v>
       </c>
       <c r="I35">
-        <v>3.14</v>
+        <v>0.33</v>
       </c>
       <c r="J35">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="K35">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="L35">
-        <v>93.91</v>
+        <v>118.54</v>
       </c>
       <c r="M35">
-        <v>3.26</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2399,37 +2459,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>102300</v>
+        <v>1587000</v>
       </c>
       <c r="D36" s="3">
-        <v>3.7499999999999999E-2</v>
+        <v>-1.55E-2</v>
       </c>
       <c r="E36">
-        <v>12.89</v>
+        <v>8.48</v>
       </c>
       <c r="F36">
-        <v>13.94</v>
+        <v>8.48</v>
       </c>
       <c r="G36">
-        <v>9.44</v>
+        <v>5.49</v>
       </c>
       <c r="H36" s="4">
-        <v>87743.72</v>
+        <v>542817.23</v>
       </c>
       <c r="I36">
-        <v>3.42</v>
+        <v>1.26</v>
       </c>
       <c r="J36">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="K36">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="L36">
-        <v>101.8</v>
+        <v>91</v>
       </c>
       <c r="M36">
-        <v>9.5299999999999994</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2440,37 +2500,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>78800</v>
+        <v>296000</v>
       </c>
       <c r="D37" s="3">
-        <v>7.7000000000000002E-3</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="E37">
-        <v>3.33</v>
+        <v>6.14</v>
       </c>
       <c r="F37">
-        <v>3.33</v>
+        <v>6.14</v>
       </c>
       <c r="G37">
-        <v>7.93</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="H37" s="4">
-        <v>60299.05</v>
+        <v>243518.36</v>
       </c>
       <c r="I37">
-        <v>2.11</v>
+        <v>0.64</v>
       </c>
       <c r="J37">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="K37">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L37">
-        <v>100.76</v>
+        <v>108.56</v>
       </c>
       <c r="M37">
-        <v>2.0699999999999998</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2481,37 +2541,37 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>88800</v>
+        <v>21250</v>
       </c>
       <c r="D38" s="3">
-        <v>1.6E-2</v>
+        <v>1.9199999999999998E-2</v>
       </c>
       <c r="E38">
-        <v>14.42</v>
+        <v>6.9</v>
       </c>
       <c r="F38">
-        <v>24.2</v>
+        <v>6.9</v>
       </c>
       <c r="G38">
-        <v>15.82</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="H38" s="4">
-        <v>36460.550000000003</v>
+        <v>28168.11</v>
       </c>
       <c r="I38">
-        <v>6.19</v>
+        <v>3.29</v>
       </c>
       <c r="J38">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="K38">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="L38">
-        <v>95.04</v>
+        <v>97.97</v>
       </c>
       <c r="M38">
-        <v>-0.11</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2522,37 +2582,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>162600</v>
+        <v>131900</v>
       </c>
       <c r="D39" s="3">
-        <v>6.7999999999999996E-3</v>
+        <v>-1.7100000000000001E-2</v>
       </c>
       <c r="E39">
-        <v>7.89</v>
+        <v>4.74</v>
       </c>
       <c r="F39">
-        <v>7.89</v>
+        <v>4.74</v>
       </c>
       <c r="G39">
-        <v>8.18</v>
+        <v>6.13</v>
       </c>
       <c r="H39" s="4">
-        <v>128172.41</v>
+        <v>215808.28</v>
       </c>
       <c r="I39">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="J39">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="K39">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="L39">
-        <v>96.42</v>
+        <v>99.74</v>
       </c>
       <c r="M39">
-        <v>0.06</v>
+        <v>8.2899999999999991</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2563,37 +2623,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>74400</v>
+        <v>400500</v>
       </c>
       <c r="D40" s="3">
-        <v>1.9199999999999998E-2</v>
+        <v>-3.0300000000000001E-2</v>
       </c>
       <c r="E40">
-        <v>18.14</v>
+        <v>7.68</v>
       </c>
       <c r="F40">
-        <v>18.14</v>
+        <v>7.68</v>
       </c>
       <c r="G40">
-        <v>18.850000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="H40" s="4">
-        <v>51783.79</v>
+        <v>545786.89</v>
       </c>
       <c r="I40">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="J40">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="K40">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="L40">
-        <v>95.93</v>
+        <v>91.74</v>
       </c>
       <c r="M40">
-        <v>2.9</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2604,37 +2664,37 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>32400</v>
+        <v>1320000</v>
       </c>
       <c r="D41" s="3">
-        <v>2.0500000000000001E-2</v>
+        <v>-0.04</v>
       </c>
       <c r="E41">
-        <v>9.5299999999999994</v>
+        <v>53.94</v>
       </c>
       <c r="F41">
-        <v>9.5299999999999994</v>
+        <v>14.72</v>
       </c>
       <c r="G41">
-        <v>16.18</v>
+        <v>28.78</v>
       </c>
       <c r="H41" s="4">
-        <v>3753.16</v>
+        <v>174991.05</v>
       </c>
       <c r="I41">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="J41">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="K41">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="L41">
-        <v>95.32</v>
+        <v>97.25</v>
       </c>
       <c r="M41">
-        <v>-1.52</v>
+        <v>-9.2799999999999994</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2645,37 +2705,37 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>24100</v>
+        <v>49150</v>
       </c>
       <c r="D42" s="3">
-        <v>1.6899999999999998E-2</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="E42">
-        <v>8.06</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="F42">
-        <v>8.64</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="G42">
-        <v>8.77</v>
+        <v>5.33</v>
       </c>
       <c r="H42" s="4">
-        <v>44443.18</v>
+        <v>75035.259999999995</v>
       </c>
       <c r="I42">
-        <v>4.42</v>
+        <v>3.14</v>
       </c>
       <c r="J42">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="K42">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="L42">
-        <v>98.45</v>
+        <v>93.91</v>
       </c>
       <c r="M42">
-        <v>4.33</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2686,37 +2746,37 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>35300</v>
+        <v>102300</v>
       </c>
       <c r="D43" s="3">
-        <v>8.2799999999999999E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="E43">
-        <v>13.76</v>
+        <v>12.89</v>
       </c>
       <c r="F43">
-        <v>13.76</v>
+        <v>13.94</v>
       </c>
       <c r="G43">
-        <v>19.29</v>
+        <v>9.44</v>
       </c>
       <c r="H43" s="4">
-        <v>24187.31</v>
+        <v>87743.72</v>
       </c>
       <c r="I43">
-        <v>2.2400000000000002</v>
+        <v>3.42</v>
       </c>
       <c r="J43">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K43">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L43">
-        <v>104.09</v>
+        <v>101.8</v>
       </c>
       <c r="M43">
-        <v>12.96</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
@@ -2727,37 +2787,37 @@
         <v>96</v>
       </c>
       <c r="C44" s="2">
-        <v>297500</v>
+        <v>78800</v>
       </c>
       <c r="D44" s="3">
-        <v>2.23E-2</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="E44">
-        <v>6.02</v>
+        <v>3.33</v>
       </c>
       <c r="F44">
-        <v>6.02</v>
+        <v>3.33</v>
       </c>
       <c r="G44">
-        <v>6.71</v>
+        <v>7.93</v>
       </c>
       <c r="H44" s="4">
-        <v>294896.78000000003</v>
+        <v>60299.05</v>
       </c>
       <c r="I44">
-        <v>0.94</v>
+        <v>2.11</v>
       </c>
       <c r="J44">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K44">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L44">
-        <v>98.23</v>
+        <v>100.76</v>
       </c>
       <c r="M44">
-        <v>8.9700000000000006</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
@@ -2768,37 +2828,37 @@
         <v>98</v>
       </c>
       <c r="C45" s="2">
-        <v>59700</v>
+        <v>88800</v>
       </c>
       <c r="D45" s="3">
-        <v>-1.6999999999999999E-3</v>
+        <v>1.6E-2</v>
       </c>
       <c r="E45">
-        <v>7.45</v>
+        <v>14.42</v>
       </c>
       <c r="F45">
-        <v>7.45</v>
+        <v>24.2</v>
       </c>
       <c r="G45">
-        <v>7.69</v>
+        <v>15.82</v>
       </c>
       <c r="H45" s="4">
-        <v>79986.48</v>
+        <v>36460.550000000003</v>
       </c>
       <c r="I45">
-        <v>4.6900000000000004</v>
+        <v>6.19</v>
       </c>
       <c r="J45">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K45">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L45">
-        <v>98.04</v>
+        <v>95.04</v>
       </c>
       <c r="M45">
-        <v>1.53</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
@@ -2809,37 +2869,37 @@
         <v>100</v>
       </c>
       <c r="C46" s="2">
-        <v>21300</v>
+        <v>162600</v>
       </c>
       <c r="D46" s="3">
-        <v>1.67E-2</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="E46">
-        <v>13.7</v>
+        <v>7.89</v>
       </c>
       <c r="F46">
-        <v>13.7</v>
+        <v>7.89</v>
       </c>
       <c r="G46">
-        <v>14.6</v>
+        <v>8.18</v>
       </c>
       <c r="H46" s="4">
-        <v>16125.49</v>
+        <v>128172.41</v>
       </c>
       <c r="I46">
-        <v>5.77</v>
+        <v>1.96</v>
       </c>
       <c r="J46">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K46">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="L46">
-        <v>100.84</v>
+        <v>96.42</v>
       </c>
       <c r="M46">
-        <v>3.4</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
@@ -2850,37 +2910,37 @@
         <v>102</v>
       </c>
       <c r="C47" s="2">
-        <v>60700</v>
+        <v>74400</v>
       </c>
       <c r="D47" s="3">
-        <v>2.3599999999999999E-2</v>
+        <v>1.9199999999999998E-2</v>
       </c>
       <c r="E47">
-        <v>10.220000000000001</v>
+        <v>18.14</v>
       </c>
       <c r="F47">
-        <v>10.220000000000001</v>
+        <v>18.14</v>
       </c>
       <c r="G47">
-        <v>6.37</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="H47" s="4">
-        <v>71885.83</v>
+        <v>51783.79</v>
       </c>
       <c r="I47">
-        <v>3.95</v>
+        <v>2.61</v>
       </c>
       <c r="J47">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="K47">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="L47">
-        <v>98.58</v>
+        <v>95.93</v>
       </c>
       <c r="M47">
-        <v>-0.16</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
@@ -2891,37 +2951,37 @@
         <v>104</v>
       </c>
       <c r="C48" s="2">
-        <v>15820</v>
+        <v>32400</v>
       </c>
       <c r="D48" s="3">
-        <v>1.2800000000000001E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="E48">
-        <v>6.01</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="F48">
-        <v>6.01</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="G48">
-        <v>5.97</v>
+        <v>16.18</v>
       </c>
       <c r="H48" s="4">
-        <v>20769.650000000001</v>
+        <v>3753.16</v>
       </c>
       <c r="I48">
-        <v>4.17</v>
+        <v>0.39</v>
       </c>
       <c r="J48">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="K48">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="L48">
-        <v>99.7</v>
+        <v>95.32</v>
       </c>
       <c r="M48">
-        <v>7.18</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.4">
@@ -2932,37 +2992,37 @@
         <v>106</v>
       </c>
       <c r="C49" s="2">
-        <v>231500</v>
+        <v>24100</v>
       </c>
       <c r="D49" s="3">
-        <v>4.3E-3</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="E49">
-        <v>4.66</v>
+        <v>8.06</v>
       </c>
       <c r="F49">
-        <v>4.66</v>
+        <v>8.64</v>
       </c>
       <c r="G49">
-        <v>4.88</v>
+        <v>8.77</v>
       </c>
       <c r="H49" s="4">
-        <v>324173.33</v>
+        <v>44443.18</v>
       </c>
       <c r="I49">
-        <v>2.29</v>
+        <v>4.42</v>
       </c>
       <c r="J49">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="K49">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="L49">
-        <v>104.47</v>
+        <v>98.45</v>
       </c>
       <c r="M49">
-        <v>9.4600000000000009</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.4">
@@ -2973,37 +3033,37 @@
         <v>108</v>
       </c>
       <c r="C50" s="2">
-        <v>157500</v>
+        <v>35300</v>
       </c>
       <c r="D50" s="3">
-        <v>3.2000000000000002E-3</v>
+        <v>8.2799999999999999E-2</v>
       </c>
       <c r="E50">
-        <v>11.77</v>
+        <v>13.76</v>
       </c>
       <c r="F50">
-        <v>11.77</v>
+        <v>13.76</v>
       </c>
       <c r="G50">
-        <v>11.4</v>
+        <v>19.29</v>
       </c>
       <c r="H50" s="4">
-        <v>85735.74</v>
+        <v>24187.31</v>
       </c>
       <c r="I50">
-        <v>3.81</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="J50">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K50">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L50">
-        <v>97.91</v>
+        <v>104.09</v>
       </c>
       <c r="M50">
-        <v>1.88</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.4">
@@ -3014,37 +3074,37 @@
         <v>110</v>
       </c>
       <c r="C51" s="2">
-        <v>18190</v>
+        <v>297500</v>
       </c>
       <c r="D51" s="3">
-        <v>1.9E-2</v>
+        <v>2.23E-2</v>
       </c>
       <c r="E51">
-        <v>8.11</v>
+        <v>6.02</v>
       </c>
       <c r="F51">
-        <v>8.11</v>
+        <v>6.02</v>
       </c>
       <c r="G51">
-        <v>9.93</v>
+        <v>6.71</v>
       </c>
       <c r="H51" s="4">
-        <v>19583.27</v>
+        <v>294896.78000000003</v>
       </c>
       <c r="I51">
-        <v>5.22</v>
+        <v>0.94</v>
       </c>
       <c r="J51">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="K51">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="L51">
-        <v>98.7</v>
+        <v>98.23</v>
       </c>
       <c r="M51">
-        <v>1.9</v>
+        <v>8.9700000000000006</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.4">
@@ -3055,37 +3115,37 @@
         <v>112</v>
       </c>
       <c r="C52" s="2">
-        <v>221500</v>
+        <v>59700</v>
       </c>
       <c r="D52" s="3">
-        <v>4.4999999999999997E-3</v>
+        <v>-1.6999999999999999E-3</v>
       </c>
       <c r="E52">
-        <v>7.36</v>
+        <v>7.45</v>
       </c>
       <c r="F52">
-        <v>7.36</v>
+        <v>7.45</v>
       </c>
       <c r="G52">
-        <v>6.56</v>
+        <v>7.69</v>
       </c>
       <c r="H52" s="4">
-        <v>180116.6</v>
+        <v>79986.48</v>
       </c>
       <c r="I52">
-        <v>1.19</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="J52">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="K52">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="L52">
-        <v>95.56</v>
+        <v>98.04</v>
       </c>
       <c r="M52">
-        <v>0.45</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.4">
@@ -3096,37 +3156,37 @@
         <v>114</v>
       </c>
       <c r="C53" s="2">
-        <v>50000</v>
-      </c>
-      <c r="D53" s="5">
-        <v>0</v>
+        <v>21300</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1.67E-2</v>
       </c>
       <c r="E53">
-        <v>0.56000000000000005</v>
+        <v>13.7</v>
       </c>
       <c r="F53">
-        <v>5.88</v>
+        <v>13.7</v>
       </c>
       <c r="G53">
-        <v>1.31</v>
+        <v>14.6</v>
       </c>
       <c r="H53" s="4">
-        <v>24000.959999999999</v>
+        <v>16125.49</v>
       </c>
       <c r="I53">
-        <v>0.14000000000000001</v>
+        <v>5.77</v>
       </c>
       <c r="J53">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="K53">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L53">
-        <v>93.44</v>
+        <v>100.84</v>
       </c>
       <c r="M53">
-        <v>-3.47</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.4">
@@ -3137,37 +3197,37 @@
         <v>116</v>
       </c>
       <c r="C54" s="2">
-        <v>37700</v>
+        <v>60700</v>
       </c>
       <c r="D54" s="3">
-        <v>0.04</v>
+        <v>2.3599999999999999E-2</v>
       </c>
       <c r="E54">
-        <v>1.23</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="F54">
-        <v>1.23</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="G54">
-        <v>1.59</v>
+        <v>6.37</v>
       </c>
       <c r="H54" s="4">
-        <v>118301.94</v>
+        <v>71885.83</v>
       </c>
       <c r="I54">
-        <v>3.06</v>
+        <v>3.95</v>
       </c>
       <c r="J54">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="K54">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="L54">
-        <v>97.4</v>
+        <v>98.58</v>
       </c>
       <c r="M54">
-        <v>4.43</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.4">
@@ -3178,37 +3238,37 @@
         <v>118</v>
       </c>
       <c r="C55" s="2">
-        <v>460500</v>
+        <v>15820</v>
       </c>
       <c r="D55" s="3">
-        <v>2.5600000000000001E-2</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="E55">
-        <v>15.98</v>
+        <v>6.01</v>
       </c>
       <c r="F55">
-        <v>19.260000000000002</v>
+        <v>6.01</v>
       </c>
       <c r="G55">
-        <v>12.25</v>
+        <v>5.97</v>
       </c>
       <c r="H55" s="4">
-        <v>238844.91</v>
+        <v>20769.650000000001</v>
       </c>
       <c r="I55">
-        <v>1.63</v>
+        <v>4.17</v>
       </c>
       <c r="J55">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="K55">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="L55">
-        <v>103.17</v>
+        <v>99.7</v>
       </c>
       <c r="M55">
-        <v>7.97</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.4">
@@ -3219,37 +3279,37 @@
         <v>120</v>
       </c>
       <c r="C56" s="2">
-        <v>309500</v>
+        <v>231500</v>
       </c>
       <c r="D56" s="3">
-        <v>8.0999999999999996E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="E56">
-        <v>34.76</v>
+        <v>4.66</v>
       </c>
       <c r="F56">
-        <v>34.76</v>
+        <v>4.66</v>
       </c>
       <c r="G56">
-        <v>39.24</v>
+        <v>4.88</v>
       </c>
       <c r="H56" s="4">
-        <v>7523.78</v>
+        <v>324173.33</v>
       </c>
       <c r="I56">
-        <v>0.26</v>
+        <v>2.29</v>
       </c>
       <c r="J56">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="K56">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="L56">
-        <v>108.41</v>
+        <v>104.47</v>
       </c>
       <c r="M56">
-        <v>-4.4800000000000004</v>
+        <v>9.4600000000000009</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.4">
@@ -3260,37 +3320,37 @@
         <v>122</v>
       </c>
       <c r="C57" s="2">
-        <v>77000</v>
+        <v>157500</v>
       </c>
       <c r="D57" s="3">
-        <v>7.2400000000000006E-2</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="E57">
-        <v>9.27</v>
+        <v>11.77</v>
       </c>
       <c r="F57">
-        <v>9.27</v>
+        <v>11.77</v>
       </c>
       <c r="G57">
-        <v>10.26</v>
+        <v>11.4</v>
       </c>
       <c r="H57" s="4">
-        <v>38290.26</v>
+        <v>85735.74</v>
       </c>
       <c r="I57">
-        <v>2.4</v>
+        <v>3.81</v>
       </c>
       <c r="J57">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K57">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L57">
-        <v>105.33</v>
+        <v>97.91</v>
       </c>
       <c r="M57">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.4">
@@ -3301,37 +3361,37 @@
         <v>124</v>
       </c>
       <c r="C58" s="2">
-        <v>185700</v>
+        <v>18190</v>
       </c>
       <c r="D58" s="3">
-        <v>-2.47E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="E58">
-        <v>10.42</v>
+        <v>8.11</v>
       </c>
       <c r="F58">
-        <v>9.58</v>
+        <v>8.11</v>
       </c>
       <c r="G58">
-        <v>11.34</v>
+        <v>9.93</v>
       </c>
       <c r="H58" s="4">
-        <v>18284.689999999999</v>
+        <v>19583.27</v>
       </c>
       <c r="I58">
-        <v>0.27</v>
+        <v>5.22</v>
       </c>
       <c r="J58">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="K58">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="L58">
-        <v>101.39</v>
+        <v>98.7</v>
       </c>
       <c r="M58">
-        <v>6.66</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.4">
@@ -3342,37 +3402,37 @@
         <v>126</v>
       </c>
       <c r="C59" s="2">
-        <v>97900</v>
+        <v>221500</v>
       </c>
       <c r="D59" s="3">
-        <v>1.4500000000000001E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="E59">
-        <v>8.11</v>
+        <v>7.36</v>
       </c>
       <c r="F59">
-        <v>10.44</v>
+        <v>7.36</v>
       </c>
       <c r="G59">
-        <v>8.66</v>
+        <v>6.56</v>
       </c>
       <c r="H59" s="4">
-        <v>119742.76</v>
+        <v>180116.6</v>
       </c>
       <c r="I59">
-        <v>2.21</v>
+        <v>1.19</v>
       </c>
       <c r="J59">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="K59">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="L59">
-        <v>103.42</v>
+        <v>95.56</v>
       </c>
       <c r="M59">
-        <v>9.75</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.4">
@@ -3383,37 +3443,37 @@
         <v>128</v>
       </c>
       <c r="C60" s="2">
-        <v>180100</v>
-      </c>
-      <c r="D60" s="3">
-        <v>-3.3300000000000003E-2</v>
+        <v>50000</v>
+      </c>
+      <c r="D60" s="5">
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>30.05</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F60">
-        <v>30.05</v>
+        <v>5.88</v>
       </c>
       <c r="G60">
-        <v>20.65</v>
+        <v>1.31</v>
       </c>
       <c r="H60" s="4">
-        <v>28211.09</v>
+        <v>24000.959999999999</v>
       </c>
       <c r="I60">
-        <v>0.33</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J60">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="K60">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="L60">
-        <v>85.34</v>
+        <v>93.44</v>
       </c>
       <c r="M60">
-        <v>-13.2</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.4">
@@ -3424,37 +3484,37 @@
         <v>130</v>
       </c>
       <c r="C61" s="2">
-        <v>117900</v>
+        <v>37700</v>
       </c>
       <c r="D61" s="3">
-        <v>1.46E-2</v>
+        <v>0.04</v>
       </c>
       <c r="E61">
-        <v>4.28</v>
+        <v>1.23</v>
       </c>
       <c r="F61">
-        <v>4.28</v>
+        <v>1.23</v>
       </c>
       <c r="G61">
-        <v>3.26</v>
+        <v>1.59</v>
       </c>
       <c r="H61" s="4">
-        <v>132655.74</v>
+        <v>118301.94</v>
       </c>
       <c r="I61">
-        <v>1.1499999999999999</v>
+        <v>3.06</v>
       </c>
       <c r="J61">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="K61">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="L61">
-        <v>96.5</v>
+        <v>97.4</v>
       </c>
       <c r="M61">
-        <v>1.73</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.4">
@@ -3465,37 +3525,37 @@
         <v>132</v>
       </c>
       <c r="C62" s="2">
-        <v>202000</v>
-      </c>
-      <c r="D62" s="5">
-        <v>0</v>
+        <v>460500</v>
+      </c>
+      <c r="D62" s="3">
+        <v>2.5600000000000001E-2</v>
       </c>
       <c r="E62">
-        <v>2.46</v>
+        <v>15.98</v>
       </c>
       <c r="F62">
-        <v>3.92</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="G62">
-        <v>6.96</v>
+        <v>12.25</v>
       </c>
       <c r="H62" s="4">
-        <v>81630.009999999995</v>
+        <v>238844.91</v>
       </c>
       <c r="I62">
-        <v>0.37</v>
+        <v>1.63</v>
       </c>
       <c r="J62">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="K62">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="L62">
-        <v>92.77</v>
+        <v>103.17</v>
       </c>
       <c r="M62">
-        <v>-1.94</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.4">
@@ -3506,37 +3566,37 @@
         <v>134</v>
       </c>
       <c r="C63" s="2">
-        <v>234500</v>
+        <v>309500</v>
       </c>
       <c r="D63" s="3">
-        <v>2.4E-2</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="E63">
-        <v>11.54</v>
+        <v>34.76</v>
       </c>
       <c r="F63">
-        <v>20.98</v>
+        <v>34.76</v>
       </c>
       <c r="G63">
-        <v>9.6</v>
+        <v>39.24</v>
       </c>
       <c r="H63" s="4">
-        <v>189057.03</v>
+        <v>7523.78</v>
       </c>
       <c r="I63">
-        <v>1.7</v>
+        <v>0.26</v>
       </c>
       <c r="J63">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="K63">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="L63">
-        <v>97.34</v>
+        <v>108.41</v>
       </c>
       <c r="M63">
-        <v>6.59</v>
+        <v>-4.4800000000000004</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.4">
@@ -3547,37 +3607,37 @@
         <v>136</v>
       </c>
       <c r="C64" s="2">
-        <v>69000</v>
+        <v>77000</v>
       </c>
       <c r="D64" s="3">
-        <v>5.5E-2</v>
+        <v>7.2400000000000006E-2</v>
       </c>
       <c r="E64">
-        <v>4.12</v>
+        <v>9.27</v>
       </c>
       <c r="F64">
-        <v>5.22</v>
+        <v>9.27</v>
       </c>
       <c r="G64">
-        <v>11.01</v>
+        <v>10.26</v>
       </c>
       <c r="H64" s="4">
-        <v>151788</v>
+        <v>38290.26</v>
       </c>
       <c r="I64">
-        <v>3.91</v>
+        <v>2.4</v>
       </c>
       <c r="J64">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K64">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L64">
-        <v>102.23</v>
+        <v>105.33</v>
       </c>
       <c r="M64">
-        <v>7.81</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.4">
@@ -3588,37 +3648,37 @@
         <v>138</v>
       </c>
       <c r="C65" s="2">
-        <v>661000</v>
+        <v>185700</v>
       </c>
       <c r="D65" s="3">
-        <v>-5.8400000000000001E-2</v>
+        <v>-2.47E-2</v>
       </c>
       <c r="E65">
-        <v>19.59</v>
+        <v>10.42</v>
       </c>
       <c r="F65">
-        <v>25.3</v>
+        <v>9.58</v>
       </c>
       <c r="G65">
-        <v>17.23</v>
+        <v>11.34</v>
       </c>
       <c r="H65" s="4">
-        <v>64298.52</v>
+        <v>18284.689999999999</v>
       </c>
       <c r="I65">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="J65">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K65">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L65">
-        <v>100.48</v>
+        <v>101.39</v>
       </c>
       <c r="M65">
-        <v>-12.91</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.4">
@@ -3629,37 +3689,37 @@
         <v>140</v>
       </c>
       <c r="C66" s="2">
-        <v>230500</v>
-      </c>
-      <c r="D66" s="5">
-        <v>0</v>
+        <v>97900</v>
+      </c>
+      <c r="D66" s="3">
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="E66">
-        <v>13.24</v>
+        <v>8.11</v>
       </c>
       <c r="F66">
-        <v>18.559999999999999</v>
+        <v>10.44</v>
       </c>
       <c r="G66">
-        <v>15.51</v>
+        <v>8.66</v>
       </c>
       <c r="H66" s="4">
-        <v>130762.28</v>
+        <v>119742.76</v>
       </c>
       <c r="I66">
-        <v>1.61</v>
+        <v>2.21</v>
       </c>
       <c r="J66">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="K66">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="L66">
-        <v>93.21</v>
+        <v>103.42</v>
       </c>
       <c r="M66">
-        <v>-1.71</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.4">
@@ -3670,37 +3730,37 @@
         <v>142</v>
       </c>
       <c r="C67" s="2">
-        <v>113200</v>
-      </c>
-      <c r="D67" s="5">
-        <v>0</v>
+        <v>180100</v>
+      </c>
+      <c r="D67" s="3">
+        <v>-3.3300000000000003E-2</v>
       </c>
       <c r="E67">
-        <v>9.17</v>
+        <v>30.05</v>
       </c>
       <c r="F67">
-        <v>9.17</v>
+        <v>30.05</v>
       </c>
       <c r="G67">
-        <v>9.1</v>
+        <v>20.65</v>
       </c>
       <c r="H67" s="4">
-        <v>162088.94</v>
+        <v>28211.09</v>
       </c>
       <c r="I67">
-        <v>3.63</v>
+        <v>0.33</v>
       </c>
       <c r="J67">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="K67">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="L67">
-        <v>97.67</v>
+        <v>85.34</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.4">
@@ -3711,37 +3771,37 @@
         <v>144</v>
       </c>
       <c r="C68" s="2">
-        <v>140800</v>
+        <v>117900</v>
       </c>
       <c r="D68" s="3">
-        <v>4.53E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="E68">
-        <v>11.69</v>
+        <v>4.28</v>
       </c>
       <c r="F68">
-        <v>5.33</v>
+        <v>4.28</v>
       </c>
       <c r="G68">
-        <v>6.07</v>
+        <v>3.26</v>
       </c>
       <c r="H68" s="4">
-        <v>77979.460000000006</v>
+        <v>132655.74</v>
       </c>
       <c r="I68">
-        <v>0.8</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="J68">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="K68">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L68">
-        <v>101.19</v>
+        <v>96.5</v>
       </c>
       <c r="M68">
-        <v>8.98</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.4">
@@ -3752,37 +3812,37 @@
         <v>146</v>
       </c>
       <c r="C69" s="2">
-        <v>155200</v>
-      </c>
-      <c r="D69" s="3">
-        <v>-3.2000000000000002E-3</v>
+        <v>202000</v>
+      </c>
+      <c r="D69" s="5">
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>8.86</v>
+        <v>2.46</v>
       </c>
       <c r="F69">
-        <v>11.63</v>
+        <v>3.92</v>
       </c>
       <c r="G69">
-        <v>8.51</v>
+        <v>6.96</v>
       </c>
       <c r="H69" s="4">
-        <v>160038.65</v>
+        <v>81630.009999999995</v>
       </c>
       <c r="I69">
-        <v>2.0499999999999998</v>
+        <v>0.37</v>
       </c>
       <c r="J69">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="K69">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="L69">
-        <v>100.49</v>
+        <v>92.77</v>
       </c>
       <c r="M69">
-        <v>5.29</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.4">
@@ -3793,37 +3853,37 @@
         <v>148</v>
       </c>
       <c r="C70" s="2">
-        <v>560000</v>
+        <v>234500</v>
       </c>
       <c r="D70" s="3">
-        <v>7.9000000000000001E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="E70">
-        <v>11.89</v>
+        <v>11.54</v>
       </c>
       <c r="F70">
-        <v>14.27</v>
+        <v>20.98</v>
       </c>
       <c r="G70">
-        <v>12.6</v>
+        <v>9.6</v>
       </c>
       <c r="H70" s="4">
-        <v>95809.42</v>
+        <v>189057.03</v>
       </c>
       <c r="I70">
-        <v>0.22</v>
+        <v>1.7</v>
       </c>
       <c r="J70">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K70">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L70">
-        <v>103.69</v>
+        <v>97.34</v>
       </c>
       <c r="M70">
-        <v>9.59</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.4">
@@ -3834,37 +3894,37 @@
         <v>150</v>
       </c>
       <c r="C71" s="2">
-        <v>110100</v>
+        <v>69000</v>
       </c>
       <c r="D71" s="3">
-        <v>-7.1999999999999998E-3</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E71">
-        <v>23.44</v>
+        <v>4.12</v>
       </c>
       <c r="F71">
-        <v>25.94</v>
+        <v>5.22</v>
       </c>
       <c r="G71">
-        <v>27.89</v>
+        <v>11.01</v>
       </c>
       <c r="H71" s="4">
-        <v>59980.14</v>
+        <v>151788</v>
       </c>
       <c r="I71">
-        <v>1.23</v>
+        <v>3.91</v>
       </c>
       <c r="J71">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K71">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L71">
-        <v>91.91</v>
+        <v>102.23</v>
       </c>
       <c r="M71">
-        <v>-2.57</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.4">
@@ -3875,37 +3935,37 @@
         <v>152</v>
       </c>
       <c r="C72" s="2">
-        <v>18850</v>
+        <v>661000</v>
       </c>
       <c r="D72" s="3">
-        <v>0.02</v>
+        <v>-5.8400000000000001E-2</v>
       </c>
       <c r="E72">
-        <v>6.96</v>
+        <v>19.59</v>
       </c>
       <c r="F72">
-        <v>9.58</v>
+        <v>25.3</v>
       </c>
       <c r="G72">
-        <v>7.18</v>
+        <v>17.23</v>
       </c>
       <c r="H72" s="4">
-        <v>34223.949999999997</v>
+        <v>64298.52</v>
       </c>
       <c r="I72">
-        <v>3.45</v>
+        <v>0.36</v>
       </c>
       <c r="J72">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K72">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L72">
-        <v>97.04</v>
+        <v>100.48</v>
       </c>
       <c r="M72">
-        <v>2.84</v>
+        <v>-12.91</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.4">
@@ -3916,37 +3976,37 @@
         <v>154</v>
       </c>
       <c r="C73" s="2">
-        <v>17240</v>
-      </c>
-      <c r="D73" s="3">
-        <v>2.6200000000000001E-2</v>
+        <v>230500</v>
+      </c>
+      <c r="D73" s="5">
+        <v>0</v>
       </c>
       <c r="E73">
-        <v>3.6</v>
+        <v>13.24</v>
       </c>
       <c r="F73">
-        <v>9.42</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="G73">
-        <v>5.91</v>
+        <v>15.51</v>
       </c>
       <c r="H73" s="4">
-        <v>38541.279999999999</v>
+        <v>130762.28</v>
       </c>
       <c r="I73">
-        <v>2.9</v>
+        <v>1.61</v>
       </c>
       <c r="J73">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K73">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L73">
-        <v>96.19</v>
+        <v>93.21</v>
       </c>
       <c r="M73">
-        <v>0.76</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.4">
@@ -3957,37 +4017,37 @@
         <v>156</v>
       </c>
       <c r="C74" s="2">
-        <v>57400</v>
-      </c>
-      <c r="D74" s="3">
-        <v>7.0000000000000001E-3</v>
+        <v>113200</v>
+      </c>
+      <c r="D74" s="5">
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>10.79</v>
+        <v>9.17</v>
       </c>
       <c r="F74">
-        <v>10.55</v>
+        <v>9.17</v>
       </c>
       <c r="G74">
-        <v>8.93</v>
+        <v>9.1</v>
       </c>
       <c r="H74" s="4">
-        <v>92723.77</v>
+        <v>162088.94</v>
       </c>
       <c r="I74">
-        <v>3.48</v>
+        <v>3.63</v>
       </c>
       <c r="J74">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="K74">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="L74">
-        <v>90.82</v>
+        <v>97.67</v>
       </c>
       <c r="M74">
-        <v>-2.88</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.4">
@@ -3998,37 +4058,37 @@
         <v>158</v>
       </c>
       <c r="C75" s="2">
-        <v>30950</v>
+        <v>140800</v>
       </c>
       <c r="D75" s="3">
-        <v>2.4799999999999999E-2</v>
+        <v>4.53E-2</v>
       </c>
       <c r="E75">
-        <v>12.8</v>
+        <v>11.69</v>
       </c>
       <c r="F75">
-        <v>13.49</v>
+        <v>5.33</v>
       </c>
       <c r="G75">
-        <v>12.93</v>
+        <v>6.07</v>
       </c>
       <c r="H75" s="4">
-        <v>31004.78</v>
+        <v>77979.460000000006</v>
       </c>
       <c r="I75">
-        <v>3.21</v>
+        <v>0.8</v>
       </c>
       <c r="J75">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="K75">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="L75">
-        <v>98.82</v>
+        <v>101.19</v>
       </c>
       <c r="M75">
-        <v>1.1399999999999999</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.4">
@@ -4039,37 +4099,37 @@
         <v>160</v>
       </c>
       <c r="C76" s="2">
-        <v>130000</v>
+        <v>155200</v>
       </c>
       <c r="D76" s="3">
-        <v>1.5599999999999999E-2</v>
+        <v>-3.2000000000000002E-3</v>
       </c>
       <c r="E76">
-        <v>16.75</v>
+        <v>8.86</v>
       </c>
       <c r="F76">
-        <v>4.34</v>
+        <v>11.63</v>
       </c>
       <c r="G76">
-        <v>21.73</v>
+        <v>8.51</v>
       </c>
       <c r="H76" s="4">
-        <v>49146.79</v>
+        <v>160038.65</v>
       </c>
       <c r="I76">
-        <v>0.28000000000000003</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="J76">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="K76">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="L76">
-        <v>97.56</v>
+        <v>100.49</v>
       </c>
       <c r="M76">
-        <v>4.42</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.4">
@@ -4080,37 +4140,37 @@
         <v>162</v>
       </c>
       <c r="C77" s="2">
-        <v>50900</v>
+        <v>560000</v>
       </c>
       <c r="D77" s="3">
-        <v>1.1900000000000001E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="E77">
-        <v>18.690000000000001</v>
+        <v>11.89</v>
       </c>
       <c r="F77">
-        <v>11.56</v>
+        <v>14.27</v>
       </c>
       <c r="G77">
-        <v>6.83</v>
+        <v>12.6</v>
       </c>
       <c r="H77" s="4">
-        <v>57293.3</v>
+        <v>95809.42</v>
       </c>
       <c r="I77">
-        <v>2.36</v>
+        <v>0.22</v>
       </c>
       <c r="J77">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="K77">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="L77">
-        <v>98.67</v>
+        <v>103.69</v>
       </c>
       <c r="M77">
-        <v>3.46</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.4">
@@ -4121,37 +4181,37 @@
         <v>164</v>
       </c>
       <c r="C78" s="2">
-        <v>63100</v>
+        <v>110100</v>
       </c>
       <c r="D78" s="3">
-        <v>2.1000000000000001E-2</v>
+        <v>-7.1999999999999998E-3</v>
       </c>
       <c r="E78">
-        <v>8.77</v>
+        <v>23.44</v>
       </c>
       <c r="F78">
-        <v>6.11</v>
+        <v>25.94</v>
       </c>
       <c r="G78">
-        <v>13.11</v>
+        <v>27.89</v>
       </c>
       <c r="H78" s="4">
-        <v>72587.83</v>
+        <v>59980.14</v>
       </c>
       <c r="I78">
-        <v>2.54</v>
+        <v>1.23</v>
       </c>
       <c r="J78">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="K78">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="L78">
-        <v>102.94</v>
+        <v>91.91</v>
       </c>
       <c r="M78">
-        <v>5.7</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.4">
@@ -4162,37 +4222,37 @@
         <v>166</v>
       </c>
       <c r="C79" s="2">
-        <v>265500</v>
+        <v>18850</v>
       </c>
       <c r="D79" s="3">
-        <v>1.72E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E79">
-        <v>6.36</v>
+        <v>6.96</v>
       </c>
       <c r="F79">
-        <v>7.5</v>
+        <v>9.58</v>
       </c>
       <c r="G79">
-        <v>10.119999999999999</v>
+        <v>7.18</v>
       </c>
       <c r="H79" s="4">
-        <v>128102.48</v>
+        <v>34223.949999999997</v>
       </c>
       <c r="I79">
-        <v>1.36</v>
+        <v>3.45</v>
       </c>
       <c r="J79">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K79">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L79">
-        <v>95.58</v>
+        <v>97.04</v>
       </c>
       <c r="M79">
-        <v>-1.3</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.4">
@@ -4203,37 +4263,37 @@
         <v>168</v>
       </c>
       <c r="C80" s="2">
-        <v>959000</v>
+        <v>17240</v>
       </c>
       <c r="D80" s="3">
-        <v>1E-3</v>
+        <v>2.6200000000000001E-2</v>
       </c>
       <c r="E80">
-        <v>41.5</v>
+        <v>3.6</v>
       </c>
       <c r="F80">
-        <v>41.5</v>
+        <v>9.42</v>
       </c>
       <c r="G80">
-        <v>36.18</v>
+        <v>5.91</v>
       </c>
       <c r="H80" s="4">
-        <v>56703.88</v>
+        <v>38541.279999999999</v>
       </c>
       <c r="I80">
-        <v>0.74</v>
+        <v>2.9</v>
       </c>
       <c r="J80">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="K80">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="L80">
-        <v>98</v>
+        <v>96.19</v>
       </c>
       <c r="M80">
-        <v>1.91</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.4">
@@ -4244,37 +4304,37 @@
         <v>170</v>
       </c>
       <c r="C81" s="2">
-        <v>133000</v>
+        <v>57400</v>
       </c>
       <c r="D81" s="3">
-        <v>9.9000000000000008E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="E81">
-        <v>6.18</v>
+        <v>10.79</v>
       </c>
       <c r="F81">
-        <v>5.98</v>
+        <v>10.55</v>
       </c>
       <c r="G81">
-        <v>7.78</v>
+        <v>8.93</v>
       </c>
       <c r="H81" s="4">
-        <v>102514.49</v>
+        <v>92723.77</v>
       </c>
       <c r="I81">
-        <v>0.38</v>
+        <v>3.48</v>
       </c>
       <c r="J81">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="K81">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="L81">
-        <v>100.4</v>
+        <v>90.82</v>
       </c>
       <c r="M81">
-        <v>2.86</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.4">
@@ -4285,37 +4345,37 @@
         <v>172</v>
       </c>
       <c r="C82" s="2">
-        <v>136000</v>
+        <v>30950</v>
       </c>
       <c r="D82" s="3">
-        <v>-3.5499999999999997E-2</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="E82">
-        <v>6.6</v>
+        <v>12.8</v>
       </c>
       <c r="F82">
-        <v>6.6</v>
+        <v>13.49</v>
       </c>
       <c r="G82">
-        <v>14.36</v>
+        <v>12.93</v>
       </c>
       <c r="H82" s="4">
-        <v>25848.86</v>
+        <v>31004.78</v>
       </c>
       <c r="I82">
-        <v>0.37</v>
+        <v>3.21</v>
       </c>
       <c r="J82">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K82">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L82">
-        <v>100.53</v>
+        <v>98.82</v>
       </c>
       <c r="M82">
-        <v>-12.93</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.4">
@@ -4326,37 +4386,37 @@
         <v>174</v>
       </c>
       <c r="C83" s="2">
-        <v>2735000</v>
+        <v>130000</v>
       </c>
       <c r="D83" s="3">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="E83">
-        <v>24.41</v>
+        <v>16.75</v>
       </c>
       <c r="F83">
-        <v>24.41</v>
+        <v>4.34</v>
       </c>
       <c r="G83">
-        <v>16.87</v>
+        <v>21.73</v>
       </c>
       <c r="H83" s="4">
-        <v>252284.7</v>
+        <v>49146.79</v>
       </c>
       <c r="I83">
-        <v>0.27</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J83">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="K83">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="L83">
-        <v>104.52</v>
+        <v>97.56</v>
       </c>
       <c r="M83">
-        <v>7.25</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.4">
@@ -4367,37 +4427,37 @@
         <v>176</v>
       </c>
       <c r="C84" s="2">
-        <v>430500</v>
+        <v>12800</v>
       </c>
       <c r="D84" s="3">
-        <v>1.06E-2</v>
+        <v>6.7599999999999993E-2</v>
       </c>
       <c r="E84">
-        <v>10.4</v>
+        <v>7.65</v>
       </c>
       <c r="F84">
-        <v>9.8800000000000008</v>
+        <v>4</v>
       </c>
       <c r="G84">
-        <v>9.14</v>
+        <v>7.8</v>
       </c>
       <c r="H84" s="4">
-        <v>65279.4</v>
+        <v>30039.25</v>
       </c>
       <c r="I84">
-        <v>0.41</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J84">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="K84">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="L84">
-        <v>100.33</v>
+        <v>103.97</v>
       </c>
       <c r="M84">
-        <v>7.76</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.4">
@@ -4408,36 +4468,446 @@
         <v>178</v>
       </c>
       <c r="C85" s="2">
+        <v>50900</v>
+      </c>
+      <c r="D85" s="3">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="E85">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="F85">
+        <v>11.56</v>
+      </c>
+      <c r="G85">
+        <v>6.83</v>
+      </c>
+      <c r="H85" s="4">
+        <v>57293.3</v>
+      </c>
+      <c r="I85">
+        <v>2.36</v>
+      </c>
+      <c r="J85">
+        <v>47</v>
+      </c>
+      <c r="K85">
+        <v>47</v>
+      </c>
+      <c r="L85">
+        <v>98.67</v>
+      </c>
+      <c r="M85">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A86" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B86" t="s">
+        <v>180</v>
+      </c>
+      <c r="C86" s="2">
+        <v>19570</v>
+      </c>
+      <c r="D86" s="5">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="F86">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="G86">
+        <v>10.31</v>
+      </c>
+      <c r="H86" s="4">
+        <v>26617.85</v>
+      </c>
+      <c r="I86">
+        <v>6</v>
+      </c>
+      <c r="J86">
+        <v>19</v>
+      </c>
+      <c r="K86">
+        <v>19</v>
+      </c>
+      <c r="L86">
+        <v>99.56</v>
+      </c>
+      <c r="M86">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A87" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B87" t="s">
+        <v>182</v>
+      </c>
+      <c r="C87" s="2">
+        <v>63100</v>
+      </c>
+      <c r="D87" s="3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E87">
+        <v>8.77</v>
+      </c>
+      <c r="F87">
+        <v>6.11</v>
+      </c>
+      <c r="G87">
+        <v>13.11</v>
+      </c>
+      <c r="H87" s="4">
+        <v>72587.83</v>
+      </c>
+      <c r="I87">
+        <v>2.54</v>
+      </c>
+      <c r="J87">
+        <v>77</v>
+      </c>
+      <c r="K87">
+        <v>77</v>
+      </c>
+      <c r="L87">
+        <v>102.94</v>
+      </c>
+      <c r="M87">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A88" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B88" t="s">
+        <v>184</v>
+      </c>
+      <c r="C88" s="2">
+        <v>265500</v>
+      </c>
+      <c r="D88" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="E88">
+        <v>6.36</v>
+      </c>
+      <c r="F88">
+        <v>7.5</v>
+      </c>
+      <c r="G88">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="H88" s="4">
+        <v>128102.48</v>
+      </c>
+      <c r="I88">
+        <v>1.36</v>
+      </c>
+      <c r="J88">
+        <v>81</v>
+      </c>
+      <c r="K88">
+        <v>81</v>
+      </c>
+      <c r="L88">
+        <v>95.58</v>
+      </c>
+      <c r="M88">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A89" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B89" t="s">
+        <v>186</v>
+      </c>
+      <c r="C89" s="2">
+        <v>959000</v>
+      </c>
+      <c r="D89" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="E89">
+        <v>41.5</v>
+      </c>
+      <c r="F89">
+        <v>41.5</v>
+      </c>
+      <c r="G89">
+        <v>36.18</v>
+      </c>
+      <c r="H89" s="4">
+        <v>56703.88</v>
+      </c>
+      <c r="I89">
+        <v>0.74</v>
+      </c>
+      <c r="J89">
+        <v>86</v>
+      </c>
+      <c r="K89">
+        <v>86</v>
+      </c>
+      <c r="L89">
+        <v>98</v>
+      </c>
+      <c r="M89">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A90" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B90" t="s">
+        <v>188</v>
+      </c>
+      <c r="C90" s="2">
+        <v>133000</v>
+      </c>
+      <c r="D90" s="3">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="E90">
+        <v>6.18</v>
+      </c>
+      <c r="F90">
+        <v>5.98</v>
+      </c>
+      <c r="G90">
+        <v>7.78</v>
+      </c>
+      <c r="H90" s="4">
+        <v>102514.49</v>
+      </c>
+      <c r="I90">
+        <v>0.38</v>
+      </c>
+      <c r="J90">
+        <v>87</v>
+      </c>
+      <c r="K90">
+        <v>87</v>
+      </c>
+      <c r="L90">
+        <v>100.4</v>
+      </c>
+      <c r="M90">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A91" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B91" t="s">
+        <v>190</v>
+      </c>
+      <c r="C91" s="2">
+        <v>136000</v>
+      </c>
+      <c r="D91" s="3">
+        <v>-3.5499999999999997E-2</v>
+      </c>
+      <c r="E91">
+        <v>6.6</v>
+      </c>
+      <c r="F91">
+        <v>6.6</v>
+      </c>
+      <c r="G91">
+        <v>14.36</v>
+      </c>
+      <c r="H91" s="4">
+        <v>25848.86</v>
+      </c>
+      <c r="I91">
+        <v>0.37</v>
+      </c>
+      <c r="J91">
+        <v>72</v>
+      </c>
+      <c r="K91">
+        <v>72</v>
+      </c>
+      <c r="L91">
+        <v>100.53</v>
+      </c>
+      <c r="M91">
+        <v>-12.93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A92" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B92" t="s">
+        <v>192</v>
+      </c>
+      <c r="C92" s="2">
+        <v>2735000</v>
+      </c>
+      <c r="D92" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="E92">
+        <v>24.41</v>
+      </c>
+      <c r="F92">
+        <v>24.41</v>
+      </c>
+      <c r="G92">
+        <v>16.87</v>
+      </c>
+      <c r="H92" s="4">
+        <v>252284.7</v>
+      </c>
+      <c r="I92">
+        <v>0.27</v>
+      </c>
+      <c r="J92">
+        <v>93</v>
+      </c>
+      <c r="K92">
+        <v>93</v>
+      </c>
+      <c r="L92">
+        <v>104.52</v>
+      </c>
+      <c r="M92">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A93" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B93" t="s">
+        <v>194</v>
+      </c>
+      <c r="C93" s="2">
+        <v>17370</v>
+      </c>
+      <c r="D93" s="3">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="E93">
+        <v>11.13</v>
+      </c>
+      <c r="F93">
+        <v>5.01</v>
+      </c>
+      <c r="G93">
+        <v>9.31</v>
+      </c>
+      <c r="H93" s="4">
+        <v>24921.41</v>
+      </c>
+      <c r="I93">
+        <v>5.76</v>
+      </c>
+      <c r="J93">
+        <v>43</v>
+      </c>
+      <c r="K93">
+        <v>43</v>
+      </c>
+      <c r="L93">
+        <v>101.1</v>
+      </c>
+      <c r="M93">
+        <v>6.76</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A94" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B94" t="s">
+        <v>196</v>
+      </c>
+      <c r="C94" s="2">
+        <v>430500</v>
+      </c>
+      <c r="D94" s="3">
+        <v>1.06E-2</v>
+      </c>
+      <c r="E94">
+        <v>10.4</v>
+      </c>
+      <c r="F94">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="G94">
+        <v>9.14</v>
+      </c>
+      <c r="H94" s="4">
+        <v>65279.4</v>
+      </c>
+      <c r="I94">
+        <v>0.41</v>
+      </c>
+      <c r="J94">
+        <v>75</v>
+      </c>
+      <c r="K94">
+        <v>75</v>
+      </c>
+      <c r="L94">
+        <v>100.33</v>
+      </c>
+      <c r="M94">
+        <v>7.76</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A95" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B95" t="s">
+        <v>198</v>
+      </c>
+      <c r="C95" s="2">
         <v>33900</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D95" s="3">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="E85">
+      <c r="E95">
         <v>9.39</v>
       </c>
-      <c r="F85">
+      <c r="F95">
         <v>10.74</v>
       </c>
-      <c r="G85">
+      <c r="G95">
         <v>9.73</v>
       </c>
-      <c r="H85" s="4">
+      <c r="H95" s="4">
         <v>48211.77</v>
       </c>
-      <c r="I85">
+      <c r="I95">
         <v>3.54</v>
       </c>
-      <c r="J85">
+      <c r="J95">
         <v>76</v>
       </c>
-      <c r="K85">
+      <c r="K95">
         <v>76</v>
       </c>
-      <c r="L85">
+      <c r="L95">
         <v>97.67</v>
       </c>
-      <c r="M85">
+      <c r="M95">
         <v>5.61</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{992102F2-0DCA-4964-B51B-99F621F8F94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E18E3FD7-1BEF-423C-8519-4B7A16F9C6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E524DFF4-9F2F-46DB-97BD-49B189E3F2FB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{80DF4D2B-2962-4151-AADE-F0DF0BBFB806}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -999,7 +999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2C218F-EC09-4E63-8518-5903438C7951}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45648007-4BFF-4D3D-8889-7BF2B750C615}">
   <dimension ref="A1:M95"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECAB0C0A-9A28-4756-A494-015975408F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F81F81FD-1518-4FE2-8040-83A9C31DEA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{2FD46682-2C92-4B5F-BDE2-2B7037E7C764}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{93006A8B-507B-4244-9C63-47DB8F437467}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="95">
   <si>
     <t>종목코드</t>
   </si>
@@ -96,12 +96,6 @@
     <t>세아베스틸지주</t>
   </si>
   <si>
-    <t>001680</t>
-  </si>
-  <si>
-    <t>대상</t>
-  </si>
-  <si>
     <t>002310</t>
   </si>
   <si>
@@ -126,24 +120,12 @@
     <t>코리안리</t>
   </si>
   <si>
-    <t>004370</t>
-  </si>
-  <si>
-    <t>농심</t>
-  </si>
-  <si>
     <t>004980</t>
   </si>
   <si>
     <t>성신양회</t>
   </si>
   <si>
-    <t>005180</t>
-  </si>
-  <si>
-    <t>빙그레</t>
-  </si>
-  <si>
     <t>005380</t>
   </si>
   <si>
@@ -162,12 +144,6 @@
     <t>NH투자증권</t>
   </si>
   <si>
-    <t>007310</t>
-  </si>
-  <si>
-    <t>오뚜기</t>
-  </si>
-  <si>
     <t>007340</t>
   </si>
   <si>
@@ -328,12 +304,6 @@
   </si>
   <si>
     <t>이노션</t>
-  </si>
-  <si>
-    <t>300720</t>
-  </si>
-  <si>
-    <t>한일시멘트</t>
   </si>
   <si>
     <t>316140</t>
@@ -717,8 +687,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0A3B9B-DA4F-40BF-9B1A-1F4A82E2F559}">
-  <dimension ref="A1:M48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE03462F-EA1C-4D0C-BF56-C9F6057B17B6}">
+  <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
@@ -783,37 +753,37 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>27100</v>
+        <v>26100</v>
       </c>
       <c r="D2" s="3">
-        <v>1.8800000000000001E-2</v>
+        <v>-3.6900000000000002E-2</v>
       </c>
       <c r="E2">
-        <v>8.2799999999999994</v>
+        <v>7.52</v>
       </c>
       <c r="F2">
-        <v>8.9</v>
+        <v>7.52</v>
       </c>
       <c r="G2">
-        <v>5.8</v>
+        <v>6.85</v>
       </c>
       <c r="H2" s="4">
-        <v>48390.96</v>
+        <v>50396.34</v>
       </c>
       <c r="I2">
-        <v>3.69</v>
+        <v>4.21</v>
       </c>
       <c r="J2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="K2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L2">
-        <v>96.42</v>
+        <v>98.86</v>
       </c>
       <c r="M2">
-        <v>7.97</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -824,10 +794,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>168500</v>
+        <v>152100</v>
       </c>
       <c r="D3" s="3">
-        <v>-1.17E-2</v>
+        <v>-1.6799999999999999E-2</v>
       </c>
       <c r="E3">
         <v>12.92</v>
@@ -842,19 +812,19 @@
         <v>157169.68</v>
       </c>
       <c r="I3">
-        <v>4.04</v>
+        <v>4.47</v>
       </c>
       <c r="J3">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="K3">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="L3">
-        <v>97.69</v>
+        <v>91.81</v>
       </c>
       <c r="M3">
-        <v>4.66</v>
+        <v>-9.09</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -865,10 +835,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>474500</v>
+        <v>436500</v>
       </c>
       <c r="D4" s="3">
-        <v>-8.3999999999999995E-3</v>
+        <v>-3.6400000000000002E-2</v>
       </c>
       <c r="E4">
         <v>13.09</v>
@@ -883,19 +853,19 @@
         <v>405451.96</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="J4">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K4">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="L4">
-        <v>93.46</v>
+        <v>90.58</v>
       </c>
       <c r="M4">
-        <v>-2.87</v>
+        <v>-8.59</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -906,37 +876,37 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>47150</v>
+        <v>46000</v>
       </c>
       <c r="D5" s="3">
-        <v>5.96E-2</v>
+        <v>-4.5600000000000002E-2</v>
       </c>
       <c r="E5">
-        <v>7.12</v>
+        <v>5.22</v>
       </c>
       <c r="F5">
-        <v>9.6199999999999992</v>
+        <v>5.22</v>
       </c>
       <c r="G5">
-        <v>12.61</v>
+        <v>5.84</v>
       </c>
       <c r="H5" s="4">
-        <v>72041.39</v>
+        <v>72566.75</v>
       </c>
       <c r="I5">
-        <v>4.24</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="J5">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="K5">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="L5">
-        <v>107.59</v>
+        <v>105.3</v>
       </c>
       <c r="M5">
-        <v>14.72</v>
+        <v>2.2200000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -947,10 +917,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>78600</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1.95E-2</v>
+        <v>75000</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
       </c>
       <c r="E6">
         <v>4.05</v>
@@ -965,19 +935,19 @@
         <v>65679.45</v>
       </c>
       <c r="I6">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K6">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L6">
-        <v>94.13</v>
+        <v>96.09</v>
       </c>
       <c r="M6">
-        <v>1.81</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -988,37 +958,37 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>66200</v>
+        <v>65100</v>
       </c>
       <c r="D7" s="3">
-        <v>1.6899999999999998E-2</v>
+        <v>-7.2599999999999998E-2</v>
       </c>
       <c r="E7">
-        <v>1.04</v>
+        <v>2.89</v>
       </c>
       <c r="F7">
-        <v>3.97</v>
+        <v>2.89</v>
       </c>
       <c r="G7">
-        <v>4.21</v>
+        <v>3.54</v>
       </c>
       <c r="H7" s="4">
-        <v>53899.69</v>
+        <v>54191.72</v>
       </c>
       <c r="I7">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="J7">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K7">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L7">
-        <v>98.89</v>
+        <v>98.54</v>
       </c>
       <c r="M7">
-        <v>6.95</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -1029,37 +999,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>20700</v>
+        <v>8620</v>
       </c>
       <c r="D8" s="3">
-        <v>1.9699999999999999E-2</v>
+        <v>-4.7500000000000001E-2</v>
       </c>
       <c r="E8">
-        <v>6.94</v>
+        <v>2.84</v>
       </c>
       <c r="F8">
-        <v>6.38</v>
+        <v>4.16</v>
       </c>
       <c r="G8">
-        <v>6.21</v>
+        <v>8.36</v>
       </c>
       <c r="H8" s="4">
-        <v>39784.050000000003</v>
+        <v>20859.37</v>
       </c>
       <c r="I8">
-        <v>4.1100000000000003</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K8">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L8">
-        <v>96.5</v>
+        <v>93.5</v>
       </c>
       <c r="M8">
-        <v>1.22</v>
+        <v>-6.51</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1070,37 +1040,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>9090</v>
+        <v>37650</v>
       </c>
       <c r="D9" s="3">
-        <v>2.3599999999999999E-2</v>
+        <v>-1.44E-2</v>
       </c>
       <c r="E9">
-        <v>2.84</v>
+        <v>4.57</v>
       </c>
       <c r="F9">
-        <v>4.16</v>
+        <v>7.42</v>
       </c>
       <c r="G9">
-        <v>8.36</v>
+        <v>4.55</v>
       </c>
       <c r="H9" s="4">
-        <v>20859.37</v>
+        <v>42814.52</v>
       </c>
       <c r="I9">
-        <v>2.42</v>
+        <v>3.19</v>
       </c>
       <c r="J9">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="K9">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="L9">
-        <v>94.11</v>
+        <v>95.11</v>
       </c>
       <c r="M9">
-        <v>-2.4700000000000002</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1111,37 +1081,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>40350</v>
+        <v>85700</v>
       </c>
       <c r="D10" s="3">
-        <v>1.77E-2</v>
+        <v>-2.06E-2</v>
       </c>
       <c r="E10">
-        <v>4.57</v>
+        <v>2.64</v>
       </c>
       <c r="F10">
-        <v>7.42</v>
+        <v>2.64</v>
       </c>
       <c r="G10">
-        <v>4.55</v>
+        <v>3.23</v>
       </c>
       <c r="H10" s="4">
-        <v>42814.52</v>
+        <v>184176.03</v>
       </c>
       <c r="I10">
-        <v>2.97</v>
+        <v>3.62</v>
       </c>
       <c r="J10">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="K10">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="L10">
-        <v>96.72</v>
+        <v>92.8</v>
       </c>
       <c r="M10">
-        <v>3.59</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1152,37 +1122,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>95500</v>
+        <v>13170</v>
       </c>
       <c r="D11" s="3">
-        <v>5.5199999999999999E-2</v>
+        <v>-1.35E-2</v>
       </c>
       <c r="E11">
-        <v>2.16</v>
+        <v>9.44</v>
       </c>
       <c r="F11">
-        <v>5.36</v>
+        <v>10.67</v>
       </c>
       <c r="G11">
-        <v>5.18</v>
+        <v>9.86</v>
       </c>
       <c r="H11" s="4">
-        <v>177736.27</v>
+        <v>19219.419999999998</v>
       </c>
       <c r="I11">
-        <v>3.25</v>
+        <v>3.91</v>
       </c>
       <c r="J11">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="K11">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="L11">
-        <v>99.9</v>
+        <v>100.06</v>
       </c>
       <c r="M11">
-        <v>1.49</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1193,37 +1163,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>13170</v>
+        <v>9410</v>
       </c>
       <c r="D12" s="3">
-        <v>5.3E-3</v>
+        <v>-2.69E-2</v>
       </c>
       <c r="E12">
-        <v>9.44</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="F12">
-        <v>10.67</v>
+        <v>3.26</v>
       </c>
       <c r="G12">
-        <v>9.86</v>
+        <v>5.34</v>
       </c>
       <c r="H12" s="4">
-        <v>19219.419999999998</v>
+        <v>22736.17</v>
       </c>
       <c r="I12">
-        <v>3.91</v>
+        <v>3.72</v>
       </c>
       <c r="J12">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="K12">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="L12">
-        <v>98.16</v>
+        <v>98.79</v>
       </c>
       <c r="M12">
-        <v>2.57</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1234,37 +1204,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>380500</v>
+        <v>475750</v>
       </c>
       <c r="D13" s="3">
-        <v>2.5600000000000001E-2</v>
+        <v>-2.9100000000000001E-2</v>
       </c>
       <c r="E13">
-        <v>6.18</v>
+        <v>8.41</v>
       </c>
       <c r="F13">
-        <v>6.18</v>
+        <v>8.41</v>
       </c>
       <c r="G13">
-        <v>6.54</v>
+        <v>11.51</v>
       </c>
       <c r="H13" s="4">
-        <v>476371.16</v>
+        <v>436418.31</v>
       </c>
       <c r="I13">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="K13">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="L13">
-        <v>94.68</v>
+        <v>90.39</v>
       </c>
       <c r="M13">
-        <v>-1.81</v>
+        <v>-8.86</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1275,37 +1245,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>10090</v>
+        <v>169000</v>
       </c>
       <c r="D14" s="3">
-        <v>8.3799999999999999E-2</v>
+        <v>-3.9199999999999999E-2</v>
       </c>
       <c r="E14">
-        <v>8.2100000000000009</v>
+        <v>18.96</v>
       </c>
       <c r="F14">
-        <v>3.26</v>
+        <v>19.43</v>
       </c>
       <c r="G14">
-        <v>5.34</v>
+        <v>18.8</v>
       </c>
       <c r="H14" s="4">
-        <v>22736.17</v>
+        <v>144109.65</v>
       </c>
       <c r="I14">
-        <v>3.47</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J14">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="K14">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L14">
-        <v>104.46</v>
+        <v>92.78</v>
       </c>
       <c r="M14">
-        <v>8.85</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1316,37 +1286,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>75600</v>
+        <v>33600</v>
       </c>
       <c r="D15" s="3">
-        <v>1.0699999999999999E-2</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="E15">
-        <v>7.58</v>
+        <v>8.73</v>
       </c>
       <c r="F15">
-        <v>7.58</v>
+        <v>11.57</v>
       </c>
       <c r="G15">
-        <v>12.29</v>
+        <v>6.85</v>
       </c>
       <c r="H15" s="4">
-        <v>79498.27</v>
+        <v>24348.21</v>
       </c>
       <c r="I15">
-        <v>4.37</v>
+        <v>2.83</v>
       </c>
       <c r="J15">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="K15">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="L15">
-        <v>95.94</v>
+        <v>102.52</v>
       </c>
       <c r="M15">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1357,37 +1327,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>517000</v>
+        <v>39400</v>
       </c>
       <c r="D16" s="3">
-        <v>-9.5999999999999992E-3</v>
+        <v>-4.48E-2</v>
       </c>
       <c r="E16">
-        <v>8.41</v>
+        <v>15.02</v>
       </c>
       <c r="F16">
-        <v>8.41</v>
+        <v>15.02</v>
       </c>
       <c r="G16">
-        <v>11.51</v>
+        <v>20.7</v>
       </c>
       <c r="H16" s="4">
-        <v>436418.31</v>
+        <v>34750.239999999998</v>
       </c>
       <c r="I16">
-        <v>1.93</v>
+        <v>2.54</v>
       </c>
       <c r="J16">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="K16">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="L16">
-        <v>95.56</v>
+        <v>121.28</v>
       </c>
       <c r="M16">
-        <v>-1.52</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1398,37 +1368,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>186700</v>
+        <v>217500</v>
       </c>
       <c r="D17" s="3">
-        <v>1.1900000000000001E-2</v>
+        <v>-6.7999999999999996E-3</v>
       </c>
       <c r="E17">
-        <v>18.96</v>
+        <v>13.17</v>
       </c>
       <c r="F17">
-        <v>19.43</v>
+        <v>11.69</v>
       </c>
       <c r="G17">
-        <v>18.8</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="H17" s="4">
-        <v>144109.65</v>
+        <v>207156.6</v>
       </c>
       <c r="I17">
-        <v>3.64</v>
+        <v>2.46</v>
       </c>
       <c r="J17">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K17">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>96.12</v>
       </c>
       <c r="M17">
-        <v>1.74</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1439,37 +1409,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>35600</v>
+        <v>123100</v>
       </c>
       <c r="D18" s="3">
-        <v>6.59E-2</v>
+        <v>-3.8300000000000001E-2</v>
       </c>
       <c r="E18">
-        <v>8.73</v>
+        <v>4.74</v>
       </c>
       <c r="F18">
-        <v>11.57</v>
+        <v>4.74</v>
       </c>
       <c r="G18">
-        <v>6.85</v>
+        <v>6.13</v>
       </c>
       <c r="H18" s="4">
-        <v>24348.21</v>
+        <v>215808.28</v>
       </c>
       <c r="I18">
-        <v>2.67</v>
+        <v>1.38</v>
       </c>
       <c r="J18">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="K18">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="L18">
-        <v>105.4</v>
+        <v>97.31</v>
       </c>
       <c r="M18">
-        <v>13.38</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1480,37 +1450,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>368000</v>
+        <v>95600</v>
       </c>
       <c r="D19" s="3">
-        <v>-1.4E-3</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="E19">
-        <v>6.85</v>
+        <v>12.89</v>
       </c>
       <c r="F19">
-        <v>6.19</v>
+        <v>13.94</v>
       </c>
       <c r="G19">
-        <v>10.64</v>
+        <v>9.44</v>
       </c>
       <c r="H19" s="4">
-        <v>605494.72</v>
+        <v>87743.72</v>
       </c>
       <c r="I19">
-        <v>2.4500000000000002</v>
+        <v>3.66</v>
       </c>
       <c r="J19">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="K19">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="L19">
-        <v>96.91</v>
+        <v>98.88</v>
       </c>
       <c r="M19">
-        <v>2.2200000000000002</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1521,37 +1491,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>39750</v>
+        <v>78500</v>
       </c>
       <c r="D20" s="3">
-        <v>3.8E-3</v>
+        <v>-1.8800000000000001E-2</v>
       </c>
       <c r="E20">
-        <v>15.02</v>
+        <v>3.33</v>
       </c>
       <c r="F20">
-        <v>15.02</v>
+        <v>3.33</v>
       </c>
       <c r="G20">
-        <v>20.7</v>
+        <v>7.93</v>
       </c>
       <c r="H20" s="4">
-        <v>34750.239999999998</v>
+        <v>60299.05</v>
       </c>
       <c r="I20">
-        <v>2.52</v>
+        <v>2.11</v>
       </c>
       <c r="J20">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="K20">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L20">
-        <v>131.59</v>
+        <v>101.41</v>
       </c>
       <c r="M20">
-        <v>43.24</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1562,37 +1532,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>227000</v>
+        <v>84900</v>
       </c>
       <c r="D21" s="3">
-        <v>2.4799999999999999E-2</v>
+        <v>-2.0799999999999999E-2</v>
       </c>
       <c r="E21">
-        <v>13.17</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="F21">
-        <v>11.69</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="G21">
-        <v>18.010000000000002</v>
+        <v>20.22</v>
       </c>
       <c r="H21" s="4">
-        <v>207156.6</v>
+        <v>37882.559999999998</v>
       </c>
       <c r="I21">
-        <v>2.36</v>
+        <v>16.5</v>
       </c>
       <c r="J21">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="K21">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="L21">
-        <v>98.43</v>
+        <v>96.68</v>
       </c>
       <c r="M21">
-        <v>2.02</v>
+        <v>-2.5299999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1603,37 +1573,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>131900</v>
+        <v>23150</v>
       </c>
       <c r="D22" s="3">
-        <v>-1.7100000000000001E-2</v>
+        <v>-1.0699999999999999E-2</v>
       </c>
       <c r="E22">
-        <v>4.74</v>
+        <v>8.06</v>
       </c>
       <c r="F22">
-        <v>4.74</v>
+        <v>8.64</v>
       </c>
       <c r="G22">
-        <v>6.13</v>
+        <v>8.77</v>
       </c>
       <c r="H22" s="4">
-        <v>215808.28</v>
+        <v>44443.18</v>
       </c>
       <c r="I22">
-        <v>1.29</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J22">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="K22">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="L22">
-        <v>99.74</v>
+        <v>98.39</v>
       </c>
       <c r="M22">
-        <v>8.2899999999999991</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1644,37 +1614,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>102300</v>
+        <v>53900</v>
       </c>
       <c r="D23" s="3">
-        <v>3.7499999999999999E-2</v>
+        <v>-1.0999999999999999E-2</v>
       </c>
       <c r="E23">
-        <v>12.89</v>
+        <v>7.45</v>
       </c>
       <c r="F23">
-        <v>13.94</v>
+        <v>7.45</v>
       </c>
       <c r="G23">
-        <v>9.44</v>
+        <v>7.69</v>
       </c>
       <c r="H23" s="4">
-        <v>87743.72</v>
+        <v>79986.48</v>
       </c>
       <c r="I23">
-        <v>3.42</v>
+        <v>5.19</v>
       </c>
       <c r="J23">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="K23">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="L23">
-        <v>101.8</v>
+        <v>91.61</v>
       </c>
       <c r="M23">
-        <v>9.5299999999999994</v>
+        <v>-8.02</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1685,37 +1655,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>78800</v>
+        <v>19670</v>
       </c>
       <c r="D24" s="3">
-        <v>7.7000000000000002E-3</v>
+        <v>-8.0999999999999996E-3</v>
       </c>
       <c r="E24">
-        <v>3.33</v>
+        <v>13.7</v>
       </c>
       <c r="F24">
-        <v>3.33</v>
+        <v>13.7</v>
       </c>
       <c r="G24">
-        <v>7.93</v>
+        <v>14.6</v>
       </c>
       <c r="H24" s="4">
-        <v>60299.05</v>
+        <v>16125.49</v>
       </c>
       <c r="I24">
-        <v>2.11</v>
+        <v>6.25</v>
       </c>
       <c r="J24">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="K24">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="L24">
-        <v>100.76</v>
+        <v>95.63</v>
       </c>
       <c r="M24">
-        <v>2.0699999999999998</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1726,37 +1696,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>88800</v>
+        <v>60200</v>
       </c>
       <c r="D25" s="3">
-        <v>1.6E-2</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="E25">
-        <v>14.42</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="F25">
-        <v>24.2</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="G25">
-        <v>15.82</v>
+        <v>6.37</v>
       </c>
       <c r="H25" s="4">
-        <v>36460.550000000003</v>
+        <v>71885.83</v>
       </c>
       <c r="I25">
-        <v>6.19</v>
+        <v>3.99</v>
       </c>
       <c r="J25">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K25">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L25">
-        <v>95.04</v>
+        <v>100.65</v>
       </c>
       <c r="M25">
-        <v>-0.11</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1767,37 +1737,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>24100</v>
+        <v>15860</v>
       </c>
       <c r="D26" s="3">
-        <v>1.6899999999999998E-2</v>
+        <v>-5.5999999999999999E-3</v>
       </c>
       <c r="E26">
-        <v>8.06</v>
+        <v>6.01</v>
       </c>
       <c r="F26">
-        <v>8.64</v>
+        <v>6.01</v>
       </c>
       <c r="G26">
-        <v>8.77</v>
+        <v>5.97</v>
       </c>
       <c r="H26" s="4">
-        <v>44443.18</v>
+        <v>20769.650000000001</v>
       </c>
       <c r="I26">
-        <v>4.42</v>
+        <v>4.16</v>
       </c>
       <c r="J26">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K26">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L26">
-        <v>98.45</v>
+        <v>103.06</v>
       </c>
       <c r="M26">
-        <v>4.33</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1808,37 +1778,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>59700</v>
+        <v>218500</v>
       </c>
       <c r="D27" s="3">
-        <v>-1.6999999999999999E-3</v>
+        <v>-1.5800000000000002E-2</v>
       </c>
       <c r="E27">
-        <v>7.45</v>
+        <v>4.66</v>
       </c>
       <c r="F27">
-        <v>7.45</v>
+        <v>4.66</v>
       </c>
       <c r="G27">
-        <v>7.69</v>
+        <v>4.88</v>
       </c>
       <c r="H27" s="4">
-        <v>79986.48</v>
+        <v>324173.33</v>
       </c>
       <c r="I27">
-        <v>4.6900000000000004</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="J27">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K27">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L27">
-        <v>98.04</v>
+        <v>99.78</v>
       </c>
       <c r="M27">
-        <v>1.53</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1849,37 +1819,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>21300</v>
+        <v>156500</v>
       </c>
       <c r="D28" s="3">
-        <v>1.67E-2</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="E28">
-        <v>13.7</v>
+        <v>11.77</v>
       </c>
       <c r="F28">
-        <v>13.7</v>
+        <v>11.77</v>
       </c>
       <c r="G28">
-        <v>14.6</v>
+        <v>11.4</v>
       </c>
       <c r="H28" s="4">
-        <v>16125.49</v>
+        <v>85735.74</v>
       </c>
       <c r="I28">
-        <v>5.77</v>
+        <v>3.83</v>
       </c>
       <c r="J28">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="K28">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="L28">
-        <v>100.84</v>
+        <v>100.38</v>
       </c>
       <c r="M28">
-        <v>3.4</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1890,37 +1860,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>60700</v>
+        <v>18120</v>
       </c>
       <c r="D29" s="3">
-        <v>2.3599999999999999E-2</v>
+        <v>-6.6E-3</v>
       </c>
       <c r="E29">
-        <v>10.220000000000001</v>
+        <v>8.11</v>
       </c>
       <c r="F29">
-        <v>10.220000000000001</v>
+        <v>8.11</v>
       </c>
       <c r="G29">
-        <v>6.37</v>
+        <v>9.93</v>
       </c>
       <c r="H29" s="4">
-        <v>71885.83</v>
+        <v>19583.27</v>
       </c>
       <c r="I29">
-        <v>3.95</v>
+        <v>5.24</v>
       </c>
       <c r="J29">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="K29">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="L29">
-        <v>98.58</v>
+        <v>100.18</v>
       </c>
       <c r="M29">
-        <v>-0.16</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1931,37 +1901,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>15820</v>
+        <v>34850</v>
       </c>
       <c r="D30" s="3">
-        <v>1.2800000000000001E-2</v>
+        <v>-3.1899999999999998E-2</v>
       </c>
       <c r="E30">
-        <v>6.01</v>
+        <v>1.23</v>
       </c>
       <c r="F30">
-        <v>6.01</v>
+        <v>1.23</v>
       </c>
       <c r="G30">
-        <v>5.97</v>
+        <v>1.59</v>
       </c>
       <c r="H30" s="4">
-        <v>20769.650000000001</v>
+        <v>118301.94</v>
       </c>
       <c r="I30">
-        <v>4.17</v>
+        <v>3.31</v>
       </c>
       <c r="J30">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="K30">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="L30">
-        <v>99.7</v>
+        <v>95.46</v>
       </c>
       <c r="M30">
-        <v>7.18</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1972,37 +1942,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>231500</v>
+        <v>91600</v>
       </c>
       <c r="D31" s="3">
-        <v>4.3E-3</v>
+        <v>-1.9300000000000001E-2</v>
       </c>
       <c r="E31">
-        <v>4.66</v>
+        <v>8.11</v>
       </c>
       <c r="F31">
-        <v>4.66</v>
+        <v>10.44</v>
       </c>
       <c r="G31">
-        <v>4.88</v>
+        <v>8.66</v>
       </c>
       <c r="H31" s="4">
-        <v>324173.33</v>
+        <v>119742.76</v>
       </c>
       <c r="I31">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="J31">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="K31">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L31">
-        <v>104.47</v>
+        <v>99.23</v>
       </c>
       <c r="M31">
-        <v>9.4600000000000009</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -2013,37 +1983,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>157500</v>
+        <v>214500</v>
       </c>
       <c r="D32" s="3">
-        <v>3.2000000000000002E-3</v>
+        <v>-6.8999999999999999E-3</v>
       </c>
       <c r="E32">
-        <v>11.77</v>
+        <v>11.54</v>
       </c>
       <c r="F32">
-        <v>11.77</v>
+        <v>20.98</v>
       </c>
       <c r="G32">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
       <c r="H32" s="4">
-        <v>85735.74</v>
+        <v>189057.03</v>
       </c>
       <c r="I32">
-        <v>3.81</v>
+        <v>1.86</v>
       </c>
       <c r="J32">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="K32">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L32">
-        <v>97.91</v>
+        <v>95.03</v>
       </c>
       <c r="M32">
-        <v>1.88</v>
+        <v>-8.14</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2054,37 +2024,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>18190</v>
+        <v>66100</v>
       </c>
       <c r="D33" s="3">
-        <v>1.9E-2</v>
+        <v>-2.5100000000000001E-2</v>
       </c>
       <c r="E33">
-        <v>8.11</v>
+        <v>5.55</v>
       </c>
       <c r="F33">
-        <v>8.11</v>
+        <v>5.55</v>
       </c>
       <c r="G33">
-        <v>9.93</v>
+        <v>6.57</v>
       </c>
       <c r="H33" s="4">
-        <v>19583.27</v>
+        <v>155269.29999999999</v>
       </c>
       <c r="I33">
-        <v>5.22</v>
+        <v>4.54</v>
       </c>
       <c r="J33">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="K33">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="L33">
-        <v>98.7</v>
+        <v>100.02</v>
       </c>
       <c r="M33">
-        <v>1.9</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2095,37 +2065,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>37700</v>
+        <v>107400</v>
       </c>
       <c r="D34" s="3">
-        <v>0.04</v>
+        <v>-1.29E-2</v>
       </c>
       <c r="E34">
-        <v>1.23</v>
+        <v>9.17</v>
       </c>
       <c r="F34">
-        <v>1.23</v>
+        <v>9.17</v>
       </c>
       <c r="G34">
-        <v>1.59</v>
+        <v>9.1</v>
       </c>
       <c r="H34" s="4">
-        <v>118301.94</v>
+        <v>162088.94</v>
       </c>
       <c r="I34">
-        <v>3.06</v>
+        <v>3.82</v>
       </c>
       <c r="J34">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="K34">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="L34">
-        <v>97.4</v>
+        <v>96.84</v>
       </c>
       <c r="M34">
-        <v>4.43</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2136,37 +2106,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>97900</v>
+        <v>150700</v>
       </c>
       <c r="D35" s="3">
-        <v>1.4500000000000001E-2</v>
+        <v>-9.9000000000000008E-3</v>
       </c>
       <c r="E35">
-        <v>8.11</v>
+        <v>8.86</v>
       </c>
       <c r="F35">
-        <v>10.44</v>
+        <v>11.63</v>
       </c>
       <c r="G35">
-        <v>8.66</v>
+        <v>8.51</v>
       </c>
       <c r="H35" s="4">
-        <v>119742.76</v>
+        <v>160038.65</v>
       </c>
       <c r="I35">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="J35">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="K35">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L35">
-        <v>103.42</v>
+        <v>100.6</v>
       </c>
       <c r="M35">
-        <v>9.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2177,37 +2147,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>234500</v>
+        <v>18260</v>
       </c>
       <c r="D36" s="3">
-        <v>2.4E-2</v>
+        <v>-9.1999999999999998E-3</v>
       </c>
       <c r="E36">
-        <v>11.54</v>
+        <v>6.96</v>
       </c>
       <c r="F36">
-        <v>20.98</v>
+        <v>9.58</v>
       </c>
       <c r="G36">
-        <v>9.6</v>
+        <v>7.18</v>
       </c>
       <c r="H36" s="4">
-        <v>189057.03</v>
+        <v>34223.949999999997</v>
       </c>
       <c r="I36">
-        <v>1.7</v>
+        <v>3.56</v>
       </c>
       <c r="J36">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K36">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L36">
-        <v>97.34</v>
+        <v>98.66</v>
       </c>
       <c r="M36">
-        <v>6.59</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2218,37 +2188,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>69000</v>
+        <v>17250</v>
       </c>
       <c r="D37" s="3">
-        <v>5.5E-2</v>
+        <v>1.5900000000000001E-2</v>
       </c>
       <c r="E37">
-        <v>4.12</v>
+        <v>3.6</v>
       </c>
       <c r="F37">
-        <v>5.22</v>
+        <v>9.42</v>
       </c>
       <c r="G37">
-        <v>11.01</v>
+        <v>5.91</v>
       </c>
       <c r="H37" s="4">
-        <v>151788</v>
+        <v>38541.279999999999</v>
       </c>
       <c r="I37">
-        <v>3.91</v>
+        <v>2.9</v>
       </c>
       <c r="J37">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="K37">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L37">
-        <v>102.23</v>
+        <v>101.46</v>
       </c>
       <c r="M37">
-        <v>7.81</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2259,37 +2229,37 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>113200</v>
-      </c>
-      <c r="D38" s="5">
-        <v>0</v>
+        <v>57000</v>
+      </c>
+      <c r="D38" s="3">
+        <v>-7.0000000000000001E-3</v>
       </c>
       <c r="E38">
-        <v>9.17</v>
+        <v>9.39</v>
       </c>
       <c r="F38">
-        <v>9.17</v>
+        <v>9.39</v>
       </c>
       <c r="G38">
-        <v>9.1</v>
+        <v>9.34</v>
       </c>
       <c r="H38" s="4">
-        <v>162088.94</v>
+        <v>98085.37</v>
       </c>
       <c r="I38">
-        <v>3.63</v>
+        <v>4.04</v>
       </c>
       <c r="J38">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="K38">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="L38">
-        <v>97.67</v>
+        <v>97.25</v>
       </c>
       <c r="M38">
-        <v>3</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2300,37 +2270,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>155200</v>
+        <v>30950</v>
       </c>
       <c r="D39" s="3">
-        <v>-3.2000000000000002E-3</v>
+        <v>3.1699999999999999E-2</v>
       </c>
       <c r="E39">
-        <v>8.86</v>
+        <v>12.8</v>
       </c>
       <c r="F39">
-        <v>11.63</v>
+        <v>13.49</v>
       </c>
       <c r="G39">
-        <v>8.51</v>
+        <v>12.93</v>
       </c>
       <c r="H39" s="4">
-        <v>160038.65</v>
+        <v>31004.78</v>
       </c>
       <c r="I39">
-        <v>2.0499999999999998</v>
+        <v>3.21</v>
       </c>
       <c r="J39">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K39">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="L39">
-        <v>100.49</v>
+        <v>103.13</v>
       </c>
       <c r="M39">
-        <v>5.29</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2341,37 +2311,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>18850</v>
+        <v>11230</v>
       </c>
       <c r="D40" s="3">
-        <v>0.02</v>
+        <v>-2.9399999999999999E-2</v>
       </c>
       <c r="E40">
-        <v>6.96</v>
+        <v>7.65</v>
       </c>
       <c r="F40">
-        <v>9.58</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>7.18</v>
+        <v>7.8</v>
       </c>
       <c r="H40" s="4">
-        <v>34223.949999999997</v>
+        <v>30039.25</v>
       </c>
       <c r="I40">
-        <v>3.45</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="J40">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="K40">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="L40">
-        <v>97.04</v>
+        <v>93.96</v>
       </c>
       <c r="M40">
-        <v>2.84</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2382,37 +2352,37 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>17240</v>
+        <v>49600</v>
       </c>
       <c r="D41" s="3">
-        <v>2.6200000000000001E-2</v>
+        <v>-1.3899999999999999E-2</v>
       </c>
       <c r="E41">
-        <v>3.6</v>
+        <v>11.33</v>
       </c>
       <c r="F41">
-        <v>9.42</v>
+        <v>11.33</v>
       </c>
       <c r="G41">
-        <v>5.91</v>
+        <v>16.21</v>
       </c>
       <c r="H41" s="4">
-        <v>38541.279999999999</v>
+        <v>59573.64</v>
       </c>
       <c r="I41">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="J41">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="K41">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="L41">
-        <v>96.19</v>
+        <v>99.02</v>
       </c>
       <c r="M41">
-        <v>0.76</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2423,37 +2393,37 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>57400</v>
+        <v>18000</v>
       </c>
       <c r="D42" s="3">
-        <v>7.0000000000000001E-3</v>
+        <v>-1.21E-2</v>
       </c>
       <c r="E42">
-        <v>10.79</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="F42">
-        <v>10.55</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="G42">
-        <v>8.93</v>
+        <v>10.31</v>
       </c>
       <c r="H42" s="4">
-        <v>92723.77</v>
+        <v>26617.85</v>
       </c>
       <c r="I42">
-        <v>3.48</v>
+        <v>6.53</v>
       </c>
       <c r="J42">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="K42">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>90.82</v>
+        <v>93.76</v>
       </c>
       <c r="M42">
-        <v>-2.88</v>
+        <v>-8.49</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2464,242 +2434,37 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>30950</v>
+        <v>33050</v>
       </c>
       <c r="D43" s="3">
-        <v>2.4799999999999999E-2</v>
+        <v>-4.4999999999999997E-3</v>
       </c>
       <c r="E43">
-        <v>12.8</v>
+        <v>9.39</v>
       </c>
       <c r="F43">
-        <v>13.49</v>
+        <v>10.74</v>
       </c>
       <c r="G43">
-        <v>12.93</v>
+        <v>9.73</v>
       </c>
       <c r="H43" s="4">
-        <v>31004.78</v>
+        <v>48211.77</v>
       </c>
       <c r="I43">
-        <v>3.21</v>
+        <v>3.63</v>
       </c>
       <c r="J43">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K43">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L43">
-        <v>98.82</v>
+        <v>100.1</v>
       </c>
       <c r="M43">
-        <v>1.1399999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A44" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B44" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" s="2">
-        <v>12800</v>
-      </c>
-      <c r="D44" s="3">
-        <v>6.7599999999999993E-2</v>
-      </c>
-      <c r="E44">
-        <v>7.65</v>
-      </c>
-      <c r="F44">
-        <v>4</v>
-      </c>
-      <c r="G44">
-        <v>7.8</v>
-      </c>
-      <c r="H44" s="4">
-        <v>30039.25</v>
-      </c>
-      <c r="I44">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="J44">
-        <v>47</v>
-      </c>
-      <c r="K44">
-        <v>47</v>
-      </c>
-      <c r="L44">
-        <v>103.97</v>
-      </c>
-      <c r="M44">
-        <v>7.29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A45" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="2">
-        <v>50900</v>
-      </c>
-      <c r="D45" s="3">
-        <v>1.1900000000000001E-2</v>
-      </c>
-      <c r="E45">
-        <v>18.690000000000001</v>
-      </c>
-      <c r="F45">
-        <v>11.56</v>
-      </c>
-      <c r="G45">
-        <v>6.83</v>
-      </c>
-      <c r="H45" s="4">
-        <v>57293.3</v>
-      </c>
-      <c r="I45">
-        <v>2.36</v>
-      </c>
-      <c r="J45">
-        <v>47</v>
-      </c>
-      <c r="K45">
-        <v>47</v>
-      </c>
-      <c r="L45">
-        <v>98.67</v>
-      </c>
-      <c r="M45">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A46" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B46" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" s="2">
-        <v>19570</v>
-      </c>
-      <c r="D46" s="5">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="F46">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="G46">
-        <v>10.31</v>
-      </c>
-      <c r="H46" s="4">
-        <v>26617.85</v>
-      </c>
-      <c r="I46">
-        <v>6</v>
-      </c>
-      <c r="J46">
-        <v>19</v>
-      </c>
-      <c r="K46">
-        <v>19</v>
-      </c>
-      <c r="L46">
-        <v>99.56</v>
-      </c>
-      <c r="M46">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A47" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B47" t="s">
-        <v>102</v>
-      </c>
-      <c r="C47" s="2">
-        <v>17370</v>
-      </c>
-      <c r="D47" s="3">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="E47">
-        <v>11.13</v>
-      </c>
-      <c r="F47">
-        <v>5.01</v>
-      </c>
-      <c r="G47">
-        <v>9.31</v>
-      </c>
-      <c r="H47" s="4">
-        <v>24921.41</v>
-      </c>
-      <c r="I47">
-        <v>5.76</v>
-      </c>
-      <c r="J47">
-        <v>43</v>
-      </c>
-      <c r="K47">
-        <v>43</v>
-      </c>
-      <c r="L47">
-        <v>101.1</v>
-      </c>
-      <c r="M47">
-        <v>6.76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A48" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B48" t="s">
-        <v>104</v>
-      </c>
-      <c r="C48" s="2">
-        <v>33900</v>
-      </c>
-      <c r="D48" s="3">
-        <v>8.8999999999999999E-3</v>
-      </c>
-      <c r="E48">
-        <v>9.39</v>
-      </c>
-      <c r="F48">
-        <v>10.74</v>
-      </c>
-      <c r="G48">
-        <v>9.73</v>
-      </c>
-      <c r="H48" s="4">
-        <v>48211.77</v>
-      </c>
-      <c r="I48">
-        <v>3.54</v>
-      </c>
-      <c r="J48">
-        <v>76</v>
-      </c>
-      <c r="K48">
-        <v>76</v>
-      </c>
-      <c r="L48">
-        <v>97.67</v>
-      </c>
-      <c r="M48">
-        <v>5.61</v>
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F81F81FD-1518-4FE2-8040-83A9C31DEA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D954F5A-D853-45D9-9F6C-DDFA62EFF73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{93006A8B-507B-4244-9C63-47DB8F437467}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{622B0009-7A1C-4A9B-BEF2-E5B4DCAA0069}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -355,7 +355,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -369,9 +369,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -687,7 +684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE03462F-EA1C-4D0C-BF56-C9F6057B17B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C96E9814-2D5D-4511-B2B4-FDECBB4D5262}">
   <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -753,10 +750,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>26100</v>
+        <v>23450</v>
       </c>
       <c r="D2" s="3">
-        <v>-3.6900000000000002E-2</v>
+        <v>-5.4399999999999997E-2</v>
       </c>
       <c r="E2">
         <v>7.52</v>
@@ -771,19 +768,19 @@
         <v>50396.34</v>
       </c>
       <c r="I2">
-        <v>4.21</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L2">
-        <v>98.86</v>
+        <v>90.94</v>
       </c>
       <c r="M2">
-        <v>-0.19</v>
+        <v>-9.81</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -794,10 +791,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>152100</v>
+        <v>150600</v>
       </c>
       <c r="D3" s="3">
-        <v>-1.6799999999999999E-2</v>
+        <v>-3.0300000000000001E-2</v>
       </c>
       <c r="E3">
         <v>12.92</v>
@@ -812,19 +809,19 @@
         <v>157169.68</v>
       </c>
       <c r="I3">
-        <v>4.47</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="J3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L3">
-        <v>91.81</v>
+        <v>93.87</v>
       </c>
       <c r="M3">
-        <v>-9.09</v>
+        <v>-9.82</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -835,10 +832,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>436500</v>
+        <v>444000</v>
       </c>
       <c r="D4" s="3">
-        <v>-3.6400000000000002E-2</v>
+        <v>-2.1999999999999999E-2</v>
       </c>
       <c r="E4">
         <v>13.09</v>
@@ -853,19 +850,19 @@
         <v>405451.96</v>
       </c>
       <c r="I4">
-        <v>4.3499999999999996</v>
+        <v>4.28</v>
       </c>
       <c r="J4">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K4">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L4">
-        <v>90.58</v>
+        <v>94.3</v>
       </c>
       <c r="M4">
-        <v>-8.59</v>
+        <v>-10.57</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -876,10 +873,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>46000</v>
+        <v>53400</v>
       </c>
       <c r="D5" s="3">
-        <v>-4.5600000000000002E-2</v>
+        <v>4.7100000000000003E-2</v>
       </c>
       <c r="E5">
         <v>5.22</v>
@@ -894,19 +891,19 @@
         <v>72566.75</v>
       </c>
       <c r="I5">
-        <v>4.3499999999999996</v>
+        <v>3.75</v>
       </c>
       <c r="J5">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K5">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L5">
-        <v>105.3</v>
+        <v>117.8</v>
       </c>
       <c r="M5">
-        <v>2.2200000000000002</v>
+        <v>35.19</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -917,10 +914,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>75000</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0</v>
+        <v>71400</v>
+      </c>
+      <c r="D6" s="3">
+        <v>-7.2700000000000001E-2</v>
       </c>
       <c r="E6">
         <v>4.05</v>
@@ -935,19 +932,19 @@
         <v>65679.45</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J6">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K6">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L6">
-        <v>96.09</v>
+        <v>92.47</v>
       </c>
       <c r="M6">
-        <v>-3.35</v>
+        <v>-9.39</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -958,10 +955,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>65100</v>
+        <v>64800</v>
       </c>
       <c r="D7" s="3">
-        <v>-7.2599999999999998E-2</v>
+        <v>-8.7300000000000003E-2</v>
       </c>
       <c r="E7">
         <v>2.89</v>
@@ -976,7 +973,7 @@
         <v>54191.72</v>
       </c>
       <c r="I7">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J7">
         <v>65</v>
@@ -985,10 +982,10 @@
         <v>65</v>
       </c>
       <c r="L7">
-        <v>98.54</v>
+        <v>96.91</v>
       </c>
       <c r="M7">
-        <v>-4.55</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -999,10 +996,10 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>8620</v>
+        <v>8500</v>
       </c>
       <c r="D8" s="3">
-        <v>-4.7500000000000001E-2</v>
+        <v>-2.63E-2</v>
       </c>
       <c r="E8">
         <v>2.84</v>
@@ -1017,19 +1014,19 @@
         <v>20859.37</v>
       </c>
       <c r="I8">
-        <v>2.5499999999999998</v>
+        <v>2.59</v>
       </c>
       <c r="J8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L8">
-        <v>93.5</v>
+        <v>94.67</v>
       </c>
       <c r="M8">
-        <v>-6.51</v>
+        <v>-9.86</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1040,10 +1037,10 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>37650</v>
+        <v>35100</v>
       </c>
       <c r="D9" s="3">
-        <v>-1.44E-2</v>
+        <v>-5.8999999999999997E-2</v>
       </c>
       <c r="E9">
         <v>4.57</v>
@@ -1058,19 +1055,19 @@
         <v>42814.52</v>
       </c>
       <c r="I9">
-        <v>3.19</v>
+        <v>3.42</v>
       </c>
       <c r="J9">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K9">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L9">
-        <v>95.11</v>
+        <v>90.76</v>
       </c>
       <c r="M9">
-        <v>-5.16</v>
+        <v>-12.25</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1081,10 +1078,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>85700</v>
+        <v>84800</v>
       </c>
       <c r="D10" s="3">
-        <v>-2.06E-2</v>
+        <v>-2.75E-2</v>
       </c>
       <c r="E10">
         <v>2.64</v>
@@ -1099,19 +1096,19 @@
         <v>184176.03</v>
       </c>
       <c r="I10">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="J10">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K10">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L10">
-        <v>92.8</v>
+        <v>94.67</v>
       </c>
       <c r="M10">
-        <v>-5.82</v>
+        <v>-9.7899999999999991</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1122,10 +1119,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>13170</v>
+        <v>12200</v>
       </c>
       <c r="D11" s="3">
-        <v>-1.35E-2</v>
+        <v>-2.01E-2</v>
       </c>
       <c r="E11">
         <v>9.44</v>
@@ -1140,19 +1137,19 @@
         <v>19219.419999999998</v>
       </c>
       <c r="I11">
-        <v>3.91</v>
+        <v>4.22</v>
       </c>
       <c r="J11">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K11">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="L11">
-        <v>100.06</v>
+        <v>93.57</v>
       </c>
       <c r="M11">
-        <v>0.15</v>
+        <v>-4.6100000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1163,10 +1160,10 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>9410</v>
+        <v>9050</v>
       </c>
       <c r="D12" s="3">
-        <v>-2.69E-2</v>
+        <v>-3.9300000000000002E-2</v>
       </c>
       <c r="E12">
         <v>8.2100000000000009</v>
@@ -1181,19 +1178,19 @@
         <v>22736.17</v>
       </c>
       <c r="I12">
-        <v>3.72</v>
+        <v>3.87</v>
       </c>
       <c r="J12">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K12">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L12">
-        <v>98.79</v>
+        <v>95.64</v>
       </c>
       <c r="M12">
-        <v>-0.32</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1204,10 +1201,10 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>475750</v>
+        <v>465500</v>
       </c>
       <c r="D13" s="3">
-        <v>-2.9100000000000001E-2</v>
+        <v>-4.6100000000000002E-2</v>
       </c>
       <c r="E13">
         <v>8.41</v>
@@ -1222,19 +1219,19 @@
         <v>436418.31</v>
       </c>
       <c r="I13">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="J13">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K13">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L13">
-        <v>90.39</v>
+        <v>92.21</v>
       </c>
       <c r="M13">
-        <v>-8.86</v>
+        <v>-15.82</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1245,10 +1242,10 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>169000</v>
+        <v>162200</v>
       </c>
       <c r="D14" s="3">
-        <v>-3.9199999999999999E-2</v>
+        <v>-3.4500000000000003E-2</v>
       </c>
       <c r="E14">
         <v>18.96</v>
@@ -1263,19 +1260,19 @@
         <v>144109.65</v>
       </c>
       <c r="I14">
-        <v>4.0199999999999996</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="J14">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K14">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="L14">
-        <v>92.78</v>
+        <v>90.88</v>
       </c>
       <c r="M14">
-        <v>-5.64</v>
+        <v>-13.91</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1286,10 +1283,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>33600</v>
+        <v>29750</v>
       </c>
       <c r="D15" s="3">
-        <v>1.0500000000000001E-2</v>
+        <v>-6.59E-2</v>
       </c>
       <c r="E15">
         <v>8.73</v>
@@ -1304,19 +1301,19 @@
         <v>24348.21</v>
       </c>
       <c r="I15">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="J15">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="K15">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="L15">
-        <v>102.52</v>
+        <v>91.73</v>
       </c>
       <c r="M15">
-        <v>3.7</v>
+        <v>-7.61</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1327,10 +1324,10 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>39400</v>
+        <v>37300</v>
       </c>
       <c r="D16" s="3">
-        <v>-4.48E-2</v>
+        <v>-8.3500000000000005E-2</v>
       </c>
       <c r="E16">
         <v>15.02</v>
@@ -1345,19 +1342,19 @@
         <v>34750.239999999998</v>
       </c>
       <c r="I16">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="J16">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="K16">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L16">
-        <v>121.28</v>
+        <v>106.02</v>
       </c>
       <c r="M16">
-        <v>10.06</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1368,10 +1365,10 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>217500</v>
+        <v>216000</v>
       </c>
       <c r="D17" s="3">
-        <v>-6.7999999999999996E-3</v>
+        <v>-0.04</v>
       </c>
       <c r="E17">
         <v>13.17</v>
@@ -1386,19 +1383,19 @@
         <v>207156.6</v>
       </c>
       <c r="I17">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J17">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K17">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L17">
-        <v>96.12</v>
+        <v>96.45</v>
       </c>
       <c r="M17">
-        <v>-3.33</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1409,10 +1406,10 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>123100</v>
+        <v>118000</v>
       </c>
       <c r="D18" s="3">
-        <v>-3.8300000000000001E-2</v>
+        <v>-3.6700000000000003E-2</v>
       </c>
       <c r="E18">
         <v>4.74</v>
@@ -1427,19 +1424,19 @@
         <v>215808.28</v>
       </c>
       <c r="I18">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="J18">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K18">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L18">
-        <v>97.31</v>
+        <v>95.25</v>
       </c>
       <c r="M18">
-        <v>0.16</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1450,10 +1447,10 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>95600</v>
+        <v>92600</v>
       </c>
       <c r="D19" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>-5.8900000000000001E-2</v>
       </c>
       <c r="E19">
         <v>12.89</v>
@@ -1468,19 +1465,19 @@
         <v>87743.72</v>
       </c>
       <c r="I19">
-        <v>3.66</v>
+        <v>3.78</v>
       </c>
       <c r="J19">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K19">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L19">
-        <v>98.88</v>
+        <v>96.3</v>
       </c>
       <c r="M19">
-        <v>-1.85</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1491,10 +1488,10 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>78500</v>
+        <v>77800</v>
       </c>
       <c r="D20" s="3">
-        <v>-1.8800000000000001E-2</v>
+        <v>-8.8999999999999999E-3</v>
       </c>
       <c r="E20">
         <v>3.33</v>
@@ -1509,19 +1506,19 @@
         <v>60299.05</v>
       </c>
       <c r="I20">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="J20">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K20">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L20">
-        <v>101.41</v>
+        <v>100.11</v>
       </c>
       <c r="M20">
-        <v>-1.51</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1532,10 +1529,10 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>84900</v>
+        <v>84600</v>
       </c>
       <c r="D21" s="3">
-        <v>-2.0799999999999999E-2</v>
+        <v>-3.5299999999999998E-2</v>
       </c>
       <c r="E21">
         <v>20.100000000000001</v>
@@ -1550,7 +1547,7 @@
         <v>37882.559999999998</v>
       </c>
       <c r="I21">
-        <v>16.5</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="J21">
         <v>69</v>
@@ -1559,10 +1556,10 @@
         <v>69</v>
       </c>
       <c r="L21">
-        <v>96.68</v>
+        <v>97.34</v>
       </c>
       <c r="M21">
-        <v>-2.5299999999999998</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1573,10 +1570,10 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>23150</v>
+        <v>21650</v>
       </c>
       <c r="D22" s="3">
-        <v>-1.0699999999999999E-2</v>
+        <v>-1.5900000000000001E-2</v>
       </c>
       <c r="E22">
         <v>8.06</v>
@@ -1591,19 +1588,19 @@
         <v>44443.18</v>
       </c>
       <c r="I22">
-        <v>4.5999999999999996</v>
+        <v>4.92</v>
       </c>
       <c r="J22">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K22">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L22">
-        <v>98.39</v>
+        <v>93.94</v>
       </c>
       <c r="M22">
-        <v>-0.22</v>
+        <v>-8.4600000000000009</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1614,10 +1611,10 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>53900</v>
+        <v>51600</v>
       </c>
       <c r="D23" s="3">
-        <v>-1.0999999999999999E-2</v>
+        <v>-3.0099999999999998E-2</v>
       </c>
       <c r="E23">
         <v>7.45</v>
@@ -1632,19 +1629,19 @@
         <v>79986.48</v>
       </c>
       <c r="I23">
-        <v>5.19</v>
+        <v>5.43</v>
       </c>
       <c r="J23">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K23">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L23">
-        <v>91.61</v>
+        <v>89.91</v>
       </c>
       <c r="M23">
-        <v>-8.02</v>
+        <v>-12.98</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1655,10 +1652,10 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>19670</v>
+        <v>18670</v>
       </c>
       <c r="D24" s="3">
-        <v>-8.0999999999999996E-3</v>
+        <v>-3.2099999999999997E-2</v>
       </c>
       <c r="E24">
         <v>13.7</v>
@@ -1673,19 +1670,19 @@
         <v>16125.49</v>
       </c>
       <c r="I24">
-        <v>6.25</v>
+        <v>6.59</v>
       </c>
       <c r="J24">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K24">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="L24">
-        <v>95.63</v>
+        <v>92.35</v>
       </c>
       <c r="M24">
-        <v>-5.43</v>
+        <v>-7.57</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1696,10 +1693,10 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>60200</v>
+        <v>59400</v>
       </c>
       <c r="D25" s="3">
-        <v>8.3999999999999995E-3</v>
+        <v>-3.2599999999999997E-2</v>
       </c>
       <c r="E25">
         <v>10.220000000000001</v>
@@ -1714,19 +1711,19 @@
         <v>71885.83</v>
       </c>
       <c r="I25">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="J25">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K25">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L25">
-        <v>100.65</v>
+        <v>99.06</v>
       </c>
       <c r="M25">
-        <v>0.33</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1737,10 +1734,10 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>15860</v>
+        <v>15500</v>
       </c>
       <c r="D26" s="3">
-        <v>-5.5999999999999999E-3</v>
+        <v>-8.9999999999999993E-3</v>
       </c>
       <c r="E26">
         <v>6.01</v>
@@ -1755,19 +1752,19 @@
         <v>20769.650000000001</v>
       </c>
       <c r="I26">
-        <v>4.16</v>
+        <v>4.26</v>
       </c>
       <c r="J26">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K26">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L26">
-        <v>103.06</v>
+        <v>100.7</v>
       </c>
       <c r="M26">
-        <v>0.38</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1778,10 +1775,10 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>218500</v>
+        <v>217000</v>
       </c>
       <c r="D27" s="3">
-        <v>-1.5800000000000002E-2</v>
+        <v>-4.41E-2</v>
       </c>
       <c r="E27">
         <v>4.66</v>
@@ -1796,19 +1793,19 @@
         <v>324173.33</v>
       </c>
       <c r="I27">
-        <v>2.4300000000000002</v>
+        <v>2.44</v>
       </c>
       <c r="J27">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K27">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L27">
-        <v>99.78</v>
+        <v>98.75</v>
       </c>
       <c r="M27">
-        <v>0.69</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1819,10 +1816,10 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>156500</v>
+        <v>154600</v>
       </c>
       <c r="D28" s="3">
-        <v>6.4000000000000003E-3</v>
+        <v>-3.3799999999999997E-2</v>
       </c>
       <c r="E28">
         <v>11.77</v>
@@ -1837,19 +1834,19 @@
         <v>85735.74</v>
       </c>
       <c r="I28">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="J28">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K28">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L28">
-        <v>100.38</v>
+        <v>99.2</v>
       </c>
       <c r="M28">
-        <v>0.64</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1860,10 +1857,10 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>18120</v>
+        <v>16780</v>
       </c>
       <c r="D29" s="3">
-        <v>-6.6E-3</v>
+        <v>-2.2100000000000002E-2</v>
       </c>
       <c r="E29">
         <v>8.11</v>
@@ -1878,19 +1875,19 @@
         <v>19583.27</v>
       </c>
       <c r="I29">
-        <v>5.24</v>
+        <v>5.66</v>
       </c>
       <c r="J29">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K29">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L29">
-        <v>100.18</v>
+        <v>93.81</v>
       </c>
       <c r="M29">
-        <v>0.11</v>
+        <v>-7.19</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1901,10 +1898,10 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>34850</v>
+        <v>34350</v>
       </c>
       <c r="D30" s="3">
-        <v>-3.1899999999999998E-2</v>
+        <v>-4.0500000000000001E-2</v>
       </c>
       <c r="E30">
         <v>1.23</v>
@@ -1919,19 +1916,19 @@
         <v>118301.94</v>
       </c>
       <c r="I30">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="J30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L30">
-        <v>95.46</v>
+        <v>95.97</v>
       </c>
       <c r="M30">
-        <v>0.14000000000000001</v>
+        <v>-6.91</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1942,10 +1939,10 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>91600</v>
+        <v>91700</v>
       </c>
       <c r="D31" s="3">
-        <v>-1.9300000000000001E-2</v>
+        <v>-1.7100000000000001E-2</v>
       </c>
       <c r="E31">
         <v>8.11</v>
@@ -1969,10 +1966,10 @@
         <v>79</v>
       </c>
       <c r="L31">
-        <v>99.23</v>
+        <v>99.89</v>
       </c>
       <c r="M31">
-        <v>0.44</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1983,10 +1980,10 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>214500</v>
+        <v>213500</v>
       </c>
       <c r="D32" s="3">
-        <v>-6.8999999999999999E-3</v>
+        <v>-4.6899999999999997E-2</v>
       </c>
       <c r="E32">
         <v>11.54</v>
@@ -2010,10 +2007,10 @@
         <v>66</v>
       </c>
       <c r="L32">
-        <v>95.03</v>
+        <v>96.3</v>
       </c>
       <c r="M32">
-        <v>-8.14</v>
+        <v>-7.17</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2024,10 +2021,10 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>66100</v>
+        <v>62800</v>
       </c>
       <c r="D33" s="3">
-        <v>-2.5100000000000001E-2</v>
+        <v>-6.5500000000000003E-2</v>
       </c>
       <c r="E33">
         <v>5.55</v>
@@ -2042,19 +2039,19 @@
         <v>155269.29999999999</v>
       </c>
       <c r="I33">
-        <v>4.54</v>
+        <v>4.78</v>
       </c>
       <c r="J33">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="K33">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L33">
-        <v>100.02</v>
+        <v>95.43</v>
       </c>
       <c r="M33">
-        <v>2.96</v>
+        <v>-4.2699999999999996</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2065,10 +2062,10 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>107400</v>
+        <v>110400</v>
       </c>
       <c r="D34" s="3">
-        <v>-1.29E-2</v>
+        <v>-2.1299999999999999E-2</v>
       </c>
       <c r="E34">
         <v>9.17</v>
@@ -2083,19 +2080,19 @@
         <v>162088.94</v>
       </c>
       <c r="I34">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="J34">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K34">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L34">
-        <v>96.84</v>
+        <v>100.39</v>
       </c>
       <c r="M34">
-        <v>-2.27</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2106,10 +2103,10 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>150700</v>
+        <v>146500</v>
       </c>
       <c r="D35" s="3">
-        <v>-9.9000000000000008E-3</v>
+        <v>-1.21E-2</v>
       </c>
       <c r="E35">
         <v>8.86</v>
@@ -2124,19 +2121,19 @@
         <v>160038.65</v>
       </c>
       <c r="I35">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="J35">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K35">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L35">
-        <v>100.6</v>
+        <v>98.29</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2147,10 +2144,10 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>18260</v>
+        <v>17630</v>
       </c>
       <c r="D36" s="3">
-        <v>-9.1999999999999998E-3</v>
+        <v>-3.2899999999999999E-2</v>
       </c>
       <c r="E36">
         <v>6.96</v>
@@ -2165,19 +2162,19 @@
         <v>34223.949999999997</v>
       </c>
       <c r="I36">
-        <v>3.56</v>
+        <v>3.69</v>
       </c>
       <c r="J36">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K36">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L36">
-        <v>98.66</v>
+        <v>96.2</v>
       </c>
       <c r="M36">
-        <v>-1.19</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2188,10 +2185,10 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>17250</v>
+        <v>16570</v>
       </c>
       <c r="D37" s="3">
-        <v>1.5900000000000001E-2</v>
+        <v>-3.5499999999999997E-2</v>
       </c>
       <c r="E37">
         <v>3.6</v>
@@ -2206,19 +2203,19 @@
         <v>38541.279999999999</v>
       </c>
       <c r="I37">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="J37">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K37">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L37">
-        <v>101.46</v>
+        <v>98.13</v>
       </c>
       <c r="M37">
-        <v>4.04</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2229,10 +2226,10 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>57000</v>
+        <v>53900</v>
       </c>
       <c r="D38" s="3">
-        <v>-7.0000000000000001E-3</v>
+        <v>-4.4299999999999999E-2</v>
       </c>
       <c r="E38">
         <v>9.39</v>
@@ -2247,19 +2244,19 @@
         <v>98085.37</v>
       </c>
       <c r="I38">
-        <v>4.04</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J38">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K38">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L38">
-        <v>97.25</v>
+        <v>95.15</v>
       </c>
       <c r="M38">
-        <v>1.24</v>
+        <v>-9.11</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2270,10 +2267,10 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>30950</v>
+        <v>28850</v>
       </c>
       <c r="D39" s="3">
-        <v>3.1699999999999999E-2</v>
+        <v>-5.4100000000000002E-2</v>
       </c>
       <c r="E39">
         <v>12.8</v>
@@ -2288,19 +2285,19 @@
         <v>31004.78</v>
       </c>
       <c r="I39">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="J39">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K39">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L39">
-        <v>103.13</v>
+        <v>96.31</v>
       </c>
       <c r="M39">
-        <v>5.09</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2311,10 +2308,10 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>11230</v>
+        <v>10450</v>
       </c>
       <c r="D40" s="3">
-        <v>-2.9399999999999999E-2</v>
+        <v>-4.1300000000000003E-2</v>
       </c>
       <c r="E40">
         <v>7.65</v>
@@ -2329,19 +2326,19 @@
         <v>30039.25</v>
       </c>
       <c r="I40">
-        <v>2.3199999999999998</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="J40">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K40">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="L40">
-        <v>93.96</v>
+        <v>89.49</v>
       </c>
       <c r="M40">
-        <v>-5.71</v>
+        <v>-11.52</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2352,10 +2349,10 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>49600</v>
+        <v>49150</v>
       </c>
       <c r="D41" s="3">
-        <v>-1.3899999999999999E-2</v>
+        <v>-3.2500000000000001E-2</v>
       </c>
       <c r="E41">
         <v>11.33</v>
@@ -2370,19 +2367,19 @@
         <v>59573.64</v>
       </c>
       <c r="I41">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J41">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K41">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L41">
-        <v>99.02</v>
+        <v>98.24</v>
       </c>
       <c r="M41">
-        <v>-1.78</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2393,10 +2390,10 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>18000</v>
+        <v>17620</v>
       </c>
       <c r="D42" s="3">
-        <v>-1.21E-2</v>
+        <v>-3.0800000000000001E-2</v>
       </c>
       <c r="E42">
         <v>8.8800000000000008</v>
@@ -2411,19 +2408,19 @@
         <v>26617.85</v>
       </c>
       <c r="I42">
-        <v>6.53</v>
+        <v>6.67</v>
       </c>
       <c r="J42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L42">
-        <v>93.76</v>
+        <v>93.22</v>
       </c>
       <c r="M42">
-        <v>-8.49</v>
+        <v>-8.6999999999999993</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2434,10 +2431,10 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>33050</v>
+        <v>32200</v>
       </c>
       <c r="D43" s="3">
-        <v>-4.4999999999999997E-3</v>
+        <v>-2.1299999999999999E-2</v>
       </c>
       <c r="E43">
         <v>9.39</v>
@@ -2452,19 +2449,19 @@
         <v>48211.77</v>
       </c>
       <c r="I43">
-        <v>3.63</v>
+        <v>3.73</v>
       </c>
       <c r="J43">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K43">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L43">
-        <v>100.1</v>
+        <v>98.52</v>
       </c>
       <c r="M43">
-        <v>1.38</v>
+        <v>-2.57</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D954F5A-D853-45D9-9F6C-DDFA62EFF73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08C57344-4C06-4D3F-8521-4323ED1307F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{622B0009-7A1C-4A9B-BEF2-E5B4DCAA0069}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9861FD74-9465-43D9-A02A-F26F4037D08C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -355,7 +355,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -369,6 +369,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -684,7 +687,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C96E9814-2D5D-4511-B2B4-FDECBB4D5262}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02BEEAD3-5D89-43D2-AD2A-2B09ED6DBA3E}">
   <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -750,10 +753,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>23450</v>
+        <v>25000</v>
       </c>
       <c r="D2" s="3">
-        <v>-5.4399999999999997E-2</v>
+        <v>-1.5699999999999999E-2</v>
       </c>
       <c r="E2">
         <v>7.52</v>
@@ -768,19 +771,19 @@
         <v>50396.34</v>
       </c>
       <c r="I2">
-        <v>4.6900000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K2">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="L2">
-        <v>90.94</v>
+        <v>99.88</v>
       </c>
       <c r="M2">
-        <v>-9.81</v>
+        <v>-4.21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -791,10 +794,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>150600</v>
+        <v>159200</v>
       </c>
       <c r="D3" s="3">
-        <v>-3.0300000000000001E-2</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="E3">
         <v>12.92</v>
@@ -809,19 +812,19 @@
         <v>157169.68</v>
       </c>
       <c r="I3">
-        <v>4.5199999999999996</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="L3">
-        <v>93.87</v>
+        <v>103.81</v>
       </c>
       <c r="M3">
-        <v>-9.82</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -832,37 +835,37 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>444000</v>
+        <v>480000</v>
       </c>
       <c r="D4" s="3">
-        <v>-2.1999999999999999E-2</v>
+        <v>-2.0400000000000001E-2</v>
       </c>
       <c r="E4">
-        <v>13.09</v>
+        <v>10.96</v>
       </c>
       <c r="F4">
-        <v>13.88</v>
+        <v>10.96</v>
       </c>
       <c r="G4">
-        <v>12.47</v>
+        <v>12.25</v>
       </c>
       <c r="H4" s="4">
-        <v>405451.96</v>
+        <v>457603.51</v>
       </c>
       <c r="I4">
-        <v>4.28</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="J4">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K4">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L4">
-        <v>94.3</v>
+        <v>103.67</v>
       </c>
       <c r="M4">
-        <v>-10.57</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -873,10 +876,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>53400</v>
+        <v>49550</v>
       </c>
       <c r="D5" s="3">
-        <v>4.7100000000000003E-2</v>
+        <v>-5.0000000000000001E-3</v>
       </c>
       <c r="E5">
         <v>5.22</v>
@@ -891,19 +894,19 @@
         <v>72566.75</v>
       </c>
       <c r="I5">
-        <v>3.75</v>
+        <v>4.04</v>
       </c>
       <c r="J5">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K5">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="L5">
-        <v>117.8</v>
+        <v>101.71</v>
       </c>
       <c r="M5">
-        <v>35.19</v>
+        <v>4.9800000000000004</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -914,37 +917,37 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>71400</v>
+        <v>76100</v>
       </c>
       <c r="D6" s="3">
-        <v>-7.2700000000000001E-2</v>
+        <v>-5.1999999999999998E-3</v>
       </c>
       <c r="E6">
-        <v>4.05</v>
+        <v>5.69</v>
       </c>
       <c r="F6">
-        <v>7.82</v>
+        <v>5.69</v>
       </c>
       <c r="G6">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="H6" s="4">
-        <v>65679.45</v>
+        <v>66692.75</v>
       </c>
       <c r="I6">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="J6">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K6">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L6">
-        <v>92.47</v>
+        <v>101.71</v>
       </c>
       <c r="M6">
-        <v>-9.39</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -955,10 +958,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>64800</v>
+        <v>75100</v>
       </c>
       <c r="D7" s="3">
-        <v>-8.7300000000000003E-2</v>
+        <v>6.5199999999999994E-2</v>
       </c>
       <c r="E7">
         <v>2.89</v>
@@ -973,19 +976,19 @@
         <v>54191.72</v>
       </c>
       <c r="I7">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="J7">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="K7">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="L7">
-        <v>96.91</v>
+        <v>110.9</v>
       </c>
       <c r="M7">
-        <v>4.68</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -996,37 +999,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>8500</v>
+        <v>9250</v>
       </c>
       <c r="D8" s="3">
-        <v>-2.63E-2</v>
+        <v>-1.18E-2</v>
       </c>
       <c r="E8">
-        <v>2.84</v>
+        <v>3.52</v>
       </c>
       <c r="F8">
-        <v>4.16</v>
+        <v>3.52</v>
       </c>
       <c r="G8">
-        <v>8.36</v>
+        <v>5.39</v>
       </c>
       <c r="H8" s="4">
-        <v>20859.37</v>
+        <v>21278.16</v>
       </c>
       <c r="I8">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="J8">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K8">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="L8">
-        <v>94.67</v>
+        <v>102.32</v>
       </c>
       <c r="M8">
-        <v>-9.86</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1037,37 +1040,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>35100</v>
+        <v>39100</v>
       </c>
       <c r="D9" s="3">
-        <v>-5.8999999999999997E-2</v>
+        <v>-2.5999999999999999E-3</v>
       </c>
       <c r="E9">
-        <v>4.57</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="F9">
-        <v>7.42</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="G9">
-        <v>4.55</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="H9" s="4">
-        <v>42814.52</v>
+        <v>45197.48</v>
       </c>
       <c r="I9">
-        <v>3.42</v>
+        <v>3.07</v>
       </c>
       <c r="J9">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="K9">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L9">
-        <v>90.76</v>
+        <v>104.25</v>
       </c>
       <c r="M9">
-        <v>-12.25</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1078,10 +1081,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>84800</v>
+        <v>94800</v>
       </c>
       <c r="D10" s="3">
-        <v>-2.75E-2</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="E10">
         <v>2.64</v>
@@ -1096,19 +1099,19 @@
         <v>184176.03</v>
       </c>
       <c r="I10">
-        <v>3.66</v>
+        <v>3.27</v>
       </c>
       <c r="J10">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="K10">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="L10">
-        <v>94.67</v>
+        <v>106.43</v>
       </c>
       <c r="M10">
-        <v>-9.7899999999999991</v>
+        <v>9.2200000000000006</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1119,37 +1122,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>12200</v>
+        <v>12310</v>
       </c>
       <c r="D11" s="3">
-        <v>-2.01E-2</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="E11">
-        <v>9.44</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F11">
-        <v>10.67</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="G11">
-        <v>9.86</v>
+        <v>9.33</v>
       </c>
       <c r="H11" s="4">
-        <v>19219.419999999998</v>
+        <v>19594.84</v>
       </c>
       <c r="I11">
-        <v>4.22</v>
+        <v>4.63</v>
       </c>
       <c r="J11">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K11">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L11">
-        <v>93.57</v>
+        <v>98.87</v>
       </c>
       <c r="M11">
-        <v>-4.6100000000000003</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1160,37 +1163,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>9050</v>
+        <v>11400</v>
       </c>
       <c r="D12" s="3">
-        <v>-3.9300000000000002E-2</v>
+        <v>-7.6899999999999996E-2</v>
       </c>
       <c r="E12">
-        <v>8.2100000000000009</v>
+        <v>4.49</v>
       </c>
       <c r="F12">
-        <v>3.26</v>
+        <v>4.49</v>
       </c>
       <c r="G12">
-        <v>5.34</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="H12" s="4">
-        <v>22736.17</v>
+        <v>23274.23</v>
       </c>
       <c r="I12">
-        <v>3.87</v>
+        <v>3.07</v>
       </c>
       <c r="J12">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="K12">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L12">
-        <v>95.64</v>
+        <v>113.4</v>
       </c>
       <c r="M12">
-        <v>-5.04</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1201,10 +1204,10 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>465500</v>
+        <v>538000</v>
       </c>
       <c r="D13" s="3">
-        <v>-4.6100000000000002E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="E13">
         <v>8.41</v>
@@ -1219,19 +1222,19 @@
         <v>436418.31</v>
       </c>
       <c r="I13">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="J13">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="K13">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="L13">
-        <v>92.21</v>
+        <v>110</v>
       </c>
       <c r="M13">
-        <v>-15.82</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1242,37 +1245,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>162200</v>
+        <v>173300</v>
       </c>
       <c r="D14" s="3">
-        <v>-3.4500000000000003E-2</v>
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="E14">
-        <v>18.96</v>
+        <v>17.72</v>
       </c>
       <c r="F14">
-        <v>19.43</v>
+        <v>17.72</v>
       </c>
       <c r="G14">
-        <v>18.8</v>
+        <v>17.440000000000001</v>
       </c>
       <c r="H14" s="4">
-        <v>144109.65</v>
+        <v>158606.49</v>
       </c>
       <c r="I14">
-        <v>4.1900000000000004</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="J14">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K14">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L14">
-        <v>90.88</v>
+        <v>102.13</v>
       </c>
       <c r="M14">
-        <v>-13.91</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1283,37 +1286,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>29750</v>
+        <v>35300</v>
       </c>
       <c r="D15" s="3">
-        <v>-6.59E-2</v>
+        <v>2.8E-3</v>
       </c>
       <c r="E15">
-        <v>8.73</v>
+        <v>11.76</v>
       </c>
       <c r="F15">
-        <v>11.57</v>
+        <v>11.76</v>
       </c>
       <c r="G15">
-        <v>6.85</v>
+        <v>9.33</v>
       </c>
       <c r="H15" s="4">
-        <v>24348.21</v>
+        <v>25179.95</v>
       </c>
       <c r="I15">
-        <v>3.19</v>
+        <v>3.68</v>
       </c>
       <c r="J15">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="K15">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="L15">
-        <v>91.73</v>
+        <v>107.48</v>
       </c>
       <c r="M15">
-        <v>-7.61</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1324,10 +1327,10 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>37300</v>
+        <v>39400</v>
       </c>
       <c r="D16" s="3">
-        <v>-8.3500000000000005E-2</v>
+        <v>5.4899999999999997E-2</v>
       </c>
       <c r="E16">
         <v>15.02</v>
@@ -1342,19 +1345,19 @@
         <v>34750.239999999998</v>
       </c>
       <c r="I16">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="J16">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K16">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="L16">
-        <v>106.02</v>
+        <v>104.79</v>
       </c>
       <c r="M16">
-        <v>48.61</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1365,37 +1368,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>216000</v>
+        <v>211000</v>
       </c>
       <c r="D17" s="3">
-        <v>-0.04</v>
+        <v>-2.0899999999999998E-2</v>
       </c>
       <c r="E17">
-        <v>13.17</v>
+        <v>12.83</v>
       </c>
       <c r="F17">
-        <v>11.69</v>
+        <v>12.83</v>
       </c>
       <c r="G17">
-        <v>18.010000000000002</v>
+        <v>14.29</v>
       </c>
       <c r="H17" s="4">
-        <v>207156.6</v>
+        <v>223707.87</v>
       </c>
       <c r="I17">
-        <v>2.48</v>
+        <v>3.12</v>
       </c>
       <c r="J17">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K17">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L17">
-        <v>96.45</v>
+        <v>97.73</v>
       </c>
       <c r="M17">
-        <v>-6.29</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1406,10 +1409,10 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>118000</v>
+        <v>137600</v>
       </c>
       <c r="D18" s="3">
-        <v>-3.6700000000000003E-2</v>
+        <v>-6.9999999999999999E-4</v>
       </c>
       <c r="E18">
         <v>4.74</v>
@@ -1424,19 +1427,19 @@
         <v>215808.28</v>
       </c>
       <c r="I18">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="J18">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K18">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L18">
-        <v>95.25</v>
+        <v>107.98</v>
       </c>
       <c r="M18">
-        <v>-3.67</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1447,37 +1450,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>92600</v>
+        <v>110000</v>
       </c>
       <c r="D19" s="3">
-        <v>-5.8900000000000001E-2</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="E19">
-        <v>12.89</v>
+        <v>13.09</v>
       </c>
       <c r="F19">
-        <v>13.94</v>
+        <v>13.09</v>
       </c>
       <c r="G19">
-        <v>9.44</v>
+        <v>11.51</v>
       </c>
       <c r="H19" s="4">
-        <v>87743.72</v>
+        <v>90347.77</v>
       </c>
       <c r="I19">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="J19">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="K19">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="L19">
-        <v>96.3</v>
+        <v>109.74</v>
       </c>
       <c r="M19">
-        <v>-3.44</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1488,10 +1491,10 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>77800</v>
+        <v>98300</v>
       </c>
       <c r="D20" s="3">
-        <v>-8.8999999999999999E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="E20">
         <v>3.33</v>
@@ -1506,19 +1509,19 @@
         <v>60299.05</v>
       </c>
       <c r="I20">
-        <v>2.13</v>
+        <v>1.69</v>
       </c>
       <c r="J20">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="K20">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="L20">
-        <v>100.11</v>
+        <v>115.61</v>
       </c>
       <c r="M20">
-        <v>1.7</v>
+        <v>32.479999999999997</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1529,10 +1532,10 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>84600</v>
+        <v>101800</v>
       </c>
       <c r="D21" s="3">
-        <v>-3.5299999999999998E-2</v>
+        <v>2.3099999999999999E-2</v>
       </c>
       <c r="E21">
         <v>20.100000000000001</v>
@@ -1547,19 +1550,19 @@
         <v>37882.559999999998</v>
       </c>
       <c r="I21">
-        <v>16.559999999999999</v>
+        <v>13.76</v>
       </c>
       <c r="J21">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="K21">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="L21">
-        <v>97.34</v>
+        <v>113.39</v>
       </c>
       <c r="M21">
-        <v>-2.76</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1570,37 +1573,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>21650</v>
+        <v>22550</v>
       </c>
       <c r="D22" s="3">
-        <v>-1.5900000000000001E-2</v>
+        <v>-1.3100000000000001E-2</v>
       </c>
       <c r="E22">
-        <v>8.06</v>
+        <v>7.7</v>
       </c>
       <c r="F22">
-        <v>8.64</v>
+        <v>7.7</v>
       </c>
       <c r="G22">
-        <v>8.77</v>
+        <v>8.18</v>
       </c>
       <c r="H22" s="4">
-        <v>44443.18</v>
+        <v>45715.519999999997</v>
       </c>
       <c r="I22">
-        <v>4.92</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="J22">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K22">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L22">
-        <v>93.94</v>
+        <v>101.01</v>
       </c>
       <c r="M22">
-        <v>-8.4600000000000009</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1611,10 +1614,10 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>51600</v>
+        <v>54400</v>
       </c>
       <c r="D23" s="3">
-        <v>-3.0099999999999998E-2</v>
+        <v>-5.4999999999999997E-3</v>
       </c>
       <c r="E23">
         <v>7.45</v>
@@ -1629,19 +1632,19 @@
         <v>79986.48</v>
       </c>
       <c r="I23">
-        <v>5.43</v>
+        <v>5.15</v>
       </c>
       <c r="J23">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K23">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="L23">
-        <v>89.91</v>
+        <v>100.06</v>
       </c>
       <c r="M23">
-        <v>-12.98</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1652,10 +1655,10 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>18670</v>
+        <v>19850</v>
       </c>
       <c r="D24" s="3">
-        <v>-3.2099999999999997E-2</v>
+        <v>1.5E-3</v>
       </c>
       <c r="E24">
         <v>13.7</v>
@@ -1670,19 +1673,19 @@
         <v>16125.49</v>
       </c>
       <c r="I24">
-        <v>6.59</v>
+        <v>6.2</v>
       </c>
       <c r="J24">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="K24">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="L24">
-        <v>92.35</v>
+        <v>101.6</v>
       </c>
       <c r="M24">
-        <v>-7.57</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1693,10 +1696,10 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>59400</v>
+        <v>63900</v>
       </c>
       <c r="D25" s="3">
-        <v>-3.2599999999999997E-2</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="E25">
         <v>10.220000000000001</v>
@@ -1711,19 +1714,19 @@
         <v>71885.83</v>
       </c>
       <c r="I25">
-        <v>4.04</v>
+        <v>3.76</v>
       </c>
       <c r="J25">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K25">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L25">
-        <v>99.06</v>
+        <v>104.61</v>
       </c>
       <c r="M25">
-        <v>0.68</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1734,10 +1737,10 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>15500</v>
+        <v>17600</v>
       </c>
       <c r="D26" s="3">
-        <v>-8.9999999999999993E-3</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="E26">
         <v>6.01</v>
@@ -1752,19 +1755,19 @@
         <v>20769.650000000001</v>
       </c>
       <c r="I26">
-        <v>4.26</v>
+        <v>3.75</v>
       </c>
       <c r="J26">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="K26">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="L26">
-        <v>100.7</v>
+        <v>108.78</v>
       </c>
       <c r="M26">
-        <v>2.72</v>
+        <v>16.329999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1775,10 +1778,10 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>217000</v>
+        <v>253500</v>
       </c>
       <c r="D27" s="3">
-        <v>-4.41E-2</v>
+        <v>-1.7399999999999999E-2</v>
       </c>
       <c r="E27">
         <v>4.66</v>
@@ -1793,19 +1796,19 @@
         <v>324173.33</v>
       </c>
       <c r="I27">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="J27">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="K27">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="L27">
-        <v>98.75</v>
+        <v>110.01</v>
       </c>
       <c r="M27">
-        <v>3.33</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1816,10 +1819,10 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>154600</v>
+        <v>171300</v>
       </c>
       <c r="D28" s="3">
-        <v>-3.3799999999999997E-2</v>
+        <v>1.8E-3</v>
       </c>
       <c r="E28">
         <v>11.77</v>
@@ -1834,19 +1837,19 @@
         <v>85735.74</v>
       </c>
       <c r="I28">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="J28">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="K28">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="L28">
-        <v>99.2</v>
+        <v>106.72</v>
       </c>
       <c r="M28">
-        <v>-0.06</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1857,10 +1860,10 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>16780</v>
+        <v>17090</v>
       </c>
       <c r="D29" s="3">
-        <v>-2.2100000000000002E-2</v>
+        <v>-2.8999999999999998E-3</v>
       </c>
       <c r="E29">
         <v>8.11</v>
@@ -1875,19 +1878,19 @@
         <v>19583.27</v>
       </c>
       <c r="I29">
-        <v>5.66</v>
+        <v>5.56</v>
       </c>
       <c r="J29">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K29">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L29">
-        <v>93.81</v>
+        <v>99.2</v>
       </c>
       <c r="M29">
-        <v>-7.19</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1898,10 +1901,10 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>34350</v>
+        <v>36700</v>
       </c>
       <c r="D30" s="3">
-        <v>-4.0500000000000001E-2</v>
+        <v>1.24E-2</v>
       </c>
       <c r="E30">
         <v>1.23</v>
@@ -1916,19 +1919,19 @@
         <v>118301.94</v>
       </c>
       <c r="I30">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="J30">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K30">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L30">
-        <v>95.97</v>
+        <v>102.77</v>
       </c>
       <c r="M30">
-        <v>-6.91</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1939,37 +1942,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>91700</v>
+        <v>99600</v>
       </c>
       <c r="D31" s="3">
-        <v>-1.7100000000000001E-2</v>
+        <v>-3.0000000000000001E-3</v>
       </c>
       <c r="E31">
-        <v>8.11</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="F31">
-        <v>10.44</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="G31">
-        <v>8.66</v>
+        <v>8.4</v>
       </c>
       <c r="H31" s="4">
-        <v>119742.76</v>
+        <v>120617.68</v>
       </c>
       <c r="I31">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="J31">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K31">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="L31">
-        <v>99.89</v>
+        <v>105.61</v>
       </c>
       <c r="M31">
-        <v>-0.11</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1980,37 +1983,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>213500</v>
-      </c>
-      <c r="D32" s="3">
-        <v>-4.6899999999999997E-2</v>
+        <v>257000</v>
+      </c>
+      <c r="D32" s="5">
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>11.54</v>
+        <v>18.66</v>
       </c>
       <c r="F32">
-        <v>20.98</v>
+        <v>18.66</v>
       </c>
       <c r="G32">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="H32" s="4">
-        <v>189057.03</v>
+        <v>195836.08</v>
       </c>
       <c r="I32">
-        <v>1.86</v>
+        <v>3.38</v>
       </c>
       <c r="J32">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="K32">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="L32">
-        <v>96.3</v>
+        <v>112.88</v>
       </c>
       <c r="M32">
-        <v>-7.17</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2021,10 +2024,10 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>62800</v>
+        <v>71900</v>
       </c>
       <c r="D33" s="3">
-        <v>-6.5500000000000003E-2</v>
+        <v>-1.5100000000000001E-2</v>
       </c>
       <c r="E33">
         <v>5.55</v>
@@ -2039,19 +2042,19 @@
         <v>155269.29999999999</v>
       </c>
       <c r="I33">
-        <v>4.78</v>
+        <v>4.17</v>
       </c>
       <c r="J33">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="K33">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L33">
-        <v>95.43</v>
+        <v>105.36</v>
       </c>
       <c r="M33">
-        <v>-4.2699999999999996</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2062,10 +2065,10 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>110400</v>
+        <v>123500</v>
       </c>
       <c r="D34" s="3">
-        <v>-2.1299999999999999E-2</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="E34">
         <v>9.17</v>
@@ -2080,19 +2083,19 @@
         <v>162088.94</v>
       </c>
       <c r="I34">
-        <v>3.72</v>
+        <v>3.32</v>
       </c>
       <c r="J34">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K34">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L34">
-        <v>100.39</v>
+        <v>108.7</v>
       </c>
       <c r="M34">
-        <v>0.09</v>
+        <v>16.510000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2103,37 +2106,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>146500</v>
-      </c>
-      <c r="D35" s="3">
-        <v>-1.21E-2</v>
+        <v>162300</v>
+      </c>
+      <c r="D35" s="5">
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>8.86</v>
+        <v>9.98</v>
       </c>
       <c r="F35">
-        <v>11.63</v>
+        <v>9.98</v>
       </c>
       <c r="G35">
-        <v>8.51</v>
+        <v>9.08</v>
       </c>
       <c r="H35" s="4">
-        <v>160038.65</v>
+        <v>159779.29999999999</v>
       </c>
       <c r="I35">
-        <v>2.17</v>
+        <v>2.69</v>
       </c>
       <c r="J35">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K35">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="L35">
-        <v>98.29</v>
+        <v>107.04</v>
       </c>
       <c r="M35">
-        <v>-0.61</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2144,37 +2147,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>17630</v>
+        <v>19160</v>
       </c>
       <c r="D36" s="3">
-        <v>-3.2899999999999999E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="E36">
-        <v>6.96</v>
+        <v>7.58</v>
       </c>
       <c r="F36">
-        <v>9.58</v>
+        <v>7.58</v>
       </c>
       <c r="G36">
-        <v>7.18</v>
+        <v>6.97</v>
       </c>
       <c r="H36" s="4">
-        <v>34223.949999999997</v>
+        <v>34779.699999999997</v>
       </c>
       <c r="I36">
-        <v>3.69</v>
+        <v>3.84</v>
       </c>
       <c r="J36">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="K36">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="L36">
-        <v>96.2</v>
+        <v>105.43</v>
       </c>
       <c r="M36">
-        <v>-4.29</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2185,37 +2188,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>16570</v>
+        <v>18700</v>
       </c>
       <c r="D37" s="3">
-        <v>-3.5499999999999997E-2</v>
+        <v>-5.0000000000000001E-4</v>
       </c>
       <c r="E37">
-        <v>3.6</v>
+        <v>7.27</v>
       </c>
       <c r="F37">
-        <v>9.42</v>
+        <v>7.27</v>
       </c>
       <c r="G37">
-        <v>5.91</v>
+        <v>5.87</v>
       </c>
       <c r="H37" s="4">
-        <v>38541.279999999999</v>
+        <v>38724.660000000003</v>
       </c>
       <c r="I37">
-        <v>3.02</v>
+        <v>3.74</v>
       </c>
       <c r="J37">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="K37">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="L37">
-        <v>98.13</v>
+        <v>108</v>
       </c>
       <c r="M37">
-        <v>-2.82</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2226,10 +2229,10 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>53900</v>
+        <v>59500</v>
       </c>
       <c r="D38" s="3">
-        <v>-4.4299999999999999E-2</v>
+        <v>-1.49E-2</v>
       </c>
       <c r="E38">
         <v>9.39</v>
@@ -2244,19 +2247,19 @@
         <v>98085.37</v>
       </c>
       <c r="I38">
-        <v>4.2699999999999996</v>
+        <v>3.87</v>
       </c>
       <c r="J38">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K38">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L38">
-        <v>95.15</v>
+        <v>103.04</v>
       </c>
       <c r="M38">
-        <v>-9.11</v>
+        <v>9.7799999999999994</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2267,37 +2270,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>28850</v>
+        <v>31000</v>
       </c>
       <c r="D39" s="3">
-        <v>-5.4100000000000002E-2</v>
+        <v>-1.6000000000000001E-3</v>
       </c>
       <c r="E39">
-        <v>12.8</v>
+        <v>12.36</v>
       </c>
       <c r="F39">
-        <v>13.49</v>
+        <v>12.36</v>
       </c>
       <c r="G39">
-        <v>12.93</v>
+        <v>12.46</v>
       </c>
       <c r="H39" s="4">
-        <v>31004.78</v>
+        <v>31515.31</v>
       </c>
       <c r="I39">
-        <v>3.45</v>
+        <v>3.68</v>
       </c>
       <c r="J39">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K39">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L39">
-        <v>96.31</v>
+        <v>102.99</v>
       </c>
       <c r="M39">
-        <v>-1.87</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2308,37 +2311,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>10450</v>
+        <v>11790</v>
       </c>
       <c r="D40" s="3">
-        <v>-4.1300000000000003E-2</v>
+        <v>-1.26E-2</v>
       </c>
       <c r="E40">
-        <v>7.65</v>
+        <v>1.55</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="G40">
-        <v>7.8</v>
+        <v>6.05</v>
       </c>
       <c r="H40" s="4">
-        <v>30039.25</v>
+        <v>29736.69</v>
       </c>
       <c r="I40">
-        <v>2.4900000000000002</v>
+        <v>2.12</v>
       </c>
       <c r="J40">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K40">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L40">
-        <v>89.49</v>
+        <v>104.85</v>
       </c>
       <c r="M40">
-        <v>-11.52</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2349,10 +2352,10 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>49150</v>
+        <v>52200</v>
       </c>
       <c r="D41" s="3">
-        <v>-3.2500000000000001E-2</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="E41">
         <v>11.33</v>
@@ -2367,19 +2370,19 @@
         <v>59573.64</v>
       </c>
       <c r="I41">
-        <v>2.44</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J41">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K41">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L41">
-        <v>98.24</v>
+        <v>104.96</v>
       </c>
       <c r="M41">
-        <v>-1.7</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2390,10 +2393,10 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>17620</v>
+        <v>18720</v>
       </c>
       <c r="D42" s="3">
-        <v>-3.0800000000000001E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="E42">
         <v>8.8800000000000008</v>
@@ -2408,19 +2411,19 @@
         <v>26617.85</v>
       </c>
       <c r="I42">
-        <v>6.67</v>
+        <v>6.28</v>
       </c>
       <c r="J42">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K42">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L42">
-        <v>93.22</v>
+        <v>102.86</v>
       </c>
       <c r="M42">
-        <v>-8.6999999999999993</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2431,37 +2434,37 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>32200</v>
+        <v>35700</v>
       </c>
       <c r="D43" s="3">
-        <v>-2.1299999999999999E-2</v>
+        <v>1.4E-3</v>
       </c>
       <c r="E43">
-        <v>9.39</v>
+        <v>8.91</v>
       </c>
       <c r="F43">
-        <v>10.74</v>
+        <v>8.91</v>
       </c>
       <c r="G43">
-        <v>9.73</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="H43" s="4">
-        <v>48211.77</v>
+        <v>49113.23</v>
       </c>
       <c r="I43">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="J43">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="K43">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="L43">
-        <v>98.52</v>
+        <v>107.19</v>
       </c>
       <c r="M43">
-        <v>-2.57</v>
+        <v>12.62</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08C57344-4C06-4D3F-8521-4323ED1307F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D16EEE35-4E67-413A-8861-A15E330D3865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9861FD74-9465-43D9-A02A-F26F4037D08C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B2638EA5-1A6B-422F-9879-EE2F92052D7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -687,7 +687,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02BEEAD3-5D89-43D2-AD2A-2B09ED6DBA3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC00A692-FB56-4996-8526-8C97612DC0C9}">
   <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -753,10 +753,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>25000</v>
+        <v>24850</v>
       </c>
       <c r="D2" s="3">
-        <v>-1.5699999999999999E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E2">
         <v>7.52</v>
@@ -771,7 +771,7 @@
         <v>50396.34</v>
       </c>
       <c r="I2">
-        <v>4.4000000000000004</v>
+        <v>4.43</v>
       </c>
       <c r="J2">
         <v>56</v>
@@ -780,10 +780,10 @@
         <v>56</v>
       </c>
       <c r="L2">
-        <v>99.88</v>
+        <v>99.63</v>
       </c>
       <c r="M2">
-        <v>-4.21</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -794,10 +794,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>159200</v>
+        <v>152600</v>
       </c>
       <c r="D3" s="3">
-        <v>8.2000000000000007E-3</v>
+        <v>-5.1999999999999998E-3</v>
       </c>
       <c r="E3">
         <v>12.92</v>
@@ -812,19 +812,19 @@
         <v>157169.68</v>
       </c>
       <c r="I3">
-        <v>4.2699999999999996</v>
+        <v>4.46</v>
       </c>
       <c r="J3">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K3">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L3">
-        <v>103.81</v>
+        <v>99.16</v>
       </c>
       <c r="M3">
-        <v>-1.55</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -835,10 +835,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>480000</v>
+        <v>461000</v>
       </c>
       <c r="D4" s="3">
-        <v>-2.0400000000000001E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="E4">
         <v>10.96</v>
@@ -853,19 +853,19 @@
         <v>457603.51</v>
       </c>
       <c r="I4">
-        <v>4.0599999999999996</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="J4">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K4">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L4">
-        <v>103.67</v>
+        <v>99.44</v>
       </c>
       <c r="M4">
-        <v>5.38</v>
+        <v>4.6500000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -876,10 +876,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>49550</v>
+        <v>54900</v>
       </c>
       <c r="D5" s="3">
-        <v>-5.0000000000000001E-3</v>
+        <v>2.4299999999999999E-2</v>
       </c>
       <c r="E5">
         <v>5.22</v>
@@ -894,19 +894,19 @@
         <v>72566.75</v>
       </c>
       <c r="I5">
-        <v>4.04</v>
+        <v>3.64</v>
       </c>
       <c r="J5">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="K5">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L5">
-        <v>101.71</v>
+        <v>110.42</v>
       </c>
       <c r="M5">
-        <v>4.9800000000000004</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -917,10 +917,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>76100</v>
+        <v>74600</v>
       </c>
       <c r="D6" s="3">
-        <v>-5.1999999999999998E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E6">
         <v>5.69</v>
@@ -935,19 +935,19 @@
         <v>66692.75</v>
       </c>
       <c r="I6">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="J6">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K6">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L6">
-        <v>101.71</v>
+        <v>99.57</v>
       </c>
       <c r="M6">
-        <v>3.12</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -958,10 +958,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>75100</v>
+        <v>72500</v>
       </c>
       <c r="D7" s="3">
-        <v>6.5199999999999994E-2</v>
+        <v>1.9699999999999999E-2</v>
       </c>
       <c r="E7">
         <v>2.89</v>
@@ -976,19 +976,19 @@
         <v>54191.72</v>
       </c>
       <c r="I7">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="J7">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K7">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L7">
-        <v>110.9</v>
+        <v>105.38</v>
       </c>
       <c r="M7">
-        <v>24.34</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -999,10 +999,10 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>9250</v>
+        <v>9110</v>
       </c>
       <c r="D8" s="3">
-        <v>-1.18E-2</v>
+        <v>-3.09E-2</v>
       </c>
       <c r="E8">
         <v>3.52</v>
@@ -1017,19 +1017,19 @@
         <v>21278.16</v>
       </c>
       <c r="I8">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L8">
-        <v>102.32</v>
+        <v>99.88</v>
       </c>
       <c r="M8">
-        <v>8.57</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1040,10 +1040,10 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>39100</v>
+        <v>39300</v>
       </c>
       <c r="D9" s="3">
-        <v>-2.5999999999999999E-3</v>
+        <v>1.29E-2</v>
       </c>
       <c r="E9">
         <v>5.0599999999999996</v>
@@ -1058,7 +1058,7 @@
         <v>45197.48</v>
       </c>
       <c r="I9">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="J9">
         <v>69</v>
@@ -1067,10 +1067,10 @@
         <v>69</v>
       </c>
       <c r="L9">
-        <v>104.25</v>
+        <v>103.85</v>
       </c>
       <c r="M9">
-        <v>2.62</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1081,10 +1081,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>94800</v>
+        <v>95500</v>
       </c>
       <c r="D10" s="3">
-        <v>1.0699999999999999E-2</v>
+        <v>-5.1999999999999998E-3</v>
       </c>
       <c r="E10">
         <v>2.64</v>
@@ -1099,19 +1099,19 @@
         <v>184176.03</v>
       </c>
       <c r="I10">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="J10">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K10">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L10">
-        <v>106.43</v>
+        <v>105.28</v>
       </c>
       <c r="M10">
-        <v>9.2200000000000006</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1122,10 +1122,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>12310</v>
+        <v>12290</v>
       </c>
       <c r="D11" s="3">
-        <v>1.0699999999999999E-2</v>
+        <v>-5.7000000000000002E-3</v>
       </c>
       <c r="E11">
         <v>9.0299999999999994</v>
@@ -1140,7 +1140,7 @@
         <v>19594.84</v>
       </c>
       <c r="I11">
-        <v>4.63</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="J11">
         <v>72</v>
@@ -1149,10 +1149,10 @@
         <v>72</v>
       </c>
       <c r="L11">
-        <v>98.87</v>
+        <v>99.1</v>
       </c>
       <c r="M11">
-        <v>-4.57</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1163,10 +1163,10 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>11400</v>
+        <v>11790</v>
       </c>
       <c r="D12" s="3">
-        <v>-7.6899999999999996E-2</v>
+        <v>6.2199999999999998E-2</v>
       </c>
       <c r="E12">
         <v>4.49</v>
@@ -1181,19 +1181,19 @@
         <v>23274.23</v>
       </c>
       <c r="I12">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K12">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L12">
-        <v>113.4</v>
+        <v>113.66</v>
       </c>
       <c r="M12">
-        <v>15.62</v>
+        <v>32.03</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1204,10 +1204,10 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>538000</v>
+        <v>524000</v>
       </c>
       <c r="D13" s="3">
-        <v>7.4999999999999997E-3</v>
+        <v>2.1399999999999999E-2</v>
       </c>
       <c r="E13">
         <v>8.41</v>
@@ -1222,19 +1222,19 @@
         <v>436418.31</v>
       </c>
       <c r="I13">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="J13">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K13">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L13">
-        <v>110</v>
+        <v>104.97</v>
       </c>
       <c r="M13">
-        <v>10.93</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1245,10 +1245,10 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>173300</v>
+        <v>171300</v>
       </c>
       <c r="D14" s="3">
-        <v>1.9400000000000001E-2</v>
+        <v>-2.1100000000000001E-2</v>
       </c>
       <c r="E14">
         <v>17.72</v>
@@ -1263,19 +1263,19 @@
         <v>158606.49</v>
       </c>
       <c r="I14">
-        <v>4.3899999999999997</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="J14">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K14">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L14">
-        <v>102.13</v>
+        <v>100.71</v>
       </c>
       <c r="M14">
-        <v>-1.98</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1286,10 +1286,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>35300</v>
+        <v>35250</v>
       </c>
       <c r="D15" s="3">
-        <v>2.8E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="E15">
         <v>11.76</v>
@@ -1304,7 +1304,7 @@
         <v>25179.95</v>
       </c>
       <c r="I15">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="J15">
         <v>79</v>
@@ -1313,10 +1313,10 @@
         <v>79</v>
       </c>
       <c r="L15">
-        <v>107.48</v>
+        <v>105.39</v>
       </c>
       <c r="M15">
-        <v>7.95</v>
+        <v>19.09</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1327,10 +1327,10 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>39400</v>
+        <v>41300</v>
       </c>
       <c r="D16" s="3">
-        <v>5.4899999999999997E-2</v>
+        <v>-3.8399999999999997E-2</v>
       </c>
       <c r="E16">
         <v>15.02</v>
@@ -1345,19 +1345,19 @@
         <v>34750.239999999998</v>
       </c>
       <c r="I16">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="J16">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K16">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L16">
-        <v>104.79</v>
+        <v>107.57</v>
       </c>
       <c r="M16">
-        <v>4.37</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1368,10 +1368,10 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>211000</v>
+        <v>209000</v>
       </c>
       <c r="D17" s="3">
-        <v>-2.0899999999999998E-2</v>
+        <v>-9.4999999999999998E-3</v>
       </c>
       <c r="E17">
         <v>12.83</v>
@@ -1386,19 +1386,19 @@
         <v>223707.87</v>
       </c>
       <c r="I17">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="J17">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K17">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L17">
-        <v>97.73</v>
+        <v>97.22</v>
       </c>
       <c r="M17">
-        <v>-2.31</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1409,10 +1409,10 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>137600</v>
+        <v>132200</v>
       </c>
       <c r="D18" s="3">
-        <v>-6.9999999999999999E-4</v>
+        <v>-8.9999999999999993E-3</v>
       </c>
       <c r="E18">
         <v>4.74</v>
@@ -1427,19 +1427,19 @@
         <v>215808.28</v>
       </c>
       <c r="I18">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="J18">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K18">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L18">
-        <v>107.98</v>
+        <v>102.17</v>
       </c>
       <c r="M18">
-        <v>8.69</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1450,10 +1450,10 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>110000</v>
+        <v>112700</v>
       </c>
       <c r="D19" s="3">
-        <v>-5.4000000000000003E-3</v>
+        <v>9.9000000000000008E-3</v>
       </c>
       <c r="E19">
         <v>13.09</v>
@@ -1468,19 +1468,19 @@
         <v>90347.77</v>
       </c>
       <c r="I19">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="J19">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K19">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L19">
-        <v>109.74</v>
+        <v>109.39</v>
       </c>
       <c r="M19">
-        <v>16.77</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1491,10 +1491,10 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>98300</v>
+        <v>98000</v>
       </c>
       <c r="D20" s="3">
-        <v>2.5000000000000001E-2</v>
+        <v>-0.02</v>
       </c>
       <c r="E20">
         <v>3.33</v>
@@ -1509,19 +1509,19 @@
         <v>60299.05</v>
       </c>
       <c r="I20">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J20">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K20">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L20">
-        <v>115.61</v>
+        <v>110.34</v>
       </c>
       <c r="M20">
-        <v>32.479999999999997</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1532,10 +1532,10 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>101800</v>
+        <v>98600</v>
       </c>
       <c r="D21" s="3">
-        <v>2.3099999999999999E-2</v>
+        <v>2.3900000000000001E-2</v>
       </c>
       <c r="E21">
         <v>20.100000000000001</v>
@@ -1550,19 +1550,19 @@
         <v>37882.559999999998</v>
       </c>
       <c r="I21">
-        <v>13.76</v>
+        <v>14.25</v>
       </c>
       <c r="J21">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K21">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L21">
-        <v>113.39</v>
+        <v>107.03</v>
       </c>
       <c r="M21">
-        <v>20.9</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1573,10 +1573,10 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>22550</v>
+        <v>22200</v>
       </c>
       <c r="D22" s="3">
-        <v>-1.3100000000000001E-2</v>
+        <v>-6.7000000000000002E-3</v>
       </c>
       <c r="E22">
         <v>7.7</v>
@@ -1591,19 +1591,19 @@
         <v>45715.519999999997</v>
       </c>
       <c r="I22">
-        <v>4.6500000000000004</v>
+        <v>4.72</v>
       </c>
       <c r="J22">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K22">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L22">
-        <v>101.01</v>
+        <v>99.5</v>
       </c>
       <c r="M22">
-        <v>-2.17</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1614,10 +1614,10 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>54400</v>
+        <v>53000</v>
       </c>
       <c r="D23" s="3">
-        <v>-5.4999999999999997E-3</v>
+        <v>-1.49E-2</v>
       </c>
       <c r="E23">
         <v>7.45</v>
@@ -1632,19 +1632,19 @@
         <v>79986.48</v>
       </c>
       <c r="I23">
-        <v>5.15</v>
+        <v>5.28</v>
       </c>
       <c r="J23">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K23">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L23">
-        <v>100.06</v>
+        <v>97.99</v>
       </c>
       <c r="M23">
-        <v>-7.8</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1655,10 +1655,10 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>19850</v>
-      </c>
-      <c r="D24" s="3">
-        <v>1.5E-3</v>
+        <v>19750</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0</v>
       </c>
       <c r="E24">
         <v>13.7</v>
@@ -1673,19 +1673,19 @@
         <v>16125.49</v>
       </c>
       <c r="I24">
-        <v>6.2</v>
+        <v>6.23</v>
       </c>
       <c r="J24">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K24">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L24">
-        <v>101.6</v>
+        <v>100.92</v>
       </c>
       <c r="M24">
-        <v>-2.46</v>
+        <v>4.1100000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1696,10 +1696,10 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>63900</v>
+        <v>61100</v>
       </c>
       <c r="D25" s="3">
-        <v>4.7000000000000002E-3</v>
+        <v>-9.7000000000000003E-3</v>
       </c>
       <c r="E25">
         <v>10.220000000000001</v>
@@ -1714,19 +1714,19 @@
         <v>71885.83</v>
       </c>
       <c r="I25">
-        <v>3.76</v>
+        <v>3.92</v>
       </c>
       <c r="J25">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K25">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="L25">
-        <v>104.61</v>
+        <v>99.45</v>
       </c>
       <c r="M25">
-        <v>10.55</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1737,10 +1737,10 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>17600</v>
+        <v>16430</v>
       </c>
       <c r="D26" s="3">
-        <v>2.7400000000000001E-2</v>
+        <v>-1.0200000000000001E-2</v>
       </c>
       <c r="E26">
         <v>6.01</v>
@@ -1755,19 +1755,19 @@
         <v>20769.650000000001</v>
       </c>
       <c r="I26">
-        <v>3.75</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J26">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K26">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L26">
-        <v>108.78</v>
+        <v>100.23</v>
       </c>
       <c r="M26">
-        <v>16.329999999999998</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1778,10 +1778,10 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>253500</v>
+        <v>250000</v>
       </c>
       <c r="D27" s="3">
-        <v>-1.7399999999999999E-2</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="E27">
         <v>4.66</v>
@@ -1796,19 +1796,19 @@
         <v>324173.33</v>
       </c>
       <c r="I27">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="J27">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K27">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L27">
-        <v>110.01</v>
+        <v>105.97</v>
       </c>
       <c r="M27">
-        <v>16.55</v>
+        <v>18.760000000000002</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1819,10 +1819,10 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>171300</v>
+        <v>177800</v>
       </c>
       <c r="D28" s="3">
-        <v>1.8E-3</v>
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="E28">
         <v>11.77</v>
@@ -1837,19 +1837,19 @@
         <v>85735.74</v>
       </c>
       <c r="I28">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="J28">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K28">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L28">
-        <v>106.72</v>
+        <v>108.44</v>
       </c>
       <c r="M28">
-        <v>12.85</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1860,10 +1860,10 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>17090</v>
+        <v>17160</v>
       </c>
       <c r="D29" s="3">
-        <v>-2.8999999999999998E-3</v>
+        <v>1.24E-2</v>
       </c>
       <c r="E29">
         <v>8.11</v>
@@ -1878,7 +1878,7 @@
         <v>19583.27</v>
       </c>
       <c r="I29">
-        <v>5.56</v>
+        <v>5.54</v>
       </c>
       <c r="J29">
         <v>23</v>
@@ -1887,10 +1887,10 @@
         <v>23</v>
       </c>
       <c r="L29">
-        <v>99.2</v>
+        <v>100.16</v>
       </c>
       <c r="M29">
-        <v>-3.88</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1901,10 +1901,10 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>36700</v>
+        <v>38300</v>
       </c>
       <c r="D30" s="3">
-        <v>1.24E-2</v>
+        <v>-2.5999999999999999E-3</v>
       </c>
       <c r="E30">
         <v>1.23</v>
@@ -1919,19 +1919,19 @@
         <v>118301.94</v>
       </c>
       <c r="I30">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="J30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L30">
-        <v>102.77</v>
+        <v>106</v>
       </c>
       <c r="M30">
-        <v>3.38</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1942,7 +1942,7 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>99600</v>
+        <v>99700</v>
       </c>
       <c r="D31" s="3">
         <v>-3.0000000000000001E-3</v>
@@ -1969,10 +1969,10 @@
         <v>90</v>
       </c>
       <c r="L31">
-        <v>105.61</v>
+        <v>104.11</v>
       </c>
       <c r="M31">
-        <v>10.79</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1983,10 +1983,10 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>257000</v>
-      </c>
-      <c r="D32" s="5">
-        <v>0</v>
+        <v>260500</v>
+      </c>
+      <c r="D32" s="3">
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="E32">
         <v>18.66</v>
@@ -2001,19 +2001,19 @@
         <v>195836.08</v>
       </c>
       <c r="I32">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="J32">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K32">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L32">
-        <v>112.88</v>
+        <v>110.34</v>
       </c>
       <c r="M32">
-        <v>21.8</v>
+        <v>28.64</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2024,10 +2024,10 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>71900</v>
+        <v>76500</v>
       </c>
       <c r="D33" s="3">
-        <v>-1.5100000000000001E-2</v>
+        <v>1.06E-2</v>
       </c>
       <c r="E33">
         <v>5.55</v>
@@ -2042,19 +2042,19 @@
         <v>155269.29999999999</v>
       </c>
       <c r="I33">
-        <v>4.17</v>
+        <v>3.92</v>
       </c>
       <c r="J33">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K33">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L33">
-        <v>105.36</v>
+        <v>109.84</v>
       </c>
       <c r="M33">
-        <v>10.11</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2065,10 +2065,10 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>123500</v>
+        <v>124000</v>
       </c>
       <c r="D34" s="3">
-        <v>8.2000000000000007E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="E34">
         <v>9.17</v>
@@ -2083,7 +2083,7 @@
         <v>162088.94</v>
       </c>
       <c r="I34">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="J34">
         <v>90</v>
@@ -2092,10 +2092,10 @@
         <v>90</v>
       </c>
       <c r="L34">
-        <v>108.7</v>
+        <v>106.91</v>
       </c>
       <c r="M34">
-        <v>16.510000000000002</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2106,7 +2106,7 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>162300</v>
+        <v>157400</v>
       </c>
       <c r="D35" s="5">
         <v>0</v>
@@ -2124,19 +2124,19 @@
         <v>159779.29999999999</v>
       </c>
       <c r="I35">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="J35">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K35">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L35">
-        <v>107.04</v>
+        <v>102.51</v>
       </c>
       <c r="M35">
-        <v>11.7</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2147,10 +2147,10 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>19160</v>
+        <v>18740</v>
       </c>
       <c r="D36" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>-1.37E-2</v>
       </c>
       <c r="E36">
         <v>7.58</v>
@@ -2165,19 +2165,19 @@
         <v>34779.699999999997</v>
       </c>
       <c r="I36">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="J36">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K36">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L36">
-        <v>105.43</v>
+        <v>102.03</v>
       </c>
       <c r="M36">
-        <v>8.19</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2188,10 +2188,10 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>18700</v>
+        <v>19020</v>
       </c>
       <c r="D37" s="3">
-        <v>-5.0000000000000001E-4</v>
+        <v>-4.1999999999999997E-3</v>
       </c>
       <c r="E37">
         <v>7.27</v>
@@ -2206,19 +2206,19 @@
         <v>38724.660000000003</v>
       </c>
       <c r="I37">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="J37">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K37">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L37">
-        <v>108</v>
+        <v>107.08</v>
       </c>
       <c r="M37">
-        <v>13.26</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2229,10 +2229,10 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>59500</v>
+        <v>62200</v>
       </c>
       <c r="D38" s="3">
-        <v>-1.49E-2</v>
+        <v>-8.0000000000000002E-3</v>
       </c>
       <c r="E38">
         <v>9.39</v>
@@ -2247,19 +2247,19 @@
         <v>98085.37</v>
       </c>
       <c r="I38">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="J38">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K38">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L38">
-        <v>103.04</v>
+        <v>105.44</v>
       </c>
       <c r="M38">
-        <v>9.7799999999999994</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2270,10 +2270,10 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>31000</v>
+        <v>27500</v>
       </c>
       <c r="D39" s="3">
-        <v>-1.6000000000000001E-3</v>
+        <v>-4.1799999999999997E-2</v>
       </c>
       <c r="E39">
         <v>12.36</v>
@@ -2288,19 +2288,19 @@
         <v>31515.31</v>
       </c>
       <c r="I39">
-        <v>3.68</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="J39">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="K39">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="L39">
-        <v>102.99</v>
+        <v>91.4</v>
       </c>
       <c r="M39">
-        <v>9.15</v>
+        <v>-7.41</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2311,10 +2311,10 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>11790</v>
+        <v>12090</v>
       </c>
       <c r="D40" s="3">
-        <v>-1.26E-2</v>
+        <v>2.8899999999999999E-2</v>
       </c>
       <c r="E40">
         <v>1.55</v>
@@ -2329,19 +2329,19 @@
         <v>29736.69</v>
       </c>
       <c r="I40">
-        <v>2.12</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="J40">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K40">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L40">
-        <v>104.85</v>
+        <v>106.83</v>
       </c>
       <c r="M40">
-        <v>-3.76</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2352,10 +2352,10 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>52200</v>
+        <v>57100</v>
       </c>
       <c r="D41" s="3">
-        <v>5.7999999999999996E-3</v>
+        <v>-7.0000000000000001E-3</v>
       </c>
       <c r="E41">
         <v>11.33</v>
@@ -2370,19 +2370,19 @@
         <v>59573.64</v>
       </c>
       <c r="I41">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="J41">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="K41">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="L41">
-        <v>104.96</v>
+        <v>112.48</v>
       </c>
       <c r="M41">
-        <v>5.78</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2393,10 +2393,10 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>18720</v>
+        <v>19350</v>
       </c>
       <c r="D42" s="3">
-        <v>7.0000000000000001E-3</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="E42">
         <v>8.8800000000000008</v>
@@ -2411,19 +2411,19 @@
         <v>26617.85</v>
       </c>
       <c r="I42">
-        <v>6.28</v>
+        <v>6.07</v>
       </c>
       <c r="J42">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K42">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L42">
-        <v>102.86</v>
+        <v>105.19</v>
       </c>
       <c r="M42">
-        <v>-1.99</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2434,10 +2434,10 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>35700</v>
+        <v>33200</v>
       </c>
       <c r="D43" s="3">
-        <v>1.4E-3</v>
+        <v>-5.28E-2</v>
       </c>
       <c r="E43">
         <v>8.91</v>
@@ -2452,19 +2452,19 @@
         <v>49113.23</v>
       </c>
       <c r="I43">
-        <v>3.81</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="J43">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="K43">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="L43">
-        <v>107.19</v>
+        <v>98.35</v>
       </c>
       <c r="M43">
-        <v>12.62</v>
+        <v>3.59</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D16EEE35-4E67-413A-8861-A15E330D3865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FBC2777-8B74-4A5D-9F5B-FE8AA92CB638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B2638EA5-1A6B-422F-9879-EE2F92052D7E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{28B06CDE-4F93-4526-B3AB-42DA7771D09B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -687,7 +687,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC00A692-FB56-4996-8526-8C97612DC0C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4DB2E0C-C22D-4FAB-9C2F-5C10DDB0808B}">
   <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1386,7 +1386,7 @@
         <v>223707.87</v>
       </c>
       <c r="I17">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="J17">
         <v>76</v>
@@ -1509,7 +1509,7 @@
         <v>60299.05</v>
       </c>
       <c r="I20">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J20">
         <v>92</v>
@@ -1550,7 +1550,7 @@
         <v>37882.559999999998</v>
       </c>
       <c r="I21">
-        <v>14.25</v>
+        <v>14.21</v>
       </c>
       <c r="J21">
         <v>84</v>
@@ -1714,7 +1714,7 @@
         <v>71885.83</v>
       </c>
       <c r="I25">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="J25">
         <v>80</v>
@@ -1837,7 +1837,7 @@
         <v>85735.74</v>
       </c>
       <c r="I28">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="J28">
         <v>96</v>
@@ -1919,7 +1919,7 @@
         <v>118301.94</v>
       </c>
       <c r="I30">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="J30">
         <v>37</v>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FBC2777-8B74-4A5D-9F5B-FE8AA92CB638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72510481-5562-40C0-9D04-F624A8B6B7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{28B06CDE-4F93-4526-B3AB-42DA7771D09B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B48E9298-8D1E-4DAF-A404-BDCBBBA44F24}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="187">
   <si>
     <t>종목코드</t>
   </si>
@@ -60,256 +60,532 @@
     <t>해당등락률</t>
   </si>
   <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>삼성전자</t>
+  </si>
+  <si>
+    <t>032830</t>
+  </si>
+  <si>
+    <t>삼성생명</t>
+  </si>
+  <si>
+    <t>039490</t>
+  </si>
+  <si>
+    <t>키움증권</t>
+  </si>
+  <si>
+    <t>006120</t>
+  </si>
+  <si>
+    <t>SK디스커버리</t>
+  </si>
+  <si>
+    <t>000660</t>
+  </si>
+  <si>
+    <t>SK하이닉스</t>
+  </si>
+  <si>
+    <t>016360</t>
+  </si>
+  <si>
+    <t>삼성증권</t>
+  </si>
+  <si>
+    <t>071050</t>
+  </si>
+  <si>
+    <t>한국금융지주</t>
+  </si>
+  <si>
+    <t>010120</t>
+  </si>
+  <si>
+    <t>LS ELECTRIC</t>
+  </si>
+  <si>
+    <t>011070</t>
+  </si>
+  <si>
+    <t>LG이노텍</t>
+  </si>
+  <si>
+    <t>005940</t>
+  </si>
+  <si>
+    <t>NH투자증권</t>
+  </si>
+  <si>
+    <t>003540</t>
+  </si>
+  <si>
+    <t>대신증권</t>
+  </si>
+  <si>
+    <t>006260</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>281820</t>
+  </si>
+  <si>
+    <t>케이씨텍</t>
+  </si>
+  <si>
+    <t>001270</t>
+  </si>
+  <si>
+    <t>부국증권</t>
+  </si>
+  <si>
+    <t>120110</t>
+  </si>
+  <si>
+    <t>코오롱인더</t>
+  </si>
+  <si>
+    <t>000720</t>
+  </si>
+  <si>
+    <t>현대건설</t>
+  </si>
+  <si>
+    <t>000810</t>
+  </si>
+  <si>
+    <t>삼성화재</t>
+  </si>
+  <si>
+    <t>018260</t>
+  </si>
+  <si>
+    <t>삼성에스디에스</t>
+  </si>
+  <si>
+    <t>005380</t>
+  </si>
+  <si>
+    <t>현대차</t>
+  </si>
+  <si>
+    <t>005490</t>
+  </si>
+  <si>
+    <t>POSCO홀딩스</t>
+  </si>
+  <si>
+    <t>105560</t>
+  </si>
+  <si>
+    <t>KB금융</t>
+  </si>
+  <si>
+    <t>375500</t>
+  </si>
+  <si>
+    <t>DL이앤씨</t>
+  </si>
+  <si>
+    <t>012330</t>
+  </si>
+  <si>
+    <t>현대모비스</t>
+  </si>
+  <si>
+    <t>000880</t>
+  </si>
+  <si>
+    <t>한화</t>
+  </si>
+  <si>
+    <t>029460</t>
+  </si>
+  <si>
+    <t>케이씨</t>
+  </si>
+  <si>
+    <t>057050</t>
+  </si>
+  <si>
+    <t>현대홈쇼핑</t>
+  </si>
+  <si>
+    <t>000270</t>
+  </si>
+  <si>
+    <t>기아</t>
+  </si>
+  <si>
+    <t>003550</t>
+  </si>
+  <si>
+    <t>LG</t>
+  </si>
+  <si>
+    <t>009150</t>
+  </si>
+  <si>
+    <t>삼성전기</t>
+  </si>
+  <si>
+    <t>192820</t>
+  </si>
+  <si>
+    <t>코스맥스</t>
+  </si>
+  <si>
+    <t>086790</t>
+  </si>
+  <si>
+    <t>하나금융지주</t>
+  </si>
+  <si>
+    <t>004170</t>
+  </si>
+  <si>
+    <t>신세계</t>
+  </si>
+  <si>
+    <t>055550</t>
+  </si>
+  <si>
+    <t>신한지주</t>
+  </si>
+  <si>
+    <t>001430</t>
+  </si>
+  <si>
+    <t>세아베스틸지주</t>
+  </si>
+  <si>
+    <t>138930</t>
+  </si>
+  <si>
+    <t>BNK금융지주</t>
+  </si>
+  <si>
+    <t>035420</t>
+  </si>
+  <si>
+    <t>NAVER</t>
+  </si>
+  <si>
+    <t>036530</t>
+  </si>
+  <si>
+    <t>SNT홀딩스</t>
+  </si>
+  <si>
+    <t>003690</t>
+  </si>
+  <si>
+    <t>코리안리</t>
+  </si>
+  <si>
+    <t>068270</t>
+  </si>
+  <si>
+    <t>셀트리온</t>
+  </si>
+  <si>
+    <t>214320</t>
+  </si>
+  <si>
+    <t>이노션</t>
+  </si>
+  <si>
+    <t>006040</t>
+  </si>
+  <si>
+    <t>동원산업</t>
+  </si>
+  <si>
+    <t>012450</t>
+  </si>
+  <si>
+    <t>한화에어로스페이스</t>
+  </si>
+  <si>
+    <t>139130</t>
+  </si>
+  <si>
+    <t>iM금융지주</t>
+  </si>
+  <si>
+    <t>029780</t>
+  </si>
+  <si>
+    <t>삼성카드</t>
+  </si>
+  <si>
+    <t>316140</t>
+  </si>
+  <si>
+    <t>우리금융지주</t>
+  </si>
+  <si>
+    <t>241560</t>
+  </si>
+  <si>
+    <t>두산밥캣</t>
+  </si>
+  <si>
+    <t>086280</t>
+  </si>
+  <si>
+    <t>현대글로비스</t>
+  </si>
+  <si>
+    <t>033780</t>
+  </si>
+  <si>
+    <t>KT&amp;G</t>
+  </si>
+  <si>
+    <t>036460</t>
+  </si>
+  <si>
+    <t>한국가스공사</t>
+  </si>
+  <si>
+    <t>175330</t>
+  </si>
+  <si>
+    <t>JB금융지주</t>
+  </si>
+  <si>
+    <t>017670</t>
+  </si>
+  <si>
+    <t>SK텔레콤</t>
+  </si>
+  <si>
+    <t>064350</t>
+  </si>
+  <si>
+    <t>현대로템</t>
+  </si>
+  <si>
+    <t>029530</t>
+  </si>
+  <si>
+    <t>신도리코</t>
+  </si>
+  <si>
+    <t>011760</t>
+  </si>
+  <si>
+    <t>현대코퍼레이션</t>
+  </si>
+  <si>
+    <t>024110</t>
+  </si>
+  <si>
+    <t>기업은행</t>
+  </si>
+  <si>
+    <t>004980</t>
+  </si>
+  <si>
+    <t>성신양회</t>
+  </si>
+  <si>
+    <t>002310</t>
+  </si>
+  <si>
+    <t>아세아제지</t>
+  </si>
+  <si>
+    <t>003850</t>
+  </si>
+  <si>
+    <t>보령</t>
+  </si>
+  <si>
+    <t>002960</t>
+  </si>
+  <si>
+    <t>한국쉘석유</t>
+  </si>
+  <si>
+    <t>000640</t>
+  </si>
+  <si>
+    <t>동아쏘시오홀딩스</t>
+  </si>
+  <si>
+    <t>003090</t>
+  </si>
+  <si>
+    <t>대웅</t>
+  </si>
+  <si>
+    <t>183190</t>
+  </si>
+  <si>
+    <t>아세아시멘트</t>
+  </si>
+  <si>
+    <t>004000</t>
+  </si>
+  <si>
+    <t>롯데정밀화학</t>
+  </si>
+  <si>
+    <t>007070</t>
+  </si>
+  <si>
+    <t>GS리테일</t>
+  </si>
+  <si>
+    <t>007340</t>
+  </si>
+  <si>
+    <t>DN오토모티브</t>
+  </si>
+  <si>
+    <t>000100</t>
+  </si>
+  <si>
+    <t>유한양행</t>
+  </si>
+  <si>
+    <t>005830</t>
+  </si>
+  <si>
+    <t>DB손해보험</t>
+  </si>
+  <si>
+    <t>009540</t>
+  </si>
+  <si>
+    <t>HD한국조선해양</t>
+  </si>
+  <si>
+    <t>011780</t>
+  </si>
+  <si>
+    <t>금호석유화학</t>
+  </si>
+  <si>
+    <t>030200</t>
+  </si>
+  <si>
+    <t>KT</t>
+  </si>
+  <si>
+    <t>002350</t>
+  </si>
+  <si>
+    <t>넥센타이어</t>
+  </si>
+  <si>
+    <t>032640</t>
+  </si>
+  <si>
+    <t>LG유플러스</t>
+  </si>
+  <si>
+    <t>192080</t>
+  </si>
+  <si>
+    <t>더블유게임즈</t>
+  </si>
+  <si>
+    <t>035250</t>
+  </si>
+  <si>
+    <t>강원랜드</t>
+  </si>
+  <si>
+    <t>017800</t>
+  </si>
+  <si>
+    <t>현대엘리베이터</t>
+  </si>
+  <si>
+    <t>009970</t>
+  </si>
+  <si>
+    <t>영원무역홀딩스</t>
+  </si>
+  <si>
+    <t>161390</t>
+  </si>
+  <si>
+    <t>한국타이어앤테크놀로</t>
+  </si>
+  <si>
+    <t>030000</t>
+  </si>
+  <si>
+    <t>제일기획</t>
+  </si>
+  <si>
+    <t>185750</t>
+  </si>
+  <si>
+    <t>종근당</t>
+  </si>
+  <si>
+    <t>286940</t>
+  </si>
+  <si>
+    <t>롯데이노베이트</t>
+  </si>
+  <si>
     <t>000240</t>
   </si>
   <si>
     <t>한국앤컴퍼니</t>
   </si>
   <si>
-    <t>000270</t>
-  </si>
-  <si>
-    <t>기아</t>
-  </si>
-  <si>
-    <t>000810</t>
-  </si>
-  <si>
-    <t>삼성화재</t>
+    <t>021240</t>
+  </si>
+  <si>
+    <t>코웨이</t>
+  </si>
+  <si>
+    <t>047050</t>
+  </si>
+  <si>
+    <t>포스코인터내셔널</t>
+  </si>
+  <si>
+    <t>089470</t>
+  </si>
+  <si>
+    <t>HDC현대EP</t>
+  </si>
+  <si>
+    <t>005300</t>
+  </si>
+  <si>
+    <t>롯데칠성</t>
+  </si>
+  <si>
+    <t>267250</t>
+  </si>
+  <si>
+    <t>HD현대</t>
+  </si>
+  <si>
+    <t>078930</t>
+  </si>
+  <si>
+    <t>GS</t>
   </si>
   <si>
     <t>001120</t>
   </si>
   <si>
     <t>LX인터내셔널</t>
-  </si>
-  <si>
-    <t>001270</t>
-  </si>
-  <si>
-    <t>부국증권</t>
-  </si>
-  <si>
-    <t>001430</t>
-  </si>
-  <si>
-    <t>세아베스틸지주</t>
-  </si>
-  <si>
-    <t>002310</t>
-  </si>
-  <si>
-    <t>아세아제지</t>
-  </si>
-  <si>
-    <t>003540</t>
-  </si>
-  <si>
-    <t>대신증권</t>
-  </si>
-  <si>
-    <t>003550</t>
-  </si>
-  <si>
-    <t>LG</t>
-  </si>
-  <si>
-    <t>003690</t>
-  </si>
-  <si>
-    <t>코리안리</t>
-  </si>
-  <si>
-    <t>004980</t>
-  </si>
-  <si>
-    <t>성신양회</t>
-  </si>
-  <si>
-    <t>005380</t>
-  </si>
-  <si>
-    <t>현대차</t>
-  </si>
-  <si>
-    <t>005830</t>
-  </si>
-  <si>
-    <t>DB손해보험</t>
-  </si>
-  <si>
-    <t>005940</t>
-  </si>
-  <si>
-    <t>NH투자증권</t>
-  </si>
-  <si>
-    <t>007340</t>
-  </si>
-  <si>
-    <t>DN오토모티브</t>
-  </si>
-  <si>
-    <t>009970</t>
-  </si>
-  <si>
-    <t>영원무역홀딩스</t>
-  </si>
-  <si>
-    <t>011780</t>
-  </si>
-  <si>
-    <t>금호석유화학</t>
-  </si>
-  <si>
-    <t>016360</t>
-  </si>
-  <si>
-    <t>삼성증권</t>
-  </si>
-  <si>
-    <t>017670</t>
-  </si>
-  <si>
-    <t>SK텔레콤</t>
-  </si>
-  <si>
-    <t>017800</t>
-  </si>
-  <si>
-    <t>현대엘리베이터</t>
-  </si>
-  <si>
-    <t>024110</t>
-  </si>
-  <si>
-    <t>기업은행</t>
-  </si>
-  <si>
-    <t>029780</t>
-  </si>
-  <si>
-    <t>삼성카드</t>
-  </si>
-  <si>
-    <t>030000</t>
-  </si>
-  <si>
-    <t>제일기획</t>
-  </si>
-  <si>
-    <t>030200</t>
-  </si>
-  <si>
-    <t>KT</t>
-  </si>
-  <si>
-    <t>032640</t>
-  </si>
-  <si>
-    <t>LG유플러스</t>
-  </si>
-  <si>
-    <t>032830</t>
-  </si>
-  <si>
-    <t>삼성생명</t>
-  </si>
-  <si>
-    <t>033780</t>
-  </si>
-  <si>
-    <t>KT&amp;G</t>
-  </si>
-  <si>
-    <t>035250</t>
-  </si>
-  <si>
-    <t>강원랜드</t>
-  </si>
-  <si>
-    <t>036460</t>
-  </si>
-  <si>
-    <t>한국가스공사</t>
-  </si>
-  <si>
-    <t>055550</t>
-  </si>
-  <si>
-    <t>신한지주</t>
-  </si>
-  <si>
-    <t>071050</t>
-  </si>
-  <si>
-    <t>한국금융지주</t>
-  </si>
-  <si>
-    <t>078930</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>086790</t>
-  </si>
-  <si>
-    <t>하나금융지주</t>
-  </si>
-  <si>
-    <t>105560</t>
-  </si>
-  <si>
-    <t>KB금융</t>
-  </si>
-  <si>
-    <t>138930</t>
-  </si>
-  <si>
-    <t>BNK금융지주</t>
-  </si>
-  <si>
-    <t>139130</t>
-  </si>
-  <si>
-    <t>iM금융지주</t>
-  </si>
-  <si>
-    <t>161390</t>
-  </si>
-  <si>
-    <t>한국타이어앤테크놀로</t>
-  </si>
-  <si>
-    <t>175330</t>
-  </si>
-  <si>
-    <t>JB금융지주</t>
-  </si>
-  <si>
-    <t>183190</t>
-  </si>
-  <si>
-    <t>아세아시멘트</t>
-  </si>
-  <si>
-    <t>192080</t>
-  </si>
-  <si>
-    <t>더블유게임즈</t>
-  </si>
-  <si>
-    <t>214320</t>
-  </si>
-  <si>
-    <t>이노션</t>
-  </si>
-  <si>
-    <t>316140</t>
-  </si>
-  <si>
-    <t>우리금융지주</t>
   </si>
 </sst>
 </file>
@@ -687,14 +963,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4DB2E0C-C22D-4FAB-9C2F-5C10DDB0808B}">
-  <dimension ref="A1:M43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE39AAC-59F9-4D9E-A685-96C99125A543}">
+  <dimension ref="A1:M89"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.296875" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -753,37 +1029,37 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>24850</v>
+        <v>267500</v>
       </c>
       <c r="D2" s="3">
-        <v>4.0000000000000001E-3</v>
+        <v>0.15049999999999999</v>
       </c>
       <c r="E2">
-        <v>7.52</v>
+        <v>10.85</v>
       </c>
       <c r="F2">
-        <v>7.52</v>
+        <v>10.85</v>
       </c>
       <c r="G2">
-        <v>6.85</v>
+        <v>8.01</v>
       </c>
       <c r="H2" s="4">
-        <v>50396.34</v>
+        <v>63976.31</v>
       </c>
       <c r="I2">
-        <v>4.43</v>
+        <v>0.62</v>
       </c>
       <c r="J2">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="K2">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="L2">
-        <v>99.63</v>
+        <v>126.86</v>
       </c>
       <c r="M2">
-        <v>3.54</v>
+        <v>36.130000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -794,37 +1070,37 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>152600</v>
+        <v>304500</v>
       </c>
       <c r="D3" s="3">
-        <v>-5.1999999999999998E-3</v>
+        <v>0.14910000000000001</v>
       </c>
       <c r="E3">
-        <v>12.92</v>
+        <v>4.66</v>
       </c>
       <c r="F3">
-        <v>12.92</v>
+        <v>4.66</v>
       </c>
       <c r="G3">
-        <v>17.48</v>
+        <v>4.88</v>
       </c>
       <c r="H3" s="4">
-        <v>157169.68</v>
+        <v>324173.33</v>
       </c>
       <c r="I3">
-        <v>4.46</v>
+        <v>1.74</v>
       </c>
       <c r="J3">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="K3">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="L3">
-        <v>99.16</v>
+        <v>124.65</v>
       </c>
       <c r="M3">
-        <v>5.0999999999999996</v>
+        <v>37.159999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -835,37 +1111,37 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>461000</v>
+        <v>484500</v>
       </c>
       <c r="D4" s="3">
-        <v>1.0999999999999999E-2</v>
+        <v>0.1467</v>
       </c>
       <c r="E4">
-        <v>10.96</v>
+        <v>18.12</v>
       </c>
       <c r="F4">
-        <v>10.96</v>
+        <v>18.12</v>
       </c>
       <c r="G4">
-        <v>12.25</v>
+        <v>14.46</v>
       </c>
       <c r="H4" s="4">
-        <v>457603.51</v>
+        <v>249475.01</v>
       </c>
       <c r="I4">
-        <v>4.2300000000000004</v>
+        <v>2.37</v>
       </c>
       <c r="J4">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="K4">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="L4">
-        <v>99.44</v>
+        <v>109.8</v>
       </c>
       <c r="M4">
-        <v>4.6500000000000004</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -876,37 +1152,37 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>54900</v>
+        <v>62900</v>
       </c>
       <c r="D5" s="3">
-        <v>2.4299999999999999E-2</v>
+        <v>0.1313</v>
       </c>
       <c r="E5">
-        <v>5.22</v>
+        <v>4.49</v>
       </c>
       <c r="F5">
-        <v>5.22</v>
+        <v>4.49</v>
       </c>
       <c r="G5">
-        <v>5.84</v>
+        <v>4.13</v>
       </c>
       <c r="H5" s="4">
-        <v>72566.75</v>
+        <v>150877.26</v>
       </c>
       <c r="I5">
-        <v>3.64</v>
+        <v>3.18</v>
       </c>
       <c r="J5">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="K5">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="L5">
-        <v>110.42</v>
+        <v>109.3</v>
       </c>
       <c r="M5">
-        <v>21.33</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -917,37 +1193,37 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>74600</v>
+        <v>1605000</v>
       </c>
       <c r="D6" s="3">
-        <v>4.0000000000000001E-3</v>
+        <v>0.10920000000000001</v>
       </c>
       <c r="E6">
-        <v>5.69</v>
+        <v>44.15</v>
       </c>
       <c r="F6">
-        <v>5.69</v>
+        <v>44.15</v>
       </c>
       <c r="G6">
-        <v>5.88</v>
+        <v>19.87</v>
       </c>
       <c r="H6" s="4">
-        <v>66692.75</v>
+        <v>167604.03</v>
       </c>
       <c r="I6">
-        <v>3.22</v>
+        <v>0.19</v>
       </c>
       <c r="J6">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>99.57</v>
+        <v>142.74</v>
       </c>
       <c r="M6">
-        <v>0.95</v>
+        <v>75.22</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -958,37 +1234,37 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>72500</v>
+        <v>151600</v>
       </c>
       <c r="D7" s="3">
-        <v>1.9699999999999999E-2</v>
+        <v>9.9299999999999999E-2</v>
       </c>
       <c r="E7">
-        <v>2.89</v>
+        <v>13.09</v>
       </c>
       <c r="F7">
-        <v>2.89</v>
+        <v>13.09</v>
       </c>
       <c r="G7">
-        <v>3.54</v>
+        <v>11.51</v>
       </c>
       <c r="H7" s="4">
-        <v>54191.72</v>
+        <v>90347.77</v>
       </c>
       <c r="I7">
-        <v>1.66</v>
+        <v>2.64</v>
       </c>
       <c r="J7">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="K7">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="L7">
-        <v>105.38</v>
+        <v>139.68</v>
       </c>
       <c r="M7">
-        <v>12.58</v>
+        <v>59.24</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -999,37 +1275,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>9110</v>
+        <v>283000</v>
       </c>
       <c r="D8" s="3">
-        <v>-3.09E-2</v>
+        <v>8.0199999999999994E-2</v>
       </c>
       <c r="E8">
-        <v>3.52</v>
+        <v>18.66</v>
       </c>
       <c r="F8">
-        <v>3.52</v>
+        <v>18.66</v>
       </c>
       <c r="G8">
-        <v>5.39</v>
+        <v>13</v>
       </c>
       <c r="H8" s="4">
-        <v>21278.16</v>
+        <v>195836.08</v>
       </c>
       <c r="I8">
-        <v>2.74</v>
+        <v>3.07</v>
       </c>
       <c r="J8">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="K8">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="L8">
-        <v>99.88</v>
+        <v>115.66</v>
       </c>
       <c r="M8">
-        <v>7.05</v>
+        <v>32.86</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1040,37 +1316,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>39300</v>
+        <v>317000</v>
       </c>
       <c r="D9" s="3">
-        <v>1.29E-2</v>
+        <v>7.8200000000000006E-2</v>
       </c>
       <c r="E9">
-        <v>5.0599999999999996</v>
+        <v>14.67</v>
       </c>
       <c r="F9">
-        <v>5.0599999999999996</v>
+        <v>14.67</v>
       </c>
       <c r="G9">
-        <v>4.7699999999999996</v>
+        <v>13.57</v>
       </c>
       <c r="H9" s="4">
-        <v>45197.48</v>
+        <v>13864.42</v>
       </c>
       <c r="I9">
-        <v>3.05</v>
+        <v>0.19</v>
       </c>
       <c r="J9">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="K9">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="L9">
-        <v>103.85</v>
+        <v>158.16999999999999</v>
       </c>
       <c r="M9">
-        <v>11.49</v>
+        <v>101.14</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1081,37 +1357,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>95500</v>
+        <v>633000</v>
       </c>
       <c r="D10" s="3">
-        <v>-5.1999999999999998E-3</v>
+        <v>6.3899999999999998E-2</v>
       </c>
       <c r="E10">
-        <v>2.64</v>
+        <v>6.14</v>
       </c>
       <c r="F10">
-        <v>2.64</v>
+        <v>6.14</v>
       </c>
       <c r="G10">
-        <v>3.23</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="H10" s="4">
-        <v>184176.03</v>
+        <v>243518.36</v>
       </c>
       <c r="I10">
-        <v>3.25</v>
+        <v>0.3</v>
       </c>
       <c r="J10">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="K10">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="L10">
-        <v>105.28</v>
+        <v>146.66</v>
       </c>
       <c r="M10">
-        <v>15.34</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1122,37 +1398,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>12290</v>
+        <v>38750</v>
       </c>
       <c r="D11" s="3">
-        <v>-5.7000000000000002E-3</v>
+        <v>6.3100000000000003E-2</v>
       </c>
       <c r="E11">
-        <v>9.0299999999999994</v>
+        <v>11.76</v>
       </c>
       <c r="F11">
-        <v>9.0299999999999994</v>
+        <v>11.76</v>
       </c>
       <c r="G11">
         <v>9.33</v>
       </c>
       <c r="H11" s="4">
-        <v>19594.84</v>
+        <v>25179.95</v>
       </c>
       <c r="I11">
-        <v>4.6399999999999997</v>
+        <v>3.35</v>
       </c>
       <c r="J11">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="K11">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="L11">
-        <v>99.1</v>
+        <v>114.11</v>
       </c>
       <c r="M11">
-        <v>0.41</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1163,37 +1439,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>11790</v>
+        <v>42200</v>
       </c>
       <c r="D12" s="3">
-        <v>6.2199999999999998E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
       <c r="E12">
-        <v>4.49</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="F12">
-        <v>4.49</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="G12">
-        <v>9.0299999999999994</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="H12" s="4">
-        <v>23274.23</v>
+        <v>45197.48</v>
       </c>
       <c r="I12">
-        <v>2.97</v>
+        <v>2.84</v>
       </c>
       <c r="J12">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="K12">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="L12">
-        <v>113.66</v>
+        <v>110.7</v>
       </c>
       <c r="M12">
-        <v>32.03</v>
+        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1204,37 +1480,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>524000</v>
+        <v>532000</v>
       </c>
       <c r="D13" s="3">
-        <v>2.1399999999999999E-2</v>
+        <v>4.5199999999999997E-2</v>
       </c>
       <c r="E13">
-        <v>8.41</v>
+        <v>5.64</v>
       </c>
       <c r="F13">
-        <v>8.41</v>
+        <v>5.64</v>
       </c>
       <c r="G13">
-        <v>11.51</v>
+        <v>6.79</v>
       </c>
       <c r="H13" s="4">
-        <v>436418.31</v>
+        <v>160840.6</v>
       </c>
       <c r="I13">
-        <v>1.91</v>
+        <v>0.47</v>
       </c>
       <c r="J13">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="K13">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="L13">
-        <v>104.97</v>
+        <v>154.71</v>
       </c>
       <c r="M13">
-        <v>17.62</v>
+        <v>103.44</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1245,37 +1521,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>171300</v>
+        <v>69300</v>
       </c>
       <c r="D14" s="3">
-        <v>-2.1100000000000001E-2</v>
+        <v>4.2099999999999999E-2</v>
       </c>
       <c r="E14">
-        <v>17.72</v>
+        <v>10.55</v>
       </c>
       <c r="F14">
-        <v>17.72</v>
+        <v>10.55</v>
       </c>
       <c r="G14">
-        <v>17.440000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="H14" s="4">
-        <v>158606.49</v>
+        <v>26861.5</v>
       </c>
       <c r="I14">
-        <v>4.4400000000000004</v>
+        <v>0.65</v>
       </c>
       <c r="J14">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="K14">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="L14">
-        <v>100.71</v>
+        <v>129.13999999999999</v>
       </c>
       <c r="M14">
-        <v>4.58</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1286,37 +1562,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>35250</v>
+        <v>79400</v>
       </c>
       <c r="D15" s="3">
-        <v>4.3E-3</v>
+        <v>3.9300000000000002E-2</v>
       </c>
       <c r="E15">
-        <v>11.76</v>
+        <v>5.69</v>
       </c>
       <c r="F15">
-        <v>11.76</v>
+        <v>5.69</v>
       </c>
       <c r="G15">
-        <v>9.33</v>
+        <v>5.88</v>
       </c>
       <c r="H15" s="4">
-        <v>25179.95</v>
+        <v>66692.75</v>
       </c>
       <c r="I15">
-        <v>3.69</v>
+        <v>3.02</v>
       </c>
       <c r="J15">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K15">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L15">
-        <v>105.39</v>
+        <v>106.05</v>
       </c>
       <c r="M15">
-        <v>19.09</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1327,37 +1603,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>41300</v>
+        <v>96800</v>
       </c>
       <c r="D16" s="3">
-        <v>-3.8399999999999997E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="E16">
-        <v>15.02</v>
+        <v>1.01</v>
       </c>
       <c r="F16">
-        <v>15.02</v>
+        <v>1.01</v>
       </c>
       <c r="G16">
-        <v>20.7</v>
+        <v>1.88</v>
       </c>
       <c r="H16" s="4">
-        <v>34750.239999999998</v>
+        <v>129697.52</v>
       </c>
       <c r="I16">
-        <v>2.42</v>
+        <v>1.34</v>
       </c>
       <c r="J16">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K16">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L16">
-        <v>107.57</v>
+        <v>110.22</v>
       </c>
       <c r="M16">
-        <v>8.26</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1368,37 +1644,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>209000</v>
+        <v>164300</v>
       </c>
       <c r="D17" s="3">
-        <v>-9.4999999999999998E-3</v>
+        <v>3.0700000000000002E-2</v>
       </c>
       <c r="E17">
-        <v>12.83</v>
+        <v>4.58</v>
       </c>
       <c r="F17">
-        <v>12.83</v>
+        <v>4.58</v>
       </c>
       <c r="G17">
-        <v>14.29</v>
+        <v>3.09</v>
       </c>
       <c r="H17" s="4">
-        <v>223707.87</v>
+        <v>73522.75</v>
       </c>
       <c r="I17">
-        <v>3.14</v>
+        <v>0.49</v>
       </c>
       <c r="J17">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K17">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L17">
-        <v>97.22</v>
+        <v>97.6</v>
       </c>
       <c r="M17">
-        <v>-4.57</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1409,37 +1685,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>132200</v>
+        <v>485000</v>
       </c>
       <c r="D18" s="3">
-        <v>-8.9999999999999993E-3</v>
+        <v>2.4299999999999999E-2</v>
       </c>
       <c r="E18">
-        <v>4.74</v>
+        <v>10.96</v>
       </c>
       <c r="F18">
-        <v>4.74</v>
+        <v>10.96</v>
       </c>
       <c r="G18">
-        <v>6.13</v>
+        <v>12.25</v>
       </c>
       <c r="H18" s="4">
-        <v>215808.28</v>
+        <v>457603.51</v>
       </c>
       <c r="I18">
-        <v>1.29</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="J18">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="K18">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="L18">
-        <v>102.17</v>
+        <v>104.13</v>
       </c>
       <c r="M18">
-        <v>12.13</v>
+        <v>8.6199999999999992</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1450,37 +1726,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>112700</v>
+        <v>170700</v>
       </c>
       <c r="D19" s="3">
-        <v>9.9000000000000008E-3</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="E19">
-        <v>13.09</v>
+        <v>7.89</v>
       </c>
       <c r="F19">
-        <v>13.09</v>
+        <v>7.89</v>
       </c>
       <c r="G19">
-        <v>11.51</v>
+        <v>8.18</v>
       </c>
       <c r="H19" s="4">
-        <v>90347.77</v>
+        <v>128172.41</v>
       </c>
       <c r="I19">
-        <v>3.55</v>
+        <v>1.87</v>
       </c>
       <c r="J19">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="K19">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="L19">
-        <v>109.39</v>
+        <v>103.57</v>
       </c>
       <c r="M19">
-        <v>21.97</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1491,37 +1767,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>98000</v>
+        <v>551000</v>
       </c>
       <c r="D20" s="3">
-        <v>-0.02</v>
+        <v>2.23E-2</v>
       </c>
       <c r="E20">
-        <v>3.33</v>
+        <v>8.41</v>
       </c>
       <c r="F20">
-        <v>3.33</v>
+        <v>8.41</v>
       </c>
       <c r="G20">
-        <v>7.93</v>
+        <v>11.51</v>
       </c>
       <c r="H20" s="4">
-        <v>60299.05</v>
+        <v>436418.31</v>
       </c>
       <c r="I20">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="J20">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="K20">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="L20">
-        <v>110.34</v>
+        <v>107.92</v>
       </c>
       <c r="M20">
-        <v>28.27</v>
+        <v>16.489999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1532,37 +1808,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>98600</v>
+        <v>511000</v>
       </c>
       <c r="D21" s="3">
-        <v>2.3900000000000001E-2</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="E21">
-        <v>20.100000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="F21">
-        <v>20.100000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="G21">
-        <v>20.22</v>
+        <v>2.12</v>
       </c>
       <c r="H21" s="4">
-        <v>37882.559999999998</v>
+        <v>703131.42</v>
       </c>
       <c r="I21">
-        <v>14.21</v>
+        <v>1.96</v>
       </c>
       <c r="J21">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="K21">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="L21">
-        <v>107.03</v>
+        <v>129.19999999999999</v>
       </c>
       <c r="M21">
-        <v>18.37</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1573,37 +1849,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>22200</v>
+        <v>160500</v>
       </c>
       <c r="D22" s="3">
-        <v>-6.7000000000000002E-3</v>
+        <v>1.7100000000000001E-2</v>
       </c>
       <c r="E22">
-        <v>7.7</v>
+        <v>9.98</v>
       </c>
       <c r="F22">
-        <v>7.7</v>
+        <v>9.98</v>
       </c>
       <c r="G22">
-        <v>8.18</v>
+        <v>9.08</v>
       </c>
       <c r="H22" s="4">
-        <v>45715.519999999997</v>
+        <v>159779.29999999999</v>
       </c>
       <c r="I22">
-        <v>4.72</v>
+        <v>2.72</v>
       </c>
       <c r="J22">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="K22">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="L22">
-        <v>99.5</v>
+        <v>103.14</v>
       </c>
       <c r="M22">
-        <v>3.98</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1614,37 +1890,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>53000</v>
+        <v>92700</v>
       </c>
       <c r="D23" s="3">
-        <v>-1.49E-2</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="E23">
-        <v>7.45</v>
+        <v>7.34</v>
       </c>
       <c r="F23">
-        <v>7.45</v>
+        <v>7.34</v>
       </c>
       <c r="G23">
-        <v>7.69</v>
+        <v>5.41</v>
       </c>
       <c r="H23" s="4">
-        <v>79986.48</v>
+        <v>123369.97</v>
       </c>
       <c r="I23">
-        <v>5.28</v>
+        <v>0.96</v>
       </c>
       <c r="J23">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="K23">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="L23">
-        <v>97.99</v>
+        <v>101.43</v>
       </c>
       <c r="M23">
-        <v>-0.19</v>
+        <v>22.62</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1655,37 +1931,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>19750</v>
-      </c>
-      <c r="D24" s="5">
-        <v>0</v>
+        <v>436500</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="E24">
-        <v>13.7</v>
+        <v>7.68</v>
       </c>
       <c r="F24">
-        <v>13.7</v>
+        <v>7.68</v>
       </c>
       <c r="G24">
-        <v>14.6</v>
+        <v>8.59</v>
       </c>
       <c r="H24" s="4">
-        <v>16125.49</v>
+        <v>545786.89</v>
       </c>
       <c r="I24">
-        <v>6.23</v>
+        <v>1.49</v>
       </c>
       <c r="J24">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="K24">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="L24">
-        <v>100.92</v>
+        <v>104.72</v>
       </c>
       <c r="M24">
-        <v>4.1100000000000003</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1696,37 +1972,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>61100</v>
+        <v>141400</v>
       </c>
       <c r="D25" s="3">
-        <v>-9.7000000000000003E-3</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="E25">
-        <v>10.220000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="F25">
-        <v>10.220000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="G25">
-        <v>6.37</v>
+        <v>4.66</v>
       </c>
       <c r="H25" s="4">
-        <v>71885.83</v>
+        <v>126619.82</v>
       </c>
       <c r="I25">
-        <v>3.93</v>
+        <v>0.78</v>
       </c>
       <c r="J25">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K25">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="L25">
-        <v>99.45</v>
+        <v>112.56</v>
       </c>
       <c r="M25">
-        <v>1.1599999999999999</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1737,37 +2013,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>16430</v>
+        <v>39900</v>
       </c>
       <c r="D26" s="3">
-        <v>-1.0200000000000001E-2</v>
+        <v>1.01E-2</v>
       </c>
       <c r="E26">
-        <v>6.01</v>
+        <v>5.44</v>
       </c>
       <c r="F26">
-        <v>6.01</v>
+        <v>5.44</v>
       </c>
       <c r="G26">
-        <v>5.97</v>
+        <v>5.99</v>
       </c>
       <c r="H26" s="4">
-        <v>20769.650000000001</v>
+        <v>66877.22</v>
       </c>
       <c r="I26">
-        <v>4.0199999999999996</v>
+        <v>1.08</v>
       </c>
       <c r="J26">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K26">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="L26">
-        <v>100.23</v>
+        <v>113.63</v>
       </c>
       <c r="M26">
-        <v>5.8</v>
+        <v>34.340000000000003</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1778,37 +2054,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>250000</v>
+        <v>86300</v>
       </c>
       <c r="D27" s="3">
-        <v>2.2499999999999999E-2</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="E27">
-        <v>4.66</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="F27">
-        <v>4.66</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="G27">
-        <v>4.88</v>
+        <v>6.19</v>
       </c>
       <c r="H27" s="4">
-        <v>324173.33</v>
+        <v>201920.61</v>
       </c>
       <c r="I27">
-        <v>2.12</v>
+        <v>3.24</v>
       </c>
       <c r="J27">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K27">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="L27">
-        <v>105.97</v>
+        <v>105.91</v>
       </c>
       <c r="M27">
-        <v>18.760000000000002</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1819,37 +2095,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>177800</v>
+        <v>155100</v>
       </c>
       <c r="D28" s="3">
-        <v>9.1000000000000004E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="E28">
-        <v>11.77</v>
+        <v>12.92</v>
       </c>
       <c r="F28">
-        <v>11.77</v>
+        <v>12.92</v>
       </c>
       <c r="G28">
-        <v>11.4</v>
+        <v>17.48</v>
       </c>
       <c r="H28" s="4">
-        <v>85735.74</v>
+        <v>157169.68</v>
       </c>
       <c r="I28">
-        <v>3.37</v>
+        <v>4.38</v>
       </c>
       <c r="J28">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="K28">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="L28">
-        <v>108.44</v>
+        <v>100.9</v>
       </c>
       <c r="M28">
-        <v>11.68</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1860,37 +2136,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>17160</v>
+        <v>102800</v>
       </c>
       <c r="D29" s="3">
-        <v>1.24E-2</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="E29">
-        <v>8.11</v>
+        <v>2.64</v>
       </c>
       <c r="F29">
-        <v>8.11</v>
+        <v>2.64</v>
       </c>
       <c r="G29">
-        <v>9.93</v>
+        <v>3.23</v>
       </c>
       <c r="H29" s="4">
-        <v>19583.27</v>
+        <v>184176.03</v>
       </c>
       <c r="I29">
-        <v>5.54</v>
+        <v>3.02</v>
       </c>
       <c r="J29">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="K29">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="L29">
-        <v>100.16</v>
+        <v>110.26</v>
       </c>
       <c r="M29">
-        <v>1.6</v>
+        <v>17.350000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1901,37 +2177,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>38300</v>
+        <v>920000</v>
       </c>
       <c r="D30" s="3">
-        <v>-2.5999999999999999E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="E30">
-        <v>1.23</v>
+        <v>7.7</v>
       </c>
       <c r="F30">
-        <v>1.23</v>
+        <v>7.7</v>
       </c>
       <c r="G30">
-        <v>1.59</v>
+        <v>7.12</v>
       </c>
       <c r="H30" s="4">
-        <v>118301.94</v>
+        <v>124850.23</v>
       </c>
       <c r="I30">
-        <v>3.01</v>
+        <v>0.26</v>
       </c>
       <c r="J30">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="K30">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="L30">
-        <v>106</v>
+        <v>141.29</v>
       </c>
       <c r="M30">
-        <v>9.59</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1942,37 +2218,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>99700</v>
-      </c>
-      <c r="D31" s="3">
-        <v>-3.0000000000000001E-3</v>
+        <v>209000</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>8.7200000000000006</v>
+        <v>23.86</v>
       </c>
       <c r="F31">
-        <v>8.7200000000000006</v>
+        <v>23.86</v>
       </c>
       <c r="G31">
-        <v>8.4</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="H31" s="4">
-        <v>120617.68</v>
+        <v>49205.599999999999</v>
       </c>
       <c r="I31">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="J31">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="K31">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="L31">
-        <v>104.11</v>
+        <v>102.44</v>
       </c>
       <c r="M31">
-        <v>13.68</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1983,37 +2259,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>260500</v>
+        <v>126500</v>
       </c>
       <c r="D32" s="3">
-        <v>5.7999999999999996E-3</v>
+        <v>-8.0000000000000004E-4</v>
       </c>
       <c r="E32">
-        <v>18.66</v>
+        <v>9.17</v>
       </c>
       <c r="F32">
-        <v>18.66</v>
+        <v>9.17</v>
       </c>
       <c r="G32">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="H32" s="4">
-        <v>195836.08</v>
+        <v>162088.94</v>
       </c>
       <c r="I32">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="J32">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="K32">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L32">
-        <v>110.34</v>
+        <v>105.66</v>
       </c>
       <c r="M32">
-        <v>28.64</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2024,37 +2300,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>76500</v>
+        <v>410000</v>
       </c>
       <c r="D33" s="3">
-        <v>1.06E-2</v>
+        <v>-1.1999999999999999E-3</v>
       </c>
       <c r="E33">
-        <v>5.55</v>
+        <v>0.32</v>
       </c>
       <c r="F33">
-        <v>5.55</v>
+        <v>0.32</v>
       </c>
       <c r="G33">
-        <v>6.57</v>
+        <v>2.76</v>
       </c>
       <c r="H33" s="4">
-        <v>155269.29999999999</v>
+        <v>478219.9</v>
       </c>
       <c r="I33">
-        <v>3.92</v>
+        <v>1.27</v>
       </c>
       <c r="J33">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K33">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L33">
-        <v>109.84</v>
+        <v>113.35</v>
       </c>
       <c r="M33">
-        <v>19.91</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2065,37 +2341,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>124000</v>
+        <v>97800</v>
       </c>
       <c r="D34" s="3">
-        <v>5.7000000000000002E-3</v>
+        <v>-2E-3</v>
       </c>
       <c r="E34">
-        <v>9.17</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="F34">
-        <v>9.17</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="G34">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="H34" s="4">
-        <v>162088.94</v>
+        <v>120617.68</v>
       </c>
       <c r="I34">
-        <v>3.31</v>
+        <v>2.65</v>
       </c>
       <c r="J34">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K34">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L34">
-        <v>106.91</v>
+        <v>100.6</v>
       </c>
       <c r="M34">
-        <v>16.32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2106,37 +2382,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>157400</v>
-      </c>
-      <c r="D35" s="5">
-        <v>0</v>
+        <v>71600</v>
+      </c>
+      <c r="D35" s="3">
+        <v>-2.8E-3</v>
       </c>
       <c r="E35">
-        <v>9.98</v>
+        <v>2.89</v>
       </c>
       <c r="F35">
-        <v>9.98</v>
+        <v>2.89</v>
       </c>
       <c r="G35">
-        <v>9.08</v>
+        <v>3.54</v>
       </c>
       <c r="H35" s="4">
-        <v>159779.29999999999</v>
+        <v>54191.72</v>
       </c>
       <c r="I35">
-        <v>2.77</v>
+        <v>1.68</v>
       </c>
       <c r="J35">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="K35">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="L35">
-        <v>102.51</v>
+        <v>103.05</v>
       </c>
       <c r="M35">
-        <v>10.92</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2147,10 +2423,10 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>18740</v>
+        <v>18140</v>
       </c>
       <c r="D36" s="3">
-        <v>-1.37E-2</v>
+        <v>-3.3E-3</v>
       </c>
       <c r="E36">
         <v>7.58</v>
@@ -2165,19 +2441,19 @@
         <v>34779.699999999997</v>
       </c>
       <c r="I36">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="J36">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K36">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L36">
-        <v>102.03</v>
+        <v>98.55</v>
       </c>
       <c r="M36">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2188,37 +2464,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>19020</v>
+        <v>208000</v>
       </c>
       <c r="D37" s="3">
-        <v>-4.1999999999999997E-3</v>
+        <v>-4.7999999999999996E-3</v>
       </c>
       <c r="E37">
-        <v>7.27</v>
+        <v>7.36</v>
       </c>
       <c r="F37">
-        <v>7.27</v>
+        <v>7.36</v>
       </c>
       <c r="G37">
-        <v>5.87</v>
+        <v>6.56</v>
       </c>
       <c r="H37" s="4">
-        <v>38724.660000000003</v>
+        <v>180116.6</v>
       </c>
       <c r="I37">
-        <v>3.68</v>
+        <v>1.26</v>
       </c>
       <c r="J37">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="K37">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="L37">
-        <v>107.08</v>
+        <v>99.91</v>
       </c>
       <c r="M37">
-        <v>13.82</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2229,37 +2505,37 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>62200</v>
+        <v>60800</v>
       </c>
       <c r="D38" s="3">
-        <v>-8.0000000000000002E-3</v>
+        <v>-4.8999999999999998E-3</v>
       </c>
       <c r="E38">
-        <v>9.39</v>
+        <v>9.94</v>
       </c>
       <c r="F38">
-        <v>9.39</v>
+        <v>9.94</v>
       </c>
       <c r="G38">
-        <v>9.34</v>
+        <v>10.28</v>
       </c>
       <c r="H38" s="4">
-        <v>98085.37</v>
+        <v>85726.52</v>
       </c>
       <c r="I38">
-        <v>3.7</v>
+        <v>4.93</v>
       </c>
       <c r="J38">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K38">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L38">
-        <v>105.44</v>
+        <v>99.13</v>
       </c>
       <c r="M38">
-        <v>14.97</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2270,37 +2546,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>27500</v>
+        <v>12060</v>
       </c>
       <c r="D39" s="3">
-        <v>-4.1799999999999997E-2</v>
+        <v>-8.9999999999999993E-3</v>
       </c>
       <c r="E39">
-        <v>12.36</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F39">
-        <v>12.36</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="G39">
-        <v>12.46</v>
+        <v>9.33</v>
       </c>
       <c r="H39" s="4">
-        <v>31515.31</v>
+        <v>19594.84</v>
       </c>
       <c r="I39">
-        <v>4.1500000000000004</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="J39">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K39">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="L39">
-        <v>91.4</v>
+        <v>98.8</v>
       </c>
       <c r="M39">
-        <v>-7.41</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2311,37 +2587,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>12090</v>
+        <v>195900</v>
       </c>
       <c r="D40" s="3">
-        <v>2.8899999999999999E-2</v>
+        <v>-9.5999999999999992E-3</v>
       </c>
       <c r="E40">
-        <v>1.55</v>
+        <v>5.94</v>
       </c>
       <c r="F40">
-        <v>1.55</v>
+        <v>5.94</v>
       </c>
       <c r="G40">
-        <v>6.05</v>
+        <v>4.49</v>
       </c>
       <c r="H40" s="4">
-        <v>29736.69</v>
+        <v>83971.72</v>
       </c>
       <c r="I40">
-        <v>2.0699999999999998</v>
+        <v>0.38</v>
       </c>
       <c r="J40">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="K40">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="L40">
-        <v>106.83</v>
+        <v>97.22</v>
       </c>
       <c r="M40">
-        <v>16.47</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2352,37 +2628,37 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>57100</v>
+        <v>19360</v>
       </c>
       <c r="D41" s="3">
-        <v>-7.0000000000000001E-3</v>
+        <v>-1.2200000000000001E-2</v>
       </c>
       <c r="E41">
-        <v>11.33</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="F41">
-        <v>11.33</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="G41">
-        <v>16.21</v>
+        <v>10.31</v>
       </c>
       <c r="H41" s="4">
-        <v>59573.64</v>
+        <v>26617.85</v>
       </c>
       <c r="I41">
-        <v>2.1</v>
+        <v>6.07</v>
       </c>
       <c r="J41">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="K41">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="L41">
-        <v>112.48</v>
+        <v>103.81</v>
       </c>
       <c r="M41">
-        <v>14.89</v>
+        <v>9.8800000000000008</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2393,37 +2669,37 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>19350</v>
+        <v>38050</v>
       </c>
       <c r="D42" s="3">
-        <v>3.5999999999999999E-3</v>
+        <v>-1.2999999999999999E-2</v>
       </c>
       <c r="E42">
-        <v>8.8800000000000008</v>
+        <v>11.61</v>
       </c>
       <c r="F42">
-        <v>8.8800000000000008</v>
+        <v>11.61</v>
       </c>
       <c r="G42">
-        <v>10.31</v>
+        <v>7.66</v>
       </c>
       <c r="H42" s="4">
-        <v>26617.85</v>
+        <v>79920.61</v>
       </c>
       <c r="I42">
-        <v>6.07</v>
+        <v>3.02</v>
       </c>
       <c r="J42">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="K42">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L42">
-        <v>105.19</v>
+        <v>98.85</v>
       </c>
       <c r="M42">
-        <v>7.44</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2434,37 +2710,1923 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>33200</v>
+        <v>1446000</v>
       </c>
       <c r="D43" s="3">
-        <v>-5.28E-2</v>
+        <v>-1.2999999999999999E-2</v>
       </c>
       <c r="E43">
+        <v>19.14</v>
+      </c>
+      <c r="F43">
+        <v>19.14</v>
+      </c>
+      <c r="G43">
+        <v>32.89</v>
+      </c>
+      <c r="H43" s="4">
+        <v>188232.86</v>
+      </c>
+      <c r="I43">
+        <v>0.48</v>
+      </c>
+      <c r="J43">
+        <v>87</v>
+      </c>
+      <c r="K43">
+        <v>87</v>
+      </c>
+      <c r="L43">
+        <v>100.14</v>
+      </c>
+      <c r="M43">
+        <v>-5.92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="2">
+        <v>19050</v>
+      </c>
+      <c r="D44" s="3">
+        <v>-1.2999999999999999E-2</v>
+      </c>
+      <c r="E44">
+        <v>7.27</v>
+      </c>
+      <c r="F44">
+        <v>7.27</v>
+      </c>
+      <c r="G44">
+        <v>5.87</v>
+      </c>
+      <c r="H44" s="4">
+        <v>38724.660000000003</v>
+      </c>
+      <c r="I44">
+        <v>3.67</v>
+      </c>
+      <c r="J44">
+        <v>81</v>
+      </c>
+      <c r="K44">
+        <v>81</v>
+      </c>
+      <c r="L44">
+        <v>104.74</v>
+      </c>
+      <c r="M44">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="2">
+        <v>51800</v>
+      </c>
+      <c r="D45" s="3">
+        <v>-1.3299999999999999E-2</v>
+      </c>
+      <c r="E45">
+        <v>7.45</v>
+      </c>
+      <c r="F45">
+        <v>7.45</v>
+      </c>
+      <c r="G45">
+        <v>7.69</v>
+      </c>
+      <c r="H45" s="4">
+        <v>79986.48</v>
+      </c>
+      <c r="I45">
+        <v>5.41</v>
+      </c>
+      <c r="J45">
+        <v>58</v>
+      </c>
+      <c r="K45">
+        <v>58</v>
+      </c>
+      <c r="L45">
+        <v>96.82</v>
+      </c>
+      <c r="M45">
+        <v>-2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="2">
+        <v>32800</v>
+      </c>
+      <c r="D46" s="3">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="E46">
         <v>8.91</v>
       </c>
-      <c r="F43">
+      <c r="F46">
         <v>8.91</v>
       </c>
-      <c r="G43">
+      <c r="G46">
         <v>8.8699999999999992</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H46" s="4">
         <v>49113.23</v>
       </c>
-      <c r="I43">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J43">
-        <v>73</v>
-      </c>
-      <c r="K43">
-        <v>73</v>
-      </c>
-      <c r="L43">
-        <v>98.35</v>
-      </c>
-      <c r="M43">
-        <v>3.59</v>
+      <c r="I46">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="J46">
+        <v>72</v>
+      </c>
+      <c r="K46">
+        <v>72</v>
+      </c>
+      <c r="L46">
+        <v>96.94</v>
+      </c>
+      <c r="M46">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="2">
+        <v>72700</v>
+      </c>
+      <c r="D47" s="3">
+        <v>-1.7600000000000001E-2</v>
+      </c>
+      <c r="E47">
+        <v>5.71</v>
+      </c>
+      <c r="F47">
+        <v>5.71</v>
+      </c>
+      <c r="G47">
+        <v>10.42</v>
+      </c>
+      <c r="H47" s="4">
+        <v>75092.259999999995</v>
+      </c>
+      <c r="I47">
+        <v>2.34</v>
+      </c>
+      <c r="J47">
+        <v>87</v>
+      </c>
+      <c r="K47">
+        <v>87</v>
+      </c>
+      <c r="L47">
+        <v>105.33</v>
+      </c>
+      <c r="M47">
+        <v>17.64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B48" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="2">
+        <v>221500</v>
+      </c>
+      <c r="D48" s="3">
+        <v>-1.77E-2</v>
+      </c>
+      <c r="E48">
+        <v>18.13</v>
+      </c>
+      <c r="F48">
+        <v>18.13</v>
+      </c>
+      <c r="G48">
+        <v>15.29</v>
+      </c>
+      <c r="H48" s="4">
+        <v>138016.06</v>
+      </c>
+      <c r="I48">
+        <v>2.62</v>
+      </c>
+      <c r="J48">
+        <v>67</v>
+      </c>
+      <c r="K48">
+        <v>67</v>
+      </c>
+      <c r="L48">
+        <v>99.78</v>
+      </c>
+      <c r="M48">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="2">
+        <v>176400</v>
+      </c>
+      <c r="D49" s="3">
+        <v>-1.78E-2</v>
+      </c>
+      <c r="E49">
+        <v>11.77</v>
+      </c>
+      <c r="F49">
+        <v>11.77</v>
+      </c>
+      <c r="G49">
+        <v>11.4</v>
+      </c>
+      <c r="H49" s="4">
+        <v>85735.74</v>
+      </c>
+      <c r="I49">
+        <v>3.4</v>
+      </c>
+      <c r="J49">
+        <v>95</v>
+      </c>
+      <c r="K49">
+        <v>95</v>
+      </c>
+      <c r="L49">
+        <v>104.91</v>
+      </c>
+      <c r="M49">
+        <v>14.03</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="2">
+        <v>37900</v>
+      </c>
+      <c r="D50" s="3">
+        <v>-1.8100000000000002E-2</v>
+      </c>
+      <c r="E50">
+        <v>1.23</v>
+      </c>
+      <c r="F50">
+        <v>1.23</v>
+      </c>
+      <c r="G50">
+        <v>1.59</v>
+      </c>
+      <c r="H50" s="4">
+        <v>118301.94</v>
+      </c>
+      <c r="I50">
+        <v>3.04</v>
+      </c>
+      <c r="J50">
+        <v>36</v>
+      </c>
+      <c r="K50">
+        <v>36</v>
+      </c>
+      <c r="L50">
+        <v>103.13</v>
+      </c>
+      <c r="M50">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="2">
+        <v>26850</v>
+      </c>
+      <c r="D51" s="3">
+        <v>-1.83E-2</v>
+      </c>
+      <c r="E51">
+        <v>12.36</v>
+      </c>
+      <c r="F51">
+        <v>12.36</v>
+      </c>
+      <c r="G51">
+        <v>12.46</v>
+      </c>
+      <c r="H51" s="4">
+        <v>31515.31</v>
+      </c>
+      <c r="I51">
+        <v>4.25</v>
+      </c>
+      <c r="J51">
+        <v>63</v>
+      </c>
+      <c r="K51">
+        <v>63</v>
+      </c>
+      <c r="L51">
+        <v>90.93</v>
+      </c>
+      <c r="M51">
+        <v>-7.41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="2">
+        <v>95600</v>
+      </c>
+      <c r="D52" s="3">
+        <v>-1.8499999999999999E-2</v>
+      </c>
+      <c r="E52">
+        <v>3.33</v>
+      </c>
+      <c r="F52">
+        <v>3.33</v>
+      </c>
+      <c r="G52">
+        <v>7.93</v>
+      </c>
+      <c r="H52" s="4">
+        <v>60299.05</v>
+      </c>
+      <c r="I52">
+        <v>1.74</v>
+      </c>
+      <c r="J52">
+        <v>88</v>
+      </c>
+      <c r="K52">
+        <v>88</v>
+      </c>
+      <c r="L52">
+        <v>103.63</v>
+      </c>
+      <c r="M52">
+        <v>17.16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="2">
+        <v>264000</v>
+      </c>
+      <c r="D53" s="3">
+        <v>-1.8599999999999998E-2</v>
+      </c>
+      <c r="E53">
+        <v>30.05</v>
+      </c>
+      <c r="F53">
+        <v>30.05</v>
+      </c>
+      <c r="G53">
+        <v>20.65</v>
+      </c>
+      <c r="H53" s="4">
+        <v>28211.09</v>
+      </c>
+      <c r="I53">
+        <v>0.23</v>
+      </c>
+      <c r="J53">
+        <v>93</v>
+      </c>
+      <c r="K53">
+        <v>93</v>
+      </c>
+      <c r="L53">
+        <v>118.75</v>
+      </c>
+      <c r="M53">
+        <v>25.12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="2">
+        <v>48800</v>
+      </c>
+      <c r="D54" s="3">
+        <v>-1.9099999999999999E-2</v>
+      </c>
+      <c r="E54">
+        <v>1.88</v>
+      </c>
+      <c r="F54">
+        <v>1.88</v>
+      </c>
+      <c r="G54">
+        <v>4.88</v>
+      </c>
+      <c r="H54" s="4">
+        <v>111168.71</v>
+      </c>
+      <c r="I54">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="J54">
+        <v>44</v>
+      </c>
+      <c r="K54">
+        <v>44</v>
+      </c>
+      <c r="L54">
+        <v>95.84</v>
+      </c>
+      <c r="M54">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B55" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="2">
+        <v>29500</v>
+      </c>
+      <c r="D55" s="3">
+        <v>-1.9900000000000001E-2</v>
+      </c>
+      <c r="E55">
+        <v>12.91</v>
+      </c>
+      <c r="F55">
+        <v>12.91</v>
+      </c>
+      <c r="G55">
+        <v>16.39</v>
+      </c>
+      <c r="H55" s="4">
+        <v>53952.89</v>
+      </c>
+      <c r="I55">
+        <v>2.37</v>
+      </c>
+      <c r="J55">
+        <v>82</v>
+      </c>
+      <c r="K55">
+        <v>82</v>
+      </c>
+      <c r="L55">
+        <v>104.82</v>
+      </c>
+      <c r="M55">
+        <v>9.8699999999999992</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A56" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="2">
+        <v>21650</v>
+      </c>
+      <c r="D56" s="3">
+        <v>-2.0400000000000001E-2</v>
+      </c>
+      <c r="E56">
+        <v>7.7</v>
+      </c>
+      <c r="F56">
+        <v>7.7</v>
+      </c>
+      <c r="G56">
+        <v>8.18</v>
+      </c>
+      <c r="H56" s="4">
+        <v>45715.519999999997</v>
+      </c>
+      <c r="I56">
+        <v>4.84</v>
+      </c>
+      <c r="J56">
+        <v>62</v>
+      </c>
+      <c r="K56">
+        <v>62</v>
+      </c>
+      <c r="L56">
+        <v>97.75</v>
+      </c>
+      <c r="M56">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A57" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="2">
+        <v>11280</v>
+      </c>
+      <c r="D57" s="3">
+        <v>-2.1700000000000001E-2</v>
+      </c>
+      <c r="E57">
+        <v>4.49</v>
+      </c>
+      <c r="F57">
+        <v>4.49</v>
+      </c>
+      <c r="G57">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="H57" s="4">
+        <v>23274.23</v>
+      </c>
+      <c r="I57">
+        <v>3.1</v>
+      </c>
+      <c r="J57">
+        <v>33</v>
+      </c>
+      <c r="K57">
+        <v>33</v>
+      </c>
+      <c r="L57">
+        <v>104.8</v>
+      </c>
+      <c r="M57">
+        <v>21.81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A58" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="2">
+        <v>8720</v>
+      </c>
+      <c r="D58" s="3">
+        <v>-2.24E-2</v>
+      </c>
+      <c r="E58">
+        <v>3.52</v>
+      </c>
+      <c r="F58">
+        <v>3.52</v>
+      </c>
+      <c r="G58">
+        <v>5.39</v>
+      </c>
+      <c r="H58" s="4">
+        <v>21278.16</v>
+      </c>
+      <c r="I58">
+        <v>2.87</v>
+      </c>
+      <c r="J58">
+        <v>47</v>
+      </c>
+      <c r="K58">
+        <v>47</v>
+      </c>
+      <c r="L58">
+        <v>95.51</v>
+      </c>
+      <c r="M58">
+        <v>-5.53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A59" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" s="2">
+        <v>9780</v>
+      </c>
+      <c r="D59" s="3">
+        <v>-2.3E-2</v>
+      </c>
+      <c r="E59">
+        <v>7.89</v>
+      </c>
+      <c r="F59">
+        <v>7.89</v>
+      </c>
+      <c r="G59">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="H59" s="4">
+        <v>10051.59</v>
+      </c>
+      <c r="I59">
+        <v>1.64</v>
+      </c>
+      <c r="J59">
+        <v>18</v>
+      </c>
+      <c r="K59">
+        <v>18</v>
+      </c>
+      <c r="L59">
+        <v>100.16</v>
+      </c>
+      <c r="M59">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A60" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" s="2">
+        <v>484000</v>
+      </c>
+      <c r="D60" s="3">
+        <v>-2.3199999999999998E-2</v>
+      </c>
+      <c r="E60">
+        <v>36.04</v>
+      </c>
+      <c r="F60">
+        <v>36.04</v>
+      </c>
+      <c r="G60">
+        <v>32.08</v>
+      </c>
+      <c r="H60" s="4">
+        <v>107970.64</v>
+      </c>
+      <c r="I60">
+        <v>7.44</v>
+      </c>
+      <c r="J60">
+        <v>70</v>
+      </c>
+      <c r="K60">
+        <v>70</v>
+      </c>
+      <c r="L60">
+        <v>97.9</v>
+      </c>
+      <c r="M60">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A61" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="2">
+        <v>96200</v>
+      </c>
+      <c r="D61" s="3">
+        <v>-2.3400000000000001E-2</v>
+      </c>
+      <c r="E61">
+        <v>8.32</v>
+      </c>
+      <c r="F61">
+        <v>8.32</v>
+      </c>
+      <c r="G61">
+        <v>6.59</v>
+      </c>
+      <c r="H61" s="4">
+        <v>170120.51</v>
+      </c>
+      <c r="I61">
+        <v>1.77</v>
+      </c>
+      <c r="J61">
+        <v>40</v>
+      </c>
+      <c r="K61">
+        <v>40</v>
+      </c>
+      <c r="L61">
+        <v>100.05</v>
+      </c>
+      <c r="M61">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A62" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="2">
+        <v>21850</v>
+      </c>
+      <c r="D62" s="3">
+        <v>-2.46E-2</v>
+      </c>
+      <c r="E62">
+        <v>16.11</v>
+      </c>
+      <c r="F62">
+        <v>16.11</v>
+      </c>
+      <c r="G62">
+        <v>13.14</v>
+      </c>
+      <c r="H62" s="4">
+        <v>21500.92</v>
+      </c>
+      <c r="I62">
+        <v>0.92</v>
+      </c>
+      <c r="J62">
+        <v>27</v>
+      </c>
+      <c r="K62">
+        <v>27</v>
+      </c>
+      <c r="L62">
+        <v>95.57</v>
+      </c>
+      <c r="M62">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="2">
+        <v>11370</v>
+      </c>
+      <c r="D63" s="3">
+        <v>-2.4899999999999999E-2</v>
+      </c>
+      <c r="E63">
+        <v>1.55</v>
+      </c>
+      <c r="F63">
+        <v>1.55</v>
+      </c>
+      <c r="G63">
+        <v>6.05</v>
+      </c>
+      <c r="H63" s="4">
+        <v>29736.69</v>
+      </c>
+      <c r="I63">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J63">
+        <v>31</v>
+      </c>
+      <c r="K63">
+        <v>31</v>
+      </c>
+      <c r="L63">
+        <v>100.03</v>
+      </c>
+      <c r="M63">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A64" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="2">
+        <v>64900</v>
+      </c>
+      <c r="D64" s="3">
+        <v>-2.5499999999999998E-2</v>
+      </c>
+      <c r="E64">
+        <v>4.42</v>
+      </c>
+      <c r="F64">
+        <v>4.42</v>
+      </c>
+      <c r="G64">
+        <v>4.58</v>
+      </c>
+      <c r="H64" s="4">
+        <v>94771.35</v>
+      </c>
+      <c r="I64">
+        <v>2.31</v>
+      </c>
+      <c r="J64">
+        <v>49</v>
+      </c>
+      <c r="K64">
+        <v>49</v>
+      </c>
+      <c r="L64">
+        <v>117.06</v>
+      </c>
+      <c r="M64">
+        <v>33.81</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B65" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="2">
+        <v>22450</v>
+      </c>
+      <c r="D65" s="3">
+        <v>-2.5999999999999999E-2</v>
+      </c>
+      <c r="E65">
+        <v>1.34</v>
+      </c>
+      <c r="F65">
+        <v>1.34</v>
+      </c>
+      <c r="G65">
+        <v>0.62</v>
+      </c>
+      <c r="H65" s="4">
+        <v>39516.26</v>
+      </c>
+      <c r="I65">
+        <v>2.67</v>
+      </c>
+      <c r="J65">
+        <v>44</v>
+      </c>
+      <c r="K65">
+        <v>44</v>
+      </c>
+      <c r="L65">
+        <v>98.6</v>
+      </c>
+      <c r="M65">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A66" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B66" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="2">
+        <v>49750</v>
+      </c>
+      <c r="D66" s="3">
+        <v>-2.64E-2</v>
+      </c>
+      <c r="E66">
+        <v>15.02</v>
+      </c>
+      <c r="F66">
+        <v>15.02</v>
+      </c>
+      <c r="G66">
+        <v>20.7</v>
+      </c>
+      <c r="H66" s="4">
+        <v>34750.239999999998</v>
+      </c>
+      <c r="I66">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="J66">
+        <v>93</v>
+      </c>
+      <c r="K66">
+        <v>93</v>
+      </c>
+      <c r="L66">
+        <v>125.11</v>
+      </c>
+      <c r="M66">
+        <v>44.41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A67" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="2">
+        <v>88100</v>
+      </c>
+      <c r="D67" s="3">
+        <v>-2.6499999999999999E-2</v>
+      </c>
+      <c r="E67">
+        <v>8.81</v>
+      </c>
+      <c r="F67">
+        <v>8.81</v>
+      </c>
+      <c r="G67">
+        <v>6.32</v>
+      </c>
+      <c r="H67" s="4">
+        <v>31276.98</v>
+      </c>
+      <c r="I67">
+        <v>0.68</v>
+      </c>
+      <c r="J67">
+        <v>34</v>
+      </c>
+      <c r="K67">
+        <v>34</v>
+      </c>
+      <c r="L67">
+        <v>93.66</v>
+      </c>
+      <c r="M67">
+        <v>-3.61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A68" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" s="2">
+        <v>162300</v>
+      </c>
+      <c r="D68" s="3">
+        <v>-2.7E-2</v>
+      </c>
+      <c r="E68">
+        <v>17.72</v>
+      </c>
+      <c r="F68">
+        <v>17.72</v>
+      </c>
+      <c r="G68">
+        <v>17.440000000000001</v>
+      </c>
+      <c r="H68" s="4">
+        <v>158606.49</v>
+      </c>
+      <c r="I68">
+        <v>4.68</v>
+      </c>
+      <c r="J68">
+        <v>69</v>
+      </c>
+      <c r="K68">
+        <v>69</v>
+      </c>
+      <c r="L68">
+        <v>96.53</v>
+      </c>
+      <c r="M68">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="2">
+        <v>456500</v>
+      </c>
+      <c r="D69" s="3">
+        <v>-2.7699999999999999E-2</v>
+      </c>
+      <c r="E69">
+        <v>17.78</v>
+      </c>
+      <c r="F69">
+        <v>17.78</v>
+      </c>
+      <c r="G69">
+        <v>10.4</v>
+      </c>
+      <c r="H69" s="4">
+        <v>187876.56</v>
+      </c>
+      <c r="I69">
+        <v>2.69</v>
+      </c>
+      <c r="J69">
+        <v>91</v>
+      </c>
+      <c r="K69">
+        <v>91</v>
+      </c>
+      <c r="L69">
+        <v>109.47</v>
+      </c>
+      <c r="M69">
+        <v>21.41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="2">
+        <v>140400</v>
+      </c>
+      <c r="D70" s="3">
+        <v>-2.7699999999999999E-2</v>
+      </c>
+      <c r="E70">
+        <v>4.74</v>
+      </c>
+      <c r="F70">
+        <v>4.74</v>
+      </c>
+      <c r="G70">
+        <v>6.13</v>
+      </c>
+      <c r="H70" s="4">
+        <v>215808.28</v>
+      </c>
+      <c r="I70">
+        <v>1.21</v>
+      </c>
+      <c r="J70">
+        <v>35</v>
+      </c>
+      <c r="K70">
+        <v>35</v>
+      </c>
+      <c r="L70">
+        <v>105.67</v>
+      </c>
+      <c r="M70">
+        <v>13.68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A71" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" s="2">
+        <v>58900</v>
+      </c>
+      <c r="D71" s="3">
+        <v>-2.81E-2</v>
+      </c>
+      <c r="E71">
+        <v>10.220000000000001</v>
+      </c>
+      <c r="F71">
+        <v>10.220000000000001</v>
+      </c>
+      <c r="G71">
+        <v>6.37</v>
+      </c>
+      <c r="H71" s="4">
+        <v>71885.83</v>
+      </c>
+      <c r="I71">
+        <v>4.07</v>
+      </c>
+      <c r="J71">
+        <v>74</v>
+      </c>
+      <c r="K71">
+        <v>74</v>
+      </c>
+      <c r="L71">
+        <v>95.8</v>
+      </c>
+      <c r="M71">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A72" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" s="2">
+        <v>7140</v>
+      </c>
+      <c r="D72" s="3">
+        <v>-2.86E-2</v>
+      </c>
+      <c r="E72">
+        <v>7.71</v>
+      </c>
+      <c r="F72">
+        <v>7.71</v>
+      </c>
+      <c r="G72">
+        <v>7.02</v>
+      </c>
+      <c r="H72" s="4">
+        <v>19706.72</v>
+      </c>
+      <c r="I72">
+        <v>2.8</v>
+      </c>
+      <c r="J72">
+        <v>34</v>
+      </c>
+      <c r="K72">
+        <v>34</v>
+      </c>
+      <c r="L72">
+        <v>96.22</v>
+      </c>
+      <c r="M72">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A73" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" s="2">
+        <v>15530</v>
+      </c>
+      <c r="D73" s="3">
+        <v>-2.8799999999999999E-2</v>
+      </c>
+      <c r="E73">
+        <v>6.01</v>
+      </c>
+      <c r="F73">
+        <v>6.01</v>
+      </c>
+      <c r="G73">
+        <v>5.97</v>
+      </c>
+      <c r="H73" s="4">
+        <v>20769.650000000001</v>
+      </c>
+      <c r="I73">
+        <v>4.25</v>
+      </c>
+      <c r="J73">
+        <v>67</v>
+      </c>
+      <c r="K73">
+        <v>67</v>
+      </c>
+      <c r="L73">
+        <v>94.38</v>
+      </c>
+      <c r="M73">
+        <v>-2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A74" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="2">
+        <v>59500</v>
+      </c>
+      <c r="D74" s="3">
+        <v>-2.9399999999999999E-2</v>
+      </c>
+      <c r="E74">
+        <v>11.33</v>
+      </c>
+      <c r="F74">
+        <v>11.33</v>
+      </c>
+      <c r="G74">
+        <v>16.21</v>
+      </c>
+      <c r="H74" s="4">
+        <v>59573.64</v>
+      </c>
+      <c r="I74">
+        <v>2.02</v>
+      </c>
+      <c r="J74">
+        <v>68</v>
+      </c>
+      <c r="K74">
+        <v>68</v>
+      </c>
+      <c r="L74">
+        <v>112.31</v>
+      </c>
+      <c r="M74">
+        <v>24.22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A75" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75" s="2">
+        <v>16450</v>
+      </c>
+      <c r="D75" s="3">
+        <v>-2.9499999999999998E-2</v>
+      </c>
+      <c r="E75">
+        <v>8.11</v>
+      </c>
+      <c r="F75">
+        <v>8.11</v>
+      </c>
+      <c r="G75">
+        <v>9.93</v>
+      </c>
+      <c r="H75" s="4">
+        <v>19583.27</v>
+      </c>
+      <c r="I75">
+        <v>5.78</v>
+      </c>
+      <c r="J75">
+        <v>19</v>
+      </c>
+      <c r="K75">
+        <v>19</v>
+      </c>
+      <c r="L75">
+        <v>97.29</v>
+      </c>
+      <c r="M75">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="2">
+        <v>97100</v>
+      </c>
+      <c r="D76" s="3">
+        <v>-0.03</v>
+      </c>
+      <c r="E76">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="F76">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="G76">
+        <v>20.22</v>
+      </c>
+      <c r="H76" s="4">
+        <v>37882.559999999998</v>
+      </c>
+      <c r="I76">
+        <v>14.43</v>
+      </c>
+      <c r="J76">
+        <v>82</v>
+      </c>
+      <c r="K76">
+        <v>82</v>
+      </c>
+      <c r="L76">
+        <v>102.68</v>
+      </c>
+      <c r="M76">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A77" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B77" t="s">
+        <v>162</v>
+      </c>
+      <c r="C77" s="2">
+        <v>205000</v>
+      </c>
+      <c r="D77" s="3">
+        <v>-3.0700000000000002E-2</v>
+      </c>
+      <c r="E77">
+        <v>12.83</v>
+      </c>
+      <c r="F77">
+        <v>12.83</v>
+      </c>
+      <c r="G77">
+        <v>14.29</v>
+      </c>
+      <c r="H77" s="4">
+        <v>223707.87</v>
+      </c>
+      <c r="I77">
+        <v>3.21</v>
+      </c>
+      <c r="J77">
+        <v>74</v>
+      </c>
+      <c r="K77">
+        <v>74</v>
+      </c>
+      <c r="L77">
+        <v>96.53</v>
+      </c>
+      <c r="M77">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A78" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B78" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" s="2">
+        <v>59600</v>
+      </c>
+      <c r="D78" s="3">
+        <v>-3.09E-2</v>
+      </c>
+      <c r="E78">
+        <v>9.39</v>
+      </c>
+      <c r="F78">
+        <v>9.39</v>
+      </c>
+      <c r="G78">
+        <v>9.34</v>
+      </c>
+      <c r="H78" s="4">
+        <v>98085.37</v>
+      </c>
+      <c r="I78">
+        <v>3.86</v>
+      </c>
+      <c r="J78">
+        <v>61</v>
+      </c>
+      <c r="K78">
+        <v>61</v>
+      </c>
+      <c r="L78">
+        <v>99.73</v>
+      </c>
+      <c r="M78">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A79" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B79" t="s">
+        <v>166</v>
+      </c>
+      <c r="C79" s="2">
+        <v>19130</v>
+      </c>
+      <c r="D79" s="3">
+        <v>-3.1399999999999997E-2</v>
+      </c>
+      <c r="E79">
+        <v>13.7</v>
+      </c>
+      <c r="F79">
+        <v>13.7</v>
+      </c>
+      <c r="G79">
+        <v>14.6</v>
+      </c>
+      <c r="H79" s="4">
+        <v>16125.49</v>
+      </c>
+      <c r="I79">
+        <v>6.43</v>
+      </c>
+      <c r="J79">
+        <v>27</v>
+      </c>
+      <c r="K79">
+        <v>27</v>
+      </c>
+      <c r="L79">
+        <v>98</v>
+      </c>
+      <c r="M79">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A80" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B80" t="s">
+        <v>168</v>
+      </c>
+      <c r="C80" s="2">
+        <v>83100</v>
+      </c>
+      <c r="D80" s="3">
+        <v>-3.4799999999999998E-2</v>
+      </c>
+      <c r="E80">
+        <v>8.17</v>
+      </c>
+      <c r="F80">
+        <v>8.17</v>
+      </c>
+      <c r="G80">
+        <v>16.829999999999998</v>
+      </c>
+      <c r="H80" s="4">
+        <v>77497.08</v>
+      </c>
+      <c r="I80">
+        <v>0.6</v>
+      </c>
+      <c r="J80">
+        <v>29</v>
+      </c>
+      <c r="K80">
+        <v>29</v>
+      </c>
+      <c r="L80">
+        <v>94.45</v>
+      </c>
+      <c r="M80">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A81" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B81" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" s="2">
+        <v>22100</v>
+      </c>
+      <c r="D81" s="3">
+        <v>-3.49E-2</v>
+      </c>
+      <c r="E81">
+        <v>2.35</v>
+      </c>
+      <c r="F81">
+        <v>2.35</v>
+      </c>
+      <c r="G81">
+        <v>5.13</v>
+      </c>
+      <c r="H81" s="4">
+        <v>28166.48</v>
+      </c>
+      <c r="I81">
+        <v>3.17</v>
+      </c>
+      <c r="J81">
+        <v>16</v>
+      </c>
+      <c r="K81">
+        <v>16</v>
+      </c>
+      <c r="L81">
+        <v>101.55</v>
+      </c>
+      <c r="M81">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A82" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82" s="2">
+        <v>24400</v>
+      </c>
+      <c r="D82" s="3">
+        <v>-3.56E-2</v>
+      </c>
+      <c r="E82">
+        <v>7.52</v>
+      </c>
+      <c r="F82">
+        <v>7.52</v>
+      </c>
+      <c r="G82">
+        <v>6.85</v>
+      </c>
+      <c r="H82" s="4">
+        <v>50396.34</v>
+      </c>
+      <c r="I82">
+        <v>4.51</v>
+      </c>
+      <c r="J82">
+        <v>54</v>
+      </c>
+      <c r="K82">
+        <v>54</v>
+      </c>
+      <c r="L82">
+        <v>99.13</v>
+      </c>
+      <c r="M82">
+        <v>7.02</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A83" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B83" t="s">
+        <v>174</v>
+      </c>
+      <c r="C83" s="2">
+        <v>83500</v>
+      </c>
+      <c r="D83" s="3">
+        <v>-3.6900000000000002E-2</v>
+      </c>
+      <c r="E83">
+        <v>18.14</v>
+      </c>
+      <c r="F83">
+        <v>18.14</v>
+      </c>
+      <c r="G83">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="H83" s="4">
+        <v>51783.79</v>
+      </c>
+      <c r="I83">
+        <v>2.36</v>
+      </c>
+      <c r="J83">
+        <v>58</v>
+      </c>
+      <c r="K83">
+        <v>58</v>
+      </c>
+      <c r="L83">
+        <v>104.24</v>
+      </c>
+      <c r="M83">
+        <v>7.33</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A84" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" t="s">
+        <v>176</v>
+      </c>
+      <c r="C84" s="2">
+        <v>83900</v>
+      </c>
+      <c r="D84" s="3">
+        <v>-3.8899999999999997E-2</v>
+      </c>
+      <c r="E84">
+        <v>9.27</v>
+      </c>
+      <c r="F84">
+        <v>9.27</v>
+      </c>
+      <c r="G84">
+        <v>10.26</v>
+      </c>
+      <c r="H84" s="4">
+        <v>38290.26</v>
+      </c>
+      <c r="I84">
+        <v>2.21</v>
+      </c>
+      <c r="J84">
+        <v>84</v>
+      </c>
+      <c r="K84">
+        <v>84</v>
+      </c>
+      <c r="L84">
+        <v>106.76</v>
+      </c>
+      <c r="M84">
+        <v>9.39</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A85" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B85" t="s">
+        <v>178</v>
+      </c>
+      <c r="C85" s="2">
+        <v>5550</v>
+      </c>
+      <c r="D85" s="3">
+        <v>-3.9800000000000002E-2</v>
+      </c>
+      <c r="E85">
+        <v>9.61</v>
+      </c>
+      <c r="F85">
+        <v>9.61</v>
+      </c>
+      <c r="G85">
+        <v>7.43</v>
+      </c>
+      <c r="H85" s="4">
+        <v>12231.94</v>
+      </c>
+      <c r="I85">
+        <v>2.88</v>
+      </c>
+      <c r="J85">
+        <v>67</v>
+      </c>
+      <c r="K85">
+        <v>67</v>
+      </c>
+      <c r="L85">
+        <v>106.65</v>
+      </c>
+      <c r="M85">
+        <v>14.43</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A86" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B86" t="s">
+        <v>180</v>
+      </c>
+      <c r="C86" s="2">
+        <v>120700</v>
+      </c>
+      <c r="D86" s="3">
+        <v>-4.5100000000000001E-2</v>
+      </c>
+      <c r="E86">
+        <v>3.13</v>
+      </c>
+      <c r="F86">
+        <v>3.13</v>
+      </c>
+      <c r="G86">
+        <v>6.24</v>
+      </c>
+      <c r="H86" s="4">
+        <v>151359.46</v>
+      </c>
+      <c r="I86">
+        <v>2.82</v>
+      </c>
+      <c r="J86">
+        <v>19</v>
+      </c>
+      <c r="K86">
+        <v>19</v>
+      </c>
+      <c r="L86">
+        <v>101.19</v>
+      </c>
+      <c r="M86">
+        <v>5.88</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A87" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B87" t="s">
+        <v>182</v>
+      </c>
+      <c r="C87" s="2">
+        <v>288500</v>
+      </c>
+      <c r="D87" s="3">
+        <v>-4.6300000000000001E-2</v>
+      </c>
+      <c r="E87">
+        <v>10.25</v>
+      </c>
+      <c r="F87">
+        <v>10.25</v>
+      </c>
+      <c r="G87">
+        <v>6.73</v>
+      </c>
+      <c r="H87" s="4">
+        <v>134263.78</v>
+      </c>
+      <c r="I87">
+        <v>1.39</v>
+      </c>
+      <c r="J87">
+        <v>85</v>
+      </c>
+      <c r="K87">
+        <v>85</v>
+      </c>
+      <c r="L87">
+        <v>109.45</v>
+      </c>
+      <c r="M87">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A88" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B88" t="s">
+        <v>184</v>
+      </c>
+      <c r="C88" s="2">
+        <v>77000</v>
+      </c>
+      <c r="D88" s="3">
+        <v>-4.82E-2</v>
+      </c>
+      <c r="E88">
+        <v>5.55</v>
+      </c>
+      <c r="F88">
+        <v>5.55</v>
+      </c>
+      <c r="G88">
+        <v>6.57</v>
+      </c>
+      <c r="H88" s="4">
+        <v>155269.29999999999</v>
+      </c>
+      <c r="I88">
+        <v>3.9</v>
+      </c>
+      <c r="J88">
+        <v>86</v>
+      </c>
+      <c r="K88">
+        <v>86</v>
+      </c>
+      <c r="L88">
+        <v>106.92</v>
+      </c>
+      <c r="M88">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A89" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B89" t="s">
+        <v>186</v>
+      </c>
+      <c r="C89" s="2">
+        <v>49700</v>
+      </c>
+      <c r="D89" s="3">
+        <v>-4.9700000000000001E-2</v>
+      </c>
+      <c r="E89">
+        <v>5.22</v>
+      </c>
+      <c r="F89">
+        <v>5.22</v>
+      </c>
+      <c r="G89">
+        <v>5.84</v>
+      </c>
+      <c r="H89" s="4">
+        <v>72566.75</v>
+      </c>
+      <c r="I89">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="J89">
+        <v>77</v>
+      </c>
+      <c r="K89">
+        <v>77</v>
+      </c>
+      <c r="L89">
+        <v>97.34</v>
+      </c>
+      <c r="M89">
+        <v>-1.78</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40BEA4C1-23B6-4D36-B1FB-025FFA2F0439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{742C5587-AE8C-4222-A7FC-104DE6CD6860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{07E71999-AD25-469E-B9FD-11ACD2A826CF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{FA3E43D3-216A-41E5-B6D3-E11E0DBDEE08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="97">
   <si>
     <t>종목코드</t>
   </si>
@@ -100,6 +100,12 @@
   </si>
   <si>
     <t>아세아제지</t>
+  </si>
+  <si>
+    <t>003300</t>
+  </si>
+  <si>
+    <t>한일홀딩스</t>
   </si>
   <si>
     <t>003540</t>
@@ -355,7 +361,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -369,6 +375,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -684,14 +693,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B86656A2-ED81-412B-B0C7-BCA002DEA194}">
-  <dimension ref="A1:M43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF557A4-D915-415E-837C-52060C745A6F}">
+  <dimension ref="A1:M44"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -750,10 +759,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>24450</v>
+        <v>25100</v>
       </c>
       <c r="D2" s="3">
-        <v>-3.3599999999999998E-2</v>
+        <v>3.2899999999999999E-2</v>
       </c>
       <c r="E2">
         <v>7.52</v>
@@ -768,19 +777,19 @@
         <v>50396.34</v>
       </c>
       <c r="I2">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="J2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L2">
-        <v>99.33</v>
+        <v>101.81</v>
       </c>
       <c r="M2">
-        <v>7.24</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -791,10 +800,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>154900</v>
+        <v>157600</v>
       </c>
       <c r="D3" s="3">
-        <v>5.7999999999999996E-3</v>
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="E3">
         <v>12.92</v>
@@ -809,19 +818,19 @@
         <v>157169.68</v>
       </c>
       <c r="I3">
-        <v>4.3899999999999997</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="J3">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K3">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L3">
-        <v>100.78</v>
+        <v>102.21</v>
       </c>
       <c r="M3">
-        <v>2.72</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -832,10 +841,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>483000</v>
+        <v>490000</v>
       </c>
       <c r="D4" s="3">
-        <v>2.01E-2</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="E4">
         <v>10.96</v>
@@ -850,19 +859,19 @@
         <v>457603.51</v>
       </c>
       <c r="I4">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="J4">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K4">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L4">
-        <v>103.71</v>
+        <v>104.79</v>
       </c>
       <c r="M4">
-        <v>8.17</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -873,10 +882,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>49700</v>
+        <v>48550</v>
       </c>
       <c r="D5" s="3">
-        <v>-4.9700000000000001E-2</v>
+        <v>-2.6100000000000002E-2</v>
       </c>
       <c r="E5">
         <v>5.22</v>
@@ -891,19 +900,19 @@
         <v>72566.75</v>
       </c>
       <c r="I5">
-        <v>4.0199999999999996</v>
+        <v>4.12</v>
       </c>
       <c r="J5">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K5">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L5">
-        <v>97.34</v>
+        <v>94.83</v>
       </c>
       <c r="M5">
-        <v>-1.78</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -914,10 +923,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>79600</v>
+        <v>75100</v>
       </c>
       <c r="D6" s="3">
-        <v>4.19E-2</v>
+        <v>-4.9399999999999999E-2</v>
       </c>
       <c r="E6">
         <v>5.69</v>
@@ -932,19 +941,19 @@
         <v>66692.75</v>
       </c>
       <c r="I6">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="J6">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K6">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L6">
-        <v>106.31</v>
+        <v>100.27</v>
       </c>
       <c r="M6">
-        <v>11.33</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -955,10 +964,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>71600</v>
+        <v>69700</v>
       </c>
       <c r="D7" s="3">
-        <v>-2.8E-3</v>
+        <v>-1.83E-2</v>
       </c>
       <c r="E7">
         <v>2.89</v>
@@ -973,19 +982,19 @@
         <v>54191.72</v>
       </c>
       <c r="I7">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="J7">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K7">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L7">
-        <v>103.05</v>
+        <v>100.05</v>
       </c>
       <c r="M7">
-        <v>8.32</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -996,10 +1005,10 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>8720</v>
+        <v>8610</v>
       </c>
       <c r="D8" s="3">
-        <v>-2.24E-2</v>
+        <v>-9.1999999999999998E-3</v>
       </c>
       <c r="E8">
         <v>3.52</v>
@@ -1014,19 +1023,19 @@
         <v>21278.16</v>
       </c>
       <c r="I8">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="J8">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K8">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L8">
-        <v>95.51</v>
+        <v>94.27</v>
       </c>
       <c r="M8">
-        <v>-5.53</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1037,37 +1046,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>42100</v>
+        <v>17100</v>
       </c>
       <c r="D9" s="3">
-        <v>5.3800000000000001E-2</v>
+        <v>5.3E-3</v>
       </c>
       <c r="E9">
-        <v>5.0599999999999996</v>
+        <v>1.91</v>
       </c>
       <c r="F9">
-        <v>5.0599999999999996</v>
+        <v>1.91</v>
       </c>
       <c r="G9">
-        <v>4.7699999999999996</v>
+        <v>5.53</v>
       </c>
       <c r="H9" s="4">
-        <v>45197.48</v>
+        <v>54471.92</v>
       </c>
       <c r="I9">
-        <v>2.85</v>
+        <v>5.85</v>
       </c>
       <c r="J9">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="K9">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="L9">
-        <v>110.45</v>
+        <v>99.18</v>
       </c>
       <c r="M9">
-        <v>16.62</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1078,37 +1087,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>102800</v>
+        <v>39700</v>
       </c>
       <c r="D10" s="3">
-        <v>4.8999999999999998E-3</v>
+        <v>-5.9200000000000003E-2</v>
       </c>
       <c r="E10">
-        <v>2.64</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="F10">
-        <v>2.64</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="G10">
-        <v>3.23</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="H10" s="4">
-        <v>184176.03</v>
+        <v>45197.48</v>
       </c>
       <c r="I10">
         <v>3.02</v>
       </c>
       <c r="J10">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="K10">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="L10">
-        <v>110.26</v>
+        <v>103.66</v>
       </c>
       <c r="M10">
-        <v>17.350000000000001</v>
+        <v>4.0599999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1119,37 +1128,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>12080</v>
+        <v>104600</v>
       </c>
       <c r="D11" s="3">
-        <v>-7.4000000000000003E-3</v>
+        <v>1.55E-2</v>
       </c>
       <c r="E11">
-        <v>9.0299999999999994</v>
+        <v>2.64</v>
       </c>
       <c r="F11">
-        <v>9.0299999999999994</v>
+        <v>2.64</v>
       </c>
       <c r="G11">
-        <v>9.33</v>
+        <v>3.23</v>
       </c>
       <c r="H11" s="4">
-        <v>19594.84</v>
+        <v>184176.03</v>
       </c>
       <c r="I11">
-        <v>4.72</v>
+        <v>2.96</v>
       </c>
       <c r="J11">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="K11">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="L11">
-        <v>98.96</v>
+        <v>111.14</v>
       </c>
       <c r="M11">
-        <v>-0.57999999999999996</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1160,37 +1169,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>11310</v>
+        <v>12120</v>
       </c>
       <c r="D12" s="3">
-        <v>-1.9099999999999999E-2</v>
+        <v>6.6E-3</v>
       </c>
       <c r="E12">
-        <v>4.49</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F12">
-        <v>4.49</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="G12">
-        <v>9.0299999999999994</v>
+        <v>9.33</v>
       </c>
       <c r="H12" s="4">
-        <v>23274.23</v>
+        <v>19594.84</v>
       </c>
       <c r="I12">
-        <v>3.09</v>
+        <v>4.7</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K12">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="L12">
-        <v>105.06</v>
+        <v>99.34</v>
       </c>
       <c r="M12">
-        <v>22.14</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1201,37 +1210,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>552000</v>
+        <v>11320</v>
       </c>
       <c r="D13" s="3">
-        <v>2.41E-2</v>
+        <v>-1.0500000000000001E-2</v>
       </c>
       <c r="E13">
-        <v>8.41</v>
+        <v>4.49</v>
       </c>
       <c r="F13">
-        <v>8.41</v>
+        <v>4.49</v>
       </c>
       <c r="G13">
-        <v>11.51</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="H13" s="4">
-        <v>436418.31</v>
+        <v>23274.23</v>
       </c>
       <c r="I13">
-        <v>1.81</v>
+        <v>3.09</v>
       </c>
       <c r="J13">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="K13">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="L13">
-        <v>108.11</v>
+        <v>104.18</v>
       </c>
       <c r="M13">
-        <v>16.7</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1242,37 +1251,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>161900</v>
+        <v>572000</v>
       </c>
       <c r="D14" s="3">
-        <v>-2.9399999999999999E-2</v>
+        <v>0.04</v>
       </c>
       <c r="E14">
-        <v>17.72</v>
+        <v>8.41</v>
       </c>
       <c r="F14">
-        <v>17.72</v>
+        <v>8.41</v>
       </c>
       <c r="G14">
-        <v>17.440000000000001</v>
+        <v>11.51</v>
       </c>
       <c r="H14" s="4">
-        <v>158606.49</v>
+        <v>436418.31</v>
       </c>
       <c r="I14">
-        <v>4.6900000000000004</v>
+        <v>1.75</v>
       </c>
       <c r="J14">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="K14">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="L14">
-        <v>96.3</v>
+        <v>110.94</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1283,37 +1292,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>38900</v>
+        <v>165000</v>
       </c>
       <c r="D15" s="3">
-        <v>6.7199999999999996E-2</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="E15">
-        <v>11.76</v>
+        <v>17.72</v>
       </c>
       <c r="F15">
-        <v>11.76</v>
+        <v>17.72</v>
       </c>
       <c r="G15">
-        <v>9.33</v>
+        <v>17.440000000000001</v>
       </c>
       <c r="H15" s="4">
-        <v>25179.95</v>
+        <v>158606.49</v>
       </c>
       <c r="I15">
-        <v>3.34</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="J15">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="K15">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="L15">
-        <v>114.53</v>
+        <v>98.12</v>
       </c>
       <c r="M15">
-        <v>27.33</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1324,37 +1333,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>49800</v>
+        <v>37700</v>
       </c>
       <c r="D16" s="3">
-        <v>-2.5399999999999999E-2</v>
+        <v>-1.95E-2</v>
       </c>
       <c r="E16">
-        <v>15.02</v>
+        <v>11.76</v>
       </c>
       <c r="F16">
-        <v>15.02</v>
+        <v>11.76</v>
       </c>
       <c r="G16">
-        <v>20.7</v>
+        <v>9.33</v>
       </c>
       <c r="H16" s="4">
-        <v>34750.239999999998</v>
+        <v>25179.95</v>
       </c>
       <c r="I16">
-        <v>2.0099999999999998</v>
+        <v>3.45</v>
       </c>
       <c r="J16">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="K16">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="L16">
-        <v>125.23</v>
+        <v>110.01</v>
       </c>
       <c r="M16">
-        <v>44.56</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1365,37 +1374,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>205000</v>
+        <v>51200</v>
       </c>
       <c r="D17" s="3">
-        <v>-3.0700000000000002E-2</v>
+        <v>3.4299999999999997E-2</v>
       </c>
       <c r="E17">
-        <v>12.83</v>
+        <v>15.02</v>
       </c>
       <c r="F17">
-        <v>12.83</v>
+        <v>15.02</v>
       </c>
       <c r="G17">
-        <v>14.29</v>
+        <v>20.7</v>
       </c>
       <c r="H17" s="4">
-        <v>223707.87</v>
+        <v>34750.239999999998</v>
       </c>
       <c r="I17">
-        <v>3.21</v>
+        <v>1.95</v>
       </c>
       <c r="J17">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="K17">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L17">
-        <v>96.53</v>
+        <v>127.12</v>
       </c>
       <c r="M17">
-        <v>-0.24</v>
+        <v>40.85</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1406,37 +1415,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>140100</v>
+        <v>211500</v>
       </c>
       <c r="D18" s="3">
-        <v>-2.98E-2</v>
+        <v>4.19E-2</v>
       </c>
       <c r="E18">
-        <v>4.74</v>
+        <v>12.83</v>
       </c>
       <c r="F18">
-        <v>4.74</v>
+        <v>12.83</v>
       </c>
       <c r="G18">
-        <v>6.13</v>
+        <v>14.29</v>
       </c>
       <c r="H18" s="4">
-        <v>215808.28</v>
+        <v>223707.87</v>
       </c>
       <c r="I18">
-        <v>1.21</v>
+        <v>3.11</v>
       </c>
       <c r="J18">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="K18">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="L18">
-        <v>105.45</v>
+        <v>99.76</v>
       </c>
       <c r="M18">
-        <v>13.44</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1447,37 +1456,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>150900</v>
+        <v>131800</v>
       </c>
       <c r="D19" s="3">
-        <v>9.4299999999999995E-2</v>
+        <v>-5.9200000000000003E-2</v>
       </c>
       <c r="E19">
-        <v>13.09</v>
+        <v>4.74</v>
       </c>
       <c r="F19">
-        <v>13.09</v>
+        <v>4.74</v>
       </c>
       <c r="G19">
-        <v>11.51</v>
+        <v>6.13</v>
       </c>
       <c r="H19" s="4">
-        <v>90347.77</v>
+        <v>215808.28</v>
       </c>
       <c r="I19">
-        <v>2.65</v>
+        <v>1.29</v>
       </c>
       <c r="J19">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="K19">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="L19">
-        <v>139.07</v>
+        <v>98.79</v>
       </c>
       <c r="M19">
-        <v>58.51</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1488,37 +1497,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>95700</v>
+        <v>145200</v>
       </c>
       <c r="D20" s="3">
-        <v>-1.7500000000000002E-2</v>
+        <v>-2.8799999999999999E-2</v>
       </c>
       <c r="E20">
-        <v>3.33</v>
+        <v>13.09</v>
       </c>
       <c r="F20">
-        <v>3.33</v>
+        <v>13.09</v>
       </c>
       <c r="G20">
-        <v>7.93</v>
+        <v>11.51</v>
       </c>
       <c r="H20" s="4">
-        <v>60299.05</v>
+        <v>90347.77</v>
       </c>
       <c r="I20">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="J20">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K20">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L20">
-        <v>103.73</v>
+        <v>131.33000000000001</v>
       </c>
       <c r="M20">
-        <v>17.28</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1529,37 +1538,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>97000</v>
+        <v>93200</v>
       </c>
       <c r="D21" s="3">
-        <v>-3.1E-2</v>
+        <v>-2.41E-2</v>
       </c>
       <c r="E21">
-        <v>20.100000000000001</v>
+        <v>3.33</v>
       </c>
       <c r="F21">
-        <v>20.100000000000001</v>
+        <v>3.33</v>
       </c>
       <c r="G21">
-        <v>20.22</v>
+        <v>7.93</v>
       </c>
       <c r="H21" s="4">
-        <v>37882.559999999998</v>
+        <v>60299.05</v>
       </c>
       <c r="I21">
-        <v>14.44</v>
+        <v>1.78</v>
       </c>
       <c r="J21">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K21">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L21">
-        <v>102.58</v>
+        <v>100.3</v>
       </c>
       <c r="M21">
-        <v>10.98</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1570,37 +1579,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>21650</v>
+        <v>98600</v>
       </c>
       <c r="D22" s="3">
-        <v>-2.0400000000000001E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="E22">
-        <v>7.7</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="F22">
-        <v>7.7</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="G22">
-        <v>8.18</v>
+        <v>20.22</v>
       </c>
       <c r="H22" s="4">
-        <v>45715.519999999997</v>
+        <v>37882.559999999998</v>
       </c>
       <c r="I22">
-        <v>4.84</v>
+        <v>14.21</v>
       </c>
       <c r="J22">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="K22">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="L22">
-        <v>97.75</v>
+        <v>103.6</v>
       </c>
       <c r="M22">
-        <v>1.41</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1611,37 +1620,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>51800</v>
+        <v>21750</v>
       </c>
       <c r="D23" s="3">
-        <v>-1.3299999999999999E-2</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="E23">
-        <v>7.45</v>
+        <v>7.7</v>
       </c>
       <c r="F23">
-        <v>7.45</v>
+        <v>7.7</v>
       </c>
       <c r="G23">
-        <v>7.69</v>
+        <v>8.18</v>
       </c>
       <c r="H23" s="4">
-        <v>79986.48</v>
+        <v>45715.519999999997</v>
       </c>
       <c r="I23">
-        <v>5.41</v>
+        <v>4.82</v>
       </c>
       <c r="J23">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K23">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L23">
-        <v>96.82</v>
+        <v>98.14</v>
       </c>
       <c r="M23">
-        <v>-2.2599999999999998</v>
+        <v>-1.1399999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1652,37 +1661,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>19120</v>
-      </c>
-      <c r="D24" s="3">
-        <v>-3.1899999999999998E-2</v>
+        <v>51600</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>13.7</v>
+        <v>7.45</v>
       </c>
       <c r="F24">
-        <v>13.7</v>
+        <v>7.45</v>
       </c>
       <c r="G24">
-        <v>14.6</v>
+        <v>7.69</v>
       </c>
       <c r="H24" s="4">
-        <v>16125.49</v>
+        <v>79986.48</v>
       </c>
       <c r="I24">
-        <v>6.43</v>
+        <v>5.43</v>
       </c>
       <c r="J24">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="K24">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="L24">
-        <v>97.95</v>
+        <v>96.57</v>
       </c>
       <c r="M24">
-        <v>-0.36</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1693,37 +1702,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>58800</v>
+        <v>19180</v>
       </c>
       <c r="D25" s="3">
-        <v>-2.9700000000000001E-2</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="E25">
-        <v>10.220000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="F25">
-        <v>10.220000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="G25">
-        <v>6.37</v>
+        <v>14.6</v>
       </c>
       <c r="H25" s="4">
-        <v>71885.83</v>
+        <v>16125.49</v>
       </c>
       <c r="I25">
-        <v>4.08</v>
+        <v>6.41</v>
       </c>
       <c r="J25">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="K25">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="L25">
-        <v>95.64</v>
+        <v>98.22</v>
       </c>
       <c r="M25">
-        <v>-0.51</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1734,37 +1743,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>15530</v>
+        <v>59500</v>
       </c>
       <c r="D26" s="3">
-        <v>-2.8799999999999999E-2</v>
+        <v>1.7100000000000001E-2</v>
       </c>
       <c r="E26">
-        <v>6.01</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="F26">
-        <v>6.01</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="G26">
-        <v>5.97</v>
+        <v>6.37</v>
       </c>
       <c r="H26" s="4">
-        <v>20769.650000000001</v>
+        <v>71885.83</v>
       </c>
       <c r="I26">
-        <v>4.25</v>
+        <v>4.03</v>
       </c>
       <c r="J26">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="K26">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="L26">
-        <v>94.38</v>
+        <v>96.86</v>
       </c>
       <c r="M26">
-        <v>-2.2000000000000002</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1775,37 +1784,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>302500</v>
+        <v>15370</v>
       </c>
       <c r="D27" s="3">
-        <v>0.14149999999999999</v>
+        <v>-1.9E-3</v>
       </c>
       <c r="E27">
-        <v>4.66</v>
+        <v>6.01</v>
       </c>
       <c r="F27">
-        <v>4.66</v>
+        <v>6.01</v>
       </c>
       <c r="G27">
-        <v>4.88</v>
+        <v>5.97</v>
       </c>
       <c r="H27" s="4">
-        <v>324173.33</v>
+        <v>20769.650000000001</v>
       </c>
       <c r="I27">
-        <v>1.75</v>
+        <v>4.29</v>
       </c>
       <c r="J27">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="K27">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="L27">
-        <v>123.87</v>
+        <v>93.48</v>
       </c>
       <c r="M27">
-        <v>36.26</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1816,37 +1825,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>176300</v>
+        <v>300000</v>
       </c>
       <c r="D28" s="3">
-        <v>-1.84E-2</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="E28">
-        <v>11.77</v>
+        <v>4.66</v>
       </c>
       <c r="F28">
-        <v>11.77</v>
+        <v>4.66</v>
       </c>
       <c r="G28">
-        <v>11.4</v>
+        <v>4.88</v>
       </c>
       <c r="H28" s="4">
-        <v>85735.74</v>
+        <v>324173.33</v>
       </c>
       <c r="I28">
-        <v>3.4</v>
+        <v>1.77</v>
       </c>
       <c r="J28">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K28">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L28">
-        <v>104.85</v>
+        <v>121.16</v>
       </c>
       <c r="M28">
-        <v>13.96</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1857,37 +1866,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>16440</v>
+        <v>176700</v>
       </c>
       <c r="D29" s="3">
-        <v>-3.0099999999999998E-2</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="E29">
-        <v>8.11</v>
+        <v>11.77</v>
       </c>
       <c r="F29">
-        <v>8.11</v>
+        <v>11.77</v>
       </c>
       <c r="G29">
-        <v>9.93</v>
+        <v>11.4</v>
       </c>
       <c r="H29" s="4">
-        <v>19583.27</v>
+        <v>85735.74</v>
       </c>
       <c r="I29">
-        <v>5.78</v>
+        <v>3.4</v>
       </c>
       <c r="J29">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="K29">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L29">
-        <v>97.24</v>
+        <v>104.67</v>
       </c>
       <c r="M29">
-        <v>-0.3</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1898,37 +1907,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>37900</v>
+        <v>16300</v>
       </c>
       <c r="D30" s="3">
-        <v>-1.8100000000000002E-2</v>
+        <v>-6.7000000000000002E-3</v>
       </c>
       <c r="E30">
-        <v>1.23</v>
+        <v>8.11</v>
       </c>
       <c r="F30">
-        <v>1.23</v>
+        <v>8.11</v>
       </c>
       <c r="G30">
-        <v>1.59</v>
+        <v>9.93</v>
       </c>
       <c r="H30" s="4">
-        <v>118301.94</v>
+        <v>19583.27</v>
       </c>
       <c r="I30">
-        <v>3.04</v>
+        <v>5.83</v>
       </c>
       <c r="J30">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="K30">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="L30">
-        <v>103.13</v>
+        <v>96.55</v>
       </c>
       <c r="M30">
-        <v>8.91</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1939,37 +1948,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>97600</v>
+        <v>38450</v>
       </c>
       <c r="D31" s="3">
-        <v>-4.1000000000000003E-3</v>
+        <v>1.5900000000000001E-2</v>
       </c>
       <c r="E31">
-        <v>8.7200000000000006</v>
+        <v>1.23</v>
       </c>
       <c r="F31">
-        <v>8.7200000000000006</v>
+        <v>1.23</v>
       </c>
       <c r="G31">
-        <v>8.4</v>
+        <v>1.59</v>
       </c>
       <c r="H31" s="4">
-        <v>120617.68</v>
+        <v>118301.94</v>
       </c>
       <c r="I31">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="J31">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="K31">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="L31">
-        <v>100.41</v>
+        <v>104.24</v>
       </c>
       <c r="M31">
-        <v>6.78</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1980,37 +1989,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>285500</v>
+        <v>98900</v>
       </c>
       <c r="D32" s="3">
-        <v>8.9700000000000002E-2</v>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="E32">
-        <v>18.66</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="F32">
-        <v>18.66</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="G32">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="H32" s="4">
-        <v>195836.08</v>
+        <v>120617.68</v>
       </c>
       <c r="I32">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="J32">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K32">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L32">
-        <v>116.64</v>
+        <v>101.29</v>
       </c>
       <c r="M32">
-        <v>34.04</v>
+        <v>2.2799999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2021,37 +2030,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>76900</v>
+        <v>276000</v>
       </c>
       <c r="D33" s="3">
-        <v>-4.9399999999999999E-2</v>
+        <v>-5.3199999999999997E-2</v>
       </c>
       <c r="E33">
-        <v>5.55</v>
+        <v>18.66</v>
       </c>
       <c r="F33">
-        <v>5.55</v>
+        <v>18.66</v>
       </c>
       <c r="G33">
-        <v>6.57</v>
+        <v>13</v>
       </c>
       <c r="H33" s="4">
-        <v>155269.29999999999</v>
+        <v>195836.08</v>
       </c>
       <c r="I33">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="J33">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K33">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L33">
-        <v>106.79</v>
+        <v>111.31</v>
       </c>
       <c r="M33">
-        <v>19.04</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2062,37 +2071,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>126200</v>
+        <v>78600</v>
       </c>
       <c r="D34" s="3">
-        <v>-3.2000000000000002E-3</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="E34">
-        <v>9.17</v>
+        <v>5.55</v>
       </c>
       <c r="F34">
-        <v>9.17</v>
+        <v>5.55</v>
       </c>
       <c r="G34">
-        <v>9.1</v>
+        <v>6.57</v>
       </c>
       <c r="H34" s="4">
-        <v>162088.94</v>
+        <v>155269.29999999999</v>
       </c>
       <c r="I34">
-        <v>3.25</v>
+        <v>3.82</v>
       </c>
       <c r="J34">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K34">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L34">
-        <v>105.42</v>
+        <v>108.26</v>
       </c>
       <c r="M34">
-        <v>13.49</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2103,37 +2112,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>160400</v>
+        <v>128800</v>
       </c>
       <c r="D35" s="3">
-        <v>1.6500000000000001E-2</v>
+        <v>2.63E-2</v>
       </c>
       <c r="E35">
-        <v>9.98</v>
+        <v>9.17</v>
       </c>
       <c r="F35">
-        <v>9.98</v>
+        <v>9.17</v>
       </c>
       <c r="G35">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="H35" s="4">
-        <v>159779.29999999999</v>
+        <v>162088.94</v>
       </c>
       <c r="I35">
-        <v>2.72</v>
+        <v>3.19</v>
       </c>
       <c r="J35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L35">
-        <v>103.08</v>
+        <v>106.82</v>
       </c>
       <c r="M35">
-        <v>9.34</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2144,37 +2153,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>18180</v>
+        <v>161200</v>
       </c>
       <c r="D36" s="3">
-        <v>-1.1000000000000001E-3</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="E36">
-        <v>7.58</v>
+        <v>9.98</v>
       </c>
       <c r="F36">
-        <v>7.58</v>
+        <v>9.98</v>
       </c>
       <c r="G36">
-        <v>6.97</v>
+        <v>9.08</v>
       </c>
       <c r="H36" s="4">
-        <v>34779.699999999997</v>
+        <v>159779.29999999999</v>
       </c>
       <c r="I36">
-        <v>4.04</v>
+        <v>2.71</v>
       </c>
       <c r="J36">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K36">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="L36">
-        <v>98.76</v>
+        <v>103.12</v>
       </c>
       <c r="M36">
-        <v>4.9000000000000004</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2185,37 +2194,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>19020</v>
+        <v>18200</v>
       </c>
       <c r="D37" s="3">
-        <v>-1.4500000000000001E-2</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="E37">
-        <v>7.27</v>
+        <v>7.58</v>
       </c>
       <c r="F37">
-        <v>7.27</v>
+        <v>7.58</v>
       </c>
       <c r="G37">
-        <v>5.87</v>
+        <v>6.97</v>
       </c>
       <c r="H37" s="4">
-        <v>38724.660000000003</v>
+        <v>34779.699999999997</v>
       </c>
       <c r="I37">
-        <v>3.68</v>
+        <v>4.04</v>
       </c>
       <c r="J37">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K37">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="L37">
-        <v>104.59</v>
+        <v>98.81</v>
       </c>
       <c r="M37">
-        <v>14.72</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2226,37 +2235,37 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>59600</v>
+        <v>19250</v>
       </c>
       <c r="D38" s="3">
-        <v>-3.09E-2</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="E38">
-        <v>9.39</v>
+        <v>7.27</v>
       </c>
       <c r="F38">
-        <v>9.39</v>
+        <v>7.27</v>
       </c>
       <c r="G38">
-        <v>9.34</v>
+        <v>5.87</v>
       </c>
       <c r="H38" s="4">
-        <v>98085.37</v>
+        <v>38724.660000000003</v>
       </c>
       <c r="I38">
-        <v>3.86</v>
+        <v>3.64</v>
       </c>
       <c r="J38">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="K38">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="L38">
-        <v>99.73</v>
+        <v>105.27</v>
       </c>
       <c r="M38">
-        <v>11.82</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2267,37 +2276,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>26750</v>
+        <v>64700</v>
       </c>
       <c r="D39" s="3">
-        <v>-2.1899999999999999E-2</v>
+        <v>8.7400000000000005E-2</v>
       </c>
       <c r="E39">
-        <v>12.36</v>
+        <v>9.39</v>
       </c>
       <c r="F39">
-        <v>12.36</v>
+        <v>9.39</v>
       </c>
       <c r="G39">
-        <v>12.46</v>
+        <v>9.34</v>
       </c>
       <c r="H39" s="4">
-        <v>31515.31</v>
+        <v>98085.37</v>
       </c>
       <c r="I39">
-        <v>4.26</v>
+        <v>3.55</v>
       </c>
       <c r="J39">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="K39">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="L39">
-        <v>90.6</v>
+        <v>107.51</v>
       </c>
       <c r="M39">
-        <v>-7.76</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2308,37 +2317,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>11370</v>
+        <v>26350</v>
       </c>
       <c r="D40" s="3">
-        <v>-2.4899999999999999E-2</v>
+        <v>-7.4999999999999997E-3</v>
       </c>
       <c r="E40">
-        <v>1.55</v>
+        <v>12.36</v>
       </c>
       <c r="F40">
-        <v>1.55</v>
+        <v>12.36</v>
       </c>
       <c r="G40">
-        <v>6.05</v>
+        <v>12.46</v>
       </c>
       <c r="H40" s="4">
-        <v>29736.69</v>
+        <v>31515.31</v>
       </c>
       <c r="I40">
-        <v>2.2000000000000002</v>
+        <v>4.33</v>
       </c>
       <c r="J40">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="K40">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="L40">
-        <v>100.03</v>
+        <v>89.68</v>
       </c>
       <c r="M40">
-        <v>8.6</v>
+        <v>-13.75</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2349,37 +2358,37 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>59700</v>
+        <v>11550</v>
       </c>
       <c r="D41" s="3">
-        <v>-2.6100000000000002E-2</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="E41">
-        <v>11.33</v>
+        <v>1.55</v>
       </c>
       <c r="F41">
-        <v>11.33</v>
+        <v>1.55</v>
       </c>
       <c r="G41">
-        <v>16.21</v>
+        <v>6.05</v>
       </c>
       <c r="H41" s="4">
-        <v>59573.64</v>
+        <v>29736.69</v>
       </c>
       <c r="I41">
-        <v>2.0099999999999998</v>
+        <v>2.16</v>
       </c>
       <c r="J41">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="K41">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="L41">
-        <v>112.67</v>
+        <v>101.21</v>
       </c>
       <c r="M41">
-        <v>24.63</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2390,37 +2399,37 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>19330</v>
+        <v>59000</v>
       </c>
       <c r="D42" s="3">
-        <v>-1.38E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="E42">
-        <v>8.8800000000000008</v>
+        <v>11.33</v>
       </c>
       <c r="F42">
-        <v>8.8800000000000008</v>
+        <v>11.33</v>
       </c>
       <c r="G42">
-        <v>10.31</v>
+        <v>16.21</v>
       </c>
       <c r="H42" s="4">
-        <v>26617.85</v>
+        <v>59573.64</v>
       </c>
       <c r="I42">
-        <v>6.08</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J42">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="K42">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="L42">
-        <v>103.65</v>
+        <v>110.64</v>
       </c>
       <c r="M42">
-        <v>9.6999999999999993</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2431,37 +2440,78 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>32800</v>
+        <v>19650</v>
       </c>
       <c r="D43" s="3">
-        <v>-1.4999999999999999E-2</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="E43">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="F43">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="G43">
+        <v>10.31</v>
+      </c>
+      <c r="H43" s="4">
+        <v>26617.85</v>
+      </c>
+      <c r="I43">
+        <v>5.98</v>
+      </c>
+      <c r="J43">
+        <v>19</v>
+      </c>
+      <c r="K43">
+        <v>19</v>
+      </c>
+      <c r="L43">
+        <v>105</v>
+      </c>
+      <c r="M43">
+        <v>10.02</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="2">
+        <v>33200</v>
+      </c>
+      <c r="D44" s="3">
+        <v>1.84E-2</v>
+      </c>
+      <c r="E44">
         <v>8.91</v>
       </c>
-      <c r="F43">
+      <c r="F44">
         <v>8.91</v>
       </c>
-      <c r="G43">
+      <c r="G44">
         <v>8.8699999999999992</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H44" s="4">
         <v>49113.23</v>
       </c>
-      <c r="I43">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="J43">
-        <v>72</v>
-      </c>
-      <c r="K43">
-        <v>72</v>
-      </c>
-      <c r="L43">
-        <v>96.94</v>
-      </c>
-      <c r="M43">
-        <v>2.98</v>
+      <c r="I44">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J44">
+        <v>73</v>
+      </c>
+      <c r="K44">
+        <v>73</v>
+      </c>
+      <c r="L44">
+        <v>98.02</v>
+      </c>
+      <c r="M44">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
